--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -2756,16 +2756,16 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>10382665</v>
+        <v>12157665</v>
       </c>
       <c r="N15" t="n">
-        <v>14081687</v>
+        <v>15856687</v>
       </c>
       <c r="O15" t="n">
-        <v>15353862</v>
+        <v>17128862</v>
       </c>
       <c r="P15" t="n">
-        <v>73677636</v>
+        <v>75452636</v>
       </c>
       <c r="Q15" t="n">
         <v>6968509</v>
@@ -2780,16 +2780,16 @@
         <v>20893849</v>
       </c>
       <c r="U15" t="n">
-        <v>2135000</v>
+        <v>3910000</v>
       </c>
       <c r="V15" t="n">
-        <v>16005479</v>
+        <v>17780479</v>
       </c>
       <c r="W15" t="n">
-        <v>30159510</v>
+        <v>31934510</v>
       </c>
       <c r="X15" t="n">
-        <v>48341024</v>
+        <v>50116024</v>
       </c>
       <c r="Y15" t="n">
         <v>1279156</v>
@@ -6570,16 +6570,16 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>-1268957</v>
+        <v>-1121547</v>
       </c>
       <c r="N39" t="n">
-        <v>-1612961</v>
+        <v>-1465551</v>
       </c>
       <c r="O39" t="n">
-        <v>229471</v>
+        <v>376881</v>
       </c>
       <c r="P39" t="n">
-        <v>-26611906</v>
+        <v>-26464496</v>
       </c>
       <c r="Q39" t="n">
         <v>-1741460</v>
@@ -6594,16 +6594,16 @@
         <v>-11354606</v>
       </c>
       <c r="U39" t="n">
-        <v>183000</v>
+        <v>330410</v>
       </c>
       <c r="V39" t="n">
-        <v>869617</v>
+        <v>1017027</v>
       </c>
       <c r="W39" t="n">
-        <v>808617</v>
+        <v>956027</v>
       </c>
       <c r="X39" t="n">
-        <v>-13730943</v>
+        <v>-13583533</v>
       </c>
       <c r="Y39" t="n">
         <v>289503</v>
@@ -7047,16 +7047,16 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>754872</v>
+        <v>729142</v>
       </c>
       <c r="N42" t="n">
-        <v>623232</v>
+        <v>597502</v>
       </c>
       <c r="O42" t="n">
-        <v>1748600</v>
+        <v>1722870</v>
       </c>
       <c r="P42" t="n">
-        <v>8316689</v>
+        <v>8290959</v>
       </c>
       <c r="Q42" t="n">
         <v>997028</v>
@@ -7071,16 +7071,16 @@
         <v>5840022</v>
       </c>
       <c r="U42" t="n">
-        <v>-457422</v>
+        <v>-483152</v>
       </c>
       <c r="V42" t="n">
-        <v>-370385</v>
+        <v>-396115</v>
       </c>
       <c r="W42" t="n">
-        <v>-206888</v>
+        <v>-232618</v>
       </c>
       <c r="X42" t="n">
-        <v>1872465</v>
+        <v>1846735</v>
       </c>
       <c r="Y42" t="n">
         <v>215266</v>
@@ -8319,16 +8319,16 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>1685439</v>
+        <v>1650439</v>
       </c>
       <c r="N50" t="n">
-        <v>-194928</v>
+        <v>-229928</v>
       </c>
       <c r="O50" t="n">
-        <v>-1285174</v>
+        <v>-1320174</v>
       </c>
       <c r="P50" t="n">
-        <v>-8688966</v>
+        <v>-8723966</v>
       </c>
       <c r="Q50" t="n">
         <v>1779283</v>
@@ -8343,16 +8343,16 @@
         <v>-10956111</v>
       </c>
       <c r="U50" t="n">
-        <v>334000</v>
+        <v>299000</v>
       </c>
       <c r="V50" t="n">
-        <v>735000</v>
+        <v>700000</v>
       </c>
       <c r="W50" t="n">
-        <v>727406</v>
+        <v>692406</v>
       </c>
       <c r="X50" t="n">
-        <v>2621802</v>
+        <v>2586802</v>
       </c>
       <c r="Y50" t="n">
         <v>-427844</v>
@@ -13519,12 +13519,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2498.TW</t>
+          <t>8028.TW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -13533,28 +13533,28 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>40.2</v>
+        <v>233</v>
       </c>
       <c r="E83" t="n">
-        <v>39.89</v>
+        <v>227.2</v>
       </c>
       <c r="F83" t="n">
-        <v>40.44</v>
+        <v>233.35</v>
       </c>
       <c r="G83" t="n">
-        <v>40.54</v>
+        <v>239.65</v>
       </c>
       <c r="H83" t="n">
-        <v>3120072</v>
+        <v>3815963</v>
       </c>
       <c r="I83" t="n">
-        <v>2275002</v>
+        <v>2975215</v>
       </c>
       <c r="J83" t="n">
-        <v>43.3</v>
+        <v>256</v>
       </c>
       <c r="K83" t="n">
-        <v>39.2</v>
+        <v>216.5</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -13562,52 +13562,52 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>577897</v>
+        <v>184684</v>
       </c>
       <c r="N83" t="n">
-        <v>-5854</v>
+        <v>-847501</v>
       </c>
       <c r="O83" t="n">
-        <v>-390500</v>
+        <v>-2423676</v>
       </c>
       <c r="P83" t="n">
-        <v>-5094141</v>
+        <v>-5700000</v>
       </c>
       <c r="Q83" t="n">
-        <v>330849</v>
+        <v>-1447130</v>
       </c>
       <c r="R83" t="n">
-        <v>-208514</v>
+        <v>-3294271</v>
       </c>
       <c r="S83" t="n">
-        <v>-525919</v>
+        <v>-4887144</v>
       </c>
       <c r="T83" t="n">
-        <v>-4817211</v>
+        <v>-8893544</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1590000</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>2409000</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>2444000</v>
       </c>
       <c r="X83" t="n">
-        <v>-8000</v>
+        <v>3288000</v>
       </c>
       <c r="Y83" t="n">
-        <v>247048</v>
+        <v>41814</v>
       </c>
       <c r="Z83" t="n">
-        <v>202660</v>
+        <v>37770</v>
       </c>
       <c r="AA83" t="n">
-        <v>135419</v>
+        <v>19468</v>
       </c>
       <c r="AB83" t="n">
-        <v>-268930</v>
+        <v>-94456</v>
       </c>
       <c r="AC83" t="n">
         <v>-10</v>
@@ -13616,37 +13616,37 @@
         <v>-10</v>
       </c>
       <c r="AE83" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AF83" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>-30</v>
+        <v>-40</v>
       </c>
       <c r="AI83" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AJ83" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="AK83" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AL83" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -13661,17 +13661,17 @@
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>5日法人賣超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -13996,12 +13996,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>2498.TW</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -14010,28 +14010,28 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>14.15</v>
+        <v>40.2</v>
       </c>
       <c r="E86" t="n">
-        <v>14.09</v>
+        <v>39.89</v>
       </c>
       <c r="F86" t="n">
-        <v>14.16</v>
+        <v>40.44</v>
       </c>
       <c r="G86" t="n">
-        <v>14.21</v>
+        <v>40.54</v>
       </c>
       <c r="H86" t="n">
-        <v>16856838</v>
+        <v>3120072</v>
       </c>
       <c r="I86" t="n">
-        <v>22268621</v>
+        <v>2275002</v>
       </c>
       <c r="J86" t="n">
-        <v>15.15</v>
+        <v>43.3</v>
       </c>
       <c r="K86" t="n">
-        <v>13.6</v>
+        <v>39.2</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -14039,28 +14039,28 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>6093855</v>
+        <v>577897</v>
       </c>
       <c r="N86" t="n">
-        <v>4885111</v>
+        <v>-5854</v>
       </c>
       <c r="O86" t="n">
-        <v>-13388801</v>
+        <v>-390500</v>
       </c>
       <c r="P86" t="n">
-        <v>-11050586</v>
+        <v>-5094141</v>
       </c>
       <c r="Q86" t="n">
-        <v>5426269</v>
+        <v>330849</v>
       </c>
       <c r="R86" t="n">
-        <v>4589889</v>
+        <v>-208514</v>
       </c>
       <c r="S86" t="n">
-        <v>-13292258</v>
+        <v>-525919</v>
       </c>
       <c r="T86" t="n">
-        <v>-11251835</v>
+        <v>-4817211</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -14072,58 +14072,58 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="Y86" t="n">
-        <v>667586</v>
+        <v>247048</v>
       </c>
       <c r="Z86" t="n">
-        <v>295222</v>
+        <v>202660</v>
       </c>
       <c r="AA86" t="n">
-        <v>-96543</v>
+        <v>135419</v>
       </c>
       <c r="AB86" t="n">
-        <v>201249</v>
+        <v>-268930</v>
       </c>
       <c r="AC86" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AD86" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AE86" t="n">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="AF86" t="n">
-        <v>-15</v>
+        <v>-20</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>-34</v>
+        <v>-30</v>
       </c>
       <c r="AI86" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ86" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="AK86" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AL86" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -14138,29 +14138,29 @@
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超</t>
+          <t>5日法人賣超</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6275.TWO</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -14169,28 +14169,28 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>44.85</v>
+        <v>14.15</v>
       </c>
       <c r="E87" t="n">
-        <v>45.12</v>
+        <v>14.09</v>
       </c>
       <c r="F87" t="n">
-        <v>45.61</v>
+        <v>14.16</v>
       </c>
       <c r="G87" t="n">
-        <v>45.41</v>
+        <v>14.21</v>
       </c>
       <c r="H87" t="n">
-        <v>78000</v>
+        <v>16856838</v>
       </c>
       <c r="I87" t="n">
-        <v>94000</v>
+        <v>22268621</v>
       </c>
       <c r="J87" t="n">
-        <v>48.9</v>
+        <v>15.15</v>
       </c>
       <c r="K87" t="n">
-        <v>43.65</v>
+        <v>13.6</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -14198,28 +14198,28 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>6093855</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4885111</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>-13388801</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>-11050586</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>5426269</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>4589889</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>-13292258</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>-11251835</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -14234,16 +14234,16 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>667586</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>295222</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>-96543</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>201249</v>
       </c>
       <c r="AC87" t="n">
         <v>-12</v>
@@ -14252,37 +14252,37 @@
         <v>-12</v>
       </c>
       <c r="AE87" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>-12</v>
+        <v>-34</v>
       </c>
       <c r="AI87" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="AK87" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL87" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -14297,29 +14297,29 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>6275.TWO</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -14328,28 +14328,28 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>48.7</v>
+        <v>44.85</v>
       </c>
       <c r="E88" t="n">
-        <v>48.04</v>
+        <v>45.12</v>
       </c>
       <c r="F88" t="n">
-        <v>48.57</v>
+        <v>45.61</v>
       </c>
       <c r="G88" t="n">
-        <v>47.97</v>
+        <v>45.41</v>
       </c>
       <c r="H88" t="n">
-        <v>99548905</v>
+        <v>78000</v>
       </c>
       <c r="I88" t="n">
-        <v>114045705</v>
+        <v>94000</v>
       </c>
       <c r="J88" t="n">
-        <v>52.4</v>
+        <v>48.9</v>
       </c>
       <c r="K88" t="n">
-        <v>44.95</v>
+        <v>43.65</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -14357,52 +14357,52 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>26953397</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>19366389</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>-35408266</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>55520787</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>20867981</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>14432255</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>-34510244</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>51643681</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>4900</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>-111028</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>-396154</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>6082416</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>4929234</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>-786994</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>4273260</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>-12</v>
@@ -14411,35 +14411,37 @@
         <v>-12</v>
       </c>
       <c r="AE88" t="n">
-        <v>20</v>
+        <v>-30</v>
       </c>
       <c r="AF88" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AI88" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AJ88" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>0</v>
+      </c>
       <c r="AK88" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL88" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -14454,29 +14456,29 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2362.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>藍天</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -14485,28 +14487,28 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>47</v>
+        <v>48.7</v>
       </c>
       <c r="E89" t="n">
-        <v>46.93</v>
+        <v>48.04</v>
       </c>
       <c r="F89" t="n">
-        <v>47.5</v>
+        <v>48.57</v>
       </c>
       <c r="G89" t="n">
-        <v>47.84</v>
+        <v>47.97</v>
       </c>
       <c r="H89" t="n">
-        <v>358490</v>
+        <v>99548905</v>
       </c>
       <c r="I89" t="n">
-        <v>515193</v>
+        <v>114045705</v>
       </c>
       <c r="J89" t="n">
-        <v>49.9</v>
+        <v>52.4</v>
       </c>
       <c r="K89" t="n">
-        <v>46.25</v>
+        <v>44.95</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -14514,91 +14516,89 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>30308</v>
+        <v>26953397</v>
       </c>
       <c r="N89" t="n">
-        <v>-116003</v>
+        <v>19366389</v>
       </c>
       <c r="O89" t="n">
-        <v>-410392</v>
+        <v>-35408266</v>
       </c>
       <c r="P89" t="n">
-        <v>-353753</v>
+        <v>55520787</v>
       </c>
       <c r="Q89" t="n">
-        <v>35211</v>
+        <v>20867981</v>
       </c>
       <c r="R89" t="n">
-        <v>-115907</v>
+        <v>14432255</v>
       </c>
       <c r="S89" t="n">
-        <v>-403100</v>
+        <v>-34510244</v>
       </c>
       <c r="T89" t="n">
-        <v>-352589</v>
+        <v>51643681</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>-111028</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>-396154</v>
       </c>
       <c r="Y89" t="n">
-        <v>-4903</v>
+        <v>6082416</v>
       </c>
       <c r="Z89" t="n">
-        <v>-96</v>
+        <v>4929234</v>
       </c>
       <c r="AA89" t="n">
-        <v>-7292</v>
+        <v>-786994</v>
       </c>
       <c r="AB89" t="n">
-        <v>-1164</v>
+        <v>4273260</v>
       </c>
       <c r="AC89" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AD89" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AE89" t="n">
-        <v>-15</v>
+        <v>20</v>
       </c>
       <c r="AF89" t="n">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>-36</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
-        <v>22</v>
-      </c>
-      <c r="AJ89" t="n">
-        <v>61.11</v>
-      </c>
+        <v>-12</v>
+      </c>
+      <c r="AJ89" t="inlineStr"/>
       <c r="AK89" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AL89" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -14613,29 +14613,29 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>5日法人賣超</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>2362.TW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>藍天</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -14644,28 +14644,28 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>663</v>
+        <v>47</v>
       </c>
       <c r="E90" t="n">
-        <v>666.2</v>
+        <v>46.93</v>
       </c>
       <c r="F90" t="n">
-        <v>702.8</v>
+        <v>47.5</v>
       </c>
       <c r="G90" t="n">
-        <v>730.95</v>
+        <v>47.84</v>
       </c>
       <c r="H90" t="n">
-        <v>2048000</v>
+        <v>358490</v>
       </c>
       <c r="I90" t="n">
-        <v>1630200</v>
+        <v>515193</v>
       </c>
       <c r="J90" t="n">
-        <v>814</v>
+        <v>49.9</v>
       </c>
       <c r="K90" t="n">
-        <v>631</v>
+        <v>46.25</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -14673,28 +14673,28 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>30308</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>-116003</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>-410392</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>-353753</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>35211</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>-115907</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>-403100</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>-352589</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -14709,16 +14709,16 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>-4903</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>-96</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>-7292</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>-1164</v>
       </c>
       <c r="AC90" t="n">
         <v>-14</v>
@@ -14727,37 +14727,37 @@
         <v>-14</v>
       </c>
       <c r="AE90" t="n">
-        <v>-35</v>
+        <v>-15</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>-22</v>
+        <v>-36</v>
       </c>
       <c r="AI90" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AJ90" t="n">
-        <v>36.36</v>
+        <v>61.11</v>
       </c>
       <c r="AK90" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="AL90" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -14772,29 +14772,29 @@
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人賣超</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -14803,28 +14803,28 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710</v>
+        <v>663</v>
       </c>
       <c r="E91" t="n">
-        <v>1659</v>
+        <v>666.2</v>
       </c>
       <c r="F91" t="n">
-        <v>1733</v>
+        <v>702.8</v>
       </c>
       <c r="G91" t="n">
-        <v>1752.75</v>
+        <v>730.95</v>
       </c>
       <c r="H91" t="n">
-        <v>10673726</v>
+        <v>2048000</v>
       </c>
       <c r="I91" t="n">
-        <v>14272122</v>
+        <v>1630200</v>
       </c>
       <c r="J91" t="n">
-        <v>1885</v>
+        <v>814</v>
       </c>
       <c r="K91" t="n">
-        <v>1560</v>
+        <v>631</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -14832,91 +14832,91 @@
         </is>
       </c>
       <c r="M91" t="n">
-        <v>-571318</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>908777</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>-14199939</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>-10577853</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>-844243</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1310676</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>-10969822</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>-7109015</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>546888</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>-495960</v>
+        <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>-2694443</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>-3249403</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>-273963</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>94061</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>-535674</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>-219435</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AD91" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AE91" t="n">
-        <v>-5</v>
+        <v>-35</v>
       </c>
       <c r="AF91" t="n">
-        <v>-35</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>-34</v>
+        <v>-22</v>
       </c>
       <c r="AI91" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="AK91" t="n">
         <v>18</v>
       </c>
-      <c r="AJ91" t="n">
-        <v>52.94</v>
-      </c>
-      <c r="AK91" t="n">
-        <v>45</v>
-      </c>
       <c r="AL91" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -14931,17 +14931,17 @@
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15266,12 +15266,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1718.TW</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>中纖</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -15280,28 +15280,28 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.5</v>
+        <v>1710</v>
       </c>
       <c r="E94" t="n">
-        <v>10.49</v>
+        <v>1659</v>
       </c>
       <c r="F94" t="n">
-        <v>10.54</v>
+        <v>1733</v>
       </c>
       <c r="G94" t="n">
-        <v>10.64</v>
+        <v>1752.75</v>
       </c>
       <c r="H94" t="n">
-        <v>6566522</v>
+        <v>10673726</v>
       </c>
       <c r="I94" t="n">
-        <v>9562776</v>
+        <v>14272122</v>
       </c>
       <c r="J94" t="n">
-        <v>11.95</v>
+        <v>1885</v>
       </c>
       <c r="K94" t="n">
-        <v>10.2</v>
+        <v>1560</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -15309,91 +15309,91 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>1412080</v>
+        <v>-566318</v>
       </c>
       <c r="N94" t="n">
-        <v>3763377</v>
+        <v>913777</v>
       </c>
       <c r="O94" t="n">
-        <v>-622530</v>
+        <v>-14194939</v>
       </c>
       <c r="P94" t="n">
-        <v>4655722</v>
+        <v>-10572853</v>
       </c>
       <c r="Q94" t="n">
-        <v>1213977</v>
+        <v>-844243</v>
       </c>
       <c r="R94" t="n">
-        <v>3697418</v>
+        <v>1310676</v>
       </c>
       <c r="S94" t="n">
-        <v>-601588</v>
+        <v>-10969822</v>
       </c>
       <c r="T94" t="n">
-        <v>4937717</v>
+        <v>-7109015</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>551888</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>-490960</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>-2689443</v>
       </c>
       <c r="X94" t="n">
-        <v>-65000</v>
+        <v>-3244403</v>
       </c>
       <c r="Y94" t="n">
-        <v>198103</v>
+        <v>-273963</v>
       </c>
       <c r="Z94" t="n">
-        <v>65959</v>
+        <v>94061</v>
       </c>
       <c r="AA94" t="n">
-        <v>-20942</v>
+        <v>-535674</v>
       </c>
       <c r="AB94" t="n">
-        <v>-216995</v>
+        <v>-219435</v>
       </c>
       <c r="AC94" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="AD94" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="AE94" t="n">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="AF94" t="n">
-        <v>-30</v>
+        <v>-35</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>-10</v>
+        <v>-34</v>
       </c>
       <c r="AI94" t="n">
-        <v>-8</v>
+        <v>18</v>
       </c>
       <c r="AJ94" t="n">
-        <v>-80</v>
+        <v>52.94</v>
       </c>
       <c r="AK94" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AL94" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -15408,17 +15408,17 @@
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15584,12 +15584,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1303.TW</t>
+          <t>1718.TW</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>中纖</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -15598,28 +15598,28 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>224</v>
+        <v>10.5</v>
       </c>
       <c r="E96" t="n">
-        <v>231.6</v>
+        <v>10.49</v>
       </c>
       <c r="F96" t="n">
-        <v>230.65</v>
+        <v>10.54</v>
       </c>
       <c r="G96" t="n">
-        <v>221.12</v>
+        <v>10.64</v>
       </c>
       <c r="H96" t="n">
-        <v>48008257</v>
+        <v>6566522</v>
       </c>
       <c r="I96" t="n">
-        <v>53361085</v>
+        <v>9562776</v>
       </c>
       <c r="J96" t="n">
-        <v>250</v>
+        <v>11.95</v>
       </c>
       <c r="K96" t="n">
-        <v>174</v>
+        <v>10.2</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -15627,76 +15627,76 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>-3809309</v>
+        <v>1412080</v>
       </c>
       <c r="N96" t="n">
-        <v>-22645671</v>
+        <v>3763377</v>
       </c>
       <c r="O96" t="n">
-        <v>-26959115</v>
+        <v>-622530</v>
       </c>
       <c r="P96" t="n">
-        <v>-37504582</v>
+        <v>4655722</v>
       </c>
       <c r="Q96" t="n">
-        <v>-6798444</v>
+        <v>1213977</v>
       </c>
       <c r="R96" t="n">
-        <v>-27265035</v>
+        <v>3697418</v>
       </c>
       <c r="S96" t="n">
-        <v>-33056760</v>
+        <v>-601588</v>
       </c>
       <c r="T96" t="n">
-        <v>-51665789</v>
+        <v>4937717</v>
       </c>
       <c r="U96" t="n">
-        <v>2714701</v>
+        <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>5618279</v>
+        <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>7877859</v>
+        <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>17968822</v>
+        <v>-65000</v>
       </c>
       <c r="Y96" t="n">
-        <v>274434</v>
+        <v>198103</v>
       </c>
       <c r="Z96" t="n">
-        <v>-998915</v>
+        <v>65959</v>
       </c>
       <c r="AA96" t="n">
-        <v>-1780214</v>
+        <v>-20942</v>
       </c>
       <c r="AB96" t="n">
-        <v>-3807615</v>
+        <v>-216995</v>
       </c>
       <c r="AC96" t="n">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="AD96" t="n">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="AE96" t="n">
-        <v>5</v>
+        <v>-15</v>
       </c>
       <c r="AF96" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="AI96" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AJ96" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="AK96" t="n">
         <v>20</v>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -15726,29 +15726,29 @@
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8028.TW</t>
+          <t>1303.TW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -15757,28 +15757,28 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E97" t="n">
-        <v>227.2</v>
+        <v>231.6</v>
       </c>
       <c r="F97" t="n">
-        <v>233.35</v>
+        <v>230.65</v>
       </c>
       <c r="G97" t="n">
-        <v>239.65</v>
+        <v>221.12</v>
       </c>
       <c r="H97" t="n">
-        <v>3815963</v>
+        <v>48008257</v>
       </c>
       <c r="I97" t="n">
-        <v>2975215</v>
+        <v>53361085</v>
       </c>
       <c r="J97" t="n">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="K97" t="n">
-        <v>216.5</v>
+        <v>174</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -15786,52 +15786,52 @@
         </is>
       </c>
       <c r="M97" t="n">
-        <v>-1407316</v>
+        <v>-3809309</v>
       </c>
       <c r="N97" t="n">
-        <v>-2439501</v>
+        <v>-22645671</v>
       </c>
       <c r="O97" t="n">
-        <v>-4015676</v>
+        <v>-26959115</v>
       </c>
       <c r="P97" t="n">
-        <v>-7292000</v>
+        <v>-37504582</v>
       </c>
       <c r="Q97" t="n">
-        <v>-1447130</v>
+        <v>-6798444</v>
       </c>
       <c r="R97" t="n">
-        <v>-3294271</v>
+        <v>-27265035</v>
       </c>
       <c r="S97" t="n">
-        <v>-4887144</v>
+        <v>-33056760</v>
       </c>
       <c r="T97" t="n">
-        <v>-8893544</v>
+        <v>-51665789</v>
       </c>
       <c r="U97" t="n">
-        <v>-2000</v>
+        <v>2714701</v>
       </c>
       <c r="V97" t="n">
-        <v>817000</v>
+        <v>5618279</v>
       </c>
       <c r="W97" t="n">
-        <v>852000</v>
+        <v>7877859</v>
       </c>
       <c r="X97" t="n">
-        <v>1696000</v>
+        <v>17968822</v>
       </c>
       <c r="Y97" t="n">
-        <v>41814</v>
+        <v>274434</v>
       </c>
       <c r="Z97" t="n">
-        <v>37770</v>
+        <v>-998915</v>
       </c>
       <c r="AA97" t="n">
-        <v>19468</v>
+        <v>-1780214</v>
       </c>
       <c r="AB97" t="n">
-        <v>-94456</v>
+        <v>-3807615</v>
       </c>
       <c r="AC97" t="n">
         <v>-20</v>
@@ -15849,28 +15849,28 @@
         <v>0</v>
       </c>
       <c r="AH97" t="n">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="AI97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK97" t="n">
         <v>20</v>
       </c>
-      <c r="AJ97" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK97" t="n">
-        <v>55</v>
-      </c>
       <c r="AL97" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -19443,16 +19443,16 @@
         </is>
       </c>
       <c r="M120" t="n">
-        <v>-1782085</v>
+        <v>-1728375</v>
       </c>
       <c r="N120" t="n">
-        <v>-1363213</v>
+        <v>-1309503</v>
       </c>
       <c r="O120" t="n">
-        <v>-784287</v>
+        <v>-730577</v>
       </c>
       <c r="P120" t="n">
-        <v>5893017</v>
+        <v>5946727</v>
       </c>
       <c r="Q120" t="n">
         <v>-1483357</v>
@@ -19467,16 +19467,16 @@
         <v>6662166</v>
       </c>
       <c r="U120" t="n">
-        <v>-118000</v>
+        <v>-64290</v>
       </c>
       <c r="V120" t="n">
-        <v>-184000</v>
+        <v>-130290</v>
       </c>
       <c r="W120" t="n">
-        <v>-227000</v>
+        <v>-173290</v>
       </c>
       <c r="X120" t="n">
-        <v>-358200</v>
+        <v>-304490</v>
       </c>
       <c r="Y120" t="n">
         <v>-180728</v>
@@ -19602,16 +19602,16 @@
         </is>
       </c>
       <c r="M121" t="n">
-        <v>-627291</v>
+        <v>-636351</v>
       </c>
       <c r="N121" t="n">
-        <v>-1014141</v>
+        <v>-1023201</v>
       </c>
       <c r="O121" t="n">
-        <v>-1465152</v>
+        <v>-1474212</v>
       </c>
       <c r="P121" t="n">
-        <v>-3595388</v>
+        <v>-3604448</v>
       </c>
       <c r="Q121" t="n">
         <v>-349215</v>
@@ -19626,16 +19626,16 @@
         <v>-3650</v>
       </c>
       <c r="U121" t="n">
-        <v>-260000</v>
+        <v>-269060</v>
       </c>
       <c r="V121" t="n">
-        <v>-1133640</v>
+        <v>-1142700</v>
       </c>
       <c r="W121" t="n">
-        <v>-2350126</v>
+        <v>-2359186</v>
       </c>
       <c r="X121" t="n">
-        <v>-2890703</v>
+        <v>-2899763</v>
       </c>
       <c r="Y121" t="n">
         <v>-18076</v>
@@ -22303,16 +22303,16 @@
         </is>
       </c>
       <c r="M138" t="n">
-        <v>-6391165</v>
+        <v>-6070165</v>
       </c>
       <c r="N138" t="n">
-        <v>-2815955</v>
+        <v>-2494955</v>
       </c>
       <c r="O138" t="n">
-        <v>-10024427</v>
+        <v>-9703427</v>
       </c>
       <c r="P138" t="n">
-        <v>4532834</v>
+        <v>4853834</v>
       </c>
       <c r="Q138" t="n">
         <v>-6396915</v>
@@ -22327,16 +22327,16 @@
         <v>4870528</v>
       </c>
       <c r="U138" t="n">
-        <v>357020</v>
+        <v>678020</v>
       </c>
       <c r="V138" t="n">
-        <v>1294022</v>
+        <v>1615022</v>
       </c>
       <c r="W138" t="n">
-        <v>1643029</v>
+        <v>1964029</v>
       </c>
       <c r="X138" t="n">
-        <v>-67944</v>
+        <v>253056</v>
       </c>
       <c r="Y138" t="n">
         <v>-351270</v>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>32404147</v>
+        <v>40430147</v>
       </c>
       <c r="N2" t="n">
-        <v>30050500</v>
+        <v>38076500</v>
       </c>
       <c r="O2" t="n">
-        <v>48286138</v>
+        <v>56312138</v>
       </c>
       <c r="P2" t="n">
-        <v>92032663</v>
+        <v>100058663</v>
       </c>
       <c r="Q2" t="n">
         <v>8951822</v>
@@ -713,16 +713,16 @@
         <v>7824173</v>
       </c>
       <c r="U2" t="n">
-        <v>19883000</v>
+        <v>27909000</v>
       </c>
       <c r="V2" t="n">
-        <v>33282479</v>
+        <v>41308479</v>
       </c>
       <c r="W2" t="n">
-        <v>39299704</v>
+        <v>47325704</v>
       </c>
       <c r="X2" t="n">
-        <v>78975024</v>
+        <v>87001024</v>
       </c>
       <c r="Y2" t="n">
         <v>3569325</v>
@@ -2273,16 +2273,16 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>12196060</v>
+        <v>12662060</v>
       </c>
       <c r="N12" t="n">
-        <v>22153422</v>
+        <v>22619422</v>
       </c>
       <c r="O12" t="n">
-        <v>24434077</v>
+        <v>24900077</v>
       </c>
       <c r="P12" t="n">
-        <v>46274637</v>
+        <v>46740637</v>
       </c>
       <c r="Q12" t="n">
         <v>3450313</v>
@@ -2297,16 +2297,16 @@
         <v>-17309541</v>
       </c>
       <c r="U12" t="n">
-        <v>8219000</v>
+        <v>8685000</v>
       </c>
       <c r="V12" t="n">
-        <v>20629000</v>
+        <v>21095000</v>
       </c>
       <c r="W12" t="n">
-        <v>26529362</v>
+        <v>26995362</v>
       </c>
       <c r="X12" t="n">
-        <v>62401010</v>
+        <v>62867010</v>
       </c>
       <c r="Y12" t="n">
         <v>526747</v>
@@ -7952,12 +7952,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1514.TW</t>
+          <t>1612.TW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>宏泰</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7966,81 +7966,81 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>101</v>
+        <v>34.95</v>
       </c>
       <c r="E48" t="n">
-        <v>100.18</v>
+        <v>34.77</v>
       </c>
       <c r="F48" t="n">
-        <v>101.29</v>
+        <v>34.81</v>
       </c>
       <c r="G48" t="n">
-        <v>101.92</v>
+        <v>34.85</v>
       </c>
       <c r="H48" t="n">
-        <v>758306</v>
+        <v>1069242</v>
       </c>
       <c r="I48" t="n">
-        <v>833376</v>
+        <v>452717</v>
       </c>
       <c r="J48" t="n">
-        <v>111.5</v>
+        <v>35.9</v>
       </c>
       <c r="K48" t="n">
-        <v>99.2</v>
+        <v>34.3</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>413780</v>
+        <v>98439</v>
       </c>
       <c r="N48" t="n">
-        <v>126213</v>
+        <v>112364</v>
       </c>
       <c r="O48" t="n">
-        <v>77843</v>
+        <v>272546</v>
       </c>
       <c r="P48" t="n">
-        <v>1171842</v>
+        <v>943788</v>
       </c>
       <c r="Q48" t="n">
-        <v>411456</v>
+        <v>96012</v>
       </c>
       <c r="R48" t="n">
-        <v>198520</v>
+        <v>95311</v>
       </c>
       <c r="S48" t="n">
-        <v>142063</v>
+        <v>211311</v>
       </c>
       <c r="T48" t="n">
-        <v>1064209</v>
+        <v>910221</v>
       </c>
       <c r="U48" t="n">
-        <v>-679</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>-28679</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1321</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>180321</v>
+        <v>-13678</v>
       </c>
       <c r="Y48" t="n">
-        <v>3003</v>
+        <v>2427</v>
       </c>
       <c r="Z48" t="n">
-        <v>-43628</v>
+        <v>17053</v>
       </c>
       <c r="AA48" t="n">
-        <v>-65541</v>
+        <v>61235</v>
       </c>
       <c r="AB48" t="n">
-        <v>-72688</v>
+        <v>47245</v>
       </c>
       <c r="AC48" t="n">
         <v>18</v>
@@ -8049,37 +8049,37 @@
         <v>18</v>
       </c>
       <c r="AE48" t="n">
-        <v>-15</v>
+        <v>5</v>
       </c>
       <c r="AF48" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AH48" t="n">
-        <v>-54</v>
+        <v>2</v>
       </c>
       <c r="AI48" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="AJ48" t="n">
-        <v>133.33</v>
+        <v>800</v>
       </c>
       <c r="AK48" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="AL48" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、量能偏強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -8094,29 +8094,29 @@
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、爆量、接近20日低點、爆量價未漲</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人小幅買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、爆量、接近20日低點、爆量價未漲、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2731.TW</t>
+          <t>1514.TW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>雄獅</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8125,28 +8125,28 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="E49" t="n">
-        <v>141.5</v>
+        <v>100.18</v>
       </c>
       <c r="F49" t="n">
-        <v>142.25</v>
+        <v>101.29</v>
       </c>
       <c r="G49" t="n">
-        <v>143.43</v>
+        <v>101.92</v>
       </c>
       <c r="H49" t="n">
-        <v>368125</v>
+        <v>758306</v>
       </c>
       <c r="I49" t="n">
-        <v>271258</v>
+        <v>833376</v>
       </c>
       <c r="J49" t="n">
-        <v>147.5</v>
+        <v>111.5</v>
       </c>
       <c r="K49" t="n">
-        <v>139</v>
+        <v>99.2</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -8154,52 +8154,52 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>81395</v>
+        <v>413780</v>
       </c>
       <c r="N49" t="n">
-        <v>81101</v>
+        <v>126213</v>
       </c>
       <c r="O49" t="n">
-        <v>31991</v>
+        <v>77843</v>
       </c>
       <c r="P49" t="n">
-        <v>-136801</v>
+        <v>1171842</v>
       </c>
       <c r="Q49" t="n">
-        <v>80396</v>
+        <v>411456</v>
       </c>
       <c r="R49" t="n">
-        <v>87396</v>
+        <v>198520</v>
       </c>
       <c r="S49" t="n">
-        <v>29398</v>
+        <v>142063</v>
       </c>
       <c r="T49" t="n">
-        <v>-146278</v>
+        <v>1064209</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>-679</v>
       </c>
       <c r="V49" t="n">
-        <v>-5440</v>
+        <v>-28679</v>
       </c>
       <c r="W49" t="n">
-        <v>1475</v>
+        <v>1321</v>
       </c>
       <c r="X49" t="n">
-        <v>3781</v>
+        <v>180321</v>
       </c>
       <c r="Y49" t="n">
-        <v>999</v>
+        <v>3003</v>
       </c>
       <c r="Z49" t="n">
-        <v>-855</v>
+        <v>-43628</v>
       </c>
       <c r="AA49" t="n">
-        <v>1118</v>
+        <v>-65541</v>
       </c>
       <c r="AB49" t="n">
-        <v>5696</v>
+        <v>-72688</v>
       </c>
       <c r="AC49" t="n">
         <v>18</v>
@@ -8208,37 +8208,37 @@
         <v>18</v>
       </c>
       <c r="AE49" t="n">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="AF49" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>-36</v>
+        <v>-54</v>
       </c>
       <c r="AI49" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="AJ49" t="n">
-        <v>150</v>
+        <v>133.33</v>
       </c>
       <c r="AK49" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="AL49" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -8253,17 +8253,17 @@
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>法人連續偏買、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人小幅買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人小幅買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -8429,12 +8429,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3545.TW</t>
+          <t>2731.TW</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>敦泰</t>
+          <t>雄獅</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -8443,28 +8443,28 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>50.5</v>
+        <v>144</v>
       </c>
       <c r="E51" t="n">
-        <v>49.28</v>
+        <v>141.5</v>
       </c>
       <c r="F51" t="n">
-        <v>49.96</v>
+        <v>142.25</v>
       </c>
       <c r="G51" t="n">
-        <v>50.03</v>
+        <v>143.43</v>
       </c>
       <c r="H51" t="n">
-        <v>490007</v>
+        <v>368125</v>
       </c>
       <c r="I51" t="n">
-        <v>509422</v>
+        <v>271258</v>
       </c>
       <c r="J51" t="n">
-        <v>52.8</v>
+        <v>147.5</v>
       </c>
       <c r="K51" t="n">
-        <v>47.7</v>
+        <v>139</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -8472,52 +8472,52 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>277199</v>
+        <v>81395</v>
       </c>
       <c r="N51" t="n">
-        <v>359717</v>
+        <v>81101</v>
       </c>
       <c r="O51" t="n">
-        <v>396070</v>
+        <v>31991</v>
       </c>
       <c r="P51" t="n">
-        <v>470365</v>
+        <v>-136801</v>
       </c>
       <c r="Q51" t="n">
-        <v>274199</v>
+        <v>80396</v>
       </c>
       <c r="R51" t="n">
-        <v>358796</v>
+        <v>87396</v>
       </c>
       <c r="S51" t="n">
-        <v>420796</v>
+        <v>29398</v>
       </c>
       <c r="T51" t="n">
-        <v>486171</v>
+        <v>-146278</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>-5440</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1475</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>3781</v>
       </c>
       <c r="Y51" t="n">
-        <v>3000</v>
+        <v>999</v>
       </c>
       <c r="Z51" t="n">
-        <v>921</v>
+        <v>-855</v>
       </c>
       <c r="AA51" t="n">
-        <v>-24726</v>
+        <v>1118</v>
       </c>
       <c r="AB51" t="n">
-        <v>-15806</v>
+        <v>5696</v>
       </c>
       <c r="AC51" t="n">
         <v>18</v>
@@ -8535,28 +8535,28 @@
         <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>6</v>
+        <v>-36</v>
       </c>
       <c r="AI51" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="AJ51" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AK51" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL51" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8571,29 +8571,29 @@
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>法人連續偏買、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1612.TW</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>宏泰</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -8602,57 +8602,57 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>34.95</v>
+        <v>386.5</v>
       </c>
       <c r="E52" t="n">
-        <v>34.77</v>
+        <v>375.8</v>
       </c>
       <c r="F52" t="n">
-        <v>34.81</v>
+        <v>366.2</v>
       </c>
       <c r="G52" t="n">
-        <v>34.85</v>
+        <v>368.9</v>
       </c>
       <c r="H52" t="n">
-        <v>1069242</v>
+        <v>4690000</v>
       </c>
       <c r="I52" t="n">
-        <v>452717</v>
+        <v>9925800</v>
       </c>
       <c r="J52" t="n">
-        <v>35.9</v>
+        <v>419</v>
       </c>
       <c r="K52" t="n">
-        <v>34.3</v>
+        <v>304</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>98439</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>112364</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>272546</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>943788</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>96012</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>95311</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>211311</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>910221</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -8664,19 +8664,19 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>-13678</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2427</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>17053</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>61235</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>47245</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>18</v>
@@ -8685,22 +8685,22 @@
         <v>18</v>
       </c>
       <c r="AE52" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ52" t="n">
         <v>50</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>800</v>
       </c>
       <c r="AK52" t="n">
         <v>48</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、量能偏強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8730,29 +8730,29 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、爆量、接近20日低點、爆量價未漲</t>
+          <t>站上5日線、黃金交叉、量能未放大</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、爆量、接近20日低點、爆量價未漲、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、黃金交叉、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>3443.TW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -8761,28 +8761,28 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1065</v>
+        <v>6500</v>
       </c>
       <c r="E53" t="n">
-        <v>1078</v>
+        <v>6245</v>
       </c>
       <c r="F53" t="n">
-        <v>1070</v>
+        <v>6108</v>
       </c>
       <c r="G53" t="n">
-        <v>1129</v>
+        <v>5973.25</v>
       </c>
       <c r="H53" t="n">
-        <v>8133171</v>
+        <v>2334082</v>
       </c>
       <c r="I53" t="n">
-        <v>7263900</v>
+        <v>1983791</v>
       </c>
       <c r="J53" t="n">
-        <v>1335</v>
+        <v>6610</v>
       </c>
       <c r="K53" t="n">
-        <v>1010</v>
+        <v>5205</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -8790,91 +8790,91 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>-1134820</v>
+        <v>7607</v>
       </c>
       <c r="N53" t="n">
-        <v>-417717</v>
+        <v>-106208</v>
       </c>
       <c r="O53" t="n">
-        <v>1146131</v>
+        <v>-14403</v>
       </c>
       <c r="P53" t="n">
-        <v>2989142</v>
+        <v>128408</v>
       </c>
       <c r="Q53" t="n">
-        <v>-1303101</v>
+        <v>-410128</v>
       </c>
       <c r="R53" t="n">
-        <v>-705087</v>
+        <v>-622113</v>
       </c>
       <c r="S53" t="n">
-        <v>693972</v>
+        <v>-835460</v>
       </c>
       <c r="T53" t="n">
-        <v>5984035</v>
+        <v>-657182</v>
       </c>
       <c r="U53" t="n">
-        <v>115000</v>
+        <v>430200</v>
       </c>
       <c r="V53" t="n">
-        <v>273000</v>
+        <v>564500</v>
       </c>
       <c r="W53" t="n">
-        <v>231000</v>
+        <v>984778</v>
       </c>
       <c r="X53" t="n">
-        <v>-2914275</v>
+        <v>1072732</v>
       </c>
       <c r="Y53" t="n">
-        <v>53281</v>
+        <v>-12465</v>
       </c>
       <c r="Z53" t="n">
-        <v>14370</v>
+        <v>-48595</v>
       </c>
       <c r="AA53" t="n">
-        <v>221159</v>
+        <v>-163721</v>
       </c>
       <c r="AB53" t="n">
-        <v>-80618</v>
+        <v>-287142</v>
       </c>
       <c r="AC53" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD53" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE53" t="n">
-        <v>-10</v>
+        <v>70</v>
       </c>
       <c r="AF53" t="n">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="AI53" t="n">
-        <v>-16</v>
+        <v>8</v>
       </c>
       <c r="AJ53" t="n">
-        <v>-50</v>
+        <v>80</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、分數剛升溫</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -8889,29 +8889,29 @@
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>中期買超轉短線賣壓、投信買外資賣</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、中期買超轉短線賣壓、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2881.TW</t>
+          <t>3545.TW</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>敦泰</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -8920,28 +8920,28 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>151.5</v>
+        <v>50.5</v>
       </c>
       <c r="E54" t="n">
-        <v>151.6</v>
+        <v>49.28</v>
       </c>
       <c r="F54" t="n">
-        <v>150.25</v>
+        <v>49.96</v>
       </c>
       <c r="G54" t="n">
-        <v>145.68</v>
+        <v>50.03</v>
       </c>
       <c r="H54" t="n">
-        <v>14045882</v>
+        <v>490007</v>
       </c>
       <c r="I54" t="n">
-        <v>16080882</v>
+        <v>509422</v>
       </c>
       <c r="J54" t="n">
-        <v>155.5</v>
+        <v>52.8</v>
       </c>
       <c r="K54" t="n">
-        <v>127.5</v>
+        <v>47.7</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -8949,91 +8949,91 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>384035</v>
+        <v>277199</v>
       </c>
       <c r="N54" t="n">
-        <v>-1020888</v>
+        <v>359717</v>
       </c>
       <c r="O54" t="n">
-        <v>4033984</v>
+        <v>396070</v>
       </c>
       <c r="P54" t="n">
-        <v>6053099</v>
+        <v>470365</v>
       </c>
       <c r="Q54" t="n">
-        <v>2286403</v>
+        <v>274199</v>
       </c>
       <c r="R54" t="n">
-        <v>-7308398</v>
+        <v>358796</v>
       </c>
       <c r="S54" t="n">
-        <v>-2951431</v>
+        <v>420796</v>
       </c>
       <c r="T54" t="n">
-        <v>-328330</v>
+        <v>486171</v>
       </c>
       <c r="U54" t="n">
-        <v>-1395000</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>6412960</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>6921122</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>6693628</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>-507368</v>
+        <v>3000</v>
       </c>
       <c r="Z54" t="n">
-        <v>-125450</v>
+        <v>921</v>
       </c>
       <c r="AA54" t="n">
-        <v>64293</v>
+        <v>-24726</v>
       </c>
       <c r="AB54" t="n">
-        <v>-312199</v>
+        <v>-15806</v>
       </c>
       <c r="AC54" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AD54" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE54" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AF54" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="AI54" t="n">
-        <v>-38</v>
+        <v>12</v>
       </c>
       <c r="AJ54" t="n">
-        <v>-73.08</v>
+        <v>200</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -9048,29 +9048,29 @@
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -9079,28 +9079,28 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1385</v>
+        <v>1065</v>
       </c>
       <c r="E55" t="n">
-        <v>1334</v>
+        <v>1078</v>
       </c>
       <c r="F55" t="n">
-        <v>1376</v>
+        <v>1070</v>
       </c>
       <c r="G55" t="n">
-        <v>1274.7</v>
+        <v>1129</v>
       </c>
       <c r="H55" t="n">
-        <v>6498000</v>
+        <v>8133171</v>
       </c>
       <c r="I55" t="n">
-        <v>3534600</v>
+        <v>7263900</v>
       </c>
       <c r="J55" t="n">
-        <v>1505</v>
+        <v>1335</v>
       </c>
       <c r="K55" t="n">
-        <v>965</v>
+        <v>1010</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -9108,82 +9108,82 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>-1134820</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>-417717</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1146131</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2989142</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>-1303101</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>-705087</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>693972</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>5984035</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>115000</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>273000</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>-2914275</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>53281</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>14370</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>221159</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>-80618</v>
       </c>
       <c r="AC55" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD55" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE55" t="n">
-        <v>35</v>
+        <v>-10</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AI55" t="n">
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="AJ55" t="n">
-        <v>-12.5</v>
+        <v>-50</v>
       </c>
       <c r="AK55" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -9207,29 +9207,29 @@
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>2881.TW</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -9238,28 +9238,28 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4500</v>
+        <v>151.5</v>
       </c>
       <c r="E56" t="n">
-        <v>4521</v>
+        <v>151.6</v>
       </c>
       <c r="F56" t="n">
-        <v>4583.5</v>
+        <v>150.25</v>
       </c>
       <c r="G56" t="n">
-        <v>4288.75</v>
+        <v>145.68</v>
       </c>
       <c r="H56" t="n">
-        <v>6495763</v>
+        <v>14045882</v>
       </c>
       <c r="I56" t="n">
-        <v>6612052</v>
+        <v>16080882</v>
       </c>
       <c r="J56" t="n">
-        <v>4855</v>
+        <v>155.5</v>
       </c>
       <c r="K56" t="n">
-        <v>3655</v>
+        <v>127.5</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -9267,76 +9267,76 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>341611</v>
+        <v>384035</v>
       </c>
       <c r="N56" t="n">
-        <v>87041</v>
+        <v>-1020888</v>
       </c>
       <c r="O56" t="n">
-        <v>283318</v>
+        <v>4033984</v>
       </c>
       <c r="P56" t="n">
-        <v>6944857</v>
+        <v>6053099</v>
       </c>
       <c r="Q56" t="n">
-        <v>300476</v>
+        <v>2286403</v>
       </c>
       <c r="R56" t="n">
-        <v>297505</v>
+        <v>-7308398</v>
       </c>
       <c r="S56" t="n">
-        <v>290258</v>
+        <v>-2951431</v>
       </c>
       <c r="T56" t="n">
-        <v>4968107</v>
+        <v>-328330</v>
       </c>
       <c r="U56" t="n">
-        <v>-40815</v>
+        <v>-1395000</v>
       </c>
       <c r="V56" t="n">
-        <v>-543024</v>
+        <v>6412960</v>
       </c>
       <c r="W56" t="n">
-        <v>-328908</v>
+        <v>6921122</v>
       </c>
       <c r="X56" t="n">
-        <v>1350865</v>
+        <v>6693628</v>
       </c>
       <c r="Y56" t="n">
-        <v>81950</v>
+        <v>-507368</v>
       </c>
       <c r="Z56" t="n">
-        <v>332560</v>
+        <v>-125450</v>
       </c>
       <c r="AA56" t="n">
-        <v>321968</v>
+        <v>64293</v>
       </c>
       <c r="AB56" t="n">
-        <v>625885</v>
+        <v>-312199</v>
       </c>
       <c r="AC56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE56" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="AF56" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="AI56" t="n">
-        <v>-4</v>
+        <v>-38</v>
       </c>
       <c r="AJ56" t="n">
-        <v>-25</v>
+        <v>-73.08</v>
       </c>
       <c r="AK56" t="n">
         <v>0</v>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -9366,29 +9366,29 @@
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9397,28 +9397,28 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>238</v>
+        <v>1385</v>
       </c>
       <c r="E57" t="n">
-        <v>233.1</v>
+        <v>1334</v>
       </c>
       <c r="F57" t="n">
-        <v>233.15</v>
+        <v>1376</v>
       </c>
       <c r="G57" t="n">
-        <v>210.93</v>
+        <v>1274.7</v>
       </c>
       <c r="H57" t="n">
-        <v>10332000</v>
+        <v>6498000</v>
       </c>
       <c r="I57" t="n">
-        <v>7951600</v>
+        <v>3534600</v>
       </c>
       <c r="J57" t="n">
-        <v>265</v>
+        <v>1505</v>
       </c>
       <c r="K57" t="n">
-        <v>140</v>
+        <v>965</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -9474,13 +9474,13 @@
         <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD57" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE57" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AF57" t="n">
         <v>0</v>
@@ -9489,28 +9489,28 @@
         <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AI57" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="AJ57" t="n">
-        <v>-45.45</v>
+        <v>-12.5</v>
       </c>
       <c r="AK57" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="AL57" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
@@ -9535,19 +9535,19 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6191.TW</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -9556,28 +9556,28 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>82.2</v>
+        <v>4500</v>
       </c>
       <c r="E58" t="n">
-        <v>82.04000000000001</v>
+        <v>4521</v>
       </c>
       <c r="F58" t="n">
-        <v>82.23</v>
+        <v>4583.5</v>
       </c>
       <c r="G58" t="n">
-        <v>82.45</v>
+        <v>4288.75</v>
       </c>
       <c r="H58" t="n">
-        <v>1747762</v>
+        <v>6495763</v>
       </c>
       <c r="I58" t="n">
-        <v>1101454</v>
+        <v>6612052</v>
       </c>
       <c r="J58" t="n">
-        <v>85.8</v>
+        <v>4855</v>
       </c>
       <c r="K58" t="n">
-        <v>79.2</v>
+        <v>3655</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -9585,52 +9585,52 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-166686</v>
+        <v>419611</v>
       </c>
       <c r="N58" t="n">
-        <v>233681</v>
+        <v>165041</v>
       </c>
       <c r="O58" t="n">
-        <v>711133</v>
+        <v>361318</v>
       </c>
       <c r="P58" t="n">
-        <v>1408033</v>
+        <v>7022857</v>
       </c>
       <c r="Q58" t="n">
-        <v>-189100</v>
+        <v>300476</v>
       </c>
       <c r="R58" t="n">
-        <v>302217</v>
+        <v>297505</v>
       </c>
       <c r="S58" t="n">
-        <v>749237</v>
+        <v>290258</v>
       </c>
       <c r="T58" t="n">
-        <v>1369822</v>
+        <v>4968107</v>
       </c>
       <c r="U58" t="n">
-        <v>13000</v>
+        <v>37185</v>
       </c>
       <c r="V58" t="n">
-        <v>-59000</v>
+        <v>-465024</v>
       </c>
       <c r="W58" t="n">
-        <v>-36000</v>
+        <v>-250908</v>
       </c>
       <c r="X58" t="n">
-        <v>38000</v>
+        <v>1428865</v>
       </c>
       <c r="Y58" t="n">
-        <v>9414</v>
+        <v>81950</v>
       </c>
       <c r="Z58" t="n">
-        <v>-9536</v>
+        <v>332560</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2104</v>
+        <v>321968</v>
       </c>
       <c r="AB58" t="n">
-        <v>211</v>
+        <v>625885</v>
       </c>
       <c r="AC58" t="n">
         <v>12</v>
@@ -9639,37 +9639,37 @@
         <v>12</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AF58" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AI58" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="AJ58" t="n">
-        <v>-45.45</v>
+        <v>-25</v>
       </c>
       <c r="AK58" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AL58" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9684,29 +9684,29 @@
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、成交量放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3443.TW</t>
+          <t>6191.TW</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9715,28 +9715,28 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6500</v>
+        <v>82.2</v>
       </c>
       <c r="E59" t="n">
-        <v>6245</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>6108</v>
+        <v>82.23</v>
       </c>
       <c r="G59" t="n">
-        <v>5973.25</v>
+        <v>82.45</v>
       </c>
       <c r="H59" t="n">
-        <v>2334082</v>
+        <v>1747762</v>
       </c>
       <c r="I59" t="n">
-        <v>1983791</v>
+        <v>1101454</v>
       </c>
       <c r="J59" t="n">
-        <v>6610</v>
+        <v>85.8</v>
       </c>
       <c r="K59" t="n">
-        <v>5205</v>
+        <v>79.2</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -9744,91 +9744,91 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>-290393</v>
+        <v>-166686</v>
       </c>
       <c r="N59" t="n">
-        <v>-404208</v>
+        <v>233681</v>
       </c>
       <c r="O59" t="n">
-        <v>-312403</v>
+        <v>711133</v>
       </c>
       <c r="P59" t="n">
-        <v>-169592</v>
+        <v>1408033</v>
       </c>
       <c r="Q59" t="n">
-        <v>-410128</v>
+        <v>-189100</v>
       </c>
       <c r="R59" t="n">
-        <v>-622113</v>
+        <v>302217</v>
       </c>
       <c r="S59" t="n">
-        <v>-835460</v>
+        <v>749237</v>
       </c>
       <c r="T59" t="n">
-        <v>-657182</v>
+        <v>1369822</v>
       </c>
       <c r="U59" t="n">
-        <v>132200</v>
+        <v>13000</v>
       </c>
       <c r="V59" t="n">
-        <v>266500</v>
+        <v>-59000</v>
       </c>
       <c r="W59" t="n">
-        <v>686778</v>
+        <v>-36000</v>
       </c>
       <c r="X59" t="n">
-        <v>774732</v>
+        <v>38000</v>
       </c>
       <c r="Y59" t="n">
-        <v>-12465</v>
+        <v>9414</v>
       </c>
       <c r="Z59" t="n">
-        <v>-48595</v>
+        <v>-9536</v>
       </c>
       <c r="AA59" t="n">
-        <v>-163721</v>
+        <v>-2104</v>
       </c>
       <c r="AB59" t="n">
-        <v>-287142</v>
+        <v>211</v>
       </c>
       <c r="AC59" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD59" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE59" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>-45</v>
+        <v>30</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>-45.45</v>
       </c>
       <c r="AK59" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AL59" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -9843,29 +9843,29 @@
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、空頭排列、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏賣、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、成交量放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2329.TW</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>華泰</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9874,28 +9874,28 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>42.9</v>
+        <v>238</v>
       </c>
       <c r="E60" t="n">
-        <v>42.05</v>
+        <v>233.1</v>
       </c>
       <c r="F60" t="n">
-        <v>42.4</v>
+        <v>233.15</v>
       </c>
       <c r="G60" t="n">
-        <v>42.95</v>
+        <v>210.93</v>
       </c>
       <c r="H60" t="n">
-        <v>2682148</v>
+        <v>10332000</v>
       </c>
       <c r="I60" t="n">
-        <v>1800751</v>
+        <v>7951600</v>
       </c>
       <c r="J60" t="n">
-        <v>45</v>
+        <v>265</v>
       </c>
       <c r="K60" t="n">
-        <v>40.9</v>
+        <v>140</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -9903,28 +9903,28 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-163503</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>620465</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>1193398</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1202014</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>-141151</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>581671</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>1233643</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>1211556</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -9939,28 +9939,28 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>-22352</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>38794</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>-40245</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>-9542</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE60" t="n">
-        <v>-5</v>
+        <v>30</v>
       </c>
       <c r="AF60" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -9969,10 +9969,10 @@
         <v>22</v>
       </c>
       <c r="AI60" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AJ60" t="n">
-        <v>-54.55</v>
+        <v>-45.45</v>
       </c>
       <c r="AK60" t="n">
         <v>45</v>
@@ -10002,29 +10002,29 @@
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6275.TWO</t>
+          <t>2329.TW</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>華泰</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -10033,28 +10033,28 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>45.15</v>
+        <v>42.9</v>
       </c>
       <c r="E61" t="n">
-        <v>45.05</v>
+        <v>42.05</v>
       </c>
       <c r="F61" t="n">
-        <v>45.61</v>
+        <v>42.4</v>
       </c>
       <c r="G61" t="n">
-        <v>45.46</v>
+        <v>42.95</v>
       </c>
       <c r="H61" t="n">
-        <v>125000</v>
+        <v>2682148</v>
       </c>
       <c r="I61" t="n">
-        <v>102200</v>
+        <v>1800751</v>
       </c>
       <c r="J61" t="n">
-        <v>48.9</v>
+        <v>45</v>
       </c>
       <c r="K61" t="n">
-        <v>43.65</v>
+        <v>40.9</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -10062,28 +10062,28 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>-163503</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>620465</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1193398</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1202014</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>-141151</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>581671</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>1233643</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>1211556</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>-22352</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>38794</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>-40245</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>-9542</v>
       </c>
       <c r="AC61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE61" t="n">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
       </c>
       <c r="AH61" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI61" t="n">
         <v>-12</v>
       </c>
-      <c r="AI61" t="n">
-        <v>20</v>
-      </c>
       <c r="AJ61" t="n">
-        <v>166.67</v>
+        <v>-54.55</v>
       </c>
       <c r="AK61" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AL61" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -10161,29 +10161,29 @@
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2421.TW</t>
+          <t>6275.TWO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -10192,28 +10192,28 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>162</v>
+        <v>45.15</v>
       </c>
       <c r="E62" t="n">
-        <v>161.6</v>
+        <v>45.05</v>
       </c>
       <c r="F62" t="n">
-        <v>165.8</v>
+        <v>45.61</v>
       </c>
       <c r="G62" t="n">
-        <v>162.57</v>
+        <v>45.46</v>
       </c>
       <c r="H62" t="n">
-        <v>2197326</v>
+        <v>125000</v>
       </c>
       <c r="I62" t="n">
-        <v>2197403</v>
+        <v>102200</v>
       </c>
       <c r="J62" t="n">
-        <v>184</v>
+        <v>48.9</v>
       </c>
       <c r="K62" t="n">
-        <v>140.5</v>
+        <v>43.65</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -10221,91 +10221,91 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>233314</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>-3733</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>236448</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>-1862857</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>182209</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>128495</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>591133</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>-1737461</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>-37000</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>-56000</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>-74000</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>51105</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>-95228</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>-298685</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>-51396</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE62" t="n">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AI62" t="n">
         <v>20</v>
       </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>-26</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>32</v>
-      </c>
       <c r="AJ62" t="n">
-        <v>123.08</v>
+        <v>166.67</v>
       </c>
       <c r="AK62" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AL62" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -10320,17 +10320,17 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>站上5日線、死亡交叉、量能未放大</t>
+          <t>站上5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、死亡交叉、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -10360,7 +10360,7 @@
         <v>545.7</v>
       </c>
       <c r="G63" t="n">
-        <v>559.05</v>
+        <v>562.25</v>
       </c>
       <c r="H63" t="n">
         <v>902000</v>
@@ -10369,7 +10369,7 @@
         <v>415400</v>
       </c>
       <c r="J63" t="n">
-        <v>599</v>
+        <v>619</v>
       </c>
       <c r="K63" t="n">
         <v>521</v>
@@ -10814,12 +10814,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2606.TW</t>
+          <t>2421.TW</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -10828,28 +10828,28 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>77</v>
+        <v>162</v>
       </c>
       <c r="E66" t="n">
-        <v>76.06</v>
+        <v>161.6</v>
       </c>
       <c r="F66" t="n">
-        <v>77.3</v>
+        <v>165.8</v>
       </c>
       <c r="G66" t="n">
-        <v>75.94</v>
+        <v>162.57</v>
       </c>
       <c r="H66" t="n">
-        <v>3653421</v>
+        <v>2197326</v>
       </c>
       <c r="I66" t="n">
-        <v>4381693</v>
+        <v>2197403</v>
       </c>
       <c r="J66" t="n">
-        <v>81.7</v>
+        <v>184</v>
       </c>
       <c r="K66" t="n">
-        <v>70</v>
+        <v>140.5</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -10857,91 +10857,91 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>222050</v>
+        <v>233314</v>
       </c>
       <c r="N66" t="n">
-        <v>471836</v>
+        <v>-3733</v>
       </c>
       <c r="O66" t="n">
-        <v>-63042</v>
+        <v>236448</v>
       </c>
       <c r="P66" t="n">
-        <v>1443020</v>
+        <v>-1862857</v>
       </c>
       <c r="Q66" t="n">
-        <v>-218115</v>
+        <v>182209</v>
       </c>
       <c r="R66" t="n">
-        <v>-957044</v>
+        <v>128495</v>
       </c>
       <c r="S66" t="n">
-        <v>-1263685</v>
+        <v>591133</v>
       </c>
       <c r="T66" t="n">
-        <v>453603</v>
+        <v>-1737461</v>
       </c>
       <c r="U66" t="n">
-        <v>324000</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>1455000</v>
+        <v>-37000</v>
       </c>
       <c r="W66" t="n">
-        <v>1455000</v>
+        <v>-56000</v>
       </c>
       <c r="X66" t="n">
-        <v>1489000</v>
+        <v>-74000</v>
       </c>
       <c r="Y66" t="n">
-        <v>116165</v>
+        <v>51105</v>
       </c>
       <c r="Z66" t="n">
-        <v>-26120</v>
+        <v>-95228</v>
       </c>
       <c r="AA66" t="n">
-        <v>-254357</v>
+        <v>-298685</v>
       </c>
       <c r="AB66" t="n">
-        <v>-499583</v>
+        <v>-51396</v>
       </c>
       <c r="AC66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE66" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF66" t="n">
         <v>20</v>
       </c>
-      <c r="AF66" t="n">
-        <v>-10</v>
-      </c>
       <c r="AG66" t="n">
         <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>16</v>
+        <v>-26</v>
       </c>
       <c r="AI66" t="n">
-        <v>-12</v>
+        <v>32</v>
       </c>
       <c r="AJ66" t="n">
-        <v>-75</v>
+        <v>123.08</v>
       </c>
       <c r="AK66" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AL66" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10956,29 +10956,29 @@
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、死亡交叉、量能未放大</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>5日法人小幅賣超、投信買外資賣</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、5日法人小幅賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、死亡交叉、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6230.TW</t>
+          <t>5530.TWO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>超眾</t>
+          <t>龍巖</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -10987,28 +10987,28 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>110.5</v>
+        <v>49.85</v>
       </c>
       <c r="E67" t="n">
-        <v>110.4</v>
+        <v>49.72</v>
       </c>
       <c r="F67" t="n">
-        <v>109.95</v>
+        <v>49.58</v>
       </c>
       <c r="G67" t="n">
-        <v>109.17</v>
+        <v>50.02</v>
       </c>
       <c r="H67" t="n">
-        <v>67734</v>
+        <v>63000</v>
       </c>
       <c r="I67" t="n">
-        <v>162979</v>
+        <v>115400</v>
       </c>
       <c r="J67" t="n">
-        <v>119</v>
+        <v>51.6</v>
       </c>
       <c r="K67" t="n">
-        <v>105.5</v>
+        <v>48.7</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -11016,28 +11016,28 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>13131</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>-28869</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>-12919</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>16223</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>12131</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>-29869</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>-13869</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>15119</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -11052,16 +11052,16 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1104</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>4</v>
@@ -11070,37 +11070,37 @@
         <v>4</v>
       </c>
       <c r="AE67" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AF67" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AI67" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ67" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="AK67" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL67" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -11115,29 +11115,29 @@
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日低點、中期買超轉短線賣壓。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5530.TWO</t>
+          <t>6230.TW</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>龍巖</t>
+          <t>超眾</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -11146,28 +11146,28 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>49.85</v>
+        <v>110.5</v>
       </c>
       <c r="E68" t="n">
-        <v>49.72</v>
+        <v>110.4</v>
       </c>
       <c r="F68" t="n">
-        <v>49.58</v>
+        <v>109.95</v>
       </c>
       <c r="G68" t="n">
-        <v>50.02</v>
+        <v>109.17</v>
       </c>
       <c r="H68" t="n">
-        <v>63000</v>
+        <v>67734</v>
       </c>
       <c r="I68" t="n">
-        <v>115400</v>
+        <v>162979</v>
       </c>
       <c r="J68" t="n">
-        <v>51.6</v>
+        <v>119</v>
       </c>
       <c r="K68" t="n">
-        <v>48.7</v>
+        <v>105.5</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -11175,28 +11175,28 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>13131</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>-28869</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>-12919</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>16223</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>12131</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>-29869</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>-13869</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>15119</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -11211,16 +11211,16 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1104</v>
       </c>
       <c r="AC68" t="n">
         <v>4</v>
@@ -11229,37 +11229,37 @@
         <v>4</v>
       </c>
       <c r="AE68" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI68" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="AK68" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL68" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -11274,29 +11274,29 @@
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>中期買超轉短線賣壓</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日低點、中期買超轉短線賣壓。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3231.TW</t>
+          <t>2606.TW</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -11305,28 +11305,28 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>186.5</v>
+        <v>77</v>
       </c>
       <c r="E69" t="n">
-        <v>183.7</v>
+        <v>76.06</v>
       </c>
       <c r="F69" t="n">
-        <v>187.4</v>
+        <v>77.3</v>
       </c>
       <c r="G69" t="n">
-        <v>183.85</v>
+        <v>75.94</v>
       </c>
       <c r="H69" t="n">
-        <v>31292426</v>
+        <v>3653421</v>
       </c>
       <c r="I69" t="n">
-        <v>32860103</v>
+        <v>4381693</v>
       </c>
       <c r="J69" t="n">
-        <v>200.5</v>
+        <v>81.7</v>
       </c>
       <c r="K69" t="n">
-        <v>172.5</v>
+        <v>70</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -11334,91 +11334,91 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>11571332</v>
+        <v>222050</v>
       </c>
       <c r="N69" t="n">
-        <v>1320974</v>
+        <v>471836</v>
       </c>
       <c r="O69" t="n">
-        <v>-8559657</v>
+        <v>-63042</v>
       </c>
       <c r="P69" t="n">
-        <v>-60169097</v>
+        <v>1443020</v>
       </c>
       <c r="Q69" t="n">
-        <v>8826396</v>
+        <v>-218115</v>
       </c>
       <c r="R69" t="n">
-        <v>-2553004</v>
+        <v>-957044</v>
       </c>
       <c r="S69" t="n">
-        <v>-12324778</v>
+        <v>-1263685</v>
       </c>
       <c r="T69" t="n">
-        <v>-72443795</v>
+        <v>453603</v>
       </c>
       <c r="U69" t="n">
-        <v>2001000</v>
+        <v>324000</v>
       </c>
       <c r="V69" t="n">
-        <v>4968000</v>
+        <v>1455000</v>
       </c>
       <c r="W69" t="n">
-        <v>5146852</v>
+        <v>1455000</v>
       </c>
       <c r="X69" t="n">
-        <v>12509991</v>
+        <v>1489000</v>
       </c>
       <c r="Y69" t="n">
-        <v>743936</v>
+        <v>116165</v>
       </c>
       <c r="Z69" t="n">
-        <v>-1094022</v>
+        <v>-26120</v>
       </c>
       <c r="AA69" t="n">
-        <v>-1381731</v>
+        <v>-254357</v>
       </c>
       <c r="AB69" t="n">
-        <v>-235293</v>
+        <v>-499583</v>
       </c>
       <c r="AC69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE69" t="n">
         <v>20</v>
       </c>
       <c r="AF69" t="n">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>-30</v>
+        <v>16</v>
       </c>
       <c r="AI69" t="n">
-        <v>32</v>
+        <v>-12</v>
       </c>
       <c r="AJ69" t="n">
-        <v>106.67</v>
+        <v>-75</v>
       </c>
       <c r="AK69" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AL69" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人小幅賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、5日法人小幅賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -11609,12 +11609,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>3231.TW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11623,28 +11623,28 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>48.8</v>
+        <v>186.5</v>
       </c>
       <c r="E71" t="n">
-        <v>48.27</v>
+        <v>183.7</v>
       </c>
       <c r="F71" t="n">
-        <v>44.34</v>
+        <v>187.4</v>
       </c>
       <c r="G71" t="n">
-        <v>41.64</v>
+        <v>183.85</v>
       </c>
       <c r="H71" t="n">
-        <v>56292754</v>
+        <v>31292426</v>
       </c>
       <c r="I71" t="n">
-        <v>47048857</v>
+        <v>32860103</v>
       </c>
       <c r="J71" t="n">
-        <v>54.5</v>
+        <v>200.5</v>
       </c>
       <c r="K71" t="n">
-        <v>37.15</v>
+        <v>172.5</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -11652,91 +11652,91 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>-355336</v>
+        <v>11571332</v>
       </c>
       <c r="N71" t="n">
-        <v>-2183470</v>
+        <v>1320974</v>
       </c>
       <c r="O71" t="n">
-        <v>-4434262</v>
+        <v>-8559657</v>
       </c>
       <c r="P71" t="n">
-        <v>-5218488</v>
+        <v>-60169097</v>
       </c>
       <c r="Q71" t="n">
-        <v>-39677</v>
+        <v>8826396</v>
       </c>
       <c r="R71" t="n">
-        <v>-2223388</v>
+        <v>-2553004</v>
       </c>
       <c r="S71" t="n">
-        <v>-4762432</v>
+        <v>-12324778</v>
       </c>
       <c r="T71" t="n">
-        <v>-5519785</v>
+        <v>-72443795</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>2001000</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>4968000</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>5146852</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>12509991</v>
       </c>
       <c r="Y71" t="n">
-        <v>-315659</v>
+        <v>743936</v>
       </c>
       <c r="Z71" t="n">
-        <v>39918</v>
+        <v>-1094022</v>
       </c>
       <c r="AA71" t="n">
-        <v>328170</v>
+        <v>-1381731</v>
       </c>
       <c r="AB71" t="n">
-        <v>301297</v>
+        <v>-235293</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE71" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="AF71" t="n">
-        <v>-55</v>
+        <v>-15</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
       <c r="AI71" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="AJ71" t="n">
-        <v>100</v>
+        <v>106.67</v>
       </c>
       <c r="AK71" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="AL71" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11751,29 +11751,29 @@
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -11782,28 +11782,28 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>233</v>
+        <v>48.8</v>
       </c>
       <c r="E72" t="n">
-        <v>231.9</v>
+        <v>48.27</v>
       </c>
       <c r="F72" t="n">
-        <v>239.6</v>
+        <v>44.34</v>
       </c>
       <c r="G72" t="n">
-        <v>248.78</v>
+        <v>41.64</v>
       </c>
       <c r="H72" t="n">
-        <v>3066000</v>
+        <v>56292754</v>
       </c>
       <c r="I72" t="n">
-        <v>2455800</v>
+        <v>47048857</v>
       </c>
       <c r="J72" t="n">
-        <v>288</v>
+        <v>54.5</v>
       </c>
       <c r="K72" t="n">
-        <v>223</v>
+        <v>37.15</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -11811,28 +11811,28 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>-355336</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>-2183470</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>-4434262</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>-5218488</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>-39677</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>-2223388</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>-4762432</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>-5519785</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -11847,55 +11847,55 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>-315659</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>39918</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>328170</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>301297</v>
       </c>
       <c r="AC72" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>-5</v>
+        <v>55</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="AL72" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11910,29 +11910,29 @@
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4979.TWO</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -11941,28 +11941,28 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>556</v>
+        <v>233</v>
       </c>
       <c r="E73" t="n">
-        <v>538</v>
+        <v>231.9</v>
       </c>
       <c r="F73" t="n">
-        <v>569.5</v>
+        <v>239.6</v>
       </c>
       <c r="G73" t="n">
-        <v>582.5</v>
+        <v>248.78</v>
       </c>
       <c r="H73" t="n">
-        <v>982000</v>
+        <v>3066000</v>
       </c>
       <c r="I73" t="n">
-        <v>1372800</v>
+        <v>2455800</v>
       </c>
       <c r="J73" t="n">
-        <v>658</v>
+        <v>288</v>
       </c>
       <c r="K73" t="n">
-        <v>501</v>
+        <v>223</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -12042,19 +12042,19 @@
         <v>0</v>
       </c>
       <c r="AK73" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="AL73" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
@@ -12079,19 +12079,19 @@
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>4979.TWO</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -12100,28 +12100,28 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>478.5</v>
+        <v>556</v>
       </c>
       <c r="E74" t="n">
-        <v>494.7</v>
+        <v>538</v>
       </c>
       <c r="F74" t="n">
-        <v>505.55</v>
+        <v>569.5</v>
       </c>
       <c r="G74" t="n">
-        <v>493.15</v>
+        <v>582.5</v>
       </c>
       <c r="H74" t="n">
-        <v>31177000</v>
+        <v>982000</v>
       </c>
       <c r="I74" t="n">
-        <v>25483800</v>
+        <v>1372800</v>
       </c>
       <c r="J74" t="n">
-        <v>564</v>
+        <v>658</v>
       </c>
       <c r="K74" t="n">
-        <v>399</v>
+        <v>501</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -12177,13 +12177,13 @@
         <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AD74" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AE74" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="AF74" t="n">
         <v>0</v>
@@ -12192,19 +12192,19 @@
         <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="AI74" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AJ74" t="n">
-        <v>-133.33</v>
+        <v>0</v>
       </c>
       <c r="AK74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AL74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
@@ -12238,19 +12238,19 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3363.TWO</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -12259,28 +12259,28 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>655</v>
+        <v>478.5</v>
       </c>
       <c r="E75" t="n">
-        <v>668.6</v>
+        <v>494.7</v>
       </c>
       <c r="F75" t="n">
-        <v>693.4</v>
+        <v>505.55</v>
       </c>
       <c r="G75" t="n">
-        <v>693.3</v>
+        <v>493.15</v>
       </c>
       <c r="H75" t="n">
-        <v>4183000</v>
+        <v>31177000</v>
       </c>
       <c r="I75" t="n">
-        <v>2945400</v>
+        <v>25483800</v>
       </c>
       <c r="J75" t="n">
-        <v>850</v>
+        <v>564</v>
       </c>
       <c r="K75" t="n">
-        <v>549</v>
+        <v>399</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -12360,10 +12360,10 @@
         <v>-133.33</v>
       </c>
       <c r="AK75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -12404,12 +12404,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4938.TW</t>
+          <t>3363.TWO</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -12418,28 +12418,28 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>90.40000000000001</v>
+        <v>655</v>
       </c>
       <c r="E76" t="n">
-        <v>89.78</v>
+        <v>668.6</v>
       </c>
       <c r="F76" t="n">
-        <v>91.17</v>
+        <v>693.4</v>
       </c>
       <c r="G76" t="n">
-        <v>90.48999999999999</v>
+        <v>693.3</v>
       </c>
       <c r="H76" t="n">
-        <v>7287528</v>
+        <v>4183000</v>
       </c>
       <c r="I76" t="n">
-        <v>6476242</v>
+        <v>2945400</v>
       </c>
       <c r="J76" t="n">
-        <v>95.59999999999999</v>
+        <v>850</v>
       </c>
       <c r="K76" t="n">
-        <v>87.3</v>
+        <v>549</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -12447,52 +12447,52 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>1576591</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>-1380462</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>-3213476</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>-2240446</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>1329003</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>-866501</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>-3638401</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>-10080783</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>294000</v>
+        <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>60845</v>
+        <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>379845</v>
+        <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>7767664</v>
+        <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>-46412</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>-574806</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>45080</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>72673</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>-4</v>
@@ -12501,37 +12501,37 @@
         <v>-4</v>
       </c>
       <c r="AE76" t="n">
-        <v>20</v>
+        <v>-10</v>
       </c>
       <c r="AF76" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>-30</v>
+        <v>12</v>
       </c>
       <c r="AI76" t="n">
-        <v>26</v>
+        <v>-16</v>
       </c>
       <c r="AJ76" t="n">
-        <v>86.67</v>
+        <v>-133.33</v>
       </c>
       <c r="AK76" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL76" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -12546,17 +12546,17 @@
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -12722,42 +12722,42 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>00878.TW</t>
+          <t>4938.TW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>34.73</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="E78" t="n">
-        <v>34.33</v>
+        <v>89.78</v>
       </c>
       <c r="F78" t="n">
-        <v>34.25</v>
+        <v>91.17</v>
       </c>
       <c r="G78" t="n">
-        <v>33.63</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>26931022</v>
+        <v>7287528</v>
       </c>
       <c r="I78" t="n">
-        <v>33329260</v>
+        <v>6476242</v>
       </c>
       <c r="J78" t="n">
-        <v>34.91</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>31.99</v>
+        <v>87.3</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -12765,82 +12765,82 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>10184608</v>
+        <v>1576591</v>
       </c>
       <c r="N78" t="n">
-        <v>-12744419</v>
+        <v>-1380462</v>
       </c>
       <c r="O78" t="n">
-        <v>-26384918</v>
+        <v>-3213476</v>
       </c>
       <c r="P78" t="n">
-        <v>28418963</v>
+        <v>-2240446</v>
       </c>
       <c r="Q78" t="n">
-        <v>3003312</v>
+        <v>1329003</v>
       </c>
       <c r="R78" t="n">
-        <v>-13111345</v>
+        <v>-866501</v>
       </c>
       <c r="S78" t="n">
-        <v>-28712633</v>
+        <v>-3638401</v>
       </c>
       <c r="T78" t="n">
-        <v>-17893162</v>
+        <v>-10080783</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>294000</v>
       </c>
       <c r="V78" t="n">
-        <v>-200000</v>
+        <v>60845</v>
       </c>
       <c r="W78" t="n">
-        <v>-200000</v>
+        <v>379845</v>
       </c>
       <c r="X78" t="n">
-        <v>-300000</v>
+        <v>7767664</v>
       </c>
       <c r="Y78" t="n">
-        <v>7181296</v>
+        <v>-46412</v>
       </c>
       <c r="Z78" t="n">
-        <v>566926</v>
+        <v>-574806</v>
       </c>
       <c r="AA78" t="n">
-        <v>2527715</v>
+        <v>45080</v>
       </c>
       <c r="AB78" t="n">
-        <v>46612125</v>
+        <v>72673</v>
       </c>
       <c r="AC78" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AD78" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AE78" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AF78" t="n">
-        <v>-75</v>
+        <v>-30</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>-6</v>
+        <v>-30</v>
       </c>
       <c r="AI78" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0</v>
+        <v>86.67</v>
       </c>
       <c r="AK78" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AL78" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列</t>
+          <t>DT尚未轉強、貼近5MA、分數升溫過快</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -12864,29 +12864,29 @@
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8299.TWO</t>
+          <t>8028.TW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -12895,28 +12895,28 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1970</v>
+        <v>244</v>
       </c>
       <c r="E79" t="n">
-        <v>1960</v>
+        <v>230.1</v>
       </c>
       <c r="F79" t="n">
-        <v>2014.5</v>
+        <v>234.1</v>
       </c>
       <c r="G79" t="n">
-        <v>2061.25</v>
+        <v>239.5</v>
       </c>
       <c r="H79" t="n">
-        <v>2813000</v>
+        <v>9261432</v>
       </c>
       <c r="I79" t="n">
-        <v>3060600</v>
+        <v>4278246</v>
       </c>
       <c r="J79" t="n">
-        <v>2215</v>
+        <v>256</v>
       </c>
       <c r="K79" t="n">
-        <v>1900</v>
+        <v>216.5</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -12924,52 +12924,52 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>178711</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>-511398</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>-1111167</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>-4860365</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>-1870975</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>-4586613</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>-5629606</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>-10129967</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1971000</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>3955000</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>4415000</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>5259000</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>78686</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>120215</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>103439</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>10602</v>
       </c>
       <c r="AC79" t="n">
         <v>-6</v>
@@ -12978,37 +12978,37 @@
         <v>-6</v>
       </c>
       <c r="AE79" t="n">
-        <v>-15</v>
+        <v>15</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="AI79" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="AJ79" t="n">
-        <v>-200</v>
+        <v>40</v>
       </c>
       <c r="AK79" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="AL79" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能偏強、分數剛升溫</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -13023,17 +13023,17 @@
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、爆量</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、爆量、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -13199,12 +13199,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4903.TWO</t>
+          <t>8299.TWO</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -13213,28 +13213,28 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>34.2</v>
+        <v>1970</v>
       </c>
       <c r="E81" t="n">
-        <v>34.14</v>
+        <v>1960</v>
       </c>
       <c r="F81" t="n">
-        <v>35.2</v>
+        <v>2014.5</v>
       </c>
       <c r="G81" t="n">
-        <v>35.91</v>
+        <v>2061.25</v>
       </c>
       <c r="H81" t="n">
-        <v>473000</v>
+        <v>2813000</v>
       </c>
       <c r="I81" t="n">
-        <v>1100400</v>
+        <v>3060600</v>
       </c>
       <c r="J81" t="n">
-        <v>39.15</v>
+        <v>2215</v>
       </c>
       <c r="K81" t="n">
-        <v>33.15</v>
+        <v>1900</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -13305,28 +13305,28 @@
         <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
       <c r="AI81" t="n">
-        <v>16</v>
+        <v>-4</v>
       </c>
       <c r="AJ81" t="n">
-        <v>72.73</v>
+        <v>-200</v>
       </c>
       <c r="AK81" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AL81" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -13358,42 +13358,42 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1714.TW</t>
+          <t>00878.TW</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>和桐</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>16.05</v>
+        <v>34.73</v>
       </c>
       <c r="E82" t="n">
-        <v>15.42</v>
+        <v>34.33</v>
       </c>
       <c r="F82" t="n">
-        <v>15.97</v>
+        <v>34.25</v>
       </c>
       <c r="G82" t="n">
-        <v>16.45</v>
+        <v>33.63</v>
       </c>
       <c r="H82" t="n">
-        <v>10370991</v>
+        <v>26931022</v>
       </c>
       <c r="I82" t="n">
-        <v>10863223</v>
+        <v>33329260</v>
       </c>
       <c r="J82" t="n">
-        <v>18.55</v>
+        <v>34.91</v>
       </c>
       <c r="K82" t="n">
-        <v>14.65</v>
+        <v>31.99</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -13401,70 +13401,70 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>2506361</v>
+        <v>10184608</v>
       </c>
       <c r="N82" t="n">
-        <v>1785799</v>
+        <v>-12744419</v>
       </c>
       <c r="O82" t="n">
-        <v>-2370693</v>
+        <v>-26384918</v>
       </c>
       <c r="P82" t="n">
-        <v>-6054027</v>
+        <v>28418963</v>
       </c>
       <c r="Q82" t="n">
-        <v>2497270</v>
+        <v>3003312</v>
       </c>
       <c r="R82" t="n">
-        <v>1673488</v>
+        <v>-13111345</v>
       </c>
       <c r="S82" t="n">
-        <v>-2265696</v>
+        <v>-28712633</v>
       </c>
       <c r="T82" t="n">
-        <v>-6014741</v>
+        <v>-17893162</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>-200000</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>-200000</v>
       </c>
       <c r="X82" t="n">
-        <v>-38000</v>
+        <v>-300000</v>
       </c>
       <c r="Y82" t="n">
-        <v>9091</v>
+        <v>7181296</v>
       </c>
       <c r="Z82" t="n">
-        <v>112311</v>
+        <v>566926</v>
       </c>
       <c r="AA82" t="n">
-        <v>-104997</v>
+        <v>2527715</v>
       </c>
       <c r="AB82" t="n">
-        <v>-1286</v>
+        <v>46612125</v>
       </c>
       <c r="AC82" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AD82" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AE82" t="n">
-        <v>-5</v>
+        <v>60</v>
       </c>
       <c r="AF82" t="n">
-        <v>-15</v>
+        <v>-75</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -13473,19 +13473,19 @@
         <v>0</v>
       </c>
       <c r="AK82" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AL82" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -13500,29 +13500,29 @@
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8150.TW</t>
+          <t>4903.TWO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -13531,28 +13531,28 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>86.7</v>
+        <v>34.2</v>
       </c>
       <c r="E83" t="n">
-        <v>86.3</v>
+        <v>34.14</v>
       </c>
       <c r="F83" t="n">
-        <v>88.56</v>
+        <v>35.2</v>
       </c>
       <c r="G83" t="n">
-        <v>89.05</v>
+        <v>35.91</v>
       </c>
       <c r="H83" t="n">
-        <v>15264426</v>
+        <v>473000</v>
       </c>
       <c r="I83" t="n">
-        <v>13675888</v>
+        <v>1100400</v>
       </c>
       <c r="J83" t="n">
-        <v>96.3</v>
+        <v>39.15</v>
       </c>
       <c r="K83" t="n">
-        <v>82.8</v>
+        <v>33.15</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -13560,76 +13560,76 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>1364803</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>695116</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>-9496064</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>-4305858</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>1372868</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>875048</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>-8695816</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>-3242694</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>207000</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>-8065</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>-254932</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>-880248</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>-1270164</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AD83" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AE83" t="n">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="AF83" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>-24</v>
+        <v>-22</v>
       </c>
       <c r="AI83" t="n">
         <v>16</v>
       </c>
       <c r="AJ83" t="n">
-        <v>66.67</v>
+        <v>72.73</v>
       </c>
       <c r="AK83" t="n">
         <v>45</v>
@@ -13659,17 +13659,17 @@
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14037,16 +14037,16 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>5837761</v>
+        <v>5243761</v>
       </c>
       <c r="N86" t="n">
-        <v>-5867921</v>
+        <v>-6461921</v>
       </c>
       <c r="O86" t="n">
-        <v>-25162665</v>
+        <v>-25756665</v>
       </c>
       <c r="P86" t="n">
-        <v>-5611739</v>
+        <v>-6205739</v>
       </c>
       <c r="Q86" t="n">
         <v>4794190</v>
@@ -14061,16 +14061,16 @@
         <v>-8605113</v>
       </c>
       <c r="U86" t="n">
-        <v>534410</v>
+        <v>-59590</v>
       </c>
       <c r="V86" t="n">
-        <v>687105</v>
+        <v>93105</v>
       </c>
       <c r="W86" t="n">
-        <v>1038686</v>
+        <v>444686</v>
       </c>
       <c r="X86" t="n">
-        <v>902300</v>
+        <v>308300</v>
       </c>
       <c r="Y86" t="n">
         <v>509161</v>
@@ -14153,12 +14153,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>8150.TW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -14167,81 +14167,81 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1320</v>
+        <v>86.7</v>
       </c>
       <c r="E87" t="n">
-        <v>1376</v>
+        <v>86.3</v>
       </c>
       <c r="F87" t="n">
-        <v>1370</v>
+        <v>88.56</v>
       </c>
       <c r="G87" t="n">
-        <v>1412</v>
+        <v>89.05</v>
       </c>
       <c r="H87" t="n">
-        <v>22637000</v>
+        <v>15264426</v>
       </c>
       <c r="I87" t="n">
-        <v>9695800</v>
+        <v>13675888</v>
       </c>
       <c r="J87" t="n">
-        <v>1580</v>
+        <v>96.3</v>
       </c>
       <c r="K87" t="n">
-        <v>1275</v>
+        <v>82.8</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>1364803</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>695116</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>-9496064</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>-4305858</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>1372868</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>875048</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>-8695816</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>-3242694</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="W87" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>207000</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>-8065</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>-254932</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>-880248</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>-1270164</v>
       </c>
       <c r="AC87" t="n">
         <v>-8</v>
@@ -14250,37 +14250,37 @@
         <v>-8</v>
       </c>
       <c r="AE87" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AG87" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>12</v>
+        <v>-24</v>
       </c>
       <c r="AI87" t="n">
-        <v>-20</v>
+        <v>16</v>
       </c>
       <c r="AJ87" t="n">
-        <v>-166.67</v>
+        <v>66.67</v>
       </c>
       <c r="AK87" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AL87" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -14295,29 +14295,29 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>跌破5日線、爆量、接近20日低點、爆量價未漲</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、爆量、接近20日低點、爆量價未漲、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6770.TW</t>
+          <t>1714.TW</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>和桐</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -14326,28 +14326,28 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>71.2</v>
+        <v>16.05</v>
       </c>
       <c r="E88" t="n">
-        <v>69.88</v>
+        <v>15.42</v>
       </c>
       <c r="F88" t="n">
-        <v>70.91</v>
+        <v>15.97</v>
       </c>
       <c r="G88" t="n">
-        <v>70.45</v>
+        <v>16.45</v>
       </c>
       <c r="H88" t="n">
-        <v>119460580</v>
+        <v>10370991</v>
       </c>
       <c r="I88" t="n">
-        <v>119091588</v>
+        <v>10863223</v>
       </c>
       <c r="J88" t="n">
-        <v>75.3</v>
+        <v>18.55</v>
       </c>
       <c r="K88" t="n">
-        <v>66.5</v>
+        <v>14.65</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -14355,91 +14355,91 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>36050024</v>
+        <v>2506361</v>
       </c>
       <c r="N88" t="n">
-        <v>6435761</v>
+        <v>1785799</v>
       </c>
       <c r="O88" t="n">
-        <v>-28813075</v>
+        <v>-2370693</v>
       </c>
       <c r="P88" t="n">
-        <v>112207065</v>
+        <v>-6054027</v>
       </c>
       <c r="Q88" t="n">
-        <v>32652611</v>
+        <v>2497270</v>
       </c>
       <c r="R88" t="n">
-        <v>3214983</v>
+        <v>1673488</v>
       </c>
       <c r="S88" t="n">
-        <v>-28511510</v>
+        <v>-2265696</v>
       </c>
       <c r="T88" t="n">
-        <v>99438701</v>
+        <v>-6014741</v>
       </c>
       <c r="U88" t="n">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>462000</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>451000</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>7832000</v>
+        <v>-38000</v>
       </c>
       <c r="Y88" t="n">
-        <v>3410413</v>
+        <v>9091</v>
       </c>
       <c r="Z88" t="n">
-        <v>2758778</v>
+        <v>112311</v>
       </c>
       <c r="AA88" t="n">
-        <v>-752565</v>
+        <v>-104997</v>
       </c>
       <c r="AB88" t="n">
-        <v>4936364</v>
+        <v>-1286</v>
       </c>
       <c r="AC88" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AD88" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AE88" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AF88" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
       <c r="AI88" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="AK88" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="AL88" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -14454,29 +14454,29 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>站上5日線、死亡交叉、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、死亡交叉、量能溫和放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -14485,120 +14485,120 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>170</v>
+        <v>1320</v>
       </c>
       <c r="E89" t="n">
-        <v>166</v>
+        <v>1376</v>
       </c>
       <c r="F89" t="n">
-        <v>173.45</v>
+        <v>1370</v>
       </c>
       <c r="G89" t="n">
-        <v>176.35</v>
+        <v>1412</v>
       </c>
       <c r="H89" t="n">
-        <v>120007010</v>
+        <v>22637000</v>
       </c>
       <c r="I89" t="n">
-        <v>94521248</v>
+        <v>9695800</v>
       </c>
       <c r="J89" t="n">
-        <v>192</v>
+        <v>1580</v>
       </c>
       <c r="K89" t="n">
-        <v>158.5</v>
+        <v>1275</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>-9188479</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3192007</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>-84344315</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>-5408202</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>-10245462</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>4133280</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>-69311123</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>12448408</v>
+        <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>-5298000</v>
+        <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>-15078238</v>
+        <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>-20556757</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1057983</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>4356727</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>45046</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2700147</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="AD89" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="AE89" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="AF89" t="n">
-        <v>-35</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AH89" t="n">
-        <v>-22</v>
+        <v>12</v>
       </c>
       <c r="AI89" t="n">
-        <v>10</v>
+        <v>-20</v>
       </c>
       <c r="AJ89" t="n">
-        <v>45.45</v>
+        <v>-166.67</v>
       </c>
       <c r="AK89" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AL89" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -14613,29 +14613,29 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、爆量、接近20日低點、爆量價未漲</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、爆量、接近20日低點、爆量價未漲、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>6770.TW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -14644,28 +14644,28 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>274.5</v>
+        <v>71.2</v>
       </c>
       <c r="E90" t="n">
-        <v>272.3</v>
+        <v>69.88</v>
       </c>
       <c r="F90" t="n">
-        <v>275.8</v>
+        <v>70.91</v>
       </c>
       <c r="G90" t="n">
-        <v>276.62</v>
+        <v>70.45</v>
       </c>
       <c r="H90" t="n">
-        <v>13168497</v>
+        <v>119460580</v>
       </c>
       <c r="I90" t="n">
-        <v>9521475</v>
+        <v>119091588</v>
       </c>
       <c r="J90" t="n">
-        <v>298</v>
+        <v>75.3</v>
       </c>
       <c r="K90" t="n">
-        <v>259</v>
+        <v>66.5</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -14673,82 +14673,82 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>1385170</v>
+        <v>36050024</v>
       </c>
       <c r="N90" t="n">
-        <v>1628700</v>
+        <v>6435761</v>
       </c>
       <c r="O90" t="n">
-        <v>-4150871</v>
+        <v>-28813075</v>
       </c>
       <c r="P90" t="n">
-        <v>-2019046</v>
+        <v>112207065</v>
       </c>
       <c r="Q90" t="n">
-        <v>1275987</v>
+        <v>32652611</v>
       </c>
       <c r="R90" t="n">
-        <v>2241274</v>
+        <v>3214983</v>
       </c>
       <c r="S90" t="n">
-        <v>-2291388</v>
+        <v>-28511510</v>
       </c>
       <c r="T90" t="n">
-        <v>468534</v>
+        <v>99438701</v>
       </c>
       <c r="U90" t="n">
-        <v>-4000</v>
+        <v>-13000</v>
       </c>
       <c r="V90" t="n">
-        <v>-819000</v>
+        <v>462000</v>
       </c>
       <c r="W90" t="n">
-        <v>-1781000</v>
+        <v>451000</v>
       </c>
       <c r="X90" t="n">
-        <v>-1992588</v>
+        <v>7832000</v>
       </c>
       <c r="Y90" t="n">
-        <v>113183</v>
+        <v>3410413</v>
       </c>
       <c r="Z90" t="n">
-        <v>206426</v>
+        <v>2758778</v>
       </c>
       <c r="AA90" t="n">
-        <v>-78483</v>
+        <v>-752565</v>
       </c>
       <c r="AB90" t="n">
-        <v>-494992</v>
+        <v>4936364</v>
       </c>
       <c r="AC90" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AD90" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AE90" t="n">
         <v>5</v>
       </c>
       <c r="AF90" t="n">
-        <v>-35</v>
+        <v>-30</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>-16</v>
+        <v>-30</v>
       </c>
       <c r="AI90" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AJ90" t="n">
-        <v>25</v>
+        <v>66.67</v>
       </c>
       <c r="AK90" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL90" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -14772,29 +14772,29 @@
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、死亡交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、死亡交叉、量能溫和放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -14803,28 +14803,28 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.95</v>
+        <v>170</v>
       </c>
       <c r="E91" t="n">
-        <v>13.94</v>
+        <v>166</v>
       </c>
       <c r="F91" t="n">
-        <v>14.16</v>
+        <v>173.45</v>
       </c>
       <c r="G91" t="n">
-        <v>14.21</v>
+        <v>176.35</v>
       </c>
       <c r="H91" t="n">
-        <v>18960049</v>
+        <v>120007010</v>
       </c>
       <c r="I91" t="n">
-        <v>20733511</v>
+        <v>94521248</v>
       </c>
       <c r="J91" t="n">
-        <v>15.15</v>
+        <v>192</v>
       </c>
       <c r="K91" t="n">
-        <v>13.6</v>
+        <v>158.5</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -14832,52 +14832,52 @@
         </is>
       </c>
       <c r="M91" t="n">
-        <v>-1137444</v>
+        <v>-9238479</v>
       </c>
       <c r="N91" t="n">
-        <v>3637996</v>
+        <v>3142007</v>
       </c>
       <c r="O91" t="n">
-        <v>-10316254</v>
+        <v>-84394315</v>
       </c>
       <c r="P91" t="n">
-        <v>-3717823</v>
+        <v>-5458202</v>
       </c>
       <c r="Q91" t="n">
-        <v>-687897</v>
+        <v>-10245462</v>
       </c>
       <c r="R91" t="n">
-        <v>3689978</v>
+        <v>4133280</v>
       </c>
       <c r="S91" t="n">
-        <v>-10080555</v>
+        <v>-69311123</v>
       </c>
       <c r="T91" t="n">
-        <v>-3508498</v>
+        <v>12448408</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>-51000</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>-5348000</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>-15128238</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>-20606757</v>
       </c>
       <c r="Y91" t="n">
-        <v>-449547</v>
+        <v>1057983</v>
       </c>
       <c r="Z91" t="n">
-        <v>-51982</v>
+        <v>4356727</v>
       </c>
       <c r="AA91" t="n">
-        <v>-235699</v>
+        <v>45046</v>
       </c>
       <c r="AB91" t="n">
-        <v>-209325</v>
+        <v>2700147</v>
       </c>
       <c r="AC91" t="n">
         <v>-12</v>
@@ -14886,37 +14886,37 @@
         <v>-12</v>
       </c>
       <c r="AE91" t="n">
-        <v>-15</v>
+        <v>5</v>
       </c>
       <c r="AF91" t="n">
-        <v>-15</v>
+        <v>-35</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>-12</v>
+        <v>-22</v>
       </c>
       <c r="AI91" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ91" t="n">
-        <v>0</v>
+        <v>45.45</v>
       </c>
       <c r="AK91" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AL91" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -14931,29 +14931,29 @@
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3017.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -14962,28 +14962,28 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3185</v>
+        <v>13.95</v>
       </c>
       <c r="E92" t="n">
-        <v>3231</v>
+        <v>13.94</v>
       </c>
       <c r="F92" t="n">
-        <v>3327</v>
+        <v>14.16</v>
       </c>
       <c r="G92" t="n">
-        <v>3262</v>
+        <v>14.21</v>
       </c>
       <c r="H92" t="n">
-        <v>3034388</v>
+        <v>18960049</v>
       </c>
       <c r="I92" t="n">
-        <v>2664732</v>
+        <v>20733511</v>
       </c>
       <c r="J92" t="n">
-        <v>3595</v>
+        <v>15.15</v>
       </c>
       <c r="K92" t="n">
-        <v>2740</v>
+        <v>13.6</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -14991,91 +14991,91 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>-87913</v>
+        <v>-1137444</v>
       </c>
       <c r="N92" t="n">
-        <v>254601</v>
+        <v>3637996</v>
       </c>
       <c r="O92" t="n">
-        <v>30233</v>
+        <v>-10316254</v>
       </c>
       <c r="P92" t="n">
-        <v>493922</v>
+        <v>-3717823</v>
       </c>
       <c r="Q92" t="n">
-        <v>-154755</v>
+        <v>-687897</v>
       </c>
       <c r="R92" t="n">
-        <v>145473</v>
+        <v>3689978</v>
       </c>
       <c r="S92" t="n">
-        <v>115861</v>
+        <v>-10080555</v>
       </c>
       <c r="T92" t="n">
-        <v>529500</v>
+        <v>-3508498</v>
       </c>
       <c r="U92" t="n">
-        <v>11229</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>45229</v>
+        <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>-93008</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>13080</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>55613</v>
+        <v>-449547</v>
       </c>
       <c r="Z92" t="n">
-        <v>63899</v>
+        <v>-51982</v>
       </c>
       <c r="AA92" t="n">
-        <v>7380</v>
+        <v>-235699</v>
       </c>
       <c r="AB92" t="n">
-        <v>-48658</v>
+        <v>-209325</v>
       </c>
       <c r="AC92" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AD92" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AE92" t="n">
-        <v>-35</v>
+        <v>-15</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>4</v>
+        <v>-12</v>
       </c>
       <c r="AI92" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="AJ92" t="n">
-        <v>-450</v>
+        <v>0</v>
       </c>
       <c r="AK92" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL92" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -15090,29 +15090,29 @@
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>跌破5日線、死亡交叉、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
         <is>
-          <t>籌碼中性、外資買投信賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、死亡交叉、量能溫和放大、籌碼中性、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3211.TWO</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -15121,28 +15121,28 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>360.5</v>
+        <v>274.5</v>
       </c>
       <c r="E93" t="n">
-        <v>363.2</v>
+        <v>272.3</v>
       </c>
       <c r="F93" t="n">
-        <v>370.25</v>
+        <v>275.8</v>
       </c>
       <c r="G93" t="n">
-        <v>371.55</v>
+        <v>276.62</v>
       </c>
       <c r="H93" t="n">
-        <v>2360000</v>
+        <v>13168497</v>
       </c>
       <c r="I93" t="n">
-        <v>2223800</v>
+        <v>9521475</v>
       </c>
       <c r="J93" t="n">
-        <v>414.5</v>
+        <v>298</v>
       </c>
       <c r="K93" t="n">
-        <v>315.5</v>
+        <v>259</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -15150,91 +15150,91 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>1385170</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1628700</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>-4150871</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>-2019046</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>1275987</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2241274</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>-2291388</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>468534</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>-819000</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>-1781000</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>-1992588</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>113183</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>206426</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>-78483</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>-494992</v>
       </c>
       <c r="AC93" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AD93" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AE93" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF93" t="n">
         <v>-35</v>
       </c>
-      <c r="AF93" t="n">
-        <v>0</v>
-      </c>
       <c r="AG93" t="n">
         <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>12</v>
+        <v>-16</v>
       </c>
       <c r="AI93" t="n">
-        <v>-26</v>
+        <v>4</v>
       </c>
       <c r="AJ93" t="n">
-        <v>-216.67</v>
+        <v>25</v>
       </c>
       <c r="AK93" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AL93" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -15249,29 +15249,29 @@
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>2401.TW</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>凌陽</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -15280,28 +15280,28 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>31</v>
+        <v>24.75</v>
       </c>
       <c r="E94" t="n">
-        <v>30.87</v>
+        <v>24.25</v>
       </c>
       <c r="F94" t="n">
-        <v>31.38</v>
+        <v>24.74</v>
       </c>
       <c r="G94" t="n">
-        <v>31.68</v>
+        <v>25.08</v>
       </c>
       <c r="H94" t="n">
-        <v>8741145</v>
+        <v>2242550</v>
       </c>
       <c r="I94" t="n">
-        <v>8667060</v>
+        <v>1912619</v>
       </c>
       <c r="J94" t="n">
-        <v>33.7</v>
+        <v>26.4</v>
       </c>
       <c r="K94" t="n">
-        <v>30</v>
+        <v>23.7</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -15309,52 +15309,52 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>1351240</v>
+        <v>298824</v>
       </c>
       <c r="N94" t="n">
-        <v>-2741464</v>
+        <v>-9319</v>
       </c>
       <c r="O94" t="n">
-        <v>-2633352</v>
+        <v>-639525</v>
       </c>
       <c r="P94" t="n">
-        <v>-5646202</v>
+        <v>-1376047</v>
       </c>
       <c r="Q94" t="n">
-        <v>1584468</v>
+        <v>281825</v>
       </c>
       <c r="R94" t="n">
-        <v>-2081696</v>
+        <v>-18545</v>
       </c>
       <c r="S94" t="n">
-        <v>-1848439</v>
+        <v>-445501</v>
       </c>
       <c r="T94" t="n">
-        <v>-4597247</v>
+        <v>-1194887</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
       </c>
       <c r="V94" t="n">
-        <v>293000</v>
+        <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>333000</v>
+        <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>353000</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>-233228</v>
+        <v>16999</v>
       </c>
       <c r="Z94" t="n">
-        <v>-952768</v>
+        <v>9226</v>
       </c>
       <c r="AA94" t="n">
-        <v>-1117913</v>
+        <v>-194024</v>
       </c>
       <c r="AB94" t="n">
-        <v>-1401955</v>
+        <v>-181160</v>
       </c>
       <c r="AC94" t="n">
         <v>-14</v>
@@ -15372,28 +15372,28 @@
         <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>-24</v>
+        <v>-18</v>
       </c>
       <c r="AI94" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AJ94" t="n">
-        <v>41.67</v>
+        <v>22.22</v>
       </c>
       <c r="AK94" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="AL94" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、分數剛升溫</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -15413,24 +15413,24 @@
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2401.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>凌陽</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -15439,28 +15439,28 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>24.75</v>
+        <v>31</v>
       </c>
       <c r="E95" t="n">
-        <v>24.25</v>
+        <v>30.87</v>
       </c>
       <c r="F95" t="n">
-        <v>24.74</v>
+        <v>31.38</v>
       </c>
       <c r="G95" t="n">
-        <v>25.08</v>
+        <v>31.68</v>
       </c>
       <c r="H95" t="n">
-        <v>2242550</v>
+        <v>8741145</v>
       </c>
       <c r="I95" t="n">
-        <v>1912619</v>
+        <v>8667060</v>
       </c>
       <c r="J95" t="n">
-        <v>26.4</v>
+        <v>33.7</v>
       </c>
       <c r="K95" t="n">
-        <v>23.7</v>
+        <v>30</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -15468,52 +15468,52 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>298824</v>
+        <v>1351240</v>
       </c>
       <c r="N95" t="n">
-        <v>-9319</v>
+        <v>-2741464</v>
       </c>
       <c r="O95" t="n">
-        <v>-639525</v>
+        <v>-2633352</v>
       </c>
       <c r="P95" t="n">
-        <v>-1376047</v>
+        <v>-5646202</v>
       </c>
       <c r="Q95" t="n">
-        <v>281825</v>
+        <v>1584468</v>
       </c>
       <c r="R95" t="n">
-        <v>-18545</v>
+        <v>-2081696</v>
       </c>
       <c r="S95" t="n">
-        <v>-445501</v>
+        <v>-1848439</v>
       </c>
       <c r="T95" t="n">
-        <v>-1194887</v>
+        <v>-4597247</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>293000</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>333000</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>353000</v>
       </c>
       <c r="Y95" t="n">
-        <v>16999</v>
+        <v>-233228</v>
       </c>
       <c r="Z95" t="n">
-        <v>9226</v>
+        <v>-952768</v>
       </c>
       <c r="AA95" t="n">
-        <v>-194024</v>
+        <v>-1117913</v>
       </c>
       <c r="AB95" t="n">
-        <v>-181160</v>
+        <v>-1401955</v>
       </c>
       <c r="AC95" t="n">
         <v>-14</v>
@@ -15531,28 +15531,28 @@
         <v>0</v>
       </c>
       <c r="AH95" t="n">
-        <v>-18</v>
+        <v>-24</v>
       </c>
       <c r="AI95" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AJ95" t="n">
-        <v>22.22</v>
+        <v>41.67</v>
       </c>
       <c r="AK95" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="AL95" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -15572,24 +15572,24 @@
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8028.TW</t>
+          <t>3017.TW</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -15598,28 +15598,28 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>244</v>
+        <v>3185</v>
       </c>
       <c r="E96" t="n">
-        <v>230.1</v>
+        <v>3231</v>
       </c>
       <c r="F96" t="n">
-        <v>234.1</v>
+        <v>3327</v>
       </c>
       <c r="G96" t="n">
-        <v>239.5</v>
+        <v>3262</v>
       </c>
       <c r="H96" t="n">
-        <v>9261432</v>
+        <v>3034388</v>
       </c>
       <c r="I96" t="n">
-        <v>4278246</v>
+        <v>2664732</v>
       </c>
       <c r="J96" t="n">
-        <v>256</v>
+        <v>3595</v>
       </c>
       <c r="K96" t="n">
-        <v>216.5</v>
+        <v>2740</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -15627,82 +15627,82 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>-1402289</v>
+        <v>-87913</v>
       </c>
       <c r="N96" t="n">
-        <v>-2092398</v>
+        <v>254601</v>
       </c>
       <c r="O96" t="n">
-        <v>-2692167</v>
+        <v>30233</v>
       </c>
       <c r="P96" t="n">
-        <v>-6441365</v>
+        <v>493922</v>
       </c>
       <c r="Q96" t="n">
-        <v>-1870975</v>
+        <v>-154755</v>
       </c>
       <c r="R96" t="n">
-        <v>-4586613</v>
+        <v>145473</v>
       </c>
       <c r="S96" t="n">
-        <v>-5629606</v>
+        <v>115861</v>
       </c>
       <c r="T96" t="n">
-        <v>-10129967</v>
+        <v>529500</v>
       </c>
       <c r="U96" t="n">
-        <v>390000</v>
+        <v>11229</v>
       </c>
       <c r="V96" t="n">
-        <v>2374000</v>
+        <v>45229</v>
       </c>
       <c r="W96" t="n">
-        <v>2834000</v>
+        <v>-93008</v>
       </c>
       <c r="X96" t="n">
-        <v>3678000</v>
+        <v>13080</v>
       </c>
       <c r="Y96" t="n">
-        <v>78686</v>
+        <v>55613</v>
       </c>
       <c r="Z96" t="n">
-        <v>120215</v>
+        <v>63899</v>
       </c>
       <c r="AA96" t="n">
-        <v>103439</v>
+        <v>7380</v>
       </c>
       <c r="AB96" t="n">
-        <v>10602</v>
+        <v>-48658</v>
       </c>
       <c r="AC96" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AD96" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AE96" t="n">
-        <v>15</v>
+        <v>-35</v>
       </c>
       <c r="AF96" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="AI96" t="n">
-        <v>-6</v>
+        <v>-18</v>
       </c>
       <c r="AJ96" t="n">
-        <v>-60</v>
+        <v>-450</v>
       </c>
       <c r="AK96" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL96" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -15726,17 +15726,17 @@
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、爆量</t>
+          <t>跌破5日線、死亡交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性、外資買投信賣</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、爆量、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、死亡交叉、量能溫和放大、籌碼中性、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15786,16 +15786,16 @@
         </is>
       </c>
       <c r="M97" t="n">
-        <v>-155042</v>
+        <v>-155251</v>
       </c>
       <c r="N97" t="n">
-        <v>409066</v>
+        <v>408857</v>
       </c>
       <c r="O97" t="n">
-        <v>-3045703</v>
+        <v>-3045912</v>
       </c>
       <c r="P97" t="n">
-        <v>-13176920</v>
+        <v>-13177129</v>
       </c>
       <c r="Q97" t="n">
         <v>-662977</v>
@@ -15810,16 +15810,16 @@
         <v>-9880344</v>
       </c>
       <c r="U97" t="n">
-        <v>253707</v>
+        <v>253498</v>
       </c>
       <c r="V97" t="n">
-        <v>-158744</v>
+        <v>-158953</v>
       </c>
       <c r="W97" t="n">
-        <v>-772657</v>
+        <v>-772866</v>
       </c>
       <c r="X97" t="n">
-        <v>-3128200</v>
+        <v>-3128409</v>
       </c>
       <c r="Y97" t="n">
         <v>254228</v>
@@ -18330,16 +18330,16 @@
         </is>
       </c>
       <c r="M113" t="n">
-        <v>1029351</v>
+        <v>1006351</v>
       </c>
       <c r="N113" t="n">
-        <v>1241252</v>
+        <v>1218252</v>
       </c>
       <c r="O113" t="n">
-        <v>-25700601</v>
+        <v>-25723601</v>
       </c>
       <c r="P113" t="n">
-        <v>14995713</v>
+        <v>14972713</v>
       </c>
       <c r="Q113" t="n">
         <v>308582</v>
@@ -18354,16 +18354,16 @@
         <v>20014841</v>
       </c>
       <c r="U113" t="n">
-        <v>577000</v>
+        <v>554000</v>
       </c>
       <c r="V113" t="n">
-        <v>-125000</v>
+        <v>-148000</v>
       </c>
       <c r="W113" t="n">
-        <v>-3779464</v>
+        <v>-3802464</v>
       </c>
       <c r="X113" t="n">
-        <v>-5802437</v>
+        <v>-5825437</v>
       </c>
       <c r="Y113" t="n">
         <v>143769</v>
@@ -20397,16 +20397,16 @@
         </is>
       </c>
       <c r="M126" t="n">
-        <v>-7893333</v>
+        <v>-7480333</v>
       </c>
       <c r="N126" t="n">
-        <v>-9649201</v>
+        <v>-9236201</v>
       </c>
       <c r="O126" t="n">
-        <v>-9768753</v>
+        <v>-9355753</v>
       </c>
       <c r="P126" t="n">
-        <v>-35152406</v>
+        <v>-34739406</v>
       </c>
       <c r="Q126" t="n">
         <v>-8055735</v>
@@ -20421,16 +20421,16 @@
         <v>-21196930</v>
       </c>
       <c r="U126" t="n">
-        <v>147000</v>
+        <v>560000</v>
       </c>
       <c r="V126" t="n">
-        <v>26410</v>
+        <v>439410</v>
       </c>
       <c r="W126" t="n">
-        <v>1179027</v>
+        <v>1592027</v>
       </c>
       <c r="X126" t="n">
-        <v>-13501533</v>
+        <v>-13088533</v>
       </c>
       <c r="Y126" t="n">
         <v>15402</v>
@@ -21467,12 +21467,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8039.TW</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -21481,28 +21481,28 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>257</v>
+        <v>529</v>
       </c>
       <c r="E133" t="n">
-        <v>269.7</v>
+        <v>538.2</v>
       </c>
       <c r="F133" t="n">
-        <v>283.2</v>
+        <v>554.6</v>
       </c>
       <c r="G133" t="n">
-        <v>296.98</v>
+        <v>552.4</v>
       </c>
       <c r="H133" t="n">
-        <v>22338443</v>
+        <v>22992927</v>
       </c>
       <c r="I133" t="n">
-        <v>17796239</v>
+        <v>26297320</v>
       </c>
       <c r="J133" t="n">
-        <v>364</v>
+        <v>610</v>
       </c>
       <c r="K133" t="n">
-        <v>256.5</v>
+        <v>511</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -21510,82 +21510,82 @@
         </is>
       </c>
       <c r="M133" t="n">
-        <v>-729565</v>
+        <v>-1767666</v>
       </c>
       <c r="N133" t="n">
-        <v>-3611487</v>
+        <v>-8311166</v>
       </c>
       <c r="O133" t="n">
-        <v>-4441853</v>
+        <v>-9822404</v>
       </c>
       <c r="P133" t="n">
-        <v>-17077012</v>
+        <v>8890846</v>
       </c>
       <c r="Q133" t="n">
-        <v>-476958</v>
+        <v>-2052950</v>
       </c>
       <c r="R133" t="n">
-        <v>-3166814</v>
+        <v>-9136538</v>
       </c>
       <c r="S133" t="n">
-        <v>-4172066</v>
+        <v>-11012367</v>
       </c>
       <c r="T133" t="n">
-        <v>-15695842</v>
+        <v>7458611</v>
       </c>
       <c r="U133" t="n">
-        <v>-18000</v>
+        <v>156000</v>
       </c>
       <c r="V133" t="n">
-        <v>55000</v>
+        <v>1031020</v>
       </c>
       <c r="W133" t="n">
-        <v>68000</v>
+        <v>2336128</v>
       </c>
       <c r="X133" t="n">
-        <v>-467000</v>
+        <v>1057056</v>
       </c>
       <c r="Y133" t="n">
-        <v>-234607</v>
+        <v>129284</v>
       </c>
       <c r="Z133" t="n">
-        <v>-499673</v>
+        <v>-205648</v>
       </c>
       <c r="AA133" t="n">
-        <v>-337787</v>
+        <v>-1146165</v>
       </c>
       <c r="AB133" t="n">
-        <v>-914170</v>
+        <v>375179</v>
       </c>
       <c r="AC133" t="n">
-        <v>-40</v>
+        <v>-44</v>
       </c>
       <c r="AD133" t="n">
-        <v>-40</v>
+        <v>-44</v>
       </c>
       <c r="AE133" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="AF133" t="n">
-        <v>-55</v>
+        <v>-80</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
       </c>
       <c r="AH133" t="n">
-        <v>-32</v>
+        <v>-54</v>
       </c>
       <c r="AI133" t="n">
-        <v>-8</v>
+        <v>10</v>
       </c>
       <c r="AJ133" t="n">
-        <v>-25</v>
+        <v>18.52</v>
       </c>
       <c r="AK133" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL133" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM133" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -21609,29 +21609,29 @@
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>3376.TW</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -21640,28 +21640,28 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>529</v>
+        <v>175.5</v>
       </c>
       <c r="E134" t="n">
-        <v>538.2</v>
+        <v>177.8</v>
       </c>
       <c r="F134" t="n">
-        <v>554.6</v>
+        <v>190.55</v>
       </c>
       <c r="G134" t="n">
-        <v>552.4</v>
+        <v>196.2</v>
       </c>
       <c r="H134" t="n">
-        <v>22992927</v>
+        <v>2385744</v>
       </c>
       <c r="I134" t="n">
-        <v>26297320</v>
+        <v>5398640</v>
       </c>
       <c r="J134" t="n">
-        <v>610</v>
+        <v>222</v>
       </c>
       <c r="K134" t="n">
-        <v>511</v>
+        <v>170.5</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -21669,52 +21669,52 @@
         </is>
       </c>
       <c r="M134" t="n">
-        <v>-1767666</v>
+        <v>-457186</v>
       </c>
       <c r="N134" t="n">
-        <v>-8311166</v>
+        <v>-2681477</v>
       </c>
       <c r="O134" t="n">
-        <v>-9822404</v>
+        <v>-5210346</v>
       </c>
       <c r="P134" t="n">
-        <v>8890846</v>
+        <v>-15808398</v>
       </c>
       <c r="Q134" t="n">
-        <v>-2052950</v>
+        <v>-395883</v>
       </c>
       <c r="R134" t="n">
-        <v>-9136538</v>
+        <v>-2442386</v>
       </c>
       <c r="S134" t="n">
-        <v>-11012367</v>
+        <v>-5049633</v>
       </c>
       <c r="T134" t="n">
-        <v>7458611</v>
+        <v>-14693758</v>
       </c>
       <c r="U134" t="n">
-        <v>156000</v>
+        <v>0</v>
       </c>
       <c r="V134" t="n">
-        <v>1031020</v>
+        <v>55000</v>
       </c>
       <c r="W134" t="n">
-        <v>2336128</v>
+        <v>90000</v>
       </c>
       <c r="X134" t="n">
-        <v>1057056</v>
+        <v>88000</v>
       </c>
       <c r="Y134" t="n">
-        <v>129284</v>
+        <v>-61303</v>
       </c>
       <c r="Z134" t="n">
-        <v>-205648</v>
+        <v>-294091</v>
       </c>
       <c r="AA134" t="n">
-        <v>-1146165</v>
+        <v>-250713</v>
       </c>
       <c r="AB134" t="n">
-        <v>375179</v>
+        <v>-1202640</v>
       </c>
       <c r="AC134" t="n">
         <v>-44</v>
@@ -21723,28 +21723,28 @@
         <v>-44</v>
       </c>
       <c r="AE134" t="n">
-        <v>-30</v>
+        <v>-55</v>
       </c>
       <c r="AF134" t="n">
-        <v>-80</v>
+        <v>-55</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
       </c>
       <c r="AH134" t="n">
-        <v>-54</v>
+        <v>-44</v>
       </c>
       <c r="AI134" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ134" t="n">
-        <v>18.52</v>
+        <v>0</v>
       </c>
       <c r="AK134" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL134" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM134" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -21768,29 +21768,29 @@
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3376.TW</t>
+          <t>2368.TW</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -21799,28 +21799,28 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>175.5</v>
+        <v>950</v>
       </c>
       <c r="E135" t="n">
-        <v>177.8</v>
+        <v>992.8</v>
       </c>
       <c r="F135" t="n">
-        <v>190.55</v>
+        <v>1034.9</v>
       </c>
       <c r="G135" t="n">
-        <v>196.2</v>
+        <v>1054.9</v>
       </c>
       <c r="H135" t="n">
-        <v>2385744</v>
+        <v>13646634</v>
       </c>
       <c r="I135" t="n">
-        <v>5398640</v>
+        <v>6962654</v>
       </c>
       <c r="J135" t="n">
-        <v>222</v>
+        <v>1245</v>
       </c>
       <c r="K135" t="n">
-        <v>170.5</v>
+        <v>915</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -21828,76 +21828,76 @@
         </is>
       </c>
       <c r="M135" t="n">
-        <v>-457186</v>
+        <v>-3391341</v>
       </c>
       <c r="N135" t="n">
-        <v>-2681477</v>
+        <v>-4861697</v>
       </c>
       <c r="O135" t="n">
-        <v>-5210346</v>
+        <v>-3889031</v>
       </c>
       <c r="P135" t="n">
-        <v>-15808398</v>
+        <v>-7139333</v>
       </c>
       <c r="Q135" t="n">
-        <v>-395883</v>
+        <v>-3669475</v>
       </c>
       <c r="R135" t="n">
-        <v>-2442386</v>
+        <v>-4369539</v>
       </c>
       <c r="S135" t="n">
-        <v>-5049633</v>
+        <v>-1360213</v>
       </c>
       <c r="T135" t="n">
-        <v>-14693758</v>
+        <v>-5126770</v>
       </c>
       <c r="U135" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="V135" t="n">
-        <v>55000</v>
+        <v>-414060</v>
       </c>
       <c r="W135" t="n">
-        <v>90000</v>
+        <v>-2178745</v>
       </c>
       <c r="X135" t="n">
-        <v>88000</v>
+        <v>-1565763</v>
       </c>
       <c r="Y135" t="n">
-        <v>-61303</v>
+        <v>242134</v>
       </c>
       <c r="Z135" t="n">
-        <v>-294091</v>
+        <v>-78098</v>
       </c>
       <c r="AA135" t="n">
-        <v>-250713</v>
+        <v>-350073</v>
       </c>
       <c r="AB135" t="n">
-        <v>-1202640</v>
+        <v>-446800</v>
       </c>
       <c r="AC135" t="n">
-        <v>-44</v>
+        <v>-46</v>
       </c>
       <c r="AD135" t="n">
-        <v>-44</v>
+        <v>-46</v>
       </c>
       <c r="AE135" t="n">
-        <v>-55</v>
+        <v>-40</v>
       </c>
       <c r="AF135" t="n">
-        <v>-55</v>
+        <v>-75</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
       </c>
       <c r="AH135" t="n">
-        <v>-44</v>
+        <v>-36</v>
       </c>
       <c r="AI135" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0</v>
+        <v>-27.78</v>
       </c>
       <c r="AK135" t="n">
         <v>0</v>
@@ -21912,7 +21912,7 @@
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -21927,29 +21927,29 @@
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、成交量放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2368.TW</t>
+          <t>8039.TW</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -21958,28 +21958,28 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>950</v>
+        <v>257</v>
       </c>
       <c r="E136" t="n">
-        <v>992.8</v>
+        <v>269.7</v>
       </c>
       <c r="F136" t="n">
-        <v>1034.9</v>
+        <v>283.2</v>
       </c>
       <c r="G136" t="n">
-        <v>1054.9</v>
+        <v>296.98</v>
       </c>
       <c r="H136" t="n">
-        <v>13646634</v>
+        <v>22338443</v>
       </c>
       <c r="I136" t="n">
-        <v>6962654</v>
+        <v>17796239</v>
       </c>
       <c r="J136" t="n">
-        <v>1245</v>
+        <v>364</v>
       </c>
       <c r="K136" t="n">
-        <v>915</v>
+        <v>256.5</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -21987,61 +21987,61 @@
         </is>
       </c>
       <c r="M136" t="n">
-        <v>-3391341</v>
+        <v>-2296565</v>
       </c>
       <c r="N136" t="n">
-        <v>-4861697</v>
+        <v>-5178487</v>
       </c>
       <c r="O136" t="n">
-        <v>-3889031</v>
+        <v>-6008853</v>
       </c>
       <c r="P136" t="n">
-        <v>-7139333</v>
+        <v>-18644012</v>
       </c>
       <c r="Q136" t="n">
-        <v>-3669475</v>
+        <v>-476958</v>
       </c>
       <c r="R136" t="n">
-        <v>-4369539</v>
+        <v>-3166814</v>
       </c>
       <c r="S136" t="n">
-        <v>-1360213</v>
+        <v>-4172066</v>
       </c>
       <c r="T136" t="n">
-        <v>-5126770</v>
+        <v>-15695842</v>
       </c>
       <c r="U136" t="n">
-        <v>36000</v>
+        <v>-1585000</v>
       </c>
       <c r="V136" t="n">
-        <v>-414060</v>
+        <v>-1512000</v>
       </c>
       <c r="W136" t="n">
-        <v>-2178745</v>
+        <v>-1499000</v>
       </c>
       <c r="X136" t="n">
-        <v>-1565763</v>
+        <v>-2034000</v>
       </c>
       <c r="Y136" t="n">
-        <v>242134</v>
+        <v>-234607</v>
       </c>
       <c r="Z136" t="n">
-        <v>-78098</v>
+        <v>-499673</v>
       </c>
       <c r="AA136" t="n">
-        <v>-350073</v>
+        <v>-337787</v>
       </c>
       <c r="AB136" t="n">
-        <v>-446800</v>
+        <v>-914170</v>
       </c>
       <c r="AC136" t="n">
-        <v>-46</v>
+        <v>-48</v>
       </c>
       <c r="AD136" t="n">
-        <v>-46</v>
+        <v>-48</v>
       </c>
       <c r="AE136" t="n">
-        <v>-40</v>
+        <v>-45</v>
       </c>
       <c r="AF136" t="n">
         <v>-75</v>
@@ -22050,13 +22050,13 @@
         <v>0</v>
       </c>
       <c r="AH136" t="n">
-        <v>-36</v>
+        <v>-32</v>
       </c>
       <c r="AI136" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="AJ136" t="n">
-        <v>-27.78</v>
+        <v>-50</v>
       </c>
       <c r="AK136" t="n">
         <v>0</v>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、成交量放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
@@ -22096,19 +22096,19 @@
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、成交量放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6269.TW</t>
+          <t>4967.TW</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -22117,28 +22117,28 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>63.7</v>
+        <v>271</v>
       </c>
       <c r="E137" t="n">
-        <v>64.56</v>
+        <v>273.2</v>
       </c>
       <c r="F137" t="n">
-        <v>66</v>
+        <v>275.8</v>
       </c>
       <c r="G137" t="n">
-        <v>67.36</v>
+        <v>275.43</v>
       </c>
       <c r="H137" t="n">
-        <v>2709677</v>
+        <v>1803089</v>
       </c>
       <c r="I137" t="n">
-        <v>2980530</v>
+        <v>2483234</v>
       </c>
       <c r="J137" t="n">
-        <v>82.3</v>
+        <v>291.5</v>
       </c>
       <c r="K137" t="n">
-        <v>59</v>
+        <v>264</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -22146,52 +22146,52 @@
         </is>
       </c>
       <c r="M137" t="n">
-        <v>-626976</v>
+        <v>-365010</v>
       </c>
       <c r="N137" t="n">
-        <v>-638144</v>
+        <v>-93879</v>
       </c>
       <c r="O137" t="n">
-        <v>-1002170</v>
+        <v>-129943</v>
       </c>
       <c r="P137" t="n">
-        <v>-3945088</v>
+        <v>2470791</v>
       </c>
       <c r="Q137" t="n">
-        <v>-595944</v>
+        <v>-309991</v>
       </c>
       <c r="R137" t="n">
-        <v>-628156</v>
+        <v>-55809</v>
       </c>
       <c r="S137" t="n">
-        <v>-768046</v>
+        <v>-33921</v>
       </c>
       <c r="T137" t="n">
-        <v>-3151297</v>
+        <v>2608675</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>-83000</v>
+        <v>-400</v>
       </c>
       <c r="W137" t="n">
-        <v>-83000</v>
+        <v>-400</v>
       </c>
       <c r="X137" t="n">
-        <v>-95000</v>
+        <v>20600</v>
       </c>
       <c r="Y137" t="n">
-        <v>-31032</v>
+        <v>-55019</v>
       </c>
       <c r="Z137" t="n">
-        <v>73012</v>
+        <v>-37670</v>
       </c>
       <c r="AA137" t="n">
-        <v>-151124</v>
+        <v>-95622</v>
       </c>
       <c r="AB137" t="n">
-        <v>-698791</v>
+        <v>-158484</v>
       </c>
       <c r="AC137" t="n">
         <v>-48</v>
@@ -22200,22 +22200,22 @@
         <v>-48</v>
       </c>
       <c r="AE137" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="AF137" t="n">
-        <v>-75</v>
+        <v>-90</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
       </c>
       <c r="AH137" t="n">
-        <v>-38</v>
+        <v>-26</v>
       </c>
       <c r="AI137" t="n">
-        <v>-10</v>
+        <v>-22</v>
       </c>
       <c r="AJ137" t="n">
-        <v>-26.32</v>
+        <v>-84.62</v>
       </c>
       <c r="AK137" t="n">
         <v>0</v>
@@ -22245,17 +22245,17 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22421,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4967.TW</t>
+          <t>6269.TW</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -22435,28 +22435,28 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>271</v>
+        <v>63.7</v>
       </c>
       <c r="E139" t="n">
-        <v>273.2</v>
+        <v>64.56</v>
       </c>
       <c r="F139" t="n">
-        <v>275.8</v>
+        <v>66</v>
       </c>
       <c r="G139" t="n">
-        <v>275.43</v>
+        <v>67.36</v>
       </c>
       <c r="H139" t="n">
-        <v>1803089</v>
+        <v>2709677</v>
       </c>
       <c r="I139" t="n">
-        <v>2483234</v>
+        <v>2980530</v>
       </c>
       <c r="J139" t="n">
-        <v>291.5</v>
+        <v>82.3</v>
       </c>
       <c r="K139" t="n">
-        <v>264</v>
+        <v>59</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -22464,52 +22464,52 @@
         </is>
       </c>
       <c r="M139" t="n">
-        <v>-365010</v>
+        <v>-626976</v>
       </c>
       <c r="N139" t="n">
-        <v>-93879</v>
+        <v>-638144</v>
       </c>
       <c r="O139" t="n">
-        <v>-129943</v>
+        <v>-1002170</v>
       </c>
       <c r="P139" t="n">
-        <v>2470791</v>
+        <v>-3945088</v>
       </c>
       <c r="Q139" t="n">
-        <v>-309991</v>
+        <v>-595944</v>
       </c>
       <c r="R139" t="n">
-        <v>-55809</v>
+        <v>-628156</v>
       </c>
       <c r="S139" t="n">
-        <v>-33921</v>
+        <v>-768046</v>
       </c>
       <c r="T139" t="n">
-        <v>2608675</v>
+        <v>-3151297</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
       </c>
       <c r="V139" t="n">
-        <v>-400</v>
+        <v>-83000</v>
       </c>
       <c r="W139" t="n">
-        <v>-400</v>
+        <v>-83000</v>
       </c>
       <c r="X139" t="n">
-        <v>20600</v>
+        <v>-95000</v>
       </c>
       <c r="Y139" t="n">
-        <v>-55019</v>
+        <v>-31032</v>
       </c>
       <c r="Z139" t="n">
-        <v>-37670</v>
+        <v>73012</v>
       </c>
       <c r="AA139" t="n">
-        <v>-95622</v>
+        <v>-151124</v>
       </c>
       <c r="AB139" t="n">
-        <v>-158484</v>
+        <v>-698791</v>
       </c>
       <c r="AC139" t="n">
         <v>-48</v>
@@ -22518,22 +22518,22 @@
         <v>-48</v>
       </c>
       <c r="AE139" t="n">
-        <v>-30</v>
+        <v>-45</v>
       </c>
       <c r="AF139" t="n">
-        <v>-90</v>
+        <v>-75</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
       </c>
       <c r="AH139" t="n">
-        <v>-26</v>
+        <v>-38</v>
       </c>
       <c r="AI139" t="n">
-        <v>-22</v>
+        <v>-10</v>
       </c>
       <c r="AJ139" t="n">
-        <v>-84.62</v>
+        <v>-26.32</v>
       </c>
       <c r="AK139" t="n">
         <v>0</v>
@@ -22563,17 +22563,17 @@
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR139" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -8588,12 +8588,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3211.TWO</t>
+          <t>3545.TW</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>敦泰</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -8602,28 +8602,28 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>386.5</v>
+        <v>50.5</v>
       </c>
       <c r="E52" t="n">
-        <v>375.8</v>
+        <v>49.28</v>
       </c>
       <c r="F52" t="n">
-        <v>366.2</v>
+        <v>49.96</v>
       </c>
       <c r="G52" t="n">
-        <v>368.9</v>
+        <v>50.03</v>
       </c>
       <c r="H52" t="n">
-        <v>4690000</v>
+        <v>490007</v>
       </c>
       <c r="I52" t="n">
-        <v>9925800</v>
+        <v>509422</v>
       </c>
       <c r="J52" t="n">
-        <v>419</v>
+        <v>52.8</v>
       </c>
       <c r="K52" t="n">
-        <v>304</v>
+        <v>47.7</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -8631,28 +8631,28 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>277199</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>359717</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>396070</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>470365</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>274199</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>358796</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>420796</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>486171</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -8667,16 +8667,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>-24726</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>-15806</v>
       </c>
       <c r="AC52" t="n">
         <v>18</v>
@@ -8685,28 +8685,28 @@
         <v>18</v>
       </c>
       <c r="AE52" t="n">
-        <v>45</v>
+        <v>-5</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
       </c>
       <c r="AH52" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI52" t="n">
         <v>12</v>
       </c>
-      <c r="AI52" t="n">
-        <v>6</v>
-      </c>
       <c r="AJ52" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="AK52" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL52" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8730,17 +8730,17 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、黃金交叉、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -8906,12 +8906,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3545.TW</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>敦泰</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -8920,28 +8920,28 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>50.5</v>
+        <v>1065</v>
       </c>
       <c r="E54" t="n">
-        <v>49.28</v>
+        <v>1078</v>
       </c>
       <c r="F54" t="n">
-        <v>49.96</v>
+        <v>1070</v>
       </c>
       <c r="G54" t="n">
-        <v>50.03</v>
+        <v>1129</v>
       </c>
       <c r="H54" t="n">
-        <v>490007</v>
+        <v>8133171</v>
       </c>
       <c r="I54" t="n">
-        <v>509422</v>
+        <v>7263900</v>
       </c>
       <c r="J54" t="n">
-        <v>52.8</v>
+        <v>1335</v>
       </c>
       <c r="K54" t="n">
-        <v>47.7</v>
+        <v>1010</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -8949,61 +8949,61 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>277199</v>
+        <v>-1134820</v>
       </c>
       <c r="N54" t="n">
-        <v>359717</v>
+        <v>-417717</v>
       </c>
       <c r="O54" t="n">
-        <v>396070</v>
+        <v>1146131</v>
       </c>
       <c r="P54" t="n">
-        <v>470365</v>
+        <v>2989142</v>
       </c>
       <c r="Q54" t="n">
-        <v>274199</v>
+        <v>-1303101</v>
       </c>
       <c r="R54" t="n">
-        <v>358796</v>
+        <v>-705087</v>
       </c>
       <c r="S54" t="n">
-        <v>420796</v>
+        <v>693972</v>
       </c>
       <c r="T54" t="n">
-        <v>486171</v>
+        <v>5984035</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>115000</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>273000</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>-2914275</v>
       </c>
       <c r="Y54" t="n">
-        <v>3000</v>
+        <v>53281</v>
       </c>
       <c r="Z54" t="n">
-        <v>921</v>
+        <v>14370</v>
       </c>
       <c r="AA54" t="n">
-        <v>-24726</v>
+        <v>221159</v>
       </c>
       <c r="AB54" t="n">
-        <v>-15806</v>
+        <v>-80618</v>
       </c>
       <c r="AC54" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD54" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE54" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="AF54" t="n">
         <v>50</v>
@@ -9012,28 +9012,28 @@
         <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="AI54" t="n">
-        <v>12</v>
+        <v>-16</v>
       </c>
       <c r="AJ54" t="n">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="AK54" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -9048,29 +9048,29 @@
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -9079,28 +9079,28 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1065</v>
+        <v>1385</v>
       </c>
       <c r="E55" t="n">
-        <v>1078</v>
+        <v>1334</v>
       </c>
       <c r="F55" t="n">
-        <v>1070</v>
+        <v>1376</v>
       </c>
       <c r="G55" t="n">
-        <v>1129</v>
+        <v>1274.7</v>
       </c>
       <c r="H55" t="n">
-        <v>8133171</v>
+        <v>6498000</v>
       </c>
       <c r="I55" t="n">
-        <v>7263900</v>
+        <v>3534600</v>
       </c>
       <c r="J55" t="n">
-        <v>1335</v>
+        <v>1505</v>
       </c>
       <c r="K55" t="n">
-        <v>1010</v>
+        <v>965</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -9108,82 +9108,82 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>-1134820</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>-417717</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>1146131</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2989142</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>-1303101</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>-705087</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>693972</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>5984035</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>273000</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>-2914275</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>53281</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>14370</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>221159</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>-80618</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
         <v>16</v>
       </c>
-      <c r="AD55" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>32</v>
-      </c>
       <c r="AI55" t="n">
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="AJ55" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -9207,17 +9207,17 @@
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -9383,12 +9383,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9397,28 +9397,28 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1385</v>
+        <v>238</v>
       </c>
       <c r="E57" t="n">
-        <v>1334</v>
+        <v>233.1</v>
       </c>
       <c r="F57" t="n">
-        <v>1376</v>
+        <v>233.15</v>
       </c>
       <c r="G57" t="n">
-        <v>1274.7</v>
+        <v>210.93</v>
       </c>
       <c r="H57" t="n">
-        <v>6498000</v>
+        <v>10332000</v>
       </c>
       <c r="I57" t="n">
-        <v>3534600</v>
+        <v>7951600</v>
       </c>
       <c r="J57" t="n">
-        <v>1505</v>
+        <v>265</v>
       </c>
       <c r="K57" t="n">
-        <v>965</v>
+        <v>140</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -9474,13 +9474,13 @@
         <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD57" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE57" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="AF57" t="n">
         <v>0</v>
@@ -9489,28 +9489,28 @@
         <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AI57" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="AJ57" t="n">
-        <v>-12.5</v>
+        <v>-45.45</v>
       </c>
       <c r="AK57" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="AL57" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -9860,12 +9860,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>2329.TW</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>華泰</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9874,28 +9874,28 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>238</v>
+        <v>42.9</v>
       </c>
       <c r="E60" t="n">
-        <v>233.1</v>
+        <v>42.05</v>
       </c>
       <c r="F60" t="n">
-        <v>233.15</v>
+        <v>42.4</v>
       </c>
       <c r="G60" t="n">
-        <v>210.93</v>
+        <v>42.95</v>
       </c>
       <c r="H60" t="n">
-        <v>10332000</v>
+        <v>2682148</v>
       </c>
       <c r="I60" t="n">
-        <v>7951600</v>
+        <v>1800751</v>
       </c>
       <c r="J60" t="n">
-        <v>265</v>
+        <v>45</v>
       </c>
       <c r="K60" t="n">
-        <v>140</v>
+        <v>40.9</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -9903,28 +9903,28 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>-163503</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>620465</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1193398</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1202014</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>-141151</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>581671</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1233643</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>1211556</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -9939,28 +9939,28 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>-22352</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>38794</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>-40245</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>-9542</v>
       </c>
       <c r="AC60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE60" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF60" t="n">
         <v>30</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -9969,10 +9969,10 @@
         <v>22</v>
       </c>
       <c r="AI60" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="AJ60" t="n">
-        <v>-45.45</v>
+        <v>-54.55</v>
       </c>
       <c r="AK60" t="n">
         <v>45</v>
@@ -10002,29 +10002,29 @@
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2329.TW</t>
+          <t>6275.TWO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>華泰</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -10033,28 +10033,28 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>42.9</v>
+        <v>45.15</v>
       </c>
       <c r="E61" t="n">
-        <v>42.05</v>
+        <v>45.05</v>
       </c>
       <c r="F61" t="n">
-        <v>42.4</v>
+        <v>45.61</v>
       </c>
       <c r="G61" t="n">
-        <v>42.95</v>
+        <v>45.46</v>
       </c>
       <c r="H61" t="n">
-        <v>2682148</v>
+        <v>125000</v>
       </c>
       <c r="I61" t="n">
-        <v>1800751</v>
+        <v>102200</v>
       </c>
       <c r="J61" t="n">
-        <v>45</v>
+        <v>48.9</v>
       </c>
       <c r="K61" t="n">
-        <v>40.9</v>
+        <v>43.65</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -10062,28 +10062,28 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>-163503</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>620465</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>1193398</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1202014</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>-141151</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>581671</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>1233643</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>1211556</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>-22352</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>38794</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>-40245</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>-9542</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE61" t="n">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="AF61" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>22</v>
+        <v>-12</v>
       </c>
       <c r="AI61" t="n">
-        <v>-12</v>
+        <v>20</v>
       </c>
       <c r="AJ61" t="n">
-        <v>-54.55</v>
+        <v>166.67</v>
       </c>
       <c r="AK61" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AL61" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -10161,29 +10161,29 @@
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6275.TWO</t>
+          <t>2421.TW</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -10192,28 +10192,28 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>45.15</v>
+        <v>162</v>
       </c>
       <c r="E62" t="n">
-        <v>45.05</v>
+        <v>161.6</v>
       </c>
       <c r="F62" t="n">
-        <v>45.61</v>
+        <v>165.8</v>
       </c>
       <c r="G62" t="n">
-        <v>45.46</v>
+        <v>162.57</v>
       </c>
       <c r="H62" t="n">
-        <v>125000</v>
+        <v>2197326</v>
       </c>
       <c r="I62" t="n">
-        <v>102200</v>
+        <v>2197403</v>
       </c>
       <c r="J62" t="n">
-        <v>48.9</v>
+        <v>184</v>
       </c>
       <c r="K62" t="n">
-        <v>43.65</v>
+        <v>140.5</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -10221,91 +10221,91 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>233314</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>-3733</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>236448</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>-1862857</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>182209</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>128495</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>591133</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>-1737461</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>-56000</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>-74000</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>51105</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>-95228</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>-298685</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>-51396</v>
       </c>
       <c r="AC62" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AD62" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE62" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF62" t="n">
         <v>20</v>
       </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
       <c r="AG62" t="n">
         <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>-12</v>
+        <v>-26</v>
       </c>
       <c r="AI62" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AJ62" t="n">
-        <v>166.67</v>
+        <v>123.08</v>
       </c>
       <c r="AK62" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AL62" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -10320,17 +10320,17 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、死亡交叉、量能未放大</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、死亡交叉、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -10360,7 +10360,7 @@
         <v>545.7</v>
       </c>
       <c r="G63" t="n">
-        <v>562.25</v>
+        <v>559.05</v>
       </c>
       <c r="H63" t="n">
         <v>902000</v>
@@ -10369,7 +10369,7 @@
         <v>415400</v>
       </c>
       <c r="J63" t="n">
-        <v>619</v>
+        <v>599</v>
       </c>
       <c r="K63" t="n">
         <v>521</v>
@@ -10814,12 +10814,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2421.TW</t>
+          <t>2606.TW</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -10828,28 +10828,28 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="E66" t="n">
-        <v>161.6</v>
+        <v>76.06</v>
       </c>
       <c r="F66" t="n">
-        <v>165.8</v>
+        <v>77.3</v>
       </c>
       <c r="G66" t="n">
-        <v>162.57</v>
+        <v>75.94</v>
       </c>
       <c r="H66" t="n">
-        <v>2197326</v>
+        <v>3653421</v>
       </c>
       <c r="I66" t="n">
-        <v>2197403</v>
+        <v>4381693</v>
       </c>
       <c r="J66" t="n">
-        <v>184</v>
+        <v>81.7</v>
       </c>
       <c r="K66" t="n">
-        <v>140.5</v>
+        <v>70</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -10857,91 +10857,91 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>233314</v>
+        <v>222050</v>
       </c>
       <c r="N66" t="n">
-        <v>-3733</v>
+        <v>471836</v>
       </c>
       <c r="O66" t="n">
-        <v>236448</v>
+        <v>-63042</v>
       </c>
       <c r="P66" t="n">
-        <v>-1862857</v>
+        <v>1443020</v>
       </c>
       <c r="Q66" t="n">
-        <v>182209</v>
+        <v>-218115</v>
       </c>
       <c r="R66" t="n">
-        <v>128495</v>
+        <v>-957044</v>
       </c>
       <c r="S66" t="n">
-        <v>591133</v>
+        <v>-1263685</v>
       </c>
       <c r="T66" t="n">
-        <v>-1737461</v>
+        <v>453603</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>324000</v>
       </c>
       <c r="V66" t="n">
-        <v>-37000</v>
+        <v>1455000</v>
       </c>
       <c r="W66" t="n">
-        <v>-56000</v>
+        <v>1455000</v>
       </c>
       <c r="X66" t="n">
-        <v>-74000</v>
+        <v>1489000</v>
       </c>
       <c r="Y66" t="n">
-        <v>51105</v>
+        <v>116165</v>
       </c>
       <c r="Z66" t="n">
-        <v>-95228</v>
+        <v>-26120</v>
       </c>
       <c r="AA66" t="n">
-        <v>-298685</v>
+        <v>-254357</v>
       </c>
       <c r="AB66" t="n">
-        <v>-51396</v>
+        <v>-499583</v>
       </c>
       <c r="AC66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE66" t="n">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="AF66" t="n">
-        <v>20</v>
+        <v>-10</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>-26</v>
+        <v>16</v>
       </c>
       <c r="AI66" t="n">
-        <v>32</v>
+        <v>-12</v>
       </c>
       <c r="AJ66" t="n">
-        <v>123.08</v>
+        <v>-75</v>
       </c>
       <c r="AK66" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AL66" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10956,29 +10956,29 @@
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>站上5日線、死亡交叉、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人小幅賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、死亡交叉、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、5日法人小幅賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5530.TWO</t>
+          <t>6230.TW</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>龍巖</t>
+          <t>超眾</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -10987,28 +10987,28 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>49.85</v>
+        <v>110.5</v>
       </c>
       <c r="E67" t="n">
-        <v>49.72</v>
+        <v>110.4</v>
       </c>
       <c r="F67" t="n">
-        <v>49.58</v>
+        <v>109.95</v>
       </c>
       <c r="G67" t="n">
-        <v>50.02</v>
+        <v>109.17</v>
       </c>
       <c r="H67" t="n">
-        <v>63000</v>
+        <v>67734</v>
       </c>
       <c r="I67" t="n">
-        <v>115400</v>
+        <v>162979</v>
       </c>
       <c r="J67" t="n">
-        <v>51.6</v>
+        <v>119</v>
       </c>
       <c r="K67" t="n">
-        <v>48.7</v>
+        <v>105.5</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -11016,28 +11016,28 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>13131</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>-28869</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>-12919</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>16223</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>12131</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>-29869</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>-13869</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>15119</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -11052,16 +11052,16 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1104</v>
       </c>
       <c r="AC67" t="n">
         <v>4</v>
@@ -11070,37 +11070,37 @@
         <v>4</v>
       </c>
       <c r="AE67" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI67" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="AK67" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL67" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -11115,29 +11115,29 @@
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>中期買超轉短線賣壓</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日低點、中期買超轉短線賣壓。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6230.TW</t>
+          <t>5530.TWO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>超眾</t>
+          <t>龍巖</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -11146,28 +11146,28 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>110.5</v>
+        <v>49.85</v>
       </c>
       <c r="E68" t="n">
-        <v>110.4</v>
+        <v>49.72</v>
       </c>
       <c r="F68" t="n">
-        <v>109.95</v>
+        <v>49.58</v>
       </c>
       <c r="G68" t="n">
-        <v>109.17</v>
+        <v>50.02</v>
       </c>
       <c r="H68" t="n">
-        <v>67734</v>
+        <v>63000</v>
       </c>
       <c r="I68" t="n">
-        <v>162979</v>
+        <v>115400</v>
       </c>
       <c r="J68" t="n">
-        <v>119</v>
+        <v>51.6</v>
       </c>
       <c r="K68" t="n">
-        <v>105.5</v>
+        <v>48.7</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -11175,28 +11175,28 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>13131</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>-28869</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>-12919</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>16223</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>12131</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>-29869</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>-13869</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>15119</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -11211,16 +11211,16 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1104</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>4</v>
@@ -11229,37 +11229,37 @@
         <v>4</v>
       </c>
       <c r="AE68" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AF68" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AI68" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ68" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="AK68" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL68" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -11274,29 +11274,29 @@
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日低點、中期買超轉短線賣壓。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2606.TW</t>
+          <t>3231.TW</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -11305,28 +11305,28 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>77</v>
+        <v>186.5</v>
       </c>
       <c r="E69" t="n">
-        <v>76.06</v>
+        <v>183.7</v>
       </c>
       <c r="F69" t="n">
-        <v>77.3</v>
+        <v>187.4</v>
       </c>
       <c r="G69" t="n">
-        <v>75.94</v>
+        <v>183.85</v>
       </c>
       <c r="H69" t="n">
-        <v>3653421</v>
+        <v>31292426</v>
       </c>
       <c r="I69" t="n">
-        <v>4381693</v>
+        <v>32860103</v>
       </c>
       <c r="J69" t="n">
-        <v>81.7</v>
+        <v>200.5</v>
       </c>
       <c r="K69" t="n">
-        <v>70</v>
+        <v>172.5</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -11334,91 +11334,91 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>222050</v>
+        <v>11571332</v>
       </c>
       <c r="N69" t="n">
-        <v>471836</v>
+        <v>1320974</v>
       </c>
       <c r="O69" t="n">
-        <v>-63042</v>
+        <v>-8559657</v>
       </c>
       <c r="P69" t="n">
-        <v>1443020</v>
+        <v>-60169097</v>
       </c>
       <c r="Q69" t="n">
-        <v>-218115</v>
+        <v>8826396</v>
       </c>
       <c r="R69" t="n">
-        <v>-957044</v>
+        <v>-2553004</v>
       </c>
       <c r="S69" t="n">
-        <v>-1263685</v>
+        <v>-12324778</v>
       </c>
       <c r="T69" t="n">
-        <v>453603</v>
+        <v>-72443795</v>
       </c>
       <c r="U69" t="n">
-        <v>324000</v>
+        <v>2001000</v>
       </c>
       <c r="V69" t="n">
-        <v>1455000</v>
+        <v>4968000</v>
       </c>
       <c r="W69" t="n">
-        <v>1455000</v>
+        <v>5146852</v>
       </c>
       <c r="X69" t="n">
-        <v>1489000</v>
+        <v>12509991</v>
       </c>
       <c r="Y69" t="n">
-        <v>116165</v>
+        <v>743936</v>
       </c>
       <c r="Z69" t="n">
-        <v>-26120</v>
+        <v>-1094022</v>
       </c>
       <c r="AA69" t="n">
-        <v>-254357</v>
+        <v>-1381731</v>
       </c>
       <c r="AB69" t="n">
-        <v>-499583</v>
+        <v>-235293</v>
       </c>
       <c r="AC69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE69" t="n">
         <v>20</v>
       </c>
       <c r="AF69" t="n">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>16</v>
+        <v>-30</v>
       </c>
       <c r="AI69" t="n">
-        <v>-12</v>
+        <v>32</v>
       </c>
       <c r="AJ69" t="n">
-        <v>-75</v>
+        <v>106.67</v>
       </c>
       <c r="AK69" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AL69" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>5日法人小幅賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、5日法人小幅賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -11609,12 +11609,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3231.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11623,28 +11623,28 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>186.5</v>
+        <v>48.8</v>
       </c>
       <c r="E71" t="n">
-        <v>183.7</v>
+        <v>48.27</v>
       </c>
       <c r="F71" t="n">
-        <v>187.4</v>
+        <v>44.34</v>
       </c>
       <c r="G71" t="n">
-        <v>183.85</v>
+        <v>41.64</v>
       </c>
       <c r="H71" t="n">
-        <v>31292426</v>
+        <v>56292754</v>
       </c>
       <c r="I71" t="n">
-        <v>32860103</v>
+        <v>47048857</v>
       </c>
       <c r="J71" t="n">
-        <v>200.5</v>
+        <v>54.5</v>
       </c>
       <c r="K71" t="n">
-        <v>172.5</v>
+        <v>37.15</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -11652,91 +11652,91 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>11571332</v>
+        <v>-355336</v>
       </c>
       <c r="N71" t="n">
-        <v>1320974</v>
+        <v>-2183470</v>
       </c>
       <c r="O71" t="n">
-        <v>-8559657</v>
+        <v>-4434262</v>
       </c>
       <c r="P71" t="n">
-        <v>-60169097</v>
+        <v>-5218488</v>
       </c>
       <c r="Q71" t="n">
-        <v>8826396</v>
+        <v>-39677</v>
       </c>
       <c r="R71" t="n">
-        <v>-2553004</v>
+        <v>-2223388</v>
       </c>
       <c r="S71" t="n">
-        <v>-12324778</v>
+        <v>-4762432</v>
       </c>
       <c r="T71" t="n">
-        <v>-72443795</v>
+        <v>-5519785</v>
       </c>
       <c r="U71" t="n">
-        <v>2001000</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>4968000</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>5146852</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>12509991</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>743936</v>
+        <v>-315659</v>
       </c>
       <c r="Z71" t="n">
-        <v>-1094022</v>
+        <v>39918</v>
       </c>
       <c r="AA71" t="n">
-        <v>-1381731</v>
+        <v>328170</v>
       </c>
       <c r="AB71" t="n">
-        <v>-235293</v>
+        <v>301297</v>
       </c>
       <c r="AC71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AF71" t="n">
-        <v>-15</v>
+        <v>-55</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
       <c r="AI71" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="AJ71" t="n">
-        <v>106.67</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="AL71" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11751,29 +11751,29 @@
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -11782,28 +11782,28 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>48.8</v>
+        <v>233</v>
       </c>
       <c r="E72" t="n">
-        <v>48.27</v>
+        <v>231.9</v>
       </c>
       <c r="F72" t="n">
-        <v>44.34</v>
+        <v>239.6</v>
       </c>
       <c r="G72" t="n">
-        <v>41.64</v>
+        <v>248.78</v>
       </c>
       <c r="H72" t="n">
-        <v>56292754</v>
+        <v>3066000</v>
       </c>
       <c r="I72" t="n">
-        <v>47048857</v>
+        <v>2455800</v>
       </c>
       <c r="J72" t="n">
-        <v>54.5</v>
+        <v>288</v>
       </c>
       <c r="K72" t="n">
-        <v>37.15</v>
+        <v>223</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -11811,28 +11811,28 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>-355336</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>-2183470</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>-4434262</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>-5218488</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>-39677</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>-2223388</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>-4762432</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>-5519785</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -11847,55 +11847,55 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>-315659</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>39918</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>328170</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>301297</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AE72" t="n">
-        <v>55</v>
+        <v>-5</v>
       </c>
       <c r="AF72" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AI72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ72" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK72" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="AL72" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11910,29 +11910,29 @@
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>4979.TWO</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -11941,28 +11941,28 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>233</v>
+        <v>556</v>
       </c>
       <c r="E73" t="n">
-        <v>231.9</v>
+        <v>538</v>
       </c>
       <c r="F73" t="n">
-        <v>239.6</v>
+        <v>569.5</v>
       </c>
       <c r="G73" t="n">
-        <v>248.78</v>
+        <v>582.5</v>
       </c>
       <c r="H73" t="n">
-        <v>3066000</v>
+        <v>982000</v>
       </c>
       <c r="I73" t="n">
-        <v>2455800</v>
+        <v>1372800</v>
       </c>
       <c r="J73" t="n">
-        <v>288</v>
+        <v>658</v>
       </c>
       <c r="K73" t="n">
-        <v>223</v>
+        <v>501</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -12042,19 +12042,19 @@
         <v>0</v>
       </c>
       <c r="AK73" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="AL73" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大</t>
+          <t>DT尚未轉強、5MA乖離尚可</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
@@ -12079,19 +12079,19 @@
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4979.TWO</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -12100,28 +12100,28 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>556</v>
+        <v>478.5</v>
       </c>
       <c r="E74" t="n">
-        <v>538</v>
+        <v>494.7</v>
       </c>
       <c r="F74" t="n">
-        <v>569.5</v>
+        <v>505.55</v>
       </c>
       <c r="G74" t="n">
-        <v>582.5</v>
+        <v>493.15</v>
       </c>
       <c r="H74" t="n">
-        <v>982000</v>
+        <v>31177000</v>
       </c>
       <c r="I74" t="n">
-        <v>1372800</v>
+        <v>25483800</v>
       </c>
       <c r="J74" t="n">
-        <v>658</v>
+        <v>564</v>
       </c>
       <c r="K74" t="n">
-        <v>501</v>
+        <v>399</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -12177,13 +12177,13 @@
         <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AD74" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AE74" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="AF74" t="n">
         <v>0</v>
@@ -12192,19 +12192,19 @@
         <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>-2</v>
+        <v>12</v>
       </c>
       <c r="AI74" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0</v>
+        <v>-133.33</v>
       </c>
       <c r="AK74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AL74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
@@ -12238,19 +12238,19 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>3363.TWO</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -12259,28 +12259,28 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>478.5</v>
+        <v>655</v>
       </c>
       <c r="E75" t="n">
-        <v>494.7</v>
+        <v>668.6</v>
       </c>
       <c r="F75" t="n">
-        <v>505.55</v>
+        <v>693.4</v>
       </c>
       <c r="G75" t="n">
-        <v>493.15</v>
+        <v>693.3</v>
       </c>
       <c r="H75" t="n">
-        <v>31177000</v>
+        <v>4183000</v>
       </c>
       <c r="I75" t="n">
-        <v>25483800</v>
+        <v>2945400</v>
       </c>
       <c r="J75" t="n">
-        <v>564</v>
+        <v>850</v>
       </c>
       <c r="K75" t="n">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -12360,10 +12360,10 @@
         <v>-133.33</v>
       </c>
       <c r="AK75" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL75" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -12404,12 +12404,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3363.TWO</t>
+          <t>4938.TW</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -12418,28 +12418,28 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>655</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>668.6</v>
+        <v>89.78</v>
       </c>
       <c r="F76" t="n">
-        <v>693.4</v>
+        <v>91.17</v>
       </c>
       <c r="G76" t="n">
-        <v>693.3</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>4183000</v>
+        <v>7287528</v>
       </c>
       <c r="I76" t="n">
-        <v>2945400</v>
+        <v>6476242</v>
       </c>
       <c r="J76" t="n">
-        <v>850</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>549</v>
+        <v>87.3</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -12447,52 +12447,52 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>1576591</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>-1380462</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>-3213476</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>-2240446</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>1329003</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>-866501</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>-3638401</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>-10080783</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>294000</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>60845</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>379845</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>7767664</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>-46412</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>-574806</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>45080</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>72673</v>
       </c>
       <c r="AC76" t="n">
         <v>-4</v>
@@ -12501,37 +12501,37 @@
         <v>-4</v>
       </c>
       <c r="AE76" t="n">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>12</v>
+        <v>-30</v>
       </c>
       <c r="AI76" t="n">
-        <v>-16</v>
+        <v>26</v>
       </c>
       <c r="AJ76" t="n">
-        <v>-133.33</v>
+        <v>86.67</v>
       </c>
       <c r="AK76" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL76" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、分數升溫過快</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -12546,17 +12546,17 @@
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>站上5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -12722,12 +12722,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4938.TW</t>
+          <t>8028.TW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -12736,28 +12736,28 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>90.40000000000001</v>
+        <v>244</v>
       </c>
       <c r="E78" t="n">
-        <v>89.78</v>
+        <v>230.1</v>
       </c>
       <c r="F78" t="n">
-        <v>91.17</v>
+        <v>234.1</v>
       </c>
       <c r="G78" t="n">
-        <v>90.48999999999999</v>
+        <v>239.5</v>
       </c>
       <c r="H78" t="n">
-        <v>7287528</v>
+        <v>9261432</v>
       </c>
       <c r="I78" t="n">
-        <v>6476242</v>
+        <v>4278246</v>
       </c>
       <c r="J78" t="n">
-        <v>95.59999999999999</v>
+        <v>256</v>
       </c>
       <c r="K78" t="n">
-        <v>87.3</v>
+        <v>216.5</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -12765,61 +12765,61 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>1576591</v>
+        <v>178711</v>
       </c>
       <c r="N78" t="n">
-        <v>-1380462</v>
+        <v>-511398</v>
       </c>
       <c r="O78" t="n">
-        <v>-3213476</v>
+        <v>-1111167</v>
       </c>
       <c r="P78" t="n">
-        <v>-2240446</v>
+        <v>-4860365</v>
       </c>
       <c r="Q78" t="n">
-        <v>1329003</v>
+        <v>-1870975</v>
       </c>
       <c r="R78" t="n">
-        <v>-866501</v>
+        <v>-4586613</v>
       </c>
       <c r="S78" t="n">
-        <v>-3638401</v>
+        <v>-5629606</v>
       </c>
       <c r="T78" t="n">
-        <v>-10080783</v>
+        <v>-10129967</v>
       </c>
       <c r="U78" t="n">
-        <v>294000</v>
+        <v>1971000</v>
       </c>
       <c r="V78" t="n">
-        <v>60845</v>
+        <v>3955000</v>
       </c>
       <c r="W78" t="n">
-        <v>379845</v>
+        <v>4415000</v>
       </c>
       <c r="X78" t="n">
-        <v>7767664</v>
+        <v>5259000</v>
       </c>
       <c r="Y78" t="n">
-        <v>-46412</v>
+        <v>78686</v>
       </c>
       <c r="Z78" t="n">
-        <v>-574806</v>
+        <v>120215</v>
       </c>
       <c r="AA78" t="n">
-        <v>45080</v>
+        <v>103439</v>
       </c>
       <c r="AB78" t="n">
-        <v>72673</v>
+        <v>10602</v>
       </c>
       <c r="AC78" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="AD78" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="AE78" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AF78" t="n">
         <v>-30</v>
@@ -12828,28 +12828,28 @@
         <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="AI78" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="AJ78" t="n">
-        <v>86.67</v>
+        <v>40</v>
       </c>
       <c r="AK78" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AL78" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數升溫過快</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能偏強、分數剛升溫</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、爆量</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
@@ -12874,49 +12874,49 @@
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、爆量、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8028.TW</t>
+          <t>00878.TW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>244</v>
+        <v>34.73</v>
       </c>
       <c r="E79" t="n">
-        <v>230.1</v>
+        <v>34.33</v>
       </c>
       <c r="F79" t="n">
-        <v>234.1</v>
+        <v>34.25</v>
       </c>
       <c r="G79" t="n">
-        <v>239.5</v>
+        <v>33.63</v>
       </c>
       <c r="H79" t="n">
-        <v>9261432</v>
+        <v>26931022</v>
       </c>
       <c r="I79" t="n">
-        <v>4278246</v>
+        <v>33329260</v>
       </c>
       <c r="J79" t="n">
-        <v>256</v>
+        <v>34.91</v>
       </c>
       <c r="K79" t="n">
-        <v>216.5</v>
+        <v>31.99</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -12924,52 +12924,52 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>178711</v>
+        <v>10184608</v>
       </c>
       <c r="N79" t="n">
-        <v>-511398</v>
+        <v>-12744419</v>
       </c>
       <c r="O79" t="n">
-        <v>-1111167</v>
+        <v>-26384918</v>
       </c>
       <c r="P79" t="n">
-        <v>-4860365</v>
+        <v>28418963</v>
       </c>
       <c r="Q79" t="n">
-        <v>-1870975</v>
+        <v>3003312</v>
       </c>
       <c r="R79" t="n">
-        <v>-4586613</v>
+        <v>-13111345</v>
       </c>
       <c r="S79" t="n">
-        <v>-5629606</v>
+        <v>-28712633</v>
       </c>
       <c r="T79" t="n">
-        <v>-10129967</v>
+        <v>-17893162</v>
       </c>
       <c r="U79" t="n">
-        <v>1971000</v>
+        <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>3955000</v>
+        <v>-200000</v>
       </c>
       <c r="W79" t="n">
-        <v>4415000</v>
+        <v>-200000</v>
       </c>
       <c r="X79" t="n">
-        <v>5259000</v>
+        <v>-300000</v>
       </c>
       <c r="Y79" t="n">
-        <v>78686</v>
+        <v>7181296</v>
       </c>
       <c r="Z79" t="n">
-        <v>120215</v>
+        <v>566926</v>
       </c>
       <c r="AA79" t="n">
-        <v>103439</v>
+        <v>2527715</v>
       </c>
       <c r="AB79" t="n">
-        <v>10602</v>
+        <v>46612125</v>
       </c>
       <c r="AC79" t="n">
         <v>-6</v>
@@ -12978,37 +12978,37 @@
         <v>-6</v>
       </c>
       <c r="AE79" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="AF79" t="n">
-        <v>-30</v>
+        <v>-75</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="AI79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK79" t="n">
         <v>40</v>
       </c>
-      <c r="AK79" t="n">
-        <v>46</v>
-      </c>
       <c r="AL79" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能偏強、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -13023,17 +13023,17 @@
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、爆量</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、爆量、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -13358,42 +13358,42 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>00878.TW</t>
+          <t>4903.TWO</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>34.73</v>
+        <v>34.2</v>
       </c>
       <c r="E82" t="n">
-        <v>34.33</v>
+        <v>34.14</v>
       </c>
       <c r="F82" t="n">
-        <v>34.25</v>
+        <v>35.2</v>
       </c>
       <c r="G82" t="n">
-        <v>33.63</v>
+        <v>35.91</v>
       </c>
       <c r="H82" t="n">
-        <v>26931022</v>
+        <v>473000</v>
       </c>
       <c r="I82" t="n">
-        <v>33329260</v>
+        <v>1100400</v>
       </c>
       <c r="J82" t="n">
-        <v>34.91</v>
+        <v>39.15</v>
       </c>
       <c r="K82" t="n">
-        <v>31.99</v>
+        <v>33.15</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -13401,52 +13401,52 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>10184608</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>-12744419</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>-26384918</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>28418963</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3003312</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>-13111345</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>-28712633</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>-17893162</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>-200000</v>
+        <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>-200000</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>-300000</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>7181296</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>566926</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2527715</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>46612125</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>-6</v>
@@ -13455,37 +13455,37 @@
         <v>-6</v>
       </c>
       <c r="AE82" t="n">
-        <v>60</v>
+        <v>-15</v>
       </c>
       <c r="AF82" t="n">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>-6</v>
+        <v>-22</v>
       </c>
       <c r="AI82" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="AK82" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AL82" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -13500,29 +13500,29 @@
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4903.TWO</t>
+          <t>1714.TW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>和桐</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -13531,28 +13531,28 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>34.2</v>
+        <v>16.05</v>
       </c>
       <c r="E83" t="n">
-        <v>34.14</v>
+        <v>15.42</v>
       </c>
       <c r="F83" t="n">
-        <v>35.2</v>
+        <v>15.97</v>
       </c>
       <c r="G83" t="n">
-        <v>35.91</v>
+        <v>16.45</v>
       </c>
       <c r="H83" t="n">
-        <v>473000</v>
+        <v>10370991</v>
       </c>
       <c r="I83" t="n">
-        <v>1100400</v>
+        <v>10863223</v>
       </c>
       <c r="J83" t="n">
-        <v>39.15</v>
+        <v>18.55</v>
       </c>
       <c r="K83" t="n">
-        <v>33.15</v>
+        <v>14.65</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -13560,28 +13560,28 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>2506361</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1785799</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>-2370693</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>-6054027</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>2497270</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1673488</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>-2265696</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>-6014741</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -13593,58 +13593,58 @@
         <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>-38000</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>9091</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>112311</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>-104997</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>-1286</v>
       </c>
       <c r="AC83" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AD83" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AE83" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF83" t="n">
         <v>-15</v>
       </c>
-      <c r="AF83" t="n">
-        <v>0</v>
-      </c>
       <c r="AG83" t="n">
         <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>-22</v>
+        <v>-8</v>
       </c>
       <c r="AI83" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>72.73</v>
+        <v>0</v>
       </c>
       <c r="AK83" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="AL83" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -13659,17 +13659,17 @@
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14312,12 +14312,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1714.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>和桐</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -14326,57 +14326,57 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>16.05</v>
+        <v>1320</v>
       </c>
       <c r="E88" t="n">
-        <v>15.42</v>
+        <v>1376</v>
       </c>
       <c r="F88" t="n">
-        <v>15.97</v>
+        <v>1370</v>
       </c>
       <c r="G88" t="n">
-        <v>16.45</v>
+        <v>1412</v>
       </c>
       <c r="H88" t="n">
-        <v>10370991</v>
+        <v>22637000</v>
       </c>
       <c r="I88" t="n">
-        <v>10863223</v>
+        <v>9695800</v>
       </c>
       <c r="J88" t="n">
-        <v>18.55</v>
+        <v>1580</v>
       </c>
       <c r="K88" t="n">
-        <v>14.65</v>
+        <v>1275</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>2506361</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1785799</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>-2370693</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>-6054027</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>2497270</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>1673488</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>-2265696</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>-6014741</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -14388,19 +14388,19 @@
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>-38000</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>9091</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>112311</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>-104997</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>-1286</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>-8</v>
@@ -14409,28 +14409,28 @@
         <v>-8</v>
       </c>
       <c r="AE88" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="AF88" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AH88" t="n">
-        <v>-8</v>
+        <v>12</v>
       </c>
       <c r="AI88" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0</v>
+        <v>-166.67</v>
       </c>
       <c r="AK88" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AL88" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -14454,29 +14454,29 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、爆量、接近20日低點、爆量價未漲</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、爆量、接近20日低點、爆量價未漲、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>6770.TW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -14485,120 +14485,120 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1320</v>
+        <v>71.2</v>
       </c>
       <c r="E89" t="n">
-        <v>1376</v>
+        <v>69.88</v>
       </c>
       <c r="F89" t="n">
-        <v>1370</v>
+        <v>70.91</v>
       </c>
       <c r="G89" t="n">
-        <v>1412</v>
+        <v>70.45</v>
       </c>
       <c r="H89" t="n">
-        <v>22637000</v>
+        <v>119460580</v>
       </c>
       <c r="I89" t="n">
-        <v>9695800</v>
+        <v>119091588</v>
       </c>
       <c r="J89" t="n">
-        <v>1580</v>
+        <v>75.3</v>
       </c>
       <c r="K89" t="n">
-        <v>1275</v>
+        <v>66.5</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>36050024</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>6435761</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>-28813075</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>112207065</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>32652611</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3214983</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>-28511510</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>99438701</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>-13000</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>462000</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>451000</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>7832000</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>3410413</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>2758778</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>-752565</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>4936364</v>
       </c>
       <c r="AC89" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="AD89" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="AE89" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AG89" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>12</v>
+        <v>-30</v>
       </c>
       <c r="AI89" t="n">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="AJ89" t="n">
-        <v>-166.67</v>
+        <v>66.67</v>
       </c>
       <c r="AK89" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL89" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -14613,29 +14613,29 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>跌破5日線、爆量、接近20日低點、爆量價未漲</t>
+          <t>站上5日線、死亡交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、爆量、接近20日低點、爆量價未漲、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、死亡交叉、量能溫和放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6770.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -14644,28 +14644,28 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>71.2</v>
+        <v>13.95</v>
       </c>
       <c r="E90" t="n">
-        <v>69.88</v>
+        <v>13.94</v>
       </c>
       <c r="F90" t="n">
-        <v>70.91</v>
+        <v>14.16</v>
       </c>
       <c r="G90" t="n">
-        <v>70.45</v>
+        <v>14.21</v>
       </c>
       <c r="H90" t="n">
-        <v>119460580</v>
+        <v>18960049</v>
       </c>
       <c r="I90" t="n">
-        <v>119091588</v>
+        <v>20733511</v>
       </c>
       <c r="J90" t="n">
-        <v>75.3</v>
+        <v>15.15</v>
       </c>
       <c r="K90" t="n">
-        <v>66.5</v>
+        <v>13.6</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -14673,91 +14673,91 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>36050024</v>
+        <v>-1137444</v>
       </c>
       <c r="N90" t="n">
-        <v>6435761</v>
+        <v>3637996</v>
       </c>
       <c r="O90" t="n">
-        <v>-28813075</v>
+        <v>-10316254</v>
       </c>
       <c r="P90" t="n">
-        <v>112207065</v>
+        <v>-3717823</v>
       </c>
       <c r="Q90" t="n">
-        <v>32652611</v>
+        <v>-687897</v>
       </c>
       <c r="R90" t="n">
-        <v>3214983</v>
+        <v>3689978</v>
       </c>
       <c r="S90" t="n">
-        <v>-28511510</v>
+        <v>-10080555</v>
       </c>
       <c r="T90" t="n">
-        <v>99438701</v>
+        <v>-3508498</v>
       </c>
       <c r="U90" t="n">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>462000</v>
+        <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>451000</v>
+        <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>7832000</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>3410413</v>
+        <v>-449547</v>
       </c>
       <c r="Z90" t="n">
-        <v>2758778</v>
+        <v>-51982</v>
       </c>
       <c r="AA90" t="n">
-        <v>-752565</v>
+        <v>-235699</v>
       </c>
       <c r="AB90" t="n">
-        <v>4936364</v>
+        <v>-209325</v>
       </c>
       <c r="AC90" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="AD90" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="AE90" t="n">
-        <v>5</v>
+        <v>-15</v>
       </c>
       <c r="AF90" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>-30</v>
+        <v>-12</v>
       </c>
       <c r="AI90" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AJ90" t="n">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="AK90" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AL90" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -14772,17 +14772,17 @@
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>站上5日線、死亡交叉、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、死亡交叉、量能溫和放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14948,12 +14948,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -14962,28 +14962,28 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.95</v>
+        <v>274.5</v>
       </c>
       <c r="E92" t="n">
-        <v>13.94</v>
+        <v>272.3</v>
       </c>
       <c r="F92" t="n">
-        <v>14.16</v>
+        <v>275.8</v>
       </c>
       <c r="G92" t="n">
-        <v>14.21</v>
+        <v>276.62</v>
       </c>
       <c r="H92" t="n">
-        <v>18960049</v>
+        <v>13168497</v>
       </c>
       <c r="I92" t="n">
-        <v>20733511</v>
+        <v>9521475</v>
       </c>
       <c r="J92" t="n">
-        <v>15.15</v>
+        <v>298</v>
       </c>
       <c r="K92" t="n">
-        <v>13.6</v>
+        <v>259</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -14991,52 +14991,52 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>-1137444</v>
+        <v>1385170</v>
       </c>
       <c r="N92" t="n">
-        <v>3637996</v>
+        <v>1628700</v>
       </c>
       <c r="O92" t="n">
-        <v>-10316254</v>
+        <v>-4150871</v>
       </c>
       <c r="P92" t="n">
-        <v>-3717823</v>
+        <v>-2019046</v>
       </c>
       <c r="Q92" t="n">
-        <v>-687897</v>
+        <v>1275987</v>
       </c>
       <c r="R92" t="n">
-        <v>3689978</v>
+        <v>2241274</v>
       </c>
       <c r="S92" t="n">
-        <v>-10080555</v>
+        <v>-2291388</v>
       </c>
       <c r="T92" t="n">
-        <v>-3508498</v>
+        <v>468534</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>-819000</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>-1781000</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>-1992588</v>
       </c>
       <c r="Y92" t="n">
-        <v>-449547</v>
+        <v>113183</v>
       </c>
       <c r="Z92" t="n">
-        <v>-51982</v>
+        <v>206426</v>
       </c>
       <c r="AA92" t="n">
-        <v>-235699</v>
+        <v>-78483</v>
       </c>
       <c r="AB92" t="n">
-        <v>-209325</v>
+        <v>-494992</v>
       </c>
       <c r="AC92" t="n">
         <v>-12</v>
@@ -15045,37 +15045,37 @@
         <v>-12</v>
       </c>
       <c r="AE92" t="n">
-        <v>-15</v>
+        <v>5</v>
       </c>
       <c r="AF92" t="n">
-        <v>-15</v>
+        <v>-35</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="AI92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ92" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK92" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AL92" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -15090,29 +15090,29 @@
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>2401.TW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>凌陽</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -15121,28 +15121,28 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>274.5</v>
+        <v>24.75</v>
       </c>
       <c r="E93" t="n">
-        <v>272.3</v>
+        <v>24.25</v>
       </c>
       <c r="F93" t="n">
-        <v>275.8</v>
+        <v>24.74</v>
       </c>
       <c r="G93" t="n">
-        <v>276.62</v>
+        <v>25.08</v>
       </c>
       <c r="H93" t="n">
-        <v>13168497</v>
+        <v>2242550</v>
       </c>
       <c r="I93" t="n">
-        <v>9521475</v>
+        <v>1912619</v>
       </c>
       <c r="J93" t="n">
-        <v>298</v>
+        <v>26.4</v>
       </c>
       <c r="K93" t="n">
-        <v>259</v>
+        <v>23.7</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -15150,91 +15150,91 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>1385170</v>
+        <v>298824</v>
       </c>
       <c r="N93" t="n">
-        <v>1628700</v>
+        <v>-9319</v>
       </c>
       <c r="O93" t="n">
-        <v>-4150871</v>
+        <v>-639525</v>
       </c>
       <c r="P93" t="n">
-        <v>-2019046</v>
+        <v>-1376047</v>
       </c>
       <c r="Q93" t="n">
-        <v>1275987</v>
+        <v>281825</v>
       </c>
       <c r="R93" t="n">
-        <v>2241274</v>
+        <v>-18545</v>
       </c>
       <c r="S93" t="n">
-        <v>-2291388</v>
+        <v>-445501</v>
       </c>
       <c r="T93" t="n">
-        <v>468534</v>
+        <v>-1194887</v>
       </c>
       <c r="U93" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>-819000</v>
+        <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>-1781000</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>-1992588</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>113183</v>
+        <v>16999</v>
       </c>
       <c r="Z93" t="n">
-        <v>206426</v>
+        <v>9226</v>
       </c>
       <c r="AA93" t="n">
-        <v>-78483</v>
+        <v>-194024</v>
       </c>
       <c r="AB93" t="n">
-        <v>-494992</v>
+        <v>-181160</v>
       </c>
       <c r="AC93" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="AD93" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="AE93" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AF93" t="n">
-        <v>-35</v>
+        <v>-30</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="AI93" t="n">
         <v>4</v>
       </c>
       <c r="AJ93" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="AK93" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="AL93" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、分數剛升溫</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -15249,29 +15249,29 @@
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2401.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>凌陽</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -15280,28 +15280,28 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>24.75</v>
+        <v>31</v>
       </c>
       <c r="E94" t="n">
-        <v>24.25</v>
+        <v>30.87</v>
       </c>
       <c r="F94" t="n">
-        <v>24.74</v>
+        <v>31.38</v>
       </c>
       <c r="G94" t="n">
-        <v>25.08</v>
+        <v>31.68</v>
       </c>
       <c r="H94" t="n">
-        <v>2242550</v>
+        <v>8741145</v>
       </c>
       <c r="I94" t="n">
-        <v>1912619</v>
+        <v>8667060</v>
       </c>
       <c r="J94" t="n">
-        <v>26.4</v>
+        <v>33.7</v>
       </c>
       <c r="K94" t="n">
-        <v>23.7</v>
+        <v>30</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -15309,52 +15309,52 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>298824</v>
+        <v>1351240</v>
       </c>
       <c r="N94" t="n">
-        <v>-9319</v>
+        <v>-2741464</v>
       </c>
       <c r="O94" t="n">
-        <v>-639525</v>
+        <v>-2633352</v>
       </c>
       <c r="P94" t="n">
-        <v>-1376047</v>
+        <v>-5646202</v>
       </c>
       <c r="Q94" t="n">
-        <v>281825</v>
+        <v>1584468</v>
       </c>
       <c r="R94" t="n">
-        <v>-18545</v>
+        <v>-2081696</v>
       </c>
       <c r="S94" t="n">
-        <v>-445501</v>
+        <v>-1848439</v>
       </c>
       <c r="T94" t="n">
-        <v>-1194887</v>
+        <v>-4597247</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>293000</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>333000</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>353000</v>
       </c>
       <c r="Y94" t="n">
-        <v>16999</v>
+        <v>-233228</v>
       </c>
       <c r="Z94" t="n">
-        <v>9226</v>
+        <v>-952768</v>
       </c>
       <c r="AA94" t="n">
-        <v>-194024</v>
+        <v>-1117913</v>
       </c>
       <c r="AB94" t="n">
-        <v>-181160</v>
+        <v>-1401955</v>
       </c>
       <c r="AC94" t="n">
         <v>-14</v>
@@ -15372,28 +15372,28 @@
         <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>-18</v>
+        <v>-24</v>
       </c>
       <c r="AI94" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AJ94" t="n">
-        <v>22.22</v>
+        <v>41.67</v>
       </c>
       <c r="AK94" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="AL94" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -15413,24 +15413,24 @@
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>3017.TW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -15439,28 +15439,28 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>31</v>
+        <v>3185</v>
       </c>
       <c r="E95" t="n">
-        <v>30.87</v>
+        <v>3231</v>
       </c>
       <c r="F95" t="n">
-        <v>31.38</v>
+        <v>3327</v>
       </c>
       <c r="G95" t="n">
-        <v>31.68</v>
+        <v>3262</v>
       </c>
       <c r="H95" t="n">
-        <v>8741145</v>
+        <v>3034388</v>
       </c>
       <c r="I95" t="n">
-        <v>8667060</v>
+        <v>2664732</v>
       </c>
       <c r="J95" t="n">
-        <v>33.7</v>
+        <v>3595</v>
       </c>
       <c r="K95" t="n">
-        <v>30</v>
+        <v>2740</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -15468,52 +15468,52 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>1351240</v>
+        <v>-87913</v>
       </c>
       <c r="N95" t="n">
-        <v>-2741464</v>
+        <v>254601</v>
       </c>
       <c r="O95" t="n">
-        <v>-2633352</v>
+        <v>30233</v>
       </c>
       <c r="P95" t="n">
-        <v>-5646202</v>
+        <v>493922</v>
       </c>
       <c r="Q95" t="n">
-        <v>1584468</v>
+        <v>-154755</v>
       </c>
       <c r="R95" t="n">
-        <v>-2081696</v>
+        <v>145473</v>
       </c>
       <c r="S95" t="n">
-        <v>-1848439</v>
+        <v>115861</v>
       </c>
       <c r="T95" t="n">
-        <v>-4597247</v>
+        <v>529500</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>11229</v>
       </c>
       <c r="V95" t="n">
-        <v>293000</v>
+        <v>45229</v>
       </c>
       <c r="W95" t="n">
-        <v>333000</v>
+        <v>-93008</v>
       </c>
       <c r="X95" t="n">
-        <v>353000</v>
+        <v>13080</v>
       </c>
       <c r="Y95" t="n">
-        <v>-233228</v>
+        <v>55613</v>
       </c>
       <c r="Z95" t="n">
-        <v>-952768</v>
+        <v>63899</v>
       </c>
       <c r="AA95" t="n">
-        <v>-1117913</v>
+        <v>7380</v>
       </c>
       <c r="AB95" t="n">
-        <v>-1401955</v>
+        <v>-48658</v>
       </c>
       <c r="AC95" t="n">
         <v>-14</v>
@@ -15522,37 +15522,37 @@
         <v>-14</v>
       </c>
       <c r="AE95" t="n">
-        <v>-5</v>
+        <v>-35</v>
       </c>
       <c r="AF95" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
       </c>
       <c r="AH95" t="n">
-        <v>-24</v>
+        <v>4</v>
       </c>
       <c r="AI95" t="n">
-        <v>10</v>
+        <v>-18</v>
       </c>
       <c r="AJ95" t="n">
-        <v>41.67</v>
+        <v>-450</v>
       </c>
       <c r="AK95" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AL95" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -15567,29 +15567,29 @@
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、死亡交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性、外資買投信賣</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、死亡交叉、量能溫和放大、籌碼中性、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3017.TW</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -15598,28 +15598,28 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3185</v>
+        <v>360.5</v>
       </c>
       <c r="E96" t="n">
-        <v>3231</v>
+        <v>363.2</v>
       </c>
       <c r="F96" t="n">
-        <v>3327</v>
+        <v>370.25</v>
       </c>
       <c r="G96" t="n">
-        <v>3262</v>
+        <v>371.55</v>
       </c>
       <c r="H96" t="n">
-        <v>3034388</v>
+        <v>2360000</v>
       </c>
       <c r="I96" t="n">
-        <v>2664732</v>
+        <v>2223800</v>
       </c>
       <c r="J96" t="n">
-        <v>3595</v>
+        <v>414.5</v>
       </c>
       <c r="K96" t="n">
-        <v>2740</v>
+        <v>315.5</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -15627,52 +15627,52 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>-87913</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>254601</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>30233</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>493922</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>-154755</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>145473</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>115861</v>
+        <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>529500</v>
+        <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>11229</v>
+        <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>45229</v>
+        <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>-93008</v>
+        <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>13080</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>55613</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>63899</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>7380</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>-48658</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>-14</v>
@@ -15690,13 +15690,13 @@
         <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AI96" t="n">
-        <v>-18</v>
+        <v>-26</v>
       </c>
       <c r="AJ96" t="n">
-        <v>-450</v>
+        <v>-216.67</v>
       </c>
       <c r="AK96" t="n">
         <v>0</v>
@@ -15726,17 +15726,17 @@
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>跌破5日線、死亡交叉、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>籌碼中性、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、死亡交叉、量能溫和放大、籌碼中性、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>43680549</v>
+        <v>45569549</v>
       </c>
       <c r="N4" t="n">
-        <v>96268361</v>
+        <v>98157361</v>
       </c>
       <c r="O4" t="n">
-        <v>99967383</v>
+        <v>101856383</v>
       </c>
       <c r="P4" t="n">
-        <v>115552552</v>
+        <v>117441552</v>
       </c>
       <c r="Q4" t="n">
         <v>28365568</v>
@@ -1031,16 +1031,16 @@
         <v>9639042</v>
       </c>
       <c r="U4" t="n">
-        <v>11741188</v>
+        <v>13630188</v>
       </c>
       <c r="V4" t="n">
-        <v>43560188</v>
+        <v>45449188</v>
       </c>
       <c r="W4" t="n">
-        <v>57430667</v>
+        <v>59319667</v>
       </c>
       <c r="X4" t="n">
-        <v>96268212</v>
+        <v>98157212</v>
       </c>
       <c r="Y4" t="n">
         <v>3573793</v>
@@ -4505,16 +4505,16 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>37328314</v>
+        <v>37311314</v>
       </c>
       <c r="N26" t="n">
-        <v>46472475</v>
+        <v>46455475</v>
       </c>
       <c r="O26" t="n">
-        <v>25024200</v>
+        <v>25007200</v>
       </c>
       <c r="P26" t="n">
-        <v>53535988</v>
+        <v>53518988</v>
       </c>
       <c r="Q26" t="n">
         <v>32233006</v>
@@ -4529,16 +4529,16 @@
         <v>51817904</v>
       </c>
       <c r="U26" t="n">
-        <v>3994574</v>
+        <v>3977574</v>
       </c>
       <c r="V26" t="n">
-        <v>5371574</v>
+        <v>5354574</v>
       </c>
       <c r="W26" t="n">
-        <v>306574</v>
+        <v>289574</v>
       </c>
       <c r="X26" t="n">
-        <v>123137</v>
+        <v>106137</v>
       </c>
       <c r="Y26" t="n">
         <v>1100734</v>
@@ -11342,16 +11342,16 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>-478375</v>
+        <v>-379375</v>
       </c>
       <c r="N69" t="n">
-        <v>-502042</v>
+        <v>-403042</v>
       </c>
       <c r="O69" t="n">
-        <v>-349924</v>
+        <v>-250924</v>
       </c>
       <c r="P69" t="n">
-        <v>-347147</v>
+        <v>-248147</v>
       </c>
       <c r="Q69" t="n">
         <v>-515777</v>
@@ -11366,16 +11366,16 @@
         <v>-1236204</v>
       </c>
       <c r="U69" t="n">
-        <v>-8453</v>
+        <v>90547</v>
       </c>
       <c r="V69" t="n">
-        <v>453047</v>
+        <v>552047</v>
       </c>
       <c r="W69" t="n">
-        <v>901647</v>
+        <v>1000647</v>
       </c>
       <c r="X69" t="n">
-        <v>1060679</v>
+        <v>1159679</v>
       </c>
       <c r="Y69" t="n">
         <v>45855</v>
@@ -11458,12 +11458,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>6275.TWO</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -11472,28 +11472,28 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>41.75</v>
+        <v>45.1</v>
       </c>
       <c r="E70" t="n">
-        <v>41.67</v>
+        <v>45.04</v>
       </c>
       <c r="F70" t="n">
-        <v>41.96</v>
+        <v>45.31</v>
       </c>
       <c r="G70" t="n">
-        <v>42.19</v>
+        <v>44.44</v>
       </c>
       <c r="H70" t="n">
-        <v>33904689</v>
+        <v>129000</v>
       </c>
       <c r="I70" t="n">
-        <v>18576579</v>
+        <v>107400</v>
       </c>
       <c r="J70" t="n">
-        <v>43.6</v>
+        <v>48.9</v>
       </c>
       <c r="K70" t="n">
-        <v>40.85</v>
+        <v>39.5</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -11501,52 +11501,52 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>-1736504</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4347841</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>1361784</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>11257711</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>-11354448</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>-10304291</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>-15044921</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>-6848454</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>9293811</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>14035396</v>
+        <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>16024500</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>18134041</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>324133</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>616736</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>382205</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>-27876</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>12</v>
@@ -11555,37 +11555,37 @@
         <v>12</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF70" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AI70" t="n">
-        <v>-18</v>
+        <v>4</v>
       </c>
       <c r="AJ70" t="n">
-        <v>-60</v>
+        <v>50</v>
       </c>
       <c r="AK70" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="AL70" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -11600,29 +11600,29 @@
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大、接近20日低點</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、成交量放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2801.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>彰銀</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11631,28 +11631,28 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>28.95</v>
+        <v>41.75</v>
       </c>
       <c r="E71" t="n">
-        <v>28.8</v>
+        <v>41.67</v>
       </c>
       <c r="F71" t="n">
-        <v>27.93</v>
+        <v>41.96</v>
       </c>
       <c r="G71" t="n">
-        <v>26.49</v>
+        <v>42.19</v>
       </c>
       <c r="H71" t="n">
-        <v>45992866</v>
+        <v>33904689</v>
       </c>
       <c r="I71" t="n">
-        <v>47025787</v>
+        <v>18576579</v>
       </c>
       <c r="J71" t="n">
-        <v>29.75</v>
+        <v>43.6</v>
       </c>
       <c r="K71" t="n">
-        <v>23.75</v>
+        <v>40.85</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -11660,52 +11660,52 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>-10533748</v>
+        <v>-1736504</v>
       </c>
       <c r="N71" t="n">
-        <v>4834338</v>
+        <v>4347841</v>
       </c>
       <c r="O71" t="n">
-        <v>-11626581</v>
+        <v>1361784</v>
       </c>
       <c r="P71" t="n">
-        <v>-8625450</v>
+        <v>11257711</v>
       </c>
       <c r="Q71" t="n">
-        <v>-11776156</v>
+        <v>-11354448</v>
       </c>
       <c r="R71" t="n">
-        <v>-18604121</v>
+        <v>-10304291</v>
       </c>
       <c r="S71" t="n">
-        <v>-44756022</v>
+        <v>-15044921</v>
       </c>
       <c r="T71" t="n">
-        <v>-69206723</v>
+        <v>-6848454</v>
       </c>
       <c r="U71" t="n">
-        <v>-40816</v>
+        <v>9293811</v>
       </c>
       <c r="V71" t="n">
-        <v>21622184</v>
+        <v>14035396</v>
       </c>
       <c r="W71" t="n">
-        <v>31537184</v>
+        <v>16024500</v>
       </c>
       <c r="X71" t="n">
-        <v>58330009</v>
+        <v>18134041</v>
       </c>
       <c r="Y71" t="n">
-        <v>1283224</v>
+        <v>324133</v>
       </c>
       <c r="Z71" t="n">
-        <v>1816275</v>
+        <v>616736</v>
       </c>
       <c r="AA71" t="n">
-        <v>1592257</v>
+        <v>382205</v>
       </c>
       <c r="AB71" t="n">
-        <v>2251264</v>
+        <v>-27876</v>
       </c>
       <c r="AC71" t="n">
         <v>12</v>
@@ -11714,37 +11714,37 @@
         <v>12</v>
       </c>
       <c r="AE71" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>-15</v>
+        <v>30</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AI71" t="n">
-        <v>-28</v>
+        <v>-18</v>
       </c>
       <c r="AJ71" t="n">
-        <v>-70</v>
+        <v>-60</v>
       </c>
       <c r="AK71" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL71" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11759,17 +11759,17 @@
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、成交量放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -11935,12 +11935,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>2801.TW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>彰銀</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -11949,28 +11949,28 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>64.5</v>
+        <v>28.95</v>
       </c>
       <c r="E73" t="n">
-        <v>63.44</v>
+        <v>28.8</v>
       </c>
       <c r="F73" t="n">
-        <v>63.54</v>
+        <v>27.93</v>
       </c>
       <c r="G73" t="n">
-        <v>65.05</v>
+        <v>26.49</v>
       </c>
       <c r="H73" t="n">
-        <v>2447647</v>
+        <v>45992866</v>
       </c>
       <c r="I73" t="n">
-        <v>3051887</v>
+        <v>47025787</v>
       </c>
       <c r="J73" t="n">
-        <v>69.7</v>
+        <v>29.75</v>
       </c>
       <c r="K73" t="n">
-        <v>60</v>
+        <v>23.75</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -11978,76 +11978,76 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>-331465</v>
+        <v>-10533748</v>
       </c>
       <c r="N73" t="n">
-        <v>749305</v>
+        <v>4834338</v>
       </c>
       <c r="O73" t="n">
-        <v>546219</v>
+        <v>-11626581</v>
       </c>
       <c r="P73" t="n">
-        <v>-430871</v>
+        <v>-8625450</v>
       </c>
       <c r="Q73" t="n">
-        <v>-310680</v>
+        <v>-11776156</v>
       </c>
       <c r="R73" t="n">
-        <v>690127</v>
+        <v>-18604121</v>
       </c>
       <c r="S73" t="n">
-        <v>430836</v>
+        <v>-44756022</v>
       </c>
       <c r="T73" t="n">
-        <v>-156693</v>
+        <v>-69206723</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>-40816</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>21622184</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>31537184</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>58330009</v>
       </c>
       <c r="Y73" t="n">
-        <v>-20785</v>
+        <v>1283224</v>
       </c>
       <c r="Z73" t="n">
-        <v>59178</v>
+        <v>1816275</v>
       </c>
       <c r="AA73" t="n">
-        <v>115383</v>
+        <v>1592257</v>
       </c>
       <c r="AB73" t="n">
-        <v>-274178</v>
+        <v>2251264</v>
       </c>
       <c r="AC73" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD73" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE73" t="n">
-        <v>-5</v>
+        <v>45</v>
       </c>
       <c r="AF73" t="n">
-        <v>30</v>
+        <v>-15</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="AI73" t="n">
-        <v>-12</v>
+        <v>-28</v>
       </c>
       <c r="AJ73" t="n">
-        <v>-54.55</v>
+        <v>-70</v>
       </c>
       <c r="AK73" t="n">
         <v>30</v>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -12077,59 +12077,59 @@
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>00878.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>34.83</v>
+        <v>64.5</v>
       </c>
       <c r="E74" t="n">
-        <v>34.49</v>
+        <v>63.44</v>
       </c>
       <c r="F74" t="n">
-        <v>34.32</v>
+        <v>63.54</v>
       </c>
       <c r="G74" t="n">
-        <v>33.75</v>
+        <v>65.05</v>
       </c>
       <c r="H74" t="n">
-        <v>29777735</v>
+        <v>2447647</v>
       </c>
       <c r="I74" t="n">
-        <v>31928794</v>
+        <v>3051887</v>
       </c>
       <c r="J74" t="n">
-        <v>35.06</v>
+        <v>69.7</v>
       </c>
       <c r="K74" t="n">
-        <v>32.29</v>
+        <v>60</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -12137,52 +12137,52 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>-6947368</v>
+        <v>-331465</v>
       </c>
       <c r="N74" t="n">
-        <v>4787466</v>
+        <v>749305</v>
       </c>
       <c r="O74" t="n">
-        <v>-18052412</v>
+        <v>546219</v>
       </c>
       <c r="P74" t="n">
-        <v>-19404038</v>
+        <v>-430871</v>
       </c>
       <c r="Q74" t="n">
-        <v>-2852463</v>
+        <v>-310680</v>
       </c>
       <c r="R74" t="n">
-        <v>-1470817</v>
+        <v>690127</v>
       </c>
       <c r="S74" t="n">
-        <v>-22765242</v>
+        <v>430836</v>
       </c>
       <c r="T74" t="n">
-        <v>-36767750</v>
+        <v>-156693</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>-200000</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>-300000</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>-4094905</v>
+        <v>-20785</v>
       </c>
       <c r="Z74" t="n">
-        <v>6358283</v>
+        <v>59178</v>
       </c>
       <c r="AA74" t="n">
-        <v>4912830</v>
+        <v>115383</v>
       </c>
       <c r="AB74" t="n">
-        <v>17663712</v>
+        <v>-274178</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
@@ -12191,37 +12191,37 @@
         <v>10</v>
       </c>
       <c r="AE74" t="n">
-        <v>60</v>
+        <v>-5</v>
       </c>
       <c r="AF74" t="n">
-        <v>-35</v>
+        <v>30</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>-6</v>
+        <v>22</v>
       </c>
       <c r="AI74" t="n">
-        <v>16</v>
+        <v>-12</v>
       </c>
       <c r="AJ74" t="n">
-        <v>266.67</v>
+        <v>-54.55</v>
       </c>
       <c r="AK74" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AL74" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -12236,59 +12236,59 @@
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1714.TW</t>
+          <t>00878.TW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>和桐</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>15.7</v>
+        <v>34.83</v>
       </c>
       <c r="E75" t="n">
-        <v>15.49</v>
+        <v>34.49</v>
       </c>
       <c r="F75" t="n">
-        <v>15.88</v>
+        <v>34.32</v>
       </c>
       <c r="G75" t="n">
-        <v>16.39</v>
+        <v>33.75</v>
       </c>
       <c r="H75" t="n">
-        <v>7933467</v>
+        <v>29777735</v>
       </c>
       <c r="I75" t="n">
-        <v>8497382</v>
+        <v>31928794</v>
       </c>
       <c r="J75" t="n">
-        <v>18.55</v>
+        <v>35.06</v>
       </c>
       <c r="K75" t="n">
-        <v>14.65</v>
+        <v>32.29</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -12296,52 +12296,52 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>-2420690</v>
+        <v>-6947368</v>
       </c>
       <c r="N75" t="n">
-        <v>5501</v>
+        <v>4787466</v>
       </c>
       <c r="O75" t="n">
-        <v>1437616</v>
+        <v>-18052412</v>
       </c>
       <c r="P75" t="n">
-        <v>-7551291</v>
+        <v>-19404038</v>
       </c>
       <c r="Q75" t="n">
-        <v>-2400078</v>
+        <v>-2852463</v>
       </c>
       <c r="R75" t="n">
-        <v>-81256</v>
+        <v>-1470817</v>
       </c>
       <c r="S75" t="n">
-        <v>1570032</v>
+        <v>-22765242</v>
       </c>
       <c r="T75" t="n">
-        <v>-7424403</v>
+        <v>-36767750</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>-200000</v>
       </c>
       <c r="X75" t="n">
-        <v>-38000</v>
+        <v>-300000</v>
       </c>
       <c r="Y75" t="n">
-        <v>-20612</v>
+        <v>-4094905</v>
       </c>
       <c r="Z75" t="n">
-        <v>86757</v>
+        <v>6358283</v>
       </c>
       <c r="AA75" t="n">
-        <v>-132416</v>
+        <v>4912830</v>
       </c>
       <c r="AB75" t="n">
-        <v>-88888</v>
+        <v>17663712</v>
       </c>
       <c r="AC75" t="n">
         <v>10</v>
@@ -12350,28 +12350,28 @@
         <v>10</v>
       </c>
       <c r="AE75" t="n">
-        <v>-5</v>
+        <v>60</v>
       </c>
       <c r="AF75" t="n">
-        <v>30</v>
+        <v>-35</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AI75" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ75" t="n">
-        <v>225</v>
+        <v>266.67</v>
       </c>
       <c r="AK75" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AL75" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -12395,29 +12395,29 @@
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>1714.TW</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>和桐</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -12426,28 +12426,28 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2460</v>
+        <v>15.7</v>
       </c>
       <c r="E76" t="n">
-        <v>2406</v>
+        <v>15.49</v>
       </c>
       <c r="F76" t="n">
-        <v>2428.5</v>
+        <v>15.88</v>
       </c>
       <c r="G76" t="n">
-        <v>2416.75</v>
+        <v>16.39</v>
       </c>
       <c r="H76" t="n">
-        <v>40892688</v>
+        <v>7933467</v>
       </c>
       <c r="I76" t="n">
-        <v>23333131</v>
+        <v>8497382</v>
       </c>
       <c r="J76" t="n">
-        <v>2505</v>
+        <v>18.55</v>
       </c>
       <c r="K76" t="n">
-        <v>2350</v>
+        <v>14.65</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -12455,52 +12455,52 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>7127308</v>
+        <v>-2420690</v>
       </c>
       <c r="N76" t="n">
-        <v>4555448</v>
+        <v>5501</v>
       </c>
       <c r="O76" t="n">
-        <v>-9796912</v>
+        <v>1437616</v>
       </c>
       <c r="P76" t="n">
-        <v>-1048232</v>
+        <v>-7551291</v>
       </c>
       <c r="Q76" t="n">
-        <v>6039352</v>
+        <v>-2400078</v>
       </c>
       <c r="R76" t="n">
-        <v>2089162</v>
+        <v>-81256</v>
       </c>
       <c r="S76" t="n">
-        <v>-13328620</v>
+        <v>1570032</v>
       </c>
       <c r="T76" t="n">
-        <v>-4450846</v>
+        <v>-7424403</v>
       </c>
       <c r="U76" t="n">
-        <v>-273476</v>
+        <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>-166523</v>
+        <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>352064</v>
+        <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>356848</v>
+        <v>-38000</v>
       </c>
       <c r="Y76" t="n">
-        <v>1361432</v>
+        <v>-20612</v>
       </c>
       <c r="Z76" t="n">
-        <v>2632809</v>
+        <v>86757</v>
       </c>
       <c r="AA76" t="n">
-        <v>3179644</v>
+        <v>-132416</v>
       </c>
       <c r="AB76" t="n">
-        <v>3045766</v>
+        <v>-88888</v>
       </c>
       <c r="AC76" t="n">
         <v>10</v>
@@ -12509,10 +12509,10 @@
         <v>10</v>
       </c>
       <c r="AE76" t="n">
-        <v>40</v>
+        <v>-5</v>
       </c>
       <c r="AF76" t="n">
-        <v>-15</v>
+        <v>30</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -12527,19 +12527,19 @@
         <v>225</v>
       </c>
       <c r="AK76" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="AL76" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -12554,29 +12554,29 @@
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、接近20日高點、接近20日低點、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8215.TW</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -12585,120 +12585,120 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>27.35</v>
+        <v>2460</v>
       </c>
       <c r="E77" t="n">
-        <v>25.93</v>
+        <v>2406</v>
       </c>
       <c r="F77" t="n">
-        <v>25.57</v>
+        <v>2428.5</v>
       </c>
       <c r="G77" t="n">
-        <v>25.36</v>
+        <v>2416.75</v>
       </c>
       <c r="H77" t="n">
-        <v>6504404</v>
+        <v>40892688</v>
       </c>
       <c r="I77" t="n">
-        <v>2861857</v>
+        <v>23333131</v>
       </c>
       <c r="J77" t="n">
-        <v>28.3</v>
+        <v>2505</v>
       </c>
       <c r="K77" t="n">
-        <v>23.4</v>
+        <v>2350</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>-660709</v>
+        <v>7879185</v>
       </c>
       <c r="N77" t="n">
-        <v>-1650640</v>
+        <v>5307325</v>
       </c>
       <c r="O77" t="n">
-        <v>-1671075</v>
+        <v>-9045035</v>
       </c>
       <c r="P77" t="n">
-        <v>-1253286</v>
+        <v>-296355</v>
       </c>
       <c r="Q77" t="n">
-        <v>-669709</v>
+        <v>6039352</v>
       </c>
       <c r="R77" t="n">
-        <v>-1602227</v>
+        <v>2089162</v>
       </c>
       <c r="S77" t="n">
-        <v>-1681097</v>
+        <v>-13328620</v>
       </c>
       <c r="T77" t="n">
-        <v>-1447157</v>
+        <v>-4450846</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>478401</v>
       </c>
       <c r="V77" t="n">
-        <v>-53000</v>
+        <v>585354</v>
       </c>
       <c r="W77" t="n">
-        <v>4000</v>
+        <v>1103941</v>
       </c>
       <c r="X77" t="n">
-        <v>199000</v>
+        <v>1108725</v>
       </c>
       <c r="Y77" t="n">
-        <v>9000</v>
+        <v>1361432</v>
       </c>
       <c r="Z77" t="n">
-        <v>4587</v>
+        <v>2632809</v>
       </c>
       <c r="AA77" t="n">
-        <v>6022</v>
+        <v>3179644</v>
       </c>
       <c r="AB77" t="n">
-        <v>-5129</v>
+        <v>3045766</v>
       </c>
       <c r="AC77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE77" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AF77" t="n">
-        <v>-55</v>
+        <v>-15</v>
       </c>
       <c r="AG77" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>25</v>
+        <v>-8</v>
       </c>
       <c r="AI77" t="n">
-        <v>-16</v>
+        <v>18</v>
       </c>
       <c r="AJ77" t="n">
-        <v>-64</v>
+        <v>225</v>
       </c>
       <c r="AK77" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="AL77" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -12713,29 +12713,29 @@
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+          <t>站上5日線、成交量放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、成交量放大、接近20日高點、接近20日低點、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>8215.TW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -12744,120 +12744,120 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>499.5</v>
+        <v>27.35</v>
       </c>
       <c r="E78" t="n">
-        <v>497.6</v>
+        <v>25.93</v>
       </c>
       <c r="F78" t="n">
-        <v>505.5</v>
+        <v>25.57</v>
       </c>
       <c r="G78" t="n">
-        <v>496.32</v>
+        <v>25.36</v>
       </c>
       <c r="H78" t="n">
-        <v>4532000</v>
+        <v>6504404</v>
       </c>
       <c r="I78" t="n">
-        <v>23450600</v>
+        <v>2861857</v>
       </c>
       <c r="J78" t="n">
-        <v>564</v>
+        <v>28.3</v>
       </c>
       <c r="K78" t="n">
-        <v>399</v>
+        <v>23.4</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>-660709</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>-1650640</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>-1671075</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>-1253286</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>-669709</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>-1602227</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>-1681097</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>-1447157</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>-53000</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>199000</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>4587</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>6022</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>-5129</v>
       </c>
       <c r="AC78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE78" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AH78" t="n">
-        <v>-4</v>
+        <v>25</v>
       </c>
       <c r="AI78" t="n">
-        <v>12</v>
+        <v>-16</v>
       </c>
       <c r="AJ78" t="n">
-        <v>300</v>
+        <v>-64</v>
       </c>
       <c r="AK78" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="AL78" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -12903,28 +12903,28 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>243.5</v>
+        <v>499.5</v>
       </c>
       <c r="E79" t="n">
-        <v>234.3</v>
+        <v>497.6</v>
       </c>
       <c r="F79" t="n">
-        <v>235.05</v>
+        <v>505.5</v>
       </c>
       <c r="G79" t="n">
-        <v>215.45</v>
+        <v>496.32</v>
       </c>
       <c r="H79" t="n">
-        <v>7760000</v>
+        <v>4532000</v>
       </c>
       <c r="I79" t="n">
-        <v>8155800</v>
+        <v>23450600</v>
       </c>
       <c r="J79" t="n">
-        <v>265</v>
+        <v>564</v>
       </c>
       <c r="K79" t="n">
-        <v>140</v>
+        <v>399</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -12995,28 +12995,28 @@
         <v>0</v>
       </c>
       <c r="AH79" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AI79" t="n">
         <v>12</v>
       </c>
-      <c r="AI79" t="n">
-        <v>-4</v>
-      </c>
       <c r="AJ79" t="n">
-        <v>-33.33</v>
+        <v>300</v>
       </c>
       <c r="AK79" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AL79" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -13048,12 +13048,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1303.TW</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -13062,28 +13062,28 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>238</v>
+        <v>243.5</v>
       </c>
       <c r="E80" t="n">
-        <v>230.7</v>
+        <v>234.3</v>
       </c>
       <c r="F80" t="n">
-        <v>233.4</v>
+        <v>235.05</v>
       </c>
       <c r="G80" t="n">
-        <v>225.93</v>
+        <v>215.45</v>
       </c>
       <c r="H80" t="n">
-        <v>82174219</v>
+        <v>7760000</v>
       </c>
       <c r="I80" t="n">
-        <v>66751376</v>
+        <v>8155800</v>
       </c>
       <c r="J80" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="K80" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -13091,91 +13091,91 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>-10464654</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>4798234</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>-14038128</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>-15145300</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>-10938712</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>-22704567</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>-43171158</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>-55052304</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>443167</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>26474868</v>
+        <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>29378446</v>
+        <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>41602989</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>30891</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>1027933</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>-245416</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>-1695985</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE80" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AF80" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AI80" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="AJ80" t="n">
-        <v>200</v>
+        <v>-33.33</v>
       </c>
       <c r="AK80" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="AL80" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -13190,17 +13190,17 @@
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -13366,12 +13366,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>1303.TW</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -13380,28 +13380,28 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>24.5</v>
+        <v>238</v>
       </c>
       <c r="E82" t="n">
-        <v>24.3</v>
+        <v>230.7</v>
       </c>
       <c r="F82" t="n">
-        <v>24.68</v>
+        <v>233.4</v>
       </c>
       <c r="G82" t="n">
-        <v>24.72</v>
+        <v>225.93</v>
       </c>
       <c r="H82" t="n">
-        <v>7829976</v>
+        <v>82174219</v>
       </c>
       <c r="I82" t="n">
-        <v>9954945</v>
+        <v>66751376</v>
       </c>
       <c r="J82" t="n">
-        <v>27.05</v>
+        <v>250</v>
       </c>
       <c r="K82" t="n">
-        <v>23.7</v>
+        <v>174</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -13409,52 +13409,52 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>-1183028</v>
+        <v>-10464654</v>
       </c>
       <c r="N82" t="n">
-        <v>3349217</v>
+        <v>4798234</v>
       </c>
       <c r="O82" t="n">
-        <v>1040004</v>
+        <v>-14038128</v>
       </c>
       <c r="P82" t="n">
-        <v>-8066166</v>
+        <v>-15145300</v>
       </c>
       <c r="Q82" t="n">
-        <v>-1334883</v>
+        <v>-10938712</v>
       </c>
       <c r="R82" t="n">
-        <v>3084559</v>
+        <v>-22704567</v>
       </c>
       <c r="S82" t="n">
-        <v>1356459</v>
+        <v>-43171158</v>
       </c>
       <c r="T82" t="n">
-        <v>-6494457</v>
+        <v>-55052304</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>443167</v>
       </c>
       <c r="V82" t="n">
-        <v>-22000</v>
+        <v>26474868</v>
       </c>
       <c r="W82" t="n">
-        <v>-188000</v>
+        <v>29378446</v>
       </c>
       <c r="X82" t="n">
-        <v>-198000</v>
+        <v>41602989</v>
       </c>
       <c r="Y82" t="n">
-        <v>151855</v>
+        <v>30891</v>
       </c>
       <c r="Z82" t="n">
-        <v>286658</v>
+        <v>1027933</v>
       </c>
       <c r="AA82" t="n">
-        <v>-128455</v>
+        <v>-245416</v>
       </c>
       <c r="AB82" t="n">
-        <v>-1373709</v>
+        <v>-1695985</v>
       </c>
       <c r="AC82" t="n">
         <v>6</v>
@@ -13463,28 +13463,28 @@
         <v>6</v>
       </c>
       <c r="AE82" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF82" t="n">
         <v>-15</v>
       </c>
-      <c r="AF82" t="n">
-        <v>30</v>
-      </c>
       <c r="AG82" t="n">
         <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>-16</v>
+        <v>2</v>
       </c>
       <c r="AI82" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="AJ82" t="n">
-        <v>137.5</v>
+        <v>200</v>
       </c>
       <c r="AK82" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AL82" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -13508,29 +13508,29 @@
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3231.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -13539,28 +13539,28 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>186.5</v>
+        <v>14</v>
       </c>
       <c r="E83" t="n">
-        <v>183.9</v>
+        <v>13.92</v>
       </c>
       <c r="F83" t="n">
-        <v>186.25</v>
+        <v>14.16</v>
       </c>
       <c r="G83" t="n">
-        <v>184.4</v>
+        <v>14.22</v>
       </c>
       <c r="H83" t="n">
-        <v>44060071</v>
+        <v>16464654</v>
       </c>
       <c r="I83" t="n">
-        <v>33071473</v>
+        <v>17843505</v>
       </c>
       <c r="J83" t="n">
-        <v>200.5</v>
+        <v>15.15</v>
       </c>
       <c r="K83" t="n">
-        <v>172.5</v>
+        <v>13.6</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -13568,52 +13568,52 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>174849</v>
+        <v>-2968947</v>
       </c>
       <c r="N83" t="n">
-        <v>2345587</v>
+        <v>1987464</v>
       </c>
       <c r="O83" t="n">
-        <v>-10708223</v>
+        <v>778720</v>
       </c>
       <c r="P83" t="n">
-        <v>-87721252</v>
+        <v>-5718883</v>
       </c>
       <c r="Q83" t="n">
-        <v>-3502354</v>
+        <v>-3044666</v>
       </c>
       <c r="R83" t="n">
-        <v>-4362873</v>
+        <v>1693706</v>
       </c>
       <c r="S83" t="n">
-        <v>-19086172</v>
+        <v>857326</v>
       </c>
       <c r="T83" t="n">
-        <v>-99871454</v>
+        <v>-5800426</v>
       </c>
       <c r="U83" t="n">
-        <v>3044019</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>7038019</v>
+        <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>9240019</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>12119010</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>633184</v>
+        <v>75719</v>
       </c>
       <c r="Z83" t="n">
-        <v>-329559</v>
+        <v>293758</v>
       </c>
       <c r="AA83" t="n">
-        <v>-862070</v>
+        <v>-78606</v>
       </c>
       <c r="AB83" t="n">
-        <v>31192</v>
+        <v>81543</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
@@ -13622,37 +13622,37 @@
         <v>6</v>
       </c>
       <c r="AE83" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AF83" t="n">
         <v>30</v>
       </c>
-      <c r="AF83" t="n">
-        <v>-15</v>
-      </c>
       <c r="AG83" t="n">
         <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="AI83" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AJ83" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AK83" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="AL83" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -13667,29 +13667,29 @@
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -13698,28 +13698,28 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>14</v>
+        <v>24.5</v>
       </c>
       <c r="E84" t="n">
-        <v>13.92</v>
+        <v>24.3</v>
       </c>
       <c r="F84" t="n">
-        <v>14.16</v>
+        <v>24.68</v>
       </c>
       <c r="G84" t="n">
-        <v>14.22</v>
+        <v>24.72</v>
       </c>
       <c r="H84" t="n">
-        <v>16464654</v>
+        <v>7829976</v>
       </c>
       <c r="I84" t="n">
-        <v>17843505</v>
+        <v>9954945</v>
       </c>
       <c r="J84" t="n">
-        <v>15.15</v>
+        <v>27.05</v>
       </c>
       <c r="K84" t="n">
-        <v>13.6</v>
+        <v>23.7</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -13727,52 +13727,52 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>-2968947</v>
+        <v>-1183028</v>
       </c>
       <c r="N84" t="n">
-        <v>1987464</v>
+        <v>3349217</v>
       </c>
       <c r="O84" t="n">
-        <v>778720</v>
+        <v>1040004</v>
       </c>
       <c r="P84" t="n">
-        <v>-5718883</v>
+        <v>-8066166</v>
       </c>
       <c r="Q84" t="n">
-        <v>-3044666</v>
+        <v>-1334883</v>
       </c>
       <c r="R84" t="n">
-        <v>1693706</v>
+        <v>3084559</v>
       </c>
       <c r="S84" t="n">
-        <v>857326</v>
+        <v>1356459</v>
       </c>
       <c r="T84" t="n">
-        <v>-5800426</v>
+        <v>-6494457</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>-22000</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>-188000</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>-198000</v>
       </c>
       <c r="Y84" t="n">
-        <v>75719</v>
+        <v>151855</v>
       </c>
       <c r="Z84" t="n">
-        <v>293758</v>
+        <v>286658</v>
       </c>
       <c r="AA84" t="n">
-        <v>-78606</v>
+        <v>-128455</v>
       </c>
       <c r="AB84" t="n">
-        <v>81543</v>
+        <v>-1373709</v>
       </c>
       <c r="AC84" t="n">
         <v>6</v>
@@ -13790,13 +13790,13 @@
         <v>0</v>
       </c>
       <c r="AH84" t="n">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="AI84" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AJ84" t="n">
-        <v>150</v>
+        <v>137.5</v>
       </c>
       <c r="AK84" t="n">
         <v>45</v>
@@ -13831,24 +13831,24 @@
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4966.TWO</t>
+          <t>3231.TW</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -13857,28 +13857,28 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>568</v>
+        <v>186.5</v>
       </c>
       <c r="E85" t="n">
-        <v>545</v>
+        <v>183.9</v>
       </c>
       <c r="F85" t="n">
-        <v>545.6</v>
+        <v>186.25</v>
       </c>
       <c r="G85" t="n">
-        <v>559.15</v>
+        <v>184.4</v>
       </c>
       <c r="H85" t="n">
-        <v>828000</v>
+        <v>44060071</v>
       </c>
       <c r="I85" t="n">
-        <v>512800</v>
+        <v>33071473</v>
       </c>
       <c r="J85" t="n">
-        <v>599</v>
+        <v>200.5</v>
       </c>
       <c r="K85" t="n">
-        <v>521</v>
+        <v>172.5</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -13886,91 +13886,91 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>174849</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2345587</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>-10708223</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>-87721252</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>-3502354</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>-4362873</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>-19086172</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>-99871454</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>3044019</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>7038019</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>9240019</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>12119010</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>633184</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>-329559</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>-862070</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>31192</v>
       </c>
       <c r="AC85" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI85" t="n">
         <v>4</v>
       </c>
-      <c r="AD85" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE85" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH85" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI85" t="n">
-        <v>-2</v>
-      </c>
       <c r="AJ85" t="n">
-        <v>-33.33</v>
+        <v>200</v>
       </c>
       <c r="AK85" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AL85" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -13985,29 +13985,29 @@
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8299.TWO</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -14016,28 +14016,28 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2140</v>
+        <v>550</v>
       </c>
       <c r="E86" t="n">
-        <v>1990</v>
+        <v>539.4</v>
       </c>
       <c r="F86" t="n">
-        <v>2027</v>
+        <v>553.4</v>
       </c>
       <c r="G86" t="n">
-        <v>2064.5</v>
+        <v>552.2</v>
       </c>
       <c r="H86" t="n">
-        <v>6668000</v>
+        <v>26963850</v>
       </c>
       <c r="I86" t="n">
-        <v>3395600</v>
+        <v>24578337</v>
       </c>
       <c r="J86" t="n">
-        <v>2215</v>
+        <v>610</v>
       </c>
       <c r="K86" t="n">
-        <v>1900</v>
+        <v>511</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -14045,52 +14045,52 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4064671</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>-3773160</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>-197950</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>-5789908</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>2423004</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>-6026861</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>-3002894</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>-8644217</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>637109</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>1471129</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>2408131</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>1736165</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1004558</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>782572</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>396813</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1118144</v>
       </c>
       <c r="AC86" t="n">
         <v>4</v>
@@ -14099,28 +14099,28 @@
         <v>4</v>
       </c>
       <c r="AE86" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>-6</v>
+        <v>-44</v>
       </c>
       <c r="AI86" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="AJ86" t="n">
-        <v>166.67</v>
+        <v>109.09</v>
       </c>
       <c r="AK86" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="AL86" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>DT尚未轉強、離5MA偏遠、位於20日區間中上緣、量能偏強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、分數升溫過快</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -14144,29 +14144,29 @@
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>4966.TWO</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -14175,28 +14175,28 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>944</v>
+        <v>568</v>
       </c>
       <c r="E87" t="n">
-        <v>921.4</v>
+        <v>545</v>
       </c>
       <c r="F87" t="n">
-        <v>930.7</v>
+        <v>545.6</v>
       </c>
       <c r="G87" t="n">
-        <v>947.85</v>
+        <v>559.15</v>
       </c>
       <c r="H87" t="n">
-        <v>15864000</v>
+        <v>828000</v>
       </c>
       <c r="I87" t="n">
-        <v>8917600</v>
+        <v>512800</v>
       </c>
       <c r="J87" t="n">
-        <v>1035</v>
+        <v>599</v>
       </c>
       <c r="K87" t="n">
-        <v>872</v>
+        <v>521</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -14267,28 +14267,28 @@
         <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>-16</v>
+        <v>6</v>
       </c>
       <c r="AI87" t="n">
-        <v>20</v>
+        <v>-2</v>
       </c>
       <c r="AJ87" t="n">
-        <v>125</v>
+        <v>-33.33</v>
       </c>
       <c r="AK87" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AL87" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -14320,12 +14320,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2605.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>新興</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -14334,28 +14334,28 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>36.1</v>
+        <v>944</v>
       </c>
       <c r="E88" t="n">
-        <v>36.1</v>
+        <v>921.4</v>
       </c>
       <c r="F88" t="n">
-        <v>36.3</v>
+        <v>930.7</v>
       </c>
       <c r="G88" t="n">
-        <v>35.86</v>
+        <v>947.85</v>
       </c>
       <c r="H88" t="n">
-        <v>9451516</v>
+        <v>15864000</v>
       </c>
       <c r="I88" t="n">
-        <v>10559232</v>
+        <v>8917600</v>
       </c>
       <c r="J88" t="n">
-        <v>39.2</v>
+        <v>1035</v>
       </c>
       <c r="K88" t="n">
-        <v>34.3</v>
+        <v>872</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -14363,52 +14363,52 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>-1422194</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>9178612</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>5183497</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>11427735</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>-2211083</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>6033422</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>2908139</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>8330951</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>-44000</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>-156000</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>-175000</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>788889</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>3189190</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2431358</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>3271784</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>4</v>
@@ -14417,37 +14417,37 @@
         <v>4</v>
       </c>
       <c r="AE88" t="n">
-        <v>-20</v>
+        <v>10</v>
       </c>
       <c r="AF88" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>36</v>
+        <v>-16</v>
       </c>
       <c r="AI88" t="n">
-        <v>-32</v>
+        <v>20</v>
       </c>
       <c r="AJ88" t="n">
-        <v>-88.89</v>
+        <v>125</v>
       </c>
       <c r="AK88" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL88" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -14462,17 +14462,17 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、空頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14638,12 +14638,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>2605.TW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>新興</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -14652,28 +14652,28 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>665</v>
+        <v>36.1</v>
       </c>
       <c r="E90" t="n">
-        <v>654.2</v>
+        <v>36.1</v>
       </c>
       <c r="F90" t="n">
-        <v>685</v>
+        <v>36.3</v>
       </c>
       <c r="G90" t="n">
-        <v>720.85</v>
+        <v>35.86</v>
       </c>
       <c r="H90" t="n">
-        <v>1849000</v>
+        <v>9451516</v>
       </c>
       <c r="I90" t="n">
-        <v>1637000</v>
+        <v>10559232</v>
       </c>
       <c r="J90" t="n">
-        <v>814</v>
+        <v>39.2</v>
       </c>
       <c r="K90" t="n">
-        <v>631</v>
+        <v>34.3</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -14681,91 +14681,91 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>-1422194</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>9178612</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>5183497</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>11427735</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>-2211083</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>6033422</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>2908139</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>8330951</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>-44000</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>-156000</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>-175000</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>788889</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>3189190</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2431358</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>3271784</v>
       </c>
       <c r="AC90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE90" t="n">
-        <v>5</v>
+        <v>-20</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>-18</v>
+        <v>36</v>
       </c>
       <c r="AI90" t="n">
-        <v>20</v>
+        <v>-32</v>
       </c>
       <c r="AJ90" t="n">
-        <v>111.11</v>
+        <v>-88.89</v>
       </c>
       <c r="AK90" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AL90" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -14780,29 +14780,29 @@
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>8299.TWO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -14811,28 +14811,28 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1315</v>
+        <v>2140</v>
       </c>
       <c r="E91" t="n">
-        <v>1287</v>
+        <v>1990</v>
       </c>
       <c r="F91" t="n">
-        <v>1315</v>
+        <v>2027</v>
       </c>
       <c r="G91" t="n">
-        <v>1385.75</v>
+        <v>2064.5</v>
       </c>
       <c r="H91" t="n">
-        <v>1274000</v>
+        <v>6668000</v>
       </c>
       <c r="I91" t="n">
-        <v>1012400</v>
+        <v>3395600</v>
       </c>
       <c r="J91" t="n">
-        <v>1660</v>
+        <v>2215</v>
       </c>
       <c r="K91" t="n">
-        <v>1240</v>
+        <v>1900</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -14888,13 +14888,13 @@
         <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AF91" t="n">
         <v>0</v>
@@ -14903,28 +14903,28 @@
         <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
       <c r="AI91" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AJ91" t="n">
-        <v>109.09</v>
+        <v>166.67</v>
       </c>
       <c r="AK91" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="AL91" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、離5MA偏遠、位於20日區間中上緣、量能偏強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
@@ -14949,19 +14949,19 @@
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>3260.TWO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -14970,28 +14970,28 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>550</v>
+        <v>413.5</v>
       </c>
       <c r="E92" t="n">
-        <v>539.4</v>
+        <v>415.1</v>
       </c>
       <c r="F92" t="n">
-        <v>553.4</v>
+        <v>411.95</v>
       </c>
       <c r="G92" t="n">
-        <v>552.2</v>
+        <v>409.4</v>
       </c>
       <c r="H92" t="n">
-        <v>26963850</v>
+        <v>4711000</v>
       </c>
       <c r="I92" t="n">
-        <v>24578337</v>
+        <v>8588600</v>
       </c>
       <c r="J92" t="n">
-        <v>610</v>
+        <v>459.5</v>
       </c>
       <c r="K92" t="n">
-        <v>511</v>
+        <v>375</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -14999,82 +14999,82 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>3681671</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>-4156160</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>-580950</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>-6172908</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>2423004</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>-6026861</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>-3002894</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>-8644217</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>254109</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>1088129</v>
+        <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>2025131</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>1353165</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1004558</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>782572</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>396813</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1118144</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE92" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AF92" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>-44</v>
+        <v>-22</v>
       </c>
       <c r="AI92" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="AJ92" t="n">
-        <v>100</v>
+        <v>109.09</v>
       </c>
       <c r="AK92" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AL92" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -15098,29 +15098,29 @@
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -15129,28 +15129,28 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>30.35</v>
+        <v>665</v>
       </c>
       <c r="E93" t="n">
-        <v>29.27</v>
+        <v>654.2</v>
       </c>
       <c r="F93" t="n">
-        <v>29.66</v>
+        <v>685</v>
       </c>
       <c r="G93" t="n">
-        <v>27.84</v>
+        <v>720.85</v>
       </c>
       <c r="H93" t="n">
-        <v>348900833</v>
+        <v>1849000</v>
       </c>
       <c r="I93" t="n">
-        <v>306045715</v>
+        <v>1637000</v>
       </c>
       <c r="J93" t="n">
-        <v>32.2</v>
+        <v>814</v>
       </c>
       <c r="K93" t="n">
-        <v>24.6</v>
+        <v>631</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -15158,91 +15158,91 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>-45062488</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>67072721</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>-73126209</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>172863909</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>-52162597</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>53532716</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>-72265323</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>151375622</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>3630311</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>3613311</v>
+        <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>3613311</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>3508647</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>3469798</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>9926694</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>-4474197</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>17979640</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE93" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AF93" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>-8</v>
+        <v>-18</v>
       </c>
       <c r="AI93" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AJ93" t="n">
-        <v>100</v>
+        <v>111.11</v>
       </c>
       <c r="AK93" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AL93" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -15257,29 +15257,29 @@
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2455.TW</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -15288,28 +15288,28 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>556</v>
+        <v>1315</v>
       </c>
       <c r="E94" t="n">
-        <v>532</v>
+        <v>1287</v>
       </c>
       <c r="F94" t="n">
-        <v>525.5</v>
+        <v>1315</v>
       </c>
       <c r="G94" t="n">
-        <v>497.35</v>
+        <v>1385.75</v>
       </c>
       <c r="H94" t="n">
-        <v>20026752</v>
+        <v>1274000</v>
       </c>
       <c r="I94" t="n">
-        <v>14350962</v>
+        <v>1012400</v>
       </c>
       <c r="J94" t="n">
-        <v>566</v>
+        <v>1660</v>
       </c>
       <c r="K94" t="n">
-        <v>374.5</v>
+        <v>1240</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -15317,91 +15317,91 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>-210100</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>-816337</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>-397465</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>3491811</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>-641603</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>-2043243</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>-1489341</v>
+        <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>2144149</v>
+        <v>0</v>
       </c>
       <c r="U94" t="n">
-        <v>217000</v>
+        <v>0</v>
       </c>
       <c r="V94" t="n">
-        <v>703710</v>
+        <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>637710</v>
+        <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>-151490</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>214503</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>523196</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>454166</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1499152</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE94" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="AF94" t="n">
-        <v>-70</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>34</v>
+        <v>-22</v>
       </c>
       <c r="AI94" t="n">
-        <v>-34</v>
+        <v>24</v>
       </c>
       <c r="AJ94" t="n">
-        <v>-100</v>
+        <v>109.09</v>
       </c>
       <c r="AK94" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="AL94" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -15416,29 +15416,29 @@
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -15447,120 +15447,120 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>22.9</v>
+        <v>30.35</v>
       </c>
       <c r="E95" t="n">
-        <v>20.87</v>
+        <v>29.27</v>
       </c>
       <c r="F95" t="n">
-        <v>20.76</v>
+        <v>29.66</v>
       </c>
       <c r="G95" t="n">
-        <v>21.07</v>
+        <v>27.84</v>
       </c>
       <c r="H95" t="n">
-        <v>19107976</v>
+        <v>348900833</v>
       </c>
       <c r="I95" t="n">
-        <v>6262096</v>
+        <v>306045715</v>
       </c>
       <c r="J95" t="n">
-        <v>23.85</v>
+        <v>32.2</v>
       </c>
       <c r="K95" t="n">
-        <v>19.5</v>
+        <v>24.6</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>-4204363</v>
+        <v>-45062488</v>
       </c>
       <c r="N95" t="n">
-        <v>-2356625</v>
+        <v>67072721</v>
       </c>
       <c r="O95" t="n">
-        <v>-2382255</v>
+        <v>-73126209</v>
       </c>
       <c r="P95" t="n">
-        <v>-1926175</v>
+        <v>172863909</v>
       </c>
       <c r="Q95" t="n">
-        <v>-4326155</v>
+        <v>-52162597</v>
       </c>
       <c r="R95" t="n">
-        <v>-2492741</v>
+        <v>53532716</v>
       </c>
       <c r="S95" t="n">
-        <v>-2481970</v>
+        <v>-72265323</v>
       </c>
       <c r="T95" t="n">
-        <v>-2036414</v>
+        <v>151375622</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>3630311</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>3613311</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>3613311</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>3508647</v>
       </c>
       <c r="Y95" t="n">
-        <v>121792</v>
+        <v>3469798</v>
       </c>
       <c r="Z95" t="n">
-        <v>136116</v>
+        <v>9926694</v>
       </c>
       <c r="AA95" t="n">
-        <v>99715</v>
+        <v>-4474197</v>
       </c>
       <c r="AB95" t="n">
-        <v>110239</v>
+        <v>17979640</v>
       </c>
       <c r="AC95" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AF95" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="AG95" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AH95" t="n">
-        <v>30</v>
+        <v>-8</v>
       </c>
       <c r="AI95" t="n">
-        <v>-31</v>
+        <v>8</v>
       </c>
       <c r="AJ95" t="n">
-        <v>-103.33</v>
+        <v>100</v>
       </c>
       <c r="AK95" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL95" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>DT尚未轉強、離5MA偏遠、位於20日區間中上緣、爆量後不追價、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -15575,29 +15575,29 @@
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>站上5日線、爆量、帶量突破20日高點</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3363.TWO</t>
+          <t>2455.TW</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -15606,28 +15606,28 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>683</v>
+        <v>556</v>
       </c>
       <c r="E96" t="n">
-        <v>669</v>
+        <v>532</v>
       </c>
       <c r="F96" t="n">
-        <v>688.2</v>
+        <v>525.5</v>
       </c>
       <c r="G96" t="n">
-        <v>697.45</v>
+        <v>497.35</v>
       </c>
       <c r="H96" t="n">
-        <v>2645000</v>
+        <v>20026752</v>
       </c>
       <c r="I96" t="n">
-        <v>2966800</v>
+        <v>14350962</v>
       </c>
       <c r="J96" t="n">
-        <v>850</v>
+        <v>566</v>
       </c>
       <c r="K96" t="n">
-        <v>549</v>
+        <v>374.5</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -15635,82 +15635,82 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>-216100</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>-822337</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>-403465</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>3485811</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>-641603</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>-2043243</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>-1489341</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>2144149</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>211000</v>
       </c>
       <c r="V96" t="n">
-        <v>0</v>
+        <v>697710</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>631710</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>-157490</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>214503</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>523196</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>454166</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1499152</v>
       </c>
       <c r="AC96" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>-5</v>
+        <v>70</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>-4</v>
+        <v>34</v>
       </c>
       <c r="AI96" t="n">
-        <v>2</v>
+        <v>-34</v>
       </c>
       <c r="AJ96" t="n">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="AK96" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AL96" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數剛升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -15734,29 +15734,29 @@
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -15765,57 +15765,57 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>237.5</v>
+        <v>22.9</v>
       </c>
       <c r="E97" t="n">
-        <v>232.6</v>
+        <v>20.87</v>
       </c>
       <c r="F97" t="n">
-        <v>238.25</v>
+        <v>20.76</v>
       </c>
       <c r="G97" t="n">
-        <v>246.65</v>
+        <v>21.07</v>
       </c>
       <c r="H97" t="n">
-        <v>2280000</v>
+        <v>19107976</v>
       </c>
       <c r="I97" t="n">
-        <v>2381400</v>
+        <v>6262096</v>
       </c>
       <c r="J97" t="n">
-        <v>288</v>
+        <v>23.85</v>
       </c>
       <c r="K97" t="n">
-        <v>223</v>
+        <v>19.5</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>-4204363</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>-2356625</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>-2382255</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>-1926175</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>-4326155</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>-2492741</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>-2481970</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>-2036414</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -15830,55 +15830,55 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>121792</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>136116</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>99715</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>110239</v>
       </c>
       <c r="AC97" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AD97" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AE97" t="n">
-        <v>-5</v>
+        <v>40</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AG97" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AH97" t="n">
-        <v>-2</v>
+        <v>30</v>
       </c>
       <c r="AI97" t="n">
-        <v>0</v>
+        <v>-31</v>
       </c>
       <c r="AJ97" t="n">
-        <v>0</v>
+        <v>-103.33</v>
       </c>
       <c r="AK97" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL97" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、離5MA偏遠、位於20日區間中上緣、爆量後不追價、分數轉弱</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -15893,17 +15893,17 @@
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、爆量、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -16387,12 +16387,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6275.TWO</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -16401,28 +16401,28 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>45.1</v>
+        <v>237.5</v>
       </c>
       <c r="E101" t="n">
-        <v>45.04</v>
+        <v>232.6</v>
       </c>
       <c r="F101" t="n">
-        <v>45.31</v>
+        <v>238.25</v>
       </c>
       <c r="G101" t="n">
-        <v>45.53</v>
+        <v>246.65</v>
       </c>
       <c r="H101" t="n">
-        <v>129000</v>
+        <v>2280000</v>
       </c>
       <c r="I101" t="n">
-        <v>107400</v>
+        <v>2381400</v>
       </c>
       <c r="J101" t="n">
-        <v>48.9</v>
+        <v>288</v>
       </c>
       <c r="K101" t="n">
-        <v>43.8</v>
+        <v>223</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -16493,19 +16493,19 @@
         <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="AI101" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AJ101" t="n">
-        <v>-125</v>
+        <v>0</v>
       </c>
       <c r="AK101" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="AL101" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
@@ -16539,7 +16539,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -16705,12 +16705,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3260.TWO</t>
+          <t>3363.TWO</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -16719,28 +16719,28 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>396.5</v>
+        <v>683</v>
       </c>
       <c r="E103" t="n">
-        <v>395.5</v>
+        <v>669</v>
       </c>
       <c r="F103" t="n">
-        <v>402.75</v>
+        <v>688.2</v>
       </c>
       <c r="G103" t="n">
-        <v>408.07</v>
+        <v>697.45</v>
       </c>
       <c r="H103" t="n">
-        <v>6928000</v>
+        <v>2645000</v>
       </c>
       <c r="I103" t="n">
-        <v>4937400</v>
+        <v>2966800</v>
       </c>
       <c r="J103" t="n">
-        <v>459.5</v>
+        <v>850</v>
       </c>
       <c r="K103" t="n">
-        <v>385</v>
+        <v>549</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -16811,28 +16811,28 @@
         <v>0</v>
       </c>
       <c r="AH103" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
       <c r="AI103" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="AJ103" t="n">
-        <v>90.91</v>
+        <v>50</v>
       </c>
       <c r="AK103" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="AL103" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、分數剛升溫</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -18495,16 +18495,16 @@
         </is>
       </c>
       <c r="M114" t="n">
-        <v>46095322</v>
+        <v>46055322</v>
       </c>
       <c r="N114" t="n">
-        <v>57768886</v>
+        <v>57728886</v>
       </c>
       <c r="O114" t="n">
-        <v>-3975642</v>
+        <v>-4015642</v>
       </c>
       <c r="P114" t="n">
-        <v>42604315</v>
+        <v>42564315</v>
       </c>
       <c r="Q114" t="n">
         <v>42774232</v>
@@ -18519,16 +18519,16 @@
         <v>49867921</v>
       </c>
       <c r="U114" t="n">
-        <v>-168886</v>
+        <v>-208886</v>
       </c>
       <c r="V114" t="n">
-        <v>-42886</v>
+        <v>-82886</v>
       </c>
       <c r="W114" t="n">
-        <v>-13719886</v>
+        <v>-13759886</v>
       </c>
       <c r="X114" t="n">
-        <v>-13861643</v>
+        <v>-13901643</v>
       </c>
       <c r="Y114" t="n">
         <v>3489976</v>
@@ -18654,16 +18654,16 @@
         </is>
       </c>
       <c r="M115" t="n">
-        <v>2762889</v>
+        <v>3128176</v>
       </c>
       <c r="N115" t="n">
-        <v>-5838991</v>
+        <v>-5473704</v>
       </c>
       <c r="O115" t="n">
-        <v>-6182995</v>
+        <v>-5817708</v>
       </c>
       <c r="P115" t="n">
-        <v>-37277710</v>
+        <v>-36912423</v>
       </c>
       <c r="Q115" t="n">
         <v>2897881</v>
@@ -18678,16 +18678,16 @@
         <v>-22175633</v>
       </c>
       <c r="U115" t="n">
-        <v>-379271</v>
+        <v>-13984</v>
       </c>
       <c r="V115" t="n">
-        <v>511139</v>
+        <v>876426</v>
       </c>
       <c r="W115" t="n">
-        <v>1197756</v>
+        <v>1563043</v>
       </c>
       <c r="X115" t="n">
-        <v>-14253804</v>
+        <v>-13888517</v>
       </c>
       <c r="Y115" t="n">
         <v>244279</v>
@@ -19608,16 +19608,16 @@
         </is>
       </c>
       <c r="M121" t="n">
-        <v>2146844</v>
+        <v>135844</v>
       </c>
       <c r="N121" t="n">
-        <v>-2094589</v>
+        <v>-4105589</v>
       </c>
       <c r="O121" t="n">
-        <v>-2973693</v>
+        <v>-4984693</v>
       </c>
       <c r="P121" t="n">
-        <v>-12942753</v>
+        <v>-14953753</v>
       </c>
       <c r="Q121" t="n">
         <v>1886851</v>
@@ -19632,16 +19632,16 @@
         <v>-9992718</v>
       </c>
       <c r="U121" t="n">
-        <v>20000</v>
+        <v>-1991000</v>
       </c>
       <c r="V121" t="n">
-        <v>-1553000</v>
+        <v>-3564000</v>
       </c>
       <c r="W121" t="n">
-        <v>-1482000</v>
+        <v>-3493000</v>
       </c>
       <c r="X121" t="n">
-        <v>-2070000</v>
+        <v>-4081000</v>
       </c>
       <c r="Y121" t="n">
         <v>239993</v>
@@ -21516,16 +21516,16 @@
         </is>
       </c>
       <c r="M133" t="n">
-        <v>-751447</v>
+        <v>-755447</v>
       </c>
       <c r="N133" t="n">
-        <v>-1945603</v>
+        <v>-1949603</v>
       </c>
       <c r="O133" t="n">
-        <v>-2293481</v>
+        <v>-2297481</v>
       </c>
       <c r="P133" t="n">
-        <v>-4751973</v>
+        <v>-4755973</v>
       </c>
       <c r="Q133" t="n">
         <v>-255616</v>
@@ -21540,16 +21540,16 @@
         <v>-73946</v>
       </c>
       <c r="U133" t="n">
-        <v>-666784</v>
+        <v>-670784</v>
       </c>
       <c r="V133" t="n">
-        <v>-2005288</v>
+        <v>-2009288</v>
       </c>
       <c r="W133" t="n">
-        <v>-2201618</v>
+        <v>-2205618</v>
       </c>
       <c r="X133" t="n">
-        <v>-4862843</v>
+        <v>-4866843</v>
       </c>
       <c r="Y133" t="n">
         <v>170953</v>
@@ -22152,16 +22152,16 @@
         </is>
       </c>
       <c r="M137" t="n">
-        <v>-9756910</v>
+        <v>-9711680</v>
       </c>
       <c r="N137" t="n">
-        <v>-15532518</v>
+        <v>-15487288</v>
       </c>
       <c r="O137" t="n">
-        <v>-17412885</v>
+        <v>-17367655</v>
       </c>
       <c r="P137" t="n">
-        <v>-6240613</v>
+        <v>-6195383</v>
       </c>
       <c r="Q137" t="n">
         <v>-9026745</v>
@@ -22176,16 +22176,16 @@
         <v>-8799308</v>
       </c>
       <c r="U137" t="n">
-        <v>-477627</v>
+        <v>-432397</v>
       </c>
       <c r="V137" t="n">
-        <v>-720627</v>
+        <v>-675397</v>
       </c>
       <c r="W137" t="n">
-        <v>-319627</v>
+        <v>-274397</v>
       </c>
       <c r="X137" t="n">
-        <v>2364175</v>
+        <v>2409405</v>
       </c>
       <c r="Y137" t="n">
         <v>-252538</v>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -2554,12 +2554,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2568,28 +2568,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>160</v>
+        <v>5180</v>
       </c>
       <c r="E14" t="n">
-        <v>152.5</v>
+        <v>4786</v>
       </c>
       <c r="F14" t="n">
-        <v>146.8</v>
+        <v>4685</v>
       </c>
       <c r="G14" t="n">
-        <v>138.12</v>
+        <v>4469.25</v>
       </c>
       <c r="H14" t="n">
-        <v>286598057</v>
+        <v>12131543</v>
       </c>
       <c r="I14" t="n">
-        <v>225193829</v>
+        <v>9374102</v>
       </c>
       <c r="J14" t="n">
-        <v>168.5</v>
+        <v>5480</v>
       </c>
       <c r="K14" t="n">
-        <v>117</v>
+        <v>3710</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2597,52 +2597,52 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>60018008</v>
+        <v>1972448</v>
       </c>
       <c r="N14" t="n">
-        <v>111369435</v>
+        <v>8846849</v>
       </c>
       <c r="O14" t="n">
-        <v>163957247</v>
+        <v>9995602</v>
       </c>
       <c r="P14" t="n">
-        <v>189108389</v>
+        <v>10381845</v>
       </c>
       <c r="Q14" t="n">
-        <v>50545175</v>
+        <v>1541804</v>
       </c>
       <c r="R14" t="n">
-        <v>73185205</v>
+        <v>7584866</v>
       </c>
       <c r="S14" t="n">
-        <v>89105536</v>
+        <v>8882370</v>
       </c>
       <c r="T14" t="n">
-        <v>79769078</v>
+        <v>8834536</v>
       </c>
       <c r="U14" t="n">
-        <v>7771888</v>
+        <v>373171</v>
       </c>
       <c r="V14" t="n">
-        <v>29302872</v>
+        <v>565981</v>
       </c>
       <c r="W14" t="n">
-        <v>61121872</v>
+        <v>120014</v>
       </c>
       <c r="X14" t="n">
-        <v>94190516</v>
+        <v>547894</v>
       </c>
       <c r="Y14" t="n">
-        <v>1700945</v>
+        <v>57473</v>
       </c>
       <c r="Z14" t="n">
-        <v>8881358</v>
+        <v>696002</v>
       </c>
       <c r="AA14" t="n">
-        <v>13729839</v>
+        <v>993218</v>
       </c>
       <c r="AB14" t="n">
-        <v>15148795</v>
+        <v>999415</v>
       </c>
       <c r="AC14" t="n">
         <v>54</v>
@@ -2660,19 +2660,19 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AJ14" t="n">
-        <v>8</v>
+        <v>28.57</v>
       </c>
       <c r="AK14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AL14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
+          <t>DT進入觀察區、離5MA偏遠、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2713,12 +2713,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2727,28 +2727,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>693</v>
+        <v>160</v>
       </c>
       <c r="E15" t="n">
-        <v>642.6</v>
+        <v>152.5</v>
       </c>
       <c r="F15" t="n">
-        <v>632.5</v>
+        <v>146.8</v>
       </c>
       <c r="G15" t="n">
-        <v>617.1</v>
+        <v>138.12</v>
       </c>
       <c r="H15" t="n">
-        <v>24987417</v>
+        <v>286598057</v>
       </c>
       <c r="I15" t="n">
-        <v>18142585</v>
+        <v>225193829</v>
       </c>
       <c r="J15" t="n">
-        <v>711</v>
+        <v>168.5</v>
       </c>
       <c r="K15" t="n">
-        <v>565</v>
+        <v>117</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2756,52 +2756,52 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>10751378</v>
+        <v>60104008</v>
       </c>
       <c r="N15" t="n">
-        <v>25095282</v>
+        <v>111455435</v>
       </c>
       <c r="O15" t="n">
-        <v>29813623</v>
+        <v>164043247</v>
       </c>
       <c r="P15" t="n">
-        <v>29527421</v>
+        <v>189194389</v>
       </c>
       <c r="Q15" t="n">
-        <v>8479833</v>
+        <v>50545175</v>
       </c>
       <c r="R15" t="n">
-        <v>20817830</v>
+        <v>73185205</v>
       </c>
       <c r="S15" t="n">
-        <v>25887340</v>
+        <v>89105536</v>
       </c>
       <c r="T15" t="n">
-        <v>26307158</v>
+        <v>79769078</v>
       </c>
       <c r="U15" t="n">
-        <v>1163223</v>
+        <v>7857888</v>
       </c>
       <c r="V15" t="n">
-        <v>1144202</v>
+        <v>29388872</v>
       </c>
       <c r="W15" t="n">
-        <v>481202</v>
+        <v>61207872</v>
       </c>
       <c r="X15" t="n">
-        <v>578867</v>
+        <v>94276516</v>
       </c>
       <c r="Y15" t="n">
-        <v>1108322</v>
+        <v>1700945</v>
       </c>
       <c r="Z15" t="n">
-        <v>3133250</v>
+        <v>8881358</v>
       </c>
       <c r="AA15" t="n">
-        <v>3445081</v>
+        <v>13729839</v>
       </c>
       <c r="AB15" t="n">
-        <v>2641396</v>
+        <v>15148795</v>
       </c>
       <c r="AC15" t="n">
         <v>54</v>
@@ -2819,28 +2819,28 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AI15" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>28.57</v>
+        <v>8</v>
       </c>
       <c r="AK15" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AL15" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>可優先研究</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>DT進入觀察區、離5MA偏遠、均線多頭排列、量能溫和放大、分數明顯升溫</t>
+          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2872,12 +2872,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>3711.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2886,28 +2886,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>909</v>
+        <v>693</v>
       </c>
       <c r="E16" t="n">
-        <v>838.6</v>
+        <v>642.6</v>
       </c>
       <c r="F16" t="n">
-        <v>824.7</v>
+        <v>632.5</v>
       </c>
       <c r="G16" t="n">
-        <v>834.4</v>
+        <v>617.1</v>
       </c>
       <c r="H16" t="n">
-        <v>29109027</v>
+        <v>24987417</v>
       </c>
       <c r="I16" t="n">
-        <v>19501158</v>
+        <v>18142585</v>
       </c>
       <c r="J16" t="n">
-        <v>960</v>
+        <v>711</v>
       </c>
       <c r="K16" t="n">
-        <v>766</v>
+        <v>565</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -2915,52 +2915,52 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>9544840</v>
+        <v>10751378</v>
       </c>
       <c r="N16" t="n">
-        <v>12062911</v>
+        <v>25095282</v>
       </c>
       <c r="O16" t="n">
-        <v>8624616</v>
+        <v>29813623</v>
       </c>
       <c r="P16" t="n">
-        <v>13782186</v>
+        <v>29527421</v>
       </c>
       <c r="Q16" t="n">
-        <v>8471578</v>
+        <v>8479833</v>
       </c>
       <c r="R16" t="n">
-        <v>9630758</v>
+        <v>20817830</v>
       </c>
       <c r="S16" t="n">
-        <v>5906383</v>
+        <v>25887340</v>
       </c>
       <c r="T16" t="n">
-        <v>10378021</v>
+        <v>26307158</v>
       </c>
       <c r="U16" t="n">
-        <v>179000</v>
+        <v>1163223</v>
       </c>
       <c r="V16" t="n">
-        <v>413000</v>
+        <v>1144202</v>
       </c>
       <c r="W16" t="n">
-        <v>877000</v>
+        <v>481202</v>
       </c>
       <c r="X16" t="n">
-        <v>1963000</v>
+        <v>578867</v>
       </c>
       <c r="Y16" t="n">
-        <v>894262</v>
+        <v>1108322</v>
       </c>
       <c r="Z16" t="n">
-        <v>2019153</v>
+        <v>3133250</v>
       </c>
       <c r="AA16" t="n">
-        <v>1841233</v>
+        <v>3445081</v>
       </c>
       <c r="AB16" t="n">
-        <v>1441165</v>
+        <v>2641396</v>
       </c>
       <c r="AC16" t="n">
         <v>54</v>
@@ -2978,28 +2978,28 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AI16" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>145.45</v>
+        <v>28.57</v>
       </c>
       <c r="AK16" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="AL16" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>DT進入觀察區、離5MA偏遠、位於20日區間中上緣、量能溫和放大、分數升溫過快</t>
+          <t>DT進入觀察區、離5MA偏遠、均線多頭排列、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -3024,19 +3024,19 @@
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、黃金交叉、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3045,28 +3045,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5180</v>
+        <v>909</v>
       </c>
       <c r="E17" t="n">
-        <v>4786</v>
+        <v>838.6</v>
       </c>
       <c r="F17" t="n">
-        <v>4685</v>
+        <v>824.7</v>
       </c>
       <c r="G17" t="n">
-        <v>4469.25</v>
+        <v>834.4</v>
       </c>
       <c r="H17" t="n">
-        <v>12131543</v>
+        <v>29109027</v>
       </c>
       <c r="I17" t="n">
-        <v>9374102</v>
+        <v>19501158</v>
       </c>
       <c r="J17" t="n">
-        <v>5480</v>
+        <v>960</v>
       </c>
       <c r="K17" t="n">
-        <v>3710</v>
+        <v>766</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -3074,116 +3074,116 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1815448</v>
+        <v>10209840</v>
       </c>
       <c r="N17" t="n">
-        <v>8689849</v>
+        <v>12727911</v>
       </c>
       <c r="O17" t="n">
-        <v>9838602</v>
+        <v>9289616</v>
       </c>
       <c r="P17" t="n">
-        <v>10224845</v>
+        <v>14447186</v>
       </c>
       <c r="Q17" t="n">
-        <v>1541804</v>
+        <v>9136578</v>
       </c>
       <c r="R17" t="n">
-        <v>7584866</v>
+        <v>10295758</v>
       </c>
       <c r="S17" t="n">
-        <v>8882370</v>
+        <v>6571383</v>
       </c>
       <c r="T17" t="n">
-        <v>8834536</v>
+        <v>11043021</v>
       </c>
       <c r="U17" t="n">
-        <v>216171</v>
+        <v>179000</v>
       </c>
       <c r="V17" t="n">
-        <v>408981</v>
+        <v>413000</v>
       </c>
       <c r="W17" t="n">
-        <v>-36986</v>
+        <v>877000</v>
       </c>
       <c r="X17" t="n">
-        <v>390894</v>
+        <v>1963000</v>
       </c>
       <c r="Y17" t="n">
-        <v>57473</v>
+        <v>894262</v>
       </c>
       <c r="Z17" t="n">
-        <v>696002</v>
+        <v>2019153</v>
       </c>
       <c r="AA17" t="n">
-        <v>993218</v>
+        <v>1841233</v>
       </c>
       <c r="AB17" t="n">
-        <v>999415</v>
+        <v>1441165</v>
       </c>
       <c r="AC17" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="AD17" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="AE17" t="n">
         <v>55</v>
       </c>
       <c r="AF17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="AJ17" t="n">
-        <v>9.52</v>
+        <v>145.45</v>
       </c>
       <c r="AK17" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="AL17" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>DT進入觀察區、離5MA偏遠、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
+          <t>DT進入觀察區、離5MA偏遠、位於20日區間中上緣、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、黃金交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>偏多觀察：站上5日線、黃金交叉、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
@@ -4664,16 +4664,16 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-4259014</v>
+        <v>-4267744</v>
       </c>
       <c r="N27" t="n">
-        <v>7658883</v>
+        <v>7650153</v>
       </c>
       <c r="O27" t="n">
-        <v>5087023</v>
+        <v>5078293</v>
       </c>
       <c r="P27" t="n">
-        <v>-23307884</v>
+        <v>-23316614</v>
       </c>
       <c r="Q27" t="n">
         <v>-4329504</v>
@@ -4688,16 +4688,16 @@
         <v>-27722896</v>
       </c>
       <c r="U27" t="n">
-        <v>-396904</v>
+        <v>-405634</v>
       </c>
       <c r="V27" t="n">
-        <v>816103</v>
+        <v>807373</v>
       </c>
       <c r="W27" t="n">
-        <v>923056</v>
+        <v>914326</v>
       </c>
       <c r="X27" t="n">
-        <v>609396</v>
+        <v>600666</v>
       </c>
       <c r="Y27" t="n">
         <v>467394</v>
@@ -5459,16 +5459,16 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>6121298</v>
+        <v>5982298</v>
       </c>
       <c r="N32" t="n">
-        <v>3276293</v>
+        <v>3137293</v>
       </c>
       <c r="O32" t="n">
-        <v>2069476</v>
+        <v>1930476</v>
       </c>
       <c r="P32" t="n">
-        <v>5974979</v>
+        <v>5835979</v>
       </c>
       <c r="Q32" t="n">
         <v>5863122</v>
@@ -5483,16 +5483,16 @@
         <v>5992260</v>
       </c>
       <c r="U32" t="n">
-        <v>4818</v>
+        <v>-134182</v>
       </c>
       <c r="V32" t="n">
-        <v>-631099</v>
+        <v>-770099</v>
       </c>
       <c r="W32" t="n">
-        <v>-511099</v>
+        <v>-650099</v>
       </c>
       <c r="X32" t="n">
-        <v>-411296</v>
+        <v>-550296</v>
       </c>
       <c r="Y32" t="n">
         <v>253358</v>
@@ -11340,16 +11340,16 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>-23685192</v>
+        <v>-23703192</v>
       </c>
       <c r="N69" t="n">
-        <v>9320126</v>
+        <v>9302126</v>
       </c>
       <c r="O69" t="n">
-        <v>18464287</v>
+        <v>18446287</v>
       </c>
       <c r="P69" t="n">
-        <v>-24112164</v>
+        <v>-24130164</v>
       </c>
       <c r="Q69" t="n">
         <v>-22444770</v>
@@ -11364,16 +11364,16 @@
         <v>-22722272</v>
       </c>
       <c r="U69" t="n">
-        <v>-85066</v>
+        <v>-103066</v>
       </c>
       <c r="V69" t="n">
-        <v>3854362</v>
+        <v>3836362</v>
       </c>
       <c r="W69" t="n">
-        <v>5231362</v>
+        <v>5213362</v>
       </c>
       <c r="X69" t="n">
-        <v>-509961</v>
+        <v>-527961</v>
       </c>
       <c r="Y69" t="n">
         <v>-1155356</v>
@@ -11615,12 +11615,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2886.TW</t>
+          <t>8028.TW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11629,28 +11629,28 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>50.5</v>
+        <v>263.5</v>
       </c>
       <c r="E71" t="n">
-        <v>51.1</v>
+        <v>251</v>
       </c>
       <c r="F71" t="n">
-        <v>51.17</v>
+        <v>239.4</v>
       </c>
       <c r="G71" t="n">
-        <v>49.97</v>
+        <v>242.05</v>
       </c>
       <c r="H71" t="n">
-        <v>21285539</v>
+        <v>13456615</v>
       </c>
       <c r="I71" t="n">
-        <v>26310614</v>
+        <v>10017264</v>
       </c>
       <c r="J71" t="n">
-        <v>52.9</v>
+        <v>274</v>
       </c>
       <c r="K71" t="n">
-        <v>46.1</v>
+        <v>216.5</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -11658,52 +11658,52 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>8422787</v>
+        <v>37008</v>
       </c>
       <c r="N71" t="n">
-        <v>10458339</v>
+        <v>-273376</v>
       </c>
       <c r="O71" t="n">
-        <v>15851208</v>
+        <v>90019</v>
       </c>
       <c r="P71" t="n">
-        <v>42802421</v>
+        <v>-2882038</v>
       </c>
       <c r="Q71" t="n">
-        <v>12736350</v>
+        <v>-3025665</v>
       </c>
       <c r="R71" t="n">
-        <v>18109168</v>
+        <v>-6247903</v>
       </c>
       <c r="S71" t="n">
-        <v>18087951</v>
+        <v>-9566008</v>
       </c>
       <c r="T71" t="n">
-        <v>26865435</v>
+        <v>-13282145</v>
       </c>
       <c r="U71" t="n">
-        <v>-4781067</v>
+        <v>3007000</v>
       </c>
       <c r="V71" t="n">
-        <v>-9239040</v>
+        <v>5942000</v>
       </c>
       <c r="W71" t="n">
-        <v>-4641040</v>
+        <v>9503000</v>
       </c>
       <c r="X71" t="n">
-        <v>12762213</v>
+        <v>10357000</v>
       </c>
       <c r="Y71" t="n">
-        <v>467504</v>
+        <v>55673</v>
       </c>
       <c r="Z71" t="n">
-        <v>1588211</v>
+        <v>32527</v>
       </c>
       <c r="AA71" t="n">
-        <v>2404297</v>
+        <v>153027</v>
       </c>
       <c r="AB71" t="n">
-        <v>3174773</v>
+        <v>43107</v>
       </c>
       <c r="AC71" t="n">
         <v>16</v>
@@ -11712,37 +11712,37 @@
         <v>16</v>
       </c>
       <c r="AE71" t="n">
-        <v>-20</v>
+        <v>30</v>
       </c>
       <c r="AF71" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK71" t="n">
         <v>60</v>
       </c>
-      <c r="AG71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>-18</v>
-      </c>
-      <c r="AJ71" t="n">
-        <v>-52.94</v>
-      </c>
-      <c r="AK71" t="n">
-        <v>0</v>
-      </c>
       <c r="AL71" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11757,17 +11757,17 @@
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人小幅買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、5日法人小幅買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -11933,12 +11933,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2832.TW</t>
+          <t>2886.TW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>台產</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -11947,28 +11947,28 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>58.3</v>
+        <v>50.5</v>
       </c>
       <c r="E73" t="n">
-        <v>58.54</v>
+        <v>51.1</v>
       </c>
       <c r="F73" t="n">
-        <v>57.88</v>
+        <v>51.17</v>
       </c>
       <c r="G73" t="n">
-        <v>58.34</v>
+        <v>49.97</v>
       </c>
       <c r="H73" t="n">
-        <v>161318</v>
+        <v>21285539</v>
       </c>
       <c r="I73" t="n">
-        <v>243750</v>
+        <v>26310614</v>
       </c>
       <c r="J73" t="n">
-        <v>60.8</v>
+        <v>52.9</v>
       </c>
       <c r="K73" t="n">
-        <v>55.8</v>
+        <v>46.1</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -11976,76 +11976,76 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>-13905</v>
+        <v>8422787</v>
       </c>
       <c r="N73" t="n">
-        <v>-47136</v>
+        <v>10458339</v>
       </c>
       <c r="O73" t="n">
-        <v>242200</v>
+        <v>15851208</v>
       </c>
       <c r="P73" t="n">
-        <v>452707</v>
+        <v>42802421</v>
       </c>
       <c r="Q73" t="n">
-        <v>-78300</v>
+        <v>12736350</v>
       </c>
       <c r="R73" t="n">
-        <v>-161216</v>
+        <v>18109168</v>
       </c>
       <c r="S73" t="n">
-        <v>114617</v>
+        <v>18087951</v>
       </c>
       <c r="T73" t="n">
-        <v>297780</v>
+        <v>26865435</v>
       </c>
       <c r="U73" t="n">
-        <v>62395</v>
+        <v>-4781067</v>
       </c>
       <c r="V73" t="n">
-        <v>99810</v>
+        <v>-9239040</v>
       </c>
       <c r="W73" t="n">
-        <v>113958</v>
+        <v>-4641040</v>
       </c>
       <c r="X73" t="n">
-        <v>136516</v>
+        <v>12762213</v>
       </c>
       <c r="Y73" t="n">
-        <v>2000</v>
+        <v>467504</v>
       </c>
       <c r="Z73" t="n">
-        <v>14270</v>
+        <v>1588211</v>
       </c>
       <c r="AA73" t="n">
-        <v>13625</v>
+        <v>2404297</v>
       </c>
       <c r="AB73" t="n">
-        <v>18411</v>
+        <v>3174773</v>
       </c>
       <c r="AC73" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD73" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE73" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="AF73" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI73" t="n">
         <v>-18</v>
       </c>
       <c r="AJ73" t="n">
-        <v>-56.25</v>
+        <v>-52.94</v>
       </c>
       <c r="AK73" t="n">
         <v>0</v>
@@ -12075,29 +12075,29 @@
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>跌破5日線、黃金交叉、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、黃金交叉、量能未放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2801.TW</t>
+          <t>2832.TW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>彰銀</t>
+          <t>台產</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -12106,28 +12106,28 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>28.35</v>
+        <v>58.3</v>
       </c>
       <c r="E74" t="n">
-        <v>28.85</v>
+        <v>58.54</v>
       </c>
       <c r="F74" t="n">
-        <v>28.24</v>
+        <v>57.88</v>
       </c>
       <c r="G74" t="n">
-        <v>26.94</v>
+        <v>58.34</v>
       </c>
       <c r="H74" t="n">
-        <v>14996270</v>
+        <v>161318</v>
       </c>
       <c r="I74" t="n">
-        <v>36348612</v>
+        <v>243750</v>
       </c>
       <c r="J74" t="n">
-        <v>29.75</v>
+        <v>60.8</v>
       </c>
       <c r="K74" t="n">
-        <v>23.75</v>
+        <v>55.8</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -12135,52 +12135,52 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>-94932</v>
+        <v>-13905</v>
       </c>
       <c r="N74" t="n">
-        <v>-14678560</v>
+        <v>-47136</v>
       </c>
       <c r="O74" t="n">
-        <v>689526</v>
+        <v>242200</v>
       </c>
       <c r="P74" t="n">
-        <v>-14303654</v>
+        <v>452707</v>
       </c>
       <c r="Q74" t="n">
-        <v>10545</v>
+        <v>-78300</v>
       </c>
       <c r="R74" t="n">
-        <v>-15759568</v>
+        <v>-161216</v>
       </c>
       <c r="S74" t="n">
-        <v>-22587533</v>
+        <v>114617</v>
       </c>
       <c r="T74" t="n">
-        <v>-61896584</v>
+        <v>297780</v>
       </c>
       <c r="U74" t="n">
-        <v>-143000</v>
+        <v>62395</v>
       </c>
       <c r="V74" t="n">
-        <v>-392816</v>
+        <v>99810</v>
       </c>
       <c r="W74" t="n">
-        <v>21270184</v>
+        <v>113958</v>
       </c>
       <c r="X74" t="n">
-        <v>45303009</v>
+        <v>136516</v>
       </c>
       <c r="Y74" t="n">
-        <v>37523</v>
+        <v>2000</v>
       </c>
       <c r="Z74" t="n">
-        <v>1473824</v>
+        <v>14270</v>
       </c>
       <c r="AA74" t="n">
-        <v>2006875</v>
+        <v>13625</v>
       </c>
       <c r="AB74" t="n">
-        <v>2289921</v>
+        <v>18411</v>
       </c>
       <c r="AC74" t="n">
         <v>14</v>
@@ -12189,28 +12189,28 @@
         <v>14</v>
       </c>
       <c r="AE74" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AF74" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>-20</v>
+        <v>32</v>
       </c>
       <c r="AI74" t="n">
-        <v>34</v>
+        <v>-18</v>
       </c>
       <c r="AJ74" t="n">
-        <v>170</v>
+        <v>-56.25</v>
       </c>
       <c r="AK74" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL74" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -12234,17 +12234,17 @@
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、黃金交叉、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、黃金交叉、量能未放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -12410,12 +12410,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4979.TWO</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -12424,28 +12424,28 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>605</v>
+        <v>971</v>
       </c>
       <c r="E76" t="n">
-        <v>587.4</v>
+        <v>939</v>
       </c>
       <c r="F76" t="n">
-        <v>570.5</v>
+        <v>928.3</v>
       </c>
       <c r="G76" t="n">
-        <v>587.95</v>
+        <v>943.45</v>
       </c>
       <c r="H76" t="n">
-        <v>11642000</v>
+        <v>18781000</v>
       </c>
       <c r="I76" t="n">
-        <v>7687400</v>
+        <v>11710400</v>
       </c>
       <c r="J76" t="n">
-        <v>658</v>
+        <v>1015</v>
       </c>
       <c r="K76" t="n">
-        <v>501</v>
+        <v>872</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -12516,28 +12516,28 @@
         <v>0</v>
       </c>
       <c r="AH76" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI76" t="n">
         <v>6</v>
       </c>
-      <c r="AI76" t="n">
-        <v>8</v>
-      </c>
       <c r="AJ76" t="n">
-        <v>133.33</v>
+        <v>75</v>
       </c>
       <c r="AK76" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="AL76" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -12728,12 +12728,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>2801.TW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>彰銀</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -12742,28 +12742,28 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>971</v>
+        <v>28.35</v>
       </c>
       <c r="E78" t="n">
-        <v>939</v>
+        <v>28.85</v>
       </c>
       <c r="F78" t="n">
-        <v>928.3</v>
+        <v>28.24</v>
       </c>
       <c r="G78" t="n">
-        <v>943.45</v>
+        <v>26.94</v>
       </c>
       <c r="H78" t="n">
-        <v>18781000</v>
+        <v>14996270</v>
       </c>
       <c r="I78" t="n">
-        <v>11710400</v>
+        <v>36348612</v>
       </c>
       <c r="J78" t="n">
-        <v>1015</v>
+        <v>29.75</v>
       </c>
       <c r="K78" t="n">
-        <v>872</v>
+        <v>23.75</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -12771,52 +12771,52 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>-94932</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>-14678560</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>689526</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>-14303654</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>10545</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>-15759568</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>-22587533</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>-61896584</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>-143000</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>-392816</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>21270184</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>45303009</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>37523</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1473824</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2006875</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>2289921</v>
       </c>
       <c r="AC78" t="n">
         <v>14</v>
@@ -12825,37 +12825,37 @@
         <v>14</v>
       </c>
       <c r="AE78" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>8</v>
+        <v>-20</v>
       </c>
       <c r="AI78" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AJ78" t="n">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="AK78" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="AL78" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數升溫過快</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -12870,17 +12870,17 @@
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -13046,12 +13046,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2362.TW</t>
+          <t>4979.TWO</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>藍天</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -13060,28 +13060,28 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>47.9</v>
+        <v>605</v>
       </c>
       <c r="E80" t="n">
-        <v>47.76</v>
+        <v>587.4</v>
       </c>
       <c r="F80" t="n">
-        <v>47.48</v>
+        <v>570.5</v>
       </c>
       <c r="G80" t="n">
-        <v>47.82</v>
+        <v>587.95</v>
       </c>
       <c r="H80" t="n">
-        <v>407063</v>
+        <v>11642000</v>
       </c>
       <c r="I80" t="n">
-        <v>600559</v>
+        <v>7687400</v>
       </c>
       <c r="J80" t="n">
-        <v>49.9</v>
+        <v>658</v>
       </c>
       <c r="K80" t="n">
-        <v>46.25</v>
+        <v>501</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -13089,28 +13089,28 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>-48752</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>229909</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>388231</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>261795</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>-48727</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>205921</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>357146</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>240099</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -13125,55 +13125,55 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>23988</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>31085</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>21696</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE80" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AF80" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AI80" t="n">
-        <v>-2</v>
+        <v>8</v>
       </c>
       <c r="AJ80" t="n">
-        <v>-14.29</v>
+        <v>133.33</v>
       </c>
       <c r="AK80" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="AL80" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3211.TWO</t>
+          <t>2362.TW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>藍天</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -13219,28 +13219,28 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>385</v>
+        <v>47.9</v>
       </c>
       <c r="E81" t="n">
-        <v>374.2</v>
+        <v>47.76</v>
       </c>
       <c r="F81" t="n">
-        <v>369.75</v>
+        <v>47.48</v>
       </c>
       <c r="G81" t="n">
-        <v>378.2</v>
+        <v>47.82</v>
       </c>
       <c r="H81" t="n">
-        <v>6245000</v>
+        <v>407063</v>
       </c>
       <c r="I81" t="n">
-        <v>4357000</v>
+        <v>600559</v>
       </c>
       <c r="J81" t="n">
-        <v>414.5</v>
+        <v>49.9</v>
       </c>
       <c r="K81" t="n">
-        <v>326</v>
+        <v>46.25</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -13248,28 +13248,28 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>-48752</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>229909</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>388231</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>261795</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>-48727</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>205921</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>357146</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>240099</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -13284,16 +13284,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>23988</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>31085</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>21696</v>
       </c>
       <c r="AC81" t="n">
         <v>12</v>
@@ -13302,37 +13302,37 @@
         <v>12</v>
       </c>
       <c r="AE81" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>-14.29</v>
+      </c>
+      <c r="AK81" t="n">
         <v>30</v>
       </c>
-      <c r="AF81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH81" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI81" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AJ81" t="n">
-        <v>-25</v>
-      </c>
-      <c r="AK81" t="n">
-        <v>45</v>
-      </c>
       <c r="AL81" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -13347,29 +13347,29 @@
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2816.TW</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>旺旺保</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -13378,28 +13378,28 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>40.35</v>
+        <v>385</v>
       </c>
       <c r="E82" t="n">
-        <v>40.42</v>
+        <v>374.2</v>
       </c>
       <c r="F82" t="n">
-        <v>39.77</v>
+        <v>369.75</v>
       </c>
       <c r="G82" t="n">
-        <v>39.44</v>
+        <v>378.2</v>
       </c>
       <c r="H82" t="n">
-        <v>251408</v>
+        <v>6245000</v>
       </c>
       <c r="I82" t="n">
-        <v>505881</v>
+        <v>4357000</v>
       </c>
       <c r="J82" t="n">
-        <v>41.4</v>
+        <v>414.5</v>
       </c>
       <c r="K82" t="n">
-        <v>37.45</v>
+        <v>326</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -13407,28 +13407,28 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>-17944</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>-247498</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>330635</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>619326</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>-17944</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>-255498</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>318635</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>621326</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -13446,52 +13446,52 @@
         <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE82" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="AF82" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="AI82" t="n">
-        <v>-34</v>
+        <v>-4</v>
       </c>
       <c r="AJ82" t="n">
-        <v>-77.27</v>
+        <v>-25</v>
       </c>
       <c r="AK82" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="AL82" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -13506,29 +13506,29 @@
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3081.TWO</t>
+          <t>2816.TW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>旺旺保</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -13537,28 +13537,28 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2825</v>
+        <v>40.35</v>
       </c>
       <c r="E83" t="n">
-        <v>2821</v>
+        <v>40.42</v>
       </c>
       <c r="F83" t="n">
-        <v>2801.5</v>
+        <v>39.77</v>
       </c>
       <c r="G83" t="n">
-        <v>3026</v>
+        <v>39.44</v>
       </c>
       <c r="H83" t="n">
-        <v>2370000</v>
+        <v>251408</v>
       </c>
       <c r="I83" t="n">
-        <v>3691200</v>
+        <v>505881</v>
       </c>
       <c r="J83" t="n">
-        <v>3600</v>
+        <v>41.4</v>
       </c>
       <c r="K83" t="n">
-        <v>2650</v>
+        <v>37.45</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -13566,28 +13566,28 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>-17944</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>-247498</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>330635</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>619326</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>-17944</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>-255498</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>318635</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>621326</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -13605,52 +13605,52 @@
         <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="AC83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE83" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF83" t="n">
         <v>20</v>
       </c>
-      <c r="AF83" t="n">
-        <v>0</v>
-      </c>
       <c r="AG83" t="n">
         <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>-2</v>
+        <v>44</v>
       </c>
       <c r="AI83" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>-77.27</v>
+      </c>
+      <c r="AK83" t="n">
         <v>10</v>
       </c>
-      <c r="AJ83" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK83" t="n">
-        <v>45</v>
-      </c>
       <c r="AL83" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -13665,17 +13665,17 @@
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -13841,42 +13841,42 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0056.TW</t>
+          <t>6275.TWO</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>56.85</v>
+        <v>45.45</v>
       </c>
       <c r="E85" t="n">
-        <v>56.54</v>
+        <v>45.31</v>
       </c>
       <c r="F85" t="n">
-        <v>55.98</v>
+        <v>45.29</v>
       </c>
       <c r="G85" t="n">
-        <v>55.33</v>
+        <v>45.64</v>
       </c>
       <c r="H85" t="n">
-        <v>38810100</v>
+        <v>140000</v>
       </c>
       <c r="I85" t="n">
-        <v>24734151</v>
+        <v>128800</v>
       </c>
       <c r="J85" t="n">
-        <v>57.85</v>
+        <v>48.9</v>
       </c>
       <c r="K85" t="n">
-        <v>52.4</v>
+        <v>44.35</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -13884,52 +13884,52 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>-21616831</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>-24469512</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>-9963324</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>-34341531</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>-8707052</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>-10412897</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>-4029446</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>-25138917</v>
+        <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>2450000</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>5250000</v>
+        <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>8300000</v>
+        <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>8825000</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>-15359779</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>-19306615</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>-14233878</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>-18027614</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>8</v>
@@ -13938,37 +13938,37 @@
         <v>8</v>
       </c>
       <c r="AE85" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="AF85" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>18</v>
+        <v>-2</v>
       </c>
       <c r="AI85" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="AJ85" t="n">
-        <v>-55.56</v>
+        <v>500</v>
       </c>
       <c r="AK85" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AL85" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -13983,17 +13983,17 @@
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、接近20日高點</t>
+          <t>站上5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、成交量放大、接近20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14159,42 +14159,42 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6275.TWO</t>
+          <t>0056.TW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>45.45</v>
+        <v>56.85</v>
       </c>
       <c r="E87" t="n">
-        <v>45.31</v>
+        <v>56.54</v>
       </c>
       <c r="F87" t="n">
-        <v>45.29</v>
+        <v>55.98</v>
       </c>
       <c r="G87" t="n">
-        <v>45.64</v>
+        <v>55.33</v>
       </c>
       <c r="H87" t="n">
-        <v>140000</v>
+        <v>38810100</v>
       </c>
       <c r="I87" t="n">
-        <v>128800</v>
+        <v>24734151</v>
       </c>
       <c r="J87" t="n">
-        <v>48.9</v>
+        <v>57.85</v>
       </c>
       <c r="K87" t="n">
-        <v>44.35</v>
+        <v>52.4</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -14202,52 +14202,52 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>-21616831</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>-24469512</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>-9963324</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>-34341531</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>-8707052</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>-10412897</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>-4029446</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>-25138917</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>2450000</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>5250000</v>
       </c>
       <c r="W87" t="n">
-        <v>0</v>
+        <v>8300000</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>8825000</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>-15359779</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>-19306615</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>-14233878</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>-18027614</v>
       </c>
       <c r="AC87" t="n">
         <v>8</v>
@@ -14256,37 +14256,37 @@
         <v>8</v>
       </c>
       <c r="AE87" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>-2</v>
+        <v>18</v>
       </c>
       <c r="AI87" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="AJ87" t="n">
-        <v>500</v>
+        <v>-55.56</v>
       </c>
       <c r="AK87" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AL87" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -14301,29 +14301,29 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、成交量放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、成交量放大、接近20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2882.TW</t>
+          <t>3081.TWO</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -14332,28 +14332,28 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>112</v>
+        <v>2825</v>
       </c>
       <c r="E88" t="n">
-        <v>112</v>
+        <v>2821</v>
       </c>
       <c r="F88" t="n">
-        <v>111.4</v>
+        <v>2801.5</v>
       </c>
       <c r="G88" t="n">
-        <v>110.53</v>
+        <v>3026</v>
       </c>
       <c r="H88" t="n">
-        <v>15772789</v>
+        <v>2370000</v>
       </c>
       <c r="I88" t="n">
-        <v>24527616</v>
+        <v>3691200</v>
       </c>
       <c r="J88" t="n">
-        <v>117</v>
+        <v>3600</v>
       </c>
       <c r="K88" t="n">
-        <v>102</v>
+        <v>2650</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -14361,91 +14361,91 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>-1786768</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>-2294078</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>540752</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>-5085799</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>-1749364</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>4475778</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>-139968</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>-8024767</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>-73536</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>-8503322</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>-1102322</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>972053</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>36132</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1733466</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1783042</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1966915</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD88" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE88" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI88" t="n">
         <v>10</v>
       </c>
-      <c r="AG88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH88" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI88" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ88" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AK88" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AL88" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -14460,29 +14460,29 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>2882.TW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -14491,28 +14491,28 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>240.5</v>
+        <v>112</v>
       </c>
       <c r="E89" t="n">
-        <v>237.3</v>
+        <v>112</v>
       </c>
       <c r="F89" t="n">
-        <v>237.35</v>
+        <v>111.4</v>
       </c>
       <c r="G89" t="n">
-        <v>245.8</v>
+        <v>110.53</v>
       </c>
       <c r="H89" t="n">
-        <v>5285000</v>
+        <v>15772789</v>
       </c>
       <c r="I89" t="n">
-        <v>3427000</v>
+        <v>24527616</v>
       </c>
       <c r="J89" t="n">
-        <v>288</v>
+        <v>117</v>
       </c>
       <c r="K89" t="n">
-        <v>223</v>
+        <v>102</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -14520,70 +14520,70 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>-1786768</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>-2294078</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>540752</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>-5085799</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>-1749364</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>4475778</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>-139968</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>-8024767</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>-73536</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>-8503322</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>-1102322</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>972053</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>36132</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1733466</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1783042</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1966915</v>
       </c>
       <c r="AC89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF89" t="n">
         <v>10</v>
       </c>
-      <c r="AF89" t="n">
-        <v>0</v>
-      </c>
       <c r="AG89" t="n">
         <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -14592,19 +14592,19 @@
         <v>0</v>
       </c>
       <c r="AK89" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AL89" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -14619,17 +14619,17 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14838,16 +14838,16 @@
         </is>
       </c>
       <c r="M91" t="n">
-        <v>-8008564</v>
+        <v>-8053564</v>
       </c>
       <c r="N91" t="n">
-        <v>12745443</v>
+        <v>12700443</v>
       </c>
       <c r="O91" t="n">
-        <v>24419007</v>
+        <v>24374007</v>
       </c>
       <c r="P91" t="n">
-        <v>-138392518</v>
+        <v>-138437518</v>
       </c>
       <c r="Q91" t="n">
         <v>7783688</v>
@@ -14862,16 +14862,16 @@
         <v>-105544124</v>
       </c>
       <c r="U91" t="n">
-        <v>-15449573</v>
+        <v>-15494573</v>
       </c>
       <c r="V91" t="n">
-        <v>-16513679</v>
+        <v>-16558679</v>
       </c>
       <c r="W91" t="n">
-        <v>-16387679</v>
+        <v>-16432679</v>
       </c>
       <c r="X91" t="n">
-        <v>-32770172</v>
+        <v>-32815172</v>
       </c>
       <c r="Y91" t="n">
         <v>-342679</v>
@@ -15113,12 +15113,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2606.TW</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -15127,28 +15127,28 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>76.7</v>
+        <v>240.5</v>
       </c>
       <c r="E93" t="n">
-        <v>76.88</v>
+        <v>237.3</v>
       </c>
       <c r="F93" t="n">
-        <v>76.98</v>
+        <v>237.35</v>
       </c>
       <c r="G93" t="n">
-        <v>76.36</v>
+        <v>245.8</v>
       </c>
       <c r="H93" t="n">
-        <v>2274843</v>
+        <v>5285000</v>
       </c>
       <c r="I93" t="n">
-        <v>3327511</v>
+        <v>3427000</v>
       </c>
       <c r="J93" t="n">
-        <v>81.7</v>
+        <v>288</v>
       </c>
       <c r="K93" t="n">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -15156,52 +15156,52 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>-323828</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>454778</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>987948</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>2960978</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>-295556</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>407093</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>-232722</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>1701699</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>-49000</v>
+        <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>1018000</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>1504000</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>-28272</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>96685</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>202670</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>-244721</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>4</v>
@@ -15210,37 +15210,37 @@
         <v>4</v>
       </c>
       <c r="AE93" t="n">
-        <v>-20</v>
+        <v>10</v>
       </c>
       <c r="AF93" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="AI93" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>-87.5</v>
+        <v>0</v>
       </c>
       <c r="AK93" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AL93" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -15255,17 +15255,17 @@
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、空頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15431,12 +15431,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2707.TW</t>
+          <t>2606.TW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>晶華</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -15445,28 +15445,28 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>178</v>
+        <v>76.7</v>
       </c>
       <c r="E95" t="n">
-        <v>177.3</v>
+        <v>76.88</v>
       </c>
       <c r="F95" t="n">
-        <v>177.45</v>
+        <v>76.98</v>
       </c>
       <c r="G95" t="n">
-        <v>178.28</v>
+        <v>76.36</v>
       </c>
       <c r="H95" t="n">
-        <v>153921</v>
+        <v>2274843</v>
       </c>
       <c r="I95" t="n">
-        <v>108138</v>
+        <v>3327511</v>
       </c>
       <c r="J95" t="n">
-        <v>181</v>
+        <v>81.7</v>
       </c>
       <c r="K95" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -15474,91 +15474,91 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>48000</v>
+        <v>-323828</v>
       </c>
       <c r="N95" t="n">
-        <v>11179</v>
+        <v>454778</v>
       </c>
       <c r="O95" t="n">
-        <v>-29852</v>
+        <v>987948</v>
       </c>
       <c r="P95" t="n">
-        <v>-97899</v>
+        <v>2960978</v>
       </c>
       <c r="Q95" t="n">
-        <v>48000</v>
+        <v>-295556</v>
       </c>
       <c r="R95" t="n">
-        <v>5292</v>
+        <v>407093</v>
       </c>
       <c r="S95" t="n">
-        <v>-30520</v>
+        <v>-232722</v>
       </c>
       <c r="T95" t="n">
-        <v>-77549</v>
+        <v>1701699</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>-49000</v>
       </c>
       <c r="W95" t="n">
-        <v>-6000</v>
+        <v>1018000</v>
       </c>
       <c r="X95" t="n">
-        <v>-26000</v>
+        <v>1504000</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>-28272</v>
       </c>
       <c r="Z95" t="n">
-        <v>5887</v>
+        <v>96685</v>
       </c>
       <c r="AA95" t="n">
-        <v>6668</v>
+        <v>202670</v>
       </c>
       <c r="AB95" t="n">
-        <v>5650</v>
+        <v>-244721</v>
       </c>
       <c r="AC95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE95" t="n">
-        <v>10</v>
+        <v>-20</v>
       </c>
       <c r="AF95" t="n">
-        <v>-5</v>
+        <v>30</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
       </c>
       <c r="AH95" t="n">
-        <v>-16</v>
+        <v>32</v>
       </c>
       <c r="AI95" t="n">
-        <v>18</v>
+        <v>-28</v>
       </c>
       <c r="AJ95" t="n">
-        <v>112.5</v>
+        <v>-87.5</v>
       </c>
       <c r="AK95" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AL95" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -15573,29 +15573,29 @@
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、外資投信同步賣超</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日高點、接近20日低點、短線籌碼止穩、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>6230.TW</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>超眾</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -15604,28 +15604,28 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>253.5</v>
+        <v>111</v>
       </c>
       <c r="E96" t="n">
-        <v>245.5</v>
+        <v>111.3</v>
       </c>
       <c r="F96" t="n">
-        <v>248.35</v>
+        <v>110.4</v>
       </c>
       <c r="G96" t="n">
-        <v>255.62</v>
+        <v>109.92</v>
       </c>
       <c r="H96" t="n">
-        <v>1470000</v>
+        <v>28906</v>
       </c>
       <c r="I96" t="n">
-        <v>1063200</v>
+        <v>45940</v>
       </c>
       <c r="J96" t="n">
-        <v>280.5</v>
+        <v>119</v>
       </c>
       <c r="K96" t="n">
-        <v>237</v>
+        <v>105.5</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -15633,28 +15633,28 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>-4910</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>28120</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>20251</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>17379</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>-4910</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>24120</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>15251</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>13470</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -15672,13 +15672,13 @@
         <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>3909</v>
       </c>
       <c r="AC96" t="n">
         <v>2</v>
@@ -15696,28 +15696,28 @@
         <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>-2</v>
+        <v>30</v>
       </c>
       <c r="AI96" t="n">
-        <v>4</v>
+        <v>-28</v>
       </c>
       <c r="AJ96" t="n">
-        <v>200</v>
+        <v>-93.33</v>
       </c>
       <c r="AK96" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AL96" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -15732,7 +15732,7 @@
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
@@ -15742,19 +15742,19 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6230.TW</t>
+          <t>2707.TW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>超眾</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -15763,28 +15763,28 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="E97" t="n">
-        <v>111.3</v>
+        <v>177.3</v>
       </c>
       <c r="F97" t="n">
-        <v>110.4</v>
+        <v>177.45</v>
       </c>
       <c r="G97" t="n">
-        <v>109.92</v>
+        <v>178.28</v>
       </c>
       <c r="H97" t="n">
-        <v>28906</v>
+        <v>153921</v>
       </c>
       <c r="I97" t="n">
-        <v>45940</v>
+        <v>108138</v>
       </c>
       <c r="J97" t="n">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="K97" t="n">
-        <v>105.5</v>
+        <v>176</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -15792,28 +15792,28 @@
         </is>
       </c>
       <c r="M97" t="n">
-        <v>-4910</v>
+        <v>48000</v>
       </c>
       <c r="N97" t="n">
-        <v>28120</v>
+        <v>11179</v>
       </c>
       <c r="O97" t="n">
-        <v>20251</v>
+        <v>-29852</v>
       </c>
       <c r="P97" t="n">
-        <v>17379</v>
+        <v>-97899</v>
       </c>
       <c r="Q97" t="n">
-        <v>-4910</v>
+        <v>48000</v>
       </c>
       <c r="R97" t="n">
-        <v>24120</v>
+        <v>5292</v>
       </c>
       <c r="S97" t="n">
-        <v>15251</v>
+        <v>-30520</v>
       </c>
       <c r="T97" t="n">
-        <v>13470</v>
+        <v>-77549</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -15822,22 +15822,22 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>-26000</v>
       </c>
       <c r="Y97" t="n">
         <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>4000</v>
+        <v>5887</v>
       </c>
       <c r="AA97" t="n">
-        <v>5000</v>
+        <v>6668</v>
       </c>
       <c r="AB97" t="n">
-        <v>3909</v>
+        <v>5650</v>
       </c>
       <c r="AC97" t="n">
         <v>2</v>
@@ -15846,37 +15846,37 @@
         <v>2</v>
       </c>
       <c r="AE97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
       </c>
       <c r="AH97" t="n">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="AI97" t="n">
-        <v>-28</v>
+        <v>18</v>
       </c>
       <c r="AJ97" t="n">
-        <v>-93.33</v>
+        <v>112.5</v>
       </c>
       <c r="AK97" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL97" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日高點、接近20日低點、短線籌碼止穩、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3443.TW</t>
+          <t>5439.TWO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -15922,28 +15922,28 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>8375</v>
+        <v>253.5</v>
       </c>
       <c r="E98" t="n">
-        <v>7162</v>
+        <v>245.5</v>
       </c>
       <c r="F98" t="n">
-        <v>6651.5</v>
+        <v>248.35</v>
       </c>
       <c r="G98" t="n">
-        <v>6303.5</v>
+        <v>255.62</v>
       </c>
       <c r="H98" t="n">
-        <v>711474</v>
+        <v>1470000</v>
       </c>
       <c r="I98" t="n">
-        <v>2046066</v>
+        <v>1063200</v>
       </c>
       <c r="J98" t="n">
-        <v>8375</v>
+        <v>280.5</v>
       </c>
       <c r="K98" t="n">
-        <v>5570</v>
+        <v>237</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -15951,91 +15951,91 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>-49302</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>-219628</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>-243295</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>15304</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3092</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>-323837</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>-748492</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>-1011673</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>-80378</v>
+        <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>33542</v>
+        <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>495042</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>1100481</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>27984</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>70667</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>10155</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>-73504</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE98" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="AF98" t="n">
-        <v>-70</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
       </c>
       <c r="AH98" t="n">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="AI98" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="AJ98" t="n">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="AK98" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL98" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>DT尚未轉強、離5MA過遠、均線多頭排列、接近20日高位、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -16050,29 +16050,29 @@
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2337.TW</t>
+          <t>3443.TW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -16081,28 +16081,28 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>118</v>
+        <v>8375</v>
       </c>
       <c r="E99" t="n">
-        <v>118.9</v>
+        <v>7162</v>
       </c>
       <c r="F99" t="n">
-        <v>119.3</v>
+        <v>6651.5</v>
       </c>
       <c r="G99" t="n">
-        <v>121.65</v>
+        <v>6303.5</v>
       </c>
       <c r="H99" t="n">
-        <v>24190725</v>
+        <v>711474</v>
       </c>
       <c r="I99" t="n">
-        <v>33346553</v>
+        <v>2046066</v>
       </c>
       <c r="J99" t="n">
-        <v>131</v>
+        <v>8375</v>
       </c>
       <c r="K99" t="n">
-        <v>114</v>
+        <v>5570</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -16110,76 +16110,76 @@
         </is>
       </c>
       <c r="M99" t="n">
-        <v>-3350405</v>
+        <v>-49302</v>
       </c>
       <c r="N99" t="n">
-        <v>3976103</v>
+        <v>-219628</v>
       </c>
       <c r="O99" t="n">
-        <v>4827186</v>
+        <v>-243295</v>
       </c>
       <c r="P99" t="n">
-        <v>-9383036</v>
+        <v>15304</v>
       </c>
       <c r="Q99" t="n">
-        <v>-3558480</v>
+        <v>3092</v>
       </c>
       <c r="R99" t="n">
-        <v>3225143</v>
+        <v>-323837</v>
       </c>
       <c r="S99" t="n">
-        <v>3822382</v>
+        <v>-748492</v>
       </c>
       <c r="T99" t="n">
-        <v>-8978214</v>
+        <v>-1011673</v>
       </c>
       <c r="U99" t="n">
-        <v>44000</v>
+        <v>-80378</v>
       </c>
       <c r="V99" t="n">
-        <v>125000</v>
+        <v>33542</v>
       </c>
       <c r="W99" t="n">
-        <v>324000</v>
+        <v>495042</v>
       </c>
       <c r="X99" t="n">
-        <v>-916000</v>
+        <v>1100481</v>
       </c>
       <c r="Y99" t="n">
-        <v>164075</v>
+        <v>27984</v>
       </c>
       <c r="Z99" t="n">
-        <v>625960</v>
+        <v>70667</v>
       </c>
       <c r="AA99" t="n">
-        <v>680804</v>
+        <v>10155</v>
       </c>
       <c r="AB99" t="n">
-        <v>511178</v>
+        <v>-73504</v>
       </c>
       <c r="AC99" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>-55</v>
+        <v>70</v>
       </c>
       <c r="AF99" t="n">
-        <v>50</v>
+        <v>-70</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
       </c>
       <c r="AH99" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AI99" t="n">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="AJ99" t="n">
-        <v>-111.11</v>
+        <v>-100</v>
       </c>
       <c r="AK99" t="n">
         <v>0</v>
@@ -16194,7 +16194,7 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、離5MA過遠、均線多頭排列、接近20日高位、分數轉弱</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -16209,29 +16209,29 @@
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3023.TW</t>
+          <t>2337.TW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -16240,28 +16240,28 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>320.5</v>
+        <v>118</v>
       </c>
       <c r="E100" t="n">
-        <v>321.2</v>
+        <v>118.9</v>
       </c>
       <c r="F100" t="n">
-        <v>322.4</v>
+        <v>119.3</v>
       </c>
       <c r="G100" t="n">
-        <v>323.27</v>
+        <v>121.65</v>
       </c>
       <c r="H100" t="n">
-        <v>487602</v>
+        <v>24190725</v>
       </c>
       <c r="I100" t="n">
-        <v>642931</v>
+        <v>33346553</v>
       </c>
       <c r="J100" t="n">
-        <v>348</v>
+        <v>131</v>
       </c>
       <c r="K100" t="n">
-        <v>310</v>
+        <v>114</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -16269,52 +16269,52 @@
         </is>
       </c>
       <c r="M100" t="n">
-        <v>20937</v>
+        <v>-3350405</v>
       </c>
       <c r="N100" t="n">
-        <v>259663</v>
+        <v>3976103</v>
       </c>
       <c r="O100" t="n">
-        <v>325475</v>
+        <v>4827186</v>
       </c>
       <c r="P100" t="n">
-        <v>760945</v>
+        <v>-9383036</v>
       </c>
       <c r="Q100" t="n">
-        <v>19174</v>
+        <v>-3558480</v>
       </c>
       <c r="R100" t="n">
-        <v>299067</v>
+        <v>3225143</v>
       </c>
       <c r="S100" t="n">
-        <v>394072</v>
+        <v>3822382</v>
       </c>
       <c r="T100" t="n">
-        <v>547724</v>
+        <v>-8978214</v>
       </c>
       <c r="U100" t="n">
-        <v>-2000</v>
+        <v>44000</v>
       </c>
       <c r="V100" t="n">
-        <v>-58000</v>
+        <v>125000</v>
       </c>
       <c r="W100" t="n">
-        <v>-101000</v>
+        <v>324000</v>
       </c>
       <c r="X100" t="n">
-        <v>177000</v>
+        <v>-916000</v>
       </c>
       <c r="Y100" t="n">
-        <v>3763</v>
+        <v>164075</v>
       </c>
       <c r="Z100" t="n">
-        <v>18596</v>
+        <v>625960</v>
       </c>
       <c r="AA100" t="n">
-        <v>32403</v>
+        <v>680804</v>
       </c>
       <c r="AB100" t="n">
-        <v>36221</v>
+        <v>511178</v>
       </c>
       <c r="AC100" t="n">
         <v>-2</v>
@@ -16332,19 +16332,19 @@
         <v>0</v>
       </c>
       <c r="AH100" t="n">
-        <v>-6</v>
+        <v>18</v>
       </c>
       <c r="AI100" t="n">
-        <v>4</v>
+        <v>-20</v>
       </c>
       <c r="AJ100" t="n">
-        <v>66.67</v>
+        <v>-111.11</v>
       </c>
       <c r="AK100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM100" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -16373,24 +16373,24 @@
       </c>
       <c r="AR100" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>3023.TW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -16399,28 +16399,28 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>667</v>
+        <v>320.5</v>
       </c>
       <c r="E101" t="n">
-        <v>662.8</v>
+        <v>321.2</v>
       </c>
       <c r="F101" t="n">
-        <v>670.6</v>
+        <v>322.4</v>
       </c>
       <c r="G101" t="n">
-        <v>712.7</v>
+        <v>323.27</v>
       </c>
       <c r="H101" t="n">
-        <v>1532000</v>
+        <v>487602</v>
       </c>
       <c r="I101" t="n">
-        <v>1670800</v>
+        <v>642931</v>
       </c>
       <c r="J101" t="n">
-        <v>814</v>
+        <v>348</v>
       </c>
       <c r="K101" t="n">
-        <v>631</v>
+        <v>310</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -16428,52 +16428,52 @@
         </is>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>20937</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>259663</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>325475</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>760945</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>19174</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>299067</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>394072</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>547724</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>-58000</v>
       </c>
       <c r="W101" t="n">
-        <v>0</v>
+        <v>-101000</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>177000</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>3763</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>18596</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>32403</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>36221</v>
       </c>
       <c r="AC101" t="n">
         <v>-2</v>
@@ -16482,37 +16482,37 @@
         <v>-2</v>
       </c>
       <c r="AE101" t="n">
-        <v>-5</v>
+        <v>-55</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="AI101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ101" t="n">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="AK101" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AL101" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -16527,29 +16527,29 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2455.TW</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -16558,28 +16558,28 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>547</v>
+        <v>667</v>
       </c>
       <c r="E102" t="n">
-        <v>544.8</v>
+        <v>662.8</v>
       </c>
       <c r="F102" t="n">
-        <v>535.9</v>
+        <v>670.6</v>
       </c>
       <c r="G102" t="n">
-        <v>513.25</v>
+        <v>712.7</v>
       </c>
       <c r="H102" t="n">
-        <v>18755075</v>
+        <v>1532000</v>
       </c>
       <c r="I102" t="n">
-        <v>20555460</v>
+        <v>1670800</v>
       </c>
       <c r="J102" t="n">
-        <v>590</v>
+        <v>814</v>
       </c>
       <c r="K102" t="n">
-        <v>415</v>
+        <v>631</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -16587,91 +16587,91 @@
         </is>
       </c>
       <c r="M102" t="n">
-        <v>-3369722</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>-3013575</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>-3619812</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>-1582681</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>-2880406</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>-4426659</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>-5828299</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>-3577029</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>-199000</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>1537000</v>
+        <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>2023710</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1964510</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>-290316</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>-123916</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>184777</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>29838</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AD102" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AE102" t="n">
-        <v>45</v>
+        <v>-5</v>
       </c>
       <c r="AF102" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
       </c>
       <c r="AH102" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="AI102" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AJ102" t="n">
-        <v>-166.67</v>
+        <v>0</v>
       </c>
       <c r="AK102" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AL102" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -16686,29 +16686,29 @@
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>2455.TW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -16717,28 +16717,28 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>24.1</v>
+        <v>547</v>
       </c>
       <c r="E103" t="n">
-        <v>24.36</v>
+        <v>544.8</v>
       </c>
       <c r="F103" t="n">
-        <v>24.65</v>
+        <v>535.9</v>
       </c>
       <c r="G103" t="n">
-        <v>24.71</v>
+        <v>513.25</v>
       </c>
       <c r="H103" t="n">
-        <v>9111079</v>
+        <v>18755075</v>
       </c>
       <c r="I103" t="n">
-        <v>9035091</v>
+        <v>20555460</v>
       </c>
       <c r="J103" t="n">
-        <v>27.05</v>
+        <v>590</v>
       </c>
       <c r="K103" t="n">
-        <v>23.7</v>
+        <v>415</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -16746,91 +16746,91 @@
         </is>
       </c>
       <c r="M103" t="n">
-        <v>-2690725</v>
+        <v>-3369722</v>
       </c>
       <c r="N103" t="n">
-        <v>-3359001</v>
+        <v>-3013575</v>
       </c>
       <c r="O103" t="n">
-        <v>1173244</v>
+        <v>-3619812</v>
       </c>
       <c r="P103" t="n">
-        <v>-8841171</v>
+        <v>-1582681</v>
       </c>
       <c r="Q103" t="n">
-        <v>-2699481</v>
+        <v>-2880406</v>
       </c>
       <c r="R103" t="n">
-        <v>-3420332</v>
+        <v>-4426659</v>
       </c>
       <c r="S103" t="n">
-        <v>999110</v>
+        <v>-5828299</v>
       </c>
       <c r="T103" t="n">
-        <v>-7556924</v>
+        <v>-3577029</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>-199000</v>
       </c>
       <c r="V103" t="n">
-        <v>2000</v>
+        <v>1537000</v>
       </c>
       <c r="W103" t="n">
-        <v>-20000</v>
+        <v>2023710</v>
       </c>
       <c r="X103" t="n">
-        <v>-187000</v>
+        <v>1964510</v>
       </c>
       <c r="Y103" t="n">
-        <v>8756</v>
+        <v>-290316</v>
       </c>
       <c r="Z103" t="n">
-        <v>59331</v>
+        <v>-123916</v>
       </c>
       <c r="AA103" t="n">
-        <v>194134</v>
+        <v>184777</v>
       </c>
       <c r="AB103" t="n">
-        <v>-1097247</v>
+        <v>29838</v>
       </c>
       <c r="AC103" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AD103" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AE103" t="n">
-        <v>-45</v>
+        <v>45</v>
       </c>
       <c r="AF103" t="n">
-        <v>30</v>
+        <v>-55</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
       </c>
       <c r="AH103" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AI103" t="n">
-        <v>-24</v>
+        <v>-10</v>
       </c>
       <c r="AJ103" t="n">
-        <v>-133.33</v>
+        <v>-166.67</v>
       </c>
       <c r="AK103" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AL103" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -16845,29 +16845,29 @@
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3062.TW</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>建漢</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -16876,57 +16876,57 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>22.35</v>
+        <v>1295</v>
       </c>
       <c r="E104" t="n">
-        <v>21.71</v>
+        <v>1292</v>
       </c>
       <c r="F104" t="n">
-        <v>21.06</v>
+        <v>1296.5</v>
       </c>
       <c r="G104" t="n">
-        <v>20.91</v>
+        <v>1361.25</v>
       </c>
       <c r="H104" t="n">
-        <v>7900418</v>
+        <v>957000</v>
       </c>
       <c r="I104" t="n">
-        <v>3625696</v>
+        <v>1064000</v>
       </c>
       <c r="J104" t="n">
-        <v>23.2</v>
+        <v>1535</v>
       </c>
       <c r="K104" t="n">
-        <v>20.1</v>
+        <v>1240</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M104" t="n">
-        <v>-697276</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>-1058751</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>-128249</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>318233</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>-678973</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>-1085574</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>-287871</v>
+        <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>206539</v>
+        <v>0</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -16941,16 +16941,16 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>-18303</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>26823</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>159622</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>111694</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>-6</v>
@@ -16959,37 +16959,37 @@
         <v>-6</v>
       </c>
       <c r="AE104" t="n">
-        <v>65</v>
+        <v>-15</v>
       </c>
       <c r="AF104" t="n">
-        <v>-70</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="n">
-        <v>49</v>
+        <v>-2</v>
       </c>
       <c r="AI104" t="n">
-        <v>-55</v>
+        <v>-4</v>
       </c>
       <c r="AJ104" t="n">
-        <v>-112.24</v>
+        <v>-200</v>
       </c>
       <c r="AK104" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="AL104" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -17004,29 +17004,29 @@
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2748.TW</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>雲品</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -17035,28 +17035,28 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>38.7</v>
+        <v>233.5</v>
       </c>
       <c r="E105" t="n">
-        <v>38.78</v>
+        <v>228.1</v>
       </c>
       <c r="F105" t="n">
-        <v>38.91</v>
+        <v>226.75</v>
       </c>
       <c r="G105" t="n">
-        <v>38.87</v>
+        <v>234.62</v>
       </c>
       <c r="H105" t="n">
-        <v>12237</v>
+        <v>2876664</v>
       </c>
       <c r="I105" t="n">
-        <v>54447</v>
+        <v>3722119</v>
       </c>
       <c r="J105" t="n">
-        <v>39.9</v>
+        <v>255</v>
       </c>
       <c r="K105" t="n">
-        <v>38.35</v>
+        <v>216</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -17064,52 +17064,52 @@
         </is>
       </c>
       <c r="M105" t="n">
-        <v>1000</v>
+        <v>75938</v>
       </c>
       <c r="N105" t="n">
-        <v>7000</v>
+        <v>537960</v>
       </c>
       <c r="O105" t="n">
-        <v>-14000</v>
+        <v>-703726</v>
       </c>
       <c r="P105" t="n">
-        <v>-40000</v>
+        <v>-2032342</v>
       </c>
       <c r="Q105" t="n">
-        <v>1000</v>
+        <v>28468</v>
       </c>
       <c r="R105" t="n">
-        <v>3000</v>
+        <v>394042</v>
       </c>
       <c r="S105" t="n">
-        <v>-20000</v>
+        <v>-226133</v>
       </c>
       <c r="T105" t="n">
-        <v>-46000</v>
+        <v>-1455042</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="W105" t="n">
-        <v>0</v>
+        <v>-729000</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>-557856</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>47470</v>
       </c>
       <c r="Z105" t="n">
-        <v>4000</v>
+        <v>139918</v>
       </c>
       <c r="AA105" t="n">
-        <v>6000</v>
+        <v>251407</v>
       </c>
       <c r="AB105" t="n">
-        <v>6000</v>
+        <v>-19444</v>
       </c>
       <c r="AC105" t="n">
         <v>-6</v>
@@ -17118,37 +17118,37 @@
         <v>-6</v>
       </c>
       <c r="AE105" t="n">
-        <v>-30</v>
+        <v>20</v>
       </c>
       <c r="AF105" t="n">
-        <v>15</v>
+        <v>-35</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
       </c>
       <c r="AH105" t="n">
-        <v>4</v>
+        <v>-16</v>
       </c>
       <c r="AI105" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="AJ105" t="n">
-        <v>-250</v>
+        <v>62.5</v>
       </c>
       <c r="AK105" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL105" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -17163,29 +17163,29 @@
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>短線籌碼止穩</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、短線籌碼止穩。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -17194,28 +17194,28 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1295</v>
+        <v>24.1</v>
       </c>
       <c r="E106" t="n">
-        <v>1292</v>
+        <v>24.36</v>
       </c>
       <c r="F106" t="n">
-        <v>1296.5</v>
+        <v>24.65</v>
       </c>
       <c r="G106" t="n">
-        <v>1361.25</v>
+        <v>24.71</v>
       </c>
       <c r="H106" t="n">
-        <v>957000</v>
+        <v>9111079</v>
       </c>
       <c r="I106" t="n">
-        <v>1064000</v>
+        <v>9035091</v>
       </c>
       <c r="J106" t="n">
-        <v>1535</v>
+        <v>27.05</v>
       </c>
       <c r="K106" t="n">
-        <v>1240</v>
+        <v>23.7</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -17223,52 +17223,52 @@
         </is>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>-2690725</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>-3359001</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>1173244</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>-8841171</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>-2699481</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>-3420332</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>999110</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>-7556924</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
       </c>
       <c r="V106" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="W106" t="n">
-        <v>0</v>
+        <v>-20000</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>-187000</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>8756</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>59331</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>194134</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>-1097247</v>
       </c>
       <c r="AC106" t="n">
         <v>-6</v>
@@ -17277,28 +17277,28 @@
         <v>-6</v>
       </c>
       <c r="AE106" t="n">
-        <v>-15</v>
+        <v>-45</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
       </c>
       <c r="AH106" t="n">
-        <v>-2</v>
+        <v>18</v>
       </c>
       <c r="AI106" t="n">
-        <v>-4</v>
+        <v>-24</v>
       </c>
       <c r="AJ106" t="n">
-        <v>-200</v>
+        <v>-133.33</v>
       </c>
       <c r="AK106" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AL106" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AM106" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -17322,29 +17322,29 @@
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>3062.TW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>建漢</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -17353,81 +17353,81 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>233.5</v>
+        <v>22.35</v>
       </c>
       <c r="E107" t="n">
-        <v>228.1</v>
+        <v>21.71</v>
       </c>
       <c r="F107" t="n">
-        <v>226.75</v>
+        <v>21.06</v>
       </c>
       <c r="G107" t="n">
-        <v>234.62</v>
+        <v>20.91</v>
       </c>
       <c r="H107" t="n">
-        <v>2876664</v>
+        <v>7900418</v>
       </c>
       <c r="I107" t="n">
-        <v>3722119</v>
+        <v>3625696</v>
       </c>
       <c r="J107" t="n">
-        <v>255</v>
+        <v>23.2</v>
       </c>
       <c r="K107" t="n">
-        <v>216</v>
+        <v>20.1</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="M107" t="n">
-        <v>75938</v>
+        <v>-697276</v>
       </c>
       <c r="N107" t="n">
-        <v>537960</v>
+        <v>-1058751</v>
       </c>
       <c r="O107" t="n">
-        <v>-703726</v>
+        <v>-128249</v>
       </c>
       <c r="P107" t="n">
-        <v>-2032342</v>
+        <v>318233</v>
       </c>
       <c r="Q107" t="n">
-        <v>28468</v>
+        <v>-678973</v>
       </c>
       <c r="R107" t="n">
-        <v>394042</v>
+        <v>-1085574</v>
       </c>
       <c r="S107" t="n">
-        <v>-226133</v>
+        <v>-287871</v>
       </c>
       <c r="T107" t="n">
-        <v>-1455042</v>
+        <v>206539</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>-729000</v>
+        <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>-557856</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>47470</v>
+        <v>-18303</v>
       </c>
       <c r="Z107" t="n">
-        <v>139918</v>
+        <v>26823</v>
       </c>
       <c r="AA107" t="n">
-        <v>251407</v>
+        <v>159622</v>
       </c>
       <c r="AB107" t="n">
-        <v>-19444</v>
+        <v>111694</v>
       </c>
       <c r="AC107" t="n">
         <v>-6</v>
@@ -17436,37 +17436,37 @@
         <v>-6</v>
       </c>
       <c r="AE107" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AF107" t="n">
-        <v>-35</v>
+        <v>-70</v>
       </c>
       <c r="AG107" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AH107" t="n">
-        <v>-16</v>
+        <v>49</v>
       </c>
       <c r="AI107" t="n">
-        <v>10</v>
+        <v>-55</v>
       </c>
       <c r="AJ107" t="n">
-        <v>62.5</v>
+        <v>-112.24</v>
       </c>
       <c r="AK107" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="AL107" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -17481,29 +17481,29 @@
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>2748.TW</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>雲品</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -17512,28 +17512,28 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>222.5</v>
+        <v>38.7</v>
       </c>
       <c r="E108" t="n">
-        <v>235.3</v>
+        <v>38.78</v>
       </c>
       <c r="F108" t="n">
-        <v>235.45</v>
+        <v>38.91</v>
       </c>
       <c r="G108" t="n">
-        <v>222.7</v>
+        <v>38.87</v>
       </c>
       <c r="H108" t="n">
-        <v>3130000</v>
+        <v>12237</v>
       </c>
       <c r="I108" t="n">
-        <v>7293200</v>
+        <v>54447</v>
       </c>
       <c r="J108" t="n">
-        <v>265</v>
+        <v>39.9</v>
       </c>
       <c r="K108" t="n">
-        <v>160</v>
+        <v>38.35</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -17541,28 +17541,28 @@
         </is>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>-14000</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>-40000</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>-20000</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>-46000</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -17580,43 +17580,43 @@
         <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="AC108" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AD108" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AE108" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
       </c>
       <c r="AH108" t="n">
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="AI108" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0</v>
+        <v>-250</v>
       </c>
       <c r="AK108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM108" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -17640,29 +17640,29 @@
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、短線籌碼止穩。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -17671,28 +17671,28 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>23.4</v>
+        <v>222.5</v>
       </c>
       <c r="E109" t="n">
-        <v>22.35</v>
+        <v>235.3</v>
       </c>
       <c r="F109" t="n">
-        <v>21.28</v>
+        <v>235.45</v>
       </c>
       <c r="G109" t="n">
-        <v>21.31</v>
+        <v>222.7</v>
       </c>
       <c r="H109" t="n">
-        <v>11027992</v>
+        <v>3130000</v>
       </c>
       <c r="I109" t="n">
-        <v>10024789</v>
+        <v>7293200</v>
       </c>
       <c r="J109" t="n">
-        <v>24.95</v>
+        <v>265</v>
       </c>
       <c r="K109" t="n">
-        <v>19.5</v>
+        <v>160</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -17700,28 +17700,28 @@
         </is>
       </c>
       <c r="M109" t="n">
-        <v>-620236</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>-6816036</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>-4968298</v>
+        <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>-4376414</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>-668899</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>-7005324</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>-5171910</v>
+        <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>-4551260</v>
+        <v>0</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -17736,44 +17736,46 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>48663</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>189288</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>203612</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>174846</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AD109" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AE109" t="n">
-        <v>30</v>
+        <v>-20</v>
       </c>
       <c r="AF109" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
       </c>
       <c r="AH109" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AI109" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AJ109" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>0</v>
+      </c>
       <c r="AK109" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AL109" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
@@ -17782,7 +17784,7 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -17797,17 +17799,17 @@
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -18132,12 +18134,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8028.TW</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -18146,28 +18148,28 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>263.5</v>
+        <v>23.4</v>
       </c>
       <c r="E112" t="n">
-        <v>251</v>
+        <v>22.35</v>
       </c>
       <c r="F112" t="n">
-        <v>239.4</v>
+        <v>21.28</v>
       </c>
       <c r="G112" t="n">
-        <v>242.05</v>
+        <v>21.31</v>
       </c>
       <c r="H112" t="n">
-        <v>13456615</v>
+        <v>11027992</v>
       </c>
       <c r="I112" t="n">
-        <v>10017264</v>
+        <v>10024789</v>
       </c>
       <c r="J112" t="n">
-        <v>274</v>
+        <v>24.95</v>
       </c>
       <c r="K112" t="n">
-        <v>216.5</v>
+        <v>19.5</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -18175,52 +18177,52 @@
         </is>
       </c>
       <c r="M112" t="n">
-        <v>-2969992</v>
+        <v>-620236</v>
       </c>
       <c r="N112" t="n">
-        <v>-3280376</v>
+        <v>-6816036</v>
       </c>
       <c r="O112" t="n">
-        <v>-2916981</v>
+        <v>-4968298</v>
       </c>
       <c r="P112" t="n">
-        <v>-5889038</v>
+        <v>-4376414</v>
       </c>
       <c r="Q112" t="n">
-        <v>-3025665</v>
+        <v>-668899</v>
       </c>
       <c r="R112" t="n">
-        <v>-6247903</v>
+        <v>-7005324</v>
       </c>
       <c r="S112" t="n">
-        <v>-9566008</v>
+        <v>-5171910</v>
       </c>
       <c r="T112" t="n">
-        <v>-13282145</v>
+        <v>-4551260</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>2935000</v>
+        <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>6496000</v>
+        <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>7350000</v>
+        <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>55673</v>
+        <v>48663</v>
       </c>
       <c r="Z112" t="n">
-        <v>32527</v>
+        <v>189288</v>
       </c>
       <c r="AA112" t="n">
-        <v>153027</v>
+        <v>203612</v>
       </c>
       <c r="AB112" t="n">
-        <v>43107</v>
+        <v>174846</v>
       </c>
       <c r="AC112" t="n">
         <v>-10</v>
@@ -18238,28 +18240,26 @@
         <v>0</v>
       </c>
       <c r="AH112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI112" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AJ112" t="n">
-        <v>-600</v>
-      </c>
+        <v>-10</v>
+      </c>
+      <c r="AJ112" t="inlineStr"/>
       <c r="AK112" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AL112" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -18279,12 +18279,12 @@
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -18450,12 +18450,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>7769.TW</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -18464,28 +18464,28 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>6155</v>
+        <v>491.5</v>
       </c>
       <c r="E114" t="n">
-        <v>6191</v>
+        <v>494.2</v>
       </c>
       <c r="F114" t="n">
-        <v>6290</v>
+        <v>500.3</v>
       </c>
       <c r="G114" t="n">
-        <v>6244.75</v>
+        <v>503.18</v>
       </c>
       <c r="H114" t="n">
-        <v>1210764</v>
+        <v>2206000</v>
       </c>
       <c r="I114" t="n">
-        <v>1550493</v>
+        <v>12111600</v>
       </c>
       <c r="J114" t="n">
-        <v>7160</v>
+        <v>564</v>
       </c>
       <c r="K114" t="n">
-        <v>5620</v>
+        <v>419</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -18493,82 +18493,82 @@
         </is>
       </c>
       <c r="M114" t="n">
-        <v>113976</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>-472017</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>-435843</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>-603426</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>238850</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>78959</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>85767</v>
+        <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>9814</v>
+        <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>-116441</v>
+        <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>-570100</v>
+        <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>-560100</v>
+        <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>-639022</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>-8433</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>19124</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>38490</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>25782</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="AD114" t="n">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="AE114" t="n">
-        <v>-20</v>
+        <v>-45</v>
       </c>
       <c r="AF114" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
       </c>
       <c r="AH114" t="n">
-        <v>-34</v>
+        <v>-18</v>
       </c>
       <c r="AI114" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AJ114" t="n">
-        <v>52.94</v>
+        <v>0</v>
       </c>
       <c r="AK114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AL114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -18592,29 +18592,29 @@
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>5日法人賣超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>3363.TWO</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -18623,28 +18623,28 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>491.5</v>
+        <v>660</v>
       </c>
       <c r="E115" t="n">
-        <v>494.2</v>
+        <v>668.6</v>
       </c>
       <c r="F115" t="n">
-        <v>500.3</v>
+        <v>676.9</v>
       </c>
       <c r="G115" t="n">
-        <v>503.18</v>
+        <v>704</v>
       </c>
       <c r="H115" t="n">
-        <v>2206000</v>
+        <v>2787000</v>
       </c>
       <c r="I115" t="n">
-        <v>12111600</v>
+        <v>3021400</v>
       </c>
       <c r="J115" t="n">
-        <v>564</v>
+        <v>850</v>
       </c>
       <c r="K115" t="n">
-        <v>419</v>
+        <v>623</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -18724,10 +18724,10 @@
         <v>0</v>
       </c>
       <c r="AK115" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL115" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM115" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -19086,12 +19086,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3363.TWO</t>
+          <t>3376.TW</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -19100,28 +19100,28 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>660</v>
+        <v>180.5</v>
       </c>
       <c r="E118" t="n">
-        <v>668.6</v>
+        <v>177.7</v>
       </c>
       <c r="F118" t="n">
-        <v>676.9</v>
+        <v>182.1</v>
       </c>
       <c r="G118" t="n">
-        <v>704</v>
+        <v>195.1</v>
       </c>
       <c r="H118" t="n">
-        <v>2787000</v>
+        <v>3426008</v>
       </c>
       <c r="I118" t="n">
-        <v>3021400</v>
+        <v>2772854</v>
       </c>
       <c r="J118" t="n">
-        <v>850</v>
+        <v>222</v>
       </c>
       <c r="K118" t="n">
-        <v>623</v>
+        <v>170.5</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -19129,91 +19129,91 @@
         </is>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>-570692</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>-1166899</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>-2367552</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>-14963639</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>-497226</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>-1112463</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>-2295810</v>
       </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>-13943151</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
       </c>
       <c r="V118" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="W118" t="n">
-        <v>0</v>
+        <v>114000</v>
       </c>
       <c r="X118" t="n">
-        <v>0</v>
+        <v>134000</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>-73466</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>-98436</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>-185742</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>-1154488</v>
       </c>
       <c r="AC118" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="AD118" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="AE118" t="n">
-        <v>-45</v>
+        <v>5</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
       </c>
       <c r="AH118" t="n">
-        <v>-18</v>
+        <v>-28</v>
       </c>
       <c r="AI118" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ118" t="n">
-        <v>0</v>
+        <v>28.57</v>
       </c>
       <c r="AK118" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AL118" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -19228,17 +19228,17 @@
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -19563,12 +19563,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3013.TW</t>
+          <t>7769.TW</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>晟銘電</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -19577,28 +19577,28 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>83.09999999999999</v>
+        <v>6155</v>
       </c>
       <c r="E121" t="n">
-        <v>82.86</v>
+        <v>6191</v>
       </c>
       <c r="F121" t="n">
-        <v>83.77</v>
+        <v>6290</v>
       </c>
       <c r="G121" t="n">
-        <v>85.8</v>
+        <v>6244.75</v>
       </c>
       <c r="H121" t="n">
-        <v>754735</v>
+        <v>1210764</v>
       </c>
       <c r="I121" t="n">
-        <v>644447</v>
+        <v>1550493</v>
       </c>
       <c r="J121" t="n">
-        <v>93.90000000000001</v>
+        <v>7160</v>
       </c>
       <c r="K121" t="n">
-        <v>81.5</v>
+        <v>5620</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -19606,52 +19606,52 @@
         </is>
       </c>
       <c r="M121" t="n">
-        <v>-43161</v>
+        <v>43256</v>
       </c>
       <c r="N121" t="n">
-        <v>-157268</v>
+        <v>-542737</v>
       </c>
       <c r="O121" t="n">
-        <v>-121383</v>
+        <v>-506563</v>
       </c>
       <c r="P121" t="n">
-        <v>-139897</v>
+        <v>-674146</v>
       </c>
       <c r="Q121" t="n">
-        <v>-48598</v>
+        <v>238850</v>
       </c>
       <c r="R121" t="n">
-        <v>-158090</v>
+        <v>78959</v>
       </c>
       <c r="S121" t="n">
-        <v>-126203</v>
+        <v>85767</v>
       </c>
       <c r="T121" t="n">
-        <v>-107935</v>
+        <v>9814</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>-187161</v>
       </c>
       <c r="V121" t="n">
-        <v>1000</v>
+        <v>-640820</v>
       </c>
       <c r="W121" t="n">
-        <v>3000</v>
+        <v>-630820</v>
       </c>
       <c r="X121" t="n">
-        <v>16000</v>
+        <v>-709742</v>
       </c>
       <c r="Y121" t="n">
-        <v>5437</v>
+        <v>-8433</v>
       </c>
       <c r="Z121" t="n">
-        <v>-178</v>
+        <v>19124</v>
       </c>
       <c r="AA121" t="n">
-        <v>1820</v>
+        <v>38490</v>
       </c>
       <c r="AB121" t="n">
-        <v>-47962</v>
+        <v>25782</v>
       </c>
       <c r="AC121" t="n">
         <v>-20</v>
@@ -19660,28 +19660,28 @@
         <v>-20</v>
       </c>
       <c r="AE121" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="AF121" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
       </c>
       <c r="AH121" t="n">
-        <v>-10</v>
+        <v>-34</v>
       </c>
       <c r="AI121" t="n">
-        <v>-10</v>
+        <v>14</v>
       </c>
       <c r="AJ121" t="n">
-        <v>-100</v>
+        <v>41.18</v>
       </c>
       <c r="AK121" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL121" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM121" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -19705,29 +19705,29 @@
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3376.TW</t>
+          <t>3013.TW</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>晟銘電</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -19736,28 +19736,28 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>180.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="E122" t="n">
-        <v>177.7</v>
+        <v>82.86</v>
       </c>
       <c r="F122" t="n">
-        <v>182.1</v>
+        <v>83.77</v>
       </c>
       <c r="G122" t="n">
-        <v>195.1</v>
+        <v>85.8</v>
       </c>
       <c r="H122" t="n">
-        <v>3426008</v>
+        <v>754735</v>
       </c>
       <c r="I122" t="n">
-        <v>2772854</v>
+        <v>644447</v>
       </c>
       <c r="J122" t="n">
-        <v>222</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K122" t="n">
-        <v>170.5</v>
+        <v>81.5</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -19765,52 +19765,52 @@
         </is>
       </c>
       <c r="M122" t="n">
-        <v>-570692</v>
+        <v>-43161</v>
       </c>
       <c r="N122" t="n">
-        <v>-1166899</v>
+        <v>-157268</v>
       </c>
       <c r="O122" t="n">
-        <v>-2367552</v>
+        <v>-121383</v>
       </c>
       <c r="P122" t="n">
-        <v>-14963639</v>
+        <v>-139897</v>
       </c>
       <c r="Q122" t="n">
-        <v>-497226</v>
+        <v>-48598</v>
       </c>
       <c r="R122" t="n">
-        <v>-1112463</v>
+        <v>-158090</v>
       </c>
       <c r="S122" t="n">
-        <v>-2295810</v>
+        <v>-126203</v>
       </c>
       <c r="T122" t="n">
-        <v>-13943151</v>
+        <v>-107935</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>44000</v>
+        <v>1000</v>
       </c>
       <c r="W122" t="n">
-        <v>114000</v>
+        <v>3000</v>
       </c>
       <c r="X122" t="n">
-        <v>134000</v>
+        <v>16000</v>
       </c>
       <c r="Y122" t="n">
-        <v>-73466</v>
+        <v>5437</v>
       </c>
       <c r="Z122" t="n">
-        <v>-98436</v>
+        <v>-178</v>
       </c>
       <c r="AA122" t="n">
-        <v>-185742</v>
+        <v>1820</v>
       </c>
       <c r="AB122" t="n">
-        <v>-1154488</v>
+        <v>-47962</v>
       </c>
       <c r="AC122" t="n">
         <v>-20</v>
@@ -19819,37 +19819,37 @@
         <v>-20</v>
       </c>
       <c r="AE122" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AF122" t="n">
-        <v>-55</v>
+        <v>-45</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
       </c>
       <c r="AH122" t="n">
-        <v>-28</v>
+        <v>-10</v>
       </c>
       <c r="AI122" t="n">
-        <v>8</v>
+        <v>-10</v>
       </c>
       <c r="AJ122" t="n">
-        <v>28.57</v>
+        <v>-100</v>
       </c>
       <c r="AK122" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="AL122" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -19864,17 +19864,17 @@
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -19924,16 +19924,16 @@
         </is>
       </c>
       <c r="M123" t="n">
-        <v>950911</v>
+        <v>979911</v>
       </c>
       <c r="N123" t="n">
-        <v>-5628288</v>
+        <v>-5599288</v>
       </c>
       <c r="O123" t="n">
-        <v>-14230168</v>
+        <v>-14201168</v>
       </c>
       <c r="P123" t="n">
-        <v>-16869544</v>
+        <v>-16840544</v>
       </c>
       <c r="Q123" t="n">
         <v>817185</v>
@@ -19948,16 +19948,16 @@
         <v>-12152109</v>
       </c>
       <c r="U123" t="n">
-        <v>374656</v>
+        <v>403656</v>
       </c>
       <c r="V123" t="n">
-        <v>-671758</v>
+        <v>-642758</v>
       </c>
       <c r="W123" t="n">
-        <v>218652</v>
+        <v>247652</v>
       </c>
       <c r="X123" t="n">
-        <v>-3588701</v>
+        <v>-3559701</v>
       </c>
       <c r="Y123" t="n">
         <v>-240930</v>
@@ -21630,12 +21630,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>3231.TW</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -21644,28 +21644,28 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>4860</v>
+        <v>180.5</v>
       </c>
       <c r="E134" t="n">
-        <v>4885</v>
+        <v>184.6</v>
       </c>
       <c r="F134" t="n">
-        <v>5100</v>
+        <v>184.6</v>
       </c>
       <c r="G134" t="n">
-        <v>5299.75</v>
+        <v>185.05</v>
       </c>
       <c r="H134" t="n">
-        <v>2101406</v>
+        <v>69481193</v>
       </c>
       <c r="I134" t="n">
-        <v>3155635</v>
+        <v>39867959</v>
       </c>
       <c r="J134" t="n">
-        <v>5960</v>
+        <v>200.5</v>
       </c>
       <c r="K134" t="n">
-        <v>4635</v>
+        <v>174</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -21673,82 +21673,82 @@
         </is>
       </c>
       <c r="M134" t="n">
-        <v>211866</v>
+        <v>-36167085</v>
       </c>
       <c r="N134" t="n">
-        <v>-306030</v>
+        <v>-37768352</v>
       </c>
       <c r="O134" t="n">
-        <v>-633605</v>
+        <v>-35597614</v>
       </c>
       <c r="P134" t="n">
-        <v>-1024010</v>
+        <v>-74869497</v>
       </c>
       <c r="Q134" t="n">
-        <v>331258</v>
+        <v>-30549430</v>
       </c>
       <c r="R134" t="n">
-        <v>1016703</v>
+        <v>-31951957</v>
       </c>
       <c r="S134" t="n">
-        <v>1359948</v>
+        <v>-32812476</v>
       </c>
       <c r="T134" t="n">
-        <v>1486355</v>
+        <v>-71642812</v>
       </c>
       <c r="U134" t="n">
-        <v>-169228</v>
+        <v>-5434984</v>
       </c>
       <c r="V134" t="n">
-        <v>-1521646</v>
+        <v>-6364252</v>
       </c>
       <c r="W134" t="n">
-        <v>-2411646</v>
+        <v>-2370252</v>
       </c>
       <c r="X134" t="n">
-        <v>-2837889</v>
+        <v>-2305930</v>
       </c>
       <c r="Y134" t="n">
-        <v>49836</v>
+        <v>-182671</v>
       </c>
       <c r="Z134" t="n">
-        <v>198913</v>
+        <v>547857</v>
       </c>
       <c r="AA134" t="n">
-        <v>418093</v>
+        <v>-414886</v>
       </c>
       <c r="AB134" t="n">
-        <v>327524</v>
+        <v>-920755</v>
       </c>
       <c r="AC134" t="n">
-        <v>-34</v>
+        <v>-36</v>
       </c>
       <c r="AD134" t="n">
-        <v>-34</v>
+        <v>-36</v>
       </c>
       <c r="AE134" t="n">
-        <v>-55</v>
+        <v>-15</v>
       </c>
       <c r="AF134" t="n">
-        <v>-30</v>
+        <v>-75</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
       </c>
       <c r="AH134" t="n">
-        <v>-40</v>
+        <v>16</v>
       </c>
       <c r="AI134" t="n">
-        <v>6</v>
+        <v>-52</v>
       </c>
       <c r="AJ134" t="n">
-        <v>15</v>
+        <v>-325</v>
       </c>
       <c r="AK134" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL134" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM134" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -21772,29 +21772,29 @@
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資買投信賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、成交量放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3231.TW</t>
+          <t>6269.TW</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -21803,28 +21803,28 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>180.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E135" t="n">
-        <v>184.6</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F135" t="n">
-        <v>184.6</v>
+        <v>65.27</v>
       </c>
       <c r="G135" t="n">
-        <v>185.05</v>
+        <v>67.75</v>
       </c>
       <c r="H135" t="n">
-        <v>69481193</v>
+        <v>3315776</v>
       </c>
       <c r="I135" t="n">
-        <v>39867959</v>
+        <v>3511840</v>
       </c>
       <c r="J135" t="n">
-        <v>200.5</v>
+        <v>82.3</v>
       </c>
       <c r="K135" t="n">
-        <v>174</v>
+        <v>62.4</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -21832,52 +21832,52 @@
         </is>
       </c>
       <c r="M135" t="n">
-        <v>-36167085</v>
+        <v>-498138</v>
       </c>
       <c r="N135" t="n">
-        <v>-37768352</v>
+        <v>-2764124</v>
       </c>
       <c r="O135" t="n">
-        <v>-35597614</v>
+        <v>-2961909</v>
       </c>
       <c r="P135" t="n">
-        <v>-74869497</v>
+        <v>-5194923</v>
       </c>
       <c r="Q135" t="n">
-        <v>-30549430</v>
+        <v>-507900</v>
       </c>
       <c r="R135" t="n">
-        <v>-31951957</v>
+        <v>-2924482</v>
       </c>
       <c r="S135" t="n">
-        <v>-32812476</v>
+        <v>-3199838</v>
       </c>
       <c r="T135" t="n">
-        <v>-71642812</v>
+        <v>-5014277</v>
       </c>
       <c r="U135" t="n">
-        <v>-5434984</v>
+        <v>0</v>
       </c>
       <c r="V135" t="n">
-        <v>-6364252</v>
+        <v>0</v>
       </c>
       <c r="W135" t="n">
-        <v>-2370252</v>
+        <v>-24000</v>
       </c>
       <c r="X135" t="n">
-        <v>-2305930</v>
+        <v>-91000</v>
       </c>
       <c r="Y135" t="n">
-        <v>-182671</v>
+        <v>9762</v>
       </c>
       <c r="Z135" t="n">
-        <v>547857</v>
+        <v>160358</v>
       </c>
       <c r="AA135" t="n">
-        <v>-414886</v>
+        <v>261929</v>
       </c>
       <c r="AB135" t="n">
-        <v>-920755</v>
+        <v>-89646</v>
       </c>
       <c r="AC135" t="n">
         <v>-36</v>
@@ -21895,19 +21895,19 @@
         <v>0</v>
       </c>
       <c r="AH135" t="n">
-        <v>16</v>
+        <v>-28</v>
       </c>
       <c r="AI135" t="n">
-        <v>-52</v>
+        <v>-8</v>
       </c>
       <c r="AJ135" t="n">
-        <v>-325</v>
+        <v>-28.57</v>
       </c>
       <c r="AK135" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL135" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AM135" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -21931,7 +21931,7 @@
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>跌破5日線、成交量放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
@@ -21941,19 +21941,19 @@
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、成交量放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>6269.TW</t>
+          <t>2324.TW</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -21962,28 +21962,28 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>64.59999999999999</v>
+        <v>37.05</v>
       </c>
       <c r="E136" t="n">
-        <v>64.54000000000001</v>
+        <v>37.42</v>
       </c>
       <c r="F136" t="n">
-        <v>65.27</v>
+        <v>37.73</v>
       </c>
       <c r="G136" t="n">
-        <v>67.75</v>
+        <v>38.86</v>
       </c>
       <c r="H136" t="n">
-        <v>3315776</v>
+        <v>38170830</v>
       </c>
       <c r="I136" t="n">
-        <v>3511840</v>
+        <v>33227983</v>
       </c>
       <c r="J136" t="n">
-        <v>82.3</v>
+        <v>42.1</v>
       </c>
       <c r="K136" t="n">
-        <v>62.4</v>
+        <v>36.8</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -21991,64 +21991,64 @@
         </is>
       </c>
       <c r="M136" t="n">
-        <v>-498138</v>
+        <v>-19530263</v>
       </c>
       <c r="N136" t="n">
-        <v>-2764124</v>
+        <v>-33111062</v>
       </c>
       <c r="O136" t="n">
-        <v>-2961909</v>
+        <v>-37550003</v>
       </c>
       <c r="P136" t="n">
-        <v>-5194923</v>
+        <v>-80559332</v>
       </c>
       <c r="Q136" t="n">
-        <v>-507900</v>
+        <v>-19467750</v>
       </c>
       <c r="R136" t="n">
-        <v>-2924482</v>
+        <v>-34497419</v>
       </c>
       <c r="S136" t="n">
-        <v>-3199838</v>
+        <v>-38727473</v>
       </c>
       <c r="T136" t="n">
-        <v>-5014277</v>
+        <v>-76446538</v>
       </c>
       <c r="U136" t="n">
-        <v>0</v>
+        <v>-73858</v>
       </c>
       <c r="V136" t="n">
-        <v>0</v>
+        <v>654812</v>
       </c>
       <c r="W136" t="n">
-        <v>-24000</v>
+        <v>630812</v>
       </c>
       <c r="X136" t="n">
-        <v>-91000</v>
+        <v>140952</v>
       </c>
       <c r="Y136" t="n">
-        <v>9762</v>
+        <v>11345</v>
       </c>
       <c r="Z136" t="n">
-        <v>160358</v>
+        <v>731545</v>
       </c>
       <c r="AA136" t="n">
-        <v>261929</v>
+        <v>546658</v>
       </c>
       <c r="AB136" t="n">
-        <v>-89646</v>
+        <v>-4253746</v>
       </c>
       <c r="AC136" t="n">
-        <v>-36</v>
+        <v>-40</v>
       </c>
       <c r="AD136" t="n">
-        <v>-36</v>
+        <v>-40</v>
       </c>
       <c r="AE136" t="n">
-        <v>-15</v>
+        <v>-45</v>
       </c>
       <c r="AF136" t="n">
-        <v>-75</v>
+        <v>-55</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -22057,16 +22057,16 @@
         <v>-28</v>
       </c>
       <c r="AI136" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="AJ136" t="n">
-        <v>-28.57</v>
+        <v>-42.86</v>
       </c>
       <c r="AK136" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AL136" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AM136" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -22090,17 +22090,17 @@
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -22266,12 +22266,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2324.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -22280,28 +22280,28 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>37.05</v>
+        <v>4860</v>
       </c>
       <c r="E138" t="n">
-        <v>37.42</v>
+        <v>4885</v>
       </c>
       <c r="F138" t="n">
-        <v>37.73</v>
+        <v>5100</v>
       </c>
       <c r="G138" t="n">
-        <v>38.86</v>
+        <v>5299.75</v>
       </c>
       <c r="H138" t="n">
-        <v>38170830</v>
+        <v>2101406</v>
       </c>
       <c r="I138" t="n">
-        <v>33227983</v>
+        <v>3155635</v>
       </c>
       <c r="J138" t="n">
-        <v>42.1</v>
+        <v>5960</v>
       </c>
       <c r="K138" t="n">
-        <v>36.8</v>
+        <v>4635</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -22309,61 +22309,61 @@
         </is>
       </c>
       <c r="M138" t="n">
-        <v>-19530263</v>
+        <v>-272574</v>
       </c>
       <c r="N138" t="n">
-        <v>-33111062</v>
+        <v>-790470</v>
       </c>
       <c r="O138" t="n">
-        <v>-37550003</v>
+        <v>-1118045</v>
       </c>
       <c r="P138" t="n">
-        <v>-80559332</v>
+        <v>-1508450</v>
       </c>
       <c r="Q138" t="n">
-        <v>-19467750</v>
+        <v>331258</v>
       </c>
       <c r="R138" t="n">
-        <v>-34497419</v>
+        <v>1016703</v>
       </c>
       <c r="S138" t="n">
-        <v>-38727473</v>
+        <v>1359948</v>
       </c>
       <c r="T138" t="n">
-        <v>-76446538</v>
+        <v>1486355</v>
       </c>
       <c r="U138" t="n">
-        <v>-73858</v>
+        <v>-653668</v>
       </c>
       <c r="V138" t="n">
-        <v>654812</v>
+        <v>-2006086</v>
       </c>
       <c r="W138" t="n">
-        <v>630812</v>
+        <v>-2896086</v>
       </c>
       <c r="X138" t="n">
-        <v>140952</v>
+        <v>-3322329</v>
       </c>
       <c r="Y138" t="n">
-        <v>11345</v>
+        <v>49836</v>
       </c>
       <c r="Z138" t="n">
-        <v>731545</v>
+        <v>198913</v>
       </c>
       <c r="AA138" t="n">
-        <v>546658</v>
+        <v>418093</v>
       </c>
       <c r="AB138" t="n">
-        <v>-4253746</v>
+        <v>327524</v>
       </c>
       <c r="AC138" t="n">
-        <v>-40</v>
+        <v>-44</v>
       </c>
       <c r="AD138" t="n">
-        <v>-40</v>
+        <v>-44</v>
       </c>
       <c r="AE138" t="n">
-        <v>-45</v>
+        <v>-55</v>
       </c>
       <c r="AF138" t="n">
         <v>-55</v>
@@ -22372,13 +22372,13 @@
         <v>0</v>
       </c>
       <c r="AH138" t="n">
-        <v>-28</v>
+        <v>-40</v>
       </c>
       <c r="AI138" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="AJ138" t="n">
-        <v>-42.86</v>
+        <v>-10</v>
       </c>
       <c r="AK138" t="n">
         <v>0</v>
@@ -22408,17 +22408,17 @@
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR138" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -2114,16 +2114,16 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>6473824</v>
+        <v>6304723</v>
       </c>
       <c r="N11" t="n">
-        <v>6244792</v>
+        <v>6075691</v>
       </c>
       <c r="O11" t="n">
-        <v>19367738</v>
+        <v>19198637</v>
       </c>
       <c r="P11" t="n">
-        <v>-14122065</v>
+        <v>-14291166</v>
       </c>
       <c r="Q11" t="n">
         <v>7123363</v>
@@ -2138,16 +2138,16 @@
         <v>-18040671</v>
       </c>
       <c r="U11" t="n">
-        <v>-973707</v>
+        <v>-1142808</v>
       </c>
       <c r="V11" t="n">
-        <v>-644735</v>
+        <v>-813836</v>
       </c>
       <c r="W11" t="n">
-        <v>-225924</v>
+        <v>-395025</v>
       </c>
       <c r="X11" t="n">
-        <v>-169448</v>
+        <v>-338549</v>
       </c>
       <c r="Y11" t="n">
         <v>324168</v>
@@ -2909,16 +2909,16 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>29624502</v>
+        <v>29607502</v>
       </c>
       <c r="N16" t="n">
-        <v>1615314</v>
+        <v>1598314</v>
       </c>
       <c r="O16" t="n">
-        <v>39932979</v>
+        <v>39915979</v>
       </c>
       <c r="P16" t="n">
-        <v>10484833</v>
+        <v>10467833</v>
       </c>
       <c r="Q16" t="n">
         <v>29196171</v>
@@ -2933,16 +2933,16 @@
         <v>10873298</v>
       </c>
       <c r="U16" t="n">
-        <v>-163000</v>
+        <v>-180000</v>
       </c>
       <c r="V16" t="n">
-        <v>-304212</v>
+        <v>-321212</v>
       </c>
       <c r="W16" t="n">
-        <v>4227362</v>
+        <v>4210362</v>
       </c>
       <c r="X16" t="n">
-        <v>-452218</v>
+        <v>-469218</v>
       </c>
       <c r="Y16" t="n">
         <v>591331</v>
@@ -4179,16 +4179,16 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>1858179</v>
+        <v>1907819</v>
       </c>
       <c r="N24" t="n">
-        <v>19302682</v>
+        <v>19352322</v>
       </c>
       <c r="O24" t="n">
-        <v>30008552</v>
+        <v>30058192</v>
       </c>
       <c r="P24" t="n">
-        <v>21942789</v>
+        <v>21992429</v>
       </c>
       <c r="Q24" t="n">
         <v>4008437</v>
@@ -4203,16 +4203,16 @@
         <v>21508691</v>
       </c>
       <c r="U24" t="n">
-        <v>-2326000</v>
+        <v>-2276360</v>
       </c>
       <c r="V24" t="n">
-        <v>-621200</v>
+        <v>-571560</v>
       </c>
       <c r="W24" t="n">
-        <v>-806798</v>
+        <v>-757158</v>
       </c>
       <c r="X24" t="n">
-        <v>-2136203</v>
+        <v>-2086563</v>
       </c>
       <c r="Y24" t="n">
         <v>175742</v>
@@ -4815,16 +4815,16 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>114287</v>
+        <v>135287</v>
       </c>
       <c r="N28" t="n">
-        <v>6992138</v>
+        <v>7013138</v>
       </c>
       <c r="O28" t="n">
-        <v>9987275</v>
+        <v>10008275</v>
       </c>
       <c r="P28" t="n">
-        <v>-4207664</v>
+        <v>-4186664</v>
       </c>
       <c r="Q28" t="n">
         <v>-139009</v>
@@ -4839,16 +4839,16 @@
         <v>-7990653</v>
       </c>
       <c r="U28" t="n">
-        <v>190002</v>
+        <v>211002</v>
       </c>
       <c r="V28" t="n">
-        <v>5224620</v>
+        <v>5245620</v>
       </c>
       <c r="W28" t="n">
-        <v>5457972</v>
+        <v>5478972</v>
       </c>
       <c r="X28" t="n">
-        <v>2768529</v>
+        <v>2789529</v>
       </c>
       <c r="Y28" t="n">
         <v>63294</v>
@@ -13878,16 +13878,16 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>6976172</v>
+        <v>6946172</v>
       </c>
       <c r="N85" t="n">
-        <v>-26378707</v>
+        <v>-26408707</v>
       </c>
       <c r="O85" t="n">
-        <v>10438136</v>
+        <v>10408136</v>
       </c>
       <c r="P85" t="n">
-        <v>-70414336</v>
+        <v>-70444336</v>
       </c>
       <c r="Q85" t="n">
         <v>10124159</v>
@@ -13902,16 +13902,16 @@
         <v>-37429578</v>
       </c>
       <c r="U85" t="n">
-        <v>-3242000</v>
+        <v>-3272000</v>
       </c>
       <c r="V85" t="n">
-        <v>-19591793</v>
+        <v>-19621793</v>
       </c>
       <c r="W85" t="n">
-        <v>-19851679</v>
+        <v>-19881679</v>
       </c>
       <c r="X85" t="n">
-        <v>-35636976</v>
+        <v>-35666976</v>
       </c>
       <c r="Y85" t="n">
         <v>94013</v>
@@ -16422,16 +16422,16 @@
         </is>
       </c>
       <c r="M101" t="n">
-        <v>-54090692</v>
+        <v>-57815692</v>
       </c>
       <c r="N101" t="n">
-        <v>7787557</v>
+        <v>4062557</v>
       </c>
       <c r="O101" t="n">
-        <v>-23873892</v>
+        <v>-27598892</v>
       </c>
       <c r="P101" t="n">
-        <v>-59282158</v>
+        <v>-63007158</v>
       </c>
       <c r="Q101" t="n">
         <v>-47830253</v>
@@ -16446,16 +16446,16 @@
         <v>-50974512</v>
       </c>
       <c r="U101" t="n">
-        <v>-9900</v>
+        <v>-3734900</v>
       </c>
       <c r="V101" t="n">
-        <v>-4952304</v>
+        <v>-8677304</v>
       </c>
       <c r="W101" t="n">
-        <v>-7988597</v>
+        <v>-11713597</v>
       </c>
       <c r="X101" t="n">
-        <v>-8099625</v>
+        <v>-11824625</v>
       </c>
       <c r="Y101" t="n">
         <v>-6250539</v>
@@ -20715,16 +20715,16 @@
         </is>
       </c>
       <c r="M128" t="n">
-        <v>-1118010</v>
+        <v>-1143010</v>
       </c>
       <c r="N128" t="n">
-        <v>-1876687</v>
+        <v>-1901687</v>
       </c>
       <c r="O128" t="n">
-        <v>-3326950</v>
+        <v>-3351950</v>
       </c>
       <c r="P128" t="n">
-        <v>-4583667</v>
+        <v>-4608667</v>
       </c>
       <c r="Q128" t="n">
         <v>-594803</v>
@@ -20739,16 +20739,16 @@
         <v>-172267</v>
       </c>
       <c r="U128" t="n">
-        <v>-507000</v>
+        <v>-532000</v>
       </c>
       <c r="V128" t="n">
-        <v>-1465004</v>
+        <v>-1490004</v>
       </c>
       <c r="W128" t="n">
-        <v>-3345788</v>
+        <v>-3370788</v>
       </c>
       <c r="X128" t="n">
-        <v>-4715322</v>
+        <v>-4740322</v>
       </c>
       <c r="Y128" t="n">
         <v>-16207</v>
@@ -22941,16 +22941,16 @@
         </is>
       </c>
       <c r="M142" t="n">
-        <v>-220272</v>
+        <v>-221272</v>
       </c>
       <c r="N142" t="n">
-        <v>-837807</v>
+        <v>-838807</v>
       </c>
       <c r="O142" t="n">
-        <v>-701321</v>
+        <v>-702321</v>
       </c>
       <c r="P142" t="n">
-        <v>-991487</v>
+        <v>-992487</v>
       </c>
       <c r="Q142" t="n">
         <v>-134405</v>
@@ -22965,16 +22965,16 @@
         <v>-215386</v>
       </c>
       <c r="U142" t="n">
-        <v>-83320</v>
+        <v>-84320</v>
       </c>
       <c r="V142" t="n">
-        <v>-726491</v>
+        <v>-727491</v>
       </c>
       <c r="W142" t="n">
-        <v>-725140</v>
+        <v>-726140</v>
       </c>
       <c r="X142" t="n">
-        <v>-803010</v>
+        <v>-804010</v>
       </c>
       <c r="Y142" t="n">
         <v>-2547</v>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -646,12 +646,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>6213.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -660,135 +660,135 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>962</v>
+        <v>595</v>
       </c>
       <c r="E2" t="n">
-        <v>887.2</v>
+        <v>545.2</v>
       </c>
       <c r="F2" t="n">
-        <v>847.6</v>
+        <v>531.4</v>
       </c>
       <c r="G2" t="n">
-        <v>838.05</v>
+        <v>531.2</v>
       </c>
       <c r="H2" t="n">
-        <v>44137311</v>
+        <v>16800143</v>
       </c>
       <c r="I2" t="n">
-        <v>28939897</v>
+        <v>18014851</v>
       </c>
       <c r="J2" t="n">
-        <v>996</v>
+        <v>595</v>
       </c>
       <c r="K2" t="n">
-        <v>766</v>
+        <v>482</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>8335454</v>
+        <v>1800878</v>
       </c>
       <c r="N2" t="n">
-        <v>21536918</v>
+        <v>4657254</v>
       </c>
       <c r="O2" t="n">
-        <v>24054989</v>
+        <v>13782034</v>
       </c>
       <c r="P2" t="n">
-        <v>21251778</v>
+        <v>3611772</v>
       </c>
       <c r="Q2" t="n">
-        <v>6834210</v>
+        <v>833221</v>
       </c>
       <c r="R2" t="n">
-        <v>19733652</v>
+        <v>3546220</v>
       </c>
       <c r="S2" t="n">
-        <v>20892832</v>
+        <v>11543180</v>
       </c>
       <c r="T2" t="n">
-        <v>17553928</v>
+        <v>969701</v>
       </c>
       <c r="U2" t="n">
-        <v>984001</v>
+        <v>600000</v>
       </c>
       <c r="V2" t="n">
-        <v>980001</v>
+        <v>734000</v>
       </c>
       <c r="W2" t="n">
-        <v>1214001</v>
+        <v>1511000</v>
       </c>
       <c r="X2" t="n">
-        <v>2314001</v>
+        <v>2514000</v>
       </c>
       <c r="Y2" t="n">
-        <v>517243</v>
+        <v>367657</v>
       </c>
       <c r="Z2" t="n">
-        <v>823265</v>
+        <v>377034</v>
       </c>
       <c r="AA2" t="n">
-        <v>1948156</v>
+        <v>727854</v>
       </c>
       <c r="AB2" t="n">
-        <v>1383849</v>
+        <v>128071</v>
       </c>
       <c r="AC2" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="AD2" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="AE2" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AF2" t="n">
         <v>80</v>
       </c>
       <c r="AG2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AI2" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>38.64</v>
+        <v>105.88</v>
       </c>
       <c r="AK2" t="n">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>DT趨勢已轉強、離5MA偏遠、均線多頭排列、量能溫和放大、分數明顯升溫</t>
+          <t>DT趨勢已轉強、離5MA偏遠、均線多頭排列、接近20日高位、分數升溫過快</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、黃金交叉、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -798,19 +798,19 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：站上5日線、多頭排列、黃金交叉、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2636.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台驊投控</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -819,28 +819,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>71.90000000000001</v>
+        <v>962</v>
       </c>
       <c r="E3" t="n">
-        <v>71.02</v>
+        <v>887.2</v>
       </c>
       <c r="F3" t="n">
-        <v>70.63</v>
+        <v>847.6</v>
       </c>
       <c r="G3" t="n">
-        <v>70.01000000000001</v>
+        <v>838.05</v>
       </c>
       <c r="H3" t="n">
-        <v>1009165</v>
+        <v>44137311</v>
       </c>
       <c r="I3" t="n">
-        <v>400307</v>
+        <v>28939897</v>
       </c>
       <c r="J3" t="n">
-        <v>72.3</v>
+        <v>996</v>
       </c>
       <c r="K3" t="n">
-        <v>68.09999999999999</v>
+        <v>766</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -848,52 +848,52 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>468240</v>
+        <v>8335454</v>
       </c>
       <c r="N3" t="n">
-        <v>723967</v>
+        <v>21536918</v>
       </c>
       <c r="O3" t="n">
-        <v>719883</v>
+        <v>24054989</v>
       </c>
       <c r="P3" t="n">
-        <v>1112371</v>
+        <v>21251778</v>
       </c>
       <c r="Q3" t="n">
-        <v>478240</v>
+        <v>6834210</v>
       </c>
       <c r="R3" t="n">
-        <v>732998</v>
+        <v>19733652</v>
       </c>
       <c r="S3" t="n">
-        <v>738512</v>
+        <v>20892832</v>
       </c>
       <c r="T3" t="n">
-        <v>1040842</v>
+        <v>17553928</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>984001</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>980001</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1214001</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2314001</v>
       </c>
       <c r="Y3" t="n">
-        <v>-10000</v>
+        <v>517243</v>
       </c>
       <c r="Z3" t="n">
-        <v>-9031</v>
+        <v>823265</v>
       </c>
       <c r="AA3" t="n">
-        <v>-18629</v>
+        <v>1948156</v>
       </c>
       <c r="AB3" t="n">
-        <v>71529</v>
+        <v>1383849</v>
       </c>
       <c r="AC3" t="n">
         <v>61</v>
@@ -902,22 +902,22 @@
         <v>61</v>
       </c>
       <c r="AE3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF3" t="n">
         <v>80</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>60</v>
       </c>
       <c r="AG3" t="n">
         <v>25</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="AI3" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>154.17</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>55</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>DT趨勢已轉強、貼近5MA、均線多頭排列、爆量後不追價、分數升溫過快</t>
+          <t>DT趨勢已轉強、離5MA偏遠、均線多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -947,29 +947,29 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、接近20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、爆量、接近20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2636.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>台驊投控</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -978,111 +978,111 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>206.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>199</v>
+        <v>71.02</v>
       </c>
       <c r="F4" t="n">
-        <v>185.95</v>
+        <v>70.63</v>
       </c>
       <c r="G4" t="n">
-        <v>182.6</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>4855474</v>
+        <v>1009165</v>
       </c>
       <c r="I4" t="n">
-        <v>8222326</v>
+        <v>400307</v>
       </c>
       <c r="J4" t="n">
-        <v>210</v>
+        <v>72.3</v>
       </c>
       <c r="K4" t="n">
-        <v>165</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1250927</v>
+        <v>468240</v>
       </c>
       <c r="N4" t="n">
-        <v>4546039</v>
+        <v>723967</v>
       </c>
       <c r="O4" t="n">
-        <v>7333287</v>
+        <v>719883</v>
       </c>
       <c r="P4" t="n">
-        <v>8026565</v>
+        <v>1112371</v>
       </c>
       <c r="Q4" t="n">
-        <v>1184310</v>
+        <v>478240</v>
       </c>
       <c r="R4" t="n">
-        <v>3632128</v>
+        <v>732998</v>
       </c>
       <c r="S4" t="n">
-        <v>5712493</v>
+        <v>738512</v>
       </c>
       <c r="T4" t="n">
-        <v>6523796</v>
+        <v>1040842</v>
       </c>
       <c r="U4" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>46617</v>
+        <v>-10000</v>
       </c>
       <c r="Z4" t="n">
-        <v>893911</v>
+        <v>-9031</v>
       </c>
       <c r="AA4" t="n">
-        <v>1600794</v>
+        <v>-18629</v>
       </c>
       <c r="AB4" t="n">
-        <v>1482769</v>
+        <v>71529</v>
       </c>
       <c r="AC4" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AD4" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AE4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF4" t="n">
         <v>60</v>
       </c>
-      <c r="AF4" t="n">
-        <v>80</v>
-      </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AH4" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="AI4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>86.67</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列、分數升溫過快</t>
+          <t>DT趨勢已轉強、貼近5MA、均線多頭排列、爆量後不追價</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1106,29 +1106,29 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、爆量、接近20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、爆量、接近20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1185</v>
+        <v>206.5</v>
       </c>
       <c r="E5" t="n">
-        <v>1093.2</v>
+        <v>199</v>
       </c>
       <c r="F5" t="n">
-        <v>1026.5</v>
+        <v>185.95</v>
       </c>
       <c r="G5" t="n">
-        <v>1001.65</v>
+        <v>182.6</v>
       </c>
       <c r="H5" t="n">
-        <v>16628391</v>
+        <v>4855474</v>
       </c>
       <c r="I5" t="n">
-        <v>16508345</v>
+        <v>8222326</v>
       </c>
       <c r="J5" t="n">
-        <v>1230</v>
+        <v>210</v>
       </c>
       <c r="K5" t="n">
-        <v>873</v>
+        <v>165</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1166,61 +1166,61 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1813675</v>
+        <v>1250927</v>
       </c>
       <c r="N5" t="n">
-        <v>13279105</v>
+        <v>4546039</v>
       </c>
       <c r="O5" t="n">
-        <v>19417843</v>
+        <v>7333287</v>
       </c>
       <c r="P5" t="n">
-        <v>19161983</v>
+        <v>8026565</v>
       </c>
       <c r="Q5" t="n">
-        <v>1807376</v>
+        <v>1184310</v>
       </c>
       <c r="R5" t="n">
-        <v>12884811</v>
+        <v>3632128</v>
       </c>
       <c r="S5" t="n">
-        <v>17397266</v>
+        <v>5712493</v>
       </c>
       <c r="T5" t="n">
-        <v>17872091</v>
+        <v>6523796</v>
       </c>
       <c r="U5" t="n">
-        <v>121999</v>
+        <v>20000</v>
       </c>
       <c r="V5" t="n">
-        <v>614713</v>
+        <v>20000</v>
       </c>
       <c r="W5" t="n">
-        <v>1690582</v>
+        <v>20000</v>
       </c>
       <c r="X5" t="n">
-        <v>1137957</v>
+        <v>20000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-115700</v>
+        <v>46617</v>
       </c>
       <c r="Z5" t="n">
-        <v>-220419</v>
+        <v>893911</v>
       </c>
       <c r="AA5" t="n">
-        <v>329995</v>
+        <v>1600794</v>
       </c>
       <c r="AB5" t="n">
-        <v>151935</v>
+        <v>1482769</v>
       </c>
       <c r="AC5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AD5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF5" t="n">
         <v>80</v>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1238,10 +1238,10 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>DT進入觀察區、離5MA偏遠、均線多頭排列</t>
+          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1275,19 +1275,19 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2395.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1296,28 +1296,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>722</v>
+        <v>1185</v>
       </c>
       <c r="E6" t="n">
-        <v>704.4</v>
+        <v>1093.2</v>
       </c>
       <c r="F6" t="n">
-        <v>693.2</v>
+        <v>1026.5</v>
       </c>
       <c r="G6" t="n">
-        <v>685.75</v>
+        <v>1001.65</v>
       </c>
       <c r="H6" t="n">
-        <v>2762561</v>
+        <v>16628391</v>
       </c>
       <c r="I6" t="n">
-        <v>2405882</v>
+        <v>16508345</v>
       </c>
       <c r="J6" t="n">
-        <v>728</v>
+        <v>1230</v>
       </c>
       <c r="K6" t="n">
-        <v>645</v>
+        <v>873</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1325,91 +1325,91 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>576495</v>
+        <v>1813675</v>
       </c>
       <c r="N6" t="n">
-        <v>1306111</v>
+        <v>13279105</v>
       </c>
       <c r="O6" t="n">
-        <v>2102219</v>
+        <v>19417843</v>
       </c>
       <c r="P6" t="n">
-        <v>5521059</v>
+        <v>19161983</v>
       </c>
       <c r="Q6" t="n">
-        <v>547901</v>
+        <v>1807376</v>
       </c>
       <c r="R6" t="n">
-        <v>1745820</v>
+        <v>12884811</v>
       </c>
       <c r="S6" t="n">
-        <v>2439047</v>
+        <v>17397266</v>
       </c>
       <c r="T6" t="n">
-        <v>5960365</v>
+        <v>17872091</v>
       </c>
       <c r="U6" t="n">
-        <v>-36000</v>
+        <v>121999</v>
       </c>
       <c r="V6" t="n">
-        <v>-481985</v>
+        <v>614713</v>
       </c>
       <c r="W6" t="n">
-        <v>-455970</v>
+        <v>1690582</v>
       </c>
       <c r="X6" t="n">
-        <v>-546970</v>
+        <v>1137957</v>
       </c>
       <c r="Y6" t="n">
-        <v>64594</v>
+        <v>-115700</v>
       </c>
       <c r="Z6" t="n">
-        <v>42276</v>
+        <v>-220419</v>
       </c>
       <c r="AA6" t="n">
-        <v>119142</v>
+        <v>329995</v>
       </c>
       <c r="AB6" t="n">
-        <v>107664</v>
+        <v>151935</v>
       </c>
       <c r="AC6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AD6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AE6" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="AI6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23.81</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、均線多頭排列、分數明顯升溫</t>
+          <t>DT進入觀察區、離5MA偏遠、均線多頭排列</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1424,29 +1424,29 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3042.TW</t>
+          <t>2395.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1455,111 +1455,111 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>203</v>
+        <v>722</v>
       </c>
       <c r="E7" t="n">
-        <v>190.5</v>
+        <v>704.4</v>
       </c>
       <c r="F7" t="n">
-        <v>185.15</v>
+        <v>693.2</v>
       </c>
       <c r="G7" t="n">
-        <v>182.43</v>
+        <v>685.75</v>
       </c>
       <c r="H7" t="n">
-        <v>41859153</v>
+        <v>2762561</v>
       </c>
       <c r="I7" t="n">
-        <v>19245821</v>
+        <v>2405882</v>
       </c>
       <c r="J7" t="n">
-        <v>212</v>
+        <v>728</v>
       </c>
       <c r="K7" t="n">
-        <v>170</v>
+        <v>645</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>-989916</v>
+        <v>576495</v>
       </c>
       <c r="N7" t="n">
-        <v>2819561</v>
+        <v>1306111</v>
       </c>
       <c r="O7" t="n">
-        <v>7221016</v>
+        <v>2102219</v>
       </c>
       <c r="P7" t="n">
-        <v>13108406</v>
+        <v>5521059</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2802910</v>
+        <v>547901</v>
       </c>
       <c r="R7" t="n">
-        <v>-158759</v>
+        <v>1745820</v>
       </c>
       <c r="S7" t="n">
-        <v>3859370</v>
+        <v>2439047</v>
       </c>
       <c r="T7" t="n">
-        <v>10663171</v>
+        <v>5960365</v>
       </c>
       <c r="U7" t="n">
-        <v>1179000</v>
+        <v>-36000</v>
       </c>
       <c r="V7" t="n">
-        <v>875000</v>
+        <v>-481985</v>
       </c>
       <c r="W7" t="n">
-        <v>1114000</v>
+        <v>-455970</v>
       </c>
       <c r="X7" t="n">
-        <v>883300</v>
+        <v>-546970</v>
       </c>
       <c r="Y7" t="n">
-        <v>633994</v>
+        <v>64594</v>
       </c>
       <c r="Z7" t="n">
-        <v>2103320</v>
+        <v>42276</v>
       </c>
       <c r="AA7" t="n">
-        <v>2247646</v>
+        <v>119142</v>
       </c>
       <c r="AB7" t="n">
-        <v>1561935</v>
+        <v>107664</v>
       </c>
       <c r="AC7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AD7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AG7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="AI7" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-16.39</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT進入觀察區、貼近5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1583,29 +1583,29 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、爆量、帶量突破20日高點、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2855.TW</t>
+          <t>3042.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1614,99 +1614,99 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>57.8</v>
+        <v>203</v>
       </c>
       <c r="E8" t="n">
-        <v>56.6</v>
+        <v>190.5</v>
       </c>
       <c r="F8" t="n">
-        <v>54.34</v>
+        <v>185.15</v>
       </c>
       <c r="G8" t="n">
-        <v>52.52</v>
+        <v>182.43</v>
       </c>
       <c r="H8" t="n">
-        <v>5306238</v>
+        <v>41859153</v>
       </c>
       <c r="I8" t="n">
-        <v>7489747</v>
+        <v>19245821</v>
       </c>
       <c r="J8" t="n">
-        <v>59.7</v>
+        <v>212</v>
       </c>
       <c r="K8" t="n">
-        <v>47.75</v>
+        <v>170</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>660376</v>
+        <v>-989916</v>
       </c>
       <c r="N8" t="n">
-        <v>4475707</v>
+        <v>2819561</v>
       </c>
       <c r="O8" t="n">
-        <v>13269229</v>
+        <v>7221016</v>
       </c>
       <c r="P8" t="n">
-        <v>17655173</v>
+        <v>13108406</v>
       </c>
       <c r="Q8" t="n">
-        <v>680563</v>
+        <v>-2802910</v>
       </c>
       <c r="R8" t="n">
-        <v>4561794</v>
+        <v>-158759</v>
       </c>
       <c r="S8" t="n">
-        <v>12929500</v>
+        <v>3859370</v>
       </c>
       <c r="T8" t="n">
-        <v>11534344</v>
+        <v>10663171</v>
       </c>
       <c r="U8" t="n">
-        <v>-20187</v>
+        <v>1179000</v>
       </c>
       <c r="V8" t="n">
-        <v>-86087</v>
+        <v>875000</v>
       </c>
       <c r="W8" t="n">
-        <v>339729</v>
+        <v>1114000</v>
       </c>
       <c r="X8" t="n">
-        <v>6120829</v>
+        <v>883300</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>633994</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2103320</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2247646</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1561935</v>
       </c>
       <c r="AC8" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>51</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF8" t="n">
         <v>50</v>
       </c>
-      <c r="AD8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>45</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>80</v>
-      </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AH8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1715,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AL8" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能偏強</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1742,29 +1742,29 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、爆量、帶量突破20日高點、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8150.TW</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1773,28 +1773,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>112</v>
+        <v>5285</v>
       </c>
       <c r="E9" t="n">
-        <v>104.3</v>
+        <v>5074</v>
       </c>
       <c r="F9" t="n">
-        <v>95.3</v>
+        <v>4797.5</v>
       </c>
       <c r="G9" t="n">
-        <v>92.95999999999999</v>
+        <v>4602.25</v>
       </c>
       <c r="H9" t="n">
-        <v>83883329</v>
+        <v>7817443</v>
       </c>
       <c r="I9" t="n">
-        <v>86983184</v>
+        <v>9596363</v>
       </c>
       <c r="J9" t="n">
-        <v>116</v>
+        <v>5480</v>
       </c>
       <c r="K9" t="n">
-        <v>84.3</v>
+        <v>3820</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1802,52 +1802,52 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13885187</v>
+        <v>670758</v>
       </c>
       <c r="N9" t="n">
-        <v>34063917</v>
+        <v>3162998</v>
       </c>
       <c r="O9" t="n">
-        <v>65323779</v>
+        <v>10037399</v>
       </c>
       <c r="P9" t="n">
-        <v>55827715</v>
+        <v>10398717</v>
       </c>
       <c r="Q9" t="n">
-        <v>14649145</v>
+        <v>826547</v>
       </c>
       <c r="R9" t="n">
-        <v>33771677</v>
+        <v>2864768</v>
       </c>
       <c r="S9" t="n">
-        <v>61576024</v>
+        <v>8907830</v>
       </c>
       <c r="T9" t="n">
-        <v>52880208</v>
+        <v>9198088</v>
       </c>
       <c r="U9" t="n">
-        <v>10000</v>
+        <v>-288900</v>
       </c>
       <c r="V9" t="n">
-        <v>7000</v>
+        <v>66414</v>
       </c>
       <c r="W9" t="n">
-        <v>7000</v>
+        <v>259224</v>
       </c>
       <c r="X9" t="n">
-        <v>87000</v>
+        <v>8316</v>
       </c>
       <c r="Y9" t="n">
-        <v>-773958</v>
+        <v>133111</v>
       </c>
       <c r="Z9" t="n">
-        <v>285240</v>
+        <v>231816</v>
       </c>
       <c r="AA9" t="n">
-        <v>3740755</v>
+        <v>870345</v>
       </c>
       <c r="AB9" t="n">
-        <v>2860507</v>
+        <v>1192313</v>
       </c>
       <c r="AC9" t="n">
         <v>50</v>
@@ -1865,19 +1865,19 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>DT進入觀察區、離5MA偏遠、均線多頭排列、分數剛升溫</t>
+          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1918,12 +1918,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>8150.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1932,28 +1932,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5285</v>
+        <v>112</v>
       </c>
       <c r="E10" t="n">
-        <v>5074</v>
+        <v>104.3</v>
       </c>
       <c r="F10" t="n">
-        <v>4797.5</v>
+        <v>95.3</v>
       </c>
       <c r="G10" t="n">
-        <v>4602.25</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>7817443</v>
+        <v>83883329</v>
       </c>
       <c r="I10" t="n">
-        <v>9596363</v>
+        <v>86983184</v>
       </c>
       <c r="J10" t="n">
-        <v>5480</v>
+        <v>116</v>
       </c>
       <c r="K10" t="n">
-        <v>3820</v>
+        <v>84.3</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1961,52 +1961,52 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>670758</v>
+        <v>13885187</v>
       </c>
       <c r="N10" t="n">
-        <v>3162998</v>
+        <v>34063917</v>
       </c>
       <c r="O10" t="n">
-        <v>10037399</v>
+        <v>65323779</v>
       </c>
       <c r="P10" t="n">
-        <v>10398717</v>
+        <v>55827715</v>
       </c>
       <c r="Q10" t="n">
-        <v>826547</v>
+        <v>14649145</v>
       </c>
       <c r="R10" t="n">
-        <v>2864768</v>
+        <v>33771677</v>
       </c>
       <c r="S10" t="n">
-        <v>8907830</v>
+        <v>61576024</v>
       </c>
       <c r="T10" t="n">
-        <v>9198088</v>
+        <v>52880208</v>
       </c>
       <c r="U10" t="n">
-        <v>-288900</v>
+        <v>10000</v>
       </c>
       <c r="V10" t="n">
-        <v>66414</v>
+        <v>7000</v>
       </c>
       <c r="W10" t="n">
-        <v>259224</v>
+        <v>7000</v>
       </c>
       <c r="X10" t="n">
-        <v>8316</v>
+        <v>87000</v>
       </c>
       <c r="Y10" t="n">
-        <v>133111</v>
+        <v>-773958</v>
       </c>
       <c r="Z10" t="n">
-        <v>231816</v>
+        <v>285240</v>
       </c>
       <c r="AA10" t="n">
-        <v>870345</v>
+        <v>3740755</v>
       </c>
       <c r="AB10" t="n">
-        <v>1192313</v>
+        <v>2860507</v>
       </c>
       <c r="AC10" t="n">
         <v>50</v>
@@ -2033,10 +2033,10 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列</t>
+          <t>DT進入觀察區、離5MA偏遠、均線多頭排列</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2183,28 +2183,28 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AI11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>31.58</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="AL11" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>可優先研究</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2236,12 +2236,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2603.TW</t>
+          <t>2855.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2250,28 +2250,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>243</v>
+        <v>57.8</v>
       </c>
       <c r="E12" t="n">
-        <v>242.2</v>
+        <v>56.6</v>
       </c>
       <c r="F12" t="n">
-        <v>239.75</v>
+        <v>54.34</v>
       </c>
       <c r="G12" t="n">
-        <v>236.7</v>
+        <v>52.52</v>
       </c>
       <c r="H12" t="n">
-        <v>4944813</v>
+        <v>5306238</v>
       </c>
       <c r="I12" t="n">
-        <v>6818124</v>
+        <v>7489747</v>
       </c>
       <c r="J12" t="n">
-        <v>245.5</v>
+        <v>59.7</v>
       </c>
       <c r="K12" t="n">
-        <v>227</v>
+        <v>47.75</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -2279,70 +2279,70 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>64402</v>
+        <v>660376</v>
       </c>
       <c r="N12" t="n">
-        <v>915481</v>
+        <v>4475707</v>
       </c>
       <c r="O12" t="n">
-        <v>2979870</v>
+        <v>13269229</v>
       </c>
       <c r="P12" t="n">
-        <v>12402730</v>
+        <v>17655173</v>
       </c>
       <c r="Q12" t="n">
-        <v>-852117</v>
+        <v>680563</v>
       </c>
       <c r="R12" t="n">
-        <v>-3171700</v>
+        <v>4561794</v>
       </c>
       <c r="S12" t="n">
-        <v>-1432137</v>
+        <v>12929500</v>
       </c>
       <c r="T12" t="n">
-        <v>-3572715</v>
+        <v>11534344</v>
       </c>
       <c r="U12" t="n">
-        <v>941196</v>
+        <v>-20187</v>
       </c>
       <c r="V12" t="n">
-        <v>3878107</v>
+        <v>-86087</v>
       </c>
       <c r="W12" t="n">
-        <v>3996097</v>
+        <v>339729</v>
       </c>
       <c r="X12" t="n">
-        <v>14791297</v>
+        <v>6120829</v>
       </c>
       <c r="Y12" t="n">
-        <v>-24677</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>209074</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>415910</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1184148</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AD12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AE12" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AF12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2351,86 +2351,86 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AL12" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、均線多頭排列</t>
+          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>偏多觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00403A.TW</t>
+          <t>2603.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>主動統一升級50</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.88</v>
+        <v>243</v>
       </c>
       <c r="E13" t="n">
-        <v>10.64</v>
+        <v>242.2</v>
       </c>
       <c r="F13" t="n">
-        <v>10.34</v>
+        <v>239.75</v>
       </c>
       <c r="G13" t="n">
-        <v>10.32</v>
+        <v>236.7</v>
       </c>
       <c r="H13" t="n">
-        <v>285018846</v>
+        <v>4944813</v>
       </c>
       <c r="I13" t="n">
-        <v>383449898</v>
+        <v>6818124</v>
       </c>
       <c r="J13" t="n">
-        <v>10.89</v>
+        <v>245.5</v>
       </c>
       <c r="K13" t="n">
-        <v>9.92</v>
+        <v>227</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -2438,52 +2438,52 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>192316522</v>
+        <v>64402</v>
       </c>
       <c r="N13" t="n">
-        <v>849726687</v>
+        <v>915481</v>
       </c>
       <c r="O13" t="n">
-        <v>1407591057</v>
+        <v>2979870</v>
       </c>
       <c r="P13" t="n">
-        <v>1382836880</v>
+        <v>12402730</v>
       </c>
       <c r="Q13" t="n">
-        <v>64496136</v>
+        <v>-852117</v>
       </c>
       <c r="R13" t="n">
-        <v>392938129</v>
+        <v>-3171700</v>
       </c>
       <c r="S13" t="n">
-        <v>644242478</v>
+        <v>-1432137</v>
       </c>
       <c r="T13" t="n">
-        <v>621169449</v>
+        <v>-3572715</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>941196</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3878107</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3996097</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>14791297</v>
       </c>
       <c r="Y13" t="n">
-        <v>127820386</v>
+        <v>-24677</v>
       </c>
       <c r="Z13" t="n">
-        <v>456788558</v>
+        <v>209074</v>
       </c>
       <c r="AA13" t="n">
-        <v>763348579</v>
+        <v>415910</v>
       </c>
       <c r="AB13" t="n">
-        <v>761667431</v>
+        <v>1184148</v>
       </c>
       <c r="AC13" t="n">
         <v>48</v>
@@ -2510,19 +2510,19 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AL13" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、均線多頭排列、接近20日高位</t>
+          <t>DT進入觀察區、貼近5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2542,54 +2542,54 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>00403A.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>主動統一升級50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>238</v>
+        <v>10.88</v>
       </c>
       <c r="E14" t="n">
-        <v>232.6</v>
+        <v>10.64</v>
       </c>
       <c r="F14" t="n">
-        <v>227.5</v>
+        <v>10.34</v>
       </c>
       <c r="G14" t="n">
-        <v>233.68</v>
+        <v>10.32</v>
       </c>
       <c r="H14" t="n">
-        <v>5064342</v>
+        <v>285018846</v>
       </c>
       <c r="I14" t="n">
-        <v>3657056</v>
+        <v>383449898</v>
       </c>
       <c r="J14" t="n">
-        <v>255</v>
+        <v>10.89</v>
       </c>
       <c r="K14" t="n">
-        <v>216</v>
+        <v>9.92</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2597,91 +2597,91 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1655001</v>
+        <v>192316522</v>
       </c>
       <c r="N14" t="n">
-        <v>1202788</v>
+        <v>849726687</v>
       </c>
       <c r="O14" t="n">
-        <v>1664810</v>
+        <v>1407591057</v>
       </c>
       <c r="P14" t="n">
-        <v>1085</v>
+        <v>1382836880</v>
       </c>
       <c r="Q14" t="n">
-        <v>1219953</v>
+        <v>64496136</v>
       </c>
       <c r="R14" t="n">
-        <v>784532</v>
+        <v>392938129</v>
       </c>
       <c r="S14" t="n">
-        <v>1150106</v>
+        <v>644242478</v>
       </c>
       <c r="T14" t="n">
-        <v>-51329</v>
+        <v>621169449</v>
       </c>
       <c r="U14" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-462485</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>433048</v>
+        <v>127820386</v>
       </c>
       <c r="Z14" t="n">
-        <v>415256</v>
+        <v>456788558</v>
       </c>
       <c r="AA14" t="n">
-        <v>507704</v>
+        <v>763348579</v>
       </c>
       <c r="AB14" t="n">
-        <v>514899</v>
+        <v>761667431</v>
       </c>
       <c r="AC14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
         <v>44</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AL14" t="n">
         <v>44</v>
       </c>
-      <c r="AE14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>266.67</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>72</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>72</v>
-      </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣、量能溫和放大、分數升溫過快</t>
+          <t>DT進入觀察區、貼近5MA、均線多頭排列、接近20日高位</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2696,17 +2696,17 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -2819,28 +2819,28 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="AL15" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2978,28 +2978,28 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AI16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="AL16" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -3031,12 +3031,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3045,28 +3045,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1240</v>
+        <v>238</v>
       </c>
       <c r="E17" t="n">
-        <v>1155</v>
+        <v>232.6</v>
       </c>
       <c r="F17" t="n">
-        <v>1116.5</v>
+        <v>227.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1122.5</v>
+        <v>233.68</v>
       </c>
       <c r="H17" t="n">
-        <v>13910571</v>
+        <v>5064342</v>
       </c>
       <c r="I17" t="n">
-        <v>14506905</v>
+        <v>3657056</v>
       </c>
       <c r="J17" t="n">
-        <v>1335</v>
+        <v>255</v>
       </c>
       <c r="K17" t="n">
-        <v>1010</v>
+        <v>216</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -3074,91 +3074,91 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1525669</v>
+        <v>1655001</v>
       </c>
       <c r="N17" t="n">
-        <v>11310072</v>
+        <v>1202788</v>
       </c>
       <c r="O17" t="n">
-        <v>8465067</v>
+        <v>1664810</v>
       </c>
       <c r="P17" t="n">
-        <v>9611198</v>
+        <v>1085</v>
       </c>
       <c r="Q17" t="n">
-        <v>1331474</v>
+        <v>1219953</v>
       </c>
       <c r="R17" t="n">
-        <v>10596054</v>
+        <v>784532</v>
       </c>
       <c r="S17" t="n">
-        <v>8213420</v>
+        <v>1150106</v>
       </c>
       <c r="T17" t="n">
-        <v>8907392</v>
+        <v>-51329</v>
       </c>
       <c r="U17" t="n">
-        <v>156000</v>
+        <v>2000</v>
       </c>
       <c r="V17" t="n">
-        <v>65818</v>
+        <v>3000</v>
       </c>
       <c r="W17" t="n">
-        <v>-570099</v>
+        <v>7000</v>
       </c>
       <c r="X17" t="n">
-        <v>-339099</v>
+        <v>-462485</v>
       </c>
       <c r="Y17" t="n">
-        <v>38195</v>
+        <v>433048</v>
       </c>
       <c r="Z17" t="n">
-        <v>648200</v>
+        <v>415256</v>
       </c>
       <c r="AA17" t="n">
-        <v>821746</v>
+        <v>507704</v>
       </c>
       <c r="AB17" t="n">
-        <v>1042905</v>
+        <v>514899</v>
       </c>
       <c r="AC17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE17" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AF17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="AL17" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>DT進入觀察區、離5MA偏遠、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3173,29 +3173,29 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能未放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、黃金交叉、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1102.TW</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3204,28 +3204,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>35.7</v>
+        <v>1240</v>
       </c>
       <c r="E18" t="n">
-        <v>35.5</v>
+        <v>1155</v>
       </c>
       <c r="F18" t="n">
-        <v>35.33</v>
+        <v>1116.5</v>
       </c>
       <c r="G18" t="n">
-        <v>35.2</v>
+        <v>1122.5</v>
       </c>
       <c r="H18" t="n">
-        <v>7449257</v>
+        <v>13910571</v>
       </c>
       <c r="I18" t="n">
-        <v>8045877</v>
+        <v>14506905</v>
       </c>
       <c r="J18" t="n">
-        <v>36.1</v>
+        <v>1335</v>
       </c>
       <c r="K18" t="n">
-        <v>34.3</v>
+        <v>1010</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -3233,91 +3233,91 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-1114289</v>
+        <v>1525669</v>
       </c>
       <c r="N18" t="n">
-        <v>7833834</v>
+        <v>11310072</v>
       </c>
       <c r="O18" t="n">
-        <v>8257699</v>
+        <v>8465067</v>
       </c>
       <c r="P18" t="n">
-        <v>14366449</v>
+        <v>9611198</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1329809</v>
+        <v>1331474</v>
       </c>
       <c r="R18" t="n">
-        <v>7060828</v>
+        <v>10596054</v>
       </c>
       <c r="S18" t="n">
-        <v>5721470</v>
+        <v>8213420</v>
       </c>
       <c r="T18" t="n">
-        <v>11001297</v>
+        <v>8907392</v>
       </c>
       <c r="U18" t="n">
-        <v>120477</v>
+        <v>156000</v>
       </c>
       <c r="V18" t="n">
-        <v>460917</v>
+        <v>65818</v>
       </c>
       <c r="W18" t="n">
-        <v>1998485</v>
+        <v>-570099</v>
       </c>
       <c r="X18" t="n">
-        <v>3091153</v>
+        <v>-339099</v>
       </c>
       <c r="Y18" t="n">
-        <v>95043</v>
+        <v>38195</v>
       </c>
       <c r="Z18" t="n">
-        <v>312089</v>
+        <v>648200</v>
       </c>
       <c r="AA18" t="n">
-        <v>537744</v>
+        <v>821746</v>
       </c>
       <c r="AB18" t="n">
-        <v>273999</v>
+        <v>1042905</v>
       </c>
       <c r="AC18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AD18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AE18" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF18" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="AI18" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-28.57</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT進入觀察區、離5MA偏遠、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3332,17 +3332,17 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、黃金交叉、量能未放大</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、黃金交叉、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -3667,12 +3667,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>1102.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3681,28 +3681,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>34.2</v>
+        <v>35.7</v>
       </c>
       <c r="E21" t="n">
-        <v>33.85</v>
+        <v>35.5</v>
       </c>
       <c r="F21" t="n">
-        <v>31.54</v>
+        <v>35.33</v>
       </c>
       <c r="G21" t="n">
-        <v>29.7</v>
+        <v>35.2</v>
       </c>
       <c r="H21" t="n">
-        <v>542503236</v>
+        <v>7449257</v>
       </c>
       <c r="I21" t="n">
-        <v>765090156</v>
+        <v>8045877</v>
       </c>
       <c r="J21" t="n">
-        <v>36.65</v>
+        <v>36.1</v>
       </c>
       <c r="K21" t="n">
-        <v>25.2</v>
+        <v>34.3</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -3710,61 +3710,61 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-77900786</v>
+        <v>-1114289</v>
       </c>
       <c r="N21" t="n">
-        <v>10446226</v>
+        <v>7833834</v>
       </c>
       <c r="O21" t="n">
-        <v>223662563</v>
+        <v>8257699</v>
       </c>
       <c r="P21" t="n">
-        <v>86644723</v>
+        <v>14366449</v>
       </c>
       <c r="Q21" t="n">
-        <v>-79998614</v>
+        <v>-1329809</v>
       </c>
       <c r="R21" t="n">
-        <v>11427169</v>
+        <v>7060828</v>
       </c>
       <c r="S21" t="n">
-        <v>195158038</v>
+        <v>5721470</v>
       </c>
       <c r="T21" t="n">
-        <v>73225944</v>
+        <v>11001297</v>
       </c>
       <c r="U21" t="n">
-        <v>-6000</v>
+        <v>120477</v>
       </c>
       <c r="V21" t="n">
-        <v>180137</v>
+        <v>460917</v>
       </c>
       <c r="W21" t="n">
-        <v>3783119</v>
+        <v>1998485</v>
       </c>
       <c r="X21" t="n">
-        <v>3733316</v>
+        <v>3091153</v>
       </c>
       <c r="Y21" t="n">
-        <v>2103828</v>
+        <v>95043</v>
       </c>
       <c r="Z21" t="n">
-        <v>-1161080</v>
+        <v>312089</v>
       </c>
       <c r="AA21" t="n">
-        <v>24721406</v>
+        <v>537744</v>
       </c>
       <c r="AB21" t="n">
-        <v>9685463</v>
+        <v>273999</v>
       </c>
       <c r="AC21" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AD21" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE21" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AF21" t="n">
         <v>50</v>
@@ -3773,28 +3773,28 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI21" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-9.52</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="AL21" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -3819,19 +3819,19 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1612.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>宏泰</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3840,28 +3840,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>35.05</v>
+        <v>34.2</v>
       </c>
       <c r="E22" t="n">
-        <v>35.02</v>
+        <v>33.85</v>
       </c>
       <c r="F22" t="n">
-        <v>34.9</v>
+        <v>31.54</v>
       </c>
       <c r="G22" t="n">
-        <v>34.88</v>
+        <v>29.7</v>
       </c>
       <c r="H22" t="n">
-        <v>358528</v>
+        <v>542503236</v>
       </c>
       <c r="I22" t="n">
-        <v>307861</v>
+        <v>765090156</v>
       </c>
       <c r="J22" t="n">
-        <v>35.8</v>
+        <v>36.65</v>
       </c>
       <c r="K22" t="n">
-        <v>34.5</v>
+        <v>25.2</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -3869,52 +3869,52 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>81231</v>
+        <v>-77900786</v>
       </c>
       <c r="N22" t="n">
-        <v>239458</v>
+        <v>10446226</v>
       </c>
       <c r="O22" t="n">
-        <v>335918</v>
+        <v>223662563</v>
       </c>
       <c r="P22" t="n">
-        <v>608464</v>
+        <v>86644723</v>
       </c>
       <c r="Q22" t="n">
-        <v>122382</v>
+        <v>-79998614</v>
       </c>
       <c r="R22" t="n">
-        <v>276468</v>
+        <v>11427169</v>
       </c>
       <c r="S22" t="n">
-        <v>383468</v>
+        <v>195158038</v>
       </c>
       <c r="T22" t="n">
-        <v>594779</v>
+        <v>73225944</v>
       </c>
       <c r="U22" t="n">
-        <v>-4561</v>
+        <v>-6000</v>
       </c>
       <c r="V22" t="n">
-        <v>-4561</v>
+        <v>180137</v>
       </c>
       <c r="W22" t="n">
-        <v>-9120</v>
+        <v>3783119</v>
       </c>
       <c r="X22" t="n">
-        <v>-9120</v>
+        <v>3733316</v>
       </c>
       <c r="Y22" t="n">
-        <v>-36590</v>
+        <v>2103828</v>
       </c>
       <c r="Z22" t="n">
-        <v>-32449</v>
+        <v>-1161080</v>
       </c>
       <c r="AA22" t="n">
-        <v>-38430</v>
+        <v>24721406</v>
       </c>
       <c r="AB22" t="n">
-        <v>22805</v>
+        <v>9685463</v>
       </c>
       <c r="AC22" t="n">
         <v>38</v>
@@ -3932,19 +3932,19 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="AI22" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AL22" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3968,29 +3968,29 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>1612.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>宏泰</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3999,28 +3999,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>699</v>
+        <v>35.05</v>
       </c>
       <c r="E23" t="n">
-        <v>677.2</v>
+        <v>35.02</v>
       </c>
       <c r="F23" t="n">
-        <v>642.7</v>
+        <v>34.9</v>
       </c>
       <c r="G23" t="n">
-        <v>626.85</v>
+        <v>34.88</v>
       </c>
       <c r="H23" t="n">
-        <v>10964118</v>
+        <v>358528</v>
       </c>
       <c r="I23" t="n">
-        <v>19268206</v>
+        <v>307861</v>
       </c>
       <c r="J23" t="n">
-        <v>711</v>
+        <v>35.8</v>
       </c>
       <c r="K23" t="n">
-        <v>565</v>
+        <v>34.5</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -4028,91 +4028,91 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-245173</v>
+        <v>81231</v>
       </c>
       <c r="N23" t="n">
-        <v>12414024</v>
+        <v>239458</v>
       </c>
       <c r="O23" t="n">
-        <v>26757928</v>
+        <v>335918</v>
       </c>
       <c r="P23" t="n">
-        <v>17409079</v>
+        <v>608464</v>
       </c>
       <c r="Q23" t="n">
-        <v>1906308</v>
+        <v>122382</v>
       </c>
       <c r="R23" t="n">
-        <v>14394578</v>
+        <v>276468</v>
       </c>
       <c r="S23" t="n">
-        <v>26732575</v>
+        <v>383468</v>
       </c>
       <c r="T23" t="n">
-        <v>18644582</v>
+        <v>594779</v>
       </c>
       <c r="U23" t="n">
-        <v>-2167000</v>
+        <v>-4561</v>
       </c>
       <c r="V23" t="n">
-        <v>-3280137</v>
+        <v>-4561</v>
       </c>
       <c r="W23" t="n">
-        <v>-3299158</v>
+        <v>-9120</v>
       </c>
       <c r="X23" t="n">
-        <v>-4233082</v>
+        <v>-9120</v>
       </c>
       <c r="Y23" t="n">
-        <v>15519</v>
+        <v>-36590</v>
       </c>
       <c r="Z23" t="n">
-        <v>1299583</v>
+        <v>-32449</v>
       </c>
       <c r="AA23" t="n">
-        <v>3324511</v>
+        <v>-38430</v>
       </c>
       <c r="AB23" t="n">
-        <v>2997579</v>
+        <v>22805</v>
       </c>
       <c r="AC23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AD23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AE23" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AF23" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AI23" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-14.29</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -4127,29 +4127,29 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3022.TW</t>
+          <t>3711.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>威強電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4158,28 +4158,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>93.09999999999999</v>
+        <v>699</v>
       </c>
       <c r="E24" t="n">
-        <v>91.81999999999999</v>
+        <v>677.2</v>
       </c>
       <c r="F24" t="n">
-        <v>88.86</v>
+        <v>642.7</v>
       </c>
       <c r="G24" t="n">
-        <v>89.16</v>
+        <v>626.85</v>
       </c>
       <c r="H24" t="n">
-        <v>1540683</v>
+        <v>10964118</v>
       </c>
       <c r="I24" t="n">
-        <v>1314020</v>
+        <v>19268206</v>
       </c>
       <c r="J24" t="n">
-        <v>98.59999999999999</v>
+        <v>711</v>
       </c>
       <c r="K24" t="n">
-        <v>82.09999999999999</v>
+        <v>565</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -4187,52 +4187,52 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>441071</v>
+        <v>-245173</v>
       </c>
       <c r="N24" t="n">
-        <v>324599</v>
+        <v>12414024</v>
       </c>
       <c r="O24" t="n">
-        <v>1090001</v>
+        <v>26757928</v>
       </c>
       <c r="P24" t="n">
-        <v>2776761</v>
+        <v>17409079</v>
       </c>
       <c r="Q24" t="n">
-        <v>468685</v>
+        <v>1906308</v>
       </c>
       <c r="R24" t="n">
-        <v>366463</v>
+        <v>14394578</v>
       </c>
       <c r="S24" t="n">
-        <v>1070133</v>
+        <v>26732575</v>
       </c>
       <c r="T24" t="n">
-        <v>2732312</v>
+        <v>18644582</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>-2167000</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-3280137</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-3299158</v>
       </c>
       <c r="X24" t="n">
-        <v>-1264</v>
+        <v>-4233082</v>
       </c>
       <c r="Y24" t="n">
-        <v>-27614</v>
+        <v>15519</v>
       </c>
       <c r="Z24" t="n">
-        <v>-41864</v>
+        <v>1299583</v>
       </c>
       <c r="AA24" t="n">
-        <v>19868</v>
+        <v>3324511</v>
       </c>
       <c r="AB24" t="n">
-        <v>45713</v>
+        <v>2997579</v>
       </c>
       <c r="AC24" t="n">
         <v>36</v>
@@ -4241,37 +4241,37 @@
         <v>36</v>
       </c>
       <c r="AE24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF24" t="n">
         <v>30</v>
       </c>
-      <c r="AF24" t="n">
-        <v>60</v>
-      </c>
       <c r="AG24" t="n">
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="AI24" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4286,29 +4286,29 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6213.TW</t>
+          <t>3022.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>威強電</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4317,28 +4317,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>548</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>561.2</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>528.35</v>
+        <v>88.86</v>
       </c>
       <c r="G25" t="n">
-        <v>473.6</v>
+        <v>89.16</v>
       </c>
       <c r="H25" t="n">
-        <v>17724290</v>
+        <v>1540683</v>
       </c>
       <c r="I25" t="n">
-        <v>27116007</v>
+        <v>1314020</v>
       </c>
       <c r="J25" t="n">
-        <v>599</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>289</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -4346,91 +4346,91 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>1800878</v>
+        <v>441071</v>
       </c>
       <c r="N25" t="n">
-        <v>4657254</v>
+        <v>324599</v>
       </c>
       <c r="O25" t="n">
-        <v>13782034</v>
+        <v>1090001</v>
       </c>
       <c r="P25" t="n">
-        <v>3611772</v>
+        <v>2776761</v>
       </c>
       <c r="Q25" t="n">
-        <v>833221</v>
+        <v>468685</v>
       </c>
       <c r="R25" t="n">
-        <v>3546220</v>
+        <v>366463</v>
       </c>
       <c r="S25" t="n">
-        <v>11543180</v>
+        <v>1070133</v>
       </c>
       <c r="T25" t="n">
-        <v>969701</v>
+        <v>2732312</v>
       </c>
       <c r="U25" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>734000</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1511000</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2514000</v>
+        <v>-1264</v>
       </c>
       <c r="Y25" t="n">
-        <v>367657</v>
+        <v>-27614</v>
       </c>
       <c r="Z25" t="n">
-        <v>377034</v>
+        <v>-41864</v>
       </c>
       <c r="AA25" t="n">
-        <v>727854</v>
+        <v>19868</v>
       </c>
       <c r="AB25" t="n">
-        <v>128071</v>
+        <v>45713</v>
       </c>
       <c r="AC25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AD25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE25" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="AF25" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AI25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>21.43</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AL25" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -4445,29 +4445,29 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3017.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4476,28 +4476,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3555</v>
+        <v>59.6</v>
       </c>
       <c r="E26" t="n">
-        <v>3452</v>
+        <v>60.48</v>
       </c>
       <c r="F26" t="n">
-        <v>3341.5</v>
+        <v>60.21</v>
       </c>
       <c r="G26" t="n">
-        <v>3366.75</v>
+        <v>59.04</v>
       </c>
       <c r="H26" t="n">
-        <v>2261001</v>
+        <v>12099033</v>
       </c>
       <c r="I26" t="n">
-        <v>2545420</v>
+        <v>25242602</v>
       </c>
       <c r="J26" t="n">
-        <v>3600</v>
+        <v>63.1</v>
       </c>
       <c r="K26" t="n">
-        <v>3100</v>
+        <v>55.8</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -4505,52 +4505,52 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>219840</v>
+        <v>1425</v>
       </c>
       <c r="N26" t="n">
-        <v>317013</v>
+        <v>6606447</v>
       </c>
       <c r="O26" t="n">
-        <v>387468</v>
+        <v>7485478</v>
       </c>
       <c r="P26" t="n">
-        <v>417701</v>
+        <v>64889766</v>
       </c>
       <c r="Q26" t="n">
-        <v>165864</v>
+        <v>128704</v>
       </c>
       <c r="R26" t="n">
-        <v>-30783</v>
+        <v>6950857</v>
       </c>
       <c r="S26" t="n">
-        <v>-208489</v>
+        <v>7099024</v>
       </c>
       <c r="T26" t="n">
-        <v>-92628</v>
+        <v>63528700</v>
       </c>
       <c r="U26" t="n">
-        <v>10999</v>
+        <v>50000</v>
       </c>
       <c r="V26" t="n">
-        <v>227643</v>
+        <v>195000</v>
       </c>
       <c r="W26" t="n">
-        <v>317582</v>
+        <v>133428</v>
       </c>
       <c r="X26" t="n">
-        <v>224574</v>
+        <v>-95466</v>
       </c>
       <c r="Y26" t="n">
-        <v>42977</v>
+        <v>-177279</v>
       </c>
       <c r="Z26" t="n">
-        <v>120153</v>
+        <v>-539410</v>
       </c>
       <c r="AA26" t="n">
-        <v>278375</v>
+        <v>253026</v>
       </c>
       <c r="AB26" t="n">
-        <v>285755</v>
+        <v>1456532</v>
       </c>
       <c r="AC26" t="n">
         <v>34</v>
@@ -4559,37 +4559,37 @@
         <v>34</v>
       </c>
       <c r="AE26" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AI26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>54.55</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4604,17 +4604,17 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、接近20日高點、法人連續偏買、5日法人買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -4727,28 +4727,28 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AI27" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AL27" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4780,12 +4780,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>3014.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>聯陽</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4794,28 +4794,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>59.6</v>
+        <v>140.5</v>
       </c>
       <c r="E28" t="n">
-        <v>60.48</v>
+        <v>139.5</v>
       </c>
       <c r="F28" t="n">
-        <v>60.21</v>
+        <v>135.5</v>
       </c>
       <c r="G28" t="n">
-        <v>59.04</v>
+        <v>133.2</v>
       </c>
       <c r="H28" t="n">
-        <v>12099033</v>
+        <v>2408672</v>
       </c>
       <c r="I28" t="n">
-        <v>25242602</v>
+        <v>3468544</v>
       </c>
       <c r="J28" t="n">
-        <v>63.1</v>
+        <v>144</v>
       </c>
       <c r="K28" t="n">
-        <v>55.8</v>
+        <v>128.5</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -4823,52 +4823,52 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>1425</v>
+        <v>-775236</v>
       </c>
       <c r="N28" t="n">
-        <v>6606447</v>
+        <v>-839215</v>
       </c>
       <c r="O28" t="n">
-        <v>7485478</v>
+        <v>254904</v>
       </c>
       <c r="P28" t="n">
-        <v>64889766</v>
+        <v>1469401</v>
       </c>
       <c r="Q28" t="n">
-        <v>128704</v>
+        <v>-792621</v>
       </c>
       <c r="R28" t="n">
-        <v>6950857</v>
+        <v>-936731</v>
       </c>
       <c r="S28" t="n">
-        <v>7099024</v>
+        <v>32129</v>
       </c>
       <c r="T28" t="n">
-        <v>63528700</v>
+        <v>1177943</v>
       </c>
       <c r="U28" t="n">
-        <v>50000</v>
+        <v>17649</v>
       </c>
       <c r="V28" t="n">
-        <v>195000</v>
+        <v>106171</v>
       </c>
       <c r="W28" t="n">
-        <v>133428</v>
+        <v>188422</v>
       </c>
       <c r="X28" t="n">
-        <v>-95466</v>
+        <v>254095</v>
       </c>
       <c r="Y28" t="n">
-        <v>-177279</v>
+        <v>-264</v>
       </c>
       <c r="Z28" t="n">
-        <v>-539410</v>
+        <v>-8655</v>
       </c>
       <c r="AA28" t="n">
-        <v>253026</v>
+        <v>34353</v>
       </c>
       <c r="AB28" t="n">
-        <v>1456532</v>
+        <v>37363</v>
       </c>
       <c r="AC28" t="n">
         <v>34</v>
@@ -4877,10 +4877,10 @@
         <v>34</v>
       </c>
       <c r="AE28" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="AF28" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -4895,19 +4895,19 @@
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AL28" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4922,29 +4922,29 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3045.TW</t>
+          <t>3017.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4953,28 +4953,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>122.5</v>
+        <v>3555</v>
       </c>
       <c r="E29" t="n">
-        <v>123.4</v>
+        <v>3452</v>
       </c>
       <c r="F29" t="n">
-        <v>123.2</v>
+        <v>3341.5</v>
       </c>
       <c r="G29" t="n">
-        <v>120.03</v>
+        <v>3366.75</v>
       </c>
       <c r="H29" t="n">
-        <v>4901190</v>
+        <v>2261001</v>
       </c>
       <c r="I29" t="n">
-        <v>10209533</v>
+        <v>2545420</v>
       </c>
       <c r="J29" t="n">
-        <v>125.5</v>
+        <v>3600</v>
       </c>
       <c r="K29" t="n">
-        <v>112.5</v>
+        <v>3100</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -4982,52 +4982,52 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>966522</v>
+        <v>219840</v>
       </c>
       <c r="N29" t="n">
-        <v>6361236</v>
+        <v>317013</v>
       </c>
       <c r="O29" t="n">
-        <v>10675368</v>
+        <v>387468</v>
       </c>
       <c r="P29" t="n">
-        <v>20352103</v>
+        <v>417701</v>
       </c>
       <c r="Q29" t="n">
-        <v>1434392</v>
+        <v>165864</v>
       </c>
       <c r="R29" t="n">
-        <v>6590686</v>
+        <v>-30783</v>
       </c>
       <c r="S29" t="n">
-        <v>8648199</v>
+        <v>-208489</v>
       </c>
       <c r="T29" t="n">
-        <v>18858252</v>
+        <v>-92628</v>
       </c>
       <c r="U29" t="n">
-        <v>-233000</v>
+        <v>10999</v>
       </c>
       <c r="V29" t="n">
-        <v>-444553</v>
+        <v>227643</v>
       </c>
       <c r="W29" t="n">
-        <v>1722523</v>
+        <v>317582</v>
       </c>
       <c r="X29" t="n">
-        <v>2100747</v>
+        <v>224574</v>
       </c>
       <c r="Y29" t="n">
-        <v>-234870</v>
+        <v>42977</v>
       </c>
       <c r="Z29" t="n">
-        <v>215103</v>
+        <v>120153</v>
       </c>
       <c r="AA29" t="n">
-        <v>304646</v>
+        <v>278375</v>
       </c>
       <c r="AB29" t="n">
-        <v>-606896</v>
+        <v>285755</v>
       </c>
       <c r="AC29" t="n">
         <v>34</v>
@@ -5036,28 +5036,28 @@
         <v>34</v>
       </c>
       <c r="AE29" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="AF29" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AI29" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AL29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -5081,29 +5081,29 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、接近20日高點、法人連續偏買、5日法人買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3014.TW</t>
+          <t>3045.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>聯陽</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5112,28 +5112,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>140.5</v>
+        <v>122.5</v>
       </c>
       <c r="E30" t="n">
-        <v>139.5</v>
+        <v>123.4</v>
       </c>
       <c r="F30" t="n">
-        <v>135.5</v>
+        <v>123.2</v>
       </c>
       <c r="G30" t="n">
-        <v>133.2</v>
+        <v>120.28</v>
       </c>
       <c r="H30" t="n">
-        <v>2408672</v>
+        <v>4901190</v>
       </c>
       <c r="I30" t="n">
-        <v>3468544</v>
+        <v>10209533</v>
       </c>
       <c r="J30" t="n">
-        <v>144</v>
+        <v>125.5</v>
       </c>
       <c r="K30" t="n">
-        <v>128.5</v>
+        <v>113.5</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -5141,52 +5141,52 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-775236</v>
+        <v>966522</v>
       </c>
       <c r="N30" t="n">
-        <v>-839215</v>
+        <v>6361236</v>
       </c>
       <c r="O30" t="n">
-        <v>254904</v>
+        <v>10675368</v>
       </c>
       <c r="P30" t="n">
-        <v>1469401</v>
+        <v>20352103</v>
       </c>
       <c r="Q30" t="n">
-        <v>-792621</v>
+        <v>1434392</v>
       </c>
       <c r="R30" t="n">
-        <v>-936731</v>
+        <v>6590686</v>
       </c>
       <c r="S30" t="n">
-        <v>32129</v>
+        <v>8648199</v>
       </c>
       <c r="T30" t="n">
-        <v>1177943</v>
+        <v>18858252</v>
       </c>
       <c r="U30" t="n">
-        <v>17649</v>
+        <v>-233000</v>
       </c>
       <c r="V30" t="n">
-        <v>106171</v>
+        <v>-444553</v>
       </c>
       <c r="W30" t="n">
-        <v>188422</v>
+        <v>1722523</v>
       </c>
       <c r="X30" t="n">
-        <v>254095</v>
+        <v>2100747</v>
       </c>
       <c r="Y30" t="n">
-        <v>-264</v>
+        <v>-234870</v>
       </c>
       <c r="Z30" t="n">
-        <v>-8655</v>
+        <v>215103</v>
       </c>
       <c r="AA30" t="n">
-        <v>34353</v>
+        <v>304646</v>
       </c>
       <c r="AB30" t="n">
-        <v>37363</v>
+        <v>-606896</v>
       </c>
       <c r="AC30" t="n">
         <v>34</v>
@@ -5195,37 +5195,37 @@
         <v>34</v>
       </c>
       <c r="AE30" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="AF30" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AI30" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-29.17</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5240,17 +5240,17 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -5363,28 +5363,28 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AI31" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-23.81</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AL31" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -5522,19 +5522,19 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AI32" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-27.27</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AL32" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、接近20日高位、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、接近20日高位</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5681,28 +5681,28 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="AI33" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL33" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AI34" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>-21.05</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5999,28 +5999,28 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AI35" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>85.70999999999999</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AL35" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -6317,19 +6317,19 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AI37" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>-29.41</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -6476,19 +6476,19 @@
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI38" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>-14.29</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -6635,19 +6635,19 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AI39" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6794,19 +6794,19 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>22.22</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AL40" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>DT尚未轉強、離5MA偏遠、均線多頭排列、分數剛升溫</t>
+          <t>DT尚未轉強、離5MA偏遠、均線多頭排列</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6953,19 +6953,19 @@
         <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AI41" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>-56</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -7006,12 +7006,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>2540.TW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>愛山林</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7020,28 +7020,28 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2405</v>
+        <v>49</v>
       </c>
       <c r="E42" t="n">
-        <v>2410</v>
+        <v>49.57</v>
       </c>
       <c r="F42" t="n">
-        <v>2394</v>
+        <v>49.08</v>
       </c>
       <c r="G42" t="n">
-        <v>2391</v>
+        <v>48.59</v>
       </c>
       <c r="H42" t="n">
-        <v>32792740</v>
+        <v>226455</v>
       </c>
       <c r="I42" t="n">
-        <v>20007748</v>
+        <v>670832</v>
       </c>
       <c r="J42" t="n">
-        <v>2445</v>
+        <v>54</v>
       </c>
       <c r="K42" t="n">
-        <v>2310</v>
+        <v>46.6</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -7049,52 +7049,52 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>-5712849</v>
+        <v>13142</v>
       </c>
       <c r="N42" t="n">
-        <v>-3675870</v>
+        <v>299372</v>
       </c>
       <c r="O42" t="n">
-        <v>8242027</v>
+        <v>114919</v>
       </c>
       <c r="P42" t="n">
-        <v>-17514638</v>
+        <v>1005286</v>
       </c>
       <c r="Q42" t="n">
-        <v>-4667832</v>
+        <v>14142</v>
       </c>
       <c r="R42" t="n">
-        <v>-1873973</v>
+        <v>300372</v>
       </c>
       <c r="S42" t="n">
-        <v>6854883</v>
+        <v>35919</v>
       </c>
       <c r="T42" t="n">
-        <v>-20764219</v>
+        <v>858286</v>
       </c>
       <c r="U42" t="n">
-        <v>-1287718</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>-2836160</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>-1623153</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>-1178467</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>242701</v>
+        <v>-1000</v>
       </c>
       <c r="Z42" t="n">
-        <v>1034263</v>
+        <v>-1000</v>
       </c>
       <c r="AA42" t="n">
-        <v>3010297</v>
+        <v>79000</v>
       </c>
       <c r="AB42" t="n">
-        <v>4428048</v>
+        <v>147000</v>
       </c>
       <c r="AC42" t="n">
         <v>22</v>
@@ -7103,28 +7103,28 @@
         <v>22</v>
       </c>
       <c r="AE42" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AF42" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="AI42" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>-54.17</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AL42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -7148,17 +7148,17 @@
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、成交量放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、成交量放大、接近20日高點、接近20日低點、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -7271,13 +7271,13 @@
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="AI43" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
         <v>0</v>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -7430,19 +7430,19 @@
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>22.22</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AL44" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、分數剛升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -7589,19 +7589,19 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AI45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AL45" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -7748,19 +7748,19 @@
         <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI46" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>-8.33</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AL46" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7907,19 +7907,19 @@
         <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="AI47" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>-42.11</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -8066,28 +8066,28 @@
         <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AI48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>57.14</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="AL48" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>可優先研究</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -8119,12 +8119,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2540.TW</t>
+          <t>2610.TW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>愛山林</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8133,28 +8133,28 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>49</v>
+        <v>20.3</v>
       </c>
       <c r="E49" t="n">
-        <v>49.57</v>
+        <v>20.33</v>
       </c>
       <c r="F49" t="n">
-        <v>49.08</v>
+        <v>20.24</v>
       </c>
       <c r="G49" t="n">
-        <v>48.59</v>
+        <v>20.33</v>
       </c>
       <c r="H49" t="n">
-        <v>226455</v>
+        <v>25331179</v>
       </c>
       <c r="I49" t="n">
-        <v>670832</v>
+        <v>22267928</v>
       </c>
       <c r="J49" t="n">
-        <v>54</v>
+        <v>20.65</v>
       </c>
       <c r="K49" t="n">
-        <v>46.6</v>
+        <v>19.9</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -8162,82 +8162,82 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>13142</v>
+        <v>-8757033</v>
       </c>
       <c r="N49" t="n">
-        <v>299372</v>
+        <v>22069471</v>
       </c>
       <c r="O49" t="n">
-        <v>114919</v>
+        <v>19889871</v>
       </c>
       <c r="P49" t="n">
-        <v>1005286</v>
+        <v>18060312</v>
       </c>
       <c r="Q49" t="n">
-        <v>14142</v>
+        <v>-14209150</v>
       </c>
       <c r="R49" t="n">
-        <v>300372</v>
+        <v>5626165</v>
       </c>
       <c r="S49" t="n">
-        <v>35919</v>
+        <v>-41096</v>
       </c>
       <c r="T49" t="n">
-        <v>858286</v>
+        <v>-4729597</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>5571000</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>16202000</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>19262765</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>21742765</v>
       </c>
       <c r="Y49" t="n">
-        <v>-1000</v>
+        <v>-118883</v>
       </c>
       <c r="Z49" t="n">
-        <v>-1000</v>
+        <v>241306</v>
       </c>
       <c r="AA49" t="n">
-        <v>79000</v>
+        <v>668202</v>
       </c>
       <c r="AB49" t="n">
-        <v>147000</v>
+        <v>1047144</v>
       </c>
       <c r="AC49" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD49" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE49" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="n">
         <v>5</v>
       </c>
-      <c r="AF49" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>-15.38</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>0</v>
-      </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -8261,29 +8261,29 @@
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、黃金交叉、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、黃金交叉、量能溫和放大、接近20日高點、接近20日低點、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2610.TW</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -8292,28 +8292,28 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>20.3</v>
+        <v>502</v>
       </c>
       <c r="E50" t="n">
-        <v>20.33</v>
+        <v>498.1</v>
       </c>
       <c r="F50" t="n">
-        <v>20.24</v>
+        <v>476.95</v>
       </c>
       <c r="G50" t="n">
-        <v>20.33</v>
+        <v>466.55</v>
       </c>
       <c r="H50" t="n">
-        <v>25331179</v>
+        <v>21692000</v>
       </c>
       <c r="I50" t="n">
-        <v>22267928</v>
+        <v>30228600</v>
       </c>
       <c r="J50" t="n">
-        <v>20.65</v>
+        <v>518</v>
       </c>
       <c r="K50" t="n">
-        <v>19.9</v>
+        <v>420</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -8321,128 +8321,128 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>-8757033</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>22069471</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>19889871</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>18060312</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>-14209150</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>5626165</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>-41096</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>-4729597</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>5571000</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>16202000</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>19262765</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>21742765</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>-118883</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>241306</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>668202</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1047144</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AD50" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE50" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AF50" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="AI50" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>-52.38</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>跌破5日線、黃金交叉、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、黃金交叉、量能溫和放大、接近20日高點、接近20日低點、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>4903.TWO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -8451,28 +8451,28 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>502</v>
+        <v>43</v>
       </c>
       <c r="E51" t="n">
-        <v>498.1</v>
+        <v>41.23</v>
       </c>
       <c r="F51" t="n">
-        <v>476.95</v>
+        <v>37.69</v>
       </c>
       <c r="G51" t="n">
-        <v>466.55</v>
+        <v>37.21</v>
       </c>
       <c r="H51" t="n">
-        <v>21692000</v>
+        <v>5381000</v>
       </c>
       <c r="I51" t="n">
-        <v>30228600</v>
+        <v>8197200</v>
       </c>
       <c r="J51" t="n">
-        <v>518</v>
+        <v>43.9</v>
       </c>
       <c r="K51" t="n">
-        <v>420</v>
+        <v>33.15</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -8552,19 +8552,19 @@
         <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AL51" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8702,19 +8702,19 @@
         <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AI52" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>-30.77</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8755,12 +8755,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4903.TWO</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -8769,28 +8769,28 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>43</v>
+        <v>2475</v>
       </c>
       <c r="E53" t="n">
-        <v>41.23</v>
+        <v>2475</v>
       </c>
       <c r="F53" t="n">
-        <v>37.69</v>
+        <v>2435.5</v>
       </c>
       <c r="G53" t="n">
-        <v>37.21</v>
+        <v>2432.5</v>
       </c>
       <c r="H53" t="n">
-        <v>5381000</v>
+        <v>14557662</v>
       </c>
       <c r="I53" t="n">
-        <v>8197200</v>
+        <v>23272932</v>
       </c>
       <c r="J53" t="n">
-        <v>43.9</v>
+        <v>2510</v>
       </c>
       <c r="K53" t="n">
-        <v>33.15</v>
+        <v>2375</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -8798,82 +8798,82 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>-5712849</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>-3675870</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>8242027</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>-17514638</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>-4667832</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>-1873973</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>6854883</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>-20764219</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>-1287718</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>-2836160</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>-1623153</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>-1178467</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>242701</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1034263</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>3010297</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>4428048</v>
       </c>
       <c r="AC53" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD53" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE53" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI53" t="n">
         <v>-6</v>
       </c>
       <c r="AJ53" t="n">
-        <v>-25</v>
+        <v>-27.27</v>
       </c>
       <c r="AK53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -8897,17 +8897,17 @@
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -9020,19 +9020,19 @@
         <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>-14</v>
+        <v>16</v>
       </c>
       <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" t="n">
         <v>30</v>
       </c>
-      <c r="AJ54" t="n">
-        <v>214.29</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>35</v>
-      </c>
       <c r="AL54" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、分數升溫過快</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -9179,19 +9179,19 @@
         <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AI55" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -9338,19 +9338,19 @@
         <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AI56" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>-53.33</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -9497,19 +9497,19 @@
         <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AI57" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AJ57" t="n">
-        <v>-58.82</v>
+        <v>0</v>
       </c>
       <c r="AK57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -9656,19 +9656,19 @@
         <v>0</v>
       </c>
       <c r="AH58" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK58" t="n">
         <v>40</v>
       </c>
-      <c r="AI58" t="n">
-        <v>-26</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>-65</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>30</v>
-      </c>
       <c r="AL58" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9815,19 +9815,19 @@
         <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AI59" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="AJ59" t="n">
-        <v>-70</v>
+        <v>0</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -10133,28 +10133,28 @@
         <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>-2</v>
+        <v>12</v>
       </c>
       <c r="AI61" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AJ61" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="AK61" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AL61" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -10292,19 +10292,19 @@
         <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="AI62" t="n">
-        <v>-46</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>-82.14</v>
+        <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL62" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -10451,19 +10451,19 @@
         <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>-22</v>
+        <v>10</v>
       </c>
       <c r="AI63" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ63" t="n">
-        <v>145.45</v>
+        <v>0</v>
       </c>
       <c r="AK63" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="AL63" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能偏強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能偏強</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -10610,28 +10610,28 @@
         <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>-8</v>
+        <v>8</v>
       </c>
       <c r="AI64" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AJ64" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AK64" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AL64" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10769,19 +10769,19 @@
         <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AI65" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="n">
-        <v>-33.33</v>
+        <v>0</v>
       </c>
       <c r="AK65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AL65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10928,28 +10928,28 @@
         <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AI66" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AJ66" t="n">
-        <v>-42.86</v>
+        <v>0</v>
       </c>
       <c r="AK66" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AL66" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -11246,19 +11246,19 @@
         <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AI68" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AJ68" t="n">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -11723,19 +11723,19 @@
         <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>-14</v>
+        <v>4</v>
       </c>
       <c r="AI71" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AJ71" t="n">
-        <v>128.57</v>
+        <v>0</v>
       </c>
       <c r="AK71" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL71" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11882,19 +11882,19 @@
         <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="AI72" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="AJ72" t="n">
-        <v>-87.5</v>
+        <v>0</v>
       </c>
       <c r="AK72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -12041,19 +12041,19 @@
         <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="AI73" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="AJ73" t="n">
-        <v>-84.62</v>
+        <v>0</v>
       </c>
       <c r="AK73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -12200,19 +12200,19 @@
         <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="AI74" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="AJ74" t="n">
-        <v>-85.70999999999999</v>
+        <v>0</v>
       </c>
       <c r="AK74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -12359,19 +12359,19 @@
         <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="AI75" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="AJ75" t="n">
-        <v>-81.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="AK75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -12518,19 +12518,19 @@
         <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AI76" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AJ76" t="n">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="AK76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -12677,19 +12677,19 @@
         <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AI77" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AJ77" t="n">
-        <v>-85.70999999999999</v>
+        <v>0</v>
       </c>
       <c r="AK77" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL77" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -12836,28 +12836,28 @@
         <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>-34</v>
+        <v>2</v>
       </c>
       <c r="AI78" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AJ78" t="n">
-        <v>105.88</v>
+        <v>0</v>
       </c>
       <c r="AK78" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AL78" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -12995,19 +12995,17 @@
         <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="AI79" t="n">
-        <v>-58</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>-100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr"/>
       <c r="AK79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
@@ -13016,7 +13014,7 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -13154,19 +13152,17 @@
         <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ80" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr"/>
       <c r="AK80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
@@ -13175,7 +13171,7 @@
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -13313,14 +13309,12 @@
         <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AJ81" t="n">
-        <v>-100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr"/>
       <c r="AK81" t="n">
         <v>0</v>
       </c>
@@ -13334,7 +13328,7 @@
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -13472,14 +13466,12 @@
         <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
-        <v>-22</v>
-      </c>
-      <c r="AJ82" t="n">
-        <v>-100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="n">
         <v>0</v>
       </c>
@@ -13493,7 +13485,7 @@
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -13631,12 +13623,14 @@
         <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AI83" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AJ83" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>0</v>
+      </c>
       <c r="AK83" t="n">
         <v>0</v>
       </c>
@@ -13650,7 +13644,7 @@
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -13788,13 +13782,13 @@
         <v>0</v>
       </c>
       <c r="AH84" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="AI84" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AJ84" t="n">
-        <v>-166.67</v>
+        <v>0</v>
       </c>
       <c r="AK84" t="n">
         <v>0</v>
@@ -13809,7 +13803,7 @@
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -13947,28 +13941,28 @@
         <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>-26</v>
+        <v>-4</v>
       </c>
       <c r="AI85" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AJ85" t="n">
-        <v>84.62</v>
+        <v>0</v>
       </c>
       <c r="AK85" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AL85" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -14106,19 +14100,19 @@
         <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>38</v>
+        <v>-4</v>
       </c>
       <c r="AI86" t="n">
-        <v>-42</v>
+        <v>0</v>
       </c>
       <c r="AJ86" t="n">
-        <v>-110.53</v>
+        <v>0</v>
       </c>
       <c r="AK86" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AL86" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
@@ -14127,7 +14121,7 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -14265,19 +14259,19 @@
         <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>22</v>
+        <v>-6</v>
       </c>
       <c r="AI87" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="AJ87" t="n">
-        <v>-127.27</v>
+        <v>0</v>
       </c>
       <c r="AK87" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL87" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
@@ -14286,7 +14280,7 @@
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -14424,28 +14418,28 @@
         <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
       <c r="AI88" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AK88" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AL88" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -14583,13 +14577,13 @@
         <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="AI89" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AJ89" t="n">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="AK89" t="n">
         <v>0</v>
@@ -14604,7 +14598,7 @@
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -14742,19 +14736,19 @@
         <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>12</v>
+        <v>-8</v>
       </c>
       <c r="AI90" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AJ90" t="n">
-        <v>-166.67</v>
+        <v>0</v>
       </c>
       <c r="AK90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
@@ -14763,7 +14757,7 @@
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -14901,28 +14895,28 @@
         <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="AI91" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AJ91" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AK91" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AL91" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -15219,28 +15213,28 @@
         <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="AI93" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="AK93" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="AL93" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -15378,26 +15372,28 @@
         <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AI94" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AJ94" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>0</v>
+      </c>
       <c r="AK94" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AL94" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -15535,28 +15531,28 @@
         <v>0</v>
       </c>
       <c r="AH95" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="AI95" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AJ95" t="n">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="AK95" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AL95" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -15694,13 +15690,13 @@
         <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="AI96" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ96" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="AK96" t="n">
         <v>0</v>
@@ -15715,7 +15711,7 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -15853,28 +15849,28 @@
         <v>0</v>
       </c>
       <c r="AH97" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AI97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ97" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="AK97" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AL97" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -16012,13 +16008,13 @@
         <v>0</v>
       </c>
       <c r="AH98" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="AI98" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AJ98" t="n">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="AK98" t="n">
         <v>0</v>
@@ -16033,7 +16029,7 @@
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -16171,13 +16167,13 @@
         <v>0</v>
       </c>
       <c r="AH99" t="n">
-        <v>8</v>
+        <v>-12</v>
       </c>
       <c r="AI99" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AJ99" t="n">
-        <v>-250</v>
+        <v>0</v>
       </c>
       <c r="AK99" t="n">
         <v>0</v>
@@ -16192,7 +16188,7 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -16330,13 +16326,13 @@
         <v>0</v>
       </c>
       <c r="AH100" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="AI100" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ100" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="AK100" t="n">
         <v>0</v>
@@ -16351,7 +16347,7 @@
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -16489,28 +16485,28 @@
         <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="AI101" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AJ101" t="n">
-        <v>-250</v>
+        <v>0</v>
       </c>
       <c r="AK101" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AL101" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -16648,19 +16644,19 @@
         <v>0</v>
       </c>
       <c r="AH102" t="n">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="AI102" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ102" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="AK102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
@@ -16669,7 +16665,7 @@
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -16807,28 +16803,28 @@
         <v>0</v>
       </c>
       <c r="AH103" t="n">
-        <v>-40</v>
+        <v>-18</v>
       </c>
       <c r="AI103" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AJ103" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AK103" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AL103" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -16966,19 +16962,19 @@
         <v>0</v>
       </c>
       <c r="AH104" t="n">
-        <v>-24</v>
+        <v>-18</v>
       </c>
       <c r="AI104" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ104" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AK104" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AL104" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
@@ -16987,7 +16983,7 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -17125,28 +17121,28 @@
         <v>0</v>
       </c>
       <c r="AH105" t="n">
-        <v>-34</v>
+        <v>-18</v>
       </c>
       <c r="AI105" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AJ105" t="n">
-        <v>47.06</v>
+        <v>0</v>
       </c>
       <c r="AK105" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AL105" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -17284,13 +17280,13 @@
         <v>0</v>
       </c>
       <c r="AH106" t="n">
-        <v>-8</v>
+        <v>-18</v>
       </c>
       <c r="AI106" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AJ106" t="n">
-        <v>-125</v>
+        <v>0</v>
       </c>
       <c r="AK106" t="n">
         <v>0</v>
@@ -17305,7 +17301,7 @@
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -17443,19 +17439,19 @@
         <v>0</v>
       </c>
       <c r="AH107" t="n">
-        <v>-4</v>
+        <v>-20</v>
       </c>
       <c r="AI107" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AJ107" t="n">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="AK107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
@@ -17464,7 +17460,7 @@
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -17602,19 +17598,19 @@
         <v>0</v>
       </c>
       <c r="AH108" t="n">
-        <v>-10</v>
+        <v>-20</v>
       </c>
       <c r="AI108" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AJ108" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AK108" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL108" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM108" t="inlineStr">
         <is>
@@ -17623,7 +17619,7 @@
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -17761,19 +17757,19 @@
         <v>0</v>
       </c>
       <c r="AH109" t="n">
-        <v>14</v>
+        <v>-20</v>
       </c>
       <c r="AI109" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="AJ109" t="n">
-        <v>-242.86</v>
+        <v>0</v>
       </c>
       <c r="AK109" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL109" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
@@ -17782,7 +17778,7 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -18238,13 +18234,13 @@
         <v>0</v>
       </c>
       <c r="AH112" t="n">
-        <v>-16</v>
+        <v>-22</v>
       </c>
       <c r="AI112" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AJ112" t="n">
-        <v>-37.5</v>
+        <v>0</v>
       </c>
       <c r="AK112" t="n">
         <v>0</v>
@@ -18259,7 +18255,7 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -18397,28 +18393,28 @@
         <v>0</v>
       </c>
       <c r="AH113" t="n">
-        <v>-42</v>
+        <v>-22</v>
       </c>
       <c r="AI113" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AJ113" t="n">
-        <v>47.62</v>
+        <v>0</v>
       </c>
       <c r="AK113" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AL113" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -18556,28 +18552,28 @@
         <v>0</v>
       </c>
       <c r="AH114" t="n">
-        <v>-32</v>
+        <v>-22</v>
       </c>
       <c r="AI114" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ114" t="n">
-        <v>31.25</v>
+        <v>0</v>
       </c>
       <c r="AK114" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AL114" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -18715,13 +18711,13 @@
         <v>0</v>
       </c>
       <c r="AH115" t="n">
-        <v>-18</v>
+        <v>-22</v>
       </c>
       <c r="AI115" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ115" t="n">
-        <v>-22.22</v>
+        <v>0</v>
       </c>
       <c r="AK115" t="n">
         <v>0</v>
@@ -18736,7 +18732,7 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -18874,19 +18870,19 @@
         <v>0</v>
       </c>
       <c r="AH116" t="n">
-        <v>-34</v>
+        <v>-24</v>
       </c>
       <c r="AI116" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ116" t="n">
-        <v>29.41</v>
+        <v>0</v>
       </c>
       <c r="AK116" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL116" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
@@ -18895,7 +18891,7 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -19192,19 +19188,19 @@
         <v>0</v>
       </c>
       <c r="AH118" t="n">
-        <v>-12</v>
+        <v>-26</v>
       </c>
       <c r="AI118" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="AJ118" t="n">
-        <v>-116.67</v>
+        <v>0</v>
       </c>
       <c r="AK118" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AL118" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
@@ -19213,7 +19209,7 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -19351,13 +19347,13 @@
         <v>0</v>
       </c>
       <c r="AH119" t="n">
-        <v>-12</v>
+        <v>-26</v>
       </c>
       <c r="AI119" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="AJ119" t="n">
-        <v>-116.67</v>
+        <v>0</v>
       </c>
       <c r="AK119" t="n">
         <v>0</v>
@@ -19372,7 +19368,7 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -19510,19 +19506,19 @@
         <v>0</v>
       </c>
       <c r="AH120" t="n">
-        <v>60</v>
+        <v>-30</v>
       </c>
       <c r="AI120" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="AJ120" t="n">
-        <v>-150</v>
+        <v>0</v>
       </c>
       <c r="AK120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM120" t="inlineStr">
         <is>
@@ -19531,7 +19527,7 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -19669,19 +19665,19 @@
         <v>0</v>
       </c>
       <c r="AH121" t="n">
-        <v>30</v>
+        <v>-30</v>
       </c>
       <c r="AI121" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="AJ121" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AK121" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL121" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM121" t="inlineStr">
         <is>
@@ -19690,7 +19686,7 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -19828,19 +19824,19 @@
         <v>0</v>
       </c>
       <c r="AH122" t="n">
-        <v>30</v>
+        <v>-30</v>
       </c>
       <c r="AI122" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="AJ122" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AK122" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL122" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM122" t="inlineStr">
         <is>
@@ -19849,7 +19845,7 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -19987,13 +19983,13 @@
         <v>0</v>
       </c>
       <c r="AH123" t="n">
-        <v>-26</v>
+        <v>-32</v>
       </c>
       <c r="AI123" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AJ123" t="n">
-        <v>-23.08</v>
+        <v>0</v>
       </c>
       <c r="AK123" t="n">
         <v>0</v>
@@ -20008,7 +20004,7 @@
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -20146,19 +20142,19 @@
         <v>0</v>
       </c>
       <c r="AH124" t="n">
-        <v>10</v>
+        <v>-34</v>
       </c>
       <c r="AI124" t="n">
-        <v>-44</v>
+        <v>0</v>
       </c>
       <c r="AJ124" t="n">
-        <v>-440</v>
+        <v>0</v>
       </c>
       <c r="AK124" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL124" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM124" t="inlineStr">
         <is>
@@ -20167,7 +20163,7 @@
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -20305,19 +20301,19 @@
         <v>0</v>
       </c>
       <c r="AH125" t="n">
-        <v>-4</v>
+        <v>-34</v>
       </c>
       <c r="AI125" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="AJ125" t="n">
-        <v>-750</v>
+        <v>0</v>
       </c>
       <c r="AK125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM125" t="inlineStr">
         <is>
@@ -20326,7 +20322,7 @@
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -20464,19 +20460,19 @@
         <v>0</v>
       </c>
       <c r="AH126" t="n">
-        <v>-6</v>
+        <v>-38</v>
       </c>
       <c r="AI126" t="n">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="AJ126" t="n">
-        <v>-533.33</v>
+        <v>0</v>
       </c>
       <c r="AK126" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL126" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM126" t="inlineStr">
         <is>
@@ -20485,7 +20481,7 @@
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -20623,19 +20619,19 @@
         <v>0</v>
       </c>
       <c r="AH127" t="n">
-        <v>-4</v>
+        <v>-38</v>
       </c>
       <c r="AI127" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="AJ127" t="n">
-        <v>-850</v>
+        <v>0</v>
       </c>
       <c r="AK127" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL127" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
@@ -20644,7 +20640,7 @@
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -20782,19 +20778,19 @@
         <v>0</v>
       </c>
       <c r="AH128" t="n">
-        <v>-10</v>
+        <v>-38</v>
       </c>
       <c r="AI128" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="AJ128" t="n">
-        <v>-280</v>
+        <v>0</v>
       </c>
       <c r="AK128" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL128" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM128" t="inlineStr">
         <is>
@@ -20803,7 +20799,7 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -20941,13 +20937,13 @@
         <v>0</v>
       </c>
       <c r="AH129" t="n">
-        <v>-26</v>
+        <v>-40</v>
       </c>
       <c r="AI129" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="AJ129" t="n">
-        <v>-53.85</v>
+        <v>0</v>
       </c>
       <c r="AK129" t="n">
         <v>0</v>
@@ -20962,7 +20958,7 @@
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -21100,19 +21096,19 @@
         <v>0</v>
       </c>
       <c r="AH130" t="n">
-        <v>-30</v>
+        <v>-40</v>
       </c>
       <c r="AI130" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AJ130" t="n">
-        <v>-33.33</v>
+        <v>0</v>
       </c>
       <c r="AK130" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL130" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM130" t="inlineStr">
         <is>
@@ -21121,7 +21117,7 @@
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -21259,13 +21255,13 @@
         <v>0</v>
       </c>
       <c r="AH131" t="n">
-        <v>4</v>
+        <v>-40</v>
       </c>
       <c r="AI131" t="n">
-        <v>-44</v>
+        <v>0</v>
       </c>
       <c r="AJ131" t="n">
-        <v>-1100</v>
+        <v>0</v>
       </c>
       <c r="AK131" t="n">
         <v>0</v>
@@ -21280,7 +21276,7 @@
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -21418,19 +21414,19 @@
         <v>0</v>
       </c>
       <c r="AH132" t="n">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="AI132" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AJ132" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AK132" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL132" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM132" t="inlineStr">
         <is>
@@ -21439,7 +21435,7 @@
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -21577,13 +21573,13 @@
         <v>0</v>
       </c>
       <c r="AH133" t="n">
-        <v>16</v>
+        <v>-42</v>
       </c>
       <c r="AI133" t="n">
-        <v>-58</v>
+        <v>0</v>
       </c>
       <c r="AJ133" t="n">
-        <v>-362.5</v>
+        <v>0</v>
       </c>
       <c r="AK133" t="n">
         <v>0</v>
@@ -21598,7 +21594,7 @@
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -22213,13 +22209,13 @@
         <v>0</v>
       </c>
       <c r="AH137" t="n">
-        <v>-34</v>
+        <v>-44</v>
       </c>
       <c r="AI137" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AJ137" t="n">
-        <v>-29.41</v>
+        <v>0</v>
       </c>
       <c r="AK137" t="n">
         <v>0</v>
@@ -22234,7 +22230,7 @@
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -22531,13 +22527,13 @@
         <v>0</v>
       </c>
       <c r="AH139" t="n">
-        <v>-44</v>
+        <v>-48</v>
       </c>
       <c r="AI139" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ139" t="n">
-        <v>-9.09</v>
+        <v>0</v>
       </c>
       <c r="AK139" t="n">
         <v>0</v>
@@ -22552,7 +22548,7 @@
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -22690,13 +22686,13 @@
         <v>0</v>
       </c>
       <c r="AH140" t="n">
-        <v>-40</v>
+        <v>-48</v>
       </c>
       <c r="AI140" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AJ140" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AK140" t="n">
         <v>0</v>
@@ -22711,7 +22707,7 @@
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -22849,13 +22845,13 @@
         <v>0</v>
       </c>
       <c r="AH141" t="n">
-        <v>-48</v>
+        <v>-52</v>
       </c>
       <c r="AI141" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ141" t="n">
-        <v>-8.33</v>
+        <v>0</v>
       </c>
       <c r="AK141" t="n">
         <v>0</v>
@@ -22870,7 +22866,7 @@
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -23008,13 +23004,13 @@
         <v>0</v>
       </c>
       <c r="AH142" t="n">
-        <v>-40</v>
+        <v>-52</v>
       </c>
       <c r="AI142" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AJ142" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="AK142" t="n">
         <v>0</v>
@@ -23029,7 +23025,7 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -23167,13 +23163,13 @@
         <v>0</v>
       </c>
       <c r="AH143" t="n">
-        <v>-48</v>
+        <v>-52</v>
       </c>
       <c r="AI143" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ143" t="n">
-        <v>-8.33</v>
+        <v>0</v>
       </c>
       <c r="AK143" t="n">
         <v>0</v>
@@ -23188,7 +23184,7 @@
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -23326,13 +23322,13 @@
         <v>0</v>
       </c>
       <c r="AH144" t="n">
-        <v>-54</v>
+        <v>-58</v>
       </c>
       <c r="AI144" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AJ144" t="n">
-        <v>-7.41</v>
+        <v>0</v>
       </c>
       <c r="AK144" t="n">
         <v>0</v>
@@ -23347,7 +23343,7 @@
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -9391,12 +9391,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8215.TW</t>
+          <t>2731.TW</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>雄獅</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9405,28 +9405,28 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>27.9</v>
+        <v>144</v>
       </c>
       <c r="E57" t="n">
-        <v>28.3</v>
+        <v>143.7</v>
       </c>
       <c r="F57" t="n">
-        <v>26.89</v>
+        <v>142.6</v>
       </c>
       <c r="G57" t="n">
-        <v>26.21</v>
+        <v>143</v>
       </c>
       <c r="H57" t="n">
-        <v>1084525</v>
+        <v>159511</v>
       </c>
       <c r="I57" t="n">
-        <v>6006605</v>
+        <v>177392</v>
       </c>
       <c r="J57" t="n">
-        <v>31</v>
+        <v>145.5</v>
       </c>
       <c r="K57" t="n">
-        <v>24.5</v>
+        <v>139</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -9434,28 +9434,28 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-170939</v>
+        <v>-47448</v>
       </c>
       <c r="N57" t="n">
-        <v>1691936</v>
+        <v>43719</v>
       </c>
       <c r="O57" t="n">
-        <v>1391790</v>
+        <v>70634</v>
       </c>
       <c r="P57" t="n">
-        <v>553717</v>
+        <v>102625</v>
       </c>
       <c r="Q57" t="n">
-        <v>-167928</v>
+        <v>-47409</v>
       </c>
       <c r="R57" t="n">
-        <v>1742472</v>
+        <v>44226</v>
       </c>
       <c r="S57" t="n">
-        <v>1367073</v>
+        <v>63226</v>
       </c>
       <c r="T57" t="n">
-        <v>432685</v>
+        <v>92624</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -9467,19 +9467,19 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>100000</v>
+        <v>1475</v>
       </c>
       <c r="Y57" t="n">
-        <v>-3011</v>
+        <v>-39</v>
       </c>
       <c r="Z57" t="n">
-        <v>-50536</v>
+        <v>-507</v>
       </c>
       <c r="AA57" t="n">
-        <v>24717</v>
+        <v>7408</v>
       </c>
       <c r="AB57" t="n">
-        <v>21032</v>
+        <v>8526</v>
       </c>
       <c r="AC57" t="n">
         <v>14</v>
@@ -9488,10 +9488,10 @@
         <v>14</v>
       </c>
       <c r="AE57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AF57" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -9506,19 +9506,19 @@
         <v>0</v>
       </c>
       <c r="AK57" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AL57" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -9533,29 +9533,29 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人小幅買超</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、接近20日高點、接近20日低點、5日法人小幅買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2731.TW</t>
+          <t>8215.TW</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>雄獅</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -9564,28 +9564,28 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>144</v>
+        <v>27.9</v>
       </c>
       <c r="E58" t="n">
-        <v>143.7</v>
+        <v>28.3</v>
       </c>
       <c r="F58" t="n">
-        <v>142.6</v>
+        <v>26.89</v>
       </c>
       <c r="G58" t="n">
-        <v>143</v>
+        <v>26.21</v>
       </c>
       <c r="H58" t="n">
-        <v>159511</v>
+        <v>1084525</v>
       </c>
       <c r="I58" t="n">
-        <v>177392</v>
+        <v>6006605</v>
       </c>
       <c r="J58" t="n">
-        <v>145.5</v>
+        <v>31</v>
       </c>
       <c r="K58" t="n">
-        <v>139</v>
+        <v>24.5</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -9593,28 +9593,28 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-47448</v>
+        <v>-170939</v>
       </c>
       <c r="N58" t="n">
-        <v>43719</v>
+        <v>1691936</v>
       </c>
       <c r="O58" t="n">
-        <v>70634</v>
+        <v>1391790</v>
       </c>
       <c r="P58" t="n">
-        <v>102625</v>
+        <v>553717</v>
       </c>
       <c r="Q58" t="n">
-        <v>-47409</v>
+        <v>-167928</v>
       </c>
       <c r="R58" t="n">
-        <v>44226</v>
+        <v>1742472</v>
       </c>
       <c r="S58" t="n">
-        <v>63226</v>
+        <v>1367073</v>
       </c>
       <c r="T58" t="n">
-        <v>92624</v>
+        <v>432685</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -9626,19 +9626,19 @@
         <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>1475</v>
+        <v>100000</v>
       </c>
       <c r="Y58" t="n">
-        <v>-39</v>
+        <v>-3011</v>
       </c>
       <c r="Z58" t="n">
-        <v>-507</v>
+        <v>-50536</v>
       </c>
       <c r="AA58" t="n">
-        <v>7408</v>
+        <v>24717</v>
       </c>
       <c r="AB58" t="n">
-        <v>8526</v>
+        <v>21032</v>
       </c>
       <c r="AC58" t="n">
         <v>14</v>
@@ -9647,10 +9647,10 @@
         <v>14</v>
       </c>
       <c r="AE58" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AF58" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -9665,19 +9665,19 @@
         <v>0</v>
       </c>
       <c r="AK58" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AL58" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9692,29 +9692,29 @@
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>5日法人小幅買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、接近20日高點、接近20日低點、5日法人小幅買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2376.TW</t>
+          <t>2451.TW</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9723,28 +9723,28 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>361.5</v>
+        <v>294.5</v>
       </c>
       <c r="E59" t="n">
-        <v>363.4</v>
+        <v>297.3</v>
       </c>
       <c r="F59" t="n">
-        <v>355.8</v>
+        <v>296.05</v>
       </c>
       <c r="G59" t="n">
-        <v>355.98</v>
+        <v>293.9</v>
       </c>
       <c r="H59" t="n">
-        <v>3778913</v>
+        <v>3132797</v>
       </c>
       <c r="I59" t="n">
-        <v>6557210</v>
+        <v>4343497</v>
       </c>
       <c r="J59" t="n">
-        <v>376</v>
+        <v>329.5</v>
       </c>
       <c r="K59" t="n">
-        <v>341</v>
+        <v>271</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -9752,82 +9752,82 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>-29084</v>
+        <v>-22681</v>
       </c>
       <c r="N59" t="n">
-        <v>764919</v>
+        <v>470035</v>
       </c>
       <c r="O59" t="n">
-        <v>2004553</v>
+        <v>1588390</v>
       </c>
       <c r="P59" t="n">
-        <v>570760</v>
+        <v>668253</v>
       </c>
       <c r="Q59" t="n">
-        <v>238536</v>
+        <v>-6903</v>
       </c>
       <c r="R59" t="n">
-        <v>1337507</v>
+        <v>528705</v>
       </c>
       <c r="S59" t="n">
-        <v>2254755</v>
+        <v>1618870</v>
       </c>
       <c r="T59" t="n">
-        <v>-3198845</v>
+        <v>1158443</v>
       </c>
       <c r="U59" t="n">
-        <v>-210000</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>-229446</v>
+        <v>-20200</v>
       </c>
       <c r="W59" t="n">
-        <v>40237</v>
+        <v>-37200</v>
       </c>
       <c r="X59" t="n">
-        <v>3871631</v>
+        <v>-448700</v>
       </c>
       <c r="Y59" t="n">
-        <v>-57620</v>
+        <v>-15778</v>
       </c>
       <c r="Z59" t="n">
-        <v>-343142</v>
+        <v>-38470</v>
       </c>
       <c r="AA59" t="n">
-        <v>-290439</v>
+        <v>6720</v>
       </c>
       <c r="AB59" t="n">
-        <v>-102026</v>
+        <v>-41490</v>
       </c>
       <c r="AC59" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD59" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE59" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="AF59" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AK59" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AL59" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -9851,29 +9851,29 @@
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2612.TW</t>
+          <t>2376.TW</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>中航</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9882,28 +9882,28 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>62.2</v>
+        <v>361.5</v>
       </c>
       <c r="E60" t="n">
-        <v>62.72</v>
+        <v>363.4</v>
       </c>
       <c r="F60" t="n">
-        <v>62.89</v>
+        <v>355.8</v>
       </c>
       <c r="G60" t="n">
-        <v>62.79</v>
+        <v>355.98</v>
       </c>
       <c r="H60" t="n">
-        <v>244146</v>
+        <v>3778913</v>
       </c>
       <c r="I60" t="n">
-        <v>261605</v>
+        <v>6557210</v>
       </c>
       <c r="J60" t="n">
-        <v>66.3</v>
+        <v>376</v>
       </c>
       <c r="K60" t="n">
-        <v>58.7</v>
+        <v>341</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -9911,52 +9911,52 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>30437</v>
+        <v>-29084</v>
       </c>
       <c r="N60" t="n">
-        <v>96015</v>
+        <v>764919</v>
       </c>
       <c r="O60" t="n">
-        <v>193026</v>
+        <v>2004553</v>
       </c>
       <c r="P60" t="n">
-        <v>769291</v>
+        <v>570760</v>
       </c>
       <c r="Q60" t="n">
-        <v>30000</v>
+        <v>238536</v>
       </c>
       <c r="R60" t="n">
-        <v>92573</v>
+        <v>1337507</v>
       </c>
       <c r="S60" t="n">
-        <v>179973</v>
+        <v>2254755</v>
       </c>
       <c r="T60" t="n">
-        <v>801538</v>
+        <v>-3198845</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>-210000</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>-229446</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>40237</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>3871631</v>
       </c>
       <c r="Y60" t="n">
-        <v>437</v>
+        <v>-57620</v>
       </c>
       <c r="Z60" t="n">
-        <v>3442</v>
+        <v>-343142</v>
       </c>
       <c r="AA60" t="n">
-        <v>13053</v>
+        <v>-290439</v>
       </c>
       <c r="AB60" t="n">
-        <v>-32247</v>
+        <v>-102026</v>
       </c>
       <c r="AC60" t="n">
         <v>12</v>
@@ -10015,12 +10015,12 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -10186,12 +10186,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1514.TW</t>
+          <t>2612.TW</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>中航</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -10200,28 +10200,28 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>102</v>
+        <v>62.2</v>
       </c>
       <c r="E62" t="n">
-        <v>102.6</v>
+        <v>62.72</v>
       </c>
       <c r="F62" t="n">
-        <v>101.39</v>
+        <v>62.89</v>
       </c>
       <c r="G62" t="n">
-        <v>101.99</v>
+        <v>62.79</v>
       </c>
       <c r="H62" t="n">
-        <v>1861115</v>
+        <v>244146</v>
       </c>
       <c r="I62" t="n">
-        <v>1116637</v>
+        <v>261605</v>
       </c>
       <c r="J62" t="n">
-        <v>111.5</v>
+        <v>66.3</v>
       </c>
       <c r="K62" t="n">
-        <v>99.40000000000001</v>
+        <v>58.7</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -10229,70 +10229,70 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>-291335</v>
+        <v>30437</v>
       </c>
       <c r="N62" t="n">
-        <v>-173999</v>
+        <v>96015</v>
       </c>
       <c r="O62" t="n">
-        <v>414193</v>
+        <v>193026</v>
       </c>
       <c r="P62" t="n">
-        <v>492036</v>
+        <v>769291</v>
       </c>
       <c r="Q62" t="n">
-        <v>-278414</v>
+        <v>30000</v>
       </c>
       <c r="R62" t="n">
-        <v>-163080</v>
+        <v>92573</v>
       </c>
       <c r="S62" t="n">
-        <v>412259</v>
+        <v>179973</v>
       </c>
       <c r="T62" t="n">
-        <v>554322</v>
+        <v>801538</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>5321</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>-12921</v>
+        <v>437</v>
       </c>
       <c r="Z62" t="n">
-        <v>-14919</v>
+        <v>3442</v>
       </c>
       <c r="AA62" t="n">
-        <v>-2066</v>
+        <v>13053</v>
       </c>
       <c r="AB62" t="n">
-        <v>-67607</v>
+        <v>-32247</v>
       </c>
       <c r="AC62" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD62" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE62" t="n">
-        <v>-15</v>
+        <v>-20</v>
       </c>
       <c r="AF62" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -10301,10 +10301,10 @@
         <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AL62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -10328,29 +10328,29 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>跌破5日線、成交量放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、成交量放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2748.TW</t>
+          <t>1514.TW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>雲品</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -10359,28 +10359,28 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>38.8</v>
+        <v>102</v>
       </c>
       <c r="E63" t="n">
-        <v>38.79</v>
+        <v>102.6</v>
       </c>
       <c r="F63" t="n">
-        <v>38.79</v>
+        <v>101.39</v>
       </c>
       <c r="G63" t="n">
-        <v>38.88</v>
+        <v>101.99</v>
       </c>
       <c r="H63" t="n">
-        <v>61491</v>
+        <v>1861115</v>
       </c>
       <c r="I63" t="n">
-        <v>32787</v>
+        <v>1116637</v>
       </c>
       <c r="J63" t="n">
-        <v>39.9</v>
+        <v>111.5</v>
       </c>
       <c r="K63" t="n">
-        <v>38.35</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -10388,52 +10388,52 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>-4000</v>
+        <v>-291335</v>
       </c>
       <c r="N63" t="n">
-        <v>-1000</v>
+        <v>-173999</v>
       </c>
       <c r="O63" t="n">
-        <v>5000</v>
+        <v>414193</v>
       </c>
       <c r="P63" t="n">
-        <v>-27000</v>
+        <v>492036</v>
       </c>
       <c r="Q63" t="n">
-        <v>-4000</v>
+        <v>-278414</v>
       </c>
       <c r="R63" t="n">
-        <v>-1000</v>
+        <v>-163080</v>
       </c>
       <c r="S63" t="n">
-        <v>1000</v>
+        <v>412259</v>
       </c>
       <c r="T63" t="n">
-        <v>-34000</v>
+        <v>554322</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>5321</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>-12921</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>-14919</v>
       </c>
       <c r="AA63" t="n">
-        <v>4000</v>
+        <v>-2066</v>
       </c>
       <c r="AB63" t="n">
-        <v>7000</v>
+        <v>-67607</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
@@ -10442,10 +10442,10 @@
         <v>10</v>
       </c>
       <c r="AE63" t="n">
-        <v>25</v>
+        <v>-15</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -10460,19 +10460,19 @@
         <v>0</v>
       </c>
       <c r="AK63" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="AL63" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能偏強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -10487,29 +10487,29 @@
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大、接近20日低點</t>
+          <t>跌破5日線、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、成交量放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4966.TWO</t>
+          <t>2748.TW</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>雲品</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -10518,28 +10518,28 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>572</v>
+        <v>38.8</v>
       </c>
       <c r="E64" t="n">
-        <v>570.6</v>
+        <v>38.79</v>
       </c>
       <c r="F64" t="n">
-        <v>553.8</v>
+        <v>38.79</v>
       </c>
       <c r="G64" t="n">
-        <v>559.45</v>
+        <v>38.88</v>
       </c>
       <c r="H64" t="n">
-        <v>452000</v>
+        <v>61491</v>
       </c>
       <c r="I64" t="n">
-        <v>790000</v>
+        <v>32787</v>
       </c>
       <c r="J64" t="n">
-        <v>599</v>
+        <v>39.9</v>
       </c>
       <c r="K64" t="n">
-        <v>521</v>
+        <v>38.35</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -10547,28 +10547,28 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>-27000</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>-34000</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -10589,19 +10589,19 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="AC64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE64" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AF64" t="n">
         <v>0</v>
@@ -10610,7 +10610,7 @@
         <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -10619,10 +10619,10 @@
         <v>0</v>
       </c>
       <c r="AK64" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL64" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能偏強</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
@@ -10656,19 +10656,19 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、成交量放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -10677,28 +10677,28 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>253</v>
+        <v>241.5</v>
       </c>
       <c r="E65" t="n">
-        <v>250.3</v>
+        <v>239.5</v>
       </c>
       <c r="F65" t="n">
-        <v>246.7</v>
+        <v>235.7</v>
       </c>
       <c r="G65" t="n">
-        <v>255.43</v>
+        <v>243.75</v>
       </c>
       <c r="H65" t="n">
-        <v>768000</v>
+        <v>1314000</v>
       </c>
       <c r="I65" t="n">
-        <v>1085600</v>
+        <v>2945000</v>
       </c>
       <c r="J65" t="n">
-        <v>280.5</v>
+        <v>288</v>
       </c>
       <c r="K65" t="n">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -10778,19 +10778,19 @@
         <v>0</v>
       </c>
       <c r="AK65" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL65" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10822,12 +10822,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>5439.TWO</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -10836,28 +10836,28 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1305</v>
+        <v>253</v>
       </c>
       <c r="E66" t="n">
-        <v>1303</v>
+        <v>250.3</v>
       </c>
       <c r="F66" t="n">
-        <v>1293</v>
+        <v>246.7</v>
       </c>
       <c r="G66" t="n">
-        <v>1342.25</v>
+        <v>255.43</v>
       </c>
       <c r="H66" t="n">
-        <v>979000</v>
+        <v>768000</v>
       </c>
       <c r="I66" t="n">
-        <v>1296400</v>
+        <v>1085600</v>
       </c>
       <c r="J66" t="n">
-        <v>1535</v>
+        <v>280.5</v>
       </c>
       <c r="K66" t="n">
-        <v>1240</v>
+        <v>237</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -10937,19 +10937,19 @@
         <v>0</v>
       </c>
       <c r="AK66" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL66" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10981,12 +10981,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>4966.TWO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -10995,28 +10995,28 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>241.5</v>
+        <v>572</v>
       </c>
       <c r="E67" t="n">
-        <v>239.5</v>
+        <v>570.6</v>
       </c>
       <c r="F67" t="n">
-        <v>235.7</v>
+        <v>553.8</v>
       </c>
       <c r="G67" t="n">
-        <v>243.75</v>
+        <v>559.45</v>
       </c>
       <c r="H67" t="n">
-        <v>1314000</v>
+        <v>452000</v>
       </c>
       <c r="I67" t="n">
-        <v>2945000</v>
+        <v>790000</v>
       </c>
       <c r="J67" t="n">
-        <v>288</v>
+        <v>599</v>
       </c>
       <c r="K67" t="n">
-        <v>223</v>
+        <v>521</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="AK67" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AL67" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -11140,12 +11140,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2886.TW</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -11154,28 +11154,28 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>49.6</v>
+        <v>1305</v>
       </c>
       <c r="E68" t="n">
-        <v>50.46</v>
+        <v>1303</v>
       </c>
       <c r="F68" t="n">
-        <v>51.11</v>
+        <v>1293</v>
       </c>
       <c r="G68" t="n">
-        <v>50.31</v>
+        <v>1342.25</v>
       </c>
       <c r="H68" t="n">
-        <v>8333068</v>
+        <v>979000</v>
       </c>
       <c r="I68" t="n">
-        <v>22028266</v>
+        <v>1296400</v>
       </c>
       <c r="J68" t="n">
-        <v>52.9</v>
+        <v>1535</v>
       </c>
       <c r="K68" t="n">
-        <v>46.55</v>
+        <v>1240</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -11183,91 +11183,91 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>-19404</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>10319759</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>12355311</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>38581493</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>-1019173</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>16358436</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>21731254</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>24565731</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>359000</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>-7698067</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>-12156040</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>9910905</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>640769</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1659390</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2780097</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>4104857</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AD68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE68" t="n">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK68" t="n">
         <v>30</v>
       </c>
-      <c r="AG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>5</v>
-      </c>
       <c r="AL68" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -11282,17 +11282,17 @@
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -11776,12 +11776,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2451.TW</t>
+          <t>2886.TW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -11790,28 +11790,28 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>284.5</v>
+        <v>49.6</v>
       </c>
       <c r="E72" t="n">
-        <v>284.6</v>
+        <v>50.46</v>
       </c>
       <c r="F72" t="n">
-        <v>280.6</v>
+        <v>51.11</v>
       </c>
       <c r="G72" t="n">
-        <v>285.1</v>
+        <v>50.31</v>
       </c>
       <c r="H72" t="n">
-        <v>1295375</v>
+        <v>8333068</v>
       </c>
       <c r="I72" t="n">
-        <v>1645440</v>
+        <v>22028266</v>
       </c>
       <c r="J72" t="n">
-        <v>300.5</v>
+        <v>52.9</v>
       </c>
       <c r="K72" t="n">
-        <v>270</v>
+        <v>46.55</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -11819,52 +11819,52 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>-22681</v>
+        <v>-19404</v>
       </c>
       <c r="N72" t="n">
-        <v>470035</v>
+        <v>10319759</v>
       </c>
       <c r="O72" t="n">
-        <v>1588390</v>
+        <v>12355311</v>
       </c>
       <c r="P72" t="n">
-        <v>668253</v>
+        <v>38581493</v>
       </c>
       <c r="Q72" t="n">
-        <v>-6903</v>
+        <v>-1019173</v>
       </c>
       <c r="R72" t="n">
-        <v>528705</v>
+        <v>16358436</v>
       </c>
       <c r="S72" t="n">
-        <v>1618870</v>
+        <v>21731254</v>
       </c>
       <c r="T72" t="n">
-        <v>1158443</v>
+        <v>24565731</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>359000</v>
       </c>
       <c r="V72" t="n">
-        <v>-20200</v>
+        <v>-7698067</v>
       </c>
       <c r="W72" t="n">
-        <v>-37200</v>
+        <v>-12156040</v>
       </c>
       <c r="X72" t="n">
-        <v>-448700</v>
+        <v>9910905</v>
       </c>
       <c r="Y72" t="n">
-        <v>-15778</v>
+        <v>640769</v>
       </c>
       <c r="Z72" t="n">
-        <v>-38470</v>
+        <v>1659390</v>
       </c>
       <c r="AA72" t="n">
-        <v>6720</v>
+        <v>2780097</v>
       </c>
       <c r="AB72" t="n">
-        <v>-41490</v>
+        <v>4104857</v>
       </c>
       <c r="AC72" t="n">
         <v>4</v>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -752,19 +752,19 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AI2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>105.88</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>DT趨勢已轉強、離5MA偏遠、均線多頭排列、接近20日高位、分數升溫過快</t>
+          <t>DT趨勢已轉強、離5MA偏遠、均線多頭排列、接近20日高位</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -8861,19 +8861,19 @@
         <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AI53" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>-27.27</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AL53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -9391,12 +9391,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2731.TW</t>
+          <t>8215.TW</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>雄獅</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9405,28 +9405,28 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>144</v>
+        <v>27.9</v>
       </c>
       <c r="E57" t="n">
-        <v>143.7</v>
+        <v>28.3</v>
       </c>
       <c r="F57" t="n">
-        <v>142.6</v>
+        <v>26.89</v>
       </c>
       <c r="G57" t="n">
-        <v>143</v>
+        <v>26.21</v>
       </c>
       <c r="H57" t="n">
-        <v>159511</v>
+        <v>1084525</v>
       </c>
       <c r="I57" t="n">
-        <v>177392</v>
+        <v>6006605</v>
       </c>
       <c r="J57" t="n">
-        <v>145.5</v>
+        <v>31</v>
       </c>
       <c r="K57" t="n">
-        <v>139</v>
+        <v>24.5</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -9434,28 +9434,28 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-47448</v>
+        <v>-170939</v>
       </c>
       <c r="N57" t="n">
-        <v>43719</v>
+        <v>1691936</v>
       </c>
       <c r="O57" t="n">
-        <v>70634</v>
+        <v>1391790</v>
       </c>
       <c r="P57" t="n">
-        <v>102625</v>
+        <v>553717</v>
       </c>
       <c r="Q57" t="n">
-        <v>-47409</v>
+        <v>-167928</v>
       </c>
       <c r="R57" t="n">
-        <v>44226</v>
+        <v>1742472</v>
       </c>
       <c r="S57" t="n">
-        <v>63226</v>
+        <v>1367073</v>
       </c>
       <c r="T57" t="n">
-        <v>92624</v>
+        <v>432685</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -9467,19 +9467,19 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1475</v>
+        <v>100000</v>
       </c>
       <c r="Y57" t="n">
-        <v>-39</v>
+        <v>-3011</v>
       </c>
       <c r="Z57" t="n">
-        <v>-507</v>
+        <v>-50536</v>
       </c>
       <c r="AA57" t="n">
-        <v>7408</v>
+        <v>24717</v>
       </c>
       <c r="AB57" t="n">
-        <v>8526</v>
+        <v>21032</v>
       </c>
       <c r="AC57" t="n">
         <v>14</v>
@@ -9488,10 +9488,10 @@
         <v>14</v>
       </c>
       <c r="AE57" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AF57" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -9506,19 +9506,19 @@
         <v>0</v>
       </c>
       <c r="AK57" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AL57" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -9533,29 +9533,29 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>5日法人小幅買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、接近20日高點、接近20日低點、5日法人小幅買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8215.TW</t>
+          <t>2731.TW</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>雄獅</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -9564,28 +9564,28 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>27.9</v>
+        <v>144</v>
       </c>
       <c r="E58" t="n">
-        <v>28.3</v>
+        <v>143.7</v>
       </c>
       <c r="F58" t="n">
-        <v>26.89</v>
+        <v>142.6</v>
       </c>
       <c r="G58" t="n">
-        <v>26.21</v>
+        <v>143</v>
       </c>
       <c r="H58" t="n">
-        <v>1084525</v>
+        <v>159511</v>
       </c>
       <c r="I58" t="n">
-        <v>6006605</v>
+        <v>177392</v>
       </c>
       <c r="J58" t="n">
-        <v>31</v>
+        <v>145.5</v>
       </c>
       <c r="K58" t="n">
-        <v>24.5</v>
+        <v>139</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -9593,28 +9593,28 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-170939</v>
+        <v>-47448</v>
       </c>
       <c r="N58" t="n">
-        <v>1691936</v>
+        <v>43719</v>
       </c>
       <c r="O58" t="n">
-        <v>1391790</v>
+        <v>70634</v>
       </c>
       <c r="P58" t="n">
-        <v>553717</v>
+        <v>102625</v>
       </c>
       <c r="Q58" t="n">
-        <v>-167928</v>
+        <v>-47409</v>
       </c>
       <c r="R58" t="n">
-        <v>1742472</v>
+        <v>44226</v>
       </c>
       <c r="S58" t="n">
-        <v>1367073</v>
+        <v>63226</v>
       </c>
       <c r="T58" t="n">
-        <v>432685</v>
+        <v>92624</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -9626,19 +9626,19 @@
         <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>100000</v>
+        <v>1475</v>
       </c>
       <c r="Y58" t="n">
-        <v>-3011</v>
+        <v>-39</v>
       </c>
       <c r="Z58" t="n">
-        <v>-50536</v>
+        <v>-507</v>
       </c>
       <c r="AA58" t="n">
-        <v>24717</v>
+        <v>7408</v>
       </c>
       <c r="AB58" t="n">
-        <v>21032</v>
+        <v>8526</v>
       </c>
       <c r="AC58" t="n">
         <v>14</v>
@@ -9647,10 +9647,10 @@
         <v>14</v>
       </c>
       <c r="AE58" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AF58" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -9665,19 +9665,19 @@
         <v>0</v>
       </c>
       <c r="AK58" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AL58" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9692,29 +9692,29 @@
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人小幅買超</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、接近20日高點、接近20日低點、5日法人小幅買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2451.TW</t>
+          <t>2376.TW</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9723,28 +9723,28 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>294.5</v>
+        <v>361.5</v>
       </c>
       <c r="E59" t="n">
-        <v>297.3</v>
+        <v>363.4</v>
       </c>
       <c r="F59" t="n">
-        <v>296.05</v>
+        <v>355.8</v>
       </c>
       <c r="G59" t="n">
-        <v>293.9</v>
+        <v>355.98</v>
       </c>
       <c r="H59" t="n">
-        <v>3132797</v>
+        <v>3778913</v>
       </c>
       <c r="I59" t="n">
-        <v>4343497</v>
+        <v>6557210</v>
       </c>
       <c r="J59" t="n">
-        <v>329.5</v>
+        <v>376</v>
       </c>
       <c r="K59" t="n">
-        <v>271</v>
+        <v>341</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -9752,82 +9752,82 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>-22681</v>
+        <v>-29084</v>
       </c>
       <c r="N59" t="n">
-        <v>470035</v>
+        <v>764919</v>
       </c>
       <c r="O59" t="n">
-        <v>1588390</v>
+        <v>2004553</v>
       </c>
       <c r="P59" t="n">
-        <v>668253</v>
+        <v>570760</v>
       </c>
       <c r="Q59" t="n">
-        <v>-6903</v>
+        <v>238536</v>
       </c>
       <c r="R59" t="n">
-        <v>528705</v>
+        <v>1337507</v>
       </c>
       <c r="S59" t="n">
-        <v>1618870</v>
+        <v>2254755</v>
       </c>
       <c r="T59" t="n">
-        <v>1158443</v>
+        <v>-3198845</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>-210000</v>
       </c>
       <c r="V59" t="n">
-        <v>-20200</v>
+        <v>-229446</v>
       </c>
       <c r="W59" t="n">
-        <v>-37200</v>
+        <v>40237</v>
       </c>
       <c r="X59" t="n">
-        <v>-448700</v>
+        <v>3871631</v>
       </c>
       <c r="Y59" t="n">
-        <v>-15778</v>
+        <v>-57620</v>
       </c>
       <c r="Z59" t="n">
-        <v>-38470</v>
+        <v>-343142</v>
       </c>
       <c r="AA59" t="n">
-        <v>6720</v>
+        <v>-290439</v>
       </c>
       <c r="AB59" t="n">
-        <v>-41490</v>
+        <v>-102026</v>
       </c>
       <c r="AC59" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD59" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE59" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK59" t="n">
         <v>5</v>
       </c>
-      <c r="AF59" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>250</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>20</v>
-      </c>
       <c r="AL59" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -9851,29 +9851,29 @@
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2376.TW</t>
+          <t>2612.TW</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>中航</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9882,28 +9882,28 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>361.5</v>
+        <v>62.2</v>
       </c>
       <c r="E60" t="n">
-        <v>363.4</v>
+        <v>62.72</v>
       </c>
       <c r="F60" t="n">
-        <v>355.8</v>
+        <v>62.89</v>
       </c>
       <c r="G60" t="n">
-        <v>355.98</v>
+        <v>62.79</v>
       </c>
       <c r="H60" t="n">
-        <v>3778913</v>
+        <v>244146</v>
       </c>
       <c r="I60" t="n">
-        <v>6557210</v>
+        <v>261605</v>
       </c>
       <c r="J60" t="n">
-        <v>376</v>
+        <v>66.3</v>
       </c>
       <c r="K60" t="n">
-        <v>341</v>
+        <v>58.7</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -9911,52 +9911,52 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-29084</v>
+        <v>30437</v>
       </c>
       <c r="N60" t="n">
-        <v>764919</v>
+        <v>96015</v>
       </c>
       <c r="O60" t="n">
-        <v>2004553</v>
+        <v>193026</v>
       </c>
       <c r="P60" t="n">
-        <v>570760</v>
+        <v>769291</v>
       </c>
       <c r="Q60" t="n">
-        <v>238536</v>
+        <v>30000</v>
       </c>
       <c r="R60" t="n">
-        <v>1337507</v>
+        <v>92573</v>
       </c>
       <c r="S60" t="n">
-        <v>2254755</v>
+        <v>179973</v>
       </c>
       <c r="T60" t="n">
-        <v>-3198845</v>
+        <v>801538</v>
       </c>
       <c r="U60" t="n">
-        <v>-210000</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>-229446</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>40237</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>3871631</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>-57620</v>
+        <v>437</v>
       </c>
       <c r="Z60" t="n">
-        <v>-343142</v>
+        <v>3442</v>
       </c>
       <c r="AA60" t="n">
-        <v>-290439</v>
+        <v>13053</v>
       </c>
       <c r="AB60" t="n">
-        <v>-102026</v>
+        <v>-32247</v>
       </c>
       <c r="AC60" t="n">
         <v>12</v>
@@ -10015,12 +10015,12 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -10186,12 +10186,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2612.TW</t>
+          <t>1514.TW</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>中航</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -10200,28 +10200,28 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>62.2</v>
+        <v>102</v>
       </c>
       <c r="E62" t="n">
-        <v>62.72</v>
+        <v>102.6</v>
       </c>
       <c r="F62" t="n">
-        <v>62.89</v>
+        <v>101.39</v>
       </c>
       <c r="G62" t="n">
-        <v>62.79</v>
+        <v>101.99</v>
       </c>
       <c r="H62" t="n">
-        <v>244146</v>
+        <v>1861115</v>
       </c>
       <c r="I62" t="n">
-        <v>261605</v>
+        <v>1116637</v>
       </c>
       <c r="J62" t="n">
-        <v>66.3</v>
+        <v>111.5</v>
       </c>
       <c r="K62" t="n">
-        <v>58.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -10229,70 +10229,70 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>30437</v>
+        <v>-291335</v>
       </c>
       <c r="N62" t="n">
-        <v>96015</v>
+        <v>-173999</v>
       </c>
       <c r="O62" t="n">
-        <v>193026</v>
+        <v>414193</v>
       </c>
       <c r="P62" t="n">
-        <v>769291</v>
+        <v>492036</v>
       </c>
       <c r="Q62" t="n">
-        <v>30000</v>
+        <v>-278414</v>
       </c>
       <c r="R62" t="n">
-        <v>92573</v>
+        <v>-163080</v>
       </c>
       <c r="S62" t="n">
-        <v>179973</v>
+        <v>412259</v>
       </c>
       <c r="T62" t="n">
-        <v>801538</v>
+        <v>554322</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>5321</v>
       </c>
       <c r="Y62" t="n">
-        <v>437</v>
+        <v>-12921</v>
       </c>
       <c r="Z62" t="n">
-        <v>3442</v>
+        <v>-14919</v>
       </c>
       <c r="AA62" t="n">
-        <v>13053</v>
+        <v>-2066</v>
       </c>
       <c r="AB62" t="n">
-        <v>-32247</v>
+        <v>-67607</v>
       </c>
       <c r="AC62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE62" t="n">
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="AF62" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -10301,10 +10301,10 @@
         <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AL62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -10328,29 +10328,29 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、成交量放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1514.TW</t>
+          <t>2748.TW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>雲品</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -10359,28 +10359,28 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>102</v>
+        <v>38.8</v>
       </c>
       <c r="E63" t="n">
-        <v>102.6</v>
+        <v>38.79</v>
       </c>
       <c r="F63" t="n">
-        <v>101.39</v>
+        <v>38.79</v>
       </c>
       <c r="G63" t="n">
-        <v>101.99</v>
+        <v>38.88</v>
       </c>
       <c r="H63" t="n">
-        <v>1861115</v>
+        <v>61491</v>
       </c>
       <c r="I63" t="n">
-        <v>1116637</v>
+        <v>32787</v>
       </c>
       <c r="J63" t="n">
-        <v>111.5</v>
+        <v>39.9</v>
       </c>
       <c r="K63" t="n">
-        <v>99.40000000000001</v>
+        <v>38.35</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -10388,52 +10388,52 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>-291335</v>
+        <v>-4000</v>
       </c>
       <c r="N63" t="n">
-        <v>-173999</v>
+        <v>-1000</v>
       </c>
       <c r="O63" t="n">
-        <v>414193</v>
+        <v>5000</v>
       </c>
       <c r="P63" t="n">
-        <v>492036</v>
+        <v>-27000</v>
       </c>
       <c r="Q63" t="n">
-        <v>-278414</v>
+        <v>-4000</v>
       </c>
       <c r="R63" t="n">
-        <v>-163080</v>
+        <v>-1000</v>
       </c>
       <c r="S63" t="n">
-        <v>412259</v>
+        <v>1000</v>
       </c>
       <c r="T63" t="n">
-        <v>554322</v>
+        <v>-34000</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
         <v>4000</v>
       </c>
-      <c r="W63" t="n">
-        <v>4000</v>
-      </c>
-      <c r="X63" t="n">
-        <v>5321</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>-12921</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>-14919</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>-2066</v>
-      </c>
       <c r="AB63" t="n">
-        <v>-67607</v>
+        <v>7000</v>
       </c>
       <c r="AC63" t="n">
         <v>10</v>
@@ -10442,10 +10442,10 @@
         <v>10</v>
       </c>
       <c r="AE63" t="n">
-        <v>-15</v>
+        <v>25</v>
       </c>
       <c r="AF63" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -10460,19 +10460,19 @@
         <v>0</v>
       </c>
       <c r="AK63" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="AL63" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能偏強</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -10487,29 +10487,29 @@
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>跌破5日線、成交量放大、接近20日低點</t>
+          <t>站上5日線、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、成交量放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、成交量放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2748.TW</t>
+          <t>4966.TWO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>雲品</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -10518,28 +10518,28 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>38.8</v>
+        <v>572</v>
       </c>
       <c r="E64" t="n">
-        <v>38.79</v>
+        <v>570.6</v>
       </c>
       <c r="F64" t="n">
-        <v>38.79</v>
+        <v>553.8</v>
       </c>
       <c r="G64" t="n">
-        <v>38.88</v>
+        <v>559.45</v>
       </c>
       <c r="H64" t="n">
-        <v>61491</v>
+        <v>452000</v>
       </c>
       <c r="I64" t="n">
-        <v>32787</v>
+        <v>790000</v>
       </c>
       <c r="J64" t="n">
-        <v>39.9</v>
+        <v>599</v>
       </c>
       <c r="K64" t="n">
-        <v>38.35</v>
+        <v>521</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -10547,28 +10547,28 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>-27000</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>-34000</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -10589,19 +10589,19 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE64" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AF64" t="n">
         <v>0</v>
@@ -10610,7 +10610,7 @@
         <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -10619,10 +10619,10 @@
         <v>0</v>
       </c>
       <c r="AK64" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL64" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能偏強</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大、接近20日低點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
@@ -10656,19 +10656,19 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>5439.TWO</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -10677,28 +10677,28 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>241.5</v>
+        <v>253</v>
       </c>
       <c r="E65" t="n">
-        <v>239.5</v>
+        <v>250.3</v>
       </c>
       <c r="F65" t="n">
-        <v>235.7</v>
+        <v>246.7</v>
       </c>
       <c r="G65" t="n">
-        <v>243.75</v>
+        <v>255.43</v>
       </c>
       <c r="H65" t="n">
-        <v>1314000</v>
+        <v>768000</v>
       </c>
       <c r="I65" t="n">
-        <v>2945000</v>
+        <v>1085600</v>
       </c>
       <c r="J65" t="n">
-        <v>288</v>
+        <v>280.5</v>
       </c>
       <c r="K65" t="n">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -10778,19 +10778,19 @@
         <v>0</v>
       </c>
       <c r="AK65" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL65" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10822,12 +10822,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -10836,28 +10836,28 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>253</v>
+        <v>1305</v>
       </c>
       <c r="E66" t="n">
-        <v>250.3</v>
+        <v>1303</v>
       </c>
       <c r="F66" t="n">
-        <v>246.7</v>
+        <v>1293</v>
       </c>
       <c r="G66" t="n">
-        <v>255.43</v>
+        <v>1342.25</v>
       </c>
       <c r="H66" t="n">
-        <v>768000</v>
+        <v>979000</v>
       </c>
       <c r="I66" t="n">
-        <v>1085600</v>
+        <v>1296400</v>
       </c>
       <c r="J66" t="n">
-        <v>280.5</v>
+        <v>1535</v>
       </c>
       <c r="K66" t="n">
-        <v>237</v>
+        <v>1240</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -10937,19 +10937,19 @@
         <v>0</v>
       </c>
       <c r="AK66" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL66" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10981,12 +10981,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4966.TWO</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -10995,28 +10995,28 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>572</v>
+        <v>241.5</v>
       </c>
       <c r="E67" t="n">
-        <v>570.6</v>
+        <v>239.5</v>
       </c>
       <c r="F67" t="n">
-        <v>553.8</v>
+        <v>235.7</v>
       </c>
       <c r="G67" t="n">
-        <v>559.45</v>
+        <v>243.75</v>
       </c>
       <c r="H67" t="n">
-        <v>452000</v>
+        <v>1314000</v>
       </c>
       <c r="I67" t="n">
-        <v>790000</v>
+        <v>2945000</v>
       </c>
       <c r="J67" t="n">
-        <v>599</v>
+        <v>288</v>
       </c>
       <c r="K67" t="n">
-        <v>521</v>
+        <v>223</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="AK67" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AL67" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -11140,12 +11140,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>2886.TW</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -11154,28 +11154,28 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1305</v>
+        <v>49.6</v>
       </c>
       <c r="E68" t="n">
-        <v>1303</v>
+        <v>50.46</v>
       </c>
       <c r="F68" t="n">
-        <v>1293</v>
+        <v>51.11</v>
       </c>
       <c r="G68" t="n">
-        <v>1342.25</v>
+        <v>50.31</v>
       </c>
       <c r="H68" t="n">
-        <v>979000</v>
+        <v>8333068</v>
       </c>
       <c r="I68" t="n">
-        <v>1296400</v>
+        <v>22028266</v>
       </c>
       <c r="J68" t="n">
-        <v>1535</v>
+        <v>52.9</v>
       </c>
       <c r="K68" t="n">
-        <v>1240</v>
+        <v>46.55</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -11183,70 +11183,70 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>-19404</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>10319759</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>12355311</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>38581493</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>-1019173</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>16358436</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>21731254</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>24565731</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>359000</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>-7698067</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>-12156040</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>9910905</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>640769</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1659390</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2780097</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>4104857</v>
       </c>
       <c r="AC68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AD68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE68" t="n">
-        <v>20</v>
+        <v>-20</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -11255,19 +11255,19 @@
         <v>0</v>
       </c>
       <c r="AK68" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AL68" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -11282,17 +11282,17 @@
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -11776,12 +11776,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2886.TW</t>
+          <t>2451.TW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -11790,28 +11790,28 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>49.6</v>
+        <v>284.5</v>
       </c>
       <c r="E72" t="n">
-        <v>50.46</v>
+        <v>284.6</v>
       </c>
       <c r="F72" t="n">
-        <v>51.11</v>
+        <v>280.6</v>
       </c>
       <c r="G72" t="n">
-        <v>50.31</v>
+        <v>285.1</v>
       </c>
       <c r="H72" t="n">
-        <v>8333068</v>
+        <v>1295375</v>
       </c>
       <c r="I72" t="n">
-        <v>22028266</v>
+        <v>1645440</v>
       </c>
       <c r="J72" t="n">
-        <v>52.9</v>
+        <v>300.5</v>
       </c>
       <c r="K72" t="n">
-        <v>46.55</v>
+        <v>270</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -11819,52 +11819,52 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>-19404</v>
+        <v>-22681</v>
       </c>
       <c r="N72" t="n">
-        <v>10319759</v>
+        <v>470035</v>
       </c>
       <c r="O72" t="n">
-        <v>12355311</v>
+        <v>1588390</v>
       </c>
       <c r="P72" t="n">
-        <v>38581493</v>
+        <v>668253</v>
       </c>
       <c r="Q72" t="n">
-        <v>-1019173</v>
+        <v>-6903</v>
       </c>
       <c r="R72" t="n">
-        <v>16358436</v>
+        <v>528705</v>
       </c>
       <c r="S72" t="n">
-        <v>21731254</v>
+        <v>1618870</v>
       </c>
       <c r="T72" t="n">
-        <v>24565731</v>
+        <v>1158443</v>
       </c>
       <c r="U72" t="n">
-        <v>359000</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>-7698067</v>
+        <v>-20200</v>
       </c>
       <c r="W72" t="n">
-        <v>-12156040</v>
+        <v>-37200</v>
       </c>
       <c r="X72" t="n">
-        <v>9910905</v>
+        <v>-448700</v>
       </c>
       <c r="Y72" t="n">
-        <v>640769</v>
+        <v>-15778</v>
       </c>
       <c r="Z72" t="n">
-        <v>1659390</v>
+        <v>-38470</v>
       </c>
       <c r="AA72" t="n">
-        <v>2780097</v>
+        <v>6720</v>
       </c>
       <c r="AB72" t="n">
-        <v>4104857</v>
+        <v>-41490</v>
       </c>
       <c r="AC72" t="n">
         <v>4</v>
@@ -11882,19 +11882,19 @@
         <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>-71.43000000000001</v>
       </c>
       <c r="AK72" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL72" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS144"/>
+  <dimension ref="A1:AV144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,6 +642,21 @@
           <t>AI評語</t>
         </is>
       </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>資料日期</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>籌碼資料日期</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>前次資料日期</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -752,19 +767,19 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="AL2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
@@ -773,7 +788,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>DT趨勢已轉強、離5MA偏遠、均線多頭排列、接近20日高位</t>
+          <t>DT趨勢已轉強、離5MA偏遠、均線多頭排列、接近20日高位、分數升溫過快</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -799,6 +814,21 @@
       <c r="AS2" t="inlineStr">
         <is>
           <t>強勢偏多：站上5日線、多頭排列、黃金交叉、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -911,28 +941,28 @@
         <v>25</v>
       </c>
       <c r="AH3" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>38.64</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>DT趨勢已轉強、離5MA偏遠、均線多頭排列、量能溫和放大</t>
+          <t>DT趨勢已轉強、離5MA偏遠、均線多頭排列、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -958,6 +988,21 @@
       <c r="AS3" t="inlineStr">
         <is>
           <t>偏多觀察：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1070,19 +1115,19 @@
         <v>25</v>
       </c>
       <c r="AH4" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>154.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
@@ -1091,7 +1136,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>DT趨勢已轉強、貼近5MA、均線多頭排列、爆量後不追價</t>
+          <t>DT趨勢已轉強、貼近5MA、均線多頭排列、爆量後不追價、分數升溫過快</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1117,6 +1162,21 @@
       <c r="AS4" t="inlineStr">
         <is>
           <t>偏多觀察：站上5日線、多頭排列、爆量、接近20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1229,28 +1289,28 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>86.67</v>
       </c>
       <c r="AK5" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AL5" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列</t>
+          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列、分數升溫過快</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1276,6 +1336,21 @@
       <c r="AS5" t="inlineStr">
         <is>
           <t>偏多觀察：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1437,6 +1512,21 @@
           <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1547,28 +1637,28 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>23.81</v>
       </c>
       <c r="AK7" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AL7" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、均線多頭排列</t>
+          <t>DT進入觀察區、貼近5MA、均線多頭排列、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1594,6 +1684,21 @@
       <c r="AS7" t="inlineStr">
         <is>
           <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1706,28 +1811,28 @@
         <v>25</v>
       </c>
       <c r="AH8" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-16.39</v>
       </c>
       <c r="AK8" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能偏強</t>
+          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1753,6 +1858,21 @@
       <c r="AS8" t="inlineStr">
         <is>
           <t>偏多觀察：站上5日線、多頭排列、爆量、帶量突破20日高點、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1914,6 +2034,21 @@
           <t>偏多觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2024,19 +2159,19 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
@@ -2045,7 +2180,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>DT進入觀察區、離5MA偏遠、均線多頭排列</t>
+          <t>DT進入觀察區、離5MA偏遠、均線多頭排列、分數剛升溫</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2071,6 +2206,21 @@
       <c r="AS10" t="inlineStr">
         <is>
           <t>偏多觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -2183,28 +2333,28 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>31.58</v>
       </c>
       <c r="AK11" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>可優先研究</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2230,6 +2380,21 @@
       <c r="AS11" t="inlineStr">
         <is>
           <t>偏多觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -2391,6 +2556,21 @@
           <t>偏多觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2550,6 +2730,21 @@
           <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2709,6 +2904,21 @@
           <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2819,28 +3029,28 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="AK15" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AL15" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣</t>
+          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2866,6 +3076,21 @@
       <c r="AS15" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -2978,28 +3203,28 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AK16" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AL16" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣</t>
+          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -3025,6 +3250,21 @@
       <c r="AS16" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -3137,19 +3377,19 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>266.67</v>
       </c>
       <c r="AK17" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AL17" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
@@ -3158,7 +3398,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3184,6 +3424,21 @@
       <c r="AS17" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -3296,19 +3551,19 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AL18" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
@@ -3317,7 +3572,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>DT進入觀察區、離5MA偏遠、位於20日區間中上緣</t>
+          <t>DT進入觀察區、離5MA偏遠、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3343,6 +3598,21 @@
       <c r="AS18" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、黃金交叉、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -3504,6 +3774,21 @@
           <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3663,6 +3948,21 @@
           <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3773,28 +4073,28 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>-28.57</v>
       </c>
       <c r="AK21" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="AL21" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3820,6 +4120,21 @@
       <c r="AS21" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -3932,19 +4247,19 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>-9.52</v>
       </c>
       <c r="AK22" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AL22" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
@@ -3953,7 +4268,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3979,6 +4294,21 @@
       <c r="AS22" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4091,28 +4421,28 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="AK23" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AL23" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數升溫過快</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -4138,6 +4468,21 @@
       <c r="AS23" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、多頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4250,28 +4595,28 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>-14.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4297,6 +4642,21 @@
       <c r="AS24" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4409,28 +4769,28 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="AK25" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AL25" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -4456,6 +4816,21 @@
       <c r="AS25" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4617,6 +4992,21 @@
           <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4727,28 +5117,28 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AK27" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4774,6 +5164,21 @@
       <c r="AS27" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4886,19 +5291,19 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>-29.17</v>
       </c>
       <c r="AK28" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AL28" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
@@ -4907,7 +5312,7 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4933,6 +5338,21 @@
       <c r="AS28" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -5045,28 +5465,28 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>54.55</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AL29" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA</t>
+          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -5092,6 +5512,21 @@
       <c r="AS29" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、量能未放大、接近20日高點、法人連續偏買、5日法人買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -5204,19 +5639,19 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AK30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
@@ -5225,7 +5660,7 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5251,6 +5686,21 @@
       <c r="AS30" t="inlineStr">
         <is>
           <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -5363,28 +5813,28 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>-23.81</v>
       </c>
       <c r="AK31" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AL31" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -5410,6 +5860,21 @@
       <c r="AS31" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -5522,19 +5987,19 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>-27.27</v>
       </c>
       <c r="AK32" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AL32" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
@@ -5543,7 +6008,7 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、接近20日高位</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、接近20日高位、分數轉弱</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5569,6 +6034,21 @@
       <c r="AS32" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -5681,28 +6161,28 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="AK33" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL33" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA</t>
+          <t>DT尚未轉強、貼近5MA、分數升溫過快</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5728,6 +6208,21 @@
       <c r="AS33" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -5840,19 +6335,19 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>-21.05</v>
       </c>
       <c r="AK34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
@@ -5861,7 +6356,7 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5887,6 +6382,21 @@
       <c r="AS34" t="inlineStr">
         <is>
           <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -5999,28 +6509,28 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="AK35" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AL35" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -6046,6 +6556,21 @@
       <c r="AS35" t="inlineStr">
         <is>
           <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -6207,6 +6732,21 @@
           <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6317,19 +6857,19 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>-29.41</v>
       </c>
       <c r="AK37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
@@ -6338,7 +6878,7 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -6364,6 +6904,21 @@
       <c r="AS37" t="inlineStr">
         <is>
           <t>整理觀察：跌破5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -6476,19 +7031,19 @@
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>-14.29</v>
       </c>
       <c r="AK38" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
@@ -6497,7 +7052,7 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -6523,6 +7078,21 @@
       <c r="AS38" t="inlineStr">
         <is>
           <t>整理觀察：跌破5日線、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -6635,19 +7205,19 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AK39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
@@ -6656,7 +7226,7 @@
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6682,6 +7252,21 @@
       <c r="AS39" t="inlineStr">
         <is>
           <t>整理觀察：跌破5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -6794,19 +7379,19 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="AK40" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AL40" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
@@ -6815,7 +7400,7 @@
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>DT尚未轉強、離5MA偏遠、均線多頭排列</t>
+          <t>DT尚未轉強、離5MA偏遠、均線多頭排列、分數剛升溫</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6841,6 +7426,21 @@
       <c r="AS40" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、多頭排列、量能溫和放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -6953,19 +7553,19 @@
         <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>-56</v>
       </c>
       <c r="AK41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
@@ -6974,7 +7574,7 @@
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -7000,6 +7600,21 @@
       <c r="AS41" t="inlineStr">
         <is>
           <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -7112,19 +7727,19 @@
         <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>-15.38</v>
       </c>
       <c r="AK42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
@@ -7133,7 +7748,7 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -7159,6 +7774,21 @@
       <c r="AS42" t="inlineStr">
         <is>
           <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -7271,13 +7901,13 @@
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="AK43" t="n">
         <v>0</v>
@@ -7292,7 +7922,7 @@
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -7318,6 +7948,21 @@
       <c r="AS43" t="inlineStr">
         <is>
           <t>整理觀察：跌破5日線、黃金交叉、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -7430,19 +8075,19 @@
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="AK44" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AL44" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
@@ -7451,7 +8096,7 @@
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、分數剛升溫</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -7477,6 +8122,21 @@
       <c r="AS44" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、多頭排列、量能溫和放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -7589,19 +8249,19 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="AK45" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AL45" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
@@ -7610,7 +8270,7 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -7636,6 +8296,21 @@
       <c r="AS45" t="inlineStr">
         <is>
           <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -7748,19 +8423,19 @@
         <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>-8.33</v>
       </c>
       <c r="AK46" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AL46" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
@@ -7769,7 +8444,7 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7795,6 +8470,21 @@
       <c r="AS46" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、量能未放大、接近20日高點、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -7907,19 +8597,19 @@
         <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>-42.11</v>
       </c>
       <c r="AK47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
@@ -7928,7 +8618,7 @@
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7954,6 +8644,21 @@
       <c r="AS47" t="inlineStr">
         <is>
           <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -8066,28 +8771,28 @@
         <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>57.14</v>
       </c>
       <c r="AK48" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="AL48" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>可優先研究</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -8113,6 +8818,21 @@
       <c r="AS48" t="inlineStr">
         <is>
           <t>整理觀察：站上5日線、多頭排列、量能溫和放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -8225,19 +8945,19 @@
         <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>-52.38</v>
       </c>
       <c r="AK49" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
@@ -8246,7 +8966,7 @@
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -8272,6 +8992,21 @@
       <c r="AS49" t="inlineStr">
         <is>
           <t>整理觀察：跌破5日線、黃金交叉、量能溫和放大、接近20日高點、接近20日低點、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -8433,6 +9168,21 @@
           <t>風險偏高：站上5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
+      <c r="AT50" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8543,28 +9293,28 @@
         <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AK51" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AL51" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8590,6 +9340,21 @@
       <c r="AS51" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -8702,19 +9467,19 @@
         <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>-30.77</v>
       </c>
       <c r="AK52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
@@ -8723,7 +9488,7 @@
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8749,6 +9514,21 @@
       <c r="AS52" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -8861,19 +9641,19 @@
         <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>-66.67</v>
       </c>
       <c r="AK53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
@@ -8882,7 +9662,7 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -8908,6 +9688,21 @@
       <c r="AS53" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -9020,19 +9815,19 @@
         <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>16</v>
+        <v>-14</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>214.29</v>
       </c>
       <c r="AK54" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AL54" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
@@ -9041,7 +9836,7 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、分數升溫過快</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -9067,6 +9862,21 @@
       <c r="AS54" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -9179,19 +9989,19 @@
         <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
@@ -9200,7 +10010,7 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -9226,6 +10036,21 @@
       <c r="AS55" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -9338,19 +10163,19 @@
         <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>-53.33</v>
       </c>
       <c r="AK56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
@@ -9359,7 +10184,7 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -9385,6 +10210,21 @@
       <c r="AS56" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -9497,19 +10337,19 @@
         <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>-58.82</v>
       </c>
       <c r="AK57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
@@ -9518,7 +10358,7 @@
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -9544,6 +10384,21 @@
       <c r="AS57" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -9656,19 +10511,19 @@
         <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>-65</v>
       </c>
       <c r="AK58" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AL58" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
@@ -9677,7 +10532,7 @@
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9703,6 +10558,21 @@
       <c r="AS58" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、量能未放大、接近20日高點、接近20日低點、5日法人小幅買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -9815,19 +10685,19 @@
         <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="AK59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
@@ -9836,7 +10706,7 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -9862,6 +10732,21 @@
       <c r="AS59" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -10023,6 +10908,21 @@
           <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
+      <c r="AT60" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -10133,28 +11033,28 @@
         <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="AK61" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AL61" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA</t>
+          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -10180,6 +11080,21 @@
       <c r="AS61" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -10292,19 +11207,19 @@
         <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>-82.14</v>
       </c>
       <c r="AK62" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL62" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
@@ -10313,7 +11228,7 @@
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -10339,6 +11254,21 @@
       <c r="AS62" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、成交量放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -10451,19 +11381,19 @@
         <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>10</v>
+        <v>-22</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>145.45</v>
       </c>
       <c r="AK63" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="AL63" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
@@ -10472,7 +11402,7 @@
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能偏強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能偏強、分數升溫過快</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -10498,6 +11428,21 @@
       <c r="AS63" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、成交量放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -10610,28 +11555,28 @@
         <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AK64" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AL64" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10657,6 +11602,21 @@
       <c r="AS64" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -10769,19 +11729,19 @@
         <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>-33.33</v>
       </c>
       <c r="AK65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AL65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
@@ -10790,7 +11750,7 @@
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA</t>
+          <t>DT尚未轉強、貼近5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10816,6 +11776,21 @@
       <c r="AS65" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -10928,28 +11903,28 @@
         <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AI66" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0</v>
+        <v>-42.86</v>
       </c>
       <c r="AK66" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AL66" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10975,6 +11950,21 @@
       <c r="AS66" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11136,6 +12126,21 @@
           <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
+      <c r="AT67" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -11246,19 +12251,19 @@
         <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AI68" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="AK68" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL68" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
@@ -11267,7 +12272,7 @@
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -11293,6 +12298,21 @@
       <c r="AS68" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11454,6 +12474,21 @@
           <t>風險偏高：站上5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
+      <c r="AT69" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -11613,6 +12648,21 @@
           <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
+      <c r="AT70" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -11723,19 +12773,19 @@
         <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>4</v>
+        <v>-14</v>
       </c>
       <c r="AI71" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0</v>
+        <v>128.57</v>
       </c>
       <c r="AK71" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL71" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
@@ -11744,7 +12794,7 @@
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11770,6 +12820,21 @@
       <c r="AS71" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11882,13 +12947,13 @@
         <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="AI72" t="n">
-        <v>-10</v>
+        <v>-28</v>
       </c>
       <c r="AJ72" t="n">
-        <v>-71.43000000000001</v>
+        <v>-87.5</v>
       </c>
       <c r="AK72" t="n">
         <v>0</v>
@@ -11929,6 +12994,21 @@
       <c r="AS72" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12041,19 +13121,19 @@
         <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="AI73" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0</v>
+        <v>-84.62</v>
       </c>
       <c r="AK73" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL73" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
@@ -12062,7 +13142,7 @@
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -12088,6 +13168,21 @@
       <c r="AS73" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能溫和放大、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12200,19 +13295,19 @@
         <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="AI74" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0</v>
+        <v>-85.70999999999999</v>
       </c>
       <c r="AK74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
@@ -12221,7 +13316,7 @@
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -12247,6 +13342,21 @@
       <c r="AS74" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12359,19 +13469,19 @@
         <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="AI75" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0</v>
+        <v>-81.81999999999999</v>
       </c>
       <c r="AK75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
@@ -12380,7 +13490,7 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -12406,6 +13516,21 @@
       <c r="AS75" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12518,19 +13643,19 @@
         <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AI76" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="AK76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
@@ -12539,7 +13664,7 @@
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -12565,6 +13690,21 @@
       <c r="AS76" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、黃金交叉、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12677,19 +13817,19 @@
         <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AI77" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0</v>
+        <v>-85.70999999999999</v>
       </c>
       <c r="AK77" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL77" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
@@ -12698,7 +13838,7 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -12724,6 +13864,21 @@
       <c r="AS77" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、黃金交叉、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12836,28 +13991,28 @@
         <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>2</v>
+        <v>-34</v>
       </c>
       <c r="AI78" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0</v>
+        <v>105.88</v>
       </c>
       <c r="AK78" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AL78" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數升溫過快</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -12883,6 +14038,21 @@
       <c r="AS78" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12995,17 +14165,19 @@
         <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AI79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr"/>
+        <v>-58</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>-100</v>
+      </c>
       <c r="AK79" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL79" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
@@ -13014,7 +14186,7 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -13040,6 +14212,21 @@
       <c r="AS79" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -13152,17 +14339,19 @@
         <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>100</v>
+      </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
@@ -13171,7 +14360,7 @@
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -13197,6 +14386,21 @@
       <c r="AS80" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -13309,12 +14513,14 @@
         <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr"/>
+        <v>-12</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>-100</v>
+      </c>
       <c r="AK81" t="n">
         <v>0</v>
       </c>
@@ -13328,7 +14534,7 @@
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -13354,6 +14560,21 @@
       <c r="AS81" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -13466,12 +14687,14 @@
         <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr"/>
+        <v>-22</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>-100</v>
+      </c>
       <c r="AK82" t="n">
         <v>0</v>
       </c>
@@ -13485,7 +14708,7 @@
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -13511,6 +14734,21 @@
       <c r="AS82" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏買。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -13623,14 +14861,12 @@
         <v>0</v>
       </c>
       <c r="AH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="n">
         <v>-4</v>
       </c>
-      <c r="AI83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ83" t="n">
-        <v>0</v>
-      </c>
+      <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="n">
         <v>0</v>
       </c>
@@ -13644,7 +14880,7 @@
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -13670,6 +14906,21 @@
       <c r="AS83" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -13782,13 +15033,13 @@
         <v>0</v>
       </c>
       <c r="AH84" t="n">
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="AI84" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0</v>
+        <v>-166.67</v>
       </c>
       <c r="AK84" t="n">
         <v>0</v>
@@ -13803,7 +15054,7 @@
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -13829,6 +15080,21 @@
       <c r="AS84" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -13941,28 +15207,28 @@
         <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>-4</v>
+        <v>-26</v>
       </c>
       <c r="AI85" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0</v>
+        <v>84.62</v>
       </c>
       <c r="AK85" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AL85" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -13988,6 +15254,21 @@
       <c r="AS85" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、黃金交叉、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -14100,19 +15381,19 @@
         <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>-4</v>
+        <v>38</v>
       </c>
       <c r="AI86" t="n">
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0</v>
+        <v>-110.53</v>
       </c>
       <c r="AK86" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AL86" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
@@ -14121,7 +15402,7 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -14147,6 +15428,21 @@
       <c r="AS86" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -14259,19 +15555,19 @@
         <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>-6</v>
+        <v>22</v>
       </c>
       <c r="AI87" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0</v>
+        <v>-127.27</v>
       </c>
       <c r="AK87" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL87" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
@@ -14280,7 +15576,7 @@
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -14306,6 +15602,21 @@
       <c r="AS87" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -14418,28 +15729,28 @@
         <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>-8</v>
+        <v>-20</v>
       </c>
       <c r="AI88" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK88" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AL88" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -14465,6 +15776,21 @@
       <c r="AS88" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -14577,13 +15903,13 @@
         <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="AI89" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="AK89" t="n">
         <v>0</v>
@@ -14598,7 +15924,7 @@
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -14624,6 +15950,21 @@
       <c r="AS89" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -14736,19 +16077,19 @@
         <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>-8</v>
+        <v>12</v>
       </c>
       <c r="AI90" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0</v>
+        <v>-166.67</v>
       </c>
       <c r="AK90" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL90" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
@@ -14757,7 +16098,7 @@
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -14783,6 +16124,21 @@
       <c r="AS90" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -14895,28 +16251,28 @@
         <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>-8</v>
+        <v>8</v>
       </c>
       <c r="AI91" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AJ91" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AK91" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AL91" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -14942,6 +16298,21 @@
       <c r="AS91" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、量能未放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -15103,6 +16474,21 @@
           <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
+      <c r="AT92" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -15213,28 +16599,28 @@
         <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="AI93" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="AK93" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AL93" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -15260,6 +16646,21 @@
       <c r="AS93" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -15372,28 +16773,26 @@
         <v>0</v>
       </c>
       <c r="AH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="n">
         <v>-10</v>
       </c>
-      <c r="AI94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ94" t="n">
-        <v>0</v>
-      </c>
+      <c r="AJ94" t="inlineStr"/>
       <c r="AK94" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AL94" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -15419,6 +16818,21 @@
       <c r="AS94" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -15531,28 +16945,28 @@
         <v>0</v>
       </c>
       <c r="AH95" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="AI95" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="AK95" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AL95" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -15578,6 +16992,21 @@
       <c r="AS95" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -15690,13 +17119,13 @@
         <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="AI96" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ96" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="AK96" t="n">
         <v>0</v>
@@ -15711,7 +17140,7 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -15737,6 +17166,21 @@
       <c r="AS96" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -15849,28 +17293,28 @@
         <v>0</v>
       </c>
       <c r="AH97" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="AI97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ97" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="AK97" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AL97" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -15896,6 +17340,21 @@
       <c r="AS97" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、黃金交叉、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16008,13 +17467,13 @@
         <v>0</v>
       </c>
       <c r="AH98" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="AI98" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="AK98" t="n">
         <v>0</v>
@@ -16029,7 +17488,7 @@
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -16055,6 +17514,21 @@
       <c r="AS98" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16167,13 +17641,13 @@
         <v>0</v>
       </c>
       <c r="AH99" t="n">
-        <v>-12</v>
+        <v>8</v>
       </c>
       <c r="AI99" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ99" t="n">
-        <v>0</v>
+        <v>-250</v>
       </c>
       <c r="AK99" t="n">
         <v>0</v>
@@ -16188,7 +17662,7 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -16214,6 +17688,21 @@
       <c r="AS99" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人賣超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16326,13 +17815,13 @@
         <v>0</v>
       </c>
       <c r="AH100" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="AI100" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ100" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="AK100" t="n">
         <v>0</v>
@@ -16347,7 +17836,7 @@
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -16373,6 +17862,21 @@
       <c r="AS100" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16485,28 +17989,28 @@
         <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="AI101" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ101" t="n">
-        <v>0</v>
+        <v>-250</v>
       </c>
       <c r="AK101" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AL101" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -16532,6 +18036,21 @@
       <c r="AS101" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16644,19 +18163,19 @@
         <v>0</v>
       </c>
       <c r="AH102" t="n">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="AI102" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="AK102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
@@ -16665,7 +18184,7 @@
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -16691,6 +18210,21 @@
       <c r="AS102" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16803,28 +18337,28 @@
         <v>0</v>
       </c>
       <c r="AH103" t="n">
-        <v>-18</v>
+        <v>-40</v>
       </c>
       <c r="AI103" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AJ103" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK103" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AL103" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -16850,6 +18384,21 @@
       <c r="AS103" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16962,19 +18511,19 @@
         <v>0</v>
       </c>
       <c r="AH104" t="n">
-        <v>-18</v>
+        <v>-24</v>
       </c>
       <c r="AI104" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK104" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AL104" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
@@ -16983,7 +18532,7 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -17009,6 +18558,21 @@
       <c r="AS104" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17121,28 +18685,28 @@
         <v>0</v>
       </c>
       <c r="AH105" t="n">
-        <v>-18</v>
+        <v>-34</v>
       </c>
       <c r="AI105" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0</v>
+        <v>47.06</v>
       </c>
       <c r="AK105" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AL105" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -17168,6 +18732,21 @@
       <c r="AS105" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17280,13 +18859,13 @@
         <v>0</v>
       </c>
       <c r="AH106" t="n">
-        <v>-18</v>
+        <v>-8</v>
       </c>
       <c r="AI106" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0</v>
+        <v>-125</v>
       </c>
       <c r="AK106" t="n">
         <v>0</v>
@@ -17301,7 +18880,7 @@
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -17327,6 +18906,21 @@
       <c r="AS106" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、死亡交叉、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17439,19 +19033,19 @@
         <v>0</v>
       </c>
       <c r="AH107" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="AI107" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AK107" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL107" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
@@ -17460,7 +19054,7 @@
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -17486,6 +19080,21 @@
       <c r="AS107" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17598,19 +19207,19 @@
         <v>0</v>
       </c>
       <c r="AH108" t="n">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="AI108" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AK108" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL108" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM108" t="inlineStr">
         <is>
@@ -17619,7 +19228,7 @@
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -17645,6 +19254,21 @@
       <c r="AS108" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17757,19 +19381,19 @@
         <v>0</v>
       </c>
       <c r="AH109" t="n">
-        <v>-20</v>
+        <v>14</v>
       </c>
       <c r="AI109" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0</v>
+        <v>-242.86</v>
       </c>
       <c r="AK109" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL109" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
@@ -17778,7 +19402,7 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -17804,6 +19428,21 @@
       <c r="AS109" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17965,6 +19604,21 @@
           <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
+      <c r="AT110" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -18124,6 +19778,21 @@
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
+      <c r="AT111" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -18234,13 +19903,13 @@
         <v>0</v>
       </c>
       <c r="AH112" t="n">
-        <v>-22</v>
+        <v>-16</v>
       </c>
       <c r="AI112" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0</v>
+        <v>-37.5</v>
       </c>
       <c r="AK112" t="n">
         <v>0</v>
@@ -18255,7 +19924,7 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -18281,6 +19950,21 @@
       <c r="AS112" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18393,28 +20077,28 @@
         <v>0</v>
       </c>
       <c r="AH113" t="n">
-        <v>-22</v>
+        <v>-42</v>
       </c>
       <c r="AI113" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0</v>
+        <v>47.62</v>
       </c>
       <c r="AK113" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AL113" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA</t>
+          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -18440,6 +20124,21 @@
       <c r="AS113" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18552,28 +20251,28 @@
         <v>0</v>
       </c>
       <c r="AH114" t="n">
-        <v>-22</v>
+        <v>-32</v>
       </c>
       <c r="AI114" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ114" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="AK114" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AL114" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -18599,6 +20298,21 @@
       <c r="AS114" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18711,13 +20425,13 @@
         <v>0</v>
       </c>
       <c r="AH115" t="n">
-        <v>-22</v>
+        <v>-18</v>
       </c>
       <c r="AI115" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ115" t="n">
-        <v>0</v>
+        <v>-22.22</v>
       </c>
       <c r="AK115" t="n">
         <v>0</v>
@@ -18732,7 +20446,7 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -18758,6 +20472,21 @@
       <c r="AS115" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18870,19 +20599,19 @@
         <v>0</v>
       </c>
       <c r="AH116" t="n">
-        <v>-24</v>
+        <v>-34</v>
       </c>
       <c r="AI116" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ116" t="n">
-        <v>0</v>
+        <v>29.41</v>
       </c>
       <c r="AK116" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL116" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
@@ -18891,7 +20620,7 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -18917,6 +20646,21 @@
       <c r="AS116" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -19078,6 +20822,21 @@
           <t>風險偏高：站上5日線、空頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
+      <c r="AT117" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -19188,19 +20947,19 @@
         <v>0</v>
       </c>
       <c r="AH118" t="n">
-        <v>-26</v>
+        <v>-12</v>
       </c>
       <c r="AI118" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AJ118" t="n">
-        <v>0</v>
+        <v>-116.67</v>
       </c>
       <c r="AK118" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AL118" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
@@ -19209,7 +20968,7 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -19235,6 +20994,21 @@
       <c r="AS118" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -19347,13 +21121,13 @@
         <v>0</v>
       </c>
       <c r="AH119" t="n">
-        <v>-26</v>
+        <v>-12</v>
       </c>
       <c r="AI119" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AJ119" t="n">
-        <v>0</v>
+        <v>-116.67</v>
       </c>
       <c r="AK119" t="n">
         <v>0</v>
@@ -19368,7 +21142,7 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -19394,6 +21168,21 @@
       <c r="AS119" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -19506,19 +21295,19 @@
         <v>0</v>
       </c>
       <c r="AH120" t="n">
-        <v>-30</v>
+        <v>60</v>
       </c>
       <c r="AI120" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="AJ120" t="n">
-        <v>0</v>
+        <v>-150</v>
       </c>
       <c r="AK120" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL120" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM120" t="inlineStr">
         <is>
@@ -19527,7 +21316,7 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -19553,6 +21342,21 @@
       <c r="AS120" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -19665,19 +21469,19 @@
         <v>0</v>
       </c>
       <c r="AH121" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
       <c r="AI121" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="AJ121" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AK121" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL121" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM121" t="inlineStr">
         <is>
@@ -19686,7 +21490,7 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -19712,6 +21516,21 @@
       <c r="AS121" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -19824,19 +21643,19 @@
         <v>0</v>
       </c>
       <c r="AH122" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
       <c r="AI122" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="AJ122" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AK122" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL122" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM122" t="inlineStr">
         <is>
@@ -19845,7 +21664,7 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -19871,6 +21690,21 @@
       <c r="AS122" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -19983,13 +21817,13 @@
         <v>0</v>
       </c>
       <c r="AH123" t="n">
-        <v>-32</v>
+        <v>-26</v>
       </c>
       <c r="AI123" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AJ123" t="n">
-        <v>0</v>
+        <v>-23.08</v>
       </c>
       <c r="AK123" t="n">
         <v>0</v>
@@ -20004,7 +21838,7 @@
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -20030,6 +21864,21 @@
       <c r="AS123" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -20142,19 +21991,19 @@
         <v>0</v>
       </c>
       <c r="AH124" t="n">
-        <v>-34</v>
+        <v>10</v>
       </c>
       <c r="AI124" t="n">
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="AJ124" t="n">
-        <v>0</v>
+        <v>-440</v>
       </c>
       <c r="AK124" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL124" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AM124" t="inlineStr">
         <is>
@@ -20163,7 +22012,7 @@
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -20189,6 +22038,21 @@
       <c r="AS124" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -20301,19 +22165,19 @@
         <v>0</v>
       </c>
       <c r="AH125" t="n">
-        <v>-34</v>
+        <v>-4</v>
       </c>
       <c r="AI125" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AJ125" t="n">
-        <v>0</v>
+        <v>-750</v>
       </c>
       <c r="AK125" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL125" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM125" t="inlineStr">
         <is>
@@ -20322,7 +22186,7 @@
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -20348,6 +22212,21 @@
       <c r="AS125" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -20460,19 +22339,19 @@
         <v>0</v>
       </c>
       <c r="AH126" t="n">
-        <v>-38</v>
+        <v>-6</v>
       </c>
       <c r="AI126" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="AJ126" t="n">
-        <v>0</v>
+        <v>-533.33</v>
       </c>
       <c r="AK126" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL126" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM126" t="inlineStr">
         <is>
@@ -20481,7 +22360,7 @@
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -20507,6 +22386,21 @@
       <c r="AS126" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -20619,19 +22513,19 @@
         <v>0</v>
       </c>
       <c r="AH127" t="n">
-        <v>-38</v>
+        <v>-4</v>
       </c>
       <c r="AI127" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="AJ127" t="n">
-        <v>0</v>
+        <v>-850</v>
       </c>
       <c r="AK127" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL127" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
@@ -20640,7 +22534,7 @@
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -20666,6 +22560,21 @@
       <c r="AS127" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -20778,19 +22687,19 @@
         <v>0</v>
       </c>
       <c r="AH128" t="n">
-        <v>-38</v>
+        <v>-10</v>
       </c>
       <c r="AI128" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="AJ128" t="n">
-        <v>0</v>
+        <v>-280</v>
       </c>
       <c r="AK128" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL128" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM128" t="inlineStr">
         <is>
@@ -20799,7 +22708,7 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -20825,6 +22734,21 @@
       <c r="AS128" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -20937,13 +22861,13 @@
         <v>0</v>
       </c>
       <c r="AH129" t="n">
-        <v>-40</v>
+        <v>-26</v>
       </c>
       <c r="AI129" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AJ129" t="n">
-        <v>0</v>
+        <v>-53.85</v>
       </c>
       <c r="AK129" t="n">
         <v>0</v>
@@ -20958,7 +22882,7 @@
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -20984,6 +22908,21 @@
       <c r="AS129" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT129" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -21096,19 +23035,19 @@
         <v>0</v>
       </c>
       <c r="AH130" t="n">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="AI130" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ130" t="n">
-        <v>0</v>
+        <v>-33.33</v>
       </c>
       <c r="AK130" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL130" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM130" t="inlineStr">
         <is>
@@ -21117,7 +23056,7 @@
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -21143,6 +23082,21 @@
       <c r="AS130" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT130" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -21255,13 +23209,13 @@
         <v>0</v>
       </c>
       <c r="AH131" t="n">
-        <v>-40</v>
+        <v>4</v>
       </c>
       <c r="AI131" t="n">
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="AJ131" t="n">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="AK131" t="n">
         <v>0</v>
@@ -21276,7 +23230,7 @@
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -21302,6 +23256,21 @@
       <c r="AS131" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT131" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -21414,19 +23383,19 @@
         <v>0</v>
       </c>
       <c r="AH132" t="n">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="AI132" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ132" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AK132" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL132" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM132" t="inlineStr">
         <is>
@@ -21435,7 +23404,7 @@
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -21461,6 +23430,21 @@
       <c r="AS132" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -21573,13 +23557,13 @@
         <v>0</v>
       </c>
       <c r="AH133" t="n">
-        <v>-42</v>
+        <v>16</v>
       </c>
       <c r="AI133" t="n">
-        <v>0</v>
+        <v>-58</v>
       </c>
       <c r="AJ133" t="n">
-        <v>0</v>
+        <v>-362.5</v>
       </c>
       <c r="AK133" t="n">
         <v>0</v>
@@ -21594,7 +23578,7 @@
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -21620,6 +23604,21 @@
       <c r="AS133" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT133" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -21781,6 +23780,21 @@
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
+      <c r="AT134" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21940,6 +23954,21 @@
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
+      <c r="AT135" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -22099,6 +24128,21 @@
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
+      <c r="AT136" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -22209,13 +24253,13 @@
         <v>0</v>
       </c>
       <c r="AH137" t="n">
-        <v>-44</v>
+        <v>-34</v>
       </c>
       <c r="AI137" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AJ137" t="n">
-        <v>0</v>
+        <v>-29.41</v>
       </c>
       <c r="AK137" t="n">
         <v>0</v>
@@ -22230,7 +24274,7 @@
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -22256,6 +24300,21 @@
       <c r="AS137" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -22417,6 +24476,21 @@
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
+      <c r="AT138" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -22527,13 +24601,13 @@
         <v>0</v>
       </c>
       <c r="AH139" t="n">
-        <v>-48</v>
+        <v>-44</v>
       </c>
       <c r="AI139" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ139" t="n">
-        <v>0</v>
+        <v>-9.09</v>
       </c>
       <c r="AK139" t="n">
         <v>0</v>
@@ -22548,7 +24622,7 @@
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -22574,6 +24648,21 @@
       <c r="AS139" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT139" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -22686,13 +24775,13 @@
         <v>0</v>
       </c>
       <c r="AH140" t="n">
-        <v>-48</v>
+        <v>-40</v>
       </c>
       <c r="AI140" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AJ140" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AK140" t="n">
         <v>0</v>
@@ -22707,7 +24796,7 @@
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -22733,6 +24822,21 @@
       <c r="AS140" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT140" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -22845,13 +24949,13 @@
         <v>0</v>
       </c>
       <c r="AH141" t="n">
-        <v>-52</v>
+        <v>-48</v>
       </c>
       <c r="AI141" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ141" t="n">
-        <v>0</v>
+        <v>-8.33</v>
       </c>
       <c r="AK141" t="n">
         <v>0</v>
@@ -22866,7 +24970,7 @@
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -22892,6 +24996,21 @@
       <c r="AS141" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT141" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -23004,13 +25123,13 @@
         <v>0</v>
       </c>
       <c r="AH142" t="n">
-        <v>-52</v>
+        <v>-40</v>
       </c>
       <c r="AI142" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AJ142" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AK142" t="n">
         <v>0</v>
@@ -23025,7 +25144,7 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -23051,6 +25170,21 @@
       <c r="AS142" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -23163,13 +25297,13 @@
         <v>0</v>
       </c>
       <c r="AH143" t="n">
-        <v>-52</v>
+        <v>-48</v>
       </c>
       <c r="AI143" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ143" t="n">
-        <v>0</v>
+        <v>-8.33</v>
       </c>
       <c r="AK143" t="n">
         <v>0</v>
@@ -23184,7 +25318,7 @@
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -23210,6 +25344,21 @@
       <c r="AS143" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -23322,13 +25471,13 @@
         <v>0</v>
       </c>
       <c r="AH144" t="n">
-        <v>-58</v>
+        <v>-54</v>
       </c>
       <c r="AI144" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AJ144" t="n">
-        <v>0</v>
+        <v>-7.41</v>
       </c>
       <c r="AK144" t="n">
         <v>0</v>
@@ -23343,7 +25492,7 @@
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -23369,6 +25518,21 @@
       <c r="AS144" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -16125,17 +16125,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0056.TW</t>
+          <t>2498.TW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -16149,28 +16149,28 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>56.85</v>
+        <v>43.7</v>
       </c>
       <c r="G91" t="n">
-        <v>56.72</v>
+        <v>42.61</v>
       </c>
       <c r="H91" t="n">
-        <v>56.63</v>
+        <v>41.28</v>
       </c>
       <c r="I91" t="n">
-        <v>56</v>
+        <v>40.93</v>
       </c>
       <c r="J91" t="n">
-        <v>42084968</v>
+        <v>23409453</v>
       </c>
       <c r="K91" t="n">
-        <v>32310102</v>
+        <v>15506141</v>
       </c>
       <c r="L91" t="n">
-        <v>57.85</v>
+        <v>46.85</v>
       </c>
       <c r="M91" t="n">
-        <v>54.5</v>
+        <v>39.2</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -16178,52 +16178,52 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>-33467525</v>
+        <v>-1240185</v>
       </c>
       <c r="P91" t="n">
-        <v>-72909338</v>
+        <v>-1845842</v>
       </c>
       <c r="Q91" t="n">
-        <v>-104367817</v>
+        <v>-6286070</v>
       </c>
       <c r="R91" t="n">
-        <v>-114331141</v>
+        <v>-8188859</v>
       </c>
       <c r="S91" t="n">
-        <v>-8960687</v>
+        <v>-1164408</v>
       </c>
       <c r="T91" t="n">
-        <v>-10344516</v>
+        <v>-2282129</v>
       </c>
       <c r="U91" t="n">
-        <v>-21060235</v>
+        <v>-7045029</v>
       </c>
       <c r="V91" t="n">
-        <v>-25089681</v>
+        <v>-8851563</v>
       </c>
       <c r="W91" t="n">
-        <v>180000</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>442000</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>592000</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>8892000</v>
+        <v>-344000</v>
       </c>
       <c r="AA91" t="n">
-        <v>-24686838</v>
+        <v>-75777</v>
       </c>
       <c r="AB91" t="n">
-        <v>-63006822</v>
+        <v>436287</v>
       </c>
       <c r="AC91" t="n">
-        <v>-83899582</v>
+        <v>758959</v>
       </c>
       <c r="AD91" t="n">
-        <v>-98133460</v>
+        <v>1006704</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -16241,33 +16241,31 @@
         <v>0</v>
       </c>
       <c r="AJ91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AL91" t="n">
         <v>2</v>
       </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AL91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM91" t="n">
-        <v>0</v>
-      </c>
+      <c r="AM91" t="inlineStr"/>
       <c r="AN91" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="AO91" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>可優先研究</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
@@ -16282,29 +16280,29 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、成交量放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2498.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -16323,28 +16321,28 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>43.7</v>
+        <v>1525</v>
       </c>
       <c r="G92" t="n">
-        <v>42.61</v>
+        <v>1598</v>
       </c>
       <c r="H92" t="n">
-        <v>41.28</v>
+        <v>1533.5</v>
       </c>
       <c r="I92" t="n">
-        <v>40.93</v>
+        <v>1456.75</v>
       </c>
       <c r="J92" t="n">
-        <v>23409453</v>
+        <v>3095000</v>
       </c>
       <c r="K92" t="n">
-        <v>15506141</v>
+        <v>4393600</v>
       </c>
       <c r="L92" t="n">
-        <v>46.85</v>
+        <v>1750</v>
       </c>
       <c r="M92" t="n">
-        <v>39.2</v>
+        <v>1240</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -16352,28 +16350,28 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>-1240185</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>-1845842</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>-6286070</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>-8188859</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>-1164408</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>-2282129</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>-7045029</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>-8851563</v>
+        <v>0</v>
       </c>
       <c r="W92" t="n">
         <v>0</v>
@@ -16385,19 +16383,19 @@
         <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>-344000</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>-75777</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>436287</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>758959</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
-        <v>1006704</v>
+        <v>0</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -16406,16 +16404,16 @@
         <v>2</v>
       </c>
       <c r="AG92" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="AH92" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
       </c>
       <c r="AJ92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
@@ -16423,23 +16421,25 @@
         </is>
       </c>
       <c r="AL92" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM92" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>0</v>
+      </c>
       <c r="AN92" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="AO92" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>可優先研究</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
@@ -16454,34 +16454,34 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、成交量放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>0056.TW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -16495,28 +16495,28 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1525</v>
+        <v>56.85</v>
       </c>
       <c r="G93" t="n">
-        <v>1598</v>
+        <v>56.72</v>
       </c>
       <c r="H93" t="n">
-        <v>1533.5</v>
+        <v>56.63</v>
       </c>
       <c r="I93" t="n">
-        <v>1456.75</v>
+        <v>56</v>
       </c>
       <c r="J93" t="n">
-        <v>3095000</v>
+        <v>42084968</v>
       </c>
       <c r="K93" t="n">
-        <v>4393600</v>
+        <v>32310102</v>
       </c>
       <c r="L93" t="n">
-        <v>1750</v>
+        <v>57.85</v>
       </c>
       <c r="M93" t="n">
-        <v>1240</v>
+        <v>54.5</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -16524,52 +16524,52 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>-33467525</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>-72909338</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>-104367817</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>-114331141</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>-8960687</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>-10344516</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>-21060235</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>-25089681</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>442000</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>592000</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>8892000</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>-24686838</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>-63006822</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>-83899582</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>-98133460</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -16578,10 +16578,10 @@
         <v>2</v>
       </c>
       <c r="AG93" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -16601,19 +16601,19 @@
         <v>0</v>
       </c>
       <c r="AN93" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="AO93" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
@@ -16628,29 +16628,29 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2345.TW</t>
+          <t>3363.TWO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -16669,28 +16669,28 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1900</v>
+        <v>641</v>
       </c>
       <c r="G94" t="n">
-        <v>1854</v>
+        <v>688.6</v>
       </c>
       <c r="H94" t="n">
-        <v>1852</v>
+        <v>642.7</v>
       </c>
       <c r="I94" t="n">
-        <v>1924.25</v>
+        <v>624.25</v>
       </c>
       <c r="J94" t="n">
-        <v>5872368</v>
+        <v>1137000</v>
       </c>
       <c r="K94" t="n">
-        <v>4781763</v>
+        <v>5767400</v>
       </c>
       <c r="L94" t="n">
-        <v>2205</v>
+        <v>747</v>
       </c>
       <c r="M94" t="n">
-        <v>1770</v>
+        <v>549</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -16698,70 +16698,70 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>41564</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>-2345555</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>-3969148</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>-6677428</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>486725</v>
+        <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>929669</v>
+        <v>0</v>
       </c>
       <c r="U94" t="n">
-        <v>330281</v>
+        <v>0</v>
       </c>
       <c r="V94" t="n">
-        <v>329673</v>
+        <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>-488000</v>
+        <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>-3407046</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>-4424047</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>-7391339</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>42839</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>131822</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
-        <v>124618</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
-        <v>384238</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG94" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AH94" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
       </c>
       <c r="AJ94" t="n">
-        <v>-36</v>
+        <v>-22</v>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
@@ -16769,25 +16769,25 @@
         </is>
       </c>
       <c r="AL94" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AM94" t="n">
-        <v>100</v>
+        <v>109.09</v>
       </c>
       <c r="AN94" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="AO94" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
@@ -16802,29 +16802,29 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>2345.TW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -16843,28 +16843,28 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>24.4</v>
+        <v>1900</v>
       </c>
       <c r="G95" t="n">
-        <v>24.41</v>
+        <v>1854</v>
       </c>
       <c r="H95" t="n">
-        <v>24.38</v>
+        <v>1852</v>
       </c>
       <c r="I95" t="n">
-        <v>24.59</v>
+        <v>1924.25</v>
       </c>
       <c r="J95" t="n">
-        <v>8727863</v>
+        <v>5872368</v>
       </c>
       <c r="K95" t="n">
-        <v>7809689</v>
+        <v>4781763</v>
       </c>
       <c r="L95" t="n">
-        <v>26.85</v>
+        <v>2205</v>
       </c>
       <c r="M95" t="n">
-        <v>23.8</v>
+        <v>1770</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -16872,52 +16872,52 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>-4568995</v>
+        <v>41564</v>
       </c>
       <c r="P95" t="n">
-        <v>-346498</v>
+        <v>-2345555</v>
       </c>
       <c r="Q95" t="n">
-        <v>281749</v>
+        <v>-3969148</v>
       </c>
       <c r="R95" t="n">
-        <v>1454993</v>
+        <v>-6677428</v>
       </c>
       <c r="S95" t="n">
-        <v>-4526162</v>
+        <v>486725</v>
       </c>
       <c r="T95" t="n">
-        <v>123351</v>
+        <v>929669</v>
       </c>
       <c r="U95" t="n">
-        <v>1136902</v>
+        <v>330281</v>
       </c>
       <c r="V95" t="n">
-        <v>2136012</v>
+        <v>329673</v>
       </c>
       <c r="W95" t="n">
-        <v>-154000</v>
+        <v>-488000</v>
       </c>
       <c r="X95" t="n">
-        <v>-154000</v>
+        <v>-3407046</v>
       </c>
       <c r="Y95" t="n">
-        <v>-152000</v>
+        <v>-4424047</v>
       </c>
       <c r="Z95" t="n">
-        <v>-172000</v>
+        <v>-7391339</v>
       </c>
       <c r="AA95" t="n">
-        <v>111167</v>
+        <v>42839</v>
       </c>
       <c r="AB95" t="n">
-        <v>-315849</v>
+        <v>131822</v>
       </c>
       <c r="AC95" t="n">
-        <v>-703153</v>
+        <v>124618</v>
       </c>
       <c r="AD95" t="n">
-        <v>-509019</v>
+        <v>384238</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -16926,42 +16926,42 @@
         <v>0</v>
       </c>
       <c r="AG95" t="n">
-        <v>-20</v>
+        <v>30</v>
       </c>
       <c r="AH95" t="n">
-        <v>20</v>
+        <v>-30</v>
       </c>
       <c r="AI95" t="n">
         <v>0</v>
       </c>
       <c r="AJ95" t="n">
-        <v>-12</v>
+        <v>-36</v>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AL95" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AM95" t="n">
         <v>100</v>
       </c>
       <c r="AN95" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AO95" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
@@ -16976,29 +16976,29 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2612.TW</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>中航</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -17017,28 +17017,28 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>61.4</v>
+        <v>24.4</v>
       </c>
       <c r="G96" t="n">
-        <v>61.72</v>
+        <v>24.41</v>
       </c>
       <c r="H96" t="n">
-        <v>62.33</v>
+        <v>24.38</v>
       </c>
       <c r="I96" t="n">
-        <v>62.91</v>
+        <v>24.59</v>
       </c>
       <c r="J96" t="n">
-        <v>131957</v>
+        <v>8727863</v>
       </c>
       <c r="K96" t="n">
-        <v>257591</v>
+        <v>7809689</v>
       </c>
       <c r="L96" t="n">
-        <v>66.3</v>
+        <v>26.85</v>
       </c>
       <c r="M96" t="n">
-        <v>60.5</v>
+        <v>23.8</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -17046,87 +17046,87 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>11707</v>
+        <v>-4568995</v>
       </c>
       <c r="P96" t="n">
-        <v>58434</v>
+        <v>-346498</v>
       </c>
       <c r="Q96" t="n">
-        <v>123244</v>
+        <v>281749</v>
       </c>
       <c r="R96" t="n">
-        <v>559874</v>
+        <v>1454993</v>
       </c>
       <c r="S96" t="n">
-        <v>9859</v>
+        <v>-4526162</v>
       </c>
       <c r="T96" t="n">
-        <v>119675</v>
+        <v>123351</v>
       </c>
       <c r="U96" t="n">
-        <v>192048</v>
+        <v>1136902</v>
       </c>
       <c r="V96" t="n">
-        <v>603027</v>
+        <v>2136012</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>-154000</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>-154000</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>-152000</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>-172000</v>
       </c>
       <c r="AA96" t="n">
-        <v>1848</v>
+        <v>111167</v>
       </c>
       <c r="AB96" t="n">
-        <v>-61241</v>
+        <v>-315849</v>
       </c>
       <c r="AC96" t="n">
-        <v>-68804</v>
+        <v>-703153</v>
       </c>
       <c r="AD96" t="n">
-        <v>-43153</v>
+        <v>-509019</v>
       </c>
       <c r="AE96" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
-        <v>-55</v>
+        <v>-20</v>
       </c>
       <c r="AH96" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
       </c>
       <c r="AJ96" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AL96" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="AM96" t="n">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="AN96" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO96" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
@@ -17150,29 +17150,29 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2401.TW</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>凌陽</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -17191,28 +17191,28 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>26.85</v>
+        <v>235.5</v>
       </c>
       <c r="G97" t="n">
-        <v>26.18</v>
+        <v>234.4</v>
       </c>
       <c r="H97" t="n">
-        <v>25.75</v>
+        <v>231.25</v>
       </c>
       <c r="I97" t="n">
-        <v>25.3</v>
+        <v>231.88</v>
       </c>
       <c r="J97" t="n">
-        <v>6341638</v>
+        <v>1866928</v>
       </c>
       <c r="K97" t="n">
-        <v>3206120</v>
+        <v>2897848</v>
       </c>
       <c r="L97" t="n">
-        <v>27.2</v>
+        <v>252</v>
       </c>
       <c r="M97" t="n">
-        <v>23.7</v>
+        <v>216</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -17220,52 +17220,52 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>-2402316</v>
+        <v>-602853</v>
       </c>
       <c r="P97" t="n">
-        <v>-1250763</v>
+        <v>-1128949</v>
       </c>
       <c r="Q97" t="n">
-        <v>-1171955</v>
+        <v>-2099</v>
       </c>
       <c r="R97" t="n">
-        <v>200968</v>
+        <v>-705825</v>
       </c>
       <c r="S97" t="n">
-        <v>-2467119</v>
+        <v>-609411</v>
       </c>
       <c r="T97" t="n">
-        <v>-1357063</v>
+        <v>-1063650</v>
       </c>
       <c r="U97" t="n">
-        <v>-1306119</v>
+        <v>-307586</v>
       </c>
       <c r="V97" t="n">
-        <v>-242968</v>
+        <v>-533719</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X97" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>70000</v>
+        <v>3000</v>
       </c>
       <c r="Z97" t="n">
-        <v>70000</v>
+        <v>-726000</v>
       </c>
       <c r="AA97" t="n">
-        <v>64803</v>
+        <v>4558</v>
       </c>
       <c r="AB97" t="n">
-        <v>66300</v>
+        <v>-65299</v>
       </c>
       <c r="AC97" t="n">
-        <v>64164</v>
+        <v>302487</v>
       </c>
       <c r="AD97" t="n">
-        <v>373936</v>
+        <v>553894</v>
       </c>
       <c r="AE97" t="n">
         <v>-2</v>
@@ -17274,16 +17274,16 @@
         <v>-2</v>
       </c>
       <c r="AG97" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="AH97" t="n">
-        <v>-80</v>
+        <v>-25</v>
       </c>
       <c r="AI97" t="n">
         <v>0</v>
       </c>
       <c r="AJ97" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
@@ -17291,16 +17291,16 @@
         </is>
       </c>
       <c r="AL97" t="n">
-        <v>-69</v>
+        <v>-42</v>
       </c>
       <c r="AM97" t="n">
-        <v>-102.99</v>
+        <v>-105</v>
       </c>
       <c r="AN97" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AO97" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
@@ -17324,29 +17324,29 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、接近20日高點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、投信買外資賣</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、成交量放大、接近20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、法人連續偏賣、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>2401.TW</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>凌陽</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -17365,28 +17365,28 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>235.5</v>
+        <v>26.85</v>
       </c>
       <c r="G98" t="n">
-        <v>234.4</v>
+        <v>26.18</v>
       </c>
       <c r="H98" t="n">
-        <v>231.25</v>
+        <v>25.75</v>
       </c>
       <c r="I98" t="n">
-        <v>231.88</v>
+        <v>25.3</v>
       </c>
       <c r="J98" t="n">
-        <v>1866928</v>
+        <v>6341638</v>
       </c>
       <c r="K98" t="n">
-        <v>2897848</v>
+        <v>3206120</v>
       </c>
       <c r="L98" t="n">
-        <v>252</v>
+        <v>27.2</v>
       </c>
       <c r="M98" t="n">
-        <v>216</v>
+        <v>23.7</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -17394,52 +17394,52 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>-602853</v>
+        <v>-2402316</v>
       </c>
       <c r="P98" t="n">
-        <v>-1128949</v>
+        <v>-1250763</v>
       </c>
       <c r="Q98" t="n">
-        <v>-2099</v>
+        <v>-1171955</v>
       </c>
       <c r="R98" t="n">
-        <v>-705825</v>
+        <v>200968</v>
       </c>
       <c r="S98" t="n">
-        <v>-609411</v>
+        <v>-2467119</v>
       </c>
       <c r="T98" t="n">
-        <v>-1063650</v>
+        <v>-1357063</v>
       </c>
       <c r="U98" t="n">
-        <v>-307586</v>
+        <v>-1306119</v>
       </c>
       <c r="V98" t="n">
-        <v>-533719</v>
+        <v>-242968</v>
       </c>
       <c r="W98" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="Y98" t="n">
-        <v>3000</v>
+        <v>70000</v>
       </c>
       <c r="Z98" t="n">
-        <v>-726000</v>
+        <v>70000</v>
       </c>
       <c r="AA98" t="n">
-        <v>4558</v>
+        <v>64803</v>
       </c>
       <c r="AB98" t="n">
-        <v>-65299</v>
+        <v>66300</v>
       </c>
       <c r="AC98" t="n">
-        <v>302487</v>
+        <v>64164</v>
       </c>
       <c r="AD98" t="n">
-        <v>553894</v>
+        <v>373936</v>
       </c>
       <c r="AE98" t="n">
         <v>-2</v>
@@ -17448,16 +17448,16 @@
         <v>-2</v>
       </c>
       <c r="AG98" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="AH98" t="n">
-        <v>-25</v>
+        <v>-80</v>
       </c>
       <c r="AI98" t="n">
         <v>0</v>
       </c>
       <c r="AJ98" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
@@ -17465,16 +17465,16 @@
         </is>
       </c>
       <c r="AL98" t="n">
-        <v>-42</v>
+        <v>-69</v>
       </c>
       <c r="AM98" t="n">
-        <v>-105</v>
+        <v>-102.99</v>
       </c>
       <c r="AN98" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AO98" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
@@ -17498,29 +17498,29 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、成交量放大、接近20日高點</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>法人連續偏賣、投信買外資賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、法人連續偏賣、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、成交量放大、接近20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6230.TW</t>
+          <t>2612.TW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>超眾</t>
+          <t>中航</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -17539,28 +17539,28 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>111</v>
+        <v>61.4</v>
       </c>
       <c r="G99" t="n">
-        <v>112</v>
+        <v>61.72</v>
       </c>
       <c r="H99" t="n">
-        <v>111.65</v>
+        <v>62.33</v>
       </c>
       <c r="I99" t="n">
-        <v>110.58</v>
+        <v>62.91</v>
       </c>
       <c r="J99" t="n">
-        <v>37943</v>
+        <v>131957</v>
       </c>
       <c r="K99" t="n">
-        <v>36031</v>
+        <v>257591</v>
       </c>
       <c r="L99" t="n">
-        <v>119</v>
+        <v>66.3</v>
       </c>
       <c r="M99" t="n">
-        <v>105.5</v>
+        <v>60.5</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -17568,28 +17568,28 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>7000</v>
+        <v>11707</v>
       </c>
       <c r="P99" t="n">
-        <v>-1662</v>
+        <v>58434</v>
       </c>
       <c r="Q99" t="n">
-        <v>-6662</v>
+        <v>123244</v>
       </c>
       <c r="R99" t="n">
-        <v>13589</v>
+        <v>559874</v>
       </c>
       <c r="S99" t="n">
-        <v>7000</v>
+        <v>9859</v>
       </c>
       <c r="T99" t="n">
-        <v>-1712</v>
+        <v>119675</v>
       </c>
       <c r="U99" t="n">
-        <v>-6712</v>
+        <v>192048</v>
       </c>
       <c r="V99" t="n">
-        <v>8539</v>
+        <v>603027</v>
       </c>
       <c r="W99" t="n">
         <v>0</v>
@@ -17604,45 +17604,45 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1848</v>
       </c>
       <c r="AB99" t="n">
+        <v>-61241</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>-68804</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>-43153</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AH99" t="n">
         <v>50</v>
       </c>
-      <c r="AC99" t="n">
-        <v>50</v>
-      </c>
-      <c r="AD99" t="n">
-        <v>5050</v>
-      </c>
-      <c r="AE99" t="n">
+      <c r="AI99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AL99" t="n">
         <v>-4</v>
       </c>
-      <c r="AF99" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AG99" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH99" t="n">
-        <v>-25</v>
-      </c>
-      <c r="AI99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ99" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AL99" t="n">
-        <v>-22</v>
-      </c>
       <c r="AM99" t="n">
-        <v>-122.22</v>
+        <v>-200</v>
       </c>
       <c r="AN99" t="n">
         <v>0</v>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
@@ -17672,29 +17672,29 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、中期買超轉短線賣壓。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>3017.TW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -17713,28 +17713,28 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>8.449999999999999</v>
+        <v>3510</v>
       </c>
       <c r="G100" t="n">
-        <v>8.48</v>
+        <v>3474</v>
       </c>
       <c r="H100" t="n">
-        <v>8.44</v>
+        <v>3396.5</v>
       </c>
       <c r="I100" t="n">
-        <v>8.52</v>
+        <v>3374.25</v>
       </c>
       <c r="J100" t="n">
-        <v>10908550</v>
+        <v>3303220</v>
       </c>
       <c r="K100" t="n">
-        <v>16768202</v>
+        <v>3158957</v>
       </c>
       <c r="L100" t="n">
-        <v>8.93</v>
+        <v>3600</v>
       </c>
       <c r="M100" t="n">
-        <v>8.300000000000001</v>
+        <v>3100</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -17742,52 +17742,52 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>-2521310</v>
+        <v>-47488</v>
       </c>
       <c r="P100" t="n">
-        <v>-1468671</v>
+        <v>-705417</v>
       </c>
       <c r="Q100" t="n">
-        <v>367850</v>
+        <v>-194113</v>
       </c>
       <c r="R100" t="n">
-        <v>-4982168</v>
+        <v>-496116</v>
       </c>
       <c r="S100" t="n">
-        <v>-2469084</v>
+        <v>-5336</v>
       </c>
       <c r="T100" t="n">
-        <v>-2564784</v>
+        <v>-373878</v>
       </c>
       <c r="U100" t="n">
-        <v>-1135886</v>
+        <v>-187394</v>
       </c>
       <c r="V100" t="n">
-        <v>-4641036</v>
+        <v>-937466</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>-82831</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>-411931</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>-176932</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>-3120</v>
       </c>
       <c r="AA100" t="n">
-        <v>-52226</v>
+        <v>40679</v>
       </c>
       <c r="AB100" t="n">
-        <v>1096113</v>
+        <v>80392</v>
       </c>
       <c r="AC100" t="n">
-        <v>1503736</v>
+        <v>170213</v>
       </c>
       <c r="AD100" t="n">
-        <v>-341132</v>
+        <v>444470</v>
       </c>
       <c r="AE100" t="n">
         <v>-4</v>
@@ -17796,16 +17796,16 @@
         <v>-4</v>
       </c>
       <c r="AG100" t="n">
-        <v>-30</v>
+        <v>55</v>
       </c>
       <c r="AH100" t="n">
-        <v>20</v>
+        <v>-65</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>
       </c>
       <c r="AJ100" t="n">
-        <v>18</v>
+        <v>-20</v>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
@@ -17813,25 +17813,25 @@
         </is>
       </c>
       <c r="AL100" t="n">
-        <v>-22</v>
+        <v>16</v>
       </c>
       <c r="AM100" t="n">
-        <v>-122.22</v>
+        <v>80</v>
       </c>
       <c r="AN100" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AO100" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR100" t="inlineStr">
@@ -17846,17 +17846,17 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>法人連續偏賣、5日法人賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -18037,12 +18037,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3017.TW</t>
+          <t>8028.TW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -18061,28 +18061,28 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3510</v>
+        <v>280</v>
       </c>
       <c r="G102" t="n">
-        <v>3474</v>
+        <v>275.7</v>
       </c>
       <c r="H102" t="n">
-        <v>3396.5</v>
+        <v>263.35</v>
       </c>
       <c r="I102" t="n">
-        <v>3374.25</v>
+        <v>248.97</v>
       </c>
       <c r="J102" t="n">
-        <v>3303220</v>
+        <v>5165195</v>
       </c>
       <c r="K102" t="n">
-        <v>3158957</v>
+        <v>10330646</v>
       </c>
       <c r="L102" t="n">
-        <v>3600</v>
+        <v>295.5</v>
       </c>
       <c r="M102" t="n">
-        <v>3100</v>
+        <v>216.5</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -18090,52 +18090,52 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>-47488</v>
+        <v>-1162887</v>
       </c>
       <c r="P102" t="n">
-        <v>-705417</v>
+        <v>-4310809</v>
       </c>
       <c r="Q102" t="n">
-        <v>-194113</v>
+        <v>-4438089</v>
       </c>
       <c r="R102" t="n">
-        <v>-496116</v>
+        <v>-4348070</v>
       </c>
       <c r="S102" t="n">
-        <v>-5336</v>
+        <v>-1177735</v>
       </c>
       <c r="T102" t="n">
-        <v>-373878</v>
+        <v>-6426852</v>
       </c>
       <c r="U102" t="n">
-        <v>-187394</v>
+        <v>-8994949</v>
       </c>
       <c r="V102" t="n">
-        <v>-937466</v>
+        <v>-18560957</v>
       </c>
       <c r="W102" t="n">
-        <v>-82831</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>-411931</v>
+        <v>2202000</v>
       </c>
       <c r="Y102" t="n">
-        <v>-176932</v>
+        <v>4511000</v>
       </c>
       <c r="Z102" t="n">
-        <v>-3120</v>
+        <v>14014000</v>
       </c>
       <c r="AA102" t="n">
-        <v>40679</v>
+        <v>14848</v>
       </c>
       <c r="AB102" t="n">
-        <v>80392</v>
+        <v>-85957</v>
       </c>
       <c r="AC102" t="n">
-        <v>170213</v>
+        <v>45860</v>
       </c>
       <c r="AD102" t="n">
-        <v>444470</v>
+        <v>198887</v>
       </c>
       <c r="AE102" t="n">
         <v>-4</v>
@@ -18144,42 +18144,42 @@
         <v>-4</v>
       </c>
       <c r="AG102" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN102" t="n">
         <v>55</v>
       </c>
-      <c r="AH102" t="n">
-        <v>-65</v>
-      </c>
-      <c r="AI102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ102" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AL102" t="n">
-        <v>16</v>
-      </c>
-      <c r="AM102" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN102" t="n">
-        <v>70</v>
-      </c>
       <c r="AO102" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
@@ -18194,29 +18194,29 @@
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8028.TW</t>
+          <t>6230.TW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>超眾</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -18235,28 +18235,28 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="G103" t="n">
-        <v>275.7</v>
+        <v>112</v>
       </c>
       <c r="H103" t="n">
-        <v>263.35</v>
+        <v>111.65</v>
       </c>
       <c r="I103" t="n">
-        <v>248.97</v>
+        <v>110.58</v>
       </c>
       <c r="J103" t="n">
-        <v>5165195</v>
+        <v>37943</v>
       </c>
       <c r="K103" t="n">
-        <v>10330646</v>
+        <v>36031</v>
       </c>
       <c r="L103" t="n">
-        <v>295.5</v>
+        <v>119</v>
       </c>
       <c r="M103" t="n">
-        <v>216.5</v>
+        <v>105.5</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -18264,52 +18264,52 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>-1162887</v>
+        <v>7000</v>
       </c>
       <c r="P103" t="n">
-        <v>-4310809</v>
+        <v>-1662</v>
       </c>
       <c r="Q103" t="n">
-        <v>-4438089</v>
+        <v>-6662</v>
       </c>
       <c r="R103" t="n">
-        <v>-4348070</v>
+        <v>13589</v>
       </c>
       <c r="S103" t="n">
-        <v>-1177735</v>
+        <v>7000</v>
       </c>
       <c r="T103" t="n">
-        <v>-6426852</v>
+        <v>-1712</v>
       </c>
       <c r="U103" t="n">
-        <v>-8994949</v>
+        <v>-6712</v>
       </c>
       <c r="V103" t="n">
-        <v>-18560957</v>
+        <v>8539</v>
       </c>
       <c r="W103" t="n">
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>2202000</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>4511000</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>14014000</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>14848</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>-85957</v>
+        <v>50</v>
       </c>
       <c r="AC103" t="n">
-        <v>45860</v>
+        <v>50</v>
       </c>
       <c r="AD103" t="n">
-        <v>198887</v>
+        <v>5050</v>
       </c>
       <c r="AE103" t="n">
         <v>-4</v>
@@ -18318,16 +18318,16 @@
         <v>-4</v>
       </c>
       <c r="AG103" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="AH103" t="n">
-        <v>-55</v>
+        <v>-25</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>
       </c>
       <c r="AJ103" t="n">
-        <v>-4</v>
+        <v>18</v>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
@@ -18335,25 +18335,25 @@
         </is>
       </c>
       <c r="AL103" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AM103" t="n">
-        <v>0</v>
+        <v>-122.22</v>
       </c>
       <c r="AN103" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AO103" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
@@ -18368,29 +18368,29 @@
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>中期買超轉短線賣壓</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、中期買超轉短線賣壓。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3023.TW</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -18409,28 +18409,28 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>309</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G104" t="n">
-        <v>309.3</v>
+        <v>8.48</v>
       </c>
       <c r="H104" t="n">
-        <v>315.25</v>
+        <v>8.44</v>
       </c>
       <c r="I104" t="n">
-        <v>321.4</v>
+        <v>8.52</v>
       </c>
       <c r="J104" t="n">
-        <v>715936</v>
+        <v>10908550</v>
       </c>
       <c r="K104" t="n">
-        <v>761859</v>
+        <v>16768202</v>
       </c>
       <c r="L104" t="n">
-        <v>348</v>
+        <v>8.93</v>
       </c>
       <c r="M104" t="n">
-        <v>304.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -18438,70 +18438,70 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>225657</v>
+        <v>-2521310</v>
       </c>
       <c r="P104" t="n">
-        <v>511186</v>
+        <v>-1468671</v>
       </c>
       <c r="Q104" t="n">
-        <v>93833</v>
+        <v>367850</v>
       </c>
       <c r="R104" t="n">
-        <v>419308</v>
+        <v>-4982168</v>
       </c>
       <c r="S104" t="n">
-        <v>231415</v>
+        <v>-2469084</v>
       </c>
       <c r="T104" t="n">
-        <v>495169</v>
+        <v>-2564784</v>
       </c>
       <c r="U104" t="n">
-        <v>103349</v>
+        <v>-1135886</v>
       </c>
       <c r="V104" t="n">
-        <v>497421</v>
+        <v>-4641036</v>
       </c>
       <c r="W104" t="n">
-        <v>-26000</v>
+        <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>-32000</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>-133000</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>20242</v>
+        <v>-52226</v>
       </c>
       <c r="AB104" t="n">
-        <v>46017</v>
+        <v>1096113</v>
       </c>
       <c r="AC104" t="n">
-        <v>22484</v>
+        <v>1503736</v>
       </c>
       <c r="AD104" t="n">
-        <v>54887</v>
+        <v>-341132</v>
       </c>
       <c r="AE104" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AF104" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AG104" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="AH104" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>
       </c>
       <c r="AJ104" t="n">
-        <v>-32</v>
+        <v>18</v>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
@@ -18509,10 +18509,10 @@
         </is>
       </c>
       <c r="AL104" t="n">
-        <v>26</v>
+        <v>-22</v>
       </c>
       <c r="AM104" t="n">
-        <v>81.25</v>
+        <v>-122.22</v>
       </c>
       <c r="AN104" t="n">
         <v>0</v>
@@ -18527,7 +18527,7 @@
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
@@ -18542,29 +18542,29 @@
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超、外資買投信賣</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人小幅買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5706.TW</t>
+          <t>3260.TWO</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>鳳凰</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -18583,28 +18583,28 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>44.2</v>
+        <v>380</v>
       </c>
       <c r="G105" t="n">
-        <v>44.06</v>
+        <v>379.1</v>
       </c>
       <c r="H105" t="n">
-        <v>44.09</v>
+        <v>385.95</v>
       </c>
       <c r="I105" t="n">
-        <v>44.28</v>
+        <v>395.2</v>
       </c>
       <c r="J105" t="n">
-        <v>34462</v>
+        <v>2640000</v>
       </c>
       <c r="K105" t="n">
-        <v>54115</v>
+        <v>3368000</v>
       </c>
       <c r="L105" t="n">
-        <v>45.4</v>
+        <v>428</v>
       </c>
       <c r="M105" t="n">
-        <v>43.6</v>
+        <v>373.5</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -18612,28 +18612,28 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>-4576</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>42317</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="U105" t="n">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>94893</v>
+        <v>0</v>
       </c>
       <c r="W105" t="n">
         <v>0</v>
@@ -18651,13 +18651,13 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>-22576</v>
+        <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>-52576</v>
+        <v>0</v>
       </c>
       <c r="AE105" t="n">
         <v>-6</v>
@@ -18675,7 +18675,7 @@
         <v>0</v>
       </c>
       <c r="AJ105" t="n">
-        <v>4</v>
+        <v>-22</v>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
@@ -18683,25 +18683,25 @@
         </is>
       </c>
       <c r="AL105" t="n">
-        <v>-10</v>
+        <v>16</v>
       </c>
       <c r="AM105" t="n">
-        <v>-250</v>
+        <v>72.73</v>
       </c>
       <c r="AN105" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AO105" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
@@ -18733,12 +18733,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3260.TWO</t>
+          <t>3023.TW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -18757,28 +18757,28 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>380</v>
+        <v>309</v>
       </c>
       <c r="G106" t="n">
-        <v>379.1</v>
+        <v>309.3</v>
       </c>
       <c r="H106" t="n">
-        <v>385.95</v>
+        <v>315.25</v>
       </c>
       <c r="I106" t="n">
-        <v>395.2</v>
+        <v>321.4</v>
       </c>
       <c r="J106" t="n">
-        <v>2640000</v>
+        <v>715936</v>
       </c>
       <c r="K106" t="n">
-        <v>3368000</v>
+        <v>761859</v>
       </c>
       <c r="L106" t="n">
-        <v>428</v>
+        <v>348</v>
       </c>
       <c r="M106" t="n">
-        <v>373.5</v>
+        <v>304.5</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -18786,52 +18786,52 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>225657</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>511186</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>93833</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>419308</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>231415</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>495169</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>103349</v>
       </c>
       <c r="V106" t="n">
-        <v>0</v>
+        <v>497421</v>
       </c>
       <c r="W106" t="n">
-        <v>0</v>
+        <v>-26000</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>-32000</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>-133000</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>20242</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>46017</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>22484</v>
       </c>
       <c r="AD106" t="n">
-        <v>0</v>
+        <v>54887</v>
       </c>
       <c r="AE106" t="n">
         <v>-6</v>
@@ -18840,16 +18840,16 @@
         <v>-6</v>
       </c>
       <c r="AG106" t="n">
-        <v>-15</v>
+        <v>-55</v>
       </c>
       <c r="AH106" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI106" t="n">
         <v>0</v>
       </c>
       <c r="AJ106" t="n">
-        <v>-22</v>
+        <v>-32</v>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
@@ -18857,25 +18857,25 @@
         </is>
       </c>
       <c r="AL106" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AM106" t="n">
-        <v>72.73</v>
+        <v>81.25</v>
       </c>
       <c r="AN106" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AO106" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
@@ -18890,29 +18890,29 @@
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏買、5日法人小幅買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人小幅買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1906.TW</t>
+          <t>5706.TW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>寶隆</t>
+          <t>鳳凰</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -18931,28 +18931,28 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>10.8</v>
+        <v>44.2</v>
       </c>
       <c r="G107" t="n">
-        <v>10.78</v>
+        <v>44.06</v>
       </c>
       <c r="H107" t="n">
-        <v>10.81</v>
+        <v>44.09</v>
       </c>
       <c r="I107" t="n">
-        <v>10.95</v>
+        <v>44.28</v>
       </c>
       <c r="J107" t="n">
-        <v>29188</v>
+        <v>34462</v>
       </c>
       <c r="K107" t="n">
-        <v>54597</v>
+        <v>54115</v>
       </c>
       <c r="L107" t="n">
-        <v>11.35</v>
+        <v>45.4</v>
       </c>
       <c r="M107" t="n">
-        <v>10.6</v>
+        <v>43.6</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -18960,28 +18960,28 @@
         </is>
       </c>
       <c r="O107" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="P107" t="n">
-        <v>-5000</v>
+        <v>35000</v>
       </c>
       <c r="Q107" t="n">
-        <v>-23000</v>
+        <v>-4576</v>
       </c>
       <c r="R107" t="n">
-        <v>-67000</v>
+        <v>42317</v>
       </c>
       <c r="S107" t="n">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="T107" t="n">
-        <v>-4000</v>
+        <v>48000</v>
       </c>
       <c r="U107" t="n">
-        <v>-20000</v>
+        <v>18000</v>
       </c>
       <c r="V107" t="n">
-        <v>-69000</v>
+        <v>94893</v>
       </c>
       <c r="W107" t="n">
         <v>0</v>
@@ -18996,16 +18996,16 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>-1000</v>
+        <v>-13000</v>
       </c>
       <c r="AC107" t="n">
-        <v>-3000</v>
+        <v>-22576</v>
       </c>
       <c r="AD107" t="n">
-        <v>2000</v>
+        <v>-52576</v>
       </c>
       <c r="AE107" t="n">
         <v>-6</v>
@@ -19023,7 +19023,7 @@
         <v>0</v>
       </c>
       <c r="AJ107" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
@@ -19031,10 +19031,10 @@
         </is>
       </c>
       <c r="AL107" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="AM107" t="n">
-        <v>-200</v>
+        <v>-250</v>
       </c>
       <c r="AN107" t="n">
         <v>20</v>
@@ -19081,12 +19081,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8039.TW</t>
+          <t>1906.TW</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>寶隆</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -19105,28 +19105,28 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>288.5</v>
+        <v>10.8</v>
       </c>
       <c r="G108" t="n">
-        <v>275.4</v>
+        <v>10.78</v>
       </c>
       <c r="H108" t="n">
-        <v>270.65</v>
+        <v>10.81</v>
       </c>
       <c r="I108" t="n">
-        <v>280.62</v>
+        <v>10.95</v>
       </c>
       <c r="J108" t="n">
-        <v>30321735</v>
+        <v>29188</v>
       </c>
       <c r="K108" t="n">
-        <v>18341508</v>
+        <v>54597</v>
       </c>
       <c r="L108" t="n">
-        <v>327.5</v>
+        <v>11.35</v>
       </c>
       <c r="M108" t="n">
-        <v>253</v>
+        <v>10.6</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -19134,70 +19134,70 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>-2336800</v>
+        <v>5000</v>
       </c>
       <c r="P108" t="n">
-        <v>-2991547</v>
+        <v>-5000</v>
       </c>
       <c r="Q108" t="n">
-        <v>-3015760</v>
+        <v>-23000</v>
       </c>
       <c r="R108" t="n">
-        <v>-8410452</v>
+        <v>-67000</v>
       </c>
       <c r="S108" t="n">
-        <v>-2105312</v>
+        <v>4000</v>
       </c>
       <c r="T108" t="n">
-        <v>-3669744</v>
+        <v>-4000</v>
       </c>
       <c r="U108" t="n">
-        <v>-3526813</v>
+        <v>-20000</v>
       </c>
       <c r="V108" t="n">
-        <v>-4573746</v>
+        <v>-69000</v>
       </c>
       <c r="W108" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>43000</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>-3519000</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>-221488</v>
+        <v>1000</v>
       </c>
       <c r="AB108" t="n">
-        <v>635197</v>
+        <v>-1000</v>
       </c>
       <c r="AC108" t="n">
-        <v>467053</v>
+        <v>-3000</v>
       </c>
       <c r="AD108" t="n">
-        <v>-317706</v>
+        <v>2000</v>
       </c>
       <c r="AE108" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AF108" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AG108" t="n">
-        <v>35</v>
+        <v>-15</v>
       </c>
       <c r="AH108" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AI108" t="n">
         <v>0</v>
       </c>
       <c r="AJ108" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
@@ -19205,25 +19205,25 @@
         </is>
       </c>
       <c r="AL108" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="AM108" t="n">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="AN108" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AO108" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
@@ -19238,29 +19238,29 @@
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3014.TW</t>
+          <t>8039.TW</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>聯陽</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -19279,28 +19279,28 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>142</v>
+        <v>288.5</v>
       </c>
       <c r="G109" t="n">
-        <v>142.1</v>
+        <v>275.4</v>
       </c>
       <c r="H109" t="n">
-        <v>139.05</v>
+        <v>270.65</v>
       </c>
       <c r="I109" t="n">
-        <v>134.97</v>
+        <v>280.62</v>
       </c>
       <c r="J109" t="n">
-        <v>1276071</v>
+        <v>30321735</v>
       </c>
       <c r="K109" t="n">
-        <v>2703514</v>
+        <v>18341508</v>
       </c>
       <c r="L109" t="n">
-        <v>145</v>
+        <v>327.5</v>
       </c>
       <c r="M109" t="n">
-        <v>128.5</v>
+        <v>253</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -19308,70 +19308,70 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>432150</v>
+        <v>-2336800</v>
       </c>
       <c r="P109" t="n">
-        <v>775408</v>
+        <v>-2991547</v>
       </c>
       <c r="Q109" t="n">
-        <v>-1474209</v>
+        <v>-3015760</v>
       </c>
       <c r="R109" t="n">
-        <v>1844792</v>
+        <v>-8410452</v>
       </c>
       <c r="S109" t="n">
-        <v>409346</v>
+        <v>-2105312</v>
       </c>
       <c r="T109" t="n">
-        <v>688802</v>
+        <v>-3669744</v>
       </c>
       <c r="U109" t="n">
-        <v>-1540837</v>
+        <v>-3526813</v>
       </c>
       <c r="V109" t="n">
-        <v>1502573</v>
+        <v>-4573746</v>
       </c>
       <c r="W109" t="n">
-        <v>3004</v>
+        <v>-10000</v>
       </c>
       <c r="X109" t="n">
-        <v>54933</v>
+        <v>43000</v>
       </c>
       <c r="Y109" t="n">
-        <v>23688</v>
+        <v>44000</v>
       </c>
       <c r="Z109" t="n">
-        <v>274187</v>
+        <v>-3519000</v>
       </c>
       <c r="AA109" t="n">
-        <v>19800</v>
+        <v>-221488</v>
       </c>
       <c r="AB109" t="n">
-        <v>31673</v>
+        <v>635197</v>
       </c>
       <c r="AC109" t="n">
-        <v>42940</v>
+        <v>467053</v>
       </c>
       <c r="AD109" t="n">
-        <v>68032</v>
+        <v>-317706</v>
       </c>
       <c r="AE109" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AF109" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AG109" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="AH109" t="n">
-        <v>-30</v>
+        <v>-55</v>
       </c>
       <c r="AI109" t="n">
         <v>0</v>
       </c>
       <c r="AJ109" t="n">
-        <v>-26</v>
+        <v>4</v>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
@@ -19379,10 +19379,10 @@
         </is>
       </c>
       <c r="AL109" t="n">
-        <v>16</v>
+        <v>-12</v>
       </c>
       <c r="AM109" t="n">
-        <v>61.54</v>
+        <v>-300</v>
       </c>
       <c r="AN109" t="n">
         <v>35</v>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
@@ -19412,29 +19412,29 @@
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、成交量放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2351.TW</t>
+          <t>3014.TW</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>順德</t>
+          <t>聯陽</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -19453,28 +19453,28 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>212.5</v>
+        <v>142</v>
       </c>
       <c r="G110" t="n">
-        <v>216.5</v>
+        <v>142.1</v>
       </c>
       <c r="H110" t="n">
-        <v>227.3</v>
+        <v>139.05</v>
       </c>
       <c r="I110" t="n">
-        <v>232.05</v>
+        <v>134.97</v>
       </c>
       <c r="J110" t="n">
-        <v>3449076</v>
+        <v>1276071</v>
       </c>
       <c r="K110" t="n">
-        <v>5100546</v>
+        <v>2703514</v>
       </c>
       <c r="L110" t="n">
-        <v>257</v>
+        <v>145</v>
       </c>
       <c r="M110" t="n">
-        <v>204</v>
+        <v>128.5</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -19482,52 +19482,52 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>-266712</v>
+        <v>432150</v>
       </c>
       <c r="P110" t="n">
-        <v>-1131006</v>
+        <v>775408</v>
       </c>
       <c r="Q110" t="n">
-        <v>2264797</v>
+        <v>-1474209</v>
       </c>
       <c r="R110" t="n">
-        <v>2789203</v>
+        <v>1844792</v>
       </c>
       <c r="S110" t="n">
-        <v>-317901</v>
+        <v>409346</v>
       </c>
       <c r="T110" t="n">
-        <v>-665204</v>
+        <v>688802</v>
       </c>
       <c r="U110" t="n">
-        <v>2924514</v>
+        <v>-1540837</v>
       </c>
       <c r="V110" t="n">
-        <v>3593406</v>
+        <v>1502573</v>
       </c>
       <c r="W110" t="n">
-        <v>21000</v>
+        <v>3004</v>
       </c>
       <c r="X110" t="n">
-        <v>-499000</v>
+        <v>54933</v>
       </c>
       <c r="Y110" t="n">
-        <v>-499000</v>
+        <v>23688</v>
       </c>
       <c r="Z110" t="n">
-        <v>-404000</v>
+        <v>274187</v>
       </c>
       <c r="AA110" t="n">
-        <v>30189</v>
+        <v>19800</v>
       </c>
       <c r="AB110" t="n">
-        <v>33198</v>
+        <v>31673</v>
       </c>
       <c r="AC110" t="n">
-        <v>-160717</v>
+        <v>42940</v>
       </c>
       <c r="AD110" t="n">
-        <v>-400203</v>
+        <v>68032</v>
       </c>
       <c r="AE110" t="n">
         <v>-10</v>
@@ -19536,16 +19536,16 @@
         <v>-10</v>
       </c>
       <c r="AG110" t="n">
-        <v>-55</v>
+        <v>5</v>
       </c>
       <c r="AH110" t="n">
-        <v>30</v>
+        <v>-30</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
       </c>
       <c r="AJ110" t="n">
-        <v>-6</v>
+        <v>-26</v>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
@@ -19553,25 +19553,25 @@
         </is>
       </c>
       <c r="AL110" t="n">
-        <v>-4</v>
+        <v>16</v>
       </c>
       <c r="AM110" t="n">
-        <v>-66.67</v>
+        <v>61.54</v>
       </c>
       <c r="AN110" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AO110" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
@@ -19586,29 +19586,29 @@
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>2351.TW</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>順德</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -19627,28 +19627,28 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1290</v>
+        <v>212.5</v>
       </c>
       <c r="G111" t="n">
-        <v>1294</v>
+        <v>216.5</v>
       </c>
       <c r="H111" t="n">
-        <v>1293</v>
+        <v>227.3</v>
       </c>
       <c r="I111" t="n">
-        <v>1316.75</v>
+        <v>232.05</v>
       </c>
       <c r="J111" t="n">
-        <v>488000</v>
+        <v>3449076</v>
       </c>
       <c r="K111" t="n">
-        <v>1059800</v>
+        <v>5100546</v>
       </c>
       <c r="L111" t="n">
-        <v>1455</v>
+        <v>257</v>
       </c>
       <c r="M111" t="n">
-        <v>1240</v>
+        <v>204</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -19656,70 +19656,70 @@
         </is>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>-266712</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>-1131006</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>2264797</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2789203</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>-317901</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>-665204</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>2924514</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
+        <v>3593406</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>-499000</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>-499000</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>-404000</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>30189</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>33198</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>-160717</v>
       </c>
       <c r="AD111" t="n">
-        <v>0</v>
+        <v>-400203</v>
       </c>
       <c r="AE111" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AF111" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AG111" t="n">
-        <v>-30</v>
+        <v>-55</v>
       </c>
       <c r="AH111" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
       </c>
       <c r="AJ111" t="n">
-        <v>-12</v>
+        <v>-6</v>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
@@ -19727,10 +19727,10 @@
         </is>
       </c>
       <c r="AL111" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM111" t="n">
-        <v>0</v>
+        <v>-66.67</v>
       </c>
       <c r="AN111" t="n">
         <v>0</v>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
@@ -19760,34 +19760,34 @@
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>00878.TW</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -19801,28 +19801,28 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>34.89</v>
+        <v>1290</v>
       </c>
       <c r="G112" t="n">
-        <v>34.92</v>
+        <v>1294</v>
       </c>
       <c r="H112" t="n">
-        <v>34.89</v>
+        <v>1293</v>
       </c>
       <c r="I112" t="n">
-        <v>34.47</v>
+        <v>1316.75</v>
       </c>
       <c r="J112" t="n">
-        <v>34467088</v>
+        <v>488000</v>
       </c>
       <c r="K112" t="n">
-        <v>30373766</v>
+        <v>1059800</v>
       </c>
       <c r="L112" t="n">
-        <v>35.54</v>
+        <v>1455</v>
       </c>
       <c r="M112" t="n">
-        <v>33.56</v>
+        <v>1240</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -19830,28 +19830,28 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>-23025971</v>
+        <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>-48851640</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>-89792442</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>-83429519</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>-3021568</v>
+        <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>-3073098</v>
+        <v>0</v>
       </c>
       <c r="U112" t="n">
-        <v>-10854484</v>
+        <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>-11136693</v>
+        <v>0</v>
       </c>
       <c r="W112" t="n">
         <v>0</v>
@@ -19863,37 +19863,37 @@
         <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>-20004403</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>-45778542</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>-78937958</v>
+        <v>0</v>
       </c>
       <c r="AD112" t="n">
-        <v>-72192826</v>
+        <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AF112" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AG112" t="n">
-        <v>20</v>
+        <v>-30</v>
       </c>
       <c r="AH112" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
       </c>
       <c r="AJ112" t="n">
-        <v>-18</v>
+        <v>-12</v>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
@@ -19901,16 +19901,16 @@
         </is>
       </c>
       <c r="AL112" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM112" t="n">
-        <v>22.22</v>
+        <v>0</v>
       </c>
       <c r="AN112" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AO112" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -19934,17 +19934,17 @@
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -20647,17 +20647,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3062.TW</t>
+          <t>00878.TW</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>建漢</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -20671,28 +20671,28 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>22.25</v>
+        <v>34.89</v>
       </c>
       <c r="G117" t="n">
-        <v>22.26</v>
+        <v>34.92</v>
       </c>
       <c r="H117" t="n">
-        <v>21.98</v>
+        <v>34.89</v>
       </c>
       <c r="I117" t="n">
-        <v>21.25</v>
+        <v>34.47</v>
       </c>
       <c r="J117" t="n">
-        <v>1441699</v>
+        <v>34467088</v>
       </c>
       <c r="K117" t="n">
-        <v>1935063</v>
+        <v>30373766</v>
       </c>
       <c r="L117" t="n">
-        <v>23.2</v>
+        <v>35.54</v>
       </c>
       <c r="M117" t="n">
-        <v>20.1</v>
+        <v>33.56</v>
       </c>
       <c r="N117" t="inlineStr">
         <is>
@@ -20700,28 +20700,28 @@
         </is>
       </c>
       <c r="O117" t="n">
-        <v>-511265</v>
+        <v>-23025971</v>
       </c>
       <c r="P117" t="n">
-        <v>-61538</v>
+        <v>-48851640</v>
       </c>
       <c r="Q117" t="n">
-        <v>-419216</v>
+        <v>-89792442</v>
       </c>
       <c r="R117" t="n">
-        <v>-547465</v>
+        <v>-83429519</v>
       </c>
       <c r="S117" t="n">
-        <v>-506950</v>
+        <v>-3021568</v>
       </c>
       <c r="T117" t="n">
-        <v>-69346</v>
+        <v>-3073098</v>
       </c>
       <c r="U117" t="n">
-        <v>-421346</v>
+        <v>-10854484</v>
       </c>
       <c r="V117" t="n">
-        <v>-709217</v>
+        <v>-11136693</v>
       </c>
       <c r="W117" t="n">
         <v>0</v>
@@ -20733,37 +20733,37 @@
         <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="AA117" t="n">
-        <v>-4315</v>
+        <v>-20004403</v>
       </c>
       <c r="AB117" t="n">
-        <v>7808</v>
+        <v>-45778542</v>
       </c>
       <c r="AC117" t="n">
-        <v>2130</v>
+        <v>-78937958</v>
       </c>
       <c r="AD117" t="n">
-        <v>161752</v>
+        <v>-72192826</v>
       </c>
       <c r="AE117" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AF117" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AG117" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AH117" t="n">
-        <v>-45</v>
+        <v>-55</v>
       </c>
       <c r="AI117" t="n">
         <v>0</v>
       </c>
       <c r="AJ117" t="n">
-        <v>18</v>
+        <v>-18</v>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
@@ -20771,16 +20771,16 @@
         </is>
       </c>
       <c r="AL117" t="n">
-        <v>-34</v>
+        <v>4</v>
       </c>
       <c r="AM117" t="n">
-        <v>-188.89</v>
+        <v>22.22</v>
       </c>
       <c r="AN117" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AO117" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
@@ -20804,29 +20804,29 @@
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2371.TW</t>
+          <t>3062.TW</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>大同</t>
+          <t>建漢</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -20845,28 +20845,28 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>30.5</v>
+        <v>22.25</v>
       </c>
       <c r="G118" t="n">
-        <v>29.63</v>
+        <v>22.26</v>
       </c>
       <c r="H118" t="n">
-        <v>29.48</v>
+        <v>21.98</v>
       </c>
       <c r="I118" t="n">
-        <v>28.69</v>
+        <v>21.25</v>
       </c>
       <c r="J118" t="n">
-        <v>33538127</v>
+        <v>1441699</v>
       </c>
       <c r="K118" t="n">
-        <v>16993497</v>
+        <v>1935063</v>
       </c>
       <c r="L118" t="n">
-        <v>31.6</v>
+        <v>23.2</v>
       </c>
       <c r="M118" t="n">
-        <v>27.3</v>
+        <v>20.1</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -20874,52 +20874,52 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>-11345071</v>
+        <v>-511265</v>
       </c>
       <c r="P118" t="n">
-        <v>-4071918</v>
+        <v>-61538</v>
       </c>
       <c r="Q118" t="n">
-        <v>-5593637</v>
+        <v>-419216</v>
       </c>
       <c r="R118" t="n">
-        <v>7318140</v>
+        <v>-547465</v>
       </c>
       <c r="S118" t="n">
-        <v>-10686904</v>
+        <v>-506950</v>
       </c>
       <c r="T118" t="n">
-        <v>-4573407</v>
+        <v>-69346</v>
       </c>
       <c r="U118" t="n">
-        <v>-5723190</v>
+        <v>-421346</v>
       </c>
       <c r="V118" t="n">
-        <v>7024011</v>
+        <v>-709217</v>
       </c>
       <c r="W118" t="n">
         <v>0</v>
       </c>
       <c r="X118" t="n">
-        <v>-24000</v>
+        <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>-24000</v>
+        <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>-517861</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>-658167</v>
+        <v>-4315</v>
       </c>
       <c r="AB118" t="n">
-        <v>525489</v>
+        <v>7808</v>
       </c>
       <c r="AC118" t="n">
-        <v>153553</v>
+        <v>2130</v>
       </c>
       <c r="AD118" t="n">
-        <v>811990</v>
+        <v>161752</v>
       </c>
       <c r="AE118" t="n">
         <v>-16</v>
@@ -20928,16 +20928,16 @@
         <v>-16</v>
       </c>
       <c r="AG118" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="AH118" t="n">
-        <v>-100</v>
+        <v>-45</v>
       </c>
       <c r="AI118" t="n">
         <v>0</v>
       </c>
       <c r="AJ118" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
@@ -20945,25 +20945,25 @@
         </is>
       </c>
       <c r="AL118" t="n">
-        <v>-77</v>
+        <v>-34</v>
       </c>
       <c r="AM118" t="n">
-        <v>-126.23</v>
+        <v>-188.89</v>
       </c>
       <c r="AN118" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="AO118" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
@@ -20978,29 +20978,29 @@
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人賣超</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、成交量放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4979.TWO</t>
+          <t>2371.TW</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>大同</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -21019,28 +21019,28 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>557</v>
+        <v>30.5</v>
       </c>
       <c r="G119" t="n">
-        <v>569.2</v>
+        <v>29.63</v>
       </c>
       <c r="H119" t="n">
-        <v>578.3</v>
+        <v>29.48</v>
       </c>
       <c r="I119" t="n">
-        <v>578.55</v>
+        <v>28.69</v>
       </c>
       <c r="J119" t="n">
-        <v>1104000</v>
+        <v>33538127</v>
       </c>
       <c r="K119" t="n">
-        <v>3793800</v>
+        <v>16993497</v>
       </c>
       <c r="L119" t="n">
-        <v>658</v>
+        <v>31.6</v>
       </c>
       <c r="M119" t="n">
-        <v>501</v>
+        <v>27.3</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -21048,70 +21048,70 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>-11345071</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>-4071918</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>-5593637</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>7318140</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>-10686904</v>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>-4573407</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>-5723190</v>
       </c>
       <c r="V119" t="n">
-        <v>0</v>
+        <v>7024011</v>
       </c>
       <c r="W119" t="n">
         <v>0</v>
       </c>
       <c r="X119" t="n">
-        <v>0</v>
+        <v>-24000</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>-24000</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>-517861</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>-658167</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>525489</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>153553</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>811990</v>
       </c>
       <c r="AE119" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="AF119" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="AG119" t="n">
-        <v>-45</v>
+        <v>60</v>
       </c>
       <c r="AH119" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AI119" t="n">
         <v>0</v>
       </c>
       <c r="AJ119" t="n">
-        <v>-8</v>
+        <v>61</v>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
@@ -21119,25 +21119,25 @@
         </is>
       </c>
       <c r="AL119" t="n">
-        <v>-10</v>
+        <v>-77</v>
       </c>
       <c r="AM119" t="n">
-        <v>-125</v>
+        <v>-126.23</v>
       </c>
       <c r="AN119" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AO119" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
@@ -21152,29 +21152,29 @@
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、成交量放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5530.TWO</t>
+          <t>4979.TWO</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>龍巖</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -21193,28 +21193,28 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>48.75</v>
+        <v>557</v>
       </c>
       <c r="G120" t="n">
-        <v>48.84</v>
+        <v>569.2</v>
       </c>
       <c r="H120" t="n">
-        <v>49.08</v>
+        <v>578.3</v>
       </c>
       <c r="I120" t="n">
-        <v>49.34</v>
+        <v>578.55</v>
       </c>
       <c r="J120" t="n">
-        <v>65000</v>
+        <v>1104000</v>
       </c>
       <c r="K120" t="n">
-        <v>169600</v>
+        <v>3793800</v>
       </c>
       <c r="L120" t="n">
-        <v>50.5</v>
+        <v>658</v>
       </c>
       <c r="M120" t="n">
-        <v>47.7</v>
+        <v>501</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -21270,13 +21270,13 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>-22</v>
+        <v>-18</v>
       </c>
       <c r="AF120" t="n">
-        <v>-22</v>
+        <v>-18</v>
       </c>
       <c r="AG120" t="n">
-        <v>-55</v>
+        <v>-45</v>
       </c>
       <c r="AH120" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="AJ120" t="n">
-        <v>-22</v>
+        <v>-8</v>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
@@ -21293,10 +21293,10 @@
         </is>
       </c>
       <c r="AL120" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AM120" t="n">
-        <v>0</v>
+        <v>-125</v>
       </c>
       <c r="AN120" t="n">
         <v>0</v>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
@@ -21336,19 +21336,19 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3363.TWO</t>
+          <t>5530.TWO</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>龍巖</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -21367,28 +21367,28 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>641</v>
+        <v>48.75</v>
       </c>
       <c r="G121" t="n">
-        <v>647.4</v>
+        <v>48.84</v>
       </c>
       <c r="H121" t="n">
-        <v>658</v>
+        <v>49.08</v>
       </c>
       <c r="I121" t="n">
-        <v>686.45</v>
+        <v>49.34</v>
       </c>
       <c r="J121" t="n">
-        <v>1137000</v>
+        <v>65000</v>
       </c>
       <c r="K121" t="n">
-        <v>1784600</v>
+        <v>169600</v>
       </c>
       <c r="L121" t="n">
-        <v>850</v>
+        <v>50.5</v>
       </c>
       <c r="M121" t="n">
-        <v>629</v>
+        <v>47.7</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -13169,12 +13169,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6214.TW</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -13193,28 +13193,28 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>188.5</v>
+        <v>250</v>
       </c>
       <c r="G74" t="n">
-        <v>188.6</v>
+        <v>249.7</v>
       </c>
       <c r="H74" t="n">
-        <v>190</v>
+        <v>244.6</v>
       </c>
       <c r="I74" t="n">
-        <v>189.03</v>
+        <v>242.1</v>
       </c>
       <c r="J74" t="n">
-        <v>469492</v>
+        <v>3840000</v>
       </c>
       <c r="K74" t="n">
-        <v>923981</v>
+        <v>5227600</v>
       </c>
       <c r="L74" t="n">
-        <v>195</v>
+        <v>264</v>
       </c>
       <c r="M74" t="n">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -13222,70 +13222,70 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>121804</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>434017</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>166714</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1482540</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>115804</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>415621</v>
+        <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>184350</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>1500273</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>-1604</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>-47636</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>-26733</v>
+        <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF74" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AG74" t="n">
-        <v>-30</v>
+        <v>45</v>
       </c>
       <c r="AH74" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
@@ -13293,23 +13293,25 @@
         </is>
       </c>
       <c r="AL74" t="n">
-        <v>16</v>
-      </c>
-      <c r="AM74" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>0</v>
+      </c>
       <c r="AN74" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AO74" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
@@ -13324,17 +13326,17 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -13515,12 +13517,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2485.TW</t>
+          <t>6214.TW</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -13539,99 +13541,99 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>44.6</v>
+        <v>188.5</v>
       </c>
       <c r="G76" t="n">
-        <v>41.57</v>
+        <v>188.6</v>
       </c>
       <c r="H76" t="n">
-        <v>40.65</v>
+        <v>190</v>
       </c>
       <c r="I76" t="n">
-        <v>40.09</v>
+        <v>189.03</v>
       </c>
       <c r="J76" t="n">
-        <v>18380592</v>
+        <v>469492</v>
       </c>
       <c r="K76" t="n">
-        <v>5703766</v>
+        <v>923981</v>
       </c>
       <c r="L76" t="n">
-        <v>45.3</v>
+        <v>195</v>
       </c>
       <c r="M76" t="n">
-        <v>37.55</v>
+        <v>183</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>-3459619</v>
+        <v>121804</v>
       </c>
       <c r="P76" t="n">
-        <v>-3330085</v>
+        <v>434017</v>
       </c>
       <c r="Q76" t="n">
-        <v>-1476936</v>
+        <v>166714</v>
       </c>
       <c r="R76" t="n">
-        <v>-530333</v>
+        <v>1482540</v>
       </c>
       <c r="S76" t="n">
-        <v>-3644348</v>
+        <v>115804</v>
       </c>
       <c r="T76" t="n">
-        <v>-3525950</v>
+        <v>415621</v>
       </c>
       <c r="U76" t="n">
-        <v>-1685097</v>
+        <v>184350</v>
       </c>
       <c r="V76" t="n">
-        <v>-822794</v>
+        <v>1500273</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="Y76" t="n">
-        <v>54</v>
+        <v>30000</v>
       </c>
       <c r="Z76" t="n">
-        <v>54</v>
+        <v>9000</v>
       </c>
       <c r="AA76" t="n">
-        <v>184729</v>
+        <v>-4000</v>
       </c>
       <c r="AB76" t="n">
-        <v>195865</v>
+        <v>-1604</v>
       </c>
       <c r="AC76" t="n">
-        <v>208107</v>
+        <v>-47636</v>
       </c>
       <c r="AD76" t="n">
-        <v>292407</v>
+        <v>-26733</v>
       </c>
       <c r="AE76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG76" t="n">
-        <v>80</v>
+        <v>-30</v>
       </c>
       <c r="AH76" t="n">
-        <v>-55</v>
+        <v>70</v>
       </c>
       <c r="AI76" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AJ76" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
@@ -13639,16 +13641,14 @@
         </is>
       </c>
       <c r="AL76" t="n">
-        <v>-39</v>
-      </c>
-      <c r="AM76" t="n">
-        <v>-72.22</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="AM76" t="inlineStr"/>
       <c r="AN76" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO76" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>DT尚未轉強、離5MA偏遠、均線多頭排列、爆量後不追價、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
@@ -13672,29 +13672,29 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、接近20日高點、帶量突破20日高點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、接近20日高點、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8215.TW</t>
+          <t>2485.TW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -13713,99 +13713,99 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>28.6</v>
+        <v>44.6</v>
       </c>
       <c r="G77" t="n">
-        <v>29.01</v>
+        <v>41.57</v>
       </c>
       <c r="H77" t="n">
-        <v>28.66</v>
+        <v>40.65</v>
       </c>
       <c r="I77" t="n">
-        <v>27.02</v>
+        <v>40.09</v>
       </c>
       <c r="J77" t="n">
-        <v>2080719</v>
+        <v>18380592</v>
       </c>
       <c r="K77" t="n">
-        <v>2453121</v>
+        <v>5703766</v>
       </c>
       <c r="L77" t="n">
-        <v>31</v>
+        <v>45.3</v>
       </c>
       <c r="M77" t="n">
-        <v>24.5</v>
+        <v>37.55</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>-415624</v>
+        <v>-3459619</v>
       </c>
       <c r="P77" t="n">
-        <v>515275</v>
+        <v>-3330085</v>
       </c>
       <c r="Q77" t="n">
-        <v>1048020</v>
+        <v>-1476936</v>
       </c>
       <c r="R77" t="n">
-        <v>2439810</v>
+        <v>-530333</v>
       </c>
       <c r="S77" t="n">
-        <v>-383185</v>
+        <v>-3644348</v>
       </c>
       <c r="T77" t="n">
-        <v>557582</v>
+        <v>-3525950</v>
       </c>
       <c r="U77" t="n">
-        <v>1066824</v>
+        <v>-1685097</v>
       </c>
       <c r="V77" t="n">
-        <v>2433897</v>
+        <v>-822794</v>
       </c>
       <c r="W77" t="n">
-        <v>-20000</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>-27000</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>-39000</v>
+        <v>54</v>
       </c>
       <c r="Z77" t="n">
-        <v>-39000</v>
+        <v>54</v>
       </c>
       <c r="AA77" t="n">
-        <v>-12439</v>
+        <v>184729</v>
       </c>
       <c r="AB77" t="n">
-        <v>-15307</v>
+        <v>195865</v>
       </c>
       <c r="AC77" t="n">
-        <v>20196</v>
+        <v>208107</v>
       </c>
       <c r="AD77" t="n">
-        <v>44913</v>
+        <v>292407</v>
       </c>
       <c r="AE77" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF77" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG77" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="AH77" t="n">
-        <v>30</v>
+        <v>-55</v>
       </c>
       <c r="AI77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AJ77" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
@@ -13813,16 +13813,16 @@
         </is>
       </c>
       <c r="AL77" t="n">
-        <v>-28</v>
+        <v>-39</v>
       </c>
       <c r="AM77" t="n">
-        <v>-66.67</v>
+        <v>-72.22</v>
       </c>
       <c r="AN77" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO77" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、離5MA偏遠、均線多頭排列、爆量後不追價、分數轉弱</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
@@ -13846,17 +13846,17 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、爆量、接近20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、接近20日高點、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14037,12 +14037,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2436.TW</t>
+          <t>8215.TW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>偉詮電</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -14061,28 +14061,28 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>73.2</v>
+        <v>28.6</v>
       </c>
       <c r="G79" t="n">
-        <v>74.72</v>
+        <v>29.01</v>
       </c>
       <c r="H79" t="n">
-        <v>72.45</v>
+        <v>28.66</v>
       </c>
       <c r="I79" t="n">
-        <v>70.13</v>
+        <v>27.02</v>
       </c>
       <c r="J79" t="n">
-        <v>7263426</v>
+        <v>2080719</v>
       </c>
       <c r="K79" t="n">
-        <v>8086989</v>
+        <v>2453121</v>
       </c>
       <c r="L79" t="n">
-        <v>77.5</v>
+        <v>31</v>
       </c>
       <c r="M79" t="n">
-        <v>64.09999999999999</v>
+        <v>24.5</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -14090,52 +14090,52 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>-496560</v>
+        <v>-415624</v>
       </c>
       <c r="P79" t="n">
-        <v>1568263</v>
+        <v>515275</v>
       </c>
       <c r="Q79" t="n">
-        <v>3036793</v>
+        <v>1048020</v>
       </c>
       <c r="R79" t="n">
-        <v>3736014</v>
+        <v>2439810</v>
       </c>
       <c r="S79" t="n">
-        <v>-323159</v>
+        <v>-383185</v>
       </c>
       <c r="T79" t="n">
-        <v>1853626</v>
+        <v>557582</v>
       </c>
       <c r="U79" t="n">
-        <v>3156988</v>
+        <v>1066824</v>
       </c>
       <c r="V79" t="n">
-        <v>3428748</v>
+        <v>2433897</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>-20000</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>-27000</v>
       </c>
       <c r="Y79" t="n">
-        <v>-24000</v>
+        <v>-39000</v>
       </c>
       <c r="Z79" t="n">
-        <v>-4000</v>
+        <v>-39000</v>
       </c>
       <c r="AA79" t="n">
-        <v>-173401</v>
+        <v>-12439</v>
       </c>
       <c r="AB79" t="n">
-        <v>-285363</v>
+        <v>-15307</v>
       </c>
       <c r="AC79" t="n">
-        <v>-96195</v>
+        <v>20196</v>
       </c>
       <c r="AD79" t="n">
-        <v>311266</v>
+        <v>44913</v>
       </c>
       <c r="AE79" t="n">
         <v>14</v>
@@ -14153,7 +14153,7 @@
         <v>0</v>
       </c>
       <c r="AJ79" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
@@ -14161,10 +14161,10 @@
         </is>
       </c>
       <c r="AL79" t="n">
-        <v>-34</v>
+        <v>-28</v>
       </c>
       <c r="AM79" t="n">
-        <v>-70.83</v>
+        <v>-66.67</v>
       </c>
       <c r="AN79" t="n">
         <v>10</v>
@@ -14385,12 +14385,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>2436.TW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>偉詮電</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -14409,28 +14409,28 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>709</v>
+        <v>73.2</v>
       </c>
       <c r="G81" t="n">
-        <v>672.4</v>
+        <v>74.72</v>
       </c>
       <c r="H81" t="n">
-        <v>667.7</v>
+        <v>72.45</v>
       </c>
       <c r="I81" t="n">
-        <v>681.85</v>
+        <v>70.13</v>
       </c>
       <c r="J81" t="n">
-        <v>5017000</v>
+        <v>7263426</v>
       </c>
       <c r="K81" t="n">
-        <v>3666400</v>
+        <v>8086989</v>
       </c>
       <c r="L81" t="n">
-        <v>790</v>
+        <v>77.5</v>
       </c>
       <c r="M81" t="n">
-        <v>631</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -14438,28 +14438,28 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>-496560</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1568263</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3036793</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3736014</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>-323159</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>1853626</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>3156988</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>3428748</v>
       </c>
       <c r="W81" t="n">
         <v>0</v>
@@ -14468,40 +14468,40 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>-24000</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>-173401</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>-285363</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>-96195</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>311266</v>
       </c>
       <c r="AE81" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF81" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH81" t="n">
         <v>30</v>
       </c>
-      <c r="AH81" t="n">
-        <v>0</v>
-      </c>
       <c r="AI81" t="n">
         <v>0</v>
       </c>
       <c r="AJ81" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
@@ -14509,25 +14509,25 @@
         </is>
       </c>
       <c r="AL81" t="n">
-        <v>6</v>
+        <v>-34</v>
       </c>
       <c r="AM81" t="n">
-        <v>100</v>
+        <v>-70.83</v>
       </c>
       <c r="AN81" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="AO81" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
@@ -14542,17 +14542,17 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14907,12 +14907,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>4979.TWO</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -14931,28 +14931,28 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1550</v>
+        <v>598</v>
       </c>
       <c r="G84" t="n">
-        <v>1548</v>
+        <v>575.2</v>
       </c>
       <c r="H84" t="n">
-        <v>1564.5</v>
+        <v>586.3</v>
       </c>
       <c r="I84" t="n">
-        <v>1470.25</v>
+        <v>577.9</v>
       </c>
       <c r="J84" t="n">
-        <v>4586000</v>
+        <v>1322000</v>
       </c>
       <c r="K84" t="n">
-        <v>3903800</v>
+        <v>1069800</v>
       </c>
       <c r="L84" t="n">
-        <v>1750</v>
+        <v>658</v>
       </c>
       <c r="M84" t="n">
-        <v>1240</v>
+        <v>501</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>0</v>
       </c>
       <c r="AJ84" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
@@ -15031,16 +15031,16 @@
         </is>
       </c>
       <c r="AL84" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AM84" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AN84" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AO84" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR84" t="inlineStr">
@@ -15081,12 +15081,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4979.TWO</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -15105,28 +15105,28 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>598</v>
+        <v>709</v>
       </c>
       <c r="G85" t="n">
-        <v>575.2</v>
+        <v>672.4</v>
       </c>
       <c r="H85" t="n">
-        <v>586.3</v>
+        <v>667.7</v>
       </c>
       <c r="I85" t="n">
-        <v>577.9</v>
+        <v>681.85</v>
       </c>
       <c r="J85" t="n">
-        <v>1322000</v>
+        <v>5017000</v>
       </c>
       <c r="K85" t="n">
-        <v>1069800</v>
+        <v>3666400</v>
       </c>
       <c r="L85" t="n">
-        <v>658</v>
+        <v>790</v>
       </c>
       <c r="M85" t="n">
-        <v>501</v>
+        <v>631</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>0</v>
       </c>
       <c r="AJ85" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
@@ -15205,10 +15205,10 @@
         </is>
       </c>
       <c r="AL85" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM85" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AN85" t="n">
         <v>53</v>
@@ -15255,12 +15255,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2014.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>中鴻</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -15279,28 +15279,28 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>16.85</v>
+        <v>1550</v>
       </c>
       <c r="G86" t="n">
-        <v>17.05</v>
+        <v>1548</v>
       </c>
       <c r="H86" t="n">
-        <v>16.85</v>
+        <v>1564.5</v>
       </c>
       <c r="I86" t="n">
-        <v>16.79</v>
+        <v>1470.25</v>
       </c>
       <c r="J86" t="n">
-        <v>2253453</v>
+        <v>4586000</v>
       </c>
       <c r="K86" t="n">
-        <v>3502735</v>
+        <v>3903800</v>
       </c>
       <c r="L86" t="n">
-        <v>17.45</v>
+        <v>1750</v>
       </c>
       <c r="M86" t="n">
-        <v>16.2</v>
+        <v>1240</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -15308,28 +15308,28 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>-633410</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>-1864235</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>1674567</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>5384464</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>-633410</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>-1851235</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>1681567</v>
+        <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>5307464</v>
+        <v>0</v>
       </c>
       <c r="W86" t="n">
         <v>0</v>
@@ -15347,57 +15347,57 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AL86" t="n">
         <v>10</v>
       </c>
-      <c r="AF86" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG86" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AH86" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ86" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AL86" t="n">
-        <v>-32</v>
-      </c>
       <c r="AM86" t="n">
-        <v>-76.19</v>
+        <v>500</v>
       </c>
       <c r="AN86" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="AO86" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
@@ -15412,29 +15412,29 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1612.TW</t>
+          <t>2014.TW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>宏泰</t>
+          <t>中鴻</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -15453,28 +15453,28 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>35</v>
+        <v>16.85</v>
       </c>
       <c r="G87" t="n">
-        <v>35.28</v>
+        <v>17.05</v>
       </c>
       <c r="H87" t="n">
-        <v>35.15</v>
+        <v>16.85</v>
       </c>
       <c r="I87" t="n">
-        <v>34.98</v>
+        <v>16.79</v>
       </c>
       <c r="J87" t="n">
-        <v>389026</v>
+        <v>2253453</v>
       </c>
       <c r="K87" t="n">
-        <v>621074</v>
+        <v>3502735</v>
       </c>
       <c r="L87" t="n">
-        <v>35.75</v>
+        <v>17.45</v>
       </c>
       <c r="M87" t="n">
-        <v>34.5</v>
+        <v>16.2</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -15482,52 +15482,52 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>-44486</v>
+        <v>-633410</v>
       </c>
       <c r="P87" t="n">
-        <v>-382760</v>
+        <v>-1864235</v>
       </c>
       <c r="Q87" t="n">
-        <v>541983</v>
+        <v>1674567</v>
       </c>
       <c r="R87" t="n">
-        <v>877901</v>
+        <v>5384464</v>
       </c>
       <c r="S87" t="n">
-        <v>-39000</v>
+        <v>-633410</v>
       </c>
       <c r="T87" t="n">
-        <v>-406747</v>
+        <v>-1851235</v>
       </c>
       <c r="U87" t="n">
-        <v>497122</v>
+        <v>1681567</v>
       </c>
       <c r="V87" t="n">
-        <v>880590</v>
+        <v>5307464</v>
       </c>
       <c r="W87" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>-9561</v>
+        <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>-10121</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>-19241</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>-486</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>33548</v>
+        <v>-13000</v>
       </c>
       <c r="AC87" t="n">
-        <v>54982</v>
+        <v>-7000</v>
       </c>
       <c r="AD87" t="n">
-        <v>16552</v>
+        <v>77000</v>
       </c>
       <c r="AE87" t="n">
         <v>10</v>
@@ -15545,7 +15545,7 @@
         <v>0</v>
       </c>
       <c r="AJ87" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
@@ -15553,16 +15553,16 @@
         </is>
       </c>
       <c r="AL87" t="n">
-        <v>-6</v>
+        <v>-32</v>
       </c>
       <c r="AM87" t="n">
-        <v>-37.5</v>
+        <v>-76.19</v>
       </c>
       <c r="AN87" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO87" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -15591,12 +15591,12 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15777,12 +15777,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2607.TW</t>
+          <t>1612.TW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>榮運</t>
+          <t>宏泰</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -15801,28 +15801,28 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>53.2</v>
+        <v>35</v>
       </c>
       <c r="G89" t="n">
-        <v>53.48</v>
+        <v>35.28</v>
       </c>
       <c r="H89" t="n">
-        <v>53.54</v>
+        <v>35.15</v>
       </c>
       <c r="I89" t="n">
-        <v>53.38</v>
+        <v>34.98</v>
       </c>
       <c r="J89" t="n">
-        <v>215273</v>
+        <v>389026</v>
       </c>
       <c r="K89" t="n">
-        <v>253662</v>
+        <v>621074</v>
       </c>
       <c r="L89" t="n">
-        <v>54</v>
+        <v>35.75</v>
       </c>
       <c r="M89" t="n">
-        <v>52.4</v>
+        <v>34.5</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -15830,52 +15830,52 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>43322</v>
+        <v>-44486</v>
       </c>
       <c r="P89" t="n">
-        <v>126393</v>
+        <v>-382760</v>
       </c>
       <c r="Q89" t="n">
-        <v>96314</v>
+        <v>541983</v>
       </c>
       <c r="R89" t="n">
-        <v>447068</v>
+        <v>877901</v>
       </c>
       <c r="S89" t="n">
-        <v>43322</v>
+        <v>-39000</v>
       </c>
       <c r="T89" t="n">
-        <v>121229</v>
+        <v>-406747</v>
       </c>
       <c r="U89" t="n">
-        <v>87857</v>
+        <v>497122</v>
       </c>
       <c r="V89" t="n">
-        <v>408438</v>
+        <v>880590</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>-9561</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>-10121</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>-19241</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>-486</v>
       </c>
       <c r="AB89" t="n">
-        <v>5164</v>
+        <v>33548</v>
       </c>
       <c r="AC89" t="n">
-        <v>8457</v>
+        <v>54982</v>
       </c>
       <c r="AD89" t="n">
-        <v>38630</v>
+        <v>16552</v>
       </c>
       <c r="AE89" t="n">
         <v>10</v>
@@ -15884,16 +15884,16 @@
         <v>10</v>
       </c>
       <c r="AG89" t="n">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="AH89" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
       </c>
       <c r="AJ89" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
@@ -15901,10 +15901,10 @@
         </is>
       </c>
       <c r="AL89" t="n">
-        <v>-14</v>
+        <v>-6</v>
       </c>
       <c r="AM89" t="n">
-        <v>-58.33</v>
+        <v>-37.5</v>
       </c>
       <c r="AN89" t="n">
         <v>0</v>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
@@ -15934,29 +15934,29 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日高點、接近20日低點、法人連續偏買、5日法人小幅買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>2607.TW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>榮運</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -15975,28 +15975,28 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>41.9</v>
+        <v>53.2</v>
       </c>
       <c r="G90" t="n">
-        <v>42.16</v>
+        <v>53.48</v>
       </c>
       <c r="H90" t="n">
-        <v>42.19</v>
+        <v>53.54</v>
       </c>
       <c r="I90" t="n">
-        <v>42.11</v>
+        <v>53.38</v>
       </c>
       <c r="J90" t="n">
-        <v>9545947</v>
+        <v>215273</v>
       </c>
       <c r="K90" t="n">
-        <v>15514004</v>
+        <v>253662</v>
       </c>
       <c r="L90" t="n">
-        <v>43.2</v>
+        <v>54</v>
       </c>
       <c r="M90" t="n">
-        <v>40.85</v>
+        <v>52.4</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -16004,70 +16004,70 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>-878465</v>
+        <v>43322</v>
       </c>
       <c r="P90" t="n">
-        <v>-4710436</v>
+        <v>126393</v>
       </c>
       <c r="Q90" t="n">
-        <v>7430286</v>
+        <v>96314</v>
       </c>
       <c r="R90" t="n">
-        <v>30901551</v>
+        <v>447068</v>
       </c>
       <c r="S90" t="n">
-        <v>-920518</v>
+        <v>43322</v>
       </c>
       <c r="T90" t="n">
-        <v>-4158049</v>
+        <v>121229</v>
       </c>
       <c r="U90" t="n">
-        <v>4946480</v>
+        <v>87857</v>
       </c>
       <c r="V90" t="n">
-        <v>1243816</v>
+        <v>408438</v>
       </c>
       <c r="W90" t="n">
-        <v>-27000</v>
+        <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>-1503580</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>519841</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>26358071</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>69053</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>951193</v>
+        <v>5164</v>
       </c>
       <c r="AC90" t="n">
-        <v>1963965</v>
+        <v>8457</v>
       </c>
       <c r="AD90" t="n">
-        <v>3299664</v>
+        <v>38630</v>
       </c>
       <c r="AE90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG90" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
       <c r="AH90" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
       </c>
       <c r="AJ90" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
@@ -16075,10 +16075,10 @@
         </is>
       </c>
       <c r="AL90" t="n">
-        <v>-26</v>
+        <v>-14</v>
       </c>
       <c r="AM90" t="n">
-        <v>-76.47</v>
+        <v>-58.33</v>
       </c>
       <c r="AN90" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
@@ -16108,29 +16108,29 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人小幅買超</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日高點、接近20日低點、法人連續偏買、5日法人小幅買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16149,28 +16149,28 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>234.5</v>
+        <v>41.9</v>
       </c>
       <c r="G91" t="n">
-        <v>215.2</v>
+        <v>42.16</v>
       </c>
       <c r="H91" t="n">
-        <v>219.4</v>
+        <v>42.19</v>
       </c>
       <c r="I91" t="n">
-        <v>226.28</v>
+        <v>42.11</v>
       </c>
       <c r="J91" t="n">
-        <v>9988000</v>
+        <v>9545947</v>
       </c>
       <c r="K91" t="n">
-        <v>3281400</v>
+        <v>15514004</v>
       </c>
       <c r="L91" t="n">
-        <v>265</v>
+        <v>43.2</v>
       </c>
       <c r="M91" t="n">
-        <v>199</v>
+        <v>40.85</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -16178,70 +16178,70 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>-878465</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>-4710436</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>7430286</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>30901551</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>-920518</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>-4158049</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>4946480</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>1243816</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>-27000</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>-1503580</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>519841</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>26358071</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>69053</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>951193</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1963965</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>3299664</v>
       </c>
       <c r="AE91" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF91" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG91" t="n">
-        <v>15</v>
+        <v>-30</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
       </c>
       <c r="AJ91" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
@@ -16249,16 +16249,16 @@
         </is>
       </c>
       <c r="AL91" t="n">
-        <v>2</v>
+        <v>-26</v>
       </c>
       <c r="AM91" t="n">
-        <v>50</v>
+        <v>-76.47</v>
       </c>
       <c r="AN91" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AO91" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、離5MA偏遠、位於20日區間中上緣、爆量後不追價、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
@@ -16282,17 +16282,17 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、爆量</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、爆量、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -16995,12 +16995,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6269.TW</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -17019,28 +17019,28 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>65.09999999999999</v>
+        <v>234.5</v>
       </c>
       <c r="G96" t="n">
-        <v>65.42</v>
+        <v>215.2</v>
       </c>
       <c r="H96" t="n">
-        <v>64.98999999999999</v>
+        <v>219.4</v>
       </c>
       <c r="I96" t="n">
-        <v>65.48999999999999</v>
+        <v>226.28</v>
       </c>
       <c r="J96" t="n">
-        <v>3026754</v>
+        <v>9988000</v>
       </c>
       <c r="K96" t="n">
-        <v>2884393</v>
+        <v>3281400</v>
       </c>
       <c r="L96" t="n">
-        <v>71</v>
+        <v>265</v>
       </c>
       <c r="M96" t="n">
-        <v>63</v>
+        <v>199</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -17048,28 +17048,28 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>-36556</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>402039</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>1938091</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>-394065</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>-9507</v>
+        <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>443323</v>
+        <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>1960550</v>
+        <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>-454317</v>
+        <v>0</v>
       </c>
       <c r="W96" t="n">
         <v>0</v>
@@ -17084,51 +17084,51 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>-27049</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>-41284</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>-22459</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>60252</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ96" t="n">
         <v>4</v>
       </c>
-      <c r="AF96" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG96" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AH96" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ96" t="n">
-        <v>28</v>
-      </c>
       <c r="AK96" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
       <c r="AL96" t="n">
-        <v>-24</v>
+        <v>2</v>
       </c>
       <c r="AM96" t="n">
-        <v>-85.70999999999999</v>
+        <v>50</v>
       </c>
       <c r="AN96" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO96" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、離5MA偏遠、位於20日區間中上緣、爆量後不追價、分數剛升溫</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
@@ -17152,29 +17152,29 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、爆量</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、爆量、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>6269.TW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -17193,99 +17193,99 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>30.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G97" t="n">
-        <v>30.9</v>
+        <v>65.42</v>
       </c>
       <c r="H97" t="n">
-        <v>30.91</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="I97" t="n">
-        <v>31.14</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="J97" t="n">
-        <v>5703898</v>
+        <v>3026754</v>
       </c>
       <c r="K97" t="n">
-        <v>5217809</v>
+        <v>2884393</v>
       </c>
       <c r="L97" t="n">
-        <v>33.35</v>
+        <v>71</v>
       </c>
       <c r="M97" t="n">
+        <v>63</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>-36556</v>
+      </c>
+      <c r="P97" t="n">
+        <v>402039</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1938091</v>
+      </c>
+      <c r="R97" t="n">
+        <v>-394065</v>
+      </c>
+      <c r="S97" t="n">
+        <v>-9507</v>
+      </c>
+      <c r="T97" t="n">
+        <v>443323</v>
+      </c>
+      <c r="U97" t="n">
+        <v>1960550</v>
+      </c>
+      <c r="V97" t="n">
+        <v>-454317</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>-27049</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>-41284</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>-22459</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>60252</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AH97" t="n">
         <v>30</v>
       </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>無明顯異常</t>
-        </is>
-      </c>
-      <c r="O97" t="n">
-        <v>-22296</v>
-      </c>
-      <c r="P97" t="n">
-        <v>-1871491</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>516602</v>
-      </c>
-      <c r="R97" t="n">
-        <v>260244</v>
-      </c>
-      <c r="S97" t="n">
-        <v>-67961</v>
-      </c>
-      <c r="T97" t="n">
-        <v>-2020643</v>
-      </c>
-      <c r="U97" t="n">
-        <v>239393</v>
-      </c>
-      <c r="V97" t="n">
-        <v>319032</v>
-      </c>
-      <c r="W97" t="n">
-        <v>100000</v>
-      </c>
-      <c r="X97" t="n">
-        <v>100000</v>
-      </c>
-      <c r="Y97" t="n">
-        <v>102000</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>118000</v>
-      </c>
-      <c r="AA97" t="n">
-        <v>-54335</v>
-      </c>
-      <c r="AB97" t="n">
-        <v>49152</v>
-      </c>
-      <c r="AC97" t="n">
-        <v>175209</v>
-      </c>
-      <c r="AD97" t="n">
-        <v>-176788</v>
-      </c>
-      <c r="AE97" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF97" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG97" t="n">
-        <v>-45</v>
-      </c>
-      <c r="AH97" t="n">
-        <v>50</v>
-      </c>
       <c r="AI97" t="n">
         <v>0</v>
       </c>
       <c r="AJ97" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
@@ -17293,10 +17293,10 @@
         </is>
       </c>
       <c r="AL97" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AM97" t="n">
-        <v>0</v>
+        <v>-85.70999999999999</v>
       </c>
       <c r="AN97" t="n">
         <v>0</v>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
@@ -17326,29 +17326,29 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4903.TWO</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -17367,28 +17367,28 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>43.8</v>
+        <v>30.7</v>
       </c>
       <c r="G98" t="n">
-        <v>43.83</v>
+        <v>30.9</v>
       </c>
       <c r="H98" t="n">
-        <v>42.53</v>
+        <v>30.91</v>
       </c>
       <c r="I98" t="n">
-        <v>38.87</v>
+        <v>31.14</v>
       </c>
       <c r="J98" t="n">
-        <v>4446000</v>
+        <v>5703898</v>
       </c>
       <c r="K98" t="n">
-        <v>6347400</v>
+        <v>5217809</v>
       </c>
       <c r="L98" t="n">
-        <v>46.45</v>
+        <v>33.35</v>
       </c>
       <c r="M98" t="n">
-        <v>33.15</v>
+        <v>30</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -17396,52 +17396,52 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>-22296</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>-1871491</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>516602</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>260244</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>-67961</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>-2020643</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>239393</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>319032</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>102000</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>-54335</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>49152</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>175209</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>-176788</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -17450,16 +17450,16 @@
         <v>2</v>
       </c>
       <c r="AG98" t="n">
-        <v>5</v>
+        <v>-45</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AI98" t="n">
         <v>0</v>
       </c>
       <c r="AJ98" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
@@ -17467,16 +17467,16 @@
         </is>
       </c>
       <c r="AL98" t="n">
-        <v>-27</v>
+        <v>0</v>
       </c>
       <c r="AM98" t="n">
-        <v>-93.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN98" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO98" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
@@ -17500,17 +17500,17 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -17691,12 +17691,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3363.TWO</t>
+          <t>4903.TWO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -17715,28 +17715,28 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>664</v>
+        <v>43.8</v>
       </c>
       <c r="G100" t="n">
-        <v>655.4</v>
+        <v>43.83</v>
       </c>
       <c r="H100" t="n">
-        <v>657.6</v>
+        <v>42.53</v>
       </c>
       <c r="I100" t="n">
-        <v>675.5</v>
+        <v>38.87</v>
       </c>
       <c r="J100" t="n">
-        <v>2943000</v>
+        <v>4446000</v>
       </c>
       <c r="K100" t="n">
-        <v>2200600</v>
+        <v>6347400</v>
       </c>
       <c r="L100" t="n">
-        <v>808</v>
+        <v>46.45</v>
       </c>
       <c r="M100" t="n">
-        <v>629</v>
+        <v>33.15</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>0</v>
       </c>
       <c r="AJ100" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
@@ -17815,25 +17815,25 @@
         </is>
       </c>
       <c r="AL100" t="n">
-        <v>-2</v>
+        <v>-27</v>
       </c>
       <c r="AM100" t="n">
-        <v>-50</v>
+        <v>-93.09999999999999</v>
       </c>
       <c r="AN100" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AO100" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR100" t="inlineStr">
@@ -17848,7 +17848,7 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
@@ -17858,19 +17858,19 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2345.TW</t>
+          <t>3363.TWO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -17889,28 +17889,28 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2075</v>
+        <v>664</v>
       </c>
       <c r="G101" t="n">
-        <v>1905</v>
+        <v>655.4</v>
       </c>
       <c r="H101" t="n">
-        <v>1892</v>
+        <v>657.6</v>
       </c>
       <c r="I101" t="n">
-        <v>1914.75</v>
+        <v>675.5</v>
       </c>
       <c r="J101" t="n">
-        <v>6386760</v>
+        <v>2943000</v>
       </c>
       <c r="K101" t="n">
-        <v>5773897</v>
+        <v>2200600</v>
       </c>
       <c r="L101" t="n">
-        <v>2190</v>
+        <v>808</v>
       </c>
       <c r="M101" t="n">
-        <v>1770</v>
+        <v>629</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -17918,70 +17918,70 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>132378</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>-153647</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>-2540766</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>-5678483</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>213910</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>287812</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>730756</v>
+        <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>-91339</v>
+        <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>-188994</v>
+        <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>-566271</v>
+        <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>-3485317</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>-6131106</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>107462</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>124812</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>213795</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>543962</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG101" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AH101" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="AI101" t="n">
         <v>0</v>
       </c>
       <c r="AJ101" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
@@ -17989,10 +17989,10 @@
         </is>
       </c>
       <c r="AL101" t="n">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="AM101" t="n">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="AN101" t="n">
         <v>35</v>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>DT尚未轉強、離5MA偏遠、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
@@ -18022,17 +18022,17 @@
       </c>
       <c r="AT101" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -18909,12 +18909,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>2345.TW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -18933,28 +18933,28 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>76.8</v>
+        <v>2075</v>
       </c>
       <c r="G107" t="n">
-        <v>74.98</v>
+        <v>1905</v>
       </c>
       <c r="H107" t="n">
-        <v>70.11</v>
+        <v>1892</v>
       </c>
       <c r="I107" t="n">
-        <v>66.88</v>
+        <v>1914.75</v>
       </c>
       <c r="J107" t="n">
-        <v>29000616</v>
+        <v>6386760</v>
       </c>
       <c r="K107" t="n">
-        <v>26437753</v>
+        <v>5773897</v>
       </c>
       <c r="L107" t="n">
-        <v>81</v>
+        <v>2190</v>
       </c>
       <c r="M107" t="n">
-        <v>60</v>
+        <v>1770</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -18962,52 +18962,52 @@
         </is>
       </c>
       <c r="O107" t="n">
-        <v>-6334666</v>
+        <v>132378</v>
       </c>
       <c r="P107" t="n">
-        <v>-4310655</v>
+        <v>-153647</v>
       </c>
       <c r="Q107" t="n">
-        <v>-8631987</v>
+        <v>-2540766</v>
       </c>
       <c r="R107" t="n">
-        <v>-9258248</v>
+        <v>-5678483</v>
       </c>
       <c r="S107" t="n">
-        <v>-5351754</v>
+        <v>213910</v>
       </c>
       <c r="T107" t="n">
-        <v>-4858993</v>
+        <v>287812</v>
       </c>
       <c r="U107" t="n">
-        <v>-9490346</v>
+        <v>730756</v>
       </c>
       <c r="V107" t="n">
-        <v>-10151213</v>
+        <v>-91339</v>
       </c>
       <c r="W107" t="n">
-        <v>0</v>
+        <v>-188994</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>-566271</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>-3485317</v>
       </c>
       <c r="Z107" t="n">
-        <v>76</v>
+        <v>-6131106</v>
       </c>
       <c r="AA107" t="n">
-        <v>-982912</v>
+        <v>107462</v>
       </c>
       <c r="AB107" t="n">
-        <v>548338</v>
+        <v>124812</v>
       </c>
       <c r="AC107" t="n">
-        <v>858359</v>
+        <v>213795</v>
       </c>
       <c r="AD107" t="n">
-        <v>892889</v>
+        <v>543962</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -19016,16 +19016,16 @@
         <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AH107" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="AI107" t="n">
         <v>0</v>
       </c>
       <c r="AJ107" t="n">
-        <v>20</v>
+        <v>-10</v>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
@@ -19033,25 +19033,25 @@
         </is>
       </c>
       <c r="AL107" t="n">
-        <v>-20</v>
+        <v>10</v>
       </c>
       <c r="AM107" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AN107" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AO107" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、離5MA偏遠、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
@@ -19066,17 +19066,17 @@
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -19605,12 +19605,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5706.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>鳳凰</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -19629,28 +19629,28 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>44</v>
+        <v>76.8</v>
       </c>
       <c r="G111" t="n">
-        <v>44.08</v>
+        <v>74.98</v>
       </c>
       <c r="H111" t="n">
-        <v>44.14</v>
+        <v>70.11</v>
       </c>
       <c r="I111" t="n">
-        <v>44.21</v>
+        <v>66.88</v>
       </c>
       <c r="J111" t="n">
-        <v>77570</v>
+        <v>29000616</v>
       </c>
       <c r="K111" t="n">
-        <v>63515</v>
+        <v>26437753</v>
       </c>
       <c r="L111" t="n">
-        <v>45.4</v>
+        <v>81</v>
       </c>
       <c r="M111" t="n">
-        <v>43.6</v>
+        <v>60</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -19658,28 +19658,28 @@
         </is>
       </c>
       <c r="O111" t="n">
-        <v>29850</v>
+        <v>-6334666</v>
       </c>
       <c r="P111" t="n">
-        <v>71841</v>
+        <v>-4310655</v>
       </c>
       <c r="Q111" t="n">
-        <v>96841</v>
+        <v>-8631987</v>
       </c>
       <c r="R111" t="n">
-        <v>113271</v>
+        <v>-9258248</v>
       </c>
       <c r="S111" t="n">
-        <v>29000</v>
+        <v>-5351754</v>
       </c>
       <c r="T111" t="n">
-        <v>78000</v>
+        <v>-4858993</v>
       </c>
       <c r="U111" t="n">
-        <v>116000</v>
+        <v>-9490346</v>
       </c>
       <c r="V111" t="n">
-        <v>160006</v>
+        <v>-10151213</v>
       </c>
       <c r="W111" t="n">
         <v>0</v>
@@ -19691,37 +19691,37 @@
         <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AA111" t="n">
-        <v>850</v>
+        <v>-982912</v>
       </c>
       <c r="AB111" t="n">
-        <v>-6159</v>
+        <v>548338</v>
       </c>
       <c r="AC111" t="n">
-        <v>-19159</v>
+        <v>858359</v>
       </c>
       <c r="AD111" t="n">
-        <v>-46735</v>
+        <v>892889</v>
       </c>
       <c r="AE111" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
-        <v>-45</v>
+        <v>55</v>
       </c>
       <c r="AH111" t="n">
-        <v>40</v>
+        <v>-55</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
       </c>
       <c r="AJ111" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
@@ -19729,25 +19729,25 @@
         </is>
       </c>
       <c r="AL111" t="n">
-        <v>-12</v>
+        <v>-20</v>
       </c>
       <c r="AM111" t="n">
-        <v>-120</v>
+        <v>-100</v>
       </c>
       <c r="AN111" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AO111" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
@@ -19762,29 +19762,29 @@
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人小幅買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>5706.TW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>鳳凰</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -19803,28 +19803,28 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1295</v>
+        <v>44</v>
       </c>
       <c r="G112" t="n">
-        <v>1290</v>
+        <v>44.08</v>
       </c>
       <c r="H112" t="n">
-        <v>1296.5</v>
+        <v>44.14</v>
       </c>
       <c r="I112" t="n">
-        <v>1308</v>
+        <v>44.21</v>
       </c>
       <c r="J112" t="n">
-        <v>1090000</v>
+        <v>77570</v>
       </c>
       <c r="K112" t="n">
-        <v>844200</v>
+        <v>63515</v>
       </c>
       <c r="L112" t="n">
-        <v>1445</v>
+        <v>45.4</v>
       </c>
       <c r="M112" t="n">
-        <v>1240</v>
+        <v>43.6</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -19832,28 +19832,28 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>29850</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>71841</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>96841</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>113271</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>78000</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
+        <v>116000</v>
       </c>
       <c r="V112" t="n">
-        <v>0</v>
+        <v>160006</v>
       </c>
       <c r="W112" t="n">
         <v>0</v>
@@ -19868,16 +19868,16 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>-6159</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>-19159</v>
       </c>
       <c r="AD112" t="n">
-        <v>0</v>
+        <v>-46735</v>
       </c>
       <c r="AE112" t="n">
         <v>-2</v>
@@ -19886,16 +19886,16 @@
         <v>-2</v>
       </c>
       <c r="AG112" t="n">
-        <v>-5</v>
+        <v>-45</v>
       </c>
       <c r="AH112" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
       </c>
       <c r="AJ112" t="n">
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
@@ -19903,25 +19903,25 @@
         </is>
       </c>
       <c r="AL112" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AM112" t="n">
-        <v>0</v>
+        <v>-120</v>
       </c>
       <c r="AN112" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AO112" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -19936,29 +19936,29 @@
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏買、5日法人小幅買超</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人小幅買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2027.TW</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -19977,28 +19977,28 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>47.9</v>
+        <v>1295</v>
       </c>
       <c r="G113" t="n">
-        <v>47.72</v>
+        <v>1290</v>
       </c>
       <c r="H113" t="n">
-        <v>47.33</v>
+        <v>1296.5</v>
       </c>
       <c r="I113" t="n">
-        <v>47.48</v>
+        <v>1308</v>
       </c>
       <c r="J113" t="n">
-        <v>10667229</v>
+        <v>1090000</v>
       </c>
       <c r="K113" t="n">
-        <v>10986542</v>
+        <v>844200</v>
       </c>
       <c r="L113" t="n">
-        <v>50.8</v>
+        <v>1445</v>
       </c>
       <c r="M113" t="n">
-        <v>44.95</v>
+        <v>1240</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -20006,70 +20006,70 @@
         </is>
       </c>
       <c r="O113" t="n">
-        <v>-31092</v>
+        <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>856175</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>-1208724</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>4272430</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>-133691</v>
+        <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>-2171980</v>
+        <v>0</v>
       </c>
       <c r="U113" t="n">
-        <v>-4044223</v>
+        <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>-771945</v>
+        <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>-12000</v>
+        <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>2163000</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>2161000</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>3662755</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>114599</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>865155</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>674499</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>1381620</v>
+        <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AF113" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AG113" t="n">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="AH113" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
       </c>
       <c r="AJ113" t="n">
-        <v>42</v>
+        <v>-2</v>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
@@ -20077,25 +20077,25 @@
         </is>
       </c>
       <c r="AL113" t="n">
-        <v>-46</v>
+        <v>0</v>
       </c>
       <c r="AM113" t="n">
-        <v>-109.52</v>
+        <v>0</v>
       </c>
       <c r="AN113" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AO113" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
@@ -20110,17 +20110,17 @@
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -20301,12 +20301,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2540.TW</t>
+          <t>2027.TW</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>愛山林</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -20325,28 +20325,28 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>47.45</v>
+        <v>47.9</v>
       </c>
       <c r="G115" t="n">
-        <v>48.1</v>
+        <v>47.72</v>
       </c>
       <c r="H115" t="n">
-        <v>48.83</v>
+        <v>47.33</v>
       </c>
       <c r="I115" t="n">
-        <v>48.6</v>
+        <v>47.48</v>
       </c>
       <c r="J115" t="n">
-        <v>501650</v>
+        <v>10667229</v>
       </c>
       <c r="K115" t="n">
-        <v>377311</v>
+        <v>10986542</v>
       </c>
       <c r="L115" t="n">
-        <v>54</v>
+        <v>50.8</v>
       </c>
       <c r="M115" t="n">
-        <v>46.6</v>
+        <v>44.95</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
@@ -20354,70 +20354,70 @@
         </is>
       </c>
       <c r="O115" t="n">
-        <v>-42246</v>
+        <v>-31092</v>
       </c>
       <c r="P115" t="n">
-        <v>-28173</v>
+        <v>856175</v>
       </c>
       <c r="Q115" t="n">
-        <v>36166</v>
+        <v>-1208724</v>
       </c>
       <c r="R115" t="n">
-        <v>151085</v>
+        <v>4272430</v>
       </c>
       <c r="S115" t="n">
-        <v>-34246</v>
+        <v>-133691</v>
       </c>
       <c r="T115" t="n">
-        <v>-15173</v>
+        <v>-2171980</v>
       </c>
       <c r="U115" t="n">
-        <v>41166</v>
+        <v>-4044223</v>
       </c>
       <c r="V115" t="n">
-        <v>77085</v>
+        <v>-771945</v>
       </c>
       <c r="W115" t="n">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>2163000</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2161000</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>3662755</v>
       </c>
       <c r="AA115" t="n">
-        <v>-8000</v>
+        <v>114599</v>
       </c>
       <c r="AB115" t="n">
-        <v>-13000</v>
+        <v>865155</v>
       </c>
       <c r="AC115" t="n">
-        <v>-5000</v>
+        <v>674499</v>
       </c>
       <c r="AD115" t="n">
-        <v>74000</v>
+        <v>1381620</v>
       </c>
       <c r="AE115" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="AF115" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="AG115" t="n">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="AH115" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AI115" t="n">
         <v>0</v>
       </c>
       <c r="AJ115" t="n">
-        <v>-4</v>
+        <v>42</v>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
@@ -20425,25 +20425,25 @@
         </is>
       </c>
       <c r="AL115" t="n">
-        <v>-4</v>
+        <v>-46</v>
       </c>
       <c r="AM115" t="n">
-        <v>-100</v>
+        <v>-109.52</v>
       </c>
       <c r="AN115" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO115" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
@@ -20458,17 +20458,17 @@
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -20649,17 +20649,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>00878.TW</t>
+          <t>8039.TW</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -20673,28 +20673,28 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>35.11</v>
+        <v>303.5</v>
       </c>
       <c r="G117" t="n">
-        <v>34.92</v>
+        <v>292.4</v>
       </c>
       <c r="H117" t="n">
-        <v>34.97</v>
+        <v>277.35</v>
       </c>
       <c r="I117" t="n">
-        <v>34.61</v>
+        <v>280.27</v>
       </c>
       <c r="J117" t="n">
-        <v>29467642</v>
+        <v>49438408</v>
       </c>
       <c r="K117" t="n">
-        <v>28103877</v>
+        <v>28956614</v>
       </c>
       <c r="L117" t="n">
-        <v>35.54</v>
+        <v>327.5</v>
       </c>
       <c r="M117" t="n">
-        <v>33.6</v>
+        <v>253</v>
       </c>
       <c r="N117" t="inlineStr">
         <is>
@@ -20702,52 +20702,52 @@
         </is>
       </c>
       <c r="O117" t="n">
-        <v>-2574561</v>
+        <v>-2637875</v>
       </c>
       <c r="P117" t="n">
-        <v>-37331509</v>
+        <v>-6336745</v>
       </c>
       <c r="Q117" t="n">
-        <v>-63157178</v>
+        <v>-6991492</v>
       </c>
       <c r="R117" t="n">
-        <v>-109469891</v>
+        <v>-8168964</v>
       </c>
       <c r="S117" t="n">
-        <v>564797</v>
+        <v>-2067648</v>
       </c>
       <c r="T117" t="n">
-        <v>-2590816</v>
+        <v>-5562267</v>
       </c>
       <c r="U117" t="n">
-        <v>-2642346</v>
+        <v>-7126699</v>
       </c>
       <c r="V117" t="n">
-        <v>-12087587</v>
+        <v>-6188046</v>
       </c>
       <c r="W117" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="X117" t="n">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>-1948000</v>
       </c>
       <c r="AA117" t="n">
-        <v>-3139358</v>
+        <v>-566227</v>
       </c>
       <c r="AB117" t="n">
-        <v>-34740693</v>
+        <v>-762478</v>
       </c>
       <c r="AC117" t="n">
-        <v>-60514832</v>
+        <v>94207</v>
       </c>
       <c r="AD117" t="n">
-        <v>-97382304</v>
+        <v>-32918</v>
       </c>
       <c r="AE117" t="n">
         <v>-8</v>
@@ -20765,7 +20765,7 @@
         <v>0</v>
       </c>
       <c r="AJ117" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
@@ -20773,25 +20773,25 @@
         </is>
       </c>
       <c r="AL117" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="AM117" t="n">
-        <v>33.33</v>
+        <v>-100</v>
       </c>
       <c r="AN117" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="AO117" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
@@ -20806,29 +20806,29 @@
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、接近20日高點、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、成交量放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>8039.TW</t>
+          <t>2540.TW</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>愛山林</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -20847,28 +20847,28 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>303.5</v>
+        <v>47.45</v>
       </c>
       <c r="G118" t="n">
-        <v>292.4</v>
+        <v>48.1</v>
       </c>
       <c r="H118" t="n">
-        <v>277.35</v>
+        <v>48.83</v>
       </c>
       <c r="I118" t="n">
-        <v>280.27</v>
+        <v>48.6</v>
       </c>
       <c r="J118" t="n">
-        <v>49438408</v>
+        <v>501650</v>
       </c>
       <c r="K118" t="n">
-        <v>28956614</v>
+        <v>377311</v>
       </c>
       <c r="L118" t="n">
-        <v>327.5</v>
+        <v>54</v>
       </c>
       <c r="M118" t="n">
-        <v>253</v>
+        <v>46.6</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -20876,52 +20876,52 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>-2637875</v>
+        <v>-42246</v>
       </c>
       <c r="P118" t="n">
-        <v>-6336745</v>
+        <v>-28173</v>
       </c>
       <c r="Q118" t="n">
-        <v>-6991492</v>
+        <v>36166</v>
       </c>
       <c r="R118" t="n">
-        <v>-8168964</v>
+        <v>151085</v>
       </c>
       <c r="S118" t="n">
-        <v>-2067648</v>
+        <v>-34246</v>
       </c>
       <c r="T118" t="n">
-        <v>-5562267</v>
+        <v>-15173</v>
       </c>
       <c r="U118" t="n">
-        <v>-7126699</v>
+        <v>41166</v>
       </c>
       <c r="V118" t="n">
-        <v>-6188046</v>
+        <v>77085</v>
       </c>
       <c r="W118" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="X118" t="n">
-        <v>-12000</v>
+        <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>41000</v>
+        <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>-1948000</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>-566227</v>
+        <v>-8000</v>
       </c>
       <c r="AB118" t="n">
-        <v>-762478</v>
+        <v>-13000</v>
       </c>
       <c r="AC118" t="n">
-        <v>94207</v>
+        <v>-5000</v>
       </c>
       <c r="AD118" t="n">
-        <v>-32918</v>
+        <v>74000</v>
       </c>
       <c r="AE118" t="n">
         <v>-8</v>
@@ -20930,10 +20930,10 @@
         <v>-8</v>
       </c>
       <c r="AG118" t="n">
-        <v>35</v>
+        <v>-20</v>
       </c>
       <c r="AH118" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AI118" t="n">
         <v>0</v>
@@ -20953,19 +20953,19 @@
         <v>-100</v>
       </c>
       <c r="AN118" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AO118" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
@@ -20980,34 +20980,34 @@
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>跌破5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>00878.TW</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -21021,28 +21021,28 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>250</v>
+        <v>35.11</v>
       </c>
       <c r="G119" t="n">
-        <v>256.4</v>
+        <v>34.92</v>
       </c>
       <c r="H119" t="n">
-        <v>258</v>
+        <v>34.97</v>
       </c>
       <c r="I119" t="n">
-        <v>257.52</v>
+        <v>34.61</v>
       </c>
       <c r="J119" t="n">
-        <v>3840000</v>
+        <v>29467642</v>
       </c>
       <c r="K119" t="n">
-        <v>7368400</v>
+        <v>28103877</v>
       </c>
       <c r="L119" t="n">
-        <v>288</v>
+        <v>35.54</v>
       </c>
       <c r="M119" t="n">
-        <v>213</v>
+        <v>33.6</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -21050,28 +21050,28 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>-2574561</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>-37331509</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>-63157178</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>-109469891</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>564797</v>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>-2590816</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>-2642346</v>
       </c>
       <c r="V119" t="n">
-        <v>0</v>
+        <v>-12087587</v>
       </c>
       <c r="W119" t="n">
         <v>0</v>
@@ -21086,16 +21086,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>-3139358</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>-34740693</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>-60514832</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>-97382304</v>
       </c>
       <c r="AE119" t="n">
         <v>-8</v>
@@ -21104,16 +21104,16 @@
         <v>-8</v>
       </c>
       <c r="AG119" t="n">
-        <v>-20</v>
+        <v>35</v>
       </c>
       <c r="AH119" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AI119" t="n">
         <v>0</v>
       </c>
       <c r="AJ119" t="n">
-        <v>18</v>
+        <v>-12</v>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
@@ -21121,25 +21121,25 @@
         </is>
       </c>
       <c r="AL119" t="n">
-        <v>-26</v>
+        <v>4</v>
       </c>
       <c r="AM119" t="n">
-        <v>-144.44</v>
+        <v>33.33</v>
       </c>
       <c r="AN119" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AO119" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
@@ -21154,17 +21154,17 @@
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、接近20日高點、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -18909,12 +18909,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3363.TWO</t>
+          <t>2485.TW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -18933,57 +18933,57 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>650</v>
+        <v>42.9</v>
       </c>
       <c r="G107" t="n">
-        <v>674.6</v>
+        <v>42.2</v>
       </c>
       <c r="H107" t="n">
-        <v>661.8</v>
+        <v>40.98</v>
       </c>
       <c r="I107" t="n">
-        <v>634.2</v>
+        <v>40.17</v>
       </c>
       <c r="J107" t="n">
-        <v>2392000</v>
+        <v>44642340</v>
       </c>
       <c r="K107" t="n">
-        <v>3434200</v>
+        <v>14370130</v>
       </c>
       <c r="L107" t="n">
-        <v>747</v>
+        <v>48</v>
       </c>
       <c r="M107" t="n">
-        <v>549</v>
+        <v>37.55</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>-9165746</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>-11791480</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>-11110299</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>-9922305</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>-8696383</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>-11510103</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>-10855440</v>
       </c>
       <c r="V107" t="n">
-        <v>0</v>
+        <v>-9733323</v>
       </c>
       <c r="W107" t="n">
         <v>0</v>
@@ -18992,40 +18992,40 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>-469363</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>-281377</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>-254913</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>-189036</v>
       </c>
       <c r="AE107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="AH107" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AI107" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ107" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
@@ -19033,25 +19033,25 @@
         </is>
       </c>
       <c r="AL107" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AM107" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AN107" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AO107" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、爆量後不追價、分數轉弱</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
@@ -19066,17 +19066,17 @@
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -19257,12 +19257,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2485.TW</t>
+          <t>2337.TW</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -19281,81 +19281,81 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>42.9</v>
+        <v>119.5</v>
       </c>
       <c r="G109" t="n">
-        <v>42.2</v>
+        <v>121.3</v>
       </c>
       <c r="H109" t="n">
-        <v>40.98</v>
+        <v>119.9</v>
       </c>
       <c r="I109" t="n">
-        <v>40.17</v>
+        <v>120.22</v>
       </c>
       <c r="J109" t="n">
-        <v>44642340</v>
+        <v>13171225</v>
       </c>
       <c r="K109" t="n">
-        <v>14370130</v>
+        <v>21148965</v>
       </c>
       <c r="L109" t="n">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="M109" t="n">
-        <v>37.55</v>
+        <v>114</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>-9165746</v>
+        <v>-619713</v>
       </c>
       <c r="P109" t="n">
-        <v>-11791480</v>
+        <v>1625775</v>
       </c>
       <c r="Q109" t="n">
-        <v>-11110299</v>
+        <v>11160616</v>
       </c>
       <c r="R109" t="n">
-        <v>-9922305</v>
+        <v>1981637</v>
       </c>
       <c r="S109" t="n">
-        <v>-8696383</v>
+        <v>-321098</v>
       </c>
       <c r="T109" t="n">
-        <v>-11510103</v>
+        <v>2171864</v>
       </c>
       <c r="U109" t="n">
-        <v>-10855440</v>
+        <v>11578156</v>
       </c>
       <c r="V109" t="n">
-        <v>-9733323</v>
+        <v>2336161</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>-79000</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>-55000</v>
       </c>
       <c r="Y109" t="n">
-        <v>54</v>
+        <v>-84000</v>
       </c>
       <c r="Z109" t="n">
-        <v>54</v>
+        <v>-703000</v>
       </c>
       <c r="AA109" t="n">
-        <v>-469363</v>
+        <v>-219615</v>
       </c>
       <c r="AB109" t="n">
-        <v>-281377</v>
+        <v>-491089</v>
       </c>
       <c r="AC109" t="n">
-        <v>-254913</v>
+        <v>-333540</v>
       </c>
       <c r="AD109" t="n">
-        <v>-189036</v>
+        <v>348476</v>
       </c>
       <c r="AE109" t="n">
         <v>0</v>
@@ -19364,16 +19364,16 @@
         <v>0</v>
       </c>
       <c r="AG109" t="n">
-        <v>65</v>
+        <v>-30</v>
       </c>
       <c r="AH109" t="n">
-        <v>-55</v>
+        <v>30</v>
       </c>
       <c r="AI109" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AJ109" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
@@ -19381,25 +19381,25 @@
         </is>
       </c>
       <c r="AL109" t="n">
-        <v>-15</v>
+        <v>-32</v>
       </c>
       <c r="AM109" t="n">
         <v>-100</v>
       </c>
       <c r="AN109" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AO109" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、爆量後不追價、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
@@ -19414,29 +19414,29 @@
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2337.TW</t>
+          <t>4966.TWO</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -19455,28 +19455,28 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>119.5</v>
+        <v>563</v>
       </c>
       <c r="G110" t="n">
-        <v>121.3</v>
+        <v>570.8</v>
       </c>
       <c r="H110" t="n">
-        <v>119.9</v>
+        <v>570.8</v>
       </c>
       <c r="I110" t="n">
-        <v>120.22</v>
+        <v>558.2</v>
       </c>
       <c r="J110" t="n">
-        <v>13171225</v>
+        <v>603000</v>
       </c>
       <c r="K110" t="n">
-        <v>21148965</v>
+        <v>356600</v>
       </c>
       <c r="L110" t="n">
-        <v>130</v>
+        <v>586</v>
       </c>
       <c r="M110" t="n">
-        <v>114</v>
+        <v>521</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -19484,70 +19484,70 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>-619713</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>1625775</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>11160616</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>1981637</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>-321098</v>
+        <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>2171864</v>
+        <v>0</v>
       </c>
       <c r="U110" t="n">
-        <v>11578156</v>
+        <v>0</v>
       </c>
       <c r="V110" t="n">
-        <v>2336161</v>
+        <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>-79000</v>
+        <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>-55000</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>-84000</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>-703000</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>-219615</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>-491089</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
-        <v>-333540</v>
+        <v>0</v>
       </c>
       <c r="AD110" t="n">
-        <v>348476</v>
+        <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AG110" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
       <c r="AH110" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
       </c>
       <c r="AJ110" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
@@ -19555,16 +19555,16 @@
         </is>
       </c>
       <c r="AL110" t="n">
-        <v>-32</v>
+        <v>-24</v>
       </c>
       <c r="AM110" t="n">
-        <v>-100</v>
+        <v>-109.09</v>
       </c>
       <c r="AN110" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO110" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
@@ -19588,29 +19588,29 @@
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、成交量放大</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4966.TWO</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -19629,28 +19629,28 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>563</v>
+        <v>256</v>
       </c>
       <c r="G111" t="n">
-        <v>570.8</v>
+        <v>253.3</v>
       </c>
       <c r="H111" t="n">
-        <v>570.8</v>
+        <v>252.65</v>
       </c>
       <c r="I111" t="n">
-        <v>558.2</v>
+        <v>251.45</v>
       </c>
       <c r="J111" t="n">
-        <v>603000</v>
+        <v>96969300</v>
       </c>
       <c r="K111" t="n">
-        <v>356600</v>
+        <v>47591768</v>
       </c>
       <c r="L111" t="n">
-        <v>586</v>
+        <v>266.5</v>
       </c>
       <c r="M111" t="n">
-        <v>521</v>
+        <v>243.5</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -19658,70 +19658,70 @@
         </is>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>-20729626</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>-22253598</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>-11981903</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>-23031186</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>-19982641</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>-22056883</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>-12332291</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
+        <v>-26145306</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>-1140948</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>-981245</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>-1013493</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>51138</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>393963</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>784530</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>1363881</v>
       </c>
       <c r="AD111" t="n">
-        <v>0</v>
+        <v>3062982</v>
       </c>
       <c r="AE111" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AF111" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AG111" t="n">
-        <v>-5</v>
+        <v>65</v>
       </c>
       <c r="AH111" t="n">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
       </c>
       <c r="AJ111" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
@@ -19729,25 +19729,25 @@
         </is>
       </c>
       <c r="AL111" t="n">
-        <v>-24</v>
+        <v>-62</v>
       </c>
       <c r="AM111" t="n">
-        <v>-109.09</v>
+        <v>-106.9</v>
       </c>
       <c r="AN111" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="AO111" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
@@ -19762,29 +19762,29 @@
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>跌破5日線、成交量放大</t>
+          <t>站上5日線、多頭排列、爆量</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -19803,28 +19803,28 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>256</v>
+        <v>8.5</v>
       </c>
       <c r="G112" t="n">
-        <v>253.3</v>
+        <v>8.44</v>
       </c>
       <c r="H112" t="n">
-        <v>252.65</v>
+        <v>8.43</v>
       </c>
       <c r="I112" t="n">
-        <v>251.45</v>
+        <v>8.5</v>
       </c>
       <c r="J112" t="n">
-        <v>96969300</v>
+        <v>21971312</v>
       </c>
       <c r="K112" t="n">
-        <v>47591768</v>
+        <v>16800845</v>
       </c>
       <c r="L112" t="n">
-        <v>266.5</v>
+        <v>8.93</v>
       </c>
       <c r="M112" t="n">
-        <v>243.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -19832,52 +19832,52 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>-20729626</v>
+        <v>6750273</v>
       </c>
       <c r="P112" t="n">
-        <v>-22253598</v>
+        <v>1810929</v>
       </c>
       <c r="Q112" t="n">
-        <v>-11981903</v>
+        <v>-2545757</v>
       </c>
       <c r="R112" t="n">
-        <v>-23031186</v>
+        <v>1073223</v>
       </c>
       <c r="S112" t="n">
-        <v>-19982641</v>
+        <v>6598000</v>
       </c>
       <c r="T112" t="n">
-        <v>-22056883</v>
+        <v>1657600</v>
       </c>
       <c r="U112" t="n">
-        <v>-12332291</v>
+        <v>-3051485</v>
       </c>
       <c r="V112" t="n">
-        <v>-26145306</v>
+        <v>820014</v>
       </c>
       <c r="W112" t="n">
-        <v>-1140948</v>
+        <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>-981245</v>
+        <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>-1013493</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>51138</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>393963</v>
+        <v>152273</v>
       </c>
       <c r="AB112" t="n">
-        <v>784530</v>
+        <v>153329</v>
       </c>
       <c r="AC112" t="n">
-        <v>1363881</v>
+        <v>505728</v>
       </c>
       <c r="AD112" t="n">
-        <v>3062982</v>
+        <v>253209</v>
       </c>
       <c r="AE112" t="n">
         <v>-4</v>
@@ -19886,16 +19886,16 @@
         <v>-4</v>
       </c>
       <c r="AG112" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AH112" t="n">
-        <v>-75</v>
+        <v>-30</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
       </c>
       <c r="AJ112" t="n">
-        <v>58</v>
+        <v>-34</v>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
@@ -19903,16 +19903,16 @@
         </is>
       </c>
       <c r="AL112" t="n">
-        <v>-62</v>
+        <v>30</v>
       </c>
       <c r="AM112" t="n">
-        <v>-106.9</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="AN112" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AO112" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -19936,29 +19936,29 @@
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量</t>
+          <t>站上5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>2345.TW</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -19977,28 +19977,28 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>8.5</v>
+        <v>2050</v>
       </c>
       <c r="G113" t="n">
-        <v>8.44</v>
+        <v>1953</v>
       </c>
       <c r="H113" t="n">
-        <v>8.43</v>
+        <v>1911.5</v>
       </c>
       <c r="I113" t="n">
-        <v>8.5</v>
+        <v>1912.25</v>
       </c>
       <c r="J113" t="n">
-        <v>21971312</v>
+        <v>3700393</v>
       </c>
       <c r="K113" t="n">
-        <v>16800845</v>
+        <v>5682379</v>
       </c>
       <c r="L113" t="n">
-        <v>8.93</v>
+        <v>2155</v>
       </c>
       <c r="M113" t="n">
-        <v>8.300000000000001</v>
+        <v>1770</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -20006,52 +20006,52 @@
         </is>
       </c>
       <c r="O113" t="n">
-        <v>6750273</v>
+        <v>-296362</v>
       </c>
       <c r="P113" t="n">
-        <v>1810929</v>
+        <v>-491573</v>
       </c>
       <c r="Q113" t="n">
-        <v>-2545757</v>
+        <v>-1470895</v>
       </c>
       <c r="R113" t="n">
-        <v>1073223</v>
+        <v>-5219398</v>
       </c>
       <c r="S113" t="n">
-        <v>6598000</v>
+        <v>31110</v>
       </c>
       <c r="T113" t="n">
-        <v>1657600</v>
+        <v>-167803</v>
       </c>
       <c r="U113" t="n">
-        <v>-3051485</v>
+        <v>1393961</v>
       </c>
       <c r="V113" t="n">
-        <v>820014</v>
+        <v>195387</v>
       </c>
       <c r="W113" t="n">
-        <v>0</v>
+        <v>-321020</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>-399291</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>-3070291</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>-5781342</v>
       </c>
       <c r="AA113" t="n">
-        <v>152273</v>
+        <v>-6452</v>
       </c>
       <c r="AB113" t="n">
-        <v>153329</v>
+        <v>75521</v>
       </c>
       <c r="AC113" t="n">
-        <v>505728</v>
+        <v>205435</v>
       </c>
       <c r="AD113" t="n">
-        <v>253209</v>
+        <v>366557</v>
       </c>
       <c r="AE113" t="n">
         <v>-4</v>
@@ -20060,42 +20060,40 @@
         <v>-4</v>
       </c>
       <c r="AG113" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AL113" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AM113" t="inlineStr"/>
+      <c r="AN113" t="n">
         <v>20</v>
       </c>
-      <c r="AH113" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AI113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ113" t="n">
-        <v>-34</v>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AL113" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM113" t="n">
-        <v>88.23999999999999</v>
-      </c>
-      <c r="AN113" t="n">
-        <v>50</v>
-      </c>
       <c r="AO113" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
@@ -20110,29 +20108,29 @@
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、黃金交叉、量能未放大</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、黃金交叉、量能未放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2345.TW</t>
+          <t>8299.TWO</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -20151,28 +20149,28 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2050</v>
+        <v>2090</v>
       </c>
       <c r="G114" t="n">
-        <v>1953</v>
+        <v>2109</v>
       </c>
       <c r="H114" t="n">
-        <v>1911.5</v>
+        <v>2133.5</v>
       </c>
       <c r="I114" t="n">
-        <v>1912.25</v>
+        <v>2080.25</v>
       </c>
       <c r="J114" t="n">
-        <v>3700393</v>
+        <v>1465000</v>
       </c>
       <c r="K114" t="n">
-        <v>5682379</v>
+        <v>2227400</v>
       </c>
       <c r="L114" t="n">
-        <v>2155</v>
+        <v>2350</v>
       </c>
       <c r="M114" t="n">
-        <v>1770</v>
+        <v>1900</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
@@ -20180,70 +20178,70 @@
         </is>
       </c>
       <c r="O114" t="n">
-        <v>-296362</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>-491573</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>-1470895</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>-5219398</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>31110</v>
+        <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>-167803</v>
+        <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>1393961</v>
+        <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>195387</v>
+        <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>-321020</v>
+        <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>-399291</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>-3070291</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>-5781342</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>-6452</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>75521</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>205435</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
-        <v>366557</v>
+        <v>0</v>
       </c>
       <c r="AE114" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ114" t="n">
         <v>-4</v>
-      </c>
-      <c r="AF114" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AG114" t="n">
-        <v>45</v>
-      </c>
-      <c r="AH114" t="n">
-        <v>-55</v>
-      </c>
-      <c r="AI114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ114" t="n">
-        <v>0</v>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
@@ -20253,12 +20251,14 @@
       <c r="AL114" t="n">
         <v>-4</v>
       </c>
-      <c r="AM114" t="inlineStr"/>
+      <c r="AM114" t="n">
+        <v>-100</v>
+      </c>
       <c r="AN114" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO114" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
@@ -20282,17 +20282,17 @@
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、黃金交叉、量能未放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -20473,12 +20473,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>8299.TWO</t>
+          <t>3363.TWO</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -20497,28 +20497,28 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>2090</v>
+        <v>650</v>
       </c>
       <c r="G116" t="n">
-        <v>2109</v>
+        <v>655</v>
       </c>
       <c r="H116" t="n">
-        <v>2133.5</v>
+        <v>654.3</v>
       </c>
       <c r="I116" t="n">
-        <v>2080.25</v>
+        <v>671.25</v>
       </c>
       <c r="J116" t="n">
-        <v>1465000</v>
+        <v>2392000</v>
       </c>
       <c r="K116" t="n">
-        <v>2227400</v>
+        <v>2361200</v>
       </c>
       <c r="L116" t="n">
-        <v>2350</v>
+        <v>756</v>
       </c>
       <c r="M116" t="n">
-        <v>1900</v>
+        <v>629</v>
       </c>
       <c r="N116" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>0</v>
       </c>
       <c r="AJ116" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
@@ -20597,10 +20597,10 @@
         </is>
       </c>
       <c r="AL116" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="AM116" t="n">
-        <v>-100</v>
+        <v>-500</v>
       </c>
       <c r="AN116" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
@@ -20630,7 +20630,7 @@
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
@@ -20640,7 +20640,7 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -11433,12 +11433,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>2368.TW</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -11457,99 +11457,99 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>258.5</v>
+        <v>1260</v>
       </c>
       <c r="G64" t="n">
-        <v>252.2</v>
+        <v>1159</v>
       </c>
       <c r="H64" t="n">
-        <v>246.7</v>
+        <v>1124.5</v>
       </c>
       <c r="I64" t="n">
-        <v>242.47</v>
+        <v>1078.45</v>
       </c>
       <c r="J64" t="n">
-        <v>8406000</v>
+        <v>21853878</v>
       </c>
       <c r="K64" t="n">
-        <v>5564400</v>
+        <v>12939812</v>
       </c>
       <c r="L64" t="n">
-        <v>264</v>
+        <v>1295</v>
       </c>
       <c r="M64" t="n">
-        <v>223</v>
+        <v>950</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>2391149</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>3081167</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>-1712142</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>-7087735</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>-172640</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>120279</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>-5746786</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>-14169928</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>2644500</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2651181</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>3752181</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>5899754</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>-80711</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>309707</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>282463</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1182439</v>
       </c>
       <c r="AE64" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF64" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG64" t="n">
         <v>60</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AJ64" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
@@ -11557,25 +11557,25 @@
         </is>
       </c>
       <c r="AL64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM64" t="n">
-        <v>33.33</v>
+        <v>43.75</v>
       </c>
       <c r="AN64" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AO64" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、離5MA偏遠、均線多頭排列、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
@@ -11590,29 +11590,29 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、成交量放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、成交量放大、帶量突破20日高點、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2368.TW</t>
+          <t>2882.TW</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -11631,99 +11631,99 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1260</v>
+        <v>112</v>
       </c>
       <c r="G65" t="n">
-        <v>1159</v>
+        <v>111.3</v>
       </c>
       <c r="H65" t="n">
-        <v>1124.5</v>
+        <v>111.5</v>
       </c>
       <c r="I65" t="n">
-        <v>1078.45</v>
+        <v>111.6</v>
       </c>
       <c r="J65" t="n">
-        <v>21853878</v>
+        <v>17740300</v>
       </c>
       <c r="K65" t="n">
-        <v>12939812</v>
+        <v>17588534</v>
       </c>
       <c r="L65" t="n">
-        <v>1295</v>
+        <v>117</v>
       </c>
       <c r="M65" t="n">
-        <v>950</v>
+        <v>108</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>2391149</v>
+        <v>1546841</v>
       </c>
       <c r="P65" t="n">
-        <v>3081167</v>
+        <v>5962141</v>
       </c>
       <c r="Q65" t="n">
-        <v>-1712142</v>
+        <v>4149102</v>
       </c>
       <c r="R65" t="n">
-        <v>-7087735</v>
+        <v>9015976</v>
       </c>
       <c r="S65" t="n">
-        <v>-172640</v>
+        <v>-520399</v>
       </c>
       <c r="T65" t="n">
-        <v>120279</v>
+        <v>1043313</v>
       </c>
       <c r="U65" t="n">
-        <v>-5746786</v>
+        <v>-6156277</v>
       </c>
       <c r="V65" t="n">
-        <v>-14169928</v>
+        <v>-3969084</v>
       </c>
       <c r="W65" t="n">
-        <v>2644500</v>
+        <v>1994000</v>
       </c>
       <c r="X65" t="n">
-        <v>2651181</v>
+        <v>4934028</v>
       </c>
       <c r="Y65" t="n">
-        <v>3752181</v>
+        <v>10401028</v>
       </c>
       <c r="Z65" t="n">
-        <v>5899754</v>
+        <v>13192751</v>
       </c>
       <c r="AA65" t="n">
-        <v>-80711</v>
+        <v>73240</v>
       </c>
       <c r="AB65" t="n">
-        <v>309707</v>
+        <v>-15200</v>
       </c>
       <c r="AC65" t="n">
-        <v>282463</v>
+        <v>-95649</v>
       </c>
       <c r="AD65" t="n">
-        <v>1182439</v>
+        <v>-207691</v>
       </c>
       <c r="AE65" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF65" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG65" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH65" t="n">
         <v>60</v>
       </c>
-      <c r="AH65" t="n">
-        <v>-15</v>
-      </c>
       <c r="AI65" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
@@ -11731,16 +11731,16 @@
         </is>
       </c>
       <c r="AL65" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AM65" t="n">
-        <v>43.75</v>
+        <v>22.22</v>
       </c>
       <c r="AN65" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="AO65" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>DT尚未轉強、離5MA偏遠、均線多頭排列、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、分數剛升溫</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
@@ -11764,17 +11764,17 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、成交量放大、帶量突破20日高點、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -12129,12 +12129,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6770.TW</t>
+          <t>5439.TWO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -12153,28 +12153,28 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>74.3</v>
+        <v>264.5</v>
       </c>
       <c r="G68" t="n">
-        <v>75.28</v>
+        <v>256.7</v>
       </c>
       <c r="H68" t="n">
-        <v>73.83</v>
+        <v>254.1</v>
       </c>
       <c r="I68" t="n">
-        <v>72.64</v>
+        <v>252.3</v>
       </c>
       <c r="J68" t="n">
-        <v>68121469</v>
+        <v>2781000</v>
       </c>
       <c r="K68" t="n">
-        <v>120549328</v>
+        <v>2132800</v>
       </c>
       <c r="L68" t="n">
-        <v>78.09999999999999</v>
+        <v>270</v>
       </c>
       <c r="M68" t="n">
-        <v>66.7</v>
+        <v>237</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -12182,52 +12182,52 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>-16605183</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>16104112</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>63623637</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>45110609</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>-15521747</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>14300106</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>59044059</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>40441827</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>-340000</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>-38062</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1938</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>51503</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>-743436</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1842068</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>4577640</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>4617279</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>22</v>
@@ -12236,42 +12236,42 @@
         <v>22</v>
       </c>
       <c r="AG68" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AL68" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>-8.33</v>
+      </c>
+      <c r="AN68" t="n">
         <v>50</v>
       </c>
-      <c r="AI68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AL68" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>-47.62</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>10</v>
-      </c>
       <c r="AO68" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -12477,12 +12477,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>2420.TW</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>新巨</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -12501,28 +12501,28 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>264.5</v>
+        <v>57</v>
       </c>
       <c r="G70" t="n">
-        <v>256.7</v>
+        <v>57.18</v>
       </c>
       <c r="H70" t="n">
-        <v>254.1</v>
+        <v>55.49</v>
       </c>
       <c r="I70" t="n">
-        <v>252.3</v>
+        <v>54.62</v>
       </c>
       <c r="J70" t="n">
-        <v>2781000</v>
+        <v>483846</v>
       </c>
       <c r="K70" t="n">
-        <v>2132800</v>
+        <v>726713</v>
       </c>
       <c r="L70" t="n">
-        <v>270</v>
+        <v>59.5</v>
       </c>
       <c r="M70" t="n">
-        <v>237</v>
+        <v>52.9</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -12530,28 +12530,28 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>-36886</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>244833</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>889468</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>969186</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>-34886</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>243983</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>890761</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>982762</v>
       </c>
       <c r="W70" t="n">
         <v>0</v>
@@ -12560,22 +12560,22 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>-1306</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>-13589</v>
       </c>
       <c r="AE70" t="n">
         <v>22</v>
@@ -12584,16 +12584,16 @@
         <v>22</v>
       </c>
       <c r="AG70" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
       </c>
       <c r="AJ70" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
@@ -12601,25 +12601,25 @@
         </is>
       </c>
       <c r="AL70" t="n">
-        <v>-2</v>
+        <v>-28</v>
       </c>
       <c r="AM70" t="n">
-        <v>-8.33</v>
+        <v>-56</v>
       </c>
       <c r="AN70" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="AO70" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
@@ -12634,17 +12634,17 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -12999,12 +12999,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2420.TW</t>
+          <t>6770.TW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>新巨</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -13023,28 +13023,28 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>57</v>
+        <v>74.3</v>
       </c>
       <c r="G73" t="n">
-        <v>57.18</v>
+        <v>75.28</v>
       </c>
       <c r="H73" t="n">
-        <v>55.49</v>
+        <v>73.83</v>
       </c>
       <c r="I73" t="n">
-        <v>54.62</v>
+        <v>72.64</v>
       </c>
       <c r="J73" t="n">
-        <v>483846</v>
+        <v>68121469</v>
       </c>
       <c r="K73" t="n">
-        <v>726713</v>
+        <v>120549328</v>
       </c>
       <c r="L73" t="n">
-        <v>59.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="M73" t="n">
-        <v>52.9</v>
+        <v>66.7</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -13052,52 +13052,52 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>-36886</v>
+        <v>-16605183</v>
       </c>
       <c r="P73" t="n">
-        <v>244833</v>
+        <v>16104112</v>
       </c>
       <c r="Q73" t="n">
-        <v>889468</v>
+        <v>63623637</v>
       </c>
       <c r="R73" t="n">
-        <v>969186</v>
+        <v>45110609</v>
       </c>
       <c r="S73" t="n">
-        <v>-34886</v>
+        <v>-15521747</v>
       </c>
       <c r="T73" t="n">
-        <v>243983</v>
+        <v>14300106</v>
       </c>
       <c r="U73" t="n">
-        <v>890761</v>
+        <v>59044059</v>
       </c>
       <c r="V73" t="n">
-        <v>982762</v>
+        <v>40441827</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>-340000</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>-38062</v>
       </c>
       <c r="Y73" t="n">
-        <v>13</v>
+        <v>1938</v>
       </c>
       <c r="Z73" t="n">
-        <v>13</v>
+        <v>51503</v>
       </c>
       <c r="AA73" t="n">
-        <v>-2000</v>
+        <v>-743436</v>
       </c>
       <c r="AB73" t="n">
-        <v>850</v>
+        <v>1842068</v>
       </c>
       <c r="AC73" t="n">
-        <v>-1306</v>
+        <v>4577640</v>
       </c>
       <c r="AD73" t="n">
-        <v>-13589</v>
+        <v>4617279</v>
       </c>
       <c r="AE73" t="n">
         <v>22</v>
@@ -13115,7 +13115,7 @@
         <v>0</v>
       </c>
       <c r="AJ73" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
@@ -13123,10 +13123,10 @@
         </is>
       </c>
       <c r="AL73" t="n">
-        <v>-28</v>
+        <v>-20</v>
       </c>
       <c r="AM73" t="n">
-        <v>-56</v>
+        <v>-47.62</v>
       </c>
       <c r="AN73" t="n">
         <v>10</v>
@@ -13173,12 +13173,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2882.TW</t>
+          <t>6214.TW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -13197,28 +13197,28 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>112</v>
+        <v>188.5</v>
       </c>
       <c r="G74" t="n">
-        <v>111.3</v>
+        <v>188.5</v>
       </c>
       <c r="H74" t="n">
-        <v>111.5</v>
+        <v>189.4</v>
       </c>
       <c r="I74" t="n">
-        <v>111.6</v>
+        <v>189.18</v>
       </c>
       <c r="J74" t="n">
-        <v>17740300</v>
+        <v>410803</v>
       </c>
       <c r="K74" t="n">
-        <v>17588534</v>
+        <v>776321</v>
       </c>
       <c r="L74" t="n">
-        <v>117</v>
+        <v>195</v>
       </c>
       <c r="M74" t="n">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -13226,70 +13226,70 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>1546841</v>
+        <v>139606</v>
       </c>
       <c r="P74" t="n">
-        <v>5962141</v>
+        <v>251503</v>
       </c>
       <c r="Q74" t="n">
-        <v>4149102</v>
+        <v>538748</v>
       </c>
       <c r="R74" t="n">
-        <v>9015976</v>
+        <v>1087260</v>
       </c>
       <c r="S74" t="n">
-        <v>-520399</v>
+        <v>126448</v>
       </c>
       <c r="T74" t="n">
-        <v>1043313</v>
+        <v>220015</v>
       </c>
       <c r="U74" t="n">
-        <v>-6156277</v>
+        <v>533843</v>
       </c>
       <c r="V74" t="n">
-        <v>-3969084</v>
+        <v>1111835</v>
       </c>
       <c r="W74" t="n">
-        <v>1994000</v>
+        <v>13158</v>
       </c>
       <c r="X74" t="n">
-        <v>4934028</v>
+        <v>33158</v>
       </c>
       <c r="Y74" t="n">
-        <v>10401028</v>
+        <v>33158</v>
       </c>
       <c r="Z74" t="n">
-        <v>13192751</v>
+        <v>22158</v>
       </c>
       <c r="AA74" t="n">
-        <v>73240</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>-15200</v>
+        <v>-1670</v>
       </c>
       <c r="AC74" t="n">
-        <v>-95649</v>
+        <v>-28253</v>
       </c>
       <c r="AD74" t="n">
-        <v>-207691</v>
+        <v>-46733</v>
       </c>
       <c r="AE74" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF74" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG74" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
       <c r="AH74" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
       </c>
       <c r="AJ74" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
@@ -13300,22 +13300,22 @@
         <v>4</v>
       </c>
       <c r="AM74" t="n">
-        <v>22.22</v>
+        <v>25</v>
       </c>
       <c r="AN74" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="AO74" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
@@ -13330,17 +13330,17 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -13521,12 +13521,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6214.TW</t>
+          <t>3231.TW</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -13545,28 +13545,28 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>188.5</v>
+        <v>189.5</v>
       </c>
       <c r="G76" t="n">
-        <v>188.5</v>
+        <v>188.1</v>
       </c>
       <c r="H76" t="n">
-        <v>189.4</v>
+        <v>185.75</v>
       </c>
       <c r="I76" t="n">
-        <v>189.18</v>
+        <v>186</v>
       </c>
       <c r="J76" t="n">
-        <v>410803</v>
+        <v>30082562</v>
       </c>
       <c r="K76" t="n">
-        <v>776321</v>
+        <v>38894030</v>
       </c>
       <c r="L76" t="n">
-        <v>195</v>
+        <v>200.5</v>
       </c>
       <c r="M76" t="n">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -13574,52 +13574,52 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>139606</v>
+        <v>-4980223</v>
       </c>
       <c r="P76" t="n">
-        <v>251503</v>
+        <v>-1997677</v>
       </c>
       <c r="Q76" t="n">
-        <v>538748</v>
+        <v>27029704</v>
       </c>
       <c r="R76" t="n">
-        <v>1087260</v>
+        <v>-1571024</v>
       </c>
       <c r="S76" t="n">
-        <v>126448</v>
+        <v>-3550113</v>
       </c>
       <c r="T76" t="n">
-        <v>220015</v>
+        <v>159346</v>
       </c>
       <c r="U76" t="n">
-        <v>533843</v>
+        <v>27642933</v>
       </c>
       <c r="V76" t="n">
-        <v>1111835</v>
+        <v>11124840</v>
       </c>
       <c r="W76" t="n">
-        <v>13158</v>
+        <v>-1146000</v>
       </c>
       <c r="X76" t="n">
-        <v>33158</v>
+        <v>-2672095</v>
       </c>
       <c r="Y76" t="n">
-        <v>33158</v>
+        <v>-1972095</v>
       </c>
       <c r="Z76" t="n">
-        <v>22158</v>
+        <v>-15173366</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>-284110</v>
       </c>
       <c r="AB76" t="n">
-        <v>-1670</v>
+        <v>515072</v>
       </c>
       <c r="AC76" t="n">
-        <v>-28253</v>
+        <v>1358866</v>
       </c>
       <c r="AD76" t="n">
-        <v>-46733</v>
+        <v>2477502</v>
       </c>
       <c r="AE76" t="n">
         <v>20</v>
@@ -13628,16 +13628,16 @@
         <v>20</v>
       </c>
       <c r="AG76" t="n">
-        <v>-30</v>
+        <v>20</v>
       </c>
       <c r="AH76" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
       </c>
       <c r="AJ76" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
@@ -13645,25 +13645,25 @@
         </is>
       </c>
       <c r="AL76" t="n">
-        <v>4</v>
+        <v>-26</v>
       </c>
       <c r="AM76" t="n">
-        <v>25</v>
+        <v>-56.52</v>
       </c>
       <c r="AN76" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AO76" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
@@ -13678,29 +13678,29 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3231.TW</t>
+          <t>2891.TW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -13719,28 +13719,28 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>189.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>188.1</v>
+        <v>67.88</v>
       </c>
       <c r="H77" t="n">
-        <v>185.75</v>
+        <v>68.55</v>
       </c>
       <c r="I77" t="n">
-        <v>186</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>30082562</v>
+        <v>30124093</v>
       </c>
       <c r="K77" t="n">
-        <v>38894030</v>
+        <v>24110279</v>
       </c>
       <c r="L77" t="n">
-        <v>200.5</v>
+        <v>72</v>
       </c>
       <c r="M77" t="n">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -13748,70 +13748,70 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>-4980223</v>
+        <v>11295525</v>
       </c>
       <c r="P77" t="n">
-        <v>-1997677</v>
+        <v>11994855</v>
       </c>
       <c r="Q77" t="n">
-        <v>27029704</v>
+        <v>428277</v>
       </c>
       <c r="R77" t="n">
-        <v>-1571024</v>
+        <v>1308587</v>
       </c>
       <c r="S77" t="n">
-        <v>-3550113</v>
+        <v>9406803</v>
       </c>
       <c r="T77" t="n">
-        <v>159346</v>
+        <v>6382698</v>
       </c>
       <c r="U77" t="n">
-        <v>27642933</v>
+        <v>-12308884</v>
       </c>
       <c r="V77" t="n">
-        <v>11124840</v>
+        <v>-19286323</v>
       </c>
       <c r="W77" t="n">
-        <v>-1146000</v>
+        <v>1335000</v>
       </c>
       <c r="X77" t="n">
-        <v>-2672095</v>
+        <v>3502228</v>
       </c>
       <c r="Y77" t="n">
-        <v>-1972095</v>
+        <v>9283998</v>
       </c>
       <c r="Z77" t="n">
-        <v>-15173366</v>
+        <v>14120806</v>
       </c>
       <c r="AA77" t="n">
-        <v>-284110</v>
+        <v>553722</v>
       </c>
       <c r="AB77" t="n">
-        <v>515072</v>
+        <v>2109929</v>
       </c>
       <c r="AC77" t="n">
-        <v>1358866</v>
+        <v>3453163</v>
       </c>
       <c r="AD77" t="n">
-        <v>2477502</v>
+        <v>6474104</v>
       </c>
       <c r="AE77" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF77" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG77" t="n">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="AH77" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
       </c>
       <c r="AJ77" t="n">
-        <v>46</v>
+        <v>-24</v>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
@@ -13819,62 +13819,62 @@
         </is>
       </c>
       <c r="AL77" t="n">
-        <v>-26</v>
+        <v>42</v>
       </c>
       <c r="AM77" t="n">
-        <v>-56.52</v>
+        <v>175</v>
       </c>
       <c r="AN77" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AO77" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2891.TW</t>
+          <t>1102.TW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -13893,28 +13893,28 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>68.40000000000001</v>
+        <v>35.45</v>
       </c>
       <c r="G78" t="n">
-        <v>67.88</v>
+        <v>35.53</v>
       </c>
       <c r="H78" t="n">
-        <v>68.55</v>
+        <v>35.53</v>
       </c>
       <c r="I78" t="n">
-        <v>68.56999999999999</v>
+        <v>35.36</v>
       </c>
       <c r="J78" t="n">
-        <v>30124093</v>
+        <v>6937959</v>
       </c>
       <c r="K78" t="n">
-        <v>24110279</v>
+        <v>7014235</v>
       </c>
       <c r="L78" t="n">
-        <v>72</v>
+        <v>36.1</v>
       </c>
       <c r="M78" t="n">
-        <v>66</v>
+        <v>34.6</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
@@ -13922,52 +13922,52 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>11295525</v>
+        <v>1905533</v>
       </c>
       <c r="P78" t="n">
-        <v>11994855</v>
+        <v>1876427</v>
       </c>
       <c r="Q78" t="n">
-        <v>428277</v>
+        <v>5067245</v>
       </c>
       <c r="R78" t="n">
-        <v>1308587</v>
+        <v>14053901</v>
       </c>
       <c r="S78" t="n">
-        <v>9406803</v>
+        <v>2039207</v>
       </c>
       <c r="T78" t="n">
-        <v>6382698</v>
+        <v>1819501</v>
       </c>
       <c r="U78" t="n">
-        <v>-12308884</v>
+        <v>9184767</v>
       </c>
       <c r="V78" t="n">
-        <v>-19286323</v>
+        <v>16936821</v>
       </c>
       <c r="W78" t="n">
-        <v>1335000</v>
+        <v>-299000</v>
       </c>
       <c r="X78" t="n">
-        <v>3502228</v>
+        <v>-579160</v>
       </c>
       <c r="Y78" t="n">
-        <v>9283998</v>
+        <v>-5258681</v>
       </c>
       <c r="Z78" t="n">
-        <v>14120806</v>
+        <v>-4720714</v>
       </c>
       <c r="AA78" t="n">
-        <v>553722</v>
+        <v>165326</v>
       </c>
       <c r="AB78" t="n">
-        <v>2109929</v>
+        <v>636086</v>
       </c>
       <c r="AC78" t="n">
-        <v>3453163</v>
+        <v>1141159</v>
       </c>
       <c r="AD78" t="n">
-        <v>6474104</v>
+        <v>1837794</v>
       </c>
       <c r="AE78" t="n">
         <v>18</v>
@@ -13976,16 +13976,16 @@
         <v>18</v>
       </c>
       <c r="AG78" t="n">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="AH78" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
       </c>
       <c r="AJ78" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
@@ -13993,25 +13993,23 @@
         </is>
       </c>
       <c r="AL78" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM78" t="n">
-        <v>175</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="AM78" t="inlineStr"/>
       <c r="AN78" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AO78" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
@@ -14026,17 +14024,17 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日高點、接近20日低點、法人連續偏買、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14739,12 +14737,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2607.TW</t>
+          <t>3081.TWO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>榮運</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -14763,28 +14761,28 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>53.5</v>
+        <v>2920</v>
       </c>
       <c r="G83" t="n">
-        <v>53.56</v>
+        <v>2840</v>
       </c>
       <c r="H83" t="n">
-        <v>53.56</v>
+        <v>2793</v>
       </c>
       <c r="I83" t="n">
-        <v>53.38</v>
+        <v>2809</v>
       </c>
       <c r="J83" t="n">
-        <v>371634</v>
+        <v>2492000</v>
       </c>
       <c r="K83" t="n">
-        <v>249666</v>
+        <v>3512000</v>
       </c>
       <c r="L83" t="n">
-        <v>54</v>
+        <v>3220</v>
       </c>
       <c r="M83" t="n">
-        <v>52.4</v>
+        <v>2585</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -14792,28 +14790,28 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>185283</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>244863</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>419643</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>624046</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>182013</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>242065</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>408209</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>620161</v>
+        <v>0</v>
       </c>
       <c r="W83" t="n">
         <v>0</v>
@@ -14828,16 +14826,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>3270</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2798</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>11434</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>3885</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>18</v>
@@ -14846,16 +14844,16 @@
         <v>18</v>
       </c>
       <c r="AG83" t="n">
-        <v>-5</v>
+        <v>45</v>
       </c>
       <c r="AH83" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
@@ -14863,25 +14861,25 @@
         </is>
       </c>
       <c r="AL83" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AM83" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN83" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AO83" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
@@ -14896,29 +14894,29 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、黃金交叉、量能未放大</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、黃金交叉、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1102.TW</t>
+          <t>2607.TW</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>榮運</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -14937,28 +14935,28 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>35.45</v>
+        <v>53.5</v>
       </c>
       <c r="G84" t="n">
-        <v>35.53</v>
+        <v>53.56</v>
       </c>
       <c r="H84" t="n">
-        <v>35.53</v>
+        <v>53.56</v>
       </c>
       <c r="I84" t="n">
-        <v>35.36</v>
+        <v>53.38</v>
       </c>
       <c r="J84" t="n">
-        <v>6937959</v>
+        <v>371634</v>
       </c>
       <c r="K84" t="n">
-        <v>7014235</v>
+        <v>249666</v>
       </c>
       <c r="L84" t="n">
-        <v>36.1</v>
+        <v>54</v>
       </c>
       <c r="M84" t="n">
-        <v>34.6</v>
+        <v>52.4</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -14966,52 +14964,52 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>1905533</v>
+        <v>185283</v>
       </c>
       <c r="P84" t="n">
-        <v>1876427</v>
+        <v>244863</v>
       </c>
       <c r="Q84" t="n">
-        <v>5067245</v>
+        <v>419643</v>
       </c>
       <c r="R84" t="n">
-        <v>14053901</v>
+        <v>624046</v>
       </c>
       <c r="S84" t="n">
-        <v>2039207</v>
+        <v>182013</v>
       </c>
       <c r="T84" t="n">
-        <v>1819501</v>
+        <v>242065</v>
       </c>
       <c r="U84" t="n">
-        <v>9184767</v>
+        <v>408209</v>
       </c>
       <c r="V84" t="n">
-        <v>16936821</v>
+        <v>620161</v>
       </c>
       <c r="W84" t="n">
-        <v>-299000</v>
+        <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>-579160</v>
+        <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>-5258681</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>-4720714</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>165326</v>
+        <v>3270</v>
       </c>
       <c r="AB84" t="n">
-        <v>636086</v>
+        <v>2798</v>
       </c>
       <c r="AC84" t="n">
-        <v>1141159</v>
+        <v>11434</v>
       </c>
       <c r="AD84" t="n">
-        <v>1837794</v>
+        <v>3885</v>
       </c>
       <c r="AE84" t="n">
         <v>18</v>
@@ -15020,16 +15018,16 @@
         <v>18</v>
       </c>
       <c r="AG84" t="n">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="AH84" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
@@ -15037,14 +15035,16 @@
         </is>
       </c>
       <c r="AL84" t="n">
-        <v>18</v>
-      </c>
-      <c r="AM84" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>80</v>
+      </c>
       <c r="AN84" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AO84" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR84" t="inlineStr">
@@ -15068,29 +15068,29 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日高點、接近20日低點、法人連續偏買、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3081.TWO</t>
+          <t>3029.TW</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -15109,28 +15109,28 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2920</v>
+        <v>117.5</v>
       </c>
       <c r="G85" t="n">
-        <v>2840</v>
+        <v>118.4</v>
       </c>
       <c r="H85" t="n">
-        <v>2793</v>
+        <v>119</v>
       </c>
       <c r="I85" t="n">
-        <v>2809</v>
+        <v>117.35</v>
       </c>
       <c r="J85" t="n">
-        <v>2492000</v>
+        <v>842463</v>
       </c>
       <c r="K85" t="n">
-        <v>3512000</v>
+        <v>1075369</v>
       </c>
       <c r="L85" t="n">
-        <v>3220</v>
+        <v>126</v>
       </c>
       <c r="M85" t="n">
-        <v>2585</v>
+        <v>108.5</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -15138,70 +15138,70 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1494</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>386663</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>836370</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>233567</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>-20423</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>314918</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>730491</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>174140</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>4280</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>1619</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>-41</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>-685</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>17637</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>70126</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>105920</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>60112</v>
       </c>
       <c r="AE85" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF85" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG85" t="n">
-        <v>45</v>
+        <v>-20</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
       </c>
       <c r="AJ85" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
@@ -15209,25 +15209,25 @@
         </is>
       </c>
       <c r="AL85" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AM85" t="n">
-        <v>200</v>
+        <v>33.33</v>
       </c>
       <c r="AN85" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="AO85" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
@@ -15242,17 +15242,17 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、黃金交叉、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15433,12 +15433,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3029.TW</t>
+          <t>3042.TW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -15457,28 +15457,28 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>117.5</v>
+        <v>204.5</v>
       </c>
       <c r="G87" t="n">
-        <v>118.4</v>
+        <v>217.1</v>
       </c>
       <c r="H87" t="n">
-        <v>119</v>
+        <v>206.2</v>
       </c>
       <c r="I87" t="n">
-        <v>117.35</v>
+        <v>192.95</v>
       </c>
       <c r="J87" t="n">
-        <v>842463</v>
+        <v>25656732</v>
       </c>
       <c r="K87" t="n">
-        <v>1075369</v>
+        <v>33210509</v>
       </c>
       <c r="L87" t="n">
-        <v>126</v>
+        <v>235.5</v>
       </c>
       <c r="M87" t="n">
-        <v>108.5</v>
+        <v>171.5</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -15486,87 +15486,87 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>1494</v>
+        <v>-988843</v>
       </c>
       <c r="P87" t="n">
-        <v>386663</v>
+        <v>-3098841</v>
       </c>
       <c r="Q87" t="n">
-        <v>836370</v>
+        <v>824933</v>
       </c>
       <c r="R87" t="n">
-        <v>233567</v>
+        <v>2379047</v>
       </c>
       <c r="S87" t="n">
-        <v>-20423</v>
+        <v>-744068</v>
       </c>
       <c r="T87" t="n">
-        <v>314918</v>
+        <v>-2613450</v>
       </c>
       <c r="U87" t="n">
-        <v>730491</v>
+        <v>-1106597</v>
       </c>
       <c r="V87" t="n">
-        <v>174140</v>
+        <v>-3933481</v>
       </c>
       <c r="W87" t="n">
-        <v>4280</v>
+        <v>-3000</v>
       </c>
       <c r="X87" t="n">
-        <v>1619</v>
+        <v>1133000</v>
       </c>
       <c r="Y87" t="n">
-        <v>-41</v>
+        <v>2900000</v>
       </c>
       <c r="Z87" t="n">
-        <v>-685</v>
+        <v>4904000</v>
       </c>
       <c r="AA87" t="n">
-        <v>17637</v>
+        <v>-241775</v>
       </c>
       <c r="AB87" t="n">
-        <v>70126</v>
+        <v>-1618391</v>
       </c>
       <c r="AC87" t="n">
-        <v>105920</v>
+        <v>-968470</v>
       </c>
       <c r="AD87" t="n">
-        <v>60112</v>
+        <v>1408528</v>
       </c>
       <c r="AE87" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF87" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG87" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AL87" t="n">
         <v>-20</v>
       </c>
-      <c r="AH87" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ87" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AL87" t="n">
-        <v>4</v>
-      </c>
       <c r="AM87" t="n">
-        <v>33.33</v>
+        <v>-58.82</v>
       </c>
       <c r="AN87" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AO87" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -15590,29 +15590,29 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3042.TW</t>
+          <t>1101.TW</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -15631,28 +15631,28 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>204.5</v>
+        <v>25.2</v>
       </c>
       <c r="G88" t="n">
-        <v>217.1</v>
+        <v>25.48</v>
       </c>
       <c r="H88" t="n">
-        <v>206.2</v>
+        <v>25.23</v>
       </c>
       <c r="I88" t="n">
-        <v>192.95</v>
+        <v>24.77</v>
       </c>
       <c r="J88" t="n">
-        <v>25656732</v>
+        <v>26891285</v>
       </c>
       <c r="K88" t="n">
-        <v>33210509</v>
+        <v>49530136</v>
       </c>
       <c r="L88" t="n">
-        <v>235.5</v>
+        <v>26.7</v>
       </c>
       <c r="M88" t="n">
-        <v>171.5</v>
+        <v>23.75</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -15660,52 +15660,52 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>-988843</v>
+        <v>-949075</v>
       </c>
       <c r="P88" t="n">
-        <v>-3098841</v>
+        <v>-23740782</v>
       </c>
       <c r="Q88" t="n">
-        <v>824933</v>
+        <v>1724268</v>
       </c>
       <c r="R88" t="n">
-        <v>2379047</v>
+        <v>28443790</v>
       </c>
       <c r="S88" t="n">
-        <v>-744068</v>
+        <v>-975154</v>
       </c>
       <c r="T88" t="n">
-        <v>-2613450</v>
+        <v>-23819151</v>
       </c>
       <c r="U88" t="n">
-        <v>-1106597</v>
+        <v>-4222722</v>
       </c>
       <c r="V88" t="n">
-        <v>-3933481</v>
+        <v>21846579</v>
       </c>
       <c r="W88" t="n">
-        <v>-3000</v>
+        <v>-58000</v>
       </c>
       <c r="X88" t="n">
-        <v>1133000</v>
+        <v>-192000</v>
       </c>
       <c r="Y88" t="n">
-        <v>2900000</v>
+        <v>4636000</v>
       </c>
       <c r="Z88" t="n">
-        <v>4904000</v>
+        <v>4571000</v>
       </c>
       <c r="AA88" t="n">
-        <v>-241775</v>
+        <v>84079</v>
       </c>
       <c r="AB88" t="n">
-        <v>-1618391</v>
+        <v>270369</v>
       </c>
       <c r="AC88" t="n">
-        <v>-968470</v>
+        <v>1310990</v>
       </c>
       <c r="AD88" t="n">
-        <v>1408528</v>
+        <v>2026211</v>
       </c>
       <c r="AE88" t="n">
         <v>14</v>
@@ -15723,7 +15723,7 @@
         <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
@@ -15731,16 +15731,16 @@
         </is>
       </c>
       <c r="AL88" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AM88" t="n">
-        <v>-58.82</v>
+        <v>0</v>
       </c>
       <c r="AN88" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AO88" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
@@ -15781,12 +15781,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1101.TW</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -15805,28 +15805,28 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>25.2</v>
+        <v>177.5</v>
       </c>
       <c r="G89" t="n">
-        <v>25.48</v>
+        <v>179.4</v>
       </c>
       <c r="H89" t="n">
-        <v>25.23</v>
+        <v>176</v>
       </c>
       <c r="I89" t="n">
-        <v>24.77</v>
+        <v>175</v>
       </c>
       <c r="J89" t="n">
-        <v>26891285</v>
+        <v>58643976</v>
       </c>
       <c r="K89" t="n">
-        <v>49530136</v>
+        <v>74785226</v>
       </c>
       <c r="L89" t="n">
-        <v>26.7</v>
+        <v>192</v>
       </c>
       <c r="M89" t="n">
-        <v>23.75</v>
+        <v>158.5</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -15834,52 +15834,52 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>-949075</v>
+        <v>-3829203</v>
       </c>
       <c r="P89" t="n">
-        <v>-23740782</v>
+        <v>9880173</v>
       </c>
       <c r="Q89" t="n">
-        <v>1724268</v>
+        <v>66434586</v>
       </c>
       <c r="R89" t="n">
-        <v>28443790</v>
+        <v>28086871</v>
       </c>
       <c r="S89" t="n">
-        <v>-975154</v>
+        <v>7287269</v>
       </c>
       <c r="T89" t="n">
-        <v>-23819151</v>
+        <v>31476030</v>
       </c>
       <c r="U89" t="n">
-        <v>-4222722</v>
+        <v>85976382</v>
       </c>
       <c r="V89" t="n">
-        <v>21846579</v>
+        <v>70238639</v>
       </c>
       <c r="W89" t="n">
-        <v>-58000</v>
+        <v>-10812000</v>
       </c>
       <c r="X89" t="n">
-        <v>-192000</v>
+        <v>-22884275</v>
       </c>
       <c r="Y89" t="n">
-        <v>4636000</v>
+        <v>-23384275</v>
       </c>
       <c r="Z89" t="n">
-        <v>4571000</v>
+        <v>-45170069</v>
       </c>
       <c r="AA89" t="n">
-        <v>84079</v>
+        <v>-304472</v>
       </c>
       <c r="AB89" t="n">
-        <v>270369</v>
+        <v>1288418</v>
       </c>
       <c r="AC89" t="n">
-        <v>1310990</v>
+        <v>3842479</v>
       </c>
       <c r="AD89" t="n">
-        <v>2026211</v>
+        <v>3018301</v>
       </c>
       <c r="AE89" t="n">
         <v>14</v>
@@ -15897,7 +15897,7 @@
         <v>0</v>
       </c>
       <c r="AJ89" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
@@ -15905,16 +15905,16 @@
         </is>
       </c>
       <c r="AL89" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="AM89" t="n">
-        <v>0</v>
+        <v>-69.56999999999999</v>
       </c>
       <c r="AN89" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AO89" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
@@ -15943,24 +15943,24 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>2014.TW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中鴻</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -15979,28 +15979,28 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>177.5</v>
+        <v>16.95</v>
       </c>
       <c r="G90" t="n">
-        <v>179.4</v>
+        <v>17.08</v>
       </c>
       <c r="H90" t="n">
-        <v>176</v>
+        <v>16.89</v>
       </c>
       <c r="I90" t="n">
-        <v>175</v>
+        <v>16.79</v>
       </c>
       <c r="J90" t="n">
-        <v>58643976</v>
+        <v>1156672</v>
       </c>
       <c r="K90" t="n">
-        <v>74785226</v>
+        <v>2825562</v>
       </c>
       <c r="L90" t="n">
-        <v>192</v>
+        <v>17.45</v>
       </c>
       <c r="M90" t="n">
-        <v>158.5</v>
+        <v>16.2</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -16008,61 +16008,61 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>-3829203</v>
+        <v>349079</v>
       </c>
       <c r="P90" t="n">
-        <v>9880173</v>
+        <v>-178895</v>
       </c>
       <c r="Q90" t="n">
-        <v>66434586</v>
+        <v>2324543</v>
       </c>
       <c r="R90" t="n">
-        <v>28086871</v>
+        <v>5341543</v>
       </c>
       <c r="S90" t="n">
-        <v>7287269</v>
+        <v>349079</v>
       </c>
       <c r="T90" t="n">
-        <v>31476030</v>
+        <v>-165895</v>
       </c>
       <c r="U90" t="n">
-        <v>85976382</v>
+        <v>2331543</v>
       </c>
       <c r="V90" t="n">
-        <v>70238639</v>
+        <v>5325543</v>
       </c>
       <c r="W90" t="n">
-        <v>-10812000</v>
+        <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>-22884275</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>-23384275</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>-45170069</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>-304472</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1288418</v>
+        <v>-13000</v>
       </c>
       <c r="AC90" t="n">
-        <v>3842479</v>
+        <v>-7000</v>
       </c>
       <c r="AD90" t="n">
-        <v>3018301</v>
+        <v>16000</v>
       </c>
       <c r="AE90" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AF90" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AG90" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AH90" t="n">
         <v>30</v>
@@ -16071,7 +16071,7 @@
         <v>0</v>
       </c>
       <c r="AJ90" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
@@ -16079,16 +16079,16 @@
         </is>
       </c>
       <c r="AL90" t="n">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="AM90" t="n">
-        <v>-69.56999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN90" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AO90" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
@@ -16112,29 +16112,29 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>2331.TW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>精英</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16153,28 +16153,28 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>41.55</v>
+        <v>18.8</v>
       </c>
       <c r="G91" t="n">
-        <v>42.17</v>
+        <v>19</v>
       </c>
       <c r="H91" t="n">
-        <v>42.17</v>
+        <v>19.02</v>
       </c>
       <c r="I91" t="n">
-        <v>42.06</v>
+        <v>18.94</v>
       </c>
       <c r="J91" t="n">
-        <v>15337129</v>
+        <v>681516</v>
       </c>
       <c r="K91" t="n">
-        <v>15711913</v>
+        <v>781070</v>
       </c>
       <c r="L91" t="n">
-        <v>43.2</v>
+        <v>19.9</v>
       </c>
       <c r="M91" t="n">
-        <v>40.85</v>
+        <v>18.4</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -16182,52 +16182,52 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>-71852</v>
+        <v>-65000</v>
       </c>
       <c r="P91" t="n">
-        <v>473086</v>
+        <v>-126597</v>
       </c>
       <c r="Q91" t="n">
-        <v>9082211</v>
+        <v>590410</v>
       </c>
       <c r="R91" t="n">
-        <v>32566203</v>
+        <v>903769</v>
       </c>
       <c r="S91" t="n">
-        <v>-177411</v>
+        <v>-65000</v>
       </c>
       <c r="T91" t="n">
-        <v>-681905</v>
+        <v>-123597</v>
       </c>
       <c r="U91" t="n">
-        <v>7837351</v>
+        <v>568410</v>
       </c>
       <c r="V91" t="n">
-        <v>12420853</v>
+        <v>883769</v>
       </c>
       <c r="W91" t="n">
-        <v>-108000</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>165420</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>-512159</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>16956260</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>213559</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>989571</v>
+        <v>-3000</v>
       </c>
       <c r="AC91" t="n">
-        <v>1757019</v>
+        <v>22000</v>
       </c>
       <c r="AD91" t="n">
-        <v>3189090</v>
+        <v>20000</v>
       </c>
       <c r="AE91" t="n">
         <v>10</v>
@@ -16245,7 +16245,7 @@
         <v>0</v>
       </c>
       <c r="AJ91" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
@@ -16253,16 +16253,14 @@
         </is>
       </c>
       <c r="AL91" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM91" t="n">
-        <v>25</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AM91" t="inlineStr"/>
       <c r="AN91" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AO91" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
@@ -16271,7 +16269,7 @@
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
@@ -16286,17 +16284,17 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、黃金交叉、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、黃金交叉、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -16651,12 +16649,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2014.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>中鴻</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -16675,28 +16673,28 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>16.95</v>
+        <v>41.55</v>
       </c>
       <c r="G94" t="n">
-        <v>17.08</v>
+        <v>42.17</v>
       </c>
       <c r="H94" t="n">
-        <v>16.89</v>
+        <v>42.17</v>
       </c>
       <c r="I94" t="n">
-        <v>16.79</v>
+        <v>42.06</v>
       </c>
       <c r="J94" t="n">
-        <v>1156672</v>
+        <v>15337129</v>
       </c>
       <c r="K94" t="n">
-        <v>2825562</v>
+        <v>15711913</v>
       </c>
       <c r="L94" t="n">
-        <v>17.45</v>
+        <v>43.2</v>
       </c>
       <c r="M94" t="n">
-        <v>16.2</v>
+        <v>40.85</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -16704,52 +16702,52 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>349079</v>
+        <v>-71852</v>
       </c>
       <c r="P94" t="n">
-        <v>-178895</v>
+        <v>473086</v>
       </c>
       <c r="Q94" t="n">
-        <v>2324543</v>
+        <v>9082211</v>
       </c>
       <c r="R94" t="n">
-        <v>5341543</v>
+        <v>32566203</v>
       </c>
       <c r="S94" t="n">
-        <v>349079</v>
+        <v>-177411</v>
       </c>
       <c r="T94" t="n">
-        <v>-165895</v>
+        <v>-681905</v>
       </c>
       <c r="U94" t="n">
-        <v>2331543</v>
+        <v>7837351</v>
       </c>
       <c r="V94" t="n">
-        <v>5325543</v>
+        <v>12420853</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>-108000</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>165420</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>-512159</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>16956260</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>213559</v>
       </c>
       <c r="AB94" t="n">
-        <v>-13000</v>
+        <v>989571</v>
       </c>
       <c r="AC94" t="n">
-        <v>-7000</v>
+        <v>1757019</v>
       </c>
       <c r="AD94" t="n">
-        <v>16000</v>
+        <v>3189090</v>
       </c>
       <c r="AE94" t="n">
         <v>10</v>
@@ -16767,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="AJ94" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
@@ -16775,16 +16773,16 @@
         </is>
       </c>
       <c r="AL94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM94" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AN94" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO94" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
@@ -16793,7 +16791,7 @@
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
@@ -16813,24 +16811,24 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2331.TW</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>精英</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -16849,28 +16847,28 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>18.8</v>
+        <v>231</v>
       </c>
       <c r="G95" t="n">
-        <v>19</v>
+        <v>220.3</v>
       </c>
       <c r="H95" t="n">
-        <v>19.02</v>
+        <v>218.15</v>
       </c>
       <c r="I95" t="n">
-        <v>18.94</v>
+        <v>226.6</v>
       </c>
       <c r="J95" t="n">
-        <v>681516</v>
+        <v>2652000</v>
       </c>
       <c r="K95" t="n">
-        <v>781070</v>
+        <v>3560200</v>
       </c>
       <c r="L95" t="n">
-        <v>19.9</v>
+        <v>265</v>
       </c>
       <c r="M95" t="n">
-        <v>18.4</v>
+        <v>204</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -16878,28 +16876,28 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>-65000</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>-126597</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>590410</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>903769</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>-65000</v>
+        <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>-123597</v>
+        <v>0</v>
       </c>
       <c r="U95" t="n">
-        <v>568410</v>
+        <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>883769</v>
+        <v>0</v>
       </c>
       <c r="W95" t="n">
         <v>0</v>
@@ -16917,31 +16915,31 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF95" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG95" t="n">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="AH95" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI95" t="n">
         <v>0</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
@@ -16949,14 +16947,16 @@
         </is>
       </c>
       <c r="AL95" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM95" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>33.33</v>
+      </c>
       <c r="AN95" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AO95" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、分數剛升溫</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
@@ -16980,29 +16980,29 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>跌破5日線、黃金交叉、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、黃金交叉、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -17021,28 +17021,28 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>231</v>
+        <v>1530</v>
       </c>
       <c r="G96" t="n">
-        <v>220.3</v>
+        <v>1528</v>
       </c>
       <c r="H96" t="n">
-        <v>218.15</v>
+        <v>1569.5</v>
       </c>
       <c r="I96" t="n">
-        <v>226.6</v>
+        <v>1472.5</v>
       </c>
       <c r="J96" t="n">
-        <v>2652000</v>
+        <v>1772000</v>
       </c>
       <c r="K96" t="n">
-        <v>3560200</v>
+        <v>3469400</v>
       </c>
       <c r="L96" t="n">
-        <v>265</v>
+        <v>1750</v>
       </c>
       <c r="M96" t="n">
-        <v>204</v>
+        <v>1240</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>0</v>
       </c>
       <c r="AJ96" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
@@ -17121,25 +17121,25 @@
         </is>
       </c>
       <c r="AL96" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="AM96" t="n">
-        <v>33.33</v>
+        <v>-33.33</v>
       </c>
       <c r="AN96" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AO96" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
@@ -17171,12 +17171,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>2731.TW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>雄獅</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -17195,28 +17195,28 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1530</v>
+        <v>143.5</v>
       </c>
       <c r="G97" t="n">
-        <v>1528</v>
+        <v>144</v>
       </c>
       <c r="H97" t="n">
-        <v>1569.5</v>
+        <v>143.85</v>
       </c>
       <c r="I97" t="n">
-        <v>1472.5</v>
+        <v>143</v>
       </c>
       <c r="J97" t="n">
-        <v>1772000</v>
+        <v>201177</v>
       </c>
       <c r="K97" t="n">
-        <v>3469400</v>
+        <v>166348</v>
       </c>
       <c r="L97" t="n">
-        <v>1750</v>
+        <v>145.5</v>
       </c>
       <c r="M97" t="n">
-        <v>1240</v>
+        <v>139</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -17224,28 +17224,28 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>-34000</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>59173</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>40004</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>164603</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>-34000</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>59278</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>41404</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
+        <v>165644</v>
       </c>
       <c r="W97" t="n">
         <v>0</v>
@@ -17263,13 +17263,13 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>-105</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>-1041</v>
       </c>
       <c r="AE97" t="n">
         <v>8</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="AJ97" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
@@ -17295,25 +17295,25 @@
         </is>
       </c>
       <c r="AL97" t="n">
-        <v>-4</v>
+        <v>-34</v>
       </c>
       <c r="AM97" t="n">
-        <v>-33.33</v>
+        <v>-80.95</v>
       </c>
       <c r="AN97" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AO97" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
@@ -17338,7 +17338,7 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -17519,12 +17519,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2731.TW</t>
+          <t>2002.TW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>雄獅</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -17543,28 +17543,28 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>143.5</v>
+        <v>18.95</v>
       </c>
       <c r="G99" t="n">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="H99" t="n">
-        <v>143.85</v>
+        <v>18.84</v>
       </c>
       <c r="I99" t="n">
-        <v>143</v>
+        <v>18.86</v>
       </c>
       <c r="J99" t="n">
-        <v>201177</v>
+        <v>18407918</v>
       </c>
       <c r="K99" t="n">
-        <v>166348</v>
+        <v>39078186</v>
       </c>
       <c r="L99" t="n">
-        <v>145.5</v>
+        <v>19.3</v>
       </c>
       <c r="M99" t="n">
-        <v>139</v>
+        <v>18.6</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -17572,70 +17572,70 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>-34000</v>
+        <v>-828874</v>
       </c>
       <c r="P99" t="n">
-        <v>59173</v>
+        <v>-5223215</v>
       </c>
       <c r="Q99" t="n">
-        <v>40004</v>
+        <v>27831854</v>
       </c>
       <c r="R99" t="n">
-        <v>164603</v>
+        <v>-4433966</v>
       </c>
       <c r="S99" t="n">
-        <v>-34000</v>
+        <v>-812874</v>
       </c>
       <c r="T99" t="n">
-        <v>59278</v>
+        <v>-5197606</v>
       </c>
       <c r="U99" t="n">
-        <v>41404</v>
+        <v>27539573</v>
       </c>
       <c r="V99" t="n">
-        <v>165644</v>
+        <v>-4882151</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>-64000</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>-242000</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>-311000</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>-319000</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="AB99" t="n">
-        <v>-105</v>
+        <v>216391</v>
       </c>
       <c r="AC99" t="n">
-        <v>-1400</v>
+        <v>603281</v>
       </c>
       <c r="AD99" t="n">
-        <v>-1041</v>
+        <v>767185</v>
       </c>
       <c r="AE99" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF99" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG99" t="n">
-        <v>20</v>
+        <v>-15</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI99" t="n">
         <v>0</v>
       </c>
       <c r="AJ99" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
@@ -17643,16 +17643,14 @@
         </is>
       </c>
       <c r="AL99" t="n">
-        <v>-34</v>
-      </c>
-      <c r="AM99" t="n">
-        <v>-80.95</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AM99" t="inlineStr"/>
       <c r="AN99" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AO99" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
@@ -17661,7 +17659,7 @@
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
@@ -17676,29 +17674,29 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日高點、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3211.TWO</t>
+          <t>4979.TWO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -17717,28 +17715,28 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>395</v>
+        <v>568</v>
       </c>
       <c r="G100" t="n">
-        <v>396.7</v>
+        <v>575.4</v>
       </c>
       <c r="H100" t="n">
-        <v>390.05</v>
+        <v>582</v>
       </c>
       <c r="I100" t="n">
-        <v>379.25</v>
+        <v>574.85</v>
       </c>
       <c r="J100" t="n">
-        <v>12521000</v>
+        <v>11343000</v>
       </c>
       <c r="K100" t="n">
-        <v>5999400</v>
+        <v>3147200</v>
       </c>
       <c r="L100" t="n">
-        <v>406.5</v>
+        <v>658</v>
       </c>
       <c r="M100" t="n">
-        <v>349</v>
+        <v>501</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -17809,7 +17807,7 @@
         <v>-20</v>
       </c>
       <c r="AJ100" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
@@ -17817,16 +17815,16 @@
         </is>
       </c>
       <c r="AL100" t="n">
-        <v>-18</v>
+        <v>-6</v>
       </c>
       <c r="AM100" t="n">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="AN100" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AO100" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
@@ -17835,7 +17833,7 @@
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、爆量後不追價、分數轉弱</t>
         </is>
       </c>
       <c r="AR100" t="inlineStr">
@@ -17850,7 +17848,7 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>跌破5日線、黃金交叉、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
@@ -17860,19 +17858,19 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、爆量、爆量價未漲、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、黃金交叉、爆量、爆量價未漲、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2002.TW</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -17891,81 +17889,81 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>18.95</v>
+        <v>395</v>
       </c>
       <c r="G101" t="n">
-        <v>19</v>
+        <v>396.7</v>
       </c>
       <c r="H101" t="n">
-        <v>18.84</v>
+        <v>390.05</v>
       </c>
       <c r="I101" t="n">
-        <v>18.86</v>
+        <v>379.25</v>
       </c>
       <c r="J101" t="n">
-        <v>18407918</v>
+        <v>12521000</v>
       </c>
       <c r="K101" t="n">
-        <v>39078186</v>
+        <v>5999400</v>
       </c>
       <c r="L101" t="n">
-        <v>19.3</v>
+        <v>406.5</v>
       </c>
       <c r="M101" t="n">
-        <v>18.6</v>
+        <v>349</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>-828874</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>-5223215</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>27831854</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>-4433966</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>-812874</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>-5197606</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>27539573</v>
+        <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>-4882151</v>
+        <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>-64000</v>
+        <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>-242000</v>
+        <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>-311000</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>-319000</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>216391</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>603281</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>767185</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
         <v>6</v>
@@ -17974,16 +17972,16 @@
         <v>6</v>
       </c>
       <c r="AG101" t="n">
-        <v>-15</v>
+        <v>25</v>
       </c>
       <c r="AH101" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI101" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ101" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
@@ -17991,14 +17989,16 @@
         </is>
       </c>
       <c r="AL101" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM101" t="inlineStr"/>
+        <v>-18</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>-75</v>
+      </c>
       <c r="AN101" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AO101" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
@@ -18022,17 +18022,17 @@
       </c>
       <c r="AT101" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日高點、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、爆量、爆量價未漲、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -18213,12 +18213,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>4979.TWO</t>
+          <t>2451.TW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -18237,99 +18237,99 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>568</v>
+        <v>279</v>
       </c>
       <c r="G103" t="n">
-        <v>575.4</v>
+        <v>287.4</v>
       </c>
       <c r="H103" t="n">
-        <v>582</v>
+        <v>286.3</v>
       </c>
       <c r="I103" t="n">
-        <v>574.85</v>
+        <v>283.73</v>
       </c>
       <c r="J103" t="n">
-        <v>11343000</v>
+        <v>3760489</v>
       </c>
       <c r="K103" t="n">
-        <v>3147200</v>
+        <v>2158000</v>
       </c>
       <c r="L103" t="n">
-        <v>658</v>
+        <v>294</v>
       </c>
       <c r="M103" t="n">
-        <v>501</v>
+        <v>270</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>-1499005</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>-1006045</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>15356</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>1859711</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>-1569896</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>-1340226</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>-399802</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
+        <v>1462510</v>
       </c>
       <c r="W103" t="n">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>364300</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>426000</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>413800</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>-42109</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>-30119</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>-10842</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>-16599</v>
       </c>
       <c r="AE103" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF103" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG103" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AH103" t="n">
         <v>0</v>
       </c>
       <c r="AI103" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AJ103" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
@@ -18337,16 +18337,16 @@
         </is>
       </c>
       <c r="AL103" t="n">
-        <v>-6</v>
+        <v>-56</v>
       </c>
       <c r="AM103" t="n">
-        <v>-50</v>
+        <v>-93.33</v>
       </c>
       <c r="AN103" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO103" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、爆量後不追價、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
@@ -18370,29 +18370,29 @@
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>跌破5日線、黃金交叉、爆量、爆量價未漲</t>
+          <t>跌破5日線、多頭排列、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>籌碼中性、投信買外資賣</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、黃金交叉、爆量、爆量價未漲、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、成交量放大、接近20日低點、籌碼中性、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2451.TW</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -18411,28 +18411,28 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>279</v>
+        <v>258.5</v>
       </c>
       <c r="G104" t="n">
-        <v>287.4</v>
+        <v>253.6</v>
       </c>
       <c r="H104" t="n">
-        <v>286.3</v>
+        <v>255.85</v>
       </c>
       <c r="I104" t="n">
-        <v>283.73</v>
+        <v>259.62</v>
       </c>
       <c r="J104" t="n">
-        <v>3760489</v>
+        <v>8406000</v>
       </c>
       <c r="K104" t="n">
-        <v>2158000</v>
+        <v>6335000</v>
       </c>
       <c r="L104" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="M104" t="n">
-        <v>270</v>
+        <v>230.5</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -18440,61 +18440,61 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>-1499005</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>-1006045</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>15356</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>1859711</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>-1569896</v>
+        <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>-1340226</v>
+        <v>0</v>
       </c>
       <c r="U104" t="n">
-        <v>-399802</v>
+        <v>0</v>
       </c>
       <c r="V104" t="n">
-        <v>1462510</v>
+        <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>364300</v>
+        <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>426000</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>413800</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>-42109</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>-30119</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>-10842</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
-        <v>-16599</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AH104" t="n">
         <v>0</v>
@@ -18503,7 +18503,7 @@
         <v>0</v>
       </c>
       <c r="AJ104" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
@@ -18511,25 +18511,25 @@
         </is>
       </c>
       <c r="AL104" t="n">
-        <v>-56</v>
+        <v>-16</v>
       </c>
       <c r="AM104" t="n">
-        <v>-93.33</v>
+        <v>-88.89</v>
       </c>
       <c r="AN104" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="AO104" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
@@ -18544,17 +18544,17 @@
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、成交量放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>籌碼中性、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、成交量放大、接近20日低點、籌碼中性、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -8471,10 +8471,10 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>76.33</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>74.51000000000001</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>1679171</v>
@@ -8486,7 +8486,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>70.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -22705,12 +22705,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>2449.TW</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -22720,7 +22720,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -22729,28 +22729,28 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1290</v>
+        <v>304.5</v>
       </c>
       <c r="G129" t="n">
-        <v>1295</v>
+        <v>298.3</v>
       </c>
       <c r="H129" t="n">
-        <v>1291.5</v>
+        <v>299.15</v>
       </c>
       <c r="I129" t="n">
-        <v>1324.75</v>
+        <v>287.55</v>
       </c>
       <c r="J129" t="n">
-        <v>884000</v>
+        <v>52163924</v>
       </c>
       <c r="K129" t="n">
-        <v>1153600</v>
+        <v>26437816</v>
       </c>
       <c r="L129" t="n">
-        <v>1475</v>
+        <v>330</v>
       </c>
       <c r="M129" t="n">
-        <v>1240</v>
+        <v>253</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -22758,96 +22758,96 @@
         </is>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>-10577744</v>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>-15391818</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>-22824831</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>-47163955</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>-2405213</v>
       </c>
       <c r="T129" t="n">
-        <v>0</v>
+        <v>-7021958</v>
       </c>
       <c r="U129" t="n">
-        <v>0</v>
+        <v>-13744310</v>
       </c>
       <c r="V129" t="n">
-        <v>0</v>
+        <v>-32671842</v>
       </c>
       <c r="W129" t="n">
-        <v>0</v>
+        <v>-8530419</v>
       </c>
       <c r="X129" t="n">
-        <v>0</v>
+        <v>-8932248</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>-9528667</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>-12081377</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>357888</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>562388</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>448146</v>
       </c>
       <c r="AD129" t="n">
-        <v>0</v>
+        <v>-2410736</v>
       </c>
       <c r="AE129" t="n">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="AF129" t="n">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="AG129" t="n">
-        <v>-30</v>
+        <v>35</v>
       </c>
       <c r="AH129" t="n">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="AI129" t="n">
         <v>0</v>
       </c>
       <c r="AJ129" t="n">
-        <v>-12</v>
+        <v>-18</v>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AL129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM129" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="AN129" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AO129" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
@@ -22862,29 +22862,29 @@
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、成交量放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2449.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -22903,28 +22903,28 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>304.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G130" t="n">
-        <v>298.3</v>
+        <v>76.98</v>
       </c>
       <c r="H130" t="n">
-        <v>299.15</v>
+        <v>73.28</v>
       </c>
       <c r="I130" t="n">
-        <v>287.55</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>52163924</v>
+        <v>6386854</v>
       </c>
       <c r="K130" t="n">
-        <v>26437816</v>
+        <v>18055427</v>
       </c>
       <c r="L130" t="n">
-        <v>330</v>
+        <v>81</v>
       </c>
       <c r="M130" t="n">
-        <v>253</v>
+        <v>60</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -22932,64 +22932,64 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>-10577744</v>
+        <v>129921</v>
       </c>
       <c r="P130" t="n">
-        <v>-15391818</v>
+        <v>-1437257</v>
       </c>
       <c r="Q130" t="n">
-        <v>-22824831</v>
+        <v>-3919275</v>
       </c>
       <c r="R130" t="n">
-        <v>-47163955</v>
+        <v>-10665407</v>
       </c>
       <c r="S130" t="n">
-        <v>-2405213</v>
+        <v>345776</v>
       </c>
       <c r="T130" t="n">
-        <v>-7021958</v>
+        <v>-1177775</v>
       </c>
       <c r="U130" t="n">
-        <v>-13744310</v>
+        <v>-3985015</v>
       </c>
       <c r="V130" t="n">
-        <v>-32671842</v>
+        <v>-11222528</v>
       </c>
       <c r="W130" t="n">
-        <v>-8530419</v>
+        <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>-8932248</v>
+        <v>-1000</v>
       </c>
       <c r="Y130" t="n">
-        <v>-9528667</v>
+        <v>-1000</v>
       </c>
       <c r="Z130" t="n">
-        <v>-12081377</v>
+        <v>-924</v>
       </c>
       <c r="AA130" t="n">
-        <v>357888</v>
+        <v>-215855</v>
       </c>
       <c r="AB130" t="n">
-        <v>562388</v>
+        <v>-258482</v>
       </c>
       <c r="AC130" t="n">
-        <v>448146</v>
+        <v>66740</v>
       </c>
       <c r="AD130" t="n">
-        <v>-2410736</v>
+        <v>558045</v>
       </c>
       <c r="AE130" t="n">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="AF130" t="n">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="AG130" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="AH130" t="n">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="AI130" t="n">
         <v>0</v>
@@ -23003,25 +23003,25 @@
         </is>
       </c>
       <c r="AL130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM130" t="n">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="AN130" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="AO130" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
@@ -23036,29 +23036,29 @@
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -23077,28 +23077,28 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>74.40000000000001</v>
+        <v>1250</v>
       </c>
       <c r="G131" t="n">
-        <v>76.98</v>
+        <v>1273</v>
       </c>
       <c r="H131" t="n">
-        <v>73.28</v>
+        <v>1283.5</v>
       </c>
       <c r="I131" t="n">
-        <v>68.48999999999999</v>
+        <v>1290</v>
       </c>
       <c r="J131" t="n">
-        <v>6386854</v>
+        <v>1149000</v>
       </c>
       <c r="K131" t="n">
-        <v>18055427</v>
+        <v>1129800</v>
       </c>
       <c r="L131" t="n">
-        <v>81</v>
+        <v>1395</v>
       </c>
       <c r="M131" t="n">
-        <v>60</v>
+        <v>1240</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -23106,52 +23106,52 @@
         </is>
       </c>
       <c r="O131" t="n">
-        <v>129921</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>-1437257</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>-3919275</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>-10665407</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>345776</v>
+        <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>-1177775</v>
+        <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>-3985015</v>
+        <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>-11222528</v>
+        <v>0</v>
       </c>
       <c r="W131" t="n">
         <v>0</v>
       </c>
       <c r="X131" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>-924</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>-215855</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>-258482</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>66740</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
-        <v>558045</v>
+        <v>0</v>
       </c>
       <c r="AE131" t="n">
         <v>-18</v>
@@ -23160,10 +23160,10 @@
         <v>-18</v>
       </c>
       <c r="AG131" t="n">
-        <v>5</v>
+        <v>-45</v>
       </c>
       <c r="AH131" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="AI131" t="n">
         <v>0</v>
@@ -23183,10 +23183,10 @@
         <v>0</v>
       </c>
       <c r="AN131" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO131" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
@@ -23210,17 +23210,17 @@
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -8471,10 +8471,10 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>76.40000000000001</v>
+        <v>76.33</v>
       </c>
       <c r="I47" t="n">
-        <v>74.84999999999999</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>1679171</v>
@@ -8486,7 +8486,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>69.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -5576,16 +5576,16 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>16846863</v>
+        <v>16859863</v>
       </c>
       <c r="P30" t="n">
-        <v>13621295</v>
+        <v>13634295</v>
       </c>
       <c r="Q30" t="n">
-        <v>16473994</v>
+        <v>16486994</v>
       </c>
       <c r="R30" t="n">
-        <v>47511576</v>
+        <v>47524576</v>
       </c>
       <c r="S30" t="n">
         <v>15361685</v>
@@ -5600,16 +5600,16 @@
         <v>36819624</v>
       </c>
       <c r="W30" t="n">
-        <v>1289208</v>
+        <v>1302208</v>
       </c>
       <c r="X30" t="n">
-        <v>2341208</v>
+        <v>2354208</v>
       </c>
       <c r="Y30" t="n">
-        <v>5997208</v>
+        <v>6010208</v>
       </c>
       <c r="Z30" t="n">
-        <v>10649434</v>
+        <v>10662434</v>
       </c>
       <c r="AA30" t="n">
         <v>195970</v>
@@ -10622,16 +10622,16 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>-80591</v>
+        <v>-35591</v>
       </c>
       <c r="P59" t="n">
-        <v>1143787</v>
+        <v>1188787</v>
       </c>
       <c r="Q59" t="n">
-        <v>943724</v>
+        <v>988724</v>
       </c>
       <c r="R59" t="n">
-        <v>-271700</v>
+        <v>-226700</v>
       </c>
       <c r="S59" t="n">
         <v>-35184</v>
@@ -10646,16 +10646,16 @@
         <v>-338435</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="X59" t="n">
-        <v>35000</v>
+        <v>80000</v>
       </c>
       <c r="Y59" t="n">
-        <v>60000</v>
+        <v>105000</v>
       </c>
       <c r="Z59" t="n">
-        <v>-57000</v>
+        <v>-12000</v>
       </c>
       <c r="AA59" t="n">
         <v>-45407</v>
@@ -26796,16 +26796,16 @@
         </is>
       </c>
       <c r="O152" t="n">
-        <v>748535</v>
+        <v>847535</v>
       </c>
       <c r="P152" t="n">
-        <v>-3116197</v>
+        <v>-3017197</v>
       </c>
       <c r="Q152" t="n">
-        <v>-3497828</v>
+        <v>-3398828</v>
       </c>
       <c r="R152" t="n">
-        <v>-5515432</v>
+        <v>-5416432</v>
       </c>
       <c r="S152" t="n">
         <v>4673665</v>
@@ -26820,16 +26820,16 @@
         <v>3901609</v>
       </c>
       <c r="W152" t="n">
-        <v>-4201187</v>
+        <v>-4102187</v>
       </c>
       <c r="X152" t="n">
-        <v>-8310371</v>
+        <v>-8211371</v>
       </c>
       <c r="Y152" t="n">
-        <v>-8389361</v>
+        <v>-8290361</v>
       </c>
       <c r="Z152" t="n">
-        <v>-9239031</v>
+        <v>-9140031</v>
       </c>
       <c r="AA152" t="n">
         <v>276057</v>
@@ -31492,16 +31492,16 @@
         </is>
       </c>
       <c r="O179" t="n">
-        <v>13540899</v>
+        <v>13535899</v>
       </c>
       <c r="P179" t="n">
-        <v>3161677</v>
+        <v>3156677</v>
       </c>
       <c r="Q179" t="n">
-        <v>-45253560</v>
+        <v>-45258560</v>
       </c>
       <c r="R179" t="n">
-        <v>-37044983</v>
+        <v>-37049983</v>
       </c>
       <c r="S179" t="n">
         <v>12224066</v>
@@ -31516,16 +31516,16 @@
         <v>1635917</v>
       </c>
       <c r="W179" t="n">
-        <v>286803</v>
+        <v>281803</v>
       </c>
       <c r="X179" t="n">
-        <v>-1065758</v>
+        <v>-1070758</v>
       </c>
       <c r="Y179" t="n">
-        <v>-3973998</v>
+        <v>-3978998</v>
       </c>
       <c r="Z179" t="n">
-        <v>-34390413</v>
+        <v>-34395413</v>
       </c>
       <c r="AA179" t="n">
         <v>1030030</v>
@@ -32362,16 +32362,16 @@
         </is>
       </c>
       <c r="O184" t="n">
-        <v>-999450</v>
+        <v>-991450</v>
       </c>
       <c r="P184" t="n">
-        <v>-1331449</v>
+        <v>-1323449</v>
       </c>
       <c r="Q184" t="n">
-        <v>-588904</v>
+        <v>-580904</v>
       </c>
       <c r="R184" t="n">
-        <v>3744774</v>
+        <v>3752774</v>
       </c>
       <c r="S184" t="n">
         <v>-1151597</v>
@@ -32386,16 +32386,16 @@
         <v>-476047</v>
       </c>
       <c r="W184" t="n">
-        <v>354610</v>
+        <v>362610</v>
       </c>
       <c r="X184" t="n">
-        <v>1252865</v>
+        <v>1260865</v>
       </c>
       <c r="Y184" t="n">
-        <v>1501165</v>
+        <v>1509165</v>
       </c>
       <c r="Z184" t="n">
-        <v>4450642</v>
+        <v>4458642</v>
       </c>
       <c r="AA184" t="n">
         <v>-202463</v>
@@ -33754,16 +33754,16 @@
         </is>
       </c>
       <c r="O192" t="n">
-        <v>-2004570</v>
+        <v>-2181570</v>
       </c>
       <c r="P192" t="n">
-        <v>-13791762</v>
+        <v>-13968762</v>
       </c>
       <c r="Q192" t="n">
-        <v>-23976571</v>
+        <v>-24153571</v>
       </c>
       <c r="R192" t="n">
-        <v>-18665322</v>
+        <v>-18842322</v>
       </c>
       <c r="S192" t="n">
         <v>-2133043</v>
@@ -33778,16 +33778,16 @@
         <v>-18061888</v>
       </c>
       <c r="W192" t="n">
-        <v>268561</v>
+        <v>91561</v>
       </c>
       <c r="X192" t="n">
-        <v>675077</v>
+        <v>498077</v>
       </c>
       <c r="Y192" t="n">
-        <v>-1627653</v>
+        <v>-1804653</v>
       </c>
       <c r="Z192" t="n">
-        <v>-309652</v>
+        <v>-486652</v>
       </c>
       <c r="AA192" t="n">
         <v>-140088</v>
@@ -35146,16 +35146,16 @@
         </is>
       </c>
       <c r="O200" t="n">
-        <v>-7341001</v>
+        <v>-7351001</v>
       </c>
       <c r="P200" t="n">
-        <v>-55921408</v>
+        <v>-55931408</v>
       </c>
       <c r="Q200" t="n">
-        <v>-104330210</v>
+        <v>-104340210</v>
       </c>
       <c r="R200" t="n">
-        <v>-80451411</v>
+        <v>-80461411</v>
       </c>
       <c r="S200" t="n">
         <v>-7783082</v>
@@ -35170,16 +35170,16 @@
         <v>-64845225</v>
       </c>
       <c r="W200" t="n">
-        <v>-278684</v>
+        <v>-288684</v>
       </c>
       <c r="X200" t="n">
-        <v>-10322918</v>
+        <v>-10332918</v>
       </c>
       <c r="Y200" t="n">
-        <v>-12075918</v>
+        <v>-12085918</v>
       </c>
       <c r="Z200" t="n">
-        <v>-14567021</v>
+        <v>-14577021</v>
       </c>
       <c r="AA200" t="n">
         <v>720765</v>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -17548,7 +17548,7 @@
         <v>49.92</v>
       </c>
       <c r="I99" t="n">
-        <v>43.84</v>
+        <v>45.74</v>
       </c>
       <c r="J99" t="n">
         <v>23589000</v>
@@ -17560,7 +17560,7 @@
         <v>59.3</v>
       </c>
       <c r="M99" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -3672,16 +3672,16 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>991925</v>
+        <v>1001925</v>
       </c>
       <c r="P19" t="n">
-        <v>452475</v>
+        <v>462475</v>
       </c>
       <c r="Q19" t="n">
-        <v>1676853</v>
+        <v>1686853</v>
       </c>
       <c r="R19" t="n">
-        <v>871137</v>
+        <v>881137</v>
       </c>
       <c r="S19" t="n">
         <v>656234</v>
@@ -3696,16 +3696,16 @@
         <v>359906</v>
       </c>
       <c r="W19" t="n">
-        <v>-60</v>
+        <v>9940</v>
       </c>
       <c r="X19" t="n">
-        <v>44940</v>
+        <v>54940</v>
       </c>
       <c r="Y19" t="n">
-        <v>79940</v>
+        <v>89940</v>
       </c>
       <c r="Z19" t="n">
-        <v>104940</v>
+        <v>114940</v>
       </c>
       <c r="AA19" t="n">
         <v>335751</v>
@@ -12720,16 +12720,16 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>154597</v>
+        <v>184597</v>
       </c>
       <c r="P71" t="n">
-        <v>285129</v>
+        <v>315129</v>
       </c>
       <c r="Q71" t="n">
-        <v>586608</v>
+        <v>616608</v>
       </c>
       <c r="R71" t="n">
-        <v>1241796</v>
+        <v>1271796</v>
       </c>
       <c r="S71" t="n">
         <v>45302</v>
@@ -12744,16 +12744,16 @@
         <v>457944</v>
       </c>
       <c r="W71" t="n">
-        <v>116410</v>
+        <v>146410</v>
       </c>
       <c r="X71" t="n">
-        <v>355718</v>
+        <v>385718</v>
       </c>
       <c r="Y71" t="n">
-        <v>542303</v>
+        <v>572303</v>
       </c>
       <c r="Z71" t="n">
-        <v>976810</v>
+        <v>1006810</v>
       </c>
       <c r="AA71" t="n">
         <v>-7115</v>
@@ -13711,12 +13711,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2492.TW</t>
+          <t>6275.TWO</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -13735,28 +13735,28 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>369</v>
+        <v>47.15</v>
       </c>
       <c r="G77" t="n">
-        <v>391.9</v>
+        <v>46.15</v>
       </c>
       <c r="H77" t="n">
-        <v>400.7</v>
+        <v>45.66</v>
       </c>
       <c r="I77" t="n">
-        <v>360.7</v>
+        <v>45.75</v>
       </c>
       <c r="J77" t="n">
-        <v>35893432</v>
+        <v>220000</v>
       </c>
       <c r="K77" t="n">
-        <v>14835505</v>
+        <v>162200</v>
       </c>
       <c r="L77" t="n">
-        <v>431.5</v>
+        <v>48.9</v>
       </c>
       <c r="M77" t="n">
-        <v>298.5</v>
+        <v>44.55</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -13764,52 +13764,52 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>-1796309</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>-4386965</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>1513583</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>8884028</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>-4794289</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>-6414206</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>-897237</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>5950827</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>3729038</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>3035038</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>3033038</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>5516038</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>-731058</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>-1007797</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>-622218</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>-2582837</v>
+        <v>0</v>
       </c>
       <c r="AE77" t="n">
         <v>12</v>
@@ -13818,42 +13818,42 @@
         <v>12</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AH77" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
       </c>
       <c r="AJ77" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AL77" t="n">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="AM77" t="n">
-        <v>200</v>
+        <v>-40</v>
       </c>
       <c r="AN77" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="AO77" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能偏強、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
@@ -13868,17 +13868,17 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>跌破5日線、爆量</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、爆量、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14059,12 +14059,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>2492.TW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -14083,28 +14083,28 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>25.05</v>
+        <v>369</v>
       </c>
       <c r="G79" t="n">
-        <v>25.82</v>
+        <v>391.9</v>
       </c>
       <c r="H79" t="n">
-        <v>25.85</v>
+        <v>400.7</v>
       </c>
       <c r="I79" t="n">
-        <v>25.19</v>
+        <v>360.7</v>
       </c>
       <c r="J79" t="n">
-        <v>5861982</v>
+        <v>35893432</v>
       </c>
       <c r="K79" t="n">
-        <v>17962130</v>
+        <v>14835505</v>
       </c>
       <c r="L79" t="n">
-        <v>27.4</v>
+        <v>431.5</v>
       </c>
       <c r="M79" t="n">
-        <v>23.85</v>
+        <v>298.5</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -14112,52 +14112,52 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>-1089916</v>
+        <v>-1796309</v>
       </c>
       <c r="P79" t="n">
-        <v>2206540</v>
+        <v>-4386965</v>
       </c>
       <c r="Q79" t="n">
-        <v>4956817</v>
+        <v>1513583</v>
       </c>
       <c r="R79" t="n">
-        <v>20195646</v>
+        <v>8884028</v>
       </c>
       <c r="S79" t="n">
-        <v>-700587</v>
+        <v>-4794289</v>
       </c>
       <c r="T79" t="n">
-        <v>2755407</v>
+        <v>-6414206</v>
       </c>
       <c r="U79" t="n">
-        <v>5653592</v>
+        <v>-897237</v>
       </c>
       <c r="V79" t="n">
-        <v>21294772</v>
+        <v>5950827</v>
       </c>
       <c r="W79" t="n">
-        <v>-118</v>
+        <v>3729038</v>
       </c>
       <c r="X79" t="n">
-        <v>-5118</v>
+        <v>3035038</v>
       </c>
       <c r="Y79" t="n">
-        <v>57882</v>
+        <v>3033038</v>
       </c>
       <c r="Z79" t="n">
-        <v>133882</v>
+        <v>5516038</v>
       </c>
       <c r="AA79" t="n">
-        <v>-389211</v>
+        <v>-731058</v>
       </c>
       <c r="AB79" t="n">
-        <v>-543749</v>
+        <v>-1007797</v>
       </c>
       <c r="AC79" t="n">
-        <v>-754657</v>
+        <v>-622218</v>
       </c>
       <c r="AD79" t="n">
-        <v>-1233008</v>
+        <v>-2582837</v>
       </c>
       <c r="AE79" t="n">
         <v>12</v>
@@ -14166,16 +14166,16 @@
         <v>12</v>
       </c>
       <c r="AG79" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
       </c>
       <c r="AJ79" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
@@ -14183,16 +14183,16 @@
         </is>
       </c>
       <c r="AL79" t="n">
-        <v>-10</v>
+        <v>8</v>
       </c>
       <c r="AM79" t="n">
-        <v>-45.45</v>
+        <v>200</v>
       </c>
       <c r="AN79" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO79" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能偏強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
@@ -14216,17 +14216,17 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、爆量</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、爆量、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14407,12 +14407,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -14431,28 +14431,28 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>42.35</v>
+        <v>25.05</v>
       </c>
       <c r="G81" t="n">
-        <v>43.12</v>
+        <v>25.82</v>
       </c>
       <c r="H81" t="n">
-        <v>42.55</v>
+        <v>25.85</v>
       </c>
       <c r="I81" t="n">
-        <v>42.37</v>
+        <v>25.19</v>
       </c>
       <c r="J81" t="n">
-        <v>12934352</v>
+        <v>5861982</v>
       </c>
       <c r="K81" t="n">
-        <v>17709579</v>
+        <v>17962130</v>
       </c>
       <c r="L81" t="n">
-        <v>44.05</v>
+        <v>27.4</v>
       </c>
       <c r="M81" t="n">
-        <v>41.2</v>
+        <v>23.85</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -14460,64 +14460,64 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>-565183</v>
+        <v>-1089916</v>
       </c>
       <c r="P81" t="n">
-        <v>8647559</v>
+        <v>2206540</v>
       </c>
       <c r="Q81" t="n">
-        <v>31746265</v>
+        <v>4956817</v>
       </c>
       <c r="R81" t="n">
-        <v>55302078</v>
+        <v>20195646</v>
       </c>
       <c r="S81" t="n">
-        <v>2468319</v>
+        <v>-700587</v>
       </c>
       <c r="T81" t="n">
-        <v>15169899</v>
+        <v>2755407</v>
       </c>
       <c r="U81" t="n">
-        <v>36706974</v>
+        <v>5653592</v>
       </c>
       <c r="V81" t="n">
-        <v>59089589</v>
+        <v>21294772</v>
       </c>
       <c r="W81" t="n">
-        <v>-4194039</v>
+        <v>-118</v>
       </c>
       <c r="X81" t="n">
-        <v>-9465039</v>
+        <v>-5118</v>
       </c>
       <c r="Y81" t="n">
-        <v>-10084039</v>
+        <v>57882</v>
       </c>
       <c r="Z81" t="n">
-        <v>-10691621</v>
+        <v>133882</v>
       </c>
       <c r="AA81" t="n">
-        <v>1160537</v>
+        <v>-389211</v>
       </c>
       <c r="AB81" t="n">
-        <v>2942699</v>
+        <v>-543749</v>
       </c>
       <c r="AC81" t="n">
-        <v>5123330</v>
+        <v>-754657</v>
       </c>
       <c r="AD81" t="n">
-        <v>6904110</v>
+        <v>-1233008</v>
       </c>
       <c r="AE81" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF81" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG81" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="AH81" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -14531,10 +14531,10 @@
         </is>
       </c>
       <c r="AL81" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AM81" t="n">
-        <v>-54.55</v>
+        <v>-45.45</v>
       </c>
       <c r="AN81" t="n">
         <v>0</v>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
@@ -14564,17 +14564,17 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14755,12 +14755,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3702.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -14779,28 +14779,28 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>113.5</v>
+        <v>42.35</v>
       </c>
       <c r="G83" t="n">
-        <v>115.7</v>
+        <v>43.12</v>
       </c>
       <c r="H83" t="n">
-        <v>116.85</v>
+        <v>42.55</v>
       </c>
       <c r="I83" t="n">
-        <v>116.38</v>
+        <v>42.37</v>
       </c>
       <c r="J83" t="n">
-        <v>8056263</v>
+        <v>12934352</v>
       </c>
       <c r="K83" t="n">
-        <v>10530615</v>
+        <v>17709579</v>
       </c>
       <c r="L83" t="n">
-        <v>122</v>
+        <v>44.05</v>
       </c>
       <c r="M83" t="n">
-        <v>111</v>
+        <v>41.2</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -14808,52 +14808,52 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>798220</v>
+        <v>-565183</v>
       </c>
       <c r="P83" t="n">
-        <v>1412203</v>
+        <v>8647559</v>
       </c>
       <c r="Q83" t="n">
-        <v>8445322</v>
+        <v>31746265</v>
       </c>
       <c r="R83" t="n">
-        <v>20495769</v>
+        <v>55302078</v>
       </c>
       <c r="S83" t="n">
-        <v>-48782</v>
+        <v>2468319</v>
       </c>
       <c r="T83" t="n">
-        <v>-1343073</v>
+        <v>15169899</v>
       </c>
       <c r="U83" t="n">
-        <v>4757844</v>
+        <v>36706974</v>
       </c>
       <c r="V83" t="n">
-        <v>15326882</v>
+        <v>59089589</v>
       </c>
       <c r="W83" t="n">
-        <v>245924</v>
+        <v>-4194039</v>
       </c>
       <c r="X83" t="n">
-        <v>1819964</v>
+        <v>-9465039</v>
       </c>
       <c r="Y83" t="n">
-        <v>2083249</v>
+        <v>-10084039</v>
       </c>
       <c r="Z83" t="n">
-        <v>2511843</v>
+        <v>-10691621</v>
       </c>
       <c r="AA83" t="n">
-        <v>601078</v>
+        <v>1160537</v>
       </c>
       <c r="AB83" t="n">
-        <v>935312</v>
+        <v>2942699</v>
       </c>
       <c r="AC83" t="n">
-        <v>1604229</v>
+        <v>5123330</v>
       </c>
       <c r="AD83" t="n">
-        <v>2657044</v>
+        <v>6904110</v>
       </c>
       <c r="AE83" t="n">
         <v>10</v>
@@ -14862,16 +14862,16 @@
         <v>10</v>
       </c>
       <c r="AG83" t="n">
-        <v>-55</v>
+        <v>-5</v>
       </c>
       <c r="AH83" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
@@ -14879,10 +14879,10 @@
         </is>
       </c>
       <c r="AL83" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="AM83" t="n">
-        <v>-16.67</v>
+        <v>-54.55</v>
       </c>
       <c r="AN83" t="n">
         <v>0</v>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
@@ -14912,17 +14912,17 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>跌破5日線、死亡交叉、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、死亡交叉、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15451,12 +15451,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2362.TW</t>
+          <t>3702.TW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>藍天</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -15475,28 +15475,28 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>47.75</v>
+        <v>113.5</v>
       </c>
       <c r="G87" t="n">
-        <v>48.27</v>
+        <v>115.7</v>
       </c>
       <c r="H87" t="n">
-        <v>47.58</v>
+        <v>116.85</v>
       </c>
       <c r="I87" t="n">
-        <v>47.43</v>
+        <v>116.38</v>
       </c>
       <c r="J87" t="n">
-        <v>604867</v>
+        <v>8056263</v>
       </c>
       <c r="K87" t="n">
-        <v>863095</v>
+        <v>10530615</v>
       </c>
       <c r="L87" t="n">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="M87" t="n">
-        <v>46.2</v>
+        <v>111</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -15504,52 +15504,52 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>-156</v>
+        <v>798220</v>
       </c>
       <c r="P87" t="n">
-        <v>99975</v>
+        <v>1412203</v>
       </c>
       <c r="Q87" t="n">
-        <v>1129215</v>
+        <v>8445322</v>
       </c>
       <c r="R87" t="n">
-        <v>1884131</v>
+        <v>20495769</v>
       </c>
       <c r="S87" t="n">
-        <v>15148</v>
+        <v>-48782</v>
       </c>
       <c r="T87" t="n">
-        <v>127533</v>
+        <v>-1343073</v>
       </c>
       <c r="U87" t="n">
-        <v>1159775</v>
+        <v>4757844</v>
       </c>
       <c r="V87" t="n">
-        <v>1914181</v>
+        <v>15326882</v>
       </c>
       <c r="W87" t="n">
-        <v>-303</v>
+        <v>245924</v>
       </c>
       <c r="X87" t="n">
-        <v>-303</v>
+        <v>1819964</v>
       </c>
       <c r="Y87" t="n">
-        <v>-303</v>
+        <v>2083249</v>
       </c>
       <c r="Z87" t="n">
-        <v>-303</v>
+        <v>2511843</v>
       </c>
       <c r="AA87" t="n">
-        <v>-15001</v>
+        <v>601078</v>
       </c>
       <c r="AB87" t="n">
-        <v>-27255</v>
+        <v>935312</v>
       </c>
       <c r="AC87" t="n">
-        <v>-30257</v>
+        <v>1604229</v>
       </c>
       <c r="AD87" t="n">
-        <v>-29747</v>
+        <v>2657044</v>
       </c>
       <c r="AE87" t="n">
         <v>10</v>
@@ -15558,16 +15558,16 @@
         <v>10</v>
       </c>
       <c r="AG87" t="n">
-        <v>-5</v>
+        <v>-55</v>
       </c>
       <c r="AH87" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
       </c>
       <c r="AJ87" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
@@ -15575,16 +15575,16 @@
         </is>
       </c>
       <c r="AL87" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM87" t="n">
-        <v>0</v>
+        <v>-16.67</v>
       </c>
       <c r="AN87" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AO87" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -15608,17 +15608,17 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、死亡交叉、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、死亡交叉、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15799,12 +15799,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2610.TW</t>
+          <t>2882.TW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -15823,28 +15823,28 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>20.4</v>
+        <v>110</v>
       </c>
       <c r="G89" t="n">
-        <v>20.64</v>
+        <v>113.6</v>
       </c>
       <c r="H89" t="n">
-        <v>20.47</v>
+        <v>113.05</v>
       </c>
       <c r="I89" t="n">
-        <v>20.38</v>
+        <v>112.2</v>
       </c>
       <c r="J89" t="n">
-        <v>15428590</v>
+        <v>24145665</v>
       </c>
       <c r="K89" t="n">
-        <v>22313588</v>
+        <v>23479461</v>
       </c>
       <c r="L89" t="n">
-        <v>21.2</v>
+        <v>118</v>
       </c>
       <c r="M89" t="n">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -15852,52 +15852,52 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>-5385365</v>
+        <v>-7507408</v>
       </c>
       <c r="P89" t="n">
-        <v>18354331</v>
+        <v>-1532218</v>
       </c>
       <c r="Q89" t="n">
-        <v>35796426</v>
+        <v>337060</v>
       </c>
       <c r="R89" t="n">
-        <v>54393946</v>
+        <v>20787884</v>
       </c>
       <c r="S89" t="n">
-        <v>-2807597</v>
+        <v>-7371284</v>
       </c>
       <c r="T89" t="n">
-        <v>19511431</v>
+        <v>-3164697</v>
       </c>
       <c r="U89" t="n">
-        <v>37863180</v>
+        <v>-3483300</v>
       </c>
       <c r="V89" t="n">
-        <v>53143731</v>
+        <v>10019702</v>
       </c>
       <c r="W89" t="n">
-        <v>-2382180</v>
+        <v>-426439</v>
       </c>
       <c r="X89" t="n">
-        <v>-1007180</v>
+        <v>368261</v>
       </c>
       <c r="Y89" t="n">
-        <v>-1944180</v>
+        <v>240531</v>
       </c>
       <c r="Z89" t="n">
-        <v>4268820</v>
+        <v>6202106</v>
       </c>
       <c r="AA89" t="n">
-        <v>-195588</v>
+        <v>290315</v>
       </c>
       <c r="AB89" t="n">
-        <v>-149920</v>
+        <v>1264218</v>
       </c>
       <c r="AC89" t="n">
-        <v>-122574</v>
+        <v>3579829</v>
       </c>
       <c r="AD89" t="n">
-        <v>-3018605</v>
+        <v>4566076</v>
       </c>
       <c r="AE89" t="n">
         <v>10</v>
@@ -15906,16 +15906,16 @@
         <v>10</v>
       </c>
       <c r="AG89" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AH89" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
       </c>
       <c r="AJ89" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
@@ -15923,10 +15923,10 @@
         </is>
       </c>
       <c r="AL89" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="AM89" t="n">
-        <v>-44.44</v>
+        <v>-54.55</v>
       </c>
       <c r="AN89" t="n">
         <v>0</v>
@@ -15956,29 +15956,29 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1906.TW</t>
+          <t>2610.TW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>寶隆</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -15997,28 +15997,28 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>10.9</v>
+        <v>20.4</v>
       </c>
       <c r="G90" t="n">
-        <v>10.88</v>
+        <v>20.64</v>
       </c>
       <c r="H90" t="n">
-        <v>10.82</v>
+        <v>20.47</v>
       </c>
       <c r="I90" t="n">
-        <v>10.8</v>
+        <v>20.38</v>
       </c>
       <c r="J90" t="n">
-        <v>21337</v>
+        <v>15428590</v>
       </c>
       <c r="K90" t="n">
-        <v>47932</v>
+        <v>22313588</v>
       </c>
       <c r="L90" t="n">
-        <v>11.05</v>
+        <v>21.2</v>
       </c>
       <c r="M90" t="n">
-        <v>10.6</v>
+        <v>20</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -16026,52 +16026,52 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>-3698</v>
+        <v>-5385365</v>
       </c>
       <c r="P90" t="n">
-        <v>-5838</v>
+        <v>18354331</v>
       </c>
       <c r="Q90" t="n">
-        <v>-21635</v>
+        <v>35796426</v>
       </c>
       <c r="R90" t="n">
-        <v>-19449</v>
+        <v>54393946</v>
       </c>
       <c r="S90" t="n">
-        <v>-3698</v>
+        <v>-2807597</v>
       </c>
       <c r="T90" t="n">
-        <v>-5838</v>
+        <v>19511431</v>
       </c>
       <c r="U90" t="n">
-        <v>-17635</v>
+        <v>37863180</v>
       </c>
       <c r="V90" t="n">
-        <v>-17449</v>
+        <v>53143731</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>-2382180</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>-1007180</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>-1944180</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>4268820</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>-195588</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>-149920</v>
       </c>
       <c r="AC90" t="n">
-        <v>-4000</v>
+        <v>-122574</v>
       </c>
       <c r="AD90" t="n">
-        <v>-2000</v>
+        <v>-3018605</v>
       </c>
       <c r="AE90" t="n">
         <v>10</v>
@@ -16080,16 +16080,16 @@
         <v>10</v>
       </c>
       <c r="AG90" t="n">
-        <v>50</v>
+        <v>-5</v>
       </c>
       <c r="AH90" t="n">
-        <v>-25</v>
+        <v>30</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
       </c>
       <c r="AJ90" t="n">
-        <v>-6</v>
+        <v>18</v>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
@@ -16097,25 +16097,25 @@
         </is>
       </c>
       <c r="AL90" t="n">
-        <v>16</v>
+        <v>-8</v>
       </c>
       <c r="AM90" t="n">
-        <v>266.67</v>
+        <v>-44.44</v>
       </c>
       <c r="AN90" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AO90" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
@@ -16130,29 +16130,29 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>法人連續偏賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、法人連續偏賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2882.TW</t>
+          <t>2362.TW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>藍天</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16171,28 +16171,28 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>110</v>
+        <v>47.75</v>
       </c>
       <c r="G91" t="n">
-        <v>113.6</v>
+        <v>48.27</v>
       </c>
       <c r="H91" t="n">
-        <v>113.05</v>
+        <v>47.58</v>
       </c>
       <c r="I91" t="n">
-        <v>112.2</v>
+        <v>47.43</v>
       </c>
       <c r="J91" t="n">
-        <v>24145665</v>
+        <v>604867</v>
       </c>
       <c r="K91" t="n">
-        <v>23479461</v>
+        <v>863095</v>
       </c>
       <c r="L91" t="n">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="M91" t="n">
-        <v>109</v>
+        <v>46.2</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -16200,52 +16200,52 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>-7507408</v>
+        <v>-156</v>
       </c>
       <c r="P91" t="n">
-        <v>-1532218</v>
+        <v>99975</v>
       </c>
       <c r="Q91" t="n">
-        <v>337060</v>
+        <v>1129215</v>
       </c>
       <c r="R91" t="n">
-        <v>20787884</v>
+        <v>1884131</v>
       </c>
       <c r="S91" t="n">
-        <v>-7371284</v>
+        <v>15148</v>
       </c>
       <c r="T91" t="n">
-        <v>-3164697</v>
+        <v>127533</v>
       </c>
       <c r="U91" t="n">
-        <v>-3483300</v>
+        <v>1159775</v>
       </c>
       <c r="V91" t="n">
-        <v>10019702</v>
+        <v>1914181</v>
       </c>
       <c r="W91" t="n">
-        <v>-426439</v>
+        <v>-303</v>
       </c>
       <c r="X91" t="n">
-        <v>368261</v>
+        <v>-303</v>
       </c>
       <c r="Y91" t="n">
-        <v>240531</v>
+        <v>-303</v>
       </c>
       <c r="Z91" t="n">
-        <v>6202106</v>
+        <v>-303</v>
       </c>
       <c r="AA91" t="n">
-        <v>290315</v>
+        <v>-15001</v>
       </c>
       <c r="AB91" t="n">
-        <v>1264218</v>
+        <v>-27255</v>
       </c>
       <c r="AC91" t="n">
-        <v>3579829</v>
+        <v>-30257</v>
       </c>
       <c r="AD91" t="n">
-        <v>4566076</v>
+        <v>-29747</v>
       </c>
       <c r="AE91" t="n">
         <v>10</v>
@@ -16254,33 +16254,33 @@
         <v>10</v>
       </c>
       <c r="AG91" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AL91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN91" t="n">
         <v>5</v>
       </c>
-      <c r="AH91" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ91" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AL91" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AM91" t="n">
-        <v>-54.55</v>
-      </c>
-      <c r="AN91" t="n">
-        <v>0</v>
-      </c>
       <c r="AO91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
@@ -16304,29 +16304,29 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>5日法人買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8070.TW</t>
+          <t>1906.TW</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>寶隆</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -16345,28 +16345,28 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>50.1</v>
+        <v>10.9</v>
       </c>
       <c r="G92" t="n">
-        <v>51.44</v>
+        <v>10.88</v>
       </c>
       <c r="H92" t="n">
-        <v>51.46</v>
+        <v>10.82</v>
       </c>
       <c r="I92" t="n">
-        <v>50.84</v>
+        <v>10.8</v>
       </c>
       <c r="J92" t="n">
-        <v>1684433</v>
+        <v>21337</v>
       </c>
       <c r="K92" t="n">
-        <v>1984374</v>
+        <v>47932</v>
       </c>
       <c r="L92" t="n">
-        <v>53.7</v>
+        <v>11.05</v>
       </c>
       <c r="M92" t="n">
-        <v>48.75</v>
+        <v>10.6</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -16374,70 +16374,70 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>-659184</v>
+        <v>-3698</v>
       </c>
       <c r="P92" t="n">
-        <v>100355</v>
+        <v>-5838</v>
       </c>
       <c r="Q92" t="n">
-        <v>651540</v>
+        <v>-21635</v>
       </c>
       <c r="R92" t="n">
-        <v>819741</v>
+        <v>-19449</v>
       </c>
       <c r="S92" t="n">
-        <v>-623476</v>
+        <v>-3698</v>
       </c>
       <c r="T92" t="n">
-        <v>173167</v>
+        <v>-5838</v>
       </c>
       <c r="U92" t="n">
-        <v>637315</v>
+        <v>-17635</v>
       </c>
       <c r="V92" t="n">
-        <v>-586143</v>
+        <v>-17449</v>
       </c>
       <c r="W92" t="n">
-        <v>-148</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>30646</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>50221</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1397043</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>-35560</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>-103458</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>-35996</v>
+        <v>-4000</v>
       </c>
       <c r="AD92" t="n">
-        <v>8841</v>
+        <v>-2000</v>
       </c>
       <c r="AE92" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF92" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG92" t="n">
-        <v>-30</v>
+        <v>50</v>
       </c>
       <c r="AH92" t="n">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
       </c>
       <c r="AJ92" t="n">
-        <v>34</v>
+        <v>-6</v>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
@@ -16445,25 +16445,25 @@
         </is>
       </c>
       <c r="AL92" t="n">
-        <v>-26</v>
+        <v>16</v>
       </c>
       <c r="AM92" t="n">
-        <v>-76.47</v>
+        <v>266.67</v>
       </c>
       <c r="AN92" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AO92" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
@@ -16478,29 +16478,29 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏賣</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、法人連續偏賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6230.TW</t>
+          <t>8070.TW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>超眾</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -16519,28 +16519,28 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>108.5</v>
+        <v>50.1</v>
       </c>
       <c r="G93" t="n">
-        <v>110.8</v>
+        <v>51.44</v>
       </c>
       <c r="H93" t="n">
-        <v>112.3</v>
+        <v>51.46</v>
       </c>
       <c r="I93" t="n">
-        <v>112.17</v>
+        <v>50.84</v>
       </c>
       <c r="J93" t="n">
-        <v>65727</v>
+        <v>1684433</v>
       </c>
       <c r="K93" t="n">
-        <v>35473</v>
+        <v>1984374</v>
       </c>
       <c r="L93" t="n">
-        <v>118.5</v>
+        <v>53.7</v>
       </c>
       <c r="M93" t="n">
-        <v>108.5</v>
+        <v>48.75</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -16548,70 +16548,70 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>1000</v>
+        <v>-659184</v>
       </c>
       <c r="P93" t="n">
-        <v>1091</v>
+        <v>100355</v>
       </c>
       <c r="Q93" t="n">
-        <v>25769</v>
+        <v>651540</v>
       </c>
       <c r="R93" t="n">
-        <v>33413</v>
+        <v>819741</v>
       </c>
       <c r="S93" t="n">
-        <v>3000</v>
+        <v>-623476</v>
       </c>
       <c r="T93" t="n">
-        <v>3091</v>
+        <v>173167</v>
       </c>
       <c r="U93" t="n">
-        <v>27091</v>
+        <v>637315</v>
       </c>
       <c r="V93" t="n">
-        <v>35590</v>
+        <v>-586143</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>-148</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>30646</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>50221</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1397043</v>
       </c>
       <c r="AA93" t="n">
-        <v>-2000</v>
+        <v>-35560</v>
       </c>
       <c r="AB93" t="n">
-        <v>-2000</v>
+        <v>-103458</v>
       </c>
       <c r="AC93" t="n">
-        <v>-1322</v>
+        <v>-35996</v>
       </c>
       <c r="AD93" t="n">
-        <v>-2177</v>
+        <v>8841</v>
       </c>
       <c r="AE93" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF93" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG93" t="n">
-        <v>-15</v>
+        <v>-30</v>
       </c>
       <c r="AH93" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
@@ -16619,14 +16619,16 @@
         </is>
       </c>
       <c r="AL93" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM93" t="inlineStr"/>
+        <v>-26</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>-76.47</v>
+      </c>
       <c r="AN93" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AO93" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
@@ -16635,7 +16637,7 @@
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
@@ -16650,17 +16652,17 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>跌破5日線、成交量放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>法人連續偏買</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、成交量放大、接近20日低點、法人連續偏買。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -17015,12 +17017,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2850.TW</t>
+          <t>6230.TW</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>新產</t>
+          <t>超眾</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -17039,28 +17041,28 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>162</v>
+        <v>108.5</v>
       </c>
       <c r="G96" t="n">
-        <v>168</v>
+        <v>110.8</v>
       </c>
       <c r="H96" t="n">
-        <v>166.05</v>
+        <v>112.3</v>
       </c>
       <c r="I96" t="n">
-        <v>162.7</v>
+        <v>112.17</v>
       </c>
       <c r="J96" t="n">
-        <v>287983</v>
+        <v>65727</v>
       </c>
       <c r="K96" t="n">
-        <v>317091</v>
+        <v>35473</v>
       </c>
       <c r="L96" t="n">
-        <v>174</v>
+        <v>118.5</v>
       </c>
       <c r="M96" t="n">
-        <v>156</v>
+        <v>108.5</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -17068,52 +17070,52 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>-189097</v>
+        <v>1000</v>
       </c>
       <c r="P96" t="n">
-        <v>-142716</v>
+        <v>1091</v>
       </c>
       <c r="Q96" t="n">
-        <v>364138</v>
+        <v>25769</v>
       </c>
       <c r="R96" t="n">
-        <v>922841</v>
+        <v>33413</v>
       </c>
       <c r="S96" t="n">
-        <v>-181000</v>
+        <v>3000</v>
       </c>
       <c r="T96" t="n">
-        <v>-102619</v>
+        <v>3091</v>
       </c>
       <c r="U96" t="n">
-        <v>403235</v>
+        <v>27091</v>
       </c>
       <c r="V96" t="n">
-        <v>968909</v>
+        <v>35590</v>
       </c>
       <c r="W96" t="n">
-        <v>-97</v>
+        <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>-5097</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>-5097</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>-6097</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>-8000</v>
+        <v>-2000</v>
       </c>
       <c r="AB96" t="n">
-        <v>-35000</v>
+        <v>-2000</v>
       </c>
       <c r="AC96" t="n">
-        <v>-34000</v>
+        <v>-1322</v>
       </c>
       <c r="AD96" t="n">
-        <v>-39971</v>
+        <v>-2177</v>
       </c>
       <c r="AE96" t="n">
         <v>6</v>
@@ -17122,16 +17124,16 @@
         <v>6</v>
       </c>
       <c r="AG96" t="n">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="AH96" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
       </c>
       <c r="AJ96" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
@@ -17139,16 +17141,14 @@
         </is>
       </c>
       <c r="AL96" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AM96" t="n">
-        <v>-76.92</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AM96" t="inlineStr"/>
       <c r="AN96" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AO96" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
@@ -17172,29 +17172,29 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>法人連續偏買</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、成交量放大、接近20日低點、法人連續偏買。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2368.TW</t>
+          <t>2850.TW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>新產</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -17213,28 +17213,28 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1185</v>
+        <v>162</v>
       </c>
       <c r="G97" t="n">
-        <v>1226</v>
+        <v>168</v>
       </c>
       <c r="H97" t="n">
-        <v>1232.5</v>
+        <v>166.05</v>
       </c>
       <c r="I97" t="n">
-        <v>1166.5</v>
+        <v>162.7</v>
       </c>
       <c r="J97" t="n">
-        <v>11115878</v>
+        <v>287983</v>
       </c>
       <c r="K97" t="n">
-        <v>13830861</v>
+        <v>317091</v>
       </c>
       <c r="L97" t="n">
-        <v>1310</v>
+        <v>174</v>
       </c>
       <c r="M97" t="n">
-        <v>969</v>
+        <v>156</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -17242,81 +17242,81 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>-835705</v>
+        <v>-189097</v>
       </c>
       <c r="P97" t="n">
-        <v>457174</v>
+        <v>-142716</v>
       </c>
       <c r="Q97" t="n">
-        <v>1491745</v>
+        <v>364138</v>
       </c>
       <c r="R97" t="n">
-        <v>3513900</v>
+        <v>922841</v>
       </c>
       <c r="S97" t="n">
-        <v>-1614992</v>
+        <v>-181000</v>
       </c>
       <c r="T97" t="n">
-        <v>-4762318</v>
+        <v>-102619</v>
       </c>
       <c r="U97" t="n">
-        <v>-8991435</v>
+        <v>403235</v>
       </c>
       <c r="V97" t="n">
-        <v>-13291871</v>
+        <v>968909</v>
       </c>
       <c r="W97" t="n">
-        <v>733859</v>
+        <v>-97</v>
       </c>
       <c r="X97" t="n">
-        <v>4900118</v>
+        <v>-5097</v>
       </c>
       <c r="Y97" t="n">
-        <v>10362655</v>
+        <v>-5097</v>
       </c>
       <c r="Z97" t="n">
-        <v>16959985</v>
+        <v>-6097</v>
       </c>
       <c r="AA97" t="n">
-        <v>45428</v>
+        <v>-8000</v>
       </c>
       <c r="AB97" t="n">
-        <v>319374</v>
+        <v>-35000</v>
       </c>
       <c r="AC97" t="n">
-        <v>120525</v>
+        <v>-34000</v>
       </c>
       <c r="AD97" t="n">
-        <v>-154214</v>
+        <v>-39971</v>
       </c>
       <c r="AE97" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF97" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG97" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AL97" t="n">
         <v>-20</v>
       </c>
-      <c r="AH97" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ97" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AL97" t="n">
-        <v>-16</v>
-      </c>
       <c r="AM97" t="n">
-        <v>-80</v>
+        <v>-76.92</v>
       </c>
       <c r="AN97" t="n">
         <v>0</v>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
@@ -17346,29 +17346,29 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4903.TWO</t>
+          <t>2368.TW</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -17387,28 +17387,28 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>54.2</v>
+        <v>1185</v>
       </c>
       <c r="G98" t="n">
-        <v>54.52</v>
+        <v>1226</v>
       </c>
       <c r="H98" t="n">
-        <v>50.96</v>
+        <v>1232.5</v>
       </c>
       <c r="I98" t="n">
-        <v>46.74</v>
+        <v>1166.5</v>
       </c>
       <c r="J98" t="n">
-        <v>19208000</v>
+        <v>11115878</v>
       </c>
       <c r="K98" t="n">
-        <v>21203800</v>
+        <v>13830861</v>
       </c>
       <c r="L98" t="n">
-        <v>59.3</v>
+        <v>1310</v>
       </c>
       <c r="M98" t="n">
-        <v>34.3</v>
+        <v>969</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -17416,70 +17416,70 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>-835705</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>457174</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>1491745</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3513900</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>-1614992</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>-4762318</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>-8991435</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>-13291871</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>733859</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>4900118</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>10362655</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>16959985</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>45428</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>319374</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>120525</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>-154214</v>
       </c>
       <c r="AE98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG98" t="n">
-        <v>5</v>
+        <v>-20</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI98" t="n">
         <v>0</v>
       </c>
       <c r="AJ98" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
@@ -17487,16 +17487,16 @@
         </is>
       </c>
       <c r="AL98" t="n">
-        <v>-4</v>
+        <v>-16</v>
       </c>
       <c r="AM98" t="n">
-        <v>-66.67</v>
+        <v>-80</v>
       </c>
       <c r="AN98" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO98" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
@@ -17520,17 +17520,17 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -17711,12 +17711,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>4903.TWO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -17735,28 +17735,28 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>35.75</v>
+        <v>54.2</v>
       </c>
       <c r="G100" t="n">
-        <v>35.9</v>
+        <v>54.52</v>
       </c>
       <c r="H100" t="n">
-        <v>36.12</v>
+        <v>50.96</v>
       </c>
       <c r="I100" t="n">
-        <v>36.09</v>
+        <v>46.74</v>
       </c>
       <c r="J100" t="n">
-        <v>377897050</v>
+        <v>19208000</v>
       </c>
       <c r="K100" t="n">
-        <v>334354823</v>
+        <v>21203800</v>
       </c>
       <c r="L100" t="n">
-        <v>43.55</v>
+        <v>59.3</v>
       </c>
       <c r="M100" t="n">
-        <v>29.5</v>
+        <v>34.3</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -17764,87 +17764,87 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>-30301134</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>5537819</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>83371</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>-321782169</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>-31610492</v>
+        <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>518697</v>
+        <v>0</v>
       </c>
       <c r="U100" t="n">
-        <v>-4668249</v>
+        <v>0</v>
       </c>
       <c r="V100" t="n">
-        <v>-296822806</v>
+        <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>3057168</v>
+        <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>6270074</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>6528074</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>6638140</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>-1747810</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>-1250952</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>-1776454</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>-31597503</v>
+        <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG100" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="AH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AL100" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>-66.67</v>
+      </c>
+      <c r="AN100" t="n">
         <v>10</v>
       </c>
-      <c r="AI100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ100" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AL100" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AM100" t="n">
-        <v>-100</v>
-      </c>
-      <c r="AN100" t="n">
-        <v>0</v>
-      </c>
       <c r="AO100" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR100" t="inlineStr">
@@ -17868,29 +17868,29 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>5日法人小幅買超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、5日法人小幅買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1605.TW</t>
+          <t>2108.TW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>南帝</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -17909,28 +17909,28 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>37</v>
+        <v>28.9</v>
       </c>
       <c r="G101" t="n">
-        <v>38.29</v>
+        <v>29.46</v>
       </c>
       <c r="H101" t="n">
-        <v>38.79</v>
+        <v>29.54</v>
       </c>
       <c r="I101" t="n">
-        <v>38.14</v>
+        <v>29.03</v>
       </c>
       <c r="J101" t="n">
-        <v>14221644</v>
+        <v>311484</v>
       </c>
       <c r="K101" t="n">
-        <v>43184898</v>
+        <v>686936</v>
       </c>
       <c r="L101" t="n">
-        <v>41.1</v>
+        <v>31.45</v>
       </c>
       <c r="M101" t="n">
-        <v>36.2</v>
+        <v>28.1</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -17938,52 +17938,52 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>-1480515</v>
+        <v>-71347</v>
       </c>
       <c r="P101" t="n">
-        <v>-2318108</v>
+        <v>-253883</v>
       </c>
       <c r="Q101" t="n">
-        <v>1242208</v>
+        <v>735783</v>
       </c>
       <c r="R101" t="n">
-        <v>28063558</v>
+        <v>2471710</v>
       </c>
       <c r="S101" t="n">
-        <v>-696305</v>
+        <v>-60347</v>
       </c>
       <c r="T101" t="n">
-        <v>1820830</v>
+        <v>-205340</v>
       </c>
       <c r="U101" t="n">
-        <v>-1437260</v>
+        <v>805368</v>
       </c>
       <c r="V101" t="n">
-        <v>21162428</v>
+        <v>2583019</v>
       </c>
       <c r="W101" t="n">
-        <v>-156</v>
+        <v>1000</v>
       </c>
       <c r="X101" t="n">
-        <v>-3011156</v>
+        <v>-8000</v>
       </c>
       <c r="Y101" t="n">
-        <v>3728844</v>
+        <v>-8000</v>
       </c>
       <c r="Z101" t="n">
-        <v>7220634</v>
+        <v>-9000</v>
       </c>
       <c r="AA101" t="n">
-        <v>-784054</v>
+        <v>-12000</v>
       </c>
       <c r="AB101" t="n">
-        <v>-1127782</v>
+        <v>-40543</v>
       </c>
       <c r="AC101" t="n">
-        <v>-1049376</v>
+        <v>-61585</v>
       </c>
       <c r="AD101" t="n">
-        <v>-319504</v>
+        <v>-102309</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -18001,7 +18001,7 @@
         <v>0</v>
       </c>
       <c r="AJ101" t="n">
-        <v>-44</v>
+        <v>10</v>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
@@ -18009,10 +18009,10 @@
         </is>
       </c>
       <c r="AL101" t="n">
-        <v>44</v>
+        <v>-10</v>
       </c>
       <c r="AM101" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="AN101" t="n">
         <v>0</v>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
@@ -18047,24 +18047,24 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2108.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>南帝</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -18083,28 +18083,28 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>28.9</v>
+        <v>35.75</v>
       </c>
       <c r="G102" t="n">
-        <v>29.46</v>
+        <v>35.9</v>
       </c>
       <c r="H102" t="n">
-        <v>29.54</v>
+        <v>36.12</v>
       </c>
       <c r="I102" t="n">
-        <v>29.03</v>
+        <v>36.09</v>
       </c>
       <c r="J102" t="n">
-        <v>311484</v>
+        <v>377897050</v>
       </c>
       <c r="K102" t="n">
-        <v>686936</v>
+        <v>334354823</v>
       </c>
       <c r="L102" t="n">
-        <v>31.45</v>
+        <v>43.55</v>
       </c>
       <c r="M102" t="n">
-        <v>28.1</v>
+        <v>29.5</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -18112,52 +18112,52 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>-71347</v>
+        <v>-30301134</v>
       </c>
       <c r="P102" t="n">
-        <v>-253883</v>
+        <v>5537819</v>
       </c>
       <c r="Q102" t="n">
-        <v>735783</v>
+        <v>83371</v>
       </c>
       <c r="R102" t="n">
-        <v>2471710</v>
+        <v>-321782169</v>
       </c>
       <c r="S102" t="n">
-        <v>-60347</v>
+        <v>-31610492</v>
       </c>
       <c r="T102" t="n">
-        <v>-205340</v>
+        <v>518697</v>
       </c>
       <c r="U102" t="n">
-        <v>805368</v>
+        <v>-4668249</v>
       </c>
       <c r="V102" t="n">
-        <v>2583019</v>
+        <v>-296822806</v>
       </c>
       <c r="W102" t="n">
-        <v>1000</v>
+        <v>3057168</v>
       </c>
       <c r="X102" t="n">
-        <v>-8000</v>
+        <v>6270074</v>
       </c>
       <c r="Y102" t="n">
-        <v>-8000</v>
+        <v>6528074</v>
       </c>
       <c r="Z102" t="n">
-        <v>-9000</v>
+        <v>6638140</v>
       </c>
       <c r="AA102" t="n">
-        <v>-12000</v>
+        <v>-1747810</v>
       </c>
       <c r="AB102" t="n">
-        <v>-40543</v>
+        <v>-1250952</v>
       </c>
       <c r="AC102" t="n">
-        <v>-61585</v>
+        <v>-1776454</v>
       </c>
       <c r="AD102" t="n">
-        <v>-102309</v>
+        <v>-31597503</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -18166,16 +18166,16 @@
         <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="AH102" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AI102" t="n">
         <v>0</v>
       </c>
       <c r="AJ102" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         </is>
       </c>
       <c r="AL102" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="AM102" t="n">
         <v>-100</v>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
@@ -18216,29 +18216,29 @@
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人小幅買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、5日法人小幅買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2498.TW</t>
+          <t>1605.TW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -18257,28 +18257,28 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>39.95</v>
+        <v>37</v>
       </c>
       <c r="G103" t="n">
-        <v>40.21</v>
+        <v>38.29</v>
       </c>
       <c r="H103" t="n">
-        <v>40.89</v>
+        <v>38.79</v>
       </c>
       <c r="I103" t="n">
-        <v>41.33</v>
+        <v>38.14</v>
       </c>
       <c r="J103" t="n">
-        <v>2119399</v>
+        <v>14221644</v>
       </c>
       <c r="K103" t="n">
-        <v>3064223</v>
+        <v>43184898</v>
       </c>
       <c r="L103" t="n">
-        <v>46.85</v>
+        <v>41.1</v>
       </c>
       <c r="M103" t="n">
-        <v>39.55</v>
+        <v>36.2</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -18286,70 +18286,70 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>485692</v>
+        <v>-1480515</v>
       </c>
       <c r="P103" t="n">
-        <v>1234275</v>
+        <v>-2318108</v>
       </c>
       <c r="Q103" t="n">
-        <v>148487</v>
+        <v>1242208</v>
       </c>
       <c r="R103" t="n">
-        <v>492187</v>
+        <v>28063558</v>
       </c>
       <c r="S103" t="n">
-        <v>380912</v>
+        <v>-696305</v>
       </c>
       <c r="T103" t="n">
-        <v>1143019</v>
+        <v>1820830</v>
       </c>
       <c r="U103" t="n">
-        <v>156867</v>
+        <v>-1437260</v>
       </c>
       <c r="V103" t="n">
-        <v>805698</v>
+        <v>21162428</v>
       </c>
       <c r="W103" t="n">
-        <v>-211</v>
+        <v>-156</v>
       </c>
       <c r="X103" t="n">
-        <v>-211</v>
+        <v>-3011156</v>
       </c>
       <c r="Y103" t="n">
-        <v>-9211</v>
+        <v>3728844</v>
       </c>
       <c r="Z103" t="n">
-        <v>-15211</v>
+        <v>7220634</v>
       </c>
       <c r="AA103" t="n">
-        <v>104991</v>
+        <v>-784054</v>
       </c>
       <c r="AB103" t="n">
-        <v>91467</v>
+        <v>-1127782</v>
       </c>
       <c r="AC103" t="n">
-        <v>831</v>
+        <v>-1049376</v>
       </c>
       <c r="AD103" t="n">
-        <v>-298300</v>
+        <v>-319504</v>
       </c>
       <c r="AE103" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="AH103" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>
       </c>
       <c r="AJ103" t="n">
-        <v>-36</v>
+        <v>-44</v>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
@@ -18357,10 +18357,10 @@
         </is>
       </c>
       <c r="AL103" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AM103" t="n">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="AN103" t="n">
         <v>0</v>
@@ -18390,29 +18390,29 @@
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2617.TW</t>
+          <t>2498.TW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>台航</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -18431,28 +18431,28 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>31.35</v>
+        <v>39.95</v>
       </c>
       <c r="G104" t="n">
-        <v>32.08</v>
+        <v>40.21</v>
       </c>
       <c r="H104" t="n">
-        <v>32.19</v>
+        <v>40.89</v>
       </c>
       <c r="I104" t="n">
-        <v>32.22</v>
+        <v>41.33</v>
       </c>
       <c r="J104" t="n">
-        <v>712560</v>
+        <v>2119399</v>
       </c>
       <c r="K104" t="n">
-        <v>865989</v>
+        <v>3064223</v>
       </c>
       <c r="L104" t="n">
-        <v>33.35</v>
+        <v>46.85</v>
       </c>
       <c r="M104" t="n">
-        <v>30.85</v>
+        <v>39.55</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -18460,52 +18460,52 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>-49658</v>
+        <v>485692</v>
       </c>
       <c r="P104" t="n">
-        <v>117899</v>
+        <v>1234275</v>
       </c>
       <c r="Q104" t="n">
-        <v>659502</v>
+        <v>148487</v>
       </c>
       <c r="R104" t="n">
-        <v>2166085</v>
+        <v>492187</v>
       </c>
       <c r="S104" t="n">
-        <v>-255000</v>
+        <v>380912</v>
       </c>
       <c r="T104" t="n">
-        <v>-41673</v>
+        <v>1143019</v>
       </c>
       <c r="U104" t="n">
-        <v>486215</v>
+        <v>156867</v>
       </c>
       <c r="V104" t="n">
-        <v>1981096</v>
+        <v>805698</v>
       </c>
       <c r="W104" t="n">
-        <v>218000</v>
+        <v>-211</v>
       </c>
       <c r="X104" t="n">
-        <v>220000</v>
+        <v>-211</v>
       </c>
       <c r="Y104" t="n">
-        <v>220000</v>
+        <v>-9211</v>
       </c>
       <c r="Z104" t="n">
-        <v>220000</v>
+        <v>-15211</v>
       </c>
       <c r="AA104" t="n">
-        <v>-12658</v>
+        <v>104991</v>
       </c>
       <c r="AB104" t="n">
-        <v>-60428</v>
+        <v>91467</v>
       </c>
       <c r="AC104" t="n">
-        <v>-46713</v>
+        <v>831</v>
       </c>
       <c r="AD104" t="n">
-        <v>-35011</v>
+        <v>-298300</v>
       </c>
       <c r="AE104" t="n">
         <v>-2</v>
@@ -18523,7 +18523,7 @@
         <v>0</v>
       </c>
       <c r="AJ104" t="n">
-        <v>12</v>
+        <v>-36</v>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
@@ -18531,10 +18531,10 @@
         </is>
       </c>
       <c r="AL104" t="n">
-        <v>-14</v>
+        <v>34</v>
       </c>
       <c r="AM104" t="n">
-        <v>-116.67</v>
+        <v>94.44</v>
       </c>
       <c r="AN104" t="n">
         <v>0</v>
@@ -18549,7 +18549,7 @@
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
@@ -18569,12 +18569,12 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -18755,12 +18755,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6426.TW</t>
+          <t>2617.TW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>台航</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -18779,28 +18779,28 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>331</v>
+        <v>31.35</v>
       </c>
       <c r="G106" t="n">
-        <v>328.3</v>
+        <v>32.08</v>
       </c>
       <c r="H106" t="n">
-        <v>334.2</v>
+        <v>32.19</v>
       </c>
       <c r="I106" t="n">
-        <v>349.18</v>
+        <v>32.22</v>
       </c>
       <c r="J106" t="n">
-        <v>1035920</v>
+        <v>712560</v>
       </c>
       <c r="K106" t="n">
-        <v>1255430</v>
+        <v>865989</v>
       </c>
       <c r="L106" t="n">
-        <v>412</v>
+        <v>33.35</v>
       </c>
       <c r="M106" t="n">
-        <v>310</v>
+        <v>30.85</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -18808,70 +18808,70 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>56429</v>
+        <v>-49658</v>
       </c>
       <c r="P106" t="n">
-        <v>133976</v>
+        <v>117899</v>
       </c>
       <c r="Q106" t="n">
-        <v>-139728</v>
+        <v>659502</v>
       </c>
       <c r="R106" t="n">
-        <v>-1157034</v>
+        <v>2166085</v>
       </c>
       <c r="S106" t="n">
-        <v>40950</v>
+        <v>-255000</v>
       </c>
       <c r="T106" t="n">
-        <v>94367</v>
+        <v>-41673</v>
       </c>
       <c r="U106" t="n">
-        <v>-178106</v>
+        <v>486215</v>
       </c>
       <c r="V106" t="n">
-        <v>-1156687</v>
+        <v>1981096</v>
       </c>
       <c r="W106" t="n">
-        <v>12000</v>
+        <v>218000</v>
       </c>
       <c r="X106" t="n">
-        <v>23000</v>
+        <v>220000</v>
       </c>
       <c r="Y106" t="n">
-        <v>23000</v>
+        <v>220000</v>
       </c>
       <c r="Z106" t="n">
-        <v>23000</v>
+        <v>220000</v>
       </c>
       <c r="AA106" t="n">
-        <v>3479</v>
+        <v>-12658</v>
       </c>
       <c r="AB106" t="n">
-        <v>16609</v>
+        <v>-60428</v>
       </c>
       <c r="AC106" t="n">
-        <v>15378</v>
+        <v>-46713</v>
       </c>
       <c r="AD106" t="n">
-        <v>-23347</v>
+        <v>-35011</v>
       </c>
       <c r="AE106" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AF106" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AG106" t="n">
-        <v>-5</v>
+        <v>-55</v>
       </c>
       <c r="AH106" t="n">
-        <v>-5</v>
+        <v>50</v>
       </c>
       <c r="AI106" t="n">
         <v>0</v>
       </c>
       <c r="AJ106" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
@@ -18879,25 +18879,25 @@
         </is>
       </c>
       <c r="AL106" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AM106" t="n">
-        <v>0</v>
+        <v>-116.67</v>
       </c>
       <c r="AN106" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AO106" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
@@ -18912,17 +18912,17 @@
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -19277,12 +19277,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2485.TW</t>
+          <t>6426.TW</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -19301,28 +19301,28 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>38.5</v>
+        <v>331</v>
       </c>
       <c r="G109" t="n">
-        <v>39.49</v>
+        <v>328.3</v>
       </c>
       <c r="H109" t="n">
-        <v>40.7</v>
+        <v>334.2</v>
       </c>
       <c r="I109" t="n">
-        <v>40.67</v>
+        <v>349.18</v>
       </c>
       <c r="J109" t="n">
-        <v>2869240</v>
+        <v>1035920</v>
       </c>
       <c r="K109" t="n">
-        <v>3393234</v>
+        <v>1255430</v>
       </c>
       <c r="L109" t="n">
-        <v>48</v>
+        <v>412</v>
       </c>
       <c r="M109" t="n">
-        <v>38.35</v>
+        <v>310</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -19330,52 +19330,52 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>-613883</v>
+        <v>56429</v>
       </c>
       <c r="P109" t="n">
-        <v>897300</v>
+        <v>133976</v>
       </c>
       <c r="Q109" t="n">
-        <v>498881</v>
+        <v>-139728</v>
       </c>
       <c r="R109" t="n">
-        <v>-13240499</v>
+        <v>-1157034</v>
       </c>
       <c r="S109" t="n">
-        <v>-523705</v>
+        <v>40950</v>
       </c>
       <c r="T109" t="n">
-        <v>894855</v>
+        <v>94367</v>
       </c>
       <c r="U109" t="n">
-        <v>660484</v>
+        <v>-178106</v>
       </c>
       <c r="V109" t="n">
-        <v>-12266533</v>
+        <v>-1156687</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="AA109" t="n">
-        <v>-90178</v>
+        <v>3479</v>
       </c>
       <c r="AB109" t="n">
-        <v>2445</v>
+        <v>16609</v>
       </c>
       <c r="AC109" t="n">
-        <v>-161603</v>
+        <v>15378</v>
       </c>
       <c r="AD109" t="n">
-        <v>-973966</v>
+        <v>-23347</v>
       </c>
       <c r="AE109" t="n">
         <v>-4</v>
@@ -19384,16 +19384,16 @@
         <v>-4</v>
       </c>
       <c r="AG109" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
       <c r="AH109" t="n">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="AI109" t="n">
         <v>0</v>
       </c>
       <c r="AJ109" t="n">
-        <v>-18</v>
+        <v>-4</v>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
@@ -19401,25 +19401,25 @@
         </is>
       </c>
       <c r="AL109" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AM109" t="n">
-        <v>77.78</v>
+        <v>0</v>
       </c>
       <c r="AN109" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AO109" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
@@ -19434,29 +19434,29 @@
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2540.TW</t>
+          <t>2485.TW</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>愛山林</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -19475,28 +19475,28 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>46.8</v>
+        <v>38.5</v>
       </c>
       <c r="G110" t="n">
-        <v>48.64</v>
+        <v>39.49</v>
       </c>
       <c r="H110" t="n">
-        <v>48.82</v>
+        <v>40.7</v>
       </c>
       <c r="I110" t="n">
-        <v>48.83</v>
+        <v>40.67</v>
       </c>
       <c r="J110" t="n">
-        <v>627046</v>
+        <v>2869240</v>
       </c>
       <c r="K110" t="n">
-        <v>427972</v>
+        <v>3393234</v>
       </c>
       <c r="L110" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M110" t="n">
-        <v>46.4</v>
+        <v>38.35</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -19504,70 +19504,70 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>-156485</v>
+        <v>-613883</v>
       </c>
       <c r="P110" t="n">
-        <v>-37986</v>
+        <v>897300</v>
       </c>
       <c r="Q110" t="n">
-        <v>560401</v>
+        <v>498881</v>
       </c>
       <c r="R110" t="n">
-        <v>1887942</v>
+        <v>-13240499</v>
       </c>
       <c r="S110" t="n">
-        <v>-80000</v>
+        <v>-523705</v>
       </c>
       <c r="T110" t="n">
-        <v>61499</v>
+        <v>894855</v>
       </c>
       <c r="U110" t="n">
-        <v>651886</v>
+        <v>660484</v>
       </c>
       <c r="V110" t="n">
-        <v>1982427</v>
+        <v>-12266533</v>
       </c>
       <c r="W110" t="n">
-        <v>-485</v>
+        <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>-485</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>-485</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>-485</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>-76000</v>
+        <v>-90178</v>
       </c>
       <c r="AB110" t="n">
-        <v>-99000</v>
+        <v>2445</v>
       </c>
       <c r="AC110" t="n">
-        <v>-91000</v>
+        <v>-161603</v>
       </c>
       <c r="AD110" t="n">
-        <v>-94000</v>
+        <v>-973966</v>
       </c>
       <c r="AE110" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AF110" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AG110" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="AH110" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
       </c>
       <c r="AJ110" t="n">
-        <v>12</v>
+        <v>-18</v>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
@@ -19575,16 +19575,16 @@
         </is>
       </c>
       <c r="AL110" t="n">
-        <v>-18</v>
+        <v>14</v>
       </c>
       <c r="AM110" t="n">
-        <v>-150</v>
+        <v>77.78</v>
       </c>
       <c r="AN110" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO110" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
@@ -19608,29 +19608,29 @@
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>2436.TW</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>偉詮電</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -19649,28 +19649,28 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>14.6</v>
+        <v>68.2</v>
       </c>
       <c r="G111" t="n">
-        <v>14.88</v>
+        <v>69.92</v>
       </c>
       <c r="H111" t="n">
-        <v>15.04</v>
+        <v>70.94</v>
       </c>
       <c r="I111" t="n">
-        <v>15.17</v>
+        <v>71.7</v>
       </c>
       <c r="J111" t="n">
-        <v>18141396</v>
+        <v>1453285</v>
       </c>
       <c r="K111" t="n">
-        <v>23746242</v>
+        <v>2025281</v>
       </c>
       <c r="L111" t="n">
-        <v>17.5</v>
+        <v>77.5</v>
       </c>
       <c r="M111" t="n">
-        <v>13.85</v>
+        <v>67.2</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -19678,52 +19678,52 @@
         </is>
       </c>
       <c r="O111" t="n">
-        <v>-2658630</v>
+        <v>-42891</v>
       </c>
       <c r="P111" t="n">
-        <v>1797485</v>
+        <v>111079</v>
       </c>
       <c r="Q111" t="n">
-        <v>1701026</v>
+        <v>387051</v>
       </c>
       <c r="R111" t="n">
-        <v>-15230459</v>
+        <v>1320776</v>
       </c>
       <c r="S111" t="n">
-        <v>-2482500</v>
+        <v>-19321</v>
       </c>
       <c r="T111" t="n">
-        <v>1733986</v>
+        <v>212003</v>
       </c>
       <c r="U111" t="n">
-        <v>1723577</v>
+        <v>471356</v>
       </c>
       <c r="V111" t="n">
-        <v>-15011202</v>
+        <v>1833086</v>
       </c>
       <c r="W111" t="n">
-        <v>-247</v>
+        <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>-247</v>
+        <v>59000</v>
       </c>
       <c r="Y111" t="n">
-        <v>-247</v>
+        <v>94000</v>
       </c>
       <c r="Z111" t="n">
-        <v>-247</v>
+        <v>100000</v>
       </c>
       <c r="AA111" t="n">
-        <v>-175883</v>
+        <v>-23570</v>
       </c>
       <c r="AB111" t="n">
-        <v>63746</v>
+        <v>-159924</v>
       </c>
       <c r="AC111" t="n">
-        <v>-22304</v>
+        <v>-178305</v>
       </c>
       <c r="AD111" t="n">
-        <v>-219010</v>
+        <v>-612310</v>
       </c>
       <c r="AE111" t="n">
         <v>-6</v>
@@ -19732,16 +19732,16 @@
         <v>-6</v>
       </c>
       <c r="AG111" t="n">
-        <v>-45</v>
+        <v>-55</v>
       </c>
       <c r="AH111" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
       </c>
       <c r="AJ111" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
@@ -19749,10 +19749,10 @@
         </is>
       </c>
       <c r="AL111" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="AM111" t="n">
-        <v>-250</v>
+        <v>-200</v>
       </c>
       <c r="AN111" t="n">
         <v>0</v>
@@ -19782,29 +19782,29 @@
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2436.TW</t>
+          <t>2540.TW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>偉詮電</t>
+          <t>愛山林</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -19823,28 +19823,28 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>68.2</v>
+        <v>46.8</v>
       </c>
       <c r="G112" t="n">
-        <v>69.92</v>
+        <v>48.64</v>
       </c>
       <c r="H112" t="n">
-        <v>70.94</v>
+        <v>48.82</v>
       </c>
       <c r="I112" t="n">
-        <v>71.7</v>
+        <v>48.83</v>
       </c>
       <c r="J112" t="n">
-        <v>1453285</v>
+        <v>627046</v>
       </c>
       <c r="K112" t="n">
-        <v>2025281</v>
+        <v>427972</v>
       </c>
       <c r="L112" t="n">
-        <v>77.5</v>
+        <v>54</v>
       </c>
       <c r="M112" t="n">
-        <v>67.2</v>
+        <v>46.4</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -19852,52 +19852,52 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>-42891</v>
+        <v>-156485</v>
       </c>
       <c r="P112" t="n">
-        <v>111079</v>
+        <v>-37986</v>
       </c>
       <c r="Q112" t="n">
-        <v>387051</v>
+        <v>560401</v>
       </c>
       <c r="R112" t="n">
-        <v>1320776</v>
+        <v>1887942</v>
       </c>
       <c r="S112" t="n">
-        <v>-19321</v>
+        <v>-80000</v>
       </c>
       <c r="T112" t="n">
-        <v>212003</v>
+        <v>61499</v>
       </c>
       <c r="U112" t="n">
-        <v>471356</v>
+        <v>651886</v>
       </c>
       <c r="V112" t="n">
-        <v>1833086</v>
+        <v>1982427</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>-485</v>
       </c>
       <c r="X112" t="n">
-        <v>59000</v>
+        <v>-485</v>
       </c>
       <c r="Y112" t="n">
-        <v>94000</v>
+        <v>-485</v>
       </c>
       <c r="Z112" t="n">
-        <v>100000</v>
+        <v>-485</v>
       </c>
       <c r="AA112" t="n">
-        <v>-23570</v>
+        <v>-76000</v>
       </c>
       <c r="AB112" t="n">
-        <v>-159924</v>
+        <v>-99000</v>
       </c>
       <c r="AC112" t="n">
-        <v>-178305</v>
+        <v>-91000</v>
       </c>
       <c r="AD112" t="n">
-        <v>-612310</v>
+        <v>-94000</v>
       </c>
       <c r="AE112" t="n">
         <v>-6</v>
@@ -19906,16 +19906,16 @@
         <v>-6</v>
       </c>
       <c r="AG112" t="n">
-        <v>-55</v>
+        <v>-45</v>
       </c>
       <c r="AH112" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
       </c>
       <c r="AJ112" t="n">
-        <v>-2</v>
+        <v>12</v>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
@@ -19923,10 +19923,10 @@
         </is>
       </c>
       <c r="AL112" t="n">
-        <v>-4</v>
+        <v>-18</v>
       </c>
       <c r="AM112" t="n">
-        <v>-200</v>
+        <v>-150</v>
       </c>
       <c r="AN112" t="n">
         <v>0</v>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -19956,29 +19956,29 @@
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2748.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>雲品</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -19997,28 +19997,28 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>38.3</v>
+        <v>14.6</v>
       </c>
       <c r="G113" t="n">
-        <v>38.53</v>
+        <v>14.88</v>
       </c>
       <c r="H113" t="n">
-        <v>38.62</v>
+        <v>15.04</v>
       </c>
       <c r="I113" t="n">
-        <v>38.72</v>
+        <v>15.17</v>
       </c>
       <c r="J113" t="n">
-        <v>65033</v>
+        <v>18141396</v>
       </c>
       <c r="K113" t="n">
-        <v>52089</v>
+        <v>23746242</v>
       </c>
       <c r="L113" t="n">
-        <v>39.5</v>
+        <v>17.5</v>
       </c>
       <c r="M113" t="n">
-        <v>38.1</v>
+        <v>13.85</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -20026,52 +20026,52 @@
         </is>
       </c>
       <c r="O113" t="n">
-        <v>18000</v>
+        <v>-2658630</v>
       </c>
       <c r="P113" t="n">
-        <v>12000</v>
+        <v>1797485</v>
       </c>
       <c r="Q113" t="n">
-        <v>35000</v>
+        <v>1701026</v>
       </c>
       <c r="R113" t="n">
-        <v>18000</v>
+        <v>-15230459</v>
       </c>
       <c r="S113" t="n">
-        <v>21000</v>
+        <v>-2482500</v>
       </c>
       <c r="T113" t="n">
-        <v>17000</v>
+        <v>1733986</v>
       </c>
       <c r="U113" t="n">
-        <v>38000</v>
+        <v>1723577</v>
       </c>
       <c r="V113" t="n">
-        <v>22000</v>
+        <v>-15011202</v>
       </c>
       <c r="W113" t="n">
-        <v>0</v>
+        <v>-247</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>-247</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>-247</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>-247</v>
       </c>
       <c r="AA113" t="n">
-        <v>-3000</v>
+        <v>-175883</v>
       </c>
       <c r="AB113" t="n">
-        <v>-5000</v>
+        <v>63746</v>
       </c>
       <c r="AC113" t="n">
-        <v>-3000</v>
+        <v>-22304</v>
       </c>
       <c r="AD113" t="n">
-        <v>-4000</v>
+        <v>-219010</v>
       </c>
       <c r="AE113" t="n">
         <v>-6</v>
@@ -20089,7 +20089,7 @@
         <v>0</v>
       </c>
       <c r="AJ113" t="n">
-        <v>-18</v>
+        <v>4</v>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
@@ -20097,16 +20097,16 @@
         </is>
       </c>
       <c r="AL113" t="n">
-        <v>12</v>
+        <v>-10</v>
       </c>
       <c r="AM113" t="n">
-        <v>66.67</v>
+        <v>-250</v>
       </c>
       <c r="AN113" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AO113" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
@@ -20130,29 +20130,29 @@
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>法人連續偏買</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>2748.TW</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>雲品</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -20171,28 +20171,28 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1550</v>
+        <v>38.3</v>
       </c>
       <c r="G114" t="n">
-        <v>1631</v>
+        <v>38.53</v>
       </c>
       <c r="H114" t="n">
-        <v>1676</v>
+        <v>38.62</v>
       </c>
       <c r="I114" t="n">
-        <v>1595</v>
+        <v>38.72</v>
       </c>
       <c r="J114" t="n">
-        <v>9283000</v>
+        <v>65033</v>
       </c>
       <c r="K114" t="n">
-        <v>10897600</v>
+        <v>52089</v>
       </c>
       <c r="L114" t="n">
-        <v>1835</v>
+        <v>39.5</v>
       </c>
       <c r="M114" t="n">
-        <v>1335</v>
+        <v>38.1</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
@@ -20200,28 +20200,28 @@
         </is>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="S114" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="T114" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="U114" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="V114" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="W114" t="n">
         <v>0</v>
@@ -20236,34 +20236,34 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="AD114" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="AE114" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AF114" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AG114" t="n">
-        <v>-20</v>
+        <v>-45</v>
       </c>
       <c r="AH114" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI114" t="n">
         <v>0</v>
       </c>
       <c r="AJ114" t="n">
-        <v>-8</v>
+        <v>-18</v>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
@@ -20271,16 +20271,16 @@
         </is>
       </c>
       <c r="AL114" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AM114" t="n">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="AN114" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO114" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
@@ -20304,29 +20304,29 @@
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏買</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -20345,28 +20345,28 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>475</v>
+        <v>1550</v>
       </c>
       <c r="G115" t="n">
-        <v>503.4</v>
+        <v>1631</v>
       </c>
       <c r="H115" t="n">
-        <v>541.4</v>
+        <v>1676</v>
       </c>
       <c r="I115" t="n">
-        <v>534.17</v>
+        <v>1595</v>
       </c>
       <c r="J115" t="n">
-        <v>25520000</v>
+        <v>9283000</v>
       </c>
       <c r="K115" t="n">
-        <v>18246600</v>
+        <v>10897600</v>
       </c>
       <c r="L115" t="n">
-        <v>630</v>
+        <v>1835</v>
       </c>
       <c r="M115" t="n">
-        <v>454</v>
+        <v>1335</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>0</v>
       </c>
       <c r="AJ115" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
@@ -20445,16 +20445,16 @@
         </is>
       </c>
       <c r="AL115" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AM115" t="n">
-        <v>42.86</v>
+        <v>0</v>
       </c>
       <c r="AN115" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AO115" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
@@ -20478,7 +20478,7 @@
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
@@ -20488,7 +20488,7 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -20669,12 +20669,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2331.TW</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>精英</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -20693,116 +20693,116 @@
         </is>
       </c>
       <c r="F117" t="n">
+        <v>475</v>
+      </c>
+      <c r="G117" t="n">
+        <v>503.4</v>
+      </c>
+      <c r="H117" t="n">
+        <v>541.4</v>
+      </c>
+      <c r="I117" t="n">
+        <v>534.17</v>
+      </c>
+      <c r="J117" t="n">
+        <v>25520000</v>
+      </c>
+      <c r="K117" t="n">
+        <v>18246600</v>
+      </c>
+      <c r="L117" t="n">
+        <v>630</v>
+      </c>
+      <c r="M117" t="n">
+        <v>454</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AL117" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="AN117" t="n">
         <v>18</v>
       </c>
-      <c r="G117" t="n">
-        <v>18.23</v>
-      </c>
-      <c r="H117" t="n">
-        <v>18.49</v>
-      </c>
-      <c r="I117" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="J117" t="n">
-        <v>653775</v>
-      </c>
-      <c r="K117" t="n">
-        <v>1173004</v>
-      </c>
-      <c r="L117" t="n">
-        <v>19.65</v>
-      </c>
-      <c r="M117" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>無明顯異常</t>
-        </is>
-      </c>
-      <c r="O117" t="n">
-        <v>153058</v>
-      </c>
-      <c r="P117" t="n">
-        <v>-115825</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>616771</v>
-      </c>
-      <c r="R117" t="n">
-        <v>398480</v>
-      </c>
-      <c r="S117" t="n">
-        <v>169433</v>
-      </c>
-      <c r="T117" t="n">
-        <v>88433</v>
-      </c>
-      <c r="U117" t="n">
-        <v>593029</v>
-      </c>
-      <c r="V117" t="n">
-        <v>418738</v>
-      </c>
-      <c r="W117" t="n">
-        <v>0</v>
-      </c>
-      <c r="X117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA117" t="n">
-        <v>-16375</v>
-      </c>
-      <c r="AB117" t="n">
-        <v>-204258</v>
-      </c>
-      <c r="AC117" t="n">
-        <v>23742</v>
-      </c>
-      <c r="AD117" t="n">
-        <v>-20258</v>
-      </c>
-      <c r="AE117" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AF117" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AG117" t="n">
-        <v>-55</v>
-      </c>
-      <c r="AH117" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ117" t="n">
-        <v>-22</v>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AL117" t="n">
-        <v>12</v>
-      </c>
-      <c r="AM117" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="AN117" t="n">
-        <v>10</v>
-      </c>
       <c r="AO117" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
@@ -20826,17 +20826,17 @@
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -21017,12 +21017,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1710.TW</t>
+          <t>2331.TW</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>東聯</t>
+          <t>精英</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -21041,28 +21041,28 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>17.45</v>
+        <v>18</v>
       </c>
       <c r="G119" t="n">
-        <v>18.22</v>
+        <v>18.23</v>
       </c>
       <c r="H119" t="n">
-        <v>18.16</v>
+        <v>18.49</v>
       </c>
       <c r="I119" t="n">
-        <v>17.49</v>
+        <v>18.75</v>
       </c>
       <c r="J119" t="n">
-        <v>3493614</v>
+        <v>653775</v>
       </c>
       <c r="K119" t="n">
-        <v>9983520</v>
+        <v>1173004</v>
       </c>
       <c r="L119" t="n">
-        <v>20</v>
+        <v>19.65</v>
       </c>
       <c r="M119" t="n">
-        <v>16.05</v>
+        <v>17.85</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -21070,28 +21070,28 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>324758</v>
+        <v>153058</v>
       </c>
       <c r="P119" t="n">
-        <v>536218</v>
+        <v>-115825</v>
       </c>
       <c r="Q119" t="n">
-        <v>-833957</v>
+        <v>616771</v>
       </c>
       <c r="R119" t="n">
-        <v>10427970</v>
+        <v>398480</v>
       </c>
       <c r="S119" t="n">
-        <v>853801</v>
+        <v>169433</v>
       </c>
       <c r="T119" t="n">
-        <v>1822102</v>
+        <v>88433</v>
       </c>
       <c r="U119" t="n">
-        <v>529240</v>
+        <v>593029</v>
       </c>
       <c r="V119" t="n">
-        <v>10635756</v>
+        <v>418738</v>
       </c>
       <c r="W119" t="n">
         <v>0</v>
@@ -21106,16 +21106,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>-529043</v>
+        <v>-16375</v>
       </c>
       <c r="AB119" t="n">
-        <v>-1285884</v>
+        <v>-204258</v>
       </c>
       <c r="AC119" t="n">
-        <v>-1363197</v>
+        <v>23742</v>
       </c>
       <c r="AD119" t="n">
-        <v>-207786</v>
+        <v>-20258</v>
       </c>
       <c r="AE119" t="n">
         <v>-10</v>
@@ -21124,16 +21124,16 @@
         <v>-10</v>
       </c>
       <c r="AG119" t="n">
-        <v>5</v>
+        <v>-55</v>
       </c>
       <c r="AH119" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
       <c r="AI119" t="n">
         <v>0</v>
       </c>
       <c r="AJ119" t="n">
-        <v>14</v>
+        <v>-22</v>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
@@ -21141,16 +21141,16 @@
         </is>
       </c>
       <c r="AL119" t="n">
-        <v>-24</v>
+        <v>12</v>
       </c>
       <c r="AM119" t="n">
-        <v>-171.43</v>
+        <v>54.55</v>
       </c>
       <c r="AN119" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO119" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
@@ -21174,29 +21174,29 @@
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2371.TW</t>
+          <t>1710.TW</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>大同</t>
+          <t>東聯</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -21215,28 +21215,28 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>28.3</v>
+        <v>17.45</v>
       </c>
       <c r="G120" t="n">
-        <v>29.07</v>
+        <v>18.22</v>
       </c>
       <c r="H120" t="n">
-        <v>29.59</v>
+        <v>18.16</v>
       </c>
       <c r="I120" t="n">
-        <v>29.7</v>
+        <v>17.49</v>
       </c>
       <c r="J120" t="n">
-        <v>7685780</v>
+        <v>3493614</v>
       </c>
       <c r="K120" t="n">
-        <v>9680223</v>
+        <v>9983520</v>
       </c>
       <c r="L120" t="n">
-        <v>31.6</v>
+        <v>20</v>
       </c>
       <c r="M120" t="n">
-        <v>28.3</v>
+        <v>16.05</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -21244,52 +21244,52 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>-1687696</v>
+        <v>324758</v>
       </c>
       <c r="P120" t="n">
-        <v>-1830439</v>
+        <v>536218</v>
       </c>
       <c r="Q120" t="n">
-        <v>2474254</v>
+        <v>-833957</v>
       </c>
       <c r="R120" t="n">
-        <v>-2200377</v>
+        <v>10427970</v>
       </c>
       <c r="S120" t="n">
-        <v>-1625840</v>
+        <v>853801</v>
       </c>
       <c r="T120" t="n">
-        <v>-1680248</v>
+        <v>1822102</v>
       </c>
       <c r="U120" t="n">
-        <v>2506841</v>
+        <v>529240</v>
       </c>
       <c r="V120" t="n">
-        <v>-1786722</v>
+        <v>10635756</v>
       </c>
       <c r="W120" t="n">
-        <v>-444</v>
+        <v>0</v>
       </c>
       <c r="X120" t="n">
-        <v>-444</v>
+        <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>-444</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>-122444</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>-61412</v>
+        <v>-529043</v>
       </c>
       <c r="AB120" t="n">
-        <v>-149747</v>
+        <v>-1285884</v>
       </c>
       <c r="AC120" t="n">
-        <v>-32143</v>
+        <v>-1363197</v>
       </c>
       <c r="AD120" t="n">
-        <v>-291211</v>
+        <v>-207786</v>
       </c>
       <c r="AE120" t="n">
         <v>-10</v>
@@ -21298,16 +21298,16 @@
         <v>-10</v>
       </c>
       <c r="AG120" t="n">
-        <v>-55</v>
+        <v>5</v>
       </c>
       <c r="AH120" t="n">
-        <v>30</v>
+        <v>-30</v>
       </c>
       <c r="AI120" t="n">
         <v>0</v>
       </c>
       <c r="AJ120" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
@@ -21315,10 +21315,10 @@
         </is>
       </c>
       <c r="AL120" t="n">
-        <v>-14</v>
+        <v>-24</v>
       </c>
       <c r="AM120" t="n">
-        <v>-350</v>
+        <v>-171.43</v>
       </c>
       <c r="AN120" t="n">
         <v>0</v>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
@@ -21348,17 +21348,17 @@
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -21539,12 +21539,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2731.TW</t>
+          <t>2371.TW</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>雄獅</t>
+          <t>大同</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -21563,28 +21563,28 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>142.5</v>
+        <v>28.3</v>
       </c>
       <c r="G122" t="n">
-        <v>143.2</v>
+        <v>29.07</v>
       </c>
       <c r="H122" t="n">
-        <v>143.75</v>
+        <v>29.59</v>
       </c>
       <c r="I122" t="n">
-        <v>143.78</v>
+        <v>29.7</v>
       </c>
       <c r="J122" t="n">
-        <v>219354</v>
+        <v>7685780</v>
       </c>
       <c r="K122" t="n">
-        <v>321647</v>
+        <v>9680223</v>
       </c>
       <c r="L122" t="n">
-        <v>146</v>
+        <v>31.6</v>
       </c>
       <c r="M122" t="n">
-        <v>141.5</v>
+        <v>28.3</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -21592,52 +21592,52 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>13204</v>
+        <v>-1687696</v>
       </c>
       <c r="P122" t="n">
-        <v>50289</v>
+        <v>-1830439</v>
       </c>
       <c r="Q122" t="n">
-        <v>18473</v>
+        <v>2474254</v>
       </c>
       <c r="R122" t="n">
-        <v>243634</v>
+        <v>-2200377</v>
       </c>
       <c r="S122" t="n">
-        <v>-47177</v>
+        <v>-1625840</v>
       </c>
       <c r="T122" t="n">
-        <v>18908</v>
+        <v>-1680248</v>
       </c>
       <c r="U122" t="n">
-        <v>-8908</v>
+        <v>2506841</v>
       </c>
       <c r="V122" t="n">
-        <v>215019</v>
+        <v>-1786722</v>
       </c>
       <c r="W122" t="n">
-        <v>66000</v>
+        <v>-444</v>
       </c>
       <c r="X122" t="n">
-        <v>38000</v>
+        <v>-444</v>
       </c>
       <c r="Y122" t="n">
-        <v>38000</v>
+        <v>-444</v>
       </c>
       <c r="Z122" t="n">
-        <v>38000</v>
+        <v>-122444</v>
       </c>
       <c r="AA122" t="n">
-        <v>-5619</v>
+        <v>-61412</v>
       </c>
       <c r="AB122" t="n">
-        <v>-6619</v>
+        <v>-149747</v>
       </c>
       <c r="AC122" t="n">
-        <v>-10619</v>
+        <v>-32143</v>
       </c>
       <c r="AD122" t="n">
-        <v>-9385</v>
+        <v>-291211</v>
       </c>
       <c r="AE122" t="n">
         <v>-10</v>
@@ -21655,7 +21655,7 @@
         <v>0</v>
       </c>
       <c r="AJ122" t="n">
-        <v>-12</v>
+        <v>4</v>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
@@ -21663,16 +21663,16 @@
         </is>
       </c>
       <c r="AL122" t="n">
-        <v>2</v>
+        <v>-14</v>
       </c>
       <c r="AM122" t="n">
-        <v>16.67</v>
+        <v>-350</v>
       </c>
       <c r="AN122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
@@ -21701,24 +21701,24 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>法人連續偏買、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2351.TW</t>
+          <t>2731.TW</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>順德</t>
+          <t>雄獅</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -21737,28 +21737,28 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>195.5</v>
+        <v>142.5</v>
       </c>
       <c r="G123" t="n">
-        <v>203.1</v>
+        <v>143.2</v>
       </c>
       <c r="H123" t="n">
-        <v>208.95</v>
+        <v>143.75</v>
       </c>
       <c r="I123" t="n">
-        <v>216.1</v>
+        <v>143.78</v>
       </c>
       <c r="J123" t="n">
-        <v>1830315</v>
+        <v>219354</v>
       </c>
       <c r="K123" t="n">
-        <v>2479494</v>
+        <v>321647</v>
       </c>
       <c r="L123" t="n">
-        <v>243.5</v>
+        <v>146</v>
       </c>
       <c r="M123" t="n">
-        <v>193.5</v>
+        <v>141.5</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
@@ -21766,52 +21766,52 @@
         </is>
       </c>
       <c r="O123" t="n">
-        <v>-38182</v>
+        <v>13204</v>
       </c>
       <c r="P123" t="n">
-        <v>750637</v>
+        <v>50289</v>
       </c>
       <c r="Q123" t="n">
-        <v>748019</v>
+        <v>18473</v>
       </c>
       <c r="R123" t="n">
-        <v>1213321</v>
+        <v>243634</v>
       </c>
       <c r="S123" t="n">
-        <v>8887</v>
+        <v>-47177</v>
       </c>
       <c r="T123" t="n">
-        <v>-734192</v>
+        <v>18908</v>
       </c>
       <c r="U123" t="n">
-        <v>-2113769</v>
+        <v>-8908</v>
       </c>
       <c r="V123" t="n">
-        <v>-1244842</v>
+        <v>215019</v>
       </c>
       <c r="W123" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="X123" t="n">
-        <v>1569000</v>
+        <v>38000</v>
       </c>
       <c r="Y123" t="n">
-        <v>2940000</v>
+        <v>38000</v>
       </c>
       <c r="Z123" t="n">
-        <v>2955000</v>
+        <v>38000</v>
       </c>
       <c r="AA123" t="n">
-        <v>-47069</v>
+        <v>-5619</v>
       </c>
       <c r="AB123" t="n">
-        <v>-84171</v>
+        <v>-6619</v>
       </c>
       <c r="AC123" t="n">
-        <v>-78212</v>
+        <v>-10619</v>
       </c>
       <c r="AD123" t="n">
-        <v>-496837</v>
+        <v>-9385</v>
       </c>
       <c r="AE123" t="n">
         <v>-10</v>
@@ -21829,24 +21829,24 @@
         <v>0</v>
       </c>
       <c r="AJ123" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AL123" t="n">
         <v>2</v>
       </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AL123" t="n">
-        <v>-12</v>
-      </c>
       <c r="AM123" t="n">
-        <v>-600</v>
+        <v>16.67</v>
       </c>
       <c r="AN123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR123" t="inlineStr">
@@ -21875,24 +21875,24 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、投信買外資賣</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>2351.TW</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>順德</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -21911,28 +21911,28 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>203.5</v>
+        <v>195.5</v>
       </c>
       <c r="G124" t="n">
-        <v>212.1</v>
+        <v>203.1</v>
       </c>
       <c r="H124" t="n">
-        <v>225.1</v>
+        <v>208.95</v>
       </c>
       <c r="I124" t="n">
-        <v>222.25</v>
+        <v>216.1</v>
       </c>
       <c r="J124" t="n">
-        <v>1497000</v>
+        <v>1830315</v>
       </c>
       <c r="K124" t="n">
-        <v>2580000</v>
+        <v>2479494</v>
       </c>
       <c r="L124" t="n">
-        <v>256</v>
+        <v>243.5</v>
       </c>
       <c r="M124" t="n">
-        <v>194</v>
+        <v>193.5</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
@@ -21940,81 +21940,81 @@
         </is>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>-38182</v>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>750637</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>748019</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>1213321</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>8887</v>
       </c>
       <c r="T124" t="n">
-        <v>0</v>
+        <v>-734192</v>
       </c>
       <c r="U124" t="n">
-        <v>0</v>
+        <v>-2113769</v>
       </c>
       <c r="V124" t="n">
-        <v>0</v>
+        <v>-1244842</v>
       </c>
       <c r="W124" t="n">
         <v>0</v>
       </c>
       <c r="X124" t="n">
-        <v>0</v>
+        <v>1569000</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>2940000</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>2955000</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>-47069</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>-84171</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>-78212</v>
       </c>
       <c r="AD124" t="n">
-        <v>0</v>
+        <v>-496837</v>
       </c>
       <c r="AE124" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AL124" t="n">
         <v>-12</v>
       </c>
-      <c r="AF124" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AG124" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AH124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ124" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AL124" t="n">
-        <v>0</v>
-      </c>
       <c r="AM124" t="n">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="AN124" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
@@ -22044,29 +22044,29 @@
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3081.TWO</t>
+          <t>5530.TWO</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>龍巖</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -22085,28 +22085,28 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2490</v>
+        <v>47.95</v>
       </c>
       <c r="G125" t="n">
-        <v>2625</v>
+        <v>48.17</v>
       </c>
       <c r="H125" t="n">
-        <v>2789.5</v>
+        <v>48.16</v>
       </c>
       <c r="I125" t="n">
-        <v>2789.25</v>
+        <v>48.48</v>
       </c>
       <c r="J125" t="n">
-        <v>2252000</v>
+        <v>127000</v>
       </c>
       <c r="K125" t="n">
-        <v>3285000</v>
+        <v>166400</v>
       </c>
       <c r="L125" t="n">
-        <v>3210</v>
+        <v>50.1</v>
       </c>
       <c r="M125" t="n">
-        <v>2385</v>
+        <v>47.7</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>0</v>
       </c>
       <c r="AJ125" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
@@ -22185,10 +22185,10 @@
         </is>
       </c>
       <c r="AL125" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AM125" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="AN125" t="n">
         <v>0</v>
@@ -22203,7 +22203,7 @@
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
@@ -22409,12 +22409,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5530.TWO</t>
+          <t>3081.TWO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>龍巖</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -22433,28 +22433,28 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>47.95</v>
+        <v>2490</v>
       </c>
       <c r="G127" t="n">
-        <v>48.17</v>
+        <v>2625</v>
       </c>
       <c r="H127" t="n">
-        <v>48.16</v>
+        <v>2789.5</v>
       </c>
       <c r="I127" t="n">
-        <v>48.48</v>
+        <v>2789.25</v>
       </c>
       <c r="J127" t="n">
-        <v>127000</v>
+        <v>2252000</v>
       </c>
       <c r="K127" t="n">
-        <v>166400</v>
+        <v>3285000</v>
       </c>
       <c r="L127" t="n">
-        <v>50.1</v>
+        <v>3210</v>
       </c>
       <c r="M127" t="n">
-        <v>47.7</v>
+        <v>2385</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>0</v>
       </c>
       <c r="AJ127" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
@@ -22533,10 +22533,10 @@
         </is>
       </c>
       <c r="AL127" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM127" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="AN127" t="n">
         <v>0</v>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
@@ -22583,12 +22583,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2612.TW</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>中航</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -22607,28 +22607,28 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>59.8</v>
+        <v>203.5</v>
       </c>
       <c r="G128" t="n">
-        <v>60.78</v>
+        <v>212.1</v>
       </c>
       <c r="H128" t="n">
-        <v>61.66</v>
+        <v>225.1</v>
       </c>
       <c r="I128" t="n">
-        <v>61.94</v>
+        <v>222.25</v>
       </c>
       <c r="J128" t="n">
-        <v>206950</v>
+        <v>1497000</v>
       </c>
       <c r="K128" t="n">
-        <v>350619</v>
+        <v>2580000</v>
       </c>
       <c r="L128" t="n">
-        <v>64.5</v>
+        <v>256</v>
       </c>
       <c r="M128" t="n">
-        <v>59.6</v>
+        <v>194</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -22636,28 +22636,28 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>-60000</v>
+        <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>43071</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>178913</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>812241</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>-60000</v>
+        <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>50062</v>
+        <v>0</v>
       </c>
       <c r="U128" t="n">
-        <v>172742</v>
+        <v>0</v>
       </c>
       <c r="V128" t="n">
-        <v>805227</v>
+        <v>0</v>
       </c>
       <c r="W128" t="n">
         <v>0</v>
@@ -22675,31 +22675,31 @@
         <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>-6991</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
-        <v>6171</v>
+        <v>0</v>
       </c>
       <c r="AD128" t="n">
-        <v>7014</v>
+        <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AF128" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AG128" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="AH128" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
       </c>
       <c r="AJ128" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
@@ -22707,10 +22707,10 @@
         </is>
       </c>
       <c r="AL128" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AM128" t="n">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="AN128" t="n">
         <v>0</v>
@@ -22725,7 +22725,7 @@
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
@@ -22740,17 +22740,17 @@
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -22931,12 +22931,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4967.TW</t>
+          <t>2612.TW</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>中航</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -22955,28 +22955,28 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>248.5</v>
+        <v>59.8</v>
       </c>
       <c r="G130" t="n">
-        <v>256.2</v>
+        <v>60.78</v>
       </c>
       <c r="H130" t="n">
-        <v>261.5</v>
+        <v>61.66</v>
       </c>
       <c r="I130" t="n">
-        <v>267.32</v>
+        <v>61.94</v>
       </c>
       <c r="J130" t="n">
-        <v>884108</v>
+        <v>206950</v>
       </c>
       <c r="K130" t="n">
-        <v>1402130</v>
+        <v>350619</v>
       </c>
       <c r="L130" t="n">
-        <v>278.5</v>
+        <v>64.5</v>
       </c>
       <c r="M130" t="n">
-        <v>248</v>
+        <v>59.6</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -22984,52 +22984,52 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>-145313</v>
+        <v>-60000</v>
       </c>
       <c r="P130" t="n">
-        <v>327412</v>
+        <v>43071</v>
       </c>
       <c r="Q130" t="n">
-        <v>175368</v>
+        <v>178913</v>
       </c>
       <c r="R130" t="n">
-        <v>-1986651</v>
+        <v>812241</v>
       </c>
       <c r="S130" t="n">
-        <v>-123138</v>
+        <v>-60000</v>
       </c>
       <c r="T130" t="n">
-        <v>324984</v>
+        <v>50062</v>
       </c>
       <c r="U130" t="n">
-        <v>182276</v>
+        <v>172742</v>
       </c>
       <c r="V130" t="n">
-        <v>-1881307</v>
+        <v>805227</v>
       </c>
       <c r="W130" t="n">
         <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>-22175</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>5428</v>
+        <v>-6991</v>
       </c>
       <c r="AC130" t="n">
-        <v>-3908</v>
+        <v>6171</v>
       </c>
       <c r="AD130" t="n">
-        <v>-98344</v>
+        <v>7014</v>
       </c>
       <c r="AE130" t="n">
         <v>-14</v>
@@ -23047,7 +23047,7 @@
         <v>0</v>
       </c>
       <c r="AJ130" t="n">
-        <v>-28</v>
+        <v>-2</v>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
@@ -23055,16 +23055,16 @@
         </is>
       </c>
       <c r="AL130" t="n">
-        <v>14</v>
+        <v>-12</v>
       </c>
       <c r="AM130" t="n">
-        <v>50</v>
+        <v>-600</v>
       </c>
       <c r="AN130" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO130" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
@@ -23093,24 +23093,24 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>4967.TW</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -23129,28 +23129,28 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1395</v>
+        <v>248.5</v>
       </c>
       <c r="G131" t="n">
-        <v>1420</v>
+        <v>256.2</v>
       </c>
       <c r="H131" t="n">
-        <v>1469</v>
+        <v>261.5</v>
       </c>
       <c r="I131" t="n">
-        <v>1516.75</v>
+        <v>267.32</v>
       </c>
       <c r="J131" t="n">
-        <v>3453000</v>
+        <v>884108</v>
       </c>
       <c r="K131" t="n">
-        <v>2589800</v>
+        <v>1402130</v>
       </c>
       <c r="L131" t="n">
-        <v>1750</v>
+        <v>278.5</v>
       </c>
       <c r="M131" t="n">
-        <v>1320</v>
+        <v>248</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -23158,52 +23158,52 @@
         </is>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>-145313</v>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>327412</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>175368</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>-1986651</v>
       </c>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>-123138</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>324984</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>182276</v>
       </c>
       <c r="V131" t="n">
-        <v>0</v>
+        <v>-1881307</v>
       </c>
       <c r="W131" t="n">
         <v>0</v>
       </c>
       <c r="X131" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>-22175</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>5428</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>-3908</v>
       </c>
       <c r="AD131" t="n">
-        <v>0</v>
+        <v>-98344</v>
       </c>
       <c r="AE131" t="n">
         <v>-14</v>
@@ -23212,16 +23212,16 @@
         <v>-14</v>
       </c>
       <c r="AG131" t="n">
-        <v>-35</v>
+        <v>-55</v>
       </c>
       <c r="AH131" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI131" t="n">
         <v>0</v>
       </c>
       <c r="AJ131" t="n">
-        <v>-18</v>
+        <v>-28</v>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
@@ -23229,16 +23229,16 @@
         </is>
       </c>
       <c r="AL131" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AM131" t="n">
-        <v>22.22</v>
+        <v>50</v>
       </c>
       <c r="AN131" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AO131" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
@@ -23262,29 +23262,29 @@
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8039.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -23303,28 +23303,28 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>296</v>
+        <v>1395</v>
       </c>
       <c r="G132" t="n">
-        <v>298.6</v>
+        <v>1420</v>
       </c>
       <c r="H132" t="n">
-        <v>297</v>
+        <v>1469</v>
       </c>
       <c r="I132" t="n">
-        <v>287.18</v>
+        <v>1516.75</v>
       </c>
       <c r="J132" t="n">
-        <v>62451990</v>
+        <v>3453000</v>
       </c>
       <c r="K132" t="n">
-        <v>56580279</v>
+        <v>2589800</v>
       </c>
       <c r="L132" t="n">
-        <v>331.5</v>
+        <v>1750</v>
       </c>
       <c r="M132" t="n">
-        <v>253</v>
+        <v>1320</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
@@ -23332,70 +23332,70 @@
         </is>
       </c>
       <c r="O132" t="n">
-        <v>-2836415</v>
+        <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>-585025</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>-2318301</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>-2902383</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>-2428657</v>
+        <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>-476953</v>
+        <v>0</v>
       </c>
       <c r="U132" t="n">
-        <v>-1770600</v>
+        <v>0</v>
       </c>
       <c r="V132" t="n">
-        <v>-342152</v>
+        <v>0</v>
       </c>
       <c r="W132" t="n">
-        <v>5905</v>
+        <v>0</v>
       </c>
       <c r="X132" t="n">
-        <v>98905</v>
+        <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>122905</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>173905</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>-413663</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>-206977</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
-        <v>-670606</v>
+        <v>0</v>
       </c>
       <c r="AD132" t="n">
-        <v>-2734136</v>
+        <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AF132" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AG132" t="n">
-        <v>15</v>
+        <v>-35</v>
       </c>
       <c r="AH132" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AI132" t="n">
         <v>0</v>
       </c>
       <c r="AJ132" t="n">
-        <v>46</v>
+        <v>-18</v>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
@@ -23403,16 +23403,16 @@
         </is>
       </c>
       <c r="AL132" t="n">
-        <v>-62</v>
+        <v>4</v>
       </c>
       <c r="AM132" t="n">
-        <v>-134.78</v>
+        <v>22.22</v>
       </c>
       <c r="AN132" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AO132" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
@@ -23436,29 +23436,29 @@
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>8039.TW</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -23477,28 +23477,28 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>469.5</v>
+        <v>296</v>
       </c>
       <c r="G133" t="n">
-        <v>477.8</v>
+        <v>298.6</v>
       </c>
       <c r="H133" t="n">
-        <v>503.9</v>
+        <v>297</v>
       </c>
       <c r="I133" t="n">
-        <v>505.82</v>
+        <v>287.18</v>
       </c>
       <c r="J133" t="n">
-        <v>17008000</v>
+        <v>62451990</v>
       </c>
       <c r="K133" t="n">
-        <v>12048000</v>
+        <v>56580279</v>
       </c>
       <c r="L133" t="n">
-        <v>578</v>
+        <v>331.5</v>
       </c>
       <c r="M133" t="n">
-        <v>447.5</v>
+        <v>253</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -23506,70 +23506,70 @@
         </is>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>-2836415</v>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>-585025</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>-2318301</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>-2902383</v>
       </c>
       <c r="S133" t="n">
-        <v>0</v>
+        <v>-2428657</v>
       </c>
       <c r="T133" t="n">
-        <v>0</v>
+        <v>-476953</v>
       </c>
       <c r="U133" t="n">
-        <v>0</v>
+        <v>-1770600</v>
       </c>
       <c r="V133" t="n">
-        <v>0</v>
+        <v>-342152</v>
       </c>
       <c r="W133" t="n">
-        <v>0</v>
+        <v>5905</v>
       </c>
       <c r="X133" t="n">
-        <v>0</v>
+        <v>98905</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>122905</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>173905</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>-413663</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>-206977</v>
       </c>
       <c r="AC133" t="n">
-        <v>0</v>
+        <v>-670606</v>
       </c>
       <c r="AD133" t="n">
-        <v>0</v>
+        <v>-2734136</v>
       </c>
       <c r="AE133" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="AF133" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="AG133" t="n">
-        <v>-45</v>
+        <v>15</v>
       </c>
       <c r="AH133" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AI133" t="n">
         <v>0</v>
       </c>
       <c r="AJ133" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
@@ -23577,16 +23577,16 @@
         </is>
       </c>
       <c r="AL133" t="n">
-        <v>-34</v>
+        <v>-62</v>
       </c>
       <c r="AM133" t="n">
-        <v>-212.5</v>
+        <v>-134.78</v>
       </c>
       <c r="AN133" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO133" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
@@ -23610,17 +23610,17 @@
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -23801,12 +23801,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -23825,28 +23825,28 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>32.1</v>
+        <v>469.5</v>
       </c>
       <c r="G135" t="n">
-        <v>32.31</v>
+        <v>477.8</v>
       </c>
       <c r="H135" t="n">
-        <v>31.62</v>
+        <v>503.9</v>
       </c>
       <c r="I135" t="n">
-        <v>31.26</v>
+        <v>505.82</v>
       </c>
       <c r="J135" t="n">
-        <v>18761682</v>
+        <v>17008000</v>
       </c>
       <c r="K135" t="n">
-        <v>35523503</v>
+        <v>12048000</v>
       </c>
       <c r="L135" t="n">
-        <v>33.7</v>
+        <v>578</v>
       </c>
       <c r="M135" t="n">
-        <v>30.3</v>
+        <v>447.5</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
@@ -23854,70 +23854,70 @@
         </is>
       </c>
       <c r="O135" t="n">
-        <v>-188214</v>
+        <v>0</v>
       </c>
       <c r="P135" t="n">
-        <v>-12292955</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>-5881432</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>-10268619</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
-        <v>-473231</v>
+        <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>-13190536</v>
+        <v>0</v>
       </c>
       <c r="U135" t="n">
-        <v>-6974211</v>
+        <v>0</v>
       </c>
       <c r="V135" t="n">
-        <v>-11134492</v>
+        <v>0</v>
       </c>
       <c r="W135" t="n">
-        <v>-280</v>
+        <v>0</v>
       </c>
       <c r="X135" t="n">
-        <v>26720</v>
+        <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>76720</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>271720</v>
+        <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>285297</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>870861</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
-        <v>1016059</v>
+        <v>0</v>
       </c>
       <c r="AD135" t="n">
-        <v>594153</v>
+        <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="AF135" t="n">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="AG135" t="n">
-        <v>5</v>
+        <v>-45</v>
       </c>
       <c r="AH135" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
       </c>
       <c r="AJ135" t="n">
-        <v>-16</v>
+        <v>16</v>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
@@ -23925,16 +23925,16 @@
         </is>
       </c>
       <c r="AL135" t="n">
-        <v>-4</v>
+        <v>-34</v>
       </c>
       <c r="AM135" t="n">
-        <v>-25</v>
+        <v>-212.5</v>
       </c>
       <c r="AN135" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO135" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
@@ -23958,17 +23958,17 @@
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -24028,16 +24028,16 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>-4159142</v>
+        <v>-4230142</v>
       </c>
       <c r="P136" t="n">
-        <v>-27155144</v>
+        <v>-27226144</v>
       </c>
       <c r="Q136" t="n">
-        <v>-40905824</v>
+        <v>-40976824</v>
       </c>
       <c r="R136" t="n">
-        <v>-26910933</v>
+        <v>-26981933</v>
       </c>
       <c r="S136" t="n">
         <v>-5124576</v>
@@ -24052,16 +24052,16 @@
         <v>-52925697</v>
       </c>
       <c r="W136" t="n">
-        <v>-1590704</v>
+        <v>-1661704</v>
       </c>
       <c r="X136" t="n">
-        <v>1381083</v>
+        <v>1310083</v>
       </c>
       <c r="Y136" t="n">
-        <v>11071589</v>
+        <v>11000589</v>
       </c>
       <c r="Z136" t="n">
-        <v>17550605</v>
+        <v>17479605</v>
       </c>
       <c r="AA136" t="n">
         <v>2556138</v>
@@ -24149,17 +24149,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0056.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -24173,28 +24173,28 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>57.45</v>
+        <v>32.1</v>
       </c>
       <c r="G137" t="n">
-        <v>58.41</v>
+        <v>32.31</v>
       </c>
       <c r="H137" t="n">
-        <v>58.4</v>
+        <v>31.62</v>
       </c>
       <c r="I137" t="n">
-        <v>57.67</v>
+        <v>31.26</v>
       </c>
       <c r="J137" t="n">
-        <v>103958121</v>
+        <v>18761682</v>
       </c>
       <c r="K137" t="n">
-        <v>93849690</v>
+        <v>35523503</v>
       </c>
       <c r="L137" t="n">
-        <v>59.7</v>
+        <v>33.7</v>
       </c>
       <c r="M137" t="n">
-        <v>56</v>
+        <v>30.3</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
@@ -24202,52 +24202,52 @@
         </is>
       </c>
       <c r="O137" t="n">
-        <v>-87876972</v>
+        <v>-188214</v>
       </c>
       <c r="P137" t="n">
-        <v>-208851747</v>
+        <v>-12292955</v>
       </c>
       <c r="Q137" t="n">
-        <v>-358574780</v>
+        <v>-5881432</v>
       </c>
       <c r="R137" t="n">
-        <v>-484202504</v>
+        <v>-10268619</v>
       </c>
       <c r="S137" t="n">
-        <v>-12009743</v>
+        <v>-473231</v>
       </c>
       <c r="T137" t="n">
-        <v>-25393600</v>
+        <v>-13190536</v>
       </c>
       <c r="U137" t="n">
-        <v>-41999624</v>
+        <v>-6974211</v>
       </c>
       <c r="V137" t="n">
-        <v>-62946897</v>
+        <v>-11134492</v>
       </c>
       <c r="W137" t="n">
-        <v>173000</v>
+        <v>-280</v>
       </c>
       <c r="X137" t="n">
-        <v>4708000</v>
+        <v>26720</v>
       </c>
       <c r="Y137" t="n">
-        <v>11183000</v>
+        <v>76720</v>
       </c>
       <c r="Z137" t="n">
-        <v>9285000</v>
+        <v>271720</v>
       </c>
       <c r="AA137" t="n">
-        <v>-76040229</v>
+        <v>285297</v>
       </c>
       <c r="AB137" t="n">
-        <v>-188166147</v>
+        <v>870861</v>
       </c>
       <c r="AC137" t="n">
-        <v>-327758156</v>
+        <v>1016059</v>
       </c>
       <c r="AD137" t="n">
-        <v>-430540607</v>
+        <v>594153</v>
       </c>
       <c r="AE137" t="n">
         <v>-20</v>
@@ -24265,7 +24265,7 @@
         <v>0</v>
       </c>
       <c r="AJ137" t="n">
-        <v>-20</v>
+        <v>-16</v>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
@@ -24273,16 +24273,16 @@
         </is>
       </c>
       <c r="AL137" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM137" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AN137" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AO137" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
@@ -24316,7 +24316,7 @@
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -24497,17 +24497,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>0056.TW</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -24521,28 +24521,28 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>220</v>
+        <v>57.45</v>
       </c>
       <c r="G139" t="n">
-        <v>231.6</v>
+        <v>58.41</v>
       </c>
       <c r="H139" t="n">
-        <v>243.65</v>
+        <v>58.4</v>
       </c>
       <c r="I139" t="n">
-        <v>248</v>
+        <v>57.67</v>
       </c>
       <c r="J139" t="n">
-        <v>1188000</v>
+        <v>103958121</v>
       </c>
       <c r="K139" t="n">
-        <v>1202600</v>
+        <v>93849690</v>
       </c>
       <c r="L139" t="n">
-        <v>270</v>
+        <v>59.7</v>
       </c>
       <c r="M139" t="n">
-        <v>219</v>
+        <v>56</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
@@ -24550,70 +24550,70 @@
         </is>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>-87876972</v>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>-208851747</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>-358574780</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>-484202504</v>
       </c>
       <c r="S139" t="n">
-        <v>0</v>
+        <v>-12009743</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>-25393600</v>
       </c>
       <c r="U139" t="n">
-        <v>0</v>
+        <v>-41999624</v>
       </c>
       <c r="V139" t="n">
-        <v>0</v>
+        <v>-62946897</v>
       </c>
       <c r="W139" t="n">
-        <v>0</v>
+        <v>173000</v>
       </c>
       <c r="X139" t="n">
-        <v>0</v>
+        <v>4708000</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>11183000</v>
       </c>
       <c r="Z139" t="n">
-        <v>0</v>
+        <v>9285000</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>-76040229</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>-188166147</v>
       </c>
       <c r="AC139" t="n">
-        <v>0</v>
+        <v>-327758156</v>
       </c>
       <c r="AD139" t="n">
-        <v>0</v>
+        <v>-430540607</v>
       </c>
       <c r="AE139" t="n">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="AF139" t="n">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="AG139" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH139" t="n">
         <v>-55</v>
       </c>
-      <c r="AH139" t="n">
-        <v>0</v>
-      </c>
       <c r="AI139" t="n">
         <v>0</v>
       </c>
       <c r="AJ139" t="n">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
@@ -24627,10 +24627,10 @@
         <v>0</v>
       </c>
       <c r="AN139" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO139" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AR139" t="inlineStr">
@@ -24654,17 +24654,17 @@
       </c>
       <c r="AT139" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -25541,12 +25541,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6275.TWO</t>
+          <t>5439.TWO</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -25565,28 +25565,28 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>44.85</v>
+        <v>220</v>
       </c>
       <c r="G145" t="n">
-        <v>45.36</v>
+        <v>231.6</v>
       </c>
       <c r="H145" t="n">
-        <v>45.95</v>
+        <v>243.65</v>
       </c>
       <c r="I145" t="n">
-        <v>46.21</v>
+        <v>248</v>
       </c>
       <c r="J145" t="n">
-        <v>48000</v>
+        <v>1188000</v>
       </c>
       <c r="K145" t="n">
-        <v>83000</v>
+        <v>1202600</v>
       </c>
       <c r="L145" t="n">
-        <v>48.05</v>
+        <v>270</v>
       </c>
       <c r="M145" t="n">
-        <v>44.55</v>
+        <v>219</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>0</v>
       </c>
       <c r="AJ145" t="n">
-        <v>-8</v>
+        <v>-22</v>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
@@ -25665,10 +25665,10 @@
         </is>
       </c>
       <c r="AL145" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="AM145" t="n">
-        <v>-175</v>
+        <v>0</v>
       </c>
       <c r="AN145" t="n">
         <v>0</v>
@@ -25683,7 +25683,7 @@
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
@@ -25889,12 +25889,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4979.TWO</t>
+          <t>8299.TWO</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -25913,28 +25913,28 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>470</v>
+        <v>1845</v>
       </c>
       <c r="G147" t="n">
-        <v>520</v>
+        <v>1875</v>
       </c>
       <c r="H147" t="n">
-        <v>542.9</v>
+        <v>1960.5</v>
       </c>
       <c r="I147" t="n">
-        <v>564.6</v>
+        <v>2049.5</v>
       </c>
       <c r="J147" t="n">
-        <v>1489000</v>
+        <v>1546000</v>
       </c>
       <c r="K147" t="n">
-        <v>6623600</v>
+        <v>3007800</v>
       </c>
       <c r="L147" t="n">
-        <v>650</v>
+        <v>2350</v>
       </c>
       <c r="M147" t="n">
-        <v>466</v>
+        <v>1785</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
@@ -26063,12 +26063,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>8299.TWO</t>
+          <t>4979.TWO</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -26087,28 +26087,28 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1845</v>
+        <v>470</v>
       </c>
       <c r="G148" t="n">
-        <v>1875</v>
+        <v>520</v>
       </c>
       <c r="H148" t="n">
-        <v>1960.5</v>
+        <v>542.9</v>
       </c>
       <c r="I148" t="n">
-        <v>2049.5</v>
+        <v>564.6</v>
       </c>
       <c r="J148" t="n">
-        <v>1546000</v>
+        <v>1489000</v>
       </c>
       <c r="K148" t="n">
-        <v>3007800</v>
+        <v>6623600</v>
       </c>
       <c r="L148" t="n">
-        <v>2350</v>
+        <v>650</v>
       </c>
       <c r="M148" t="n">
-        <v>1785</v>
+        <v>466</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
@@ -26638,16 +26638,16 @@
         </is>
       </c>
       <c r="O151" t="n">
-        <v>154413</v>
+        <v>214413</v>
       </c>
       <c r="P151" t="n">
-        <v>562580</v>
+        <v>622580</v>
       </c>
       <c r="Q151" t="n">
-        <v>-3302152</v>
+        <v>-3242152</v>
       </c>
       <c r="R151" t="n">
-        <v>-4736885</v>
+        <v>-4676885</v>
       </c>
       <c r="S151" t="n">
         <v>309032</v>
@@ -26662,16 +26662,16 @@
         <v>5282053</v>
       </c>
       <c r="W151" t="n">
-        <v>-186619</v>
+        <v>-126619</v>
       </c>
       <c r="X151" t="n">
-        <v>-5702434</v>
+        <v>-5642434</v>
       </c>
       <c r="Y151" t="n">
-        <v>-9811618</v>
+        <v>-9751618</v>
       </c>
       <c r="Z151" t="n">
-        <v>-9933105</v>
+        <v>-9873105</v>
       </c>
       <c r="AA151" t="n">
         <v>32000</v>
@@ -26812,16 +26812,16 @@
         </is>
       </c>
       <c r="O152" t="n">
-        <v>-894902</v>
+        <v>-722902</v>
       </c>
       <c r="P152" t="n">
-        <v>-2184656</v>
+        <v>-2012656</v>
       </c>
       <c r="Q152" t="n">
-        <v>-2516655</v>
+        <v>-2344655</v>
       </c>
       <c r="R152" t="n">
-        <v>-231524</v>
+        <v>-59524</v>
       </c>
       <c r="S152" t="n">
         <v>-1205714</v>
@@ -26836,16 +26836,16 @@
         <v>-2940139</v>
       </c>
       <c r="W152" t="n">
-        <v>602837</v>
+        <v>774837</v>
       </c>
       <c r="X152" t="n">
-        <v>1538928</v>
+        <v>1710928</v>
       </c>
       <c r="Y152" t="n">
-        <v>2437183</v>
+        <v>2609183</v>
       </c>
       <c r="Z152" t="n">
-        <v>3315188</v>
+        <v>3487188</v>
       </c>
       <c r="AA152" t="n">
         <v>-292025</v>
@@ -28204,16 +28204,16 @@
         </is>
       </c>
       <c r="O160" t="n">
-        <v>-1969526</v>
+        <v>-1979526</v>
       </c>
       <c r="P160" t="n">
-        <v>-4927495</v>
+        <v>-4937495</v>
       </c>
       <c r="Q160" t="n">
-        <v>-10481709</v>
+        <v>-10491709</v>
       </c>
       <c r="R160" t="n">
-        <v>-9011385</v>
+        <v>-9021385</v>
       </c>
       <c r="S160" t="n">
         <v>-2530676</v>
@@ -28228,16 +28228,16 @@
         <v>-8941966</v>
       </c>
       <c r="W160" t="n">
-        <v>717433</v>
+        <v>707433</v>
       </c>
       <c r="X160" t="n">
-        <v>2506922</v>
+        <v>2496922</v>
       </c>
       <c r="Y160" t="n">
-        <v>4289683</v>
+        <v>4279683</v>
       </c>
       <c r="Z160" t="n">
-        <v>-417721</v>
+        <v>-427721</v>
       </c>
       <c r="AA160" t="n">
         <v>-156283</v>
@@ -29596,16 +29596,16 @@
         </is>
       </c>
       <c r="O168" t="n">
-        <v>-8355771</v>
+        <v>-8363771</v>
       </c>
       <c r="P168" t="n">
-        <v>-35331573</v>
+        <v>-35339573</v>
       </c>
       <c r="Q168" t="n">
-        <v>-64208304</v>
+        <v>-64216304</v>
       </c>
       <c r="R168" t="n">
-        <v>-104587211</v>
+        <v>-104595211</v>
       </c>
       <c r="S168" t="n">
         <v>-9364622</v>
@@ -29620,16 +29620,16 @@
         <v>-132311700</v>
       </c>
       <c r="W168" t="n">
-        <v>1037673</v>
+        <v>1029673</v>
       </c>
       <c r="X168" t="n">
-        <v>5632487</v>
+        <v>5624487</v>
       </c>
       <c r="Y168" t="n">
-        <v>9667975</v>
+        <v>9659975</v>
       </c>
       <c r="Z168" t="n">
-        <v>14275752</v>
+        <v>14267752</v>
       </c>
       <c r="AA168" t="n">
         <v>-28822</v>
@@ -29944,16 +29944,16 @@
         </is>
       </c>
       <c r="O170" t="n">
-        <v>11700</v>
+        <v>21700</v>
       </c>
       <c r="P170" t="n">
-        <v>136110</v>
+        <v>146110</v>
       </c>
       <c r="Q170" t="n">
-        <v>-511211</v>
+        <v>-501211</v>
       </c>
       <c r="R170" t="n">
-        <v>103314</v>
+        <v>113314</v>
       </c>
       <c r="S170" t="n">
         <v>2742</v>
@@ -29968,16 +29968,16 @@
         <v>-321630</v>
       </c>
       <c r="W170" t="n">
-        <v>10029</v>
+        <v>20029</v>
       </c>
       <c r="X170" t="n">
-        <v>164950</v>
+        <v>174950</v>
       </c>
       <c r="Y170" t="n">
-        <v>212740</v>
+        <v>222740</v>
       </c>
       <c r="Z170" t="n">
-        <v>398022</v>
+        <v>408022</v>
       </c>
       <c r="AA170" t="n">
         <v>-1071</v>
@@ -30986,16 +30986,16 @@
         </is>
       </c>
       <c r="O176" t="n">
-        <v>511517</v>
+        <v>466517</v>
       </c>
       <c r="P176" t="n">
-        <v>3672607</v>
+        <v>3627607</v>
       </c>
       <c r="Q176" t="n">
-        <v>-6706615</v>
+        <v>-6751615</v>
       </c>
       <c r="R176" t="n">
-        <v>-60622651</v>
+        <v>-60667651</v>
       </c>
       <c r="S176" t="n">
         <v>423162</v>
@@ -31010,16 +31010,16 @@
         <v>-33145550</v>
       </c>
       <c r="W176" t="n">
-        <v>-478449</v>
+        <v>-523449</v>
       </c>
       <c r="X176" t="n">
-        <v>-1954830</v>
+        <v>-1999830</v>
       </c>
       <c r="Y176" t="n">
-        <v>-3307391</v>
+        <v>-3352391</v>
       </c>
       <c r="Z176" t="n">
-        <v>-24559771</v>
+        <v>-24604771</v>
       </c>
       <c r="AA176" t="n">
         <v>566804</v>
@@ -33944,16 +33944,16 @@
         </is>
       </c>
       <c r="O193" t="n">
-        <v>-3105666</v>
+        <v>-3274666</v>
       </c>
       <c r="P193" t="n">
-        <v>-6068306</v>
+        <v>-6237306</v>
       </c>
       <c r="Q193" t="n">
-        <v>-17855498</v>
+        <v>-18024498</v>
       </c>
       <c r="R193" t="n">
-        <v>-29645267</v>
+        <v>-29814267</v>
       </c>
       <c r="S193" t="n">
         <v>-3500561</v>
@@ -33968,16 +33968,16 @@
         <v>-28819414</v>
       </c>
       <c r="W193" t="n">
-        <v>772710</v>
+        <v>603710</v>
       </c>
       <c r="X193" t="n">
-        <v>1496816</v>
+        <v>1327816</v>
       </c>
       <c r="Y193" t="n">
-        <v>1903332</v>
+        <v>1734332</v>
       </c>
       <c r="Z193" t="n">
-        <v>804950</v>
+        <v>635950</v>
       </c>
       <c r="AA193" t="n">
         <v>-377815</v>
@@ -34118,16 +34118,16 @@
         </is>
       </c>
       <c r="O194" t="n">
-        <v>-1366864</v>
+        <v>-1367864</v>
       </c>
       <c r="P194" t="n">
-        <v>-3951654</v>
+        <v>-3952654</v>
       </c>
       <c r="Q194" t="n">
-        <v>-13335221</v>
+        <v>-13336221</v>
       </c>
       <c r="R194" t="n">
-        <v>-29137084</v>
+        <v>-29138084</v>
       </c>
       <c r="S194" t="n">
         <v>-1565622</v>
@@ -34142,16 +34142,16 @@
         <v>-29557421</v>
       </c>
       <c r="W194" t="n">
-        <v>296568</v>
+        <v>295568</v>
       </c>
       <c r="X194" t="n">
-        <v>933364</v>
+        <v>932364</v>
       </c>
       <c r="Y194" t="n">
-        <v>1617857</v>
+        <v>1616857</v>
       </c>
       <c r="Z194" t="n">
-        <v>556390</v>
+        <v>555390</v>
       </c>
       <c r="AA194" t="n">
         <v>-97810</v>
@@ -34988,16 +34988,16 @@
         </is>
       </c>
       <c r="O199" t="n">
-        <v>-4340168</v>
+        <v>-4365168</v>
       </c>
       <c r="P199" t="n">
-        <v>-17382029</v>
+        <v>-17407029</v>
       </c>
       <c r="Q199" t="n">
-        <v>-65962436</v>
+        <v>-65987436</v>
       </c>
       <c r="R199" t="n">
-        <v>-101204999</v>
+        <v>-101229999</v>
       </c>
       <c r="S199" t="n">
         <v>-3935043</v>
@@ -35012,16 +35012,16 @@
         <v>-84535209</v>
       </c>
       <c r="W199" t="n">
-        <v>-421457</v>
+        <v>-446457</v>
       </c>
       <c r="X199" t="n">
-        <v>-1251258</v>
+        <v>-1276258</v>
       </c>
       <c r="Y199" t="n">
-        <v>-11295492</v>
+        <v>-11320492</v>
       </c>
       <c r="Z199" t="n">
-        <v>-14858704</v>
+        <v>-14883704</v>
       </c>
       <c r="AA199" t="n">
         <v>16332</v>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -13711,12 +13711,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6275.TWO</t>
+          <t>2492.TW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -13735,28 +13735,28 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>47.15</v>
+        <v>369</v>
       </c>
       <c r="G77" t="n">
-        <v>46.15</v>
+        <v>391.9</v>
       </c>
       <c r="H77" t="n">
-        <v>45.66</v>
+        <v>400.7</v>
       </c>
       <c r="I77" t="n">
-        <v>45.75</v>
+        <v>360.7</v>
       </c>
       <c r="J77" t="n">
-        <v>220000</v>
+        <v>35893432</v>
       </c>
       <c r="K77" t="n">
-        <v>162200</v>
+        <v>14835505</v>
       </c>
       <c r="L77" t="n">
-        <v>48.9</v>
+        <v>431.5</v>
       </c>
       <c r="M77" t="n">
-        <v>44.55</v>
+        <v>298.5</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -13764,52 +13764,52 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>-1796309</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>-4386965</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>1513583</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>8884028</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>-4794289</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>-6414206</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>-897237</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>5950827</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>3729038</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>3035038</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>3033038</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>5516038</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>-731058</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>-1007797</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>-622218</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>-2582837</v>
       </c>
       <c r="AE77" t="n">
         <v>12</v>
@@ -13818,42 +13818,42 @@
         <v>12</v>
       </c>
       <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
         <v>30</v>
       </c>
-      <c r="AH77" t="n">
-        <v>0</v>
-      </c>
       <c r="AI77" t="n">
         <v>0</v>
       </c>
       <c r="AJ77" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AL77" t="n">
-        <v>-8</v>
+        <v>8</v>
       </c>
       <c r="AM77" t="n">
-        <v>-40</v>
+        <v>200</v>
       </c>
       <c r="AN77" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="AO77" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能偏強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
@@ -13868,17 +13868,17 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、爆量</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、爆量、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14059,12 +14059,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2492.TW</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -14083,28 +14083,28 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>369</v>
+        <v>25.05</v>
       </c>
       <c r="G79" t="n">
-        <v>391.9</v>
+        <v>25.82</v>
       </c>
       <c r="H79" t="n">
-        <v>400.7</v>
+        <v>25.85</v>
       </c>
       <c r="I79" t="n">
-        <v>360.7</v>
+        <v>25.19</v>
       </c>
       <c r="J79" t="n">
-        <v>35893432</v>
+        <v>5861982</v>
       </c>
       <c r="K79" t="n">
-        <v>14835505</v>
+        <v>17962130</v>
       </c>
       <c r="L79" t="n">
-        <v>431.5</v>
+        <v>27.4</v>
       </c>
       <c r="M79" t="n">
-        <v>298.5</v>
+        <v>23.85</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -14112,52 +14112,52 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>-1796309</v>
+        <v>-1089916</v>
       </c>
       <c r="P79" t="n">
-        <v>-4386965</v>
+        <v>2206540</v>
       </c>
       <c r="Q79" t="n">
-        <v>1513583</v>
+        <v>4956817</v>
       </c>
       <c r="R79" t="n">
-        <v>8884028</v>
+        <v>20195646</v>
       </c>
       <c r="S79" t="n">
-        <v>-4794289</v>
+        <v>-700587</v>
       </c>
       <c r="T79" t="n">
-        <v>-6414206</v>
+        <v>2755407</v>
       </c>
       <c r="U79" t="n">
-        <v>-897237</v>
+        <v>5653592</v>
       </c>
       <c r="V79" t="n">
-        <v>5950827</v>
+        <v>21294772</v>
       </c>
       <c r="W79" t="n">
-        <v>3729038</v>
+        <v>-118</v>
       </c>
       <c r="X79" t="n">
-        <v>3035038</v>
+        <v>-5118</v>
       </c>
       <c r="Y79" t="n">
-        <v>3033038</v>
+        <v>57882</v>
       </c>
       <c r="Z79" t="n">
-        <v>5516038</v>
+        <v>133882</v>
       </c>
       <c r="AA79" t="n">
-        <v>-731058</v>
+        <v>-389211</v>
       </c>
       <c r="AB79" t="n">
-        <v>-1007797</v>
+        <v>-543749</v>
       </c>
       <c r="AC79" t="n">
-        <v>-622218</v>
+        <v>-754657</v>
       </c>
       <c r="AD79" t="n">
-        <v>-2582837</v>
+        <v>-1233008</v>
       </c>
       <c r="AE79" t="n">
         <v>12</v>
@@ -14166,16 +14166,16 @@
         <v>12</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AH79" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
       </c>
       <c r="AJ79" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
@@ -14183,16 +14183,16 @@
         </is>
       </c>
       <c r="AL79" t="n">
-        <v>8</v>
+        <v>-10</v>
       </c>
       <c r="AM79" t="n">
-        <v>200</v>
+        <v>-45.45</v>
       </c>
       <c r="AN79" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AO79" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、量能偏強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
@@ -14216,17 +14216,17 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>跌破5日線、爆量</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、爆量、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14407,12 +14407,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -14431,28 +14431,28 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>25.05</v>
+        <v>42.35</v>
       </c>
       <c r="G81" t="n">
-        <v>25.82</v>
+        <v>43.12</v>
       </c>
       <c r="H81" t="n">
-        <v>25.85</v>
+        <v>42.55</v>
       </c>
       <c r="I81" t="n">
-        <v>25.19</v>
+        <v>42.37</v>
       </c>
       <c r="J81" t="n">
-        <v>5861982</v>
+        <v>12934352</v>
       </c>
       <c r="K81" t="n">
-        <v>17962130</v>
+        <v>17709579</v>
       </c>
       <c r="L81" t="n">
-        <v>27.4</v>
+        <v>44.05</v>
       </c>
       <c r="M81" t="n">
-        <v>23.85</v>
+        <v>41.2</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -14460,64 +14460,64 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>-1089916</v>
+        <v>-565183</v>
       </c>
       <c r="P81" t="n">
-        <v>2206540</v>
+        <v>8647559</v>
       </c>
       <c r="Q81" t="n">
-        <v>4956817</v>
+        <v>31746265</v>
       </c>
       <c r="R81" t="n">
-        <v>20195646</v>
+        <v>55302078</v>
       </c>
       <c r="S81" t="n">
-        <v>-700587</v>
+        <v>2468319</v>
       </c>
       <c r="T81" t="n">
-        <v>2755407</v>
+        <v>15169899</v>
       </c>
       <c r="U81" t="n">
-        <v>5653592</v>
+        <v>36706974</v>
       </c>
       <c r="V81" t="n">
-        <v>21294772</v>
+        <v>59089589</v>
       </c>
       <c r="W81" t="n">
-        <v>-118</v>
+        <v>-4194039</v>
       </c>
       <c r="X81" t="n">
-        <v>-5118</v>
+        <v>-9465039</v>
       </c>
       <c r="Y81" t="n">
-        <v>57882</v>
+        <v>-10084039</v>
       </c>
       <c r="Z81" t="n">
-        <v>133882</v>
+        <v>-10691621</v>
       </c>
       <c r="AA81" t="n">
-        <v>-389211</v>
+        <v>1160537</v>
       </c>
       <c r="AB81" t="n">
-        <v>-543749</v>
+        <v>2942699</v>
       </c>
       <c r="AC81" t="n">
-        <v>-754657</v>
+        <v>5123330</v>
       </c>
       <c r="AD81" t="n">
-        <v>-1233008</v>
+        <v>6904110</v>
       </c>
       <c r="AE81" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF81" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG81" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
       <c r="AH81" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -14531,10 +14531,10 @@
         </is>
       </c>
       <c r="AL81" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="AM81" t="n">
-        <v>-45.45</v>
+        <v>-54.55</v>
       </c>
       <c r="AN81" t="n">
         <v>0</v>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
@@ -14564,17 +14564,17 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14755,12 +14755,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>3702.TW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -14779,28 +14779,28 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>42.35</v>
+        <v>113.5</v>
       </c>
       <c r="G83" t="n">
-        <v>43.12</v>
+        <v>115.7</v>
       </c>
       <c r="H83" t="n">
-        <v>42.55</v>
+        <v>116.85</v>
       </c>
       <c r="I83" t="n">
-        <v>42.37</v>
+        <v>116.38</v>
       </c>
       <c r="J83" t="n">
-        <v>12934352</v>
+        <v>8056263</v>
       </c>
       <c r="K83" t="n">
-        <v>17709579</v>
+        <v>10530615</v>
       </c>
       <c r="L83" t="n">
-        <v>44.05</v>
+        <v>122</v>
       </c>
       <c r="M83" t="n">
-        <v>41.2</v>
+        <v>111</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -14808,52 +14808,52 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>-565183</v>
+        <v>798220</v>
       </c>
       <c r="P83" t="n">
-        <v>8647559</v>
+        <v>1412203</v>
       </c>
       <c r="Q83" t="n">
-        <v>31746265</v>
+        <v>8445322</v>
       </c>
       <c r="R83" t="n">
-        <v>55302078</v>
+        <v>20495769</v>
       </c>
       <c r="S83" t="n">
-        <v>2468319</v>
+        <v>-48782</v>
       </c>
       <c r="T83" t="n">
-        <v>15169899</v>
+        <v>-1343073</v>
       </c>
       <c r="U83" t="n">
-        <v>36706974</v>
+        <v>4757844</v>
       </c>
       <c r="V83" t="n">
-        <v>59089589</v>
+        <v>15326882</v>
       </c>
       <c r="W83" t="n">
-        <v>-4194039</v>
+        <v>245924</v>
       </c>
       <c r="X83" t="n">
-        <v>-9465039</v>
+        <v>1819964</v>
       </c>
       <c r="Y83" t="n">
-        <v>-10084039</v>
+        <v>2083249</v>
       </c>
       <c r="Z83" t="n">
-        <v>-10691621</v>
+        <v>2511843</v>
       </c>
       <c r="AA83" t="n">
-        <v>1160537</v>
+        <v>601078</v>
       </c>
       <c r="AB83" t="n">
-        <v>2942699</v>
+        <v>935312</v>
       </c>
       <c r="AC83" t="n">
-        <v>5123330</v>
+        <v>1604229</v>
       </c>
       <c r="AD83" t="n">
-        <v>6904110</v>
+        <v>2657044</v>
       </c>
       <c r="AE83" t="n">
         <v>10</v>
@@ -14862,16 +14862,16 @@
         <v>10</v>
       </c>
       <c r="AG83" t="n">
-        <v>-5</v>
+        <v>-55</v>
       </c>
       <c r="AH83" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
@@ -14879,10 +14879,10 @@
         </is>
       </c>
       <c r="AL83" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="AM83" t="n">
-        <v>-54.55</v>
+        <v>-16.67</v>
       </c>
       <c r="AN83" t="n">
         <v>0</v>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
@@ -14912,17 +14912,17 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、死亡交叉、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、死亡交叉、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15451,12 +15451,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3702.TW</t>
+          <t>2362.TW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>藍天</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -15475,28 +15475,28 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>113.5</v>
+        <v>47.75</v>
       </c>
       <c r="G87" t="n">
-        <v>115.7</v>
+        <v>48.27</v>
       </c>
       <c r="H87" t="n">
-        <v>116.85</v>
+        <v>47.58</v>
       </c>
       <c r="I87" t="n">
-        <v>116.38</v>
+        <v>47.43</v>
       </c>
       <c r="J87" t="n">
-        <v>8056263</v>
+        <v>604867</v>
       </c>
       <c r="K87" t="n">
-        <v>10530615</v>
+        <v>863095</v>
       </c>
       <c r="L87" t="n">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="M87" t="n">
-        <v>111</v>
+        <v>46.2</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -15504,52 +15504,52 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>798220</v>
+        <v>-156</v>
       </c>
       <c r="P87" t="n">
-        <v>1412203</v>
+        <v>99975</v>
       </c>
       <c r="Q87" t="n">
-        <v>8445322</v>
+        <v>1129215</v>
       </c>
       <c r="R87" t="n">
-        <v>20495769</v>
+        <v>1884131</v>
       </c>
       <c r="S87" t="n">
-        <v>-48782</v>
+        <v>15148</v>
       </c>
       <c r="T87" t="n">
-        <v>-1343073</v>
+        <v>127533</v>
       </c>
       <c r="U87" t="n">
-        <v>4757844</v>
+        <v>1159775</v>
       </c>
       <c r="V87" t="n">
-        <v>15326882</v>
+        <v>1914181</v>
       </c>
       <c r="W87" t="n">
-        <v>245924</v>
+        <v>-303</v>
       </c>
       <c r="X87" t="n">
-        <v>1819964</v>
+        <v>-303</v>
       </c>
       <c r="Y87" t="n">
-        <v>2083249</v>
+        <v>-303</v>
       </c>
       <c r="Z87" t="n">
-        <v>2511843</v>
+        <v>-303</v>
       </c>
       <c r="AA87" t="n">
-        <v>601078</v>
+        <v>-15001</v>
       </c>
       <c r="AB87" t="n">
-        <v>935312</v>
+        <v>-27255</v>
       </c>
       <c r="AC87" t="n">
-        <v>1604229</v>
+        <v>-30257</v>
       </c>
       <c r="AD87" t="n">
-        <v>2657044</v>
+        <v>-29747</v>
       </c>
       <c r="AE87" t="n">
         <v>10</v>
@@ -15558,16 +15558,16 @@
         <v>10</v>
       </c>
       <c r="AG87" t="n">
-        <v>-55</v>
+        <v>-5</v>
       </c>
       <c r="AH87" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
       </c>
       <c r="AJ87" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
@@ -15575,16 +15575,16 @@
         </is>
       </c>
       <c r="AL87" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AM87" t="n">
-        <v>-16.67</v>
+        <v>0</v>
       </c>
       <c r="AN87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -15608,17 +15608,17 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>跌破5日線、死亡交叉、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、死亡交叉、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15799,12 +15799,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2882.TW</t>
+          <t>2610.TW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -15823,28 +15823,28 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>110</v>
+        <v>20.4</v>
       </c>
       <c r="G89" t="n">
-        <v>113.6</v>
+        <v>20.64</v>
       </c>
       <c r="H89" t="n">
-        <v>113.05</v>
+        <v>20.47</v>
       </c>
       <c r="I89" t="n">
-        <v>112.2</v>
+        <v>20.38</v>
       </c>
       <c r="J89" t="n">
-        <v>24145665</v>
+        <v>15428590</v>
       </c>
       <c r="K89" t="n">
-        <v>23479461</v>
+        <v>22313588</v>
       </c>
       <c r="L89" t="n">
-        <v>118</v>
+        <v>21.2</v>
       </c>
       <c r="M89" t="n">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -15852,52 +15852,52 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>-7507408</v>
+        <v>-5385365</v>
       </c>
       <c r="P89" t="n">
-        <v>-1532218</v>
+        <v>18354331</v>
       </c>
       <c r="Q89" t="n">
-        <v>337060</v>
+        <v>35796426</v>
       </c>
       <c r="R89" t="n">
-        <v>20787884</v>
+        <v>54393946</v>
       </c>
       <c r="S89" t="n">
-        <v>-7371284</v>
+        <v>-2807597</v>
       </c>
       <c r="T89" t="n">
-        <v>-3164697</v>
+        <v>19511431</v>
       </c>
       <c r="U89" t="n">
-        <v>-3483300</v>
+        <v>37863180</v>
       </c>
       <c r="V89" t="n">
-        <v>10019702</v>
+        <v>53143731</v>
       </c>
       <c r="W89" t="n">
-        <v>-426439</v>
+        <v>-2382180</v>
       </c>
       <c r="X89" t="n">
-        <v>368261</v>
+        <v>-1007180</v>
       </c>
       <c r="Y89" t="n">
-        <v>240531</v>
+        <v>-1944180</v>
       </c>
       <c r="Z89" t="n">
-        <v>6202106</v>
+        <v>4268820</v>
       </c>
       <c r="AA89" t="n">
-        <v>290315</v>
+        <v>-195588</v>
       </c>
       <c r="AB89" t="n">
-        <v>1264218</v>
+        <v>-149920</v>
       </c>
       <c r="AC89" t="n">
-        <v>3579829</v>
+        <v>-122574</v>
       </c>
       <c r="AD89" t="n">
-        <v>4566076</v>
+        <v>-3018605</v>
       </c>
       <c r="AE89" t="n">
         <v>10</v>
@@ -15906,16 +15906,16 @@
         <v>10</v>
       </c>
       <c r="AG89" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AH89" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
       </c>
       <c r="AJ89" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
@@ -15923,10 +15923,10 @@
         </is>
       </c>
       <c r="AL89" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="AM89" t="n">
-        <v>-54.55</v>
+        <v>-44.44</v>
       </c>
       <c r="AN89" t="n">
         <v>0</v>
@@ -15956,29 +15956,29 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>5日法人買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2610.TW</t>
+          <t>1906.TW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>寶隆</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -15997,28 +15997,28 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>20.4</v>
+        <v>10.9</v>
       </c>
       <c r="G90" t="n">
-        <v>20.64</v>
+        <v>10.88</v>
       </c>
       <c r="H90" t="n">
-        <v>20.47</v>
+        <v>10.82</v>
       </c>
       <c r="I90" t="n">
-        <v>20.38</v>
+        <v>10.8</v>
       </c>
       <c r="J90" t="n">
-        <v>15428590</v>
+        <v>21337</v>
       </c>
       <c r="K90" t="n">
-        <v>22313588</v>
+        <v>47932</v>
       </c>
       <c r="L90" t="n">
-        <v>21.2</v>
+        <v>11.05</v>
       </c>
       <c r="M90" t="n">
-        <v>20</v>
+        <v>10.6</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -16026,52 +16026,52 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>-5385365</v>
+        <v>-3698</v>
       </c>
       <c r="P90" t="n">
-        <v>18354331</v>
+        <v>-5838</v>
       </c>
       <c r="Q90" t="n">
-        <v>35796426</v>
+        <v>-21635</v>
       </c>
       <c r="R90" t="n">
-        <v>54393946</v>
+        <v>-19449</v>
       </c>
       <c r="S90" t="n">
-        <v>-2807597</v>
+        <v>-3698</v>
       </c>
       <c r="T90" t="n">
-        <v>19511431</v>
+        <v>-5838</v>
       </c>
       <c r="U90" t="n">
-        <v>37863180</v>
+        <v>-17635</v>
       </c>
       <c r="V90" t="n">
-        <v>53143731</v>
+        <v>-17449</v>
       </c>
       <c r="W90" t="n">
-        <v>-2382180</v>
+        <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>-1007180</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>-1944180</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>4268820</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>-195588</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>-149920</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>-122574</v>
+        <v>-4000</v>
       </c>
       <c r="AD90" t="n">
-        <v>-3018605</v>
+        <v>-2000</v>
       </c>
       <c r="AE90" t="n">
         <v>10</v>
@@ -16080,16 +16080,16 @@
         <v>10</v>
       </c>
       <c r="AG90" t="n">
-        <v>-5</v>
+        <v>50</v>
       </c>
       <c r="AH90" t="n">
-        <v>30</v>
+        <v>-25</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
       </c>
       <c r="AJ90" t="n">
-        <v>18</v>
+        <v>-6</v>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
@@ -16097,25 +16097,25 @@
         </is>
       </c>
       <c r="AL90" t="n">
-        <v>-8</v>
+        <v>16</v>
       </c>
       <c r="AM90" t="n">
-        <v>-44.44</v>
+        <v>266.67</v>
       </c>
       <c r="AN90" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AO90" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
@@ -16130,29 +16130,29 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏賣</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、法人連續偏賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2362.TW</t>
+          <t>2882.TW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>藍天</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16171,28 +16171,28 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>47.75</v>
+        <v>110</v>
       </c>
       <c r="G91" t="n">
-        <v>48.27</v>
+        <v>113.6</v>
       </c>
       <c r="H91" t="n">
-        <v>47.58</v>
+        <v>113.05</v>
       </c>
       <c r="I91" t="n">
-        <v>47.43</v>
+        <v>112.2</v>
       </c>
       <c r="J91" t="n">
-        <v>604867</v>
+        <v>24145665</v>
       </c>
       <c r="K91" t="n">
-        <v>863095</v>
+        <v>23479461</v>
       </c>
       <c r="L91" t="n">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="M91" t="n">
-        <v>46.2</v>
+        <v>109</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -16200,52 +16200,52 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>-156</v>
+        <v>-7507408</v>
       </c>
       <c r="P91" t="n">
-        <v>99975</v>
+        <v>-1532218</v>
       </c>
       <c r="Q91" t="n">
-        <v>1129215</v>
+        <v>337060</v>
       </c>
       <c r="R91" t="n">
-        <v>1884131</v>
+        <v>20787884</v>
       </c>
       <c r="S91" t="n">
-        <v>15148</v>
+        <v>-7371284</v>
       </c>
       <c r="T91" t="n">
-        <v>127533</v>
+        <v>-3164697</v>
       </c>
       <c r="U91" t="n">
-        <v>1159775</v>
+        <v>-3483300</v>
       </c>
       <c r="V91" t="n">
-        <v>1914181</v>
+        <v>10019702</v>
       </c>
       <c r="W91" t="n">
-        <v>-303</v>
+        <v>-426439</v>
       </c>
       <c r="X91" t="n">
-        <v>-303</v>
+        <v>368261</v>
       </c>
       <c r="Y91" t="n">
-        <v>-303</v>
+        <v>240531</v>
       </c>
       <c r="Z91" t="n">
-        <v>-303</v>
+        <v>6202106</v>
       </c>
       <c r="AA91" t="n">
-        <v>-15001</v>
+        <v>290315</v>
       </c>
       <c r="AB91" t="n">
-        <v>-27255</v>
+        <v>1264218</v>
       </c>
       <c r="AC91" t="n">
-        <v>-30257</v>
+        <v>3579829</v>
       </c>
       <c r="AD91" t="n">
-        <v>-29747</v>
+        <v>4566076</v>
       </c>
       <c r="AE91" t="n">
         <v>10</v>
@@ -16254,16 +16254,16 @@
         <v>10</v>
       </c>
       <c r="AG91" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AH91" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
       </c>
       <c r="AJ91" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
@@ -16271,16 +16271,16 @@
         </is>
       </c>
       <c r="AL91" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AM91" t="n">
-        <v>0</v>
+        <v>-54.55</v>
       </c>
       <c r="AN91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AO91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
@@ -16304,29 +16304,29 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1906.TW</t>
+          <t>8070.TW</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>寶隆</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -16345,28 +16345,28 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>10.9</v>
+        <v>50.1</v>
       </c>
       <c r="G92" t="n">
-        <v>10.88</v>
+        <v>51.44</v>
       </c>
       <c r="H92" t="n">
-        <v>10.82</v>
+        <v>51.46</v>
       </c>
       <c r="I92" t="n">
-        <v>10.8</v>
+        <v>50.84</v>
       </c>
       <c r="J92" t="n">
-        <v>21337</v>
+        <v>1684433</v>
       </c>
       <c r="K92" t="n">
-        <v>47932</v>
+        <v>1984374</v>
       </c>
       <c r="L92" t="n">
-        <v>11.05</v>
+        <v>53.7</v>
       </c>
       <c r="M92" t="n">
-        <v>10.6</v>
+        <v>48.75</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -16374,70 +16374,70 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>-3698</v>
+        <v>-659184</v>
       </c>
       <c r="P92" t="n">
-        <v>-5838</v>
+        <v>100355</v>
       </c>
       <c r="Q92" t="n">
-        <v>-21635</v>
+        <v>651540</v>
       </c>
       <c r="R92" t="n">
-        <v>-19449</v>
+        <v>819741</v>
       </c>
       <c r="S92" t="n">
-        <v>-3698</v>
+        <v>-623476</v>
       </c>
       <c r="T92" t="n">
-        <v>-5838</v>
+        <v>173167</v>
       </c>
       <c r="U92" t="n">
-        <v>-17635</v>
+        <v>637315</v>
       </c>
       <c r="V92" t="n">
-        <v>-17449</v>
+        <v>-586143</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>-148</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>30646</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>50221</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1397043</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>-35560</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>-103458</v>
       </c>
       <c r="AC92" t="n">
-        <v>-4000</v>
+        <v>-35996</v>
       </c>
       <c r="AD92" t="n">
-        <v>-2000</v>
+        <v>8841</v>
       </c>
       <c r="AE92" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF92" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG92" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AH92" t="n">
         <v>50</v>
       </c>
-      <c r="AH92" t="n">
-        <v>-25</v>
-      </c>
       <c r="AI92" t="n">
         <v>0</v>
       </c>
       <c r="AJ92" t="n">
-        <v>-6</v>
+        <v>34</v>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
@@ -16445,25 +16445,25 @@
         </is>
       </c>
       <c r="AL92" t="n">
-        <v>16</v>
+        <v>-26</v>
       </c>
       <c r="AM92" t="n">
-        <v>266.67</v>
+        <v>-76.47</v>
       </c>
       <c r="AN92" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AO92" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
@@ -16478,29 +16478,29 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>法人連續偏賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、法人連續偏賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8070.TW</t>
+          <t>6230.TW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>超眾</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -16519,28 +16519,28 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>50.1</v>
+        <v>108.5</v>
       </c>
       <c r="G93" t="n">
-        <v>51.44</v>
+        <v>110.8</v>
       </c>
       <c r="H93" t="n">
-        <v>51.46</v>
+        <v>112.3</v>
       </c>
       <c r="I93" t="n">
-        <v>50.84</v>
+        <v>112.17</v>
       </c>
       <c r="J93" t="n">
-        <v>1684433</v>
+        <v>65727</v>
       </c>
       <c r="K93" t="n">
-        <v>1984374</v>
+        <v>35473</v>
       </c>
       <c r="L93" t="n">
-        <v>53.7</v>
+        <v>118.5</v>
       </c>
       <c r="M93" t="n">
-        <v>48.75</v>
+        <v>108.5</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -16548,70 +16548,70 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>-659184</v>
+        <v>1000</v>
       </c>
       <c r="P93" t="n">
-        <v>100355</v>
+        <v>1091</v>
       </c>
       <c r="Q93" t="n">
-        <v>651540</v>
+        <v>25769</v>
       </c>
       <c r="R93" t="n">
-        <v>819741</v>
+        <v>33413</v>
       </c>
       <c r="S93" t="n">
-        <v>-623476</v>
+        <v>3000</v>
       </c>
       <c r="T93" t="n">
-        <v>173167</v>
+        <v>3091</v>
       </c>
       <c r="U93" t="n">
-        <v>637315</v>
+        <v>27091</v>
       </c>
       <c r="V93" t="n">
-        <v>-586143</v>
+        <v>35590</v>
       </c>
       <c r="W93" t="n">
-        <v>-148</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>30646</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>50221</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1397043</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>-35560</v>
+        <v>-2000</v>
       </c>
       <c r="AB93" t="n">
-        <v>-103458</v>
+        <v>-2000</v>
       </c>
       <c r="AC93" t="n">
-        <v>-35996</v>
+        <v>-1322</v>
       </c>
       <c r="AD93" t="n">
-        <v>8841</v>
+        <v>-2177</v>
       </c>
       <c r="AE93" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF93" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG93" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
       <c r="AH93" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
@@ -16619,16 +16619,14 @@
         </is>
       </c>
       <c r="AL93" t="n">
-        <v>-26</v>
-      </c>
-      <c r="AM93" t="n">
-        <v>-76.47</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AM93" t="inlineStr"/>
       <c r="AN93" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AO93" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
@@ -16637,7 +16635,7 @@
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
@@ -16652,17 +16650,17 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、成交量放大、接近20日低點、法人連續偏買。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -17017,12 +17015,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6230.TW</t>
+          <t>2850.TW</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>超眾</t>
+          <t>新產</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -17041,28 +17039,28 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>108.5</v>
+        <v>162</v>
       </c>
       <c r="G96" t="n">
-        <v>110.8</v>
+        <v>168</v>
       </c>
       <c r="H96" t="n">
-        <v>112.3</v>
+        <v>166.05</v>
       </c>
       <c r="I96" t="n">
-        <v>112.17</v>
+        <v>162.7</v>
       </c>
       <c r="J96" t="n">
-        <v>65727</v>
+        <v>287983</v>
       </c>
       <c r="K96" t="n">
-        <v>35473</v>
+        <v>317091</v>
       </c>
       <c r="L96" t="n">
-        <v>118.5</v>
+        <v>174</v>
       </c>
       <c r="M96" t="n">
-        <v>108.5</v>
+        <v>156</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -17070,52 +17068,52 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>1000</v>
+        <v>-189097</v>
       </c>
       <c r="P96" t="n">
-        <v>1091</v>
+        <v>-142716</v>
       </c>
       <c r="Q96" t="n">
-        <v>25769</v>
+        <v>364138</v>
       </c>
       <c r="R96" t="n">
-        <v>33413</v>
+        <v>922841</v>
       </c>
       <c r="S96" t="n">
-        <v>3000</v>
+        <v>-181000</v>
       </c>
       <c r="T96" t="n">
-        <v>3091</v>
+        <v>-102619</v>
       </c>
       <c r="U96" t="n">
-        <v>27091</v>
+        <v>403235</v>
       </c>
       <c r="V96" t="n">
-        <v>35590</v>
+        <v>968909</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>-97</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>-5097</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>-5097</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>-6097</v>
       </c>
       <c r="AA96" t="n">
-        <v>-2000</v>
+        <v>-8000</v>
       </c>
       <c r="AB96" t="n">
-        <v>-2000</v>
+        <v>-35000</v>
       </c>
       <c r="AC96" t="n">
-        <v>-1322</v>
+        <v>-34000</v>
       </c>
       <c r="AD96" t="n">
-        <v>-2177</v>
+        <v>-39971</v>
       </c>
       <c r="AE96" t="n">
         <v>6</v>
@@ -17124,16 +17122,16 @@
         <v>6</v>
       </c>
       <c r="AG96" t="n">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="AH96" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
       </c>
       <c r="AJ96" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
@@ -17141,14 +17139,16 @@
         </is>
       </c>
       <c r="AL96" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM96" t="inlineStr"/>
+        <v>-20</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>-76.92</v>
+      </c>
       <c r="AN96" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AO96" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
@@ -17172,29 +17172,29 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>跌破5日線、成交量放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>法人連續偏買</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、成交量放大、接近20日低點、法人連續偏買。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2850.TW</t>
+          <t>2368.TW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>新產</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -17213,28 +17213,28 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>162</v>
+        <v>1185</v>
       </c>
       <c r="G97" t="n">
-        <v>168</v>
+        <v>1226</v>
       </c>
       <c r="H97" t="n">
-        <v>166.05</v>
+        <v>1232.5</v>
       </c>
       <c r="I97" t="n">
-        <v>162.7</v>
+        <v>1166.5</v>
       </c>
       <c r="J97" t="n">
-        <v>287983</v>
+        <v>11115878</v>
       </c>
       <c r="K97" t="n">
-        <v>317091</v>
+        <v>13830861</v>
       </c>
       <c r="L97" t="n">
-        <v>174</v>
+        <v>1310</v>
       </c>
       <c r="M97" t="n">
-        <v>156</v>
+        <v>969</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -17242,81 +17242,81 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>-189097</v>
+        <v>-835705</v>
       </c>
       <c r="P97" t="n">
-        <v>-142716</v>
+        <v>457174</v>
       </c>
       <c r="Q97" t="n">
-        <v>364138</v>
+        <v>1491745</v>
       </c>
       <c r="R97" t="n">
-        <v>922841</v>
+        <v>3513900</v>
       </c>
       <c r="S97" t="n">
-        <v>-181000</v>
+        <v>-1614992</v>
       </c>
       <c r="T97" t="n">
-        <v>-102619</v>
+        <v>-4762318</v>
       </c>
       <c r="U97" t="n">
-        <v>403235</v>
+        <v>-8991435</v>
       </c>
       <c r="V97" t="n">
-        <v>968909</v>
+        <v>-13291871</v>
       </c>
       <c r="W97" t="n">
-        <v>-97</v>
+        <v>733859</v>
       </c>
       <c r="X97" t="n">
-        <v>-5097</v>
+        <v>4900118</v>
       </c>
       <c r="Y97" t="n">
-        <v>-5097</v>
+        <v>10362655</v>
       </c>
       <c r="Z97" t="n">
-        <v>-6097</v>
+        <v>16959985</v>
       </c>
       <c r="AA97" t="n">
-        <v>-8000</v>
+        <v>45428</v>
       </c>
       <c r="AB97" t="n">
-        <v>-35000</v>
+        <v>319374</v>
       </c>
       <c r="AC97" t="n">
-        <v>-34000</v>
+        <v>120525</v>
       </c>
       <c r="AD97" t="n">
-        <v>-39971</v>
+        <v>-154214</v>
       </c>
       <c r="AE97" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF97" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG97" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="AH97" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ97" t="n">
         <v>20</v>
       </c>
-      <c r="AI97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ97" t="n">
-        <v>26</v>
-      </c>
       <c r="AK97" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
       <c r="AL97" t="n">
-        <v>-20</v>
+        <v>-16</v>
       </c>
       <c r="AM97" t="n">
-        <v>-76.92</v>
+        <v>-80</v>
       </c>
       <c r="AN97" t="n">
         <v>0</v>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
@@ -17346,29 +17346,29 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2368.TW</t>
+          <t>4903.TWO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -17387,28 +17387,28 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1185</v>
+        <v>54.2</v>
       </c>
       <c r="G98" t="n">
-        <v>1226</v>
+        <v>54.52</v>
       </c>
       <c r="H98" t="n">
-        <v>1232.5</v>
+        <v>50.96</v>
       </c>
       <c r="I98" t="n">
-        <v>1166.5</v>
+        <v>46.74</v>
       </c>
       <c r="J98" t="n">
-        <v>11115878</v>
+        <v>19208000</v>
       </c>
       <c r="K98" t="n">
-        <v>13830861</v>
+        <v>21203800</v>
       </c>
       <c r="L98" t="n">
-        <v>1310</v>
+        <v>59.3</v>
       </c>
       <c r="M98" t="n">
-        <v>969</v>
+        <v>34.3</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -17416,70 +17416,70 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>-835705</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>457174</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>1491745</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>3513900</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>-1614992</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>-4762318</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>-8991435</v>
+        <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>-13291871</v>
+        <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>733859</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>4900118</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>10362655</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>16959985</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>45428</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>319374</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>120525</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>-154214</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG98" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="AH98" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI98" t="n">
         <v>0</v>
       </c>
       <c r="AJ98" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
@@ -17487,16 +17487,16 @@
         </is>
       </c>
       <c r="AL98" t="n">
-        <v>-16</v>
+        <v>-4</v>
       </c>
       <c r="AM98" t="n">
-        <v>-80</v>
+        <v>-66.67</v>
       </c>
       <c r="AN98" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO98" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
@@ -17520,17 +17520,17 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -17711,12 +17711,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4903.TWO</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -17735,28 +17735,28 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>54.2</v>
+        <v>35.75</v>
       </c>
       <c r="G100" t="n">
-        <v>54.52</v>
+        <v>35.9</v>
       </c>
       <c r="H100" t="n">
-        <v>50.96</v>
+        <v>36.12</v>
       </c>
       <c r="I100" t="n">
-        <v>46.74</v>
+        <v>36.09</v>
       </c>
       <c r="J100" t="n">
-        <v>19208000</v>
+        <v>377897050</v>
       </c>
       <c r="K100" t="n">
-        <v>21203800</v>
+        <v>334354823</v>
       </c>
       <c r="L100" t="n">
-        <v>59.3</v>
+        <v>43.55</v>
       </c>
       <c r="M100" t="n">
-        <v>34.3</v>
+        <v>29.5</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -17764,87 +17764,87 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>-30301134</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>5537819</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>83371</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>-321782169</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>-31610492</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>518697</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>-4668249</v>
       </c>
       <c r="V100" t="n">
-        <v>0</v>
+        <v>-296822806</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>3057168</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>6270074</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>6528074</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>6638140</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>-1747810</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>-1250952</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>-1776454</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>-31597503</v>
       </c>
       <c r="AE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ100" t="n">
         <v>2</v>
       </c>
-      <c r="AF100" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG100" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ100" t="n">
-        <v>6</v>
-      </c>
       <c r="AK100" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
       <c r="AL100" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AM100" t="n">
-        <v>-66.67</v>
+        <v>-100</v>
       </c>
       <c r="AN100" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO100" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AR100" t="inlineStr">
@@ -17868,29 +17868,29 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人小幅買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、5日法人小幅買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2108.TW</t>
+          <t>1605.TW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>南帝</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -17909,28 +17909,28 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>28.9</v>
+        <v>37</v>
       </c>
       <c r="G101" t="n">
-        <v>29.46</v>
+        <v>38.29</v>
       </c>
       <c r="H101" t="n">
-        <v>29.54</v>
+        <v>38.79</v>
       </c>
       <c r="I101" t="n">
-        <v>29.03</v>
+        <v>38.14</v>
       </c>
       <c r="J101" t="n">
-        <v>311484</v>
+        <v>14221644</v>
       </c>
       <c r="K101" t="n">
-        <v>686936</v>
+        <v>43184898</v>
       </c>
       <c r="L101" t="n">
-        <v>31.45</v>
+        <v>41.1</v>
       </c>
       <c r="M101" t="n">
-        <v>28.1</v>
+        <v>36.2</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -17938,52 +17938,52 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>-71347</v>
+        <v>-1480515</v>
       </c>
       <c r="P101" t="n">
-        <v>-253883</v>
+        <v>-2318108</v>
       </c>
       <c r="Q101" t="n">
-        <v>735783</v>
+        <v>1242208</v>
       </c>
       <c r="R101" t="n">
-        <v>2471710</v>
+        <v>28063558</v>
       </c>
       <c r="S101" t="n">
-        <v>-60347</v>
+        <v>-696305</v>
       </c>
       <c r="T101" t="n">
-        <v>-205340</v>
+        <v>1820830</v>
       </c>
       <c r="U101" t="n">
-        <v>805368</v>
+        <v>-1437260</v>
       </c>
       <c r="V101" t="n">
-        <v>2583019</v>
+        <v>21162428</v>
       </c>
       <c r="W101" t="n">
-        <v>1000</v>
+        <v>-156</v>
       </c>
       <c r="X101" t="n">
-        <v>-8000</v>
+        <v>-3011156</v>
       </c>
       <c r="Y101" t="n">
-        <v>-8000</v>
+        <v>3728844</v>
       </c>
       <c r="Z101" t="n">
-        <v>-9000</v>
+        <v>7220634</v>
       </c>
       <c r="AA101" t="n">
-        <v>-12000</v>
+        <v>-784054</v>
       </c>
       <c r="AB101" t="n">
-        <v>-40543</v>
+        <v>-1127782</v>
       </c>
       <c r="AC101" t="n">
-        <v>-61585</v>
+        <v>-1049376</v>
       </c>
       <c r="AD101" t="n">
-        <v>-102309</v>
+        <v>-319504</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -18001,7 +18001,7 @@
         <v>0</v>
       </c>
       <c r="AJ101" t="n">
-        <v>10</v>
+        <v>-44</v>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
@@ -18009,10 +18009,10 @@
         </is>
       </c>
       <c r="AL101" t="n">
-        <v>-10</v>
+        <v>44</v>
       </c>
       <c r="AM101" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AN101" t="n">
         <v>0</v>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
@@ -18047,24 +18047,24 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>2108.TW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>南帝</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -18083,28 +18083,28 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>35.75</v>
+        <v>28.9</v>
       </c>
       <c r="G102" t="n">
-        <v>35.9</v>
+        <v>29.46</v>
       </c>
       <c r="H102" t="n">
-        <v>36.12</v>
+        <v>29.54</v>
       </c>
       <c r="I102" t="n">
-        <v>36.09</v>
+        <v>29.03</v>
       </c>
       <c r="J102" t="n">
-        <v>377897050</v>
+        <v>311484</v>
       </c>
       <c r="K102" t="n">
-        <v>334354823</v>
+        <v>686936</v>
       </c>
       <c r="L102" t="n">
-        <v>43.55</v>
+        <v>31.45</v>
       </c>
       <c r="M102" t="n">
-        <v>29.5</v>
+        <v>28.1</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -18112,52 +18112,52 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>-30301134</v>
+        <v>-71347</v>
       </c>
       <c r="P102" t="n">
-        <v>5537819</v>
+        <v>-253883</v>
       </c>
       <c r="Q102" t="n">
-        <v>83371</v>
+        <v>735783</v>
       </c>
       <c r="R102" t="n">
-        <v>-321782169</v>
+        <v>2471710</v>
       </c>
       <c r="S102" t="n">
-        <v>-31610492</v>
+        <v>-60347</v>
       </c>
       <c r="T102" t="n">
-        <v>518697</v>
+        <v>-205340</v>
       </c>
       <c r="U102" t="n">
-        <v>-4668249</v>
+        <v>805368</v>
       </c>
       <c r="V102" t="n">
-        <v>-296822806</v>
+        <v>2583019</v>
       </c>
       <c r="W102" t="n">
-        <v>3057168</v>
+        <v>1000</v>
       </c>
       <c r="X102" t="n">
-        <v>6270074</v>
+        <v>-8000</v>
       </c>
       <c r="Y102" t="n">
-        <v>6528074</v>
+        <v>-8000</v>
       </c>
       <c r="Z102" t="n">
-        <v>6638140</v>
+        <v>-9000</v>
       </c>
       <c r="AA102" t="n">
-        <v>-1747810</v>
+        <v>-12000</v>
       </c>
       <c r="AB102" t="n">
-        <v>-1250952</v>
+        <v>-40543</v>
       </c>
       <c r="AC102" t="n">
-        <v>-1776454</v>
+        <v>-61585</v>
       </c>
       <c r="AD102" t="n">
-        <v>-31597503</v>
+        <v>-102309</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -18166,24 +18166,24 @@
         <v>0</v>
       </c>
       <c r="AG102" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AL102" t="n">
         <v>-10</v>
-      </c>
-      <c r="AH102" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ102" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AL102" t="n">
-        <v>-2</v>
       </c>
       <c r="AM102" t="n">
         <v>-100</v>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
@@ -18216,29 +18216,29 @@
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>5日法人小幅買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、5日法人小幅買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1605.TW</t>
+          <t>2498.TW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -18257,28 +18257,28 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>37</v>
+        <v>39.95</v>
       </c>
       <c r="G103" t="n">
-        <v>38.29</v>
+        <v>40.21</v>
       </c>
       <c r="H103" t="n">
-        <v>38.79</v>
+        <v>40.89</v>
       </c>
       <c r="I103" t="n">
-        <v>38.14</v>
+        <v>41.33</v>
       </c>
       <c r="J103" t="n">
-        <v>14221644</v>
+        <v>2119399</v>
       </c>
       <c r="K103" t="n">
-        <v>43184898</v>
+        <v>3064223</v>
       </c>
       <c r="L103" t="n">
-        <v>41.1</v>
+        <v>46.85</v>
       </c>
       <c r="M103" t="n">
-        <v>36.2</v>
+        <v>39.55</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -18286,70 +18286,70 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>-1480515</v>
+        <v>485692</v>
       </c>
       <c r="P103" t="n">
-        <v>-2318108</v>
+        <v>1234275</v>
       </c>
       <c r="Q103" t="n">
-        <v>1242208</v>
+        <v>148487</v>
       </c>
       <c r="R103" t="n">
-        <v>28063558</v>
+        <v>492187</v>
       </c>
       <c r="S103" t="n">
-        <v>-696305</v>
+        <v>380912</v>
       </c>
       <c r="T103" t="n">
-        <v>1820830</v>
+        <v>1143019</v>
       </c>
       <c r="U103" t="n">
-        <v>-1437260</v>
+        <v>156867</v>
       </c>
       <c r="V103" t="n">
-        <v>21162428</v>
+        <v>805698</v>
       </c>
       <c r="W103" t="n">
-        <v>-156</v>
+        <v>-211</v>
       </c>
       <c r="X103" t="n">
-        <v>-3011156</v>
+        <v>-211</v>
       </c>
       <c r="Y103" t="n">
-        <v>3728844</v>
+        <v>-9211</v>
       </c>
       <c r="Z103" t="n">
-        <v>7220634</v>
+        <v>-15211</v>
       </c>
       <c r="AA103" t="n">
-        <v>-784054</v>
+        <v>104991</v>
       </c>
       <c r="AB103" t="n">
-        <v>-1127782</v>
+        <v>91467</v>
       </c>
       <c r="AC103" t="n">
-        <v>-1049376</v>
+        <v>831</v>
       </c>
       <c r="AD103" t="n">
-        <v>-319504</v>
+        <v>-298300</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AG103" t="n">
-        <v>-30</v>
+        <v>-55</v>
       </c>
       <c r="AH103" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>
       </c>
       <c r="AJ103" t="n">
-        <v>-44</v>
+        <v>-36</v>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
@@ -18357,10 +18357,10 @@
         </is>
       </c>
       <c r="AL103" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AM103" t="n">
-        <v>100</v>
+        <v>94.44</v>
       </c>
       <c r="AN103" t="n">
         <v>0</v>
@@ -18390,29 +18390,29 @@
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2498.TW</t>
+          <t>2617.TW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>台航</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -18431,28 +18431,28 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>39.95</v>
+        <v>31.35</v>
       </c>
       <c r="G104" t="n">
-        <v>40.21</v>
+        <v>32.08</v>
       </c>
       <c r="H104" t="n">
-        <v>40.89</v>
+        <v>32.19</v>
       </c>
       <c r="I104" t="n">
-        <v>41.33</v>
+        <v>32.22</v>
       </c>
       <c r="J104" t="n">
-        <v>2119399</v>
+        <v>712560</v>
       </c>
       <c r="K104" t="n">
-        <v>3064223</v>
+        <v>865989</v>
       </c>
       <c r="L104" t="n">
-        <v>46.85</v>
+        <v>33.35</v>
       </c>
       <c r="M104" t="n">
-        <v>39.55</v>
+        <v>30.85</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -18460,52 +18460,52 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>485692</v>
+        <v>-49658</v>
       </c>
       <c r="P104" t="n">
-        <v>1234275</v>
+        <v>117899</v>
       </c>
       <c r="Q104" t="n">
-        <v>148487</v>
+        <v>659502</v>
       </c>
       <c r="R104" t="n">
-        <v>492187</v>
+        <v>2166085</v>
       </c>
       <c r="S104" t="n">
-        <v>380912</v>
+        <v>-255000</v>
       </c>
       <c r="T104" t="n">
-        <v>1143019</v>
+        <v>-41673</v>
       </c>
       <c r="U104" t="n">
-        <v>156867</v>
+        <v>486215</v>
       </c>
       <c r="V104" t="n">
-        <v>805698</v>
+        <v>1981096</v>
       </c>
       <c r="W104" t="n">
-        <v>-211</v>
+        <v>218000</v>
       </c>
       <c r="X104" t="n">
-        <v>-211</v>
+        <v>220000</v>
       </c>
       <c r="Y104" t="n">
-        <v>-9211</v>
+        <v>220000</v>
       </c>
       <c r="Z104" t="n">
-        <v>-15211</v>
+        <v>220000</v>
       </c>
       <c r="AA104" t="n">
-        <v>104991</v>
+        <v>-12658</v>
       </c>
       <c r="AB104" t="n">
-        <v>91467</v>
+        <v>-60428</v>
       </c>
       <c r="AC104" t="n">
-        <v>831</v>
+        <v>-46713</v>
       </c>
       <c r="AD104" t="n">
-        <v>-298300</v>
+        <v>-35011</v>
       </c>
       <c r="AE104" t="n">
         <v>-2</v>
@@ -18523,7 +18523,7 @@
         <v>0</v>
       </c>
       <c r="AJ104" t="n">
-        <v>-36</v>
+        <v>12</v>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
@@ -18531,10 +18531,10 @@
         </is>
       </c>
       <c r="AL104" t="n">
-        <v>34</v>
+        <v>-14</v>
       </c>
       <c r="AM104" t="n">
-        <v>94.44</v>
+        <v>-116.67</v>
       </c>
       <c r="AN104" t="n">
         <v>0</v>
@@ -18549,7 +18549,7 @@
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
@@ -18569,12 +18569,12 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -18755,12 +18755,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2617.TW</t>
+          <t>6426.TW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>台航</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -18779,28 +18779,28 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>31.35</v>
+        <v>331</v>
       </c>
       <c r="G106" t="n">
-        <v>32.08</v>
+        <v>328.3</v>
       </c>
       <c r="H106" t="n">
-        <v>32.19</v>
+        <v>334.2</v>
       </c>
       <c r="I106" t="n">
-        <v>32.22</v>
+        <v>349.18</v>
       </c>
       <c r="J106" t="n">
-        <v>712560</v>
+        <v>1035920</v>
       </c>
       <c r="K106" t="n">
-        <v>865989</v>
+        <v>1255430</v>
       </c>
       <c r="L106" t="n">
-        <v>33.35</v>
+        <v>412</v>
       </c>
       <c r="M106" t="n">
-        <v>30.85</v>
+        <v>310</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -18808,70 +18808,70 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>-49658</v>
+        <v>56429</v>
       </c>
       <c r="P106" t="n">
-        <v>117899</v>
+        <v>133976</v>
       </c>
       <c r="Q106" t="n">
-        <v>659502</v>
+        <v>-139728</v>
       </c>
       <c r="R106" t="n">
-        <v>2166085</v>
+        <v>-1157034</v>
       </c>
       <c r="S106" t="n">
-        <v>-255000</v>
+        <v>40950</v>
       </c>
       <c r="T106" t="n">
-        <v>-41673</v>
+        <v>94367</v>
       </c>
       <c r="U106" t="n">
-        <v>486215</v>
+        <v>-178106</v>
       </c>
       <c r="V106" t="n">
-        <v>1981096</v>
+        <v>-1156687</v>
       </c>
       <c r="W106" t="n">
-        <v>218000</v>
+        <v>12000</v>
       </c>
       <c r="X106" t="n">
-        <v>220000</v>
+        <v>23000</v>
       </c>
       <c r="Y106" t="n">
-        <v>220000</v>
+        <v>23000</v>
       </c>
       <c r="Z106" t="n">
-        <v>220000</v>
+        <v>23000</v>
       </c>
       <c r="AA106" t="n">
-        <v>-12658</v>
+        <v>3479</v>
       </c>
       <c r="AB106" t="n">
-        <v>-60428</v>
+        <v>16609</v>
       </c>
       <c r="AC106" t="n">
-        <v>-46713</v>
+        <v>15378</v>
       </c>
       <c r="AD106" t="n">
-        <v>-35011</v>
+        <v>-23347</v>
       </c>
       <c r="AE106" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AF106" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="AG106" t="n">
-        <v>-55</v>
+        <v>-5</v>
       </c>
       <c r="AH106" t="n">
-        <v>50</v>
+        <v>-5</v>
       </c>
       <c r="AI106" t="n">
         <v>0</v>
       </c>
       <c r="AJ106" t="n">
-        <v>12</v>
+        <v>-4</v>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
@@ -18879,25 +18879,25 @@
         </is>
       </c>
       <c r="AL106" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="AM106" t="n">
-        <v>-116.67</v>
+        <v>0</v>
       </c>
       <c r="AN106" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO106" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
@@ -18912,17 +18912,17 @@
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -19277,12 +19277,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>6426.TW</t>
+          <t>2485.TW</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -19301,28 +19301,28 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>331</v>
+        <v>38.5</v>
       </c>
       <c r="G109" t="n">
-        <v>328.3</v>
+        <v>39.49</v>
       </c>
       <c r="H109" t="n">
-        <v>334.2</v>
+        <v>40.7</v>
       </c>
       <c r="I109" t="n">
-        <v>349.18</v>
+        <v>40.67</v>
       </c>
       <c r="J109" t="n">
-        <v>1035920</v>
+        <v>2869240</v>
       </c>
       <c r="K109" t="n">
-        <v>1255430</v>
+        <v>3393234</v>
       </c>
       <c r="L109" t="n">
-        <v>412</v>
+        <v>48</v>
       </c>
       <c r="M109" t="n">
-        <v>310</v>
+        <v>38.35</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -19330,52 +19330,52 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>56429</v>
+        <v>-613883</v>
       </c>
       <c r="P109" t="n">
-        <v>133976</v>
+        <v>897300</v>
       </c>
       <c r="Q109" t="n">
-        <v>-139728</v>
+        <v>498881</v>
       </c>
       <c r="R109" t="n">
-        <v>-1157034</v>
+        <v>-13240499</v>
       </c>
       <c r="S109" t="n">
-        <v>40950</v>
+        <v>-523705</v>
       </c>
       <c r="T109" t="n">
-        <v>94367</v>
+        <v>894855</v>
       </c>
       <c r="U109" t="n">
-        <v>-178106</v>
+        <v>660484</v>
       </c>
       <c r="V109" t="n">
-        <v>-1156687</v>
+        <v>-12266533</v>
       </c>
       <c r="W109" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>3479</v>
+        <v>-90178</v>
       </c>
       <c r="AB109" t="n">
-        <v>16609</v>
+        <v>2445</v>
       </c>
       <c r="AC109" t="n">
-        <v>15378</v>
+        <v>-161603</v>
       </c>
       <c r="AD109" t="n">
-        <v>-23347</v>
+        <v>-973966</v>
       </c>
       <c r="AE109" t="n">
         <v>-4</v>
@@ -19384,16 +19384,16 @@
         <v>-4</v>
       </c>
       <c r="AG109" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
       <c r="AH109" t="n">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="AI109" t="n">
         <v>0</v>
       </c>
       <c r="AJ109" t="n">
-        <v>-4</v>
+        <v>-18</v>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
@@ -19401,25 +19401,25 @@
         </is>
       </c>
       <c r="AL109" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AM109" t="n">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="AN109" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AO109" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
@@ -19434,29 +19434,29 @@
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2485.TW</t>
+          <t>2540.TW</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>愛山林</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -19475,28 +19475,28 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>38.5</v>
+        <v>46.8</v>
       </c>
       <c r="G110" t="n">
-        <v>39.49</v>
+        <v>48.64</v>
       </c>
       <c r="H110" t="n">
-        <v>40.7</v>
+        <v>48.82</v>
       </c>
       <c r="I110" t="n">
-        <v>40.67</v>
+        <v>48.83</v>
       </c>
       <c r="J110" t="n">
-        <v>2869240</v>
+        <v>627046</v>
       </c>
       <c r="K110" t="n">
-        <v>3393234</v>
+        <v>427972</v>
       </c>
       <c r="L110" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M110" t="n">
-        <v>38.35</v>
+        <v>46.4</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -19504,87 +19504,87 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>-613883</v>
+        <v>-156485</v>
       </c>
       <c r="P110" t="n">
-        <v>897300</v>
+        <v>-37986</v>
       </c>
       <c r="Q110" t="n">
-        <v>498881</v>
+        <v>560401</v>
       </c>
       <c r="R110" t="n">
-        <v>-13240499</v>
+        <v>1887942</v>
       </c>
       <c r="S110" t="n">
-        <v>-523705</v>
+        <v>-80000</v>
       </c>
       <c r="T110" t="n">
-        <v>894855</v>
+        <v>61499</v>
       </c>
       <c r="U110" t="n">
-        <v>660484</v>
+        <v>651886</v>
       </c>
       <c r="V110" t="n">
-        <v>-12266533</v>
+        <v>1982427</v>
       </c>
       <c r="W110" t="n">
-        <v>0</v>
+        <v>-485</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>-485</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>-485</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>-485</v>
       </c>
       <c r="AA110" t="n">
-        <v>-90178</v>
+        <v>-76000</v>
       </c>
       <c r="AB110" t="n">
-        <v>2445</v>
+        <v>-99000</v>
       </c>
       <c r="AC110" t="n">
-        <v>-161603</v>
+        <v>-91000</v>
       </c>
       <c r="AD110" t="n">
-        <v>-973966</v>
+        <v>-94000</v>
       </c>
       <c r="AE110" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="AF110" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="AG110" t="n">
-        <v>-30</v>
+        <v>-45</v>
       </c>
       <c r="AH110" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
       </c>
       <c r="AJ110" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AL110" t="n">
         <v>-18</v>
       </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AL110" t="n">
-        <v>14</v>
-      </c>
       <c r="AM110" t="n">
-        <v>77.78</v>
+        <v>-150</v>
       </c>
       <c r="AN110" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO110" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
@@ -19608,29 +19608,29 @@
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2436.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>偉詮電</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -19649,28 +19649,28 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>68.2</v>
+        <v>14.6</v>
       </c>
       <c r="G111" t="n">
-        <v>69.92</v>
+        <v>14.88</v>
       </c>
       <c r="H111" t="n">
-        <v>70.94</v>
+        <v>15.04</v>
       </c>
       <c r="I111" t="n">
-        <v>71.7</v>
+        <v>15.17</v>
       </c>
       <c r="J111" t="n">
-        <v>1453285</v>
+        <v>18141396</v>
       </c>
       <c r="K111" t="n">
-        <v>2025281</v>
+        <v>23746242</v>
       </c>
       <c r="L111" t="n">
-        <v>77.5</v>
+        <v>17.5</v>
       </c>
       <c r="M111" t="n">
-        <v>67.2</v>
+        <v>13.85</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -19678,52 +19678,52 @@
         </is>
       </c>
       <c r="O111" t="n">
-        <v>-42891</v>
+        <v>-2658630</v>
       </c>
       <c r="P111" t="n">
-        <v>111079</v>
+        <v>1797485</v>
       </c>
       <c r="Q111" t="n">
-        <v>387051</v>
+        <v>1701026</v>
       </c>
       <c r="R111" t="n">
-        <v>1320776</v>
+        <v>-15230459</v>
       </c>
       <c r="S111" t="n">
-        <v>-19321</v>
+        <v>-2482500</v>
       </c>
       <c r="T111" t="n">
-        <v>212003</v>
+        <v>1733986</v>
       </c>
       <c r="U111" t="n">
-        <v>471356</v>
+        <v>1723577</v>
       </c>
       <c r="V111" t="n">
-        <v>1833086</v>
+        <v>-15011202</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>-247</v>
       </c>
       <c r="X111" t="n">
-        <v>59000</v>
+        <v>-247</v>
       </c>
       <c r="Y111" t="n">
-        <v>94000</v>
+        <v>-247</v>
       </c>
       <c r="Z111" t="n">
-        <v>100000</v>
+        <v>-247</v>
       </c>
       <c r="AA111" t="n">
-        <v>-23570</v>
+        <v>-175883</v>
       </c>
       <c r="AB111" t="n">
-        <v>-159924</v>
+        <v>63746</v>
       </c>
       <c r="AC111" t="n">
-        <v>-178305</v>
+        <v>-22304</v>
       </c>
       <c r="AD111" t="n">
-        <v>-612310</v>
+        <v>-219010</v>
       </c>
       <c r="AE111" t="n">
         <v>-6</v>
@@ -19732,16 +19732,16 @@
         <v>-6</v>
       </c>
       <c r="AG111" t="n">
-        <v>-55</v>
+        <v>-45</v>
       </c>
       <c r="AH111" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
       </c>
       <c r="AJ111" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
@@ -19749,10 +19749,10 @@
         </is>
       </c>
       <c r="AL111" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="AM111" t="n">
-        <v>-200</v>
+        <v>-250</v>
       </c>
       <c r="AN111" t="n">
         <v>0</v>
@@ -19782,29 +19782,29 @@
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2540.TW</t>
+          <t>2436.TW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>愛山林</t>
+          <t>偉詮電</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -19823,28 +19823,28 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>46.8</v>
+        <v>68.2</v>
       </c>
       <c r="G112" t="n">
-        <v>48.64</v>
+        <v>69.92</v>
       </c>
       <c r="H112" t="n">
-        <v>48.82</v>
+        <v>70.94</v>
       </c>
       <c r="I112" t="n">
-        <v>48.83</v>
+        <v>71.7</v>
       </c>
       <c r="J112" t="n">
-        <v>627046</v>
+        <v>1453285</v>
       </c>
       <c r="K112" t="n">
-        <v>427972</v>
+        <v>2025281</v>
       </c>
       <c r="L112" t="n">
-        <v>54</v>
+        <v>77.5</v>
       </c>
       <c r="M112" t="n">
-        <v>46.4</v>
+        <v>67.2</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -19852,52 +19852,52 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>-156485</v>
+        <v>-42891</v>
       </c>
       <c r="P112" t="n">
-        <v>-37986</v>
+        <v>111079</v>
       </c>
       <c r="Q112" t="n">
-        <v>560401</v>
+        <v>387051</v>
       </c>
       <c r="R112" t="n">
-        <v>1887942</v>
+        <v>1320776</v>
       </c>
       <c r="S112" t="n">
-        <v>-80000</v>
+        <v>-19321</v>
       </c>
       <c r="T112" t="n">
-        <v>61499</v>
+        <v>212003</v>
       </c>
       <c r="U112" t="n">
-        <v>651886</v>
+        <v>471356</v>
       </c>
       <c r="V112" t="n">
-        <v>1982427</v>
+        <v>1833086</v>
       </c>
       <c r="W112" t="n">
-        <v>-485</v>
+        <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>-485</v>
+        <v>59000</v>
       </c>
       <c r="Y112" t="n">
-        <v>-485</v>
+        <v>94000</v>
       </c>
       <c r="Z112" t="n">
-        <v>-485</v>
+        <v>100000</v>
       </c>
       <c r="AA112" t="n">
-        <v>-76000</v>
+        <v>-23570</v>
       </c>
       <c r="AB112" t="n">
-        <v>-99000</v>
+        <v>-159924</v>
       </c>
       <c r="AC112" t="n">
-        <v>-91000</v>
+        <v>-178305</v>
       </c>
       <c r="AD112" t="n">
-        <v>-94000</v>
+        <v>-612310</v>
       </c>
       <c r="AE112" t="n">
         <v>-6</v>
@@ -19906,16 +19906,16 @@
         <v>-6</v>
       </c>
       <c r="AG112" t="n">
-        <v>-45</v>
+        <v>-55</v>
       </c>
       <c r="AH112" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
       </c>
       <c r="AJ112" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
@@ -19923,10 +19923,10 @@
         </is>
       </c>
       <c r="AL112" t="n">
-        <v>-18</v>
+        <v>-4</v>
       </c>
       <c r="AM112" t="n">
-        <v>-150</v>
+        <v>-200</v>
       </c>
       <c r="AN112" t="n">
         <v>0</v>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -19956,29 +19956,29 @@
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>2748.TW</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>雲品</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -19997,28 +19997,28 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>14.6</v>
+        <v>38.3</v>
       </c>
       <c r="G113" t="n">
-        <v>14.88</v>
+        <v>38.53</v>
       </c>
       <c r="H113" t="n">
-        <v>15.04</v>
+        <v>38.62</v>
       </c>
       <c r="I113" t="n">
-        <v>15.17</v>
+        <v>38.72</v>
       </c>
       <c r="J113" t="n">
-        <v>18141396</v>
+        <v>65033</v>
       </c>
       <c r="K113" t="n">
-        <v>23746242</v>
+        <v>52089</v>
       </c>
       <c r="L113" t="n">
-        <v>17.5</v>
+        <v>39.5</v>
       </c>
       <c r="M113" t="n">
-        <v>13.85</v>
+        <v>38.1</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -20026,52 +20026,52 @@
         </is>
       </c>
       <c r="O113" t="n">
-        <v>-2658630</v>
+        <v>18000</v>
       </c>
       <c r="P113" t="n">
-        <v>1797485</v>
+        <v>12000</v>
       </c>
       <c r="Q113" t="n">
-        <v>1701026</v>
+        <v>35000</v>
       </c>
       <c r="R113" t="n">
-        <v>-15230459</v>
+        <v>18000</v>
       </c>
       <c r="S113" t="n">
-        <v>-2482500</v>
+        <v>21000</v>
       </c>
       <c r="T113" t="n">
-        <v>1733986</v>
+        <v>17000</v>
       </c>
       <c r="U113" t="n">
-        <v>1723577</v>
+        <v>38000</v>
       </c>
       <c r="V113" t="n">
-        <v>-15011202</v>
+        <v>22000</v>
       </c>
       <c r="W113" t="n">
-        <v>-247</v>
+        <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>-247</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>-247</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>-247</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>-175883</v>
+        <v>-3000</v>
       </c>
       <c r="AB113" t="n">
-        <v>63746</v>
+        <v>-5000</v>
       </c>
       <c r="AC113" t="n">
-        <v>-22304</v>
+        <v>-3000</v>
       </c>
       <c r="AD113" t="n">
-        <v>-219010</v>
+        <v>-4000</v>
       </c>
       <c r="AE113" t="n">
         <v>-6</v>
@@ -20089,7 +20089,7 @@
         <v>0</v>
       </c>
       <c r="AJ113" t="n">
-        <v>4</v>
+        <v>-18</v>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
@@ -20097,16 +20097,16 @@
         </is>
       </c>
       <c r="AL113" t="n">
-        <v>-10</v>
+        <v>12</v>
       </c>
       <c r="AM113" t="n">
-        <v>-250</v>
+        <v>66.67</v>
       </c>
       <c r="AN113" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO113" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
@@ -20130,29 +20130,29 @@
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2748.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>雲品</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -20171,28 +20171,28 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>38.3</v>
+        <v>1550</v>
       </c>
       <c r="G114" t="n">
-        <v>38.53</v>
+        <v>1631</v>
       </c>
       <c r="H114" t="n">
-        <v>38.62</v>
+        <v>1676</v>
       </c>
       <c r="I114" t="n">
-        <v>38.72</v>
+        <v>1595</v>
       </c>
       <c r="J114" t="n">
-        <v>65033</v>
+        <v>9283000</v>
       </c>
       <c r="K114" t="n">
-        <v>52089</v>
+        <v>10897600</v>
       </c>
       <c r="L114" t="n">
-        <v>39.5</v>
+        <v>1835</v>
       </c>
       <c r="M114" t="n">
-        <v>38.1</v>
+        <v>1335</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
@@ -20200,28 +20200,28 @@
         </is>
       </c>
       <c r="O114" t="n">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="W114" t="n">
         <v>0</v>
@@ -20236,34 +20236,34 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AF114" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AG114" t="n">
-        <v>-45</v>
+        <v>-20</v>
       </c>
       <c r="AH114" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI114" t="n">
         <v>0</v>
       </c>
       <c r="AJ114" t="n">
-        <v>-18</v>
+        <v>-8</v>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
@@ -20271,16 +20271,16 @@
         </is>
       </c>
       <c r="AL114" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AM114" t="n">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="AN114" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AO114" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
@@ -20304,29 +20304,29 @@
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>法人連續偏買</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -20345,28 +20345,28 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1550</v>
+        <v>475</v>
       </c>
       <c r="G115" t="n">
-        <v>1631</v>
+        <v>503.4</v>
       </c>
       <c r="H115" t="n">
-        <v>1676</v>
+        <v>541.4</v>
       </c>
       <c r="I115" t="n">
-        <v>1595</v>
+        <v>534.17</v>
       </c>
       <c r="J115" t="n">
-        <v>9283000</v>
+        <v>25520000</v>
       </c>
       <c r="K115" t="n">
-        <v>10897600</v>
+        <v>18246600</v>
       </c>
       <c r="L115" t="n">
-        <v>1835</v>
+        <v>630</v>
       </c>
       <c r="M115" t="n">
-        <v>1335</v>
+        <v>454</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>0</v>
       </c>
       <c r="AJ115" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
@@ -20445,16 +20445,16 @@
         </is>
       </c>
       <c r="AL115" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM115" t="n">
-        <v>0</v>
+        <v>42.86</v>
       </c>
       <c r="AN115" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO115" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
@@ -20478,7 +20478,7 @@
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
@@ -20488,7 +20488,7 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -20669,12 +20669,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>2331.TW</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>精英</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -20693,28 +20693,28 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>475</v>
+        <v>18</v>
       </c>
       <c r="G117" t="n">
-        <v>503.4</v>
+        <v>18.23</v>
       </c>
       <c r="H117" t="n">
-        <v>541.4</v>
+        <v>18.49</v>
       </c>
       <c r="I117" t="n">
-        <v>534.17</v>
+        <v>18.75</v>
       </c>
       <c r="J117" t="n">
-        <v>25520000</v>
+        <v>653775</v>
       </c>
       <c r="K117" t="n">
-        <v>18246600</v>
+        <v>1173004</v>
       </c>
       <c r="L117" t="n">
-        <v>630</v>
+        <v>19.65</v>
       </c>
       <c r="M117" t="n">
-        <v>454</v>
+        <v>17.85</v>
       </c>
       <c r="N117" t="inlineStr">
         <is>
@@ -20722,28 +20722,28 @@
         </is>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>153058</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>-115825</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>616771</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>398480</v>
       </c>
       <c r="S117" t="n">
-        <v>0</v>
+        <v>169433</v>
       </c>
       <c r="T117" t="n">
-        <v>0</v>
+        <v>88433</v>
       </c>
       <c r="U117" t="n">
-        <v>0</v>
+        <v>593029</v>
       </c>
       <c r="V117" t="n">
-        <v>0</v>
+        <v>418738</v>
       </c>
       <c r="W117" t="n">
         <v>0</v>
@@ -20758,34 +20758,34 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>-16375</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>-204258</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>23742</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>-20258</v>
       </c>
       <c r="AE117" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="AF117" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="AG117" t="n">
-        <v>-20</v>
+        <v>-55</v>
       </c>
       <c r="AH117" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI117" t="n">
         <v>0</v>
       </c>
       <c r="AJ117" t="n">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
@@ -20793,16 +20793,16 @@
         </is>
       </c>
       <c r="AL117" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AM117" t="n">
-        <v>42.86</v>
+        <v>54.55</v>
       </c>
       <c r="AN117" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AO117" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
@@ -20826,17 +20826,17 @@
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -21017,12 +21017,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2331.TW</t>
+          <t>1710.TW</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>精英</t>
+          <t>東聯</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -21041,28 +21041,28 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>18</v>
+        <v>17.45</v>
       </c>
       <c r="G119" t="n">
-        <v>18.23</v>
+        <v>18.22</v>
       </c>
       <c r="H119" t="n">
-        <v>18.49</v>
+        <v>18.16</v>
       </c>
       <c r="I119" t="n">
-        <v>18.75</v>
+        <v>17.49</v>
       </c>
       <c r="J119" t="n">
-        <v>653775</v>
+        <v>3493614</v>
       </c>
       <c r="K119" t="n">
-        <v>1173004</v>
+        <v>9983520</v>
       </c>
       <c r="L119" t="n">
-        <v>19.65</v>
+        <v>20</v>
       </c>
       <c r="M119" t="n">
-        <v>17.85</v>
+        <v>16.05</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -21070,28 +21070,28 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>153058</v>
+        <v>324758</v>
       </c>
       <c r="P119" t="n">
-        <v>-115825</v>
+        <v>536218</v>
       </c>
       <c r="Q119" t="n">
-        <v>616771</v>
+        <v>-833957</v>
       </c>
       <c r="R119" t="n">
-        <v>398480</v>
+        <v>10427970</v>
       </c>
       <c r="S119" t="n">
-        <v>169433</v>
+        <v>853801</v>
       </c>
       <c r="T119" t="n">
-        <v>88433</v>
+        <v>1822102</v>
       </c>
       <c r="U119" t="n">
-        <v>593029</v>
+        <v>529240</v>
       </c>
       <c r="V119" t="n">
-        <v>418738</v>
+        <v>10635756</v>
       </c>
       <c r="W119" t="n">
         <v>0</v>
@@ -21106,16 +21106,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>-16375</v>
+        <v>-529043</v>
       </c>
       <c r="AB119" t="n">
-        <v>-204258</v>
+        <v>-1285884</v>
       </c>
       <c r="AC119" t="n">
-        <v>23742</v>
+        <v>-1363197</v>
       </c>
       <c r="AD119" t="n">
-        <v>-20258</v>
+        <v>-207786</v>
       </c>
       <c r="AE119" t="n">
         <v>-10</v>
@@ -21124,16 +21124,16 @@
         <v>-10</v>
       </c>
       <c r="AG119" t="n">
-        <v>-55</v>
+        <v>5</v>
       </c>
       <c r="AH119" t="n">
-        <v>30</v>
+        <v>-30</v>
       </c>
       <c r="AI119" t="n">
         <v>0</v>
       </c>
       <c r="AJ119" t="n">
-        <v>-22</v>
+        <v>14</v>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
@@ -21141,16 +21141,16 @@
         </is>
       </c>
       <c r="AL119" t="n">
-        <v>12</v>
+        <v>-24</v>
       </c>
       <c r="AM119" t="n">
-        <v>54.55</v>
+        <v>-171.43</v>
       </c>
       <c r="AN119" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO119" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
@@ -21174,29 +21174,29 @@
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1710.TW</t>
+          <t>2371.TW</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>東聯</t>
+          <t>大同</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -21215,28 +21215,28 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>17.45</v>
+        <v>28.3</v>
       </c>
       <c r="G120" t="n">
-        <v>18.22</v>
+        <v>29.07</v>
       </c>
       <c r="H120" t="n">
-        <v>18.16</v>
+        <v>29.59</v>
       </c>
       <c r="I120" t="n">
-        <v>17.49</v>
+        <v>29.7</v>
       </c>
       <c r="J120" t="n">
-        <v>3493614</v>
+        <v>7685780</v>
       </c>
       <c r="K120" t="n">
-        <v>9983520</v>
+        <v>9680223</v>
       </c>
       <c r="L120" t="n">
-        <v>20</v>
+        <v>31.6</v>
       </c>
       <c r="M120" t="n">
-        <v>16.05</v>
+        <v>28.3</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -21244,52 +21244,52 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>324758</v>
+        <v>-1687696</v>
       </c>
       <c r="P120" t="n">
-        <v>536218</v>
+        <v>-1830439</v>
       </c>
       <c r="Q120" t="n">
-        <v>-833957</v>
+        <v>2474254</v>
       </c>
       <c r="R120" t="n">
-        <v>10427970</v>
+        <v>-2200377</v>
       </c>
       <c r="S120" t="n">
-        <v>853801</v>
+        <v>-1625840</v>
       </c>
       <c r="T120" t="n">
-        <v>1822102</v>
+        <v>-1680248</v>
       </c>
       <c r="U120" t="n">
-        <v>529240</v>
+        <v>2506841</v>
       </c>
       <c r="V120" t="n">
-        <v>10635756</v>
+        <v>-1786722</v>
       </c>
       <c r="W120" t="n">
-        <v>0</v>
+        <v>-444</v>
       </c>
       <c r="X120" t="n">
-        <v>0</v>
+        <v>-444</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>-444</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>-122444</v>
       </c>
       <c r="AA120" t="n">
-        <v>-529043</v>
+        <v>-61412</v>
       </c>
       <c r="AB120" t="n">
-        <v>-1285884</v>
+        <v>-149747</v>
       </c>
       <c r="AC120" t="n">
-        <v>-1363197</v>
+        <v>-32143</v>
       </c>
       <c r="AD120" t="n">
-        <v>-207786</v>
+        <v>-291211</v>
       </c>
       <c r="AE120" t="n">
         <v>-10</v>
@@ -21298,16 +21298,16 @@
         <v>-10</v>
       </c>
       <c r="AG120" t="n">
-        <v>5</v>
+        <v>-55</v>
       </c>
       <c r="AH120" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
       <c r="AI120" t="n">
         <v>0</v>
       </c>
       <c r="AJ120" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
@@ -21315,10 +21315,10 @@
         </is>
       </c>
       <c r="AL120" t="n">
-        <v>-24</v>
+        <v>-14</v>
       </c>
       <c r="AM120" t="n">
-        <v>-171.43</v>
+        <v>-350</v>
       </c>
       <c r="AN120" t="n">
         <v>0</v>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
@@ -21348,17 +21348,17 @@
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -21539,12 +21539,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2371.TW</t>
+          <t>2731.TW</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>大同</t>
+          <t>雄獅</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -21563,28 +21563,28 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>28.3</v>
+        <v>142.5</v>
       </c>
       <c r="G122" t="n">
-        <v>29.07</v>
+        <v>143.2</v>
       </c>
       <c r="H122" t="n">
-        <v>29.59</v>
+        <v>143.75</v>
       </c>
       <c r="I122" t="n">
-        <v>29.7</v>
+        <v>143.78</v>
       </c>
       <c r="J122" t="n">
-        <v>7685780</v>
+        <v>219354</v>
       </c>
       <c r="K122" t="n">
-        <v>9680223</v>
+        <v>321647</v>
       </c>
       <c r="L122" t="n">
-        <v>31.6</v>
+        <v>146</v>
       </c>
       <c r="M122" t="n">
-        <v>28.3</v>
+        <v>141.5</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -21592,52 +21592,52 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>-1687696</v>
+        <v>13204</v>
       </c>
       <c r="P122" t="n">
-        <v>-1830439</v>
+        <v>50289</v>
       </c>
       <c r="Q122" t="n">
-        <v>2474254</v>
+        <v>18473</v>
       </c>
       <c r="R122" t="n">
-        <v>-2200377</v>
+        <v>243634</v>
       </c>
       <c r="S122" t="n">
-        <v>-1625840</v>
+        <v>-47177</v>
       </c>
       <c r="T122" t="n">
-        <v>-1680248</v>
+        <v>18908</v>
       </c>
       <c r="U122" t="n">
-        <v>2506841</v>
+        <v>-8908</v>
       </c>
       <c r="V122" t="n">
-        <v>-1786722</v>
+        <v>215019</v>
       </c>
       <c r="W122" t="n">
-        <v>-444</v>
+        <v>66000</v>
       </c>
       <c r="X122" t="n">
-        <v>-444</v>
+        <v>38000</v>
       </c>
       <c r="Y122" t="n">
-        <v>-444</v>
+        <v>38000</v>
       </c>
       <c r="Z122" t="n">
-        <v>-122444</v>
+        <v>38000</v>
       </c>
       <c r="AA122" t="n">
-        <v>-61412</v>
+        <v>-5619</v>
       </c>
       <c r="AB122" t="n">
-        <v>-149747</v>
+        <v>-6619</v>
       </c>
       <c r="AC122" t="n">
-        <v>-32143</v>
+        <v>-10619</v>
       </c>
       <c r="AD122" t="n">
-        <v>-291211</v>
+        <v>-9385</v>
       </c>
       <c r="AE122" t="n">
         <v>-10</v>
@@ -21655,7 +21655,7 @@
         <v>0</v>
       </c>
       <c r="AJ122" t="n">
-        <v>4</v>
+        <v>-12</v>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
@@ -21663,16 +21663,16 @@
         </is>
       </c>
       <c r="AL122" t="n">
-        <v>-14</v>
+        <v>2</v>
       </c>
       <c r="AM122" t="n">
-        <v>-350</v>
+        <v>16.67</v>
       </c>
       <c r="AN122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
@@ -21701,24 +21701,24 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、投信買外資賣</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2731.TW</t>
+          <t>2351.TW</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>雄獅</t>
+          <t>順德</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -21737,28 +21737,28 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>142.5</v>
+        <v>195.5</v>
       </c>
       <c r="G123" t="n">
-        <v>143.2</v>
+        <v>203.1</v>
       </c>
       <c r="H123" t="n">
-        <v>143.75</v>
+        <v>208.95</v>
       </c>
       <c r="I123" t="n">
-        <v>143.78</v>
+        <v>216.1</v>
       </c>
       <c r="J123" t="n">
-        <v>219354</v>
+        <v>1830315</v>
       </c>
       <c r="K123" t="n">
-        <v>321647</v>
+        <v>2479494</v>
       </c>
       <c r="L123" t="n">
-        <v>146</v>
+        <v>243.5</v>
       </c>
       <c r="M123" t="n">
-        <v>141.5</v>
+        <v>193.5</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
@@ -21766,52 +21766,52 @@
         </is>
       </c>
       <c r="O123" t="n">
-        <v>13204</v>
+        <v>-38182</v>
       </c>
       <c r="P123" t="n">
-        <v>50289</v>
+        <v>750637</v>
       </c>
       <c r="Q123" t="n">
-        <v>18473</v>
+        <v>748019</v>
       </c>
       <c r="R123" t="n">
-        <v>243634</v>
+        <v>1213321</v>
       </c>
       <c r="S123" t="n">
-        <v>-47177</v>
+        <v>8887</v>
       </c>
       <c r="T123" t="n">
-        <v>18908</v>
+        <v>-734192</v>
       </c>
       <c r="U123" t="n">
-        <v>-8908</v>
+        <v>-2113769</v>
       </c>
       <c r="V123" t="n">
-        <v>215019</v>
+        <v>-1244842</v>
       </c>
       <c r="W123" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="X123" t="n">
-        <v>38000</v>
+        <v>1569000</v>
       </c>
       <c r="Y123" t="n">
-        <v>38000</v>
+        <v>2940000</v>
       </c>
       <c r="Z123" t="n">
-        <v>38000</v>
+        <v>2955000</v>
       </c>
       <c r="AA123" t="n">
-        <v>-5619</v>
+        <v>-47069</v>
       </c>
       <c r="AB123" t="n">
-        <v>-6619</v>
+        <v>-84171</v>
       </c>
       <c r="AC123" t="n">
-        <v>-10619</v>
+        <v>-78212</v>
       </c>
       <c r="AD123" t="n">
-        <v>-9385</v>
+        <v>-496837</v>
       </c>
       <c r="AE123" t="n">
         <v>-10</v>
@@ -21829,24 +21829,24 @@
         <v>0</v>
       </c>
       <c r="AJ123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AL123" t="n">
         <v>-12</v>
       </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AL123" t="n">
-        <v>2</v>
-      </c>
       <c r="AM123" t="n">
-        <v>16.67</v>
+        <v>-600</v>
       </c>
       <c r="AN123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR123" t="inlineStr">
@@ -21875,24 +21875,24 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>法人連續偏買、投信買外資賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2351.TW</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>順德</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -21911,28 +21911,28 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>195.5</v>
+        <v>203.5</v>
       </c>
       <c r="G124" t="n">
-        <v>203.1</v>
+        <v>212.1</v>
       </c>
       <c r="H124" t="n">
-        <v>208.95</v>
+        <v>225.1</v>
       </c>
       <c r="I124" t="n">
-        <v>216.1</v>
+        <v>222.25</v>
       </c>
       <c r="J124" t="n">
-        <v>1830315</v>
+        <v>1497000</v>
       </c>
       <c r="K124" t="n">
-        <v>2479494</v>
+        <v>2580000</v>
       </c>
       <c r="L124" t="n">
-        <v>243.5</v>
+        <v>256</v>
       </c>
       <c r="M124" t="n">
-        <v>193.5</v>
+        <v>194</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
@@ -21940,70 +21940,70 @@
         </is>
       </c>
       <c r="O124" t="n">
-        <v>-38182</v>
+        <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>750637</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>748019</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>1213321</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>8887</v>
+        <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>-734192</v>
+        <v>0</v>
       </c>
       <c r="U124" t="n">
-        <v>-2113769</v>
+        <v>0</v>
       </c>
       <c r="V124" t="n">
-        <v>-1244842</v>
+        <v>0</v>
       </c>
       <c r="W124" t="n">
         <v>0</v>
       </c>
       <c r="X124" t="n">
-        <v>1569000</v>
+        <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>2940000</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>2955000</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>-47069</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>-84171</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>-78212</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>-496837</v>
+        <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="AF124" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="AG124" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="AH124" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
       </c>
       <c r="AJ124" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
@@ -22011,10 +22011,10 @@
         </is>
       </c>
       <c r="AL124" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AM124" t="n">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="AN124" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
@@ -22044,29 +22044,29 @@
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5530.TWO</t>
+          <t>3081.TWO</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>龍巖</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -22085,28 +22085,28 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>47.95</v>
+        <v>2490</v>
       </c>
       <c r="G125" t="n">
-        <v>48.17</v>
+        <v>2625</v>
       </c>
       <c r="H125" t="n">
-        <v>48.16</v>
+        <v>2789.5</v>
       </c>
       <c r="I125" t="n">
-        <v>48.48</v>
+        <v>2789.25</v>
       </c>
       <c r="J125" t="n">
-        <v>127000</v>
+        <v>2252000</v>
       </c>
       <c r="K125" t="n">
-        <v>166400</v>
+        <v>3285000</v>
       </c>
       <c r="L125" t="n">
-        <v>50.1</v>
+        <v>3210</v>
       </c>
       <c r="M125" t="n">
-        <v>47.7</v>
+        <v>2385</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>0</v>
       </c>
       <c r="AJ125" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
@@ -22185,10 +22185,10 @@
         </is>
       </c>
       <c r="AL125" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM125" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="AN125" t="n">
         <v>0</v>
@@ -22203,7 +22203,7 @@
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
@@ -22409,12 +22409,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3081.TWO</t>
+          <t>5530.TWO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>龍巖</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -22433,28 +22433,28 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>2490</v>
+        <v>47.95</v>
       </c>
       <c r="G127" t="n">
-        <v>2625</v>
+        <v>48.17</v>
       </c>
       <c r="H127" t="n">
-        <v>2789.5</v>
+        <v>48.16</v>
       </c>
       <c r="I127" t="n">
-        <v>2789.25</v>
+        <v>48.48</v>
       </c>
       <c r="J127" t="n">
-        <v>2252000</v>
+        <v>127000</v>
       </c>
       <c r="K127" t="n">
-        <v>3285000</v>
+        <v>166400</v>
       </c>
       <c r="L127" t="n">
-        <v>3210</v>
+        <v>50.1</v>
       </c>
       <c r="M127" t="n">
-        <v>2385</v>
+        <v>47.7</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>0</v>
       </c>
       <c r="AJ127" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
@@ -22533,10 +22533,10 @@
         </is>
       </c>
       <c r="AL127" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AM127" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="AN127" t="n">
         <v>0</v>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
@@ -22583,12 +22583,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>2612.TW</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>中航</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -22607,28 +22607,28 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>203.5</v>
+        <v>59.8</v>
       </c>
       <c r="G128" t="n">
-        <v>212.1</v>
+        <v>60.78</v>
       </c>
       <c r="H128" t="n">
-        <v>225.1</v>
+        <v>61.66</v>
       </c>
       <c r="I128" t="n">
-        <v>222.25</v>
+        <v>61.94</v>
       </c>
       <c r="J128" t="n">
-        <v>1497000</v>
+        <v>206950</v>
       </c>
       <c r="K128" t="n">
-        <v>2580000</v>
+        <v>350619</v>
       </c>
       <c r="L128" t="n">
-        <v>256</v>
+        <v>64.5</v>
       </c>
       <c r="M128" t="n">
-        <v>194</v>
+        <v>59.6</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -22636,28 +22636,28 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>-60000</v>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>43071</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>178913</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>812241</v>
       </c>
       <c r="S128" t="n">
-        <v>0</v>
+        <v>-60000</v>
       </c>
       <c r="T128" t="n">
-        <v>0</v>
+        <v>50062</v>
       </c>
       <c r="U128" t="n">
-        <v>0</v>
+        <v>172742</v>
       </c>
       <c r="V128" t="n">
-        <v>0</v>
+        <v>805227</v>
       </c>
       <c r="W128" t="n">
         <v>0</v>
@@ -22675,42 +22675,42 @@
         <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>-6991</v>
       </c>
       <c r="AC128" t="n">
-        <v>0</v>
+        <v>6171</v>
       </c>
       <c r="AD128" t="n">
-        <v>0</v>
+        <v>7014</v>
       </c>
       <c r="AE128" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AL128" t="n">
         <v>-12</v>
       </c>
-      <c r="AF128" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AG128" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AH128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ128" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AL128" t="n">
-        <v>0</v>
-      </c>
       <c r="AM128" t="n">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="AN128" t="n">
         <v>0</v>
@@ -22725,7 +22725,7 @@
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
@@ -22740,17 +22740,17 @@
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -22931,12 +22931,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2612.TW</t>
+          <t>4967.TW</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>中航</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -22955,28 +22955,28 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>59.8</v>
+        <v>248.5</v>
       </c>
       <c r="G130" t="n">
-        <v>60.78</v>
+        <v>256.2</v>
       </c>
       <c r="H130" t="n">
-        <v>61.66</v>
+        <v>261.5</v>
       </c>
       <c r="I130" t="n">
-        <v>61.94</v>
+        <v>267.32</v>
       </c>
       <c r="J130" t="n">
-        <v>206950</v>
+        <v>884108</v>
       </c>
       <c r="K130" t="n">
-        <v>350619</v>
+        <v>1402130</v>
       </c>
       <c r="L130" t="n">
-        <v>64.5</v>
+        <v>278.5</v>
       </c>
       <c r="M130" t="n">
-        <v>59.6</v>
+        <v>248</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -22984,52 +22984,52 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>-60000</v>
+        <v>-145313</v>
       </c>
       <c r="P130" t="n">
-        <v>43071</v>
+        <v>327412</v>
       </c>
       <c r="Q130" t="n">
-        <v>178913</v>
+        <v>175368</v>
       </c>
       <c r="R130" t="n">
-        <v>812241</v>
+        <v>-1986651</v>
       </c>
       <c r="S130" t="n">
-        <v>-60000</v>
+        <v>-123138</v>
       </c>
       <c r="T130" t="n">
-        <v>50062</v>
+        <v>324984</v>
       </c>
       <c r="U130" t="n">
-        <v>172742</v>
+        <v>182276</v>
       </c>
       <c r="V130" t="n">
-        <v>805227</v>
+        <v>-1881307</v>
       </c>
       <c r="W130" t="n">
         <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>-22175</v>
       </c>
       <c r="AB130" t="n">
-        <v>-6991</v>
+        <v>5428</v>
       </c>
       <c r="AC130" t="n">
-        <v>6171</v>
+        <v>-3908</v>
       </c>
       <c r="AD130" t="n">
-        <v>7014</v>
+        <v>-98344</v>
       </c>
       <c r="AE130" t="n">
         <v>-14</v>
@@ -23047,7 +23047,7 @@
         <v>0</v>
       </c>
       <c r="AJ130" t="n">
-        <v>-2</v>
+        <v>-28</v>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
@@ -23055,16 +23055,16 @@
         </is>
       </c>
       <c r="AL130" t="n">
-        <v>-12</v>
+        <v>14</v>
       </c>
       <c r="AM130" t="n">
-        <v>-600</v>
+        <v>50</v>
       </c>
       <c r="AN130" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO130" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
@@ -23093,24 +23093,24 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4967.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -23129,28 +23129,28 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>248.5</v>
+        <v>1395</v>
       </c>
       <c r="G131" t="n">
-        <v>256.2</v>
+        <v>1420</v>
       </c>
       <c r="H131" t="n">
-        <v>261.5</v>
+        <v>1469</v>
       </c>
       <c r="I131" t="n">
-        <v>267.32</v>
+        <v>1516.75</v>
       </c>
       <c r="J131" t="n">
-        <v>884108</v>
+        <v>3453000</v>
       </c>
       <c r="K131" t="n">
-        <v>1402130</v>
+        <v>2589800</v>
       </c>
       <c r="L131" t="n">
-        <v>278.5</v>
+        <v>1750</v>
       </c>
       <c r="M131" t="n">
-        <v>248</v>
+        <v>1320</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -23158,52 +23158,52 @@
         </is>
       </c>
       <c r="O131" t="n">
-        <v>-145313</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>327412</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>175368</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>-1986651</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>-123138</v>
+        <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>324984</v>
+        <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>182276</v>
+        <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>-1881307</v>
+        <v>0</v>
       </c>
       <c r="W131" t="n">
         <v>0</v>
       </c>
       <c r="X131" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>-22175</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>5428</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>-3908</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
-        <v>-98344</v>
+        <v>0</v>
       </c>
       <c r="AE131" t="n">
         <v>-14</v>
@@ -23212,16 +23212,16 @@
         <v>-14</v>
       </c>
       <c r="AG131" t="n">
-        <v>-55</v>
+        <v>-35</v>
       </c>
       <c r="AH131" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI131" t="n">
         <v>0</v>
       </c>
       <c r="AJ131" t="n">
-        <v>-28</v>
+        <v>-18</v>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
@@ -23229,16 +23229,16 @@
         </is>
       </c>
       <c r="AL131" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AM131" t="n">
-        <v>50</v>
+        <v>22.22</v>
       </c>
       <c r="AN131" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AO131" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
@@ -23262,29 +23262,29 @@
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>8039.TW</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -23303,28 +23303,28 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1395</v>
+        <v>296</v>
       </c>
       <c r="G132" t="n">
-        <v>1420</v>
+        <v>298.6</v>
       </c>
       <c r="H132" t="n">
-        <v>1469</v>
+        <v>297</v>
       </c>
       <c r="I132" t="n">
-        <v>1516.75</v>
+        <v>287.18</v>
       </c>
       <c r="J132" t="n">
-        <v>3453000</v>
+        <v>62451990</v>
       </c>
       <c r="K132" t="n">
-        <v>2589800</v>
+        <v>56580279</v>
       </c>
       <c r="L132" t="n">
-        <v>1750</v>
+        <v>331.5</v>
       </c>
       <c r="M132" t="n">
-        <v>1320</v>
+        <v>253</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
@@ -23332,70 +23332,70 @@
         </is>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>-2836415</v>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>-585025</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>-2318301</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>-2902383</v>
       </c>
       <c r="S132" t="n">
-        <v>0</v>
+        <v>-2428657</v>
       </c>
       <c r="T132" t="n">
-        <v>0</v>
+        <v>-476953</v>
       </c>
       <c r="U132" t="n">
-        <v>0</v>
+        <v>-1770600</v>
       </c>
       <c r="V132" t="n">
-        <v>0</v>
+        <v>-342152</v>
       </c>
       <c r="W132" t="n">
-        <v>0</v>
+        <v>5905</v>
       </c>
       <c r="X132" t="n">
-        <v>0</v>
+        <v>98905</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>122905</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>173905</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>-413663</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>-206977</v>
       </c>
       <c r="AC132" t="n">
-        <v>0</v>
+        <v>-670606</v>
       </c>
       <c r="AD132" t="n">
-        <v>0</v>
+        <v>-2734136</v>
       </c>
       <c r="AE132" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="AF132" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="AG132" t="n">
-        <v>-35</v>
+        <v>15</v>
       </c>
       <c r="AH132" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AI132" t="n">
         <v>0</v>
       </c>
       <c r="AJ132" t="n">
-        <v>-18</v>
+        <v>46</v>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
@@ -23403,16 +23403,16 @@
         </is>
       </c>
       <c r="AL132" t="n">
-        <v>4</v>
+        <v>-62</v>
       </c>
       <c r="AM132" t="n">
-        <v>22.22</v>
+        <v>-134.78</v>
       </c>
       <c r="AN132" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AO132" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
@@ -23436,29 +23436,29 @@
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8039.TW</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -23477,28 +23477,28 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>296</v>
+        <v>469.5</v>
       </c>
       <c r="G133" t="n">
-        <v>298.6</v>
+        <v>477.8</v>
       </c>
       <c r="H133" t="n">
-        <v>297</v>
+        <v>503.9</v>
       </c>
       <c r="I133" t="n">
-        <v>287.18</v>
+        <v>505.82</v>
       </c>
       <c r="J133" t="n">
-        <v>62451990</v>
+        <v>17008000</v>
       </c>
       <c r="K133" t="n">
-        <v>56580279</v>
+        <v>12048000</v>
       </c>
       <c r="L133" t="n">
-        <v>331.5</v>
+        <v>578</v>
       </c>
       <c r="M133" t="n">
-        <v>253</v>
+        <v>447.5</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -23506,70 +23506,70 @@
         </is>
       </c>
       <c r="O133" t="n">
-        <v>-2836415</v>
+        <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>-585025</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>-2318301</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>-2902383</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
-        <v>-2428657</v>
+        <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>-476953</v>
+        <v>0</v>
       </c>
       <c r="U133" t="n">
-        <v>-1770600</v>
+        <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>-342152</v>
+        <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>5905</v>
+        <v>0</v>
       </c>
       <c r="X133" t="n">
-        <v>98905</v>
+        <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>122905</v>
+        <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>173905</v>
+        <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>-413663</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>-206977</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
-        <v>-670606</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
-        <v>-2734136</v>
+        <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="AF133" t="n">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="AG133" t="n">
-        <v>15</v>
+        <v>-45</v>
       </c>
       <c r="AH133" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AI133" t="n">
         <v>0</v>
       </c>
       <c r="AJ133" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
@@ -23577,16 +23577,16 @@
         </is>
       </c>
       <c r="AL133" t="n">
-        <v>-62</v>
+        <v>-34</v>
       </c>
       <c r="AM133" t="n">
-        <v>-134.78</v>
+        <v>-212.5</v>
       </c>
       <c r="AN133" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO133" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
@@ -23610,17 +23610,17 @@
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -23801,12 +23801,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -23825,28 +23825,28 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>469.5</v>
+        <v>32.1</v>
       </c>
       <c r="G135" t="n">
-        <v>477.8</v>
+        <v>32.31</v>
       </c>
       <c r="H135" t="n">
-        <v>503.9</v>
+        <v>31.62</v>
       </c>
       <c r="I135" t="n">
-        <v>505.82</v>
+        <v>31.26</v>
       </c>
       <c r="J135" t="n">
-        <v>17008000</v>
+        <v>18761682</v>
       </c>
       <c r="K135" t="n">
-        <v>12048000</v>
+        <v>35523503</v>
       </c>
       <c r="L135" t="n">
-        <v>578</v>
+        <v>33.7</v>
       </c>
       <c r="M135" t="n">
-        <v>447.5</v>
+        <v>30.3</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
@@ -23854,70 +23854,70 @@
         </is>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>-188214</v>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>-12292955</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>-5881432</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>-10268619</v>
       </c>
       <c r="S135" t="n">
-        <v>0</v>
+        <v>-473231</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
+        <v>-13190536</v>
       </c>
       <c r="U135" t="n">
-        <v>0</v>
+        <v>-6974211</v>
       </c>
       <c r="V135" t="n">
-        <v>0</v>
+        <v>-11134492</v>
       </c>
       <c r="W135" t="n">
-        <v>0</v>
+        <v>-280</v>
       </c>
       <c r="X135" t="n">
-        <v>0</v>
+        <v>26720</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>76720</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>271720</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>285297</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>870861</v>
       </c>
       <c r="AC135" t="n">
-        <v>0</v>
+        <v>1016059</v>
       </c>
       <c r="AD135" t="n">
-        <v>0</v>
+        <v>594153</v>
       </c>
       <c r="AE135" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="AF135" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="AG135" t="n">
-        <v>-45</v>
+        <v>5</v>
       </c>
       <c r="AH135" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
       </c>
       <c r="AJ135" t="n">
-        <v>16</v>
+        <v>-16</v>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
@@ -23925,16 +23925,16 @@
         </is>
       </c>
       <c r="AL135" t="n">
-        <v>-34</v>
+        <v>-4</v>
       </c>
       <c r="AM135" t="n">
-        <v>-212.5</v>
+        <v>-25</v>
       </c>
       <c r="AN135" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO135" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
@@ -23958,17 +23958,17 @@
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -24149,17 +24149,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>0056.TW</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -24173,28 +24173,28 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>32.1</v>
+        <v>57.45</v>
       </c>
       <c r="G137" t="n">
-        <v>32.31</v>
+        <v>58.41</v>
       </c>
       <c r="H137" t="n">
-        <v>31.62</v>
+        <v>58.4</v>
       </c>
       <c r="I137" t="n">
-        <v>31.26</v>
+        <v>57.67</v>
       </c>
       <c r="J137" t="n">
-        <v>18761682</v>
+        <v>103958121</v>
       </c>
       <c r="K137" t="n">
-        <v>35523503</v>
+        <v>93849690</v>
       </c>
       <c r="L137" t="n">
-        <v>33.7</v>
+        <v>59.7</v>
       </c>
       <c r="M137" t="n">
-        <v>30.3</v>
+        <v>56</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
@@ -24202,52 +24202,52 @@
         </is>
       </c>
       <c r="O137" t="n">
-        <v>-188214</v>
+        <v>-87876972</v>
       </c>
       <c r="P137" t="n">
-        <v>-12292955</v>
+        <v>-208851747</v>
       </c>
       <c r="Q137" t="n">
-        <v>-5881432</v>
+        <v>-358574780</v>
       </c>
       <c r="R137" t="n">
-        <v>-10268619</v>
+        <v>-484202504</v>
       </c>
       <c r="S137" t="n">
-        <v>-473231</v>
+        <v>-12009743</v>
       </c>
       <c r="T137" t="n">
-        <v>-13190536</v>
+        <v>-25393600</v>
       </c>
       <c r="U137" t="n">
-        <v>-6974211</v>
+        <v>-41999624</v>
       </c>
       <c r="V137" t="n">
-        <v>-11134492</v>
+        <v>-62946897</v>
       </c>
       <c r="W137" t="n">
-        <v>-280</v>
+        <v>173000</v>
       </c>
       <c r="X137" t="n">
-        <v>26720</v>
+        <v>4708000</v>
       </c>
       <c r="Y137" t="n">
-        <v>76720</v>
+        <v>11183000</v>
       </c>
       <c r="Z137" t="n">
-        <v>271720</v>
+        <v>9285000</v>
       </c>
       <c r="AA137" t="n">
-        <v>285297</v>
+        <v>-76040229</v>
       </c>
       <c r="AB137" t="n">
-        <v>870861</v>
+        <v>-188166147</v>
       </c>
       <c r="AC137" t="n">
-        <v>1016059</v>
+        <v>-327758156</v>
       </c>
       <c r="AD137" t="n">
-        <v>594153</v>
+        <v>-430540607</v>
       </c>
       <c r="AE137" t="n">
         <v>-20</v>
@@ -24265,7 +24265,7 @@
         <v>0</v>
       </c>
       <c r="AJ137" t="n">
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
@@ -24273,16 +24273,16 @@
         </is>
       </c>
       <c r="AL137" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AM137" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="AN137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AO137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
@@ -24316,7 +24316,7 @@
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -24497,17 +24497,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0056.TW</t>
+          <t>5439.TWO</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -24521,28 +24521,28 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>57.45</v>
+        <v>220</v>
       </c>
       <c r="G139" t="n">
-        <v>58.41</v>
+        <v>231.6</v>
       </c>
       <c r="H139" t="n">
-        <v>58.4</v>
+        <v>243.65</v>
       </c>
       <c r="I139" t="n">
-        <v>57.67</v>
+        <v>248</v>
       </c>
       <c r="J139" t="n">
-        <v>103958121</v>
+        <v>1188000</v>
       </c>
       <c r="K139" t="n">
-        <v>93849690</v>
+        <v>1202600</v>
       </c>
       <c r="L139" t="n">
-        <v>59.7</v>
+        <v>270</v>
       </c>
       <c r="M139" t="n">
-        <v>56</v>
+        <v>219</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
@@ -24550,70 +24550,70 @@
         </is>
       </c>
       <c r="O139" t="n">
-        <v>-87876972</v>
+        <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>-208851747</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>-358574780</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>-484202504</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>-12009743</v>
+        <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>-25393600</v>
+        <v>0</v>
       </c>
       <c r="U139" t="n">
-        <v>-41999624</v>
+        <v>0</v>
       </c>
       <c r="V139" t="n">
-        <v>-62946897</v>
+        <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>173000</v>
+        <v>0</v>
       </c>
       <c r="X139" t="n">
-        <v>4708000</v>
+        <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>11183000</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="n">
-        <v>9285000</v>
+        <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>-76040229</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>-188166147</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
-        <v>-327758156</v>
+        <v>0</v>
       </c>
       <c r="AD139" t="n">
-        <v>-430540607</v>
+        <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="AF139" t="n">
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="AG139" t="n">
-        <v>5</v>
+        <v>-55</v>
       </c>
       <c r="AH139" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AI139" t="n">
         <v>0</v>
       </c>
       <c r="AJ139" t="n">
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
@@ -24627,10 +24627,10 @@
         <v>0</v>
       </c>
       <c r="AN139" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AO139" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR139" t="inlineStr">
@@ -24654,17 +24654,17 @@
       </c>
       <c r="AT139" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -25541,12 +25541,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>6275.TWO</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -25565,28 +25565,28 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>220</v>
+        <v>44.85</v>
       </c>
       <c r="G145" t="n">
-        <v>231.6</v>
+        <v>45.36</v>
       </c>
       <c r="H145" t="n">
-        <v>243.65</v>
+        <v>45.95</v>
       </c>
       <c r="I145" t="n">
-        <v>248</v>
+        <v>46.21</v>
       </c>
       <c r="J145" t="n">
-        <v>1188000</v>
+        <v>48000</v>
       </c>
       <c r="K145" t="n">
-        <v>1202600</v>
+        <v>83000</v>
       </c>
       <c r="L145" t="n">
-        <v>270</v>
+        <v>48.05</v>
       </c>
       <c r="M145" t="n">
-        <v>219</v>
+        <v>44.55</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>0</v>
       </c>
       <c r="AJ145" t="n">
-        <v>-22</v>
+        <v>-8</v>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
@@ -25665,10 +25665,10 @@
         </is>
       </c>
       <c r="AL145" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AM145" t="n">
-        <v>0</v>
+        <v>-175</v>
       </c>
       <c r="AN145" t="n">
         <v>0</v>
@@ -25683,7 +25683,7 @@
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
@@ -25889,12 +25889,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8299.TWO</t>
+          <t>4979.TWO</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -25913,28 +25913,28 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1845</v>
+        <v>470</v>
       </c>
       <c r="G147" t="n">
-        <v>1875</v>
+        <v>520</v>
       </c>
       <c r="H147" t="n">
-        <v>1960.5</v>
+        <v>542.9</v>
       </c>
       <c r="I147" t="n">
-        <v>2049.5</v>
+        <v>564.6</v>
       </c>
       <c r="J147" t="n">
-        <v>1546000</v>
+        <v>1489000</v>
       </c>
       <c r="K147" t="n">
-        <v>3007800</v>
+        <v>6623600</v>
       </c>
       <c r="L147" t="n">
-        <v>2350</v>
+        <v>650</v>
       </c>
       <c r="M147" t="n">
-        <v>1785</v>
+        <v>466</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
@@ -26063,12 +26063,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4979.TWO</t>
+          <t>8299.TWO</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -26087,28 +26087,28 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>470</v>
+        <v>1845</v>
       </c>
       <c r="G148" t="n">
-        <v>520</v>
+        <v>1875</v>
       </c>
       <c r="H148" t="n">
-        <v>542.9</v>
+        <v>1960.5</v>
       </c>
       <c r="I148" t="n">
-        <v>564.6</v>
+        <v>2049.5</v>
       </c>
       <c r="J148" t="n">
-        <v>1489000</v>
+        <v>1546000</v>
       </c>
       <c r="K148" t="n">
-        <v>6623600</v>
+        <v>3007800</v>
       </c>
       <c r="L148" t="n">
-        <v>650</v>
+        <v>2350</v>
       </c>
       <c r="M148" t="n">
-        <v>466</v>
+        <v>1785</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -1062,16 +1062,16 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1278216</v>
+        <v>1313216</v>
       </c>
       <c r="P4" t="n">
-        <v>1776282</v>
+        <v>1811282</v>
       </c>
       <c r="Q4" t="n">
-        <v>1880229</v>
+        <v>1915229</v>
       </c>
       <c r="R4" t="n">
-        <v>2441507</v>
+        <v>2476507</v>
       </c>
       <c r="S4" t="n">
         <v>1229305</v>
@@ -1086,16 +1086,16 @@
         <v>1812211</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="X4" t="n">
-        <v>9940</v>
+        <v>44940</v>
       </c>
       <c r="Y4" t="n">
-        <v>79940</v>
+        <v>114940</v>
       </c>
       <c r="Z4" t="n">
-        <v>114940</v>
+        <v>149940</v>
       </c>
       <c r="AA4" t="n">
         <v>48911</v>
@@ -3672,16 +3672,16 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>12986471</v>
+        <v>13084471</v>
       </c>
       <c r="P19" t="n">
-        <v>6009236</v>
+        <v>6107236</v>
       </c>
       <c r="Q19" t="n">
-        <v>32622433</v>
+        <v>32720433</v>
       </c>
       <c r="R19" t="n">
-        <v>74431376</v>
+        <v>74529376</v>
       </c>
       <c r="S19" t="n">
         <v>12382069</v>
@@ -3696,16 +3696,16 @@
         <v>37452092</v>
       </c>
       <c r="W19" t="n">
-        <v>-1119881</v>
+        <v>-1021881</v>
       </c>
       <c r="X19" t="n">
-        <v>-5703291</v>
+        <v>-5605291</v>
       </c>
       <c r="Y19" t="n">
-        <v>-7908113</v>
+        <v>-7810113</v>
       </c>
       <c r="Z19" t="n">
-        <v>13267338</v>
+        <v>13365338</v>
       </c>
       <c r="AA19" t="n">
         <v>1724283</v>
@@ -7150,16 +7150,16 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>14539025</v>
+        <v>14619025</v>
       </c>
       <c r="P39" t="n">
-        <v>30987280</v>
+        <v>31067280</v>
       </c>
       <c r="Q39" t="n">
-        <v>27323184</v>
+        <v>27403184</v>
       </c>
       <c r="R39" t="n">
-        <v>15339539</v>
+        <v>15419539</v>
       </c>
       <c r="S39" t="n">
         <v>15141742</v>
@@ -7174,16 +7174,16 @@
         <v>11358922</v>
       </c>
       <c r="W39" t="n">
-        <v>-1067995</v>
+        <v>-987995</v>
       </c>
       <c r="X39" t="n">
-        <v>-3140499</v>
+        <v>-3060499</v>
       </c>
       <c r="Y39" t="n">
-        <v>-2823505</v>
+        <v>-2743505</v>
       </c>
       <c r="Z39" t="n">
-        <v>-2761505</v>
+        <v>-2681505</v>
       </c>
       <c r="AA39" t="n">
         <v>465278</v>
@@ -10804,16 +10804,16 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>822499</v>
+        <v>890499</v>
       </c>
       <c r="P60" t="n">
-        <v>2779820</v>
+        <v>2847820</v>
       </c>
       <c r="Q60" t="n">
-        <v>7737149</v>
+        <v>7805149</v>
       </c>
       <c r="R60" t="n">
-        <v>42453000</v>
+        <v>42521000</v>
       </c>
       <c r="S60" t="n">
         <v>429577</v>
@@ -10828,16 +10828,16 @@
         <v>26193303</v>
       </c>
       <c r="W60" t="n">
-        <v>63990</v>
+        <v>131990</v>
       </c>
       <c r="X60" t="n">
-        <v>1520383</v>
+        <v>1588383</v>
       </c>
       <c r="Y60" t="n">
-        <v>6606263</v>
+        <v>6674263</v>
       </c>
       <c r="Z60" t="n">
-        <v>12639535</v>
+        <v>12707535</v>
       </c>
       <c r="AA60" t="n">
         <v>328932</v>
@@ -15449,12 +15449,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2707.TW</t>
+          <t>8070.TW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>晶華</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -15473,28 +15473,28 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>176.5</v>
+        <v>50.6</v>
       </c>
       <c r="G87" t="n">
-        <v>177.4</v>
+        <v>51.12</v>
       </c>
       <c r="H87" t="n">
-        <v>176.75</v>
+        <v>51.42</v>
       </c>
       <c r="I87" t="n">
-        <v>176.38</v>
+        <v>50.98</v>
       </c>
       <c r="J87" t="n">
-        <v>91345</v>
+        <v>935492</v>
       </c>
       <c r="K87" t="n">
-        <v>149422</v>
+        <v>1560200</v>
       </c>
       <c r="L87" t="n">
-        <v>179</v>
+        <v>53.9</v>
       </c>
       <c r="M87" t="n">
-        <v>174.5</v>
+        <v>47.8</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -15502,52 +15502,52 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>-18989</v>
+        <v>204862</v>
       </c>
       <c r="P87" t="n">
-        <v>-63088</v>
+        <v>-281885</v>
       </c>
       <c r="Q87" t="n">
-        <v>266684</v>
+        <v>893862</v>
       </c>
       <c r="R87" t="n">
-        <v>374932</v>
+        <v>1682960</v>
       </c>
       <c r="S87" t="n">
-        <v>-18973</v>
+        <v>209187</v>
       </c>
       <c r="T87" t="n">
-        <v>-58973</v>
+        <v>-249868</v>
       </c>
       <c r="U87" t="n">
-        <v>270799</v>
+        <v>885200</v>
       </c>
       <c r="V87" t="n">
-        <v>377234</v>
+        <v>256044</v>
       </c>
       <c r="W87" t="n">
         <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>-1000</v>
+        <v>34646</v>
       </c>
       <c r="Y87" t="n">
-        <v>-2000</v>
+        <v>53424</v>
       </c>
       <c r="Z87" t="n">
-        <v>-2000</v>
+        <v>1389441</v>
       </c>
       <c r="AA87" t="n">
-        <v>-16</v>
+        <v>-4325</v>
       </c>
       <c r="AB87" t="n">
-        <v>-3115</v>
+        <v>-66663</v>
       </c>
       <c r="AC87" t="n">
-        <v>-2115</v>
+        <v>-44762</v>
       </c>
       <c r="AD87" t="n">
-        <v>-302</v>
+        <v>37475</v>
       </c>
       <c r="AE87" t="n">
         <v>12</v>
@@ -15556,16 +15556,16 @@
         <v>12</v>
       </c>
       <c r="AG87" t="n">
-        <v>10</v>
+        <v>-20</v>
       </c>
       <c r="AH87" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
       </c>
       <c r="AJ87" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
@@ -15573,16 +15573,16 @@
         </is>
       </c>
       <c r="AL87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AN87" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AO87" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -15606,17 +15606,17 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15797,12 +15797,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2610.TW</t>
+          <t>2707.TW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -15821,99 +15821,99 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>20.35</v>
+        <v>176.5</v>
       </c>
       <c r="G89" t="n">
-        <v>20.58</v>
+        <v>177.4</v>
       </c>
       <c r="H89" t="n">
-        <v>20.49</v>
+        <v>176.75</v>
       </c>
       <c r="I89" t="n">
-        <v>20.39</v>
+        <v>176.38</v>
       </c>
       <c r="J89" t="n">
-        <v>12501711</v>
+        <v>91345</v>
       </c>
       <c r="K89" t="n">
-        <v>21779894</v>
+        <v>149422</v>
       </c>
       <c r="L89" t="n">
-        <v>21.2</v>
+        <v>179</v>
       </c>
       <c r="M89" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>-18989</v>
+      </c>
+      <c r="P89" t="n">
+        <v>-63088</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>266684</v>
+      </c>
+      <c r="R89" t="n">
+        <v>374932</v>
+      </c>
+      <c r="S89" t="n">
+        <v>-18973</v>
+      </c>
+      <c r="T89" t="n">
+        <v>-58973</v>
+      </c>
+      <c r="U89" t="n">
+        <v>270799</v>
+      </c>
+      <c r="V89" t="n">
+        <v>377234</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>-3115</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>-2115</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>-302</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH89" t="n">
         <v>20</v>
       </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>無明顯異常</t>
-        </is>
-      </c>
-      <c r="O89" t="n">
-        <v>-4881735</v>
-      </c>
-      <c r="P89" t="n">
-        <v>-15203625</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>24365037</v>
-      </c>
-      <c r="R89" t="n">
-        <v>52666211</v>
-      </c>
-      <c r="S89" t="n">
-        <v>-2445632</v>
-      </c>
-      <c r="T89" t="n">
-        <v>-5557888</v>
-      </c>
-      <c r="U89" t="n">
-        <v>28238799</v>
-      </c>
-      <c r="V89" t="n">
-        <v>53624099</v>
-      </c>
-      <c r="W89" t="n">
-        <v>-2007000</v>
-      </c>
-      <c r="X89" t="n">
-        <v>-8832180</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>-3412180</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>2484820</v>
-      </c>
-      <c r="AA89" t="n">
-        <v>-429103</v>
-      </c>
-      <c r="AB89" t="n">
-        <v>-813557</v>
-      </c>
-      <c r="AC89" t="n">
-        <v>-461582</v>
-      </c>
-      <c r="AD89" t="n">
-        <v>-3442708</v>
-      </c>
-      <c r="AE89" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF89" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG89" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AH89" t="n">
-        <v>30</v>
-      </c>
       <c r="AI89" t="n">
         <v>0</v>
       </c>
       <c r="AJ89" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
@@ -15927,10 +15927,10 @@
         <v>0</v>
       </c>
       <c r="AN89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AO89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
@@ -15954,17 +15954,17 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -16145,12 +16145,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2850.TW</t>
+          <t>2610.TW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>新產</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16169,28 +16169,28 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>165.5</v>
+        <v>20.35</v>
       </c>
       <c r="G91" t="n">
-        <v>167.5</v>
+        <v>20.58</v>
       </c>
       <c r="H91" t="n">
-        <v>166.65</v>
+        <v>20.49</v>
       </c>
       <c r="I91" t="n">
-        <v>163.03</v>
+        <v>20.39</v>
       </c>
       <c r="J91" t="n">
-        <v>179830</v>
+        <v>12501711</v>
       </c>
       <c r="K91" t="n">
-        <v>324949</v>
+        <v>21779894</v>
       </c>
       <c r="L91" t="n">
-        <v>174</v>
+        <v>21.2</v>
       </c>
       <c r="M91" t="n">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -16198,52 +16198,52 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>52062</v>
+        <v>-4881735</v>
       </c>
       <c r="P91" t="n">
-        <v>-130898</v>
+        <v>-15203625</v>
       </c>
       <c r="Q91" t="n">
-        <v>344002</v>
+        <v>24365037</v>
       </c>
       <c r="R91" t="n">
-        <v>951903</v>
+        <v>52666211</v>
       </c>
       <c r="S91" t="n">
-        <v>93062</v>
+        <v>-2445632</v>
       </c>
       <c r="T91" t="n">
-        <v>-72801</v>
+        <v>-5557888</v>
       </c>
       <c r="U91" t="n">
-        <v>423099</v>
+        <v>28238799</v>
       </c>
       <c r="V91" t="n">
-        <v>1038971</v>
+        <v>53624099</v>
       </c>
       <c r="W91" t="n">
-        <v>-41000</v>
+        <v>-2007000</v>
       </c>
       <c r="X91" t="n">
-        <v>-44097</v>
+        <v>-8832180</v>
       </c>
       <c r="Y91" t="n">
-        <v>-46097</v>
+        <v>-3412180</v>
       </c>
       <c r="Z91" t="n">
-        <v>-47097</v>
+        <v>2484820</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>-429103</v>
       </c>
       <c r="AB91" t="n">
-        <v>-14000</v>
+        <v>-813557</v>
       </c>
       <c r="AC91" t="n">
-        <v>-33000</v>
+        <v>-461582</v>
       </c>
       <c r="AD91" t="n">
-        <v>-39971</v>
+        <v>-3442708</v>
       </c>
       <c r="AE91" t="n">
         <v>10</v>
@@ -16252,16 +16252,16 @@
         <v>10</v>
       </c>
       <c r="AG91" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AH91" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
       </c>
       <c r="AJ91" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
@@ -16269,16 +16269,16 @@
         </is>
       </c>
       <c r="AL91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM91" t="n">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="AN91" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AO91" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
@@ -16302,29 +16302,29 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2014.TW</t>
+          <t>2850.TW</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>中鴻</t>
+          <t>新產</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -16343,28 +16343,28 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>16.95</v>
+        <v>165.5</v>
       </c>
       <c r="G92" t="n">
-        <v>16.98</v>
+        <v>167.5</v>
       </c>
       <c r="H92" t="n">
-        <v>16.98</v>
+        <v>166.65</v>
       </c>
       <c r="I92" t="n">
-        <v>16.93</v>
+        <v>163.03</v>
       </c>
       <c r="J92" t="n">
-        <v>1043780</v>
+        <v>179830</v>
       </c>
       <c r="K92" t="n">
-        <v>1992288</v>
+        <v>324949</v>
       </c>
       <c r="L92" t="n">
-        <v>17.45</v>
+        <v>174</v>
       </c>
       <c r="M92" t="n">
-        <v>16.3</v>
+        <v>156</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -16372,52 +16372,52 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>-477540</v>
+        <v>52062</v>
       </c>
       <c r="P92" t="n">
-        <v>-639005</v>
+        <v>-130898</v>
       </c>
       <c r="Q92" t="n">
-        <v>647237</v>
+        <v>344002</v>
       </c>
       <c r="R92" t="n">
-        <v>3733000</v>
+        <v>951903</v>
       </c>
       <c r="S92" t="n">
-        <v>-477540</v>
+        <v>93062</v>
       </c>
       <c r="T92" t="n">
-        <v>-590146</v>
+        <v>-72801</v>
       </c>
       <c r="U92" t="n">
-        <v>719096</v>
+        <v>423099</v>
       </c>
       <c r="V92" t="n">
-        <v>3695859</v>
+        <v>1038971</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>-41000</v>
       </c>
       <c r="X92" t="n">
-        <v>-393</v>
+        <v>-44097</v>
       </c>
       <c r="Y92" t="n">
-        <v>-393</v>
+        <v>-46097</v>
       </c>
       <c r="Z92" t="n">
-        <v>-393</v>
+        <v>-47097</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>-48466</v>
+        <v>-14000</v>
       </c>
       <c r="AC92" t="n">
-        <v>-71466</v>
+        <v>-33000</v>
       </c>
       <c r="AD92" t="n">
-        <v>37534</v>
+        <v>-39971</v>
       </c>
       <c r="AE92" t="n">
         <v>10</v>
@@ -16426,16 +16426,16 @@
         <v>10</v>
       </c>
       <c r="AG92" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AH92" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
       </c>
       <c r="AJ92" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
@@ -16443,16 +16443,16 @@
         </is>
       </c>
       <c r="AL92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM92" t="n">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="AN92" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AO92" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
@@ -16476,29 +16476,29 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2498.TW</t>
+          <t>2014.TW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>中鴻</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -16517,28 +16517,28 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>40.55</v>
+        <v>16.95</v>
       </c>
       <c r="G93" t="n">
-        <v>40.12</v>
+        <v>16.98</v>
       </c>
       <c r="H93" t="n">
-        <v>40.77</v>
+        <v>16.98</v>
       </c>
       <c r="I93" t="n">
-        <v>41.38</v>
+        <v>16.93</v>
       </c>
       <c r="J93" t="n">
-        <v>3605951</v>
+        <v>1043780</v>
       </c>
       <c r="K93" t="n">
-        <v>3196298</v>
+        <v>1992288</v>
       </c>
       <c r="L93" t="n">
-        <v>46.85</v>
+        <v>17.45</v>
       </c>
       <c r="M93" t="n">
-        <v>39.6</v>
+        <v>16.3</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -16546,52 +16546,52 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>500301</v>
+        <v>-477540</v>
       </c>
       <c r="P93" t="n">
-        <v>816946</v>
+        <v>-639005</v>
       </c>
       <c r="Q93" t="n">
-        <v>134650</v>
+        <v>647237</v>
       </c>
       <c r="R93" t="n">
-        <v>1112638</v>
+        <v>3733000</v>
       </c>
       <c r="S93" t="n">
-        <v>-235368</v>
+        <v>-477540</v>
       </c>
       <c r="T93" t="n">
-        <v>-37979</v>
+        <v>-590146</v>
       </c>
       <c r="U93" t="n">
-        <v>-607249</v>
+        <v>719096</v>
       </c>
       <c r="V93" t="n">
-        <v>626312</v>
+        <v>3695859</v>
       </c>
       <c r="W93" t="n">
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>-211</v>
+        <v>-393</v>
       </c>
       <c r="Y93" t="n">
-        <v>-211</v>
+        <v>-393</v>
       </c>
       <c r="Z93" t="n">
-        <v>-15211</v>
+        <v>-393</v>
       </c>
       <c r="AA93" t="n">
-        <v>735669</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>855136</v>
+        <v>-48466</v>
       </c>
       <c r="AC93" t="n">
-        <v>742110</v>
+        <v>-71466</v>
       </c>
       <c r="AD93" t="n">
-        <v>501537</v>
+        <v>37534</v>
       </c>
       <c r="AE93" t="n">
         <v>10</v>
@@ -16609,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
@@ -16617,25 +16617,25 @@
         </is>
       </c>
       <c r="AL93" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AM93" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AN93" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AO93" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
@@ -16650,29 +16650,29 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步賣超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>2498.TW</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -16691,99 +16691,99 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>30.85</v>
+        <v>40.55</v>
       </c>
       <c r="G94" t="n">
-        <v>27.64</v>
+        <v>40.12</v>
       </c>
       <c r="H94" t="n">
-        <v>25.77</v>
+        <v>40.77</v>
       </c>
       <c r="I94" t="n">
-        <v>24.71</v>
+        <v>41.38</v>
       </c>
       <c r="J94" t="n">
-        <v>54240918</v>
+        <v>3605951</v>
       </c>
       <c r="K94" t="n">
-        <v>26703055</v>
+        <v>3196298</v>
       </c>
       <c r="L94" t="n">
-        <v>32</v>
+        <v>46.85</v>
       </c>
       <c r="M94" t="n">
-        <v>22.1</v>
+        <v>39.6</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>-4587227</v>
+        <v>500301</v>
       </c>
       <c r="P94" t="n">
-        <v>-5308745</v>
+        <v>816946</v>
       </c>
       <c r="Q94" t="n">
-        <v>-6472584</v>
+        <v>134650</v>
       </c>
       <c r="R94" t="n">
-        <v>-5082800</v>
+        <v>1112638</v>
       </c>
       <c r="S94" t="n">
-        <v>-4102008</v>
+        <v>-235368</v>
       </c>
       <c r="T94" t="n">
-        <v>-5729071</v>
+        <v>-37979</v>
       </c>
       <c r="U94" t="n">
-        <v>-6972544</v>
+        <v>-607249</v>
       </c>
       <c r="V94" t="n">
-        <v>-5548008</v>
+        <v>626312</v>
       </c>
       <c r="W94" t="n">
         <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>-211</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>-211</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>-15211</v>
       </c>
       <c r="AA94" t="n">
-        <v>-485219</v>
+        <v>735669</v>
       </c>
       <c r="AB94" t="n">
-        <v>420326</v>
+        <v>855136</v>
       </c>
       <c r="AC94" t="n">
-        <v>499960</v>
+        <v>742110</v>
       </c>
       <c r="AD94" t="n">
-        <v>465208</v>
+        <v>501537</v>
       </c>
       <c r="AE94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG94" t="n">
-        <v>65</v>
+        <v>-5</v>
       </c>
       <c r="AH94" t="n">
-        <v>-55</v>
+        <v>30</v>
       </c>
       <c r="AI94" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AJ94" t="n">
-        <v>19</v>
+        <v>-2</v>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
@@ -16791,25 +16791,25 @@
         </is>
       </c>
       <c r="AL94" t="n">
-        <v>-10</v>
+        <v>12</v>
       </c>
       <c r="AM94" t="n">
-        <v>-52.63</v>
+        <v>600</v>
       </c>
       <c r="AN94" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="AO94" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>DT尚未轉強、離5MA偏遠、均線多頭排列、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
@@ -16824,29 +16824,29 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8070.TW</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -16865,99 +16865,99 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>50.6</v>
+        <v>30.85</v>
       </c>
       <c r="G95" t="n">
-        <v>51.12</v>
+        <v>27.64</v>
       </c>
       <c r="H95" t="n">
-        <v>51.42</v>
+        <v>25.77</v>
       </c>
       <c r="I95" t="n">
-        <v>50.84</v>
+        <v>24.71</v>
       </c>
       <c r="J95" t="n">
-        <v>935492</v>
+        <v>54240918</v>
       </c>
       <c r="K95" t="n">
-        <v>1560200</v>
+        <v>26703055</v>
       </c>
       <c r="L95" t="n">
-        <v>53.7</v>
+        <v>32</v>
       </c>
       <c r="M95" t="n">
-        <v>48.75</v>
+        <v>22.1</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>204862</v>
+        <v>-4587227</v>
       </c>
       <c r="P95" t="n">
-        <v>-281885</v>
+        <v>-5308745</v>
       </c>
       <c r="Q95" t="n">
-        <v>893862</v>
+        <v>-6472584</v>
       </c>
       <c r="R95" t="n">
-        <v>1682960</v>
+        <v>-5082800</v>
       </c>
       <c r="S95" t="n">
-        <v>209187</v>
+        <v>-4102008</v>
       </c>
       <c r="T95" t="n">
-        <v>-249868</v>
+        <v>-5729071</v>
       </c>
       <c r="U95" t="n">
-        <v>885200</v>
+        <v>-6972544</v>
       </c>
       <c r="V95" t="n">
-        <v>256044</v>
+        <v>-5548008</v>
       </c>
       <c r="W95" t="n">
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>34646</v>
+        <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>53424</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1389441</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>-4325</v>
+        <v>-485219</v>
       </c>
       <c r="AB95" t="n">
-        <v>-66663</v>
+        <v>420326</v>
       </c>
       <c r="AC95" t="n">
-        <v>-44762</v>
+        <v>499960</v>
       </c>
       <c r="AD95" t="n">
-        <v>37475</v>
+        <v>465208</v>
       </c>
       <c r="AE95" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF95" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG95" t="n">
-        <v>-30</v>
+        <v>65</v>
       </c>
       <c r="AH95" t="n">
-        <v>50</v>
+        <v>-55</v>
       </c>
       <c r="AI95" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AJ95" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
@@ -16965,16 +16965,16 @@
         </is>
       </c>
       <c r="AL95" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AM95" t="n">
-        <v>0</v>
+        <v>-52.63</v>
       </c>
       <c r="AN95" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO95" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA</t>
+          <t>DT尚未轉強、離5MA偏遠、均線多頭排列、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
@@ -16998,17 +16998,17 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -22636,16 +22636,16 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>11599233</v>
+        <v>11574233</v>
       </c>
       <c r="P128" t="n">
-        <v>1690941</v>
+        <v>1665941</v>
       </c>
       <c r="Q128" t="n">
-        <v>-5419724</v>
+        <v>-5444724</v>
       </c>
       <c r="R128" t="n">
-        <v>-45239215</v>
+        <v>-45264215</v>
       </c>
       <c r="S128" t="n">
         <v>11726206</v>
@@ -22660,16 +22660,16 @@
         <v>-28706613</v>
       </c>
       <c r="W128" t="n">
-        <v>-1987145</v>
+        <v>-2012145</v>
       </c>
       <c r="X128" t="n">
-        <v>-4268778</v>
+        <v>-4293778</v>
       </c>
       <c r="Y128" t="n">
-        <v>-4170975</v>
+        <v>-4195975</v>
       </c>
       <c r="Z128" t="n">
-        <v>-15779916</v>
+        <v>-15804916</v>
       </c>
       <c r="AA128" t="n">
         <v>1860172</v>
@@ -24898,16 +24898,16 @@
         </is>
       </c>
       <c r="O141" t="n">
-        <v>4065596</v>
+        <v>4040596</v>
       </c>
       <c r="P141" t="n">
-        <v>-5990432</v>
+        <v>-6015432</v>
       </c>
       <c r="Q141" t="n">
-        <v>-36845906</v>
+        <v>-36870906</v>
       </c>
       <c r="R141" t="n">
-        <v>-97756815</v>
+        <v>-97781815</v>
       </c>
       <c r="S141" t="n">
         <v>3814875</v>
@@ -24922,16 +24922,16 @@
         <v>-81533488</v>
       </c>
       <c r="W141" t="n">
-        <v>-940773</v>
+        <v>-965773</v>
       </c>
       <c r="X141" t="n">
-        <v>-1928347</v>
+        <v>-1953347</v>
       </c>
       <c r="Y141" t="n">
-        <v>-11428031</v>
+        <v>-11453031</v>
       </c>
       <c r="Z141" t="n">
-        <v>-15318477</v>
+        <v>-15343477</v>
       </c>
       <c r="AA141" t="n">
         <v>1191494</v>
@@ -29770,16 +29770,16 @@
         </is>
       </c>
       <c r="O169" t="n">
-        <v>-15737845</v>
+        <v>-15727845</v>
       </c>
       <c r="P169" t="n">
-        <v>-13937354</v>
+        <v>-13927354</v>
       </c>
       <c r="Q169" t="n">
-        <v>-6589984</v>
+        <v>-6579984</v>
       </c>
       <c r="R169" t="n">
-        <v>136993</v>
+        <v>146993</v>
       </c>
       <c r="S169" t="n">
         <v>-15445427</v>
@@ -29794,16 +29794,16 @@
         <v>-6843213</v>
       </c>
       <c r="W169" t="n">
-        <v>113036</v>
+        <v>123036</v>
       </c>
       <c r="X169" t="n">
-        <v>2090693</v>
+        <v>2100693</v>
       </c>
       <c r="Y169" t="n">
-        <v>3586901</v>
+        <v>3596901</v>
       </c>
       <c r="Z169" t="n">
-        <v>8919901</v>
+        <v>8929901</v>
       </c>
       <c r="AA169" t="n">
         <v>-405454</v>
@@ -32902,16 +32902,16 @@
         </is>
       </c>
       <c r="O187" t="n">
-        <v>-635357</v>
+        <v>-562357</v>
       </c>
       <c r="P187" t="n">
-        <v>-860312</v>
+        <v>-787312</v>
       </c>
       <c r="Q187" t="n">
-        <v>-3221787</v>
+        <v>-3148787</v>
       </c>
       <c r="R187" t="n">
-        <v>-5000661</v>
+        <v>-4927661</v>
       </c>
       <c r="S187" t="n">
         <v>-170456</v>
@@ -32926,16 +32926,16 @@
         <v>5379123</v>
       </c>
       <c r="W187" t="n">
-        <v>-194545</v>
+        <v>-121545</v>
       </c>
       <c r="X187" t="n">
-        <v>-1734792</v>
+        <v>-1661792</v>
       </c>
       <c r="Y187" t="n">
-        <v>-8355371</v>
+        <v>-8282371</v>
       </c>
       <c r="Z187" t="n">
-        <v>-10058650</v>
+        <v>-9985650</v>
       </c>
       <c r="AA187" t="n">
         <v>-270356</v>
@@ -33076,16 +33076,16 @@
         </is>
       </c>
       <c r="O188" t="n">
-        <v>-5814019</v>
+        <v>-5804019</v>
       </c>
       <c r="P188" t="n">
-        <v>-18781762</v>
+        <v>-18771762</v>
       </c>
       <c r="Q188" t="n">
-        <v>-64614076</v>
+        <v>-64604076</v>
       </c>
       <c r="R188" t="n">
-        <v>-109287560</v>
+        <v>-109277560</v>
       </c>
       <c r="S188" t="n">
         <v>-6153898</v>
@@ -33100,16 +33100,16 @@
         <v>-136793367</v>
       </c>
       <c r="W188" t="n">
-        <v>1387512</v>
+        <v>1397512</v>
       </c>
       <c r="X188" t="n">
-        <v>6301759</v>
+        <v>6311759</v>
       </c>
       <c r="Y188" t="n">
-        <v>10246999</v>
+        <v>10256999</v>
       </c>
       <c r="Z188" t="n">
-        <v>15500678</v>
+        <v>15510678</v>
       </c>
       <c r="AA188" t="n">
         <v>-1047633</v>
@@ -33610,16 +33610,16 @@
         <v>-26040390</v>
       </c>
       <c r="S191" t="n">
-        <v>-1185605</v>
+        <v>-1161605</v>
       </c>
       <c r="T191" t="n">
-        <v>-3904427</v>
+        <v>-3880427</v>
       </c>
       <c r="U191" t="n">
-        <v>-12411175</v>
+        <v>-12387175</v>
       </c>
       <c r="V191" t="n">
-        <v>-26830874</v>
+        <v>-26806874</v>
       </c>
       <c r="W191" t="n">
         <v>167225</v>
@@ -33634,16 +33634,16 @@
         <v>1585720</v>
       </c>
       <c r="AA191" t="n">
-        <v>-627508</v>
+        <v>-651508</v>
       </c>
       <c r="AB191" t="n">
-        <v>-939383</v>
+        <v>-963383</v>
       </c>
       <c r="AC191" t="n">
-        <v>-858998</v>
+        <v>-882998</v>
       </c>
       <c r="AD191" t="n">
-        <v>-795236</v>
+        <v>-819236</v>
       </c>
       <c r="AE191" t="n">
         <v>-44</v>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -15449,12 +15449,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8070.TW</t>
+          <t>2707.TW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -15473,28 +15473,28 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>50.6</v>
+        <v>176.5</v>
       </c>
       <c r="G87" t="n">
-        <v>51.12</v>
+        <v>177.4</v>
       </c>
       <c r="H87" t="n">
-        <v>51.42</v>
+        <v>176.75</v>
       </c>
       <c r="I87" t="n">
-        <v>50.98</v>
+        <v>176.38</v>
       </c>
       <c r="J87" t="n">
-        <v>935492</v>
+        <v>91345</v>
       </c>
       <c r="K87" t="n">
-        <v>1560200</v>
+        <v>149422</v>
       </c>
       <c r="L87" t="n">
-        <v>53.9</v>
+        <v>179</v>
       </c>
       <c r="M87" t="n">
-        <v>47.8</v>
+        <v>174.5</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -15502,52 +15502,52 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>204862</v>
+        <v>-18989</v>
       </c>
       <c r="P87" t="n">
-        <v>-281885</v>
+        <v>-63088</v>
       </c>
       <c r="Q87" t="n">
-        <v>893862</v>
+        <v>266684</v>
       </c>
       <c r="R87" t="n">
-        <v>1682960</v>
+        <v>374932</v>
       </c>
       <c r="S87" t="n">
-        <v>209187</v>
+        <v>-18973</v>
       </c>
       <c r="T87" t="n">
-        <v>-249868</v>
+        <v>-58973</v>
       </c>
       <c r="U87" t="n">
-        <v>885200</v>
+        <v>270799</v>
       </c>
       <c r="V87" t="n">
-        <v>256044</v>
+        <v>377234</v>
       </c>
       <c r="W87" t="n">
         <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>34646</v>
+        <v>-1000</v>
       </c>
       <c r="Y87" t="n">
-        <v>53424</v>
+        <v>-2000</v>
       </c>
       <c r="Z87" t="n">
-        <v>1389441</v>
+        <v>-2000</v>
       </c>
       <c r="AA87" t="n">
-        <v>-4325</v>
+        <v>-16</v>
       </c>
       <c r="AB87" t="n">
-        <v>-66663</v>
+        <v>-3115</v>
       </c>
       <c r="AC87" t="n">
-        <v>-44762</v>
+        <v>-2115</v>
       </c>
       <c r="AD87" t="n">
-        <v>37475</v>
+        <v>-302</v>
       </c>
       <c r="AE87" t="n">
         <v>12</v>
@@ -15556,16 +15556,16 @@
         <v>12</v>
       </c>
       <c r="AG87" t="n">
-        <v>-20</v>
+        <v>10</v>
       </c>
       <c r="AH87" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
       </c>
       <c r="AJ87" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
@@ -15573,16 +15573,16 @@
         </is>
       </c>
       <c r="AL87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM87" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AN87" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AO87" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -15606,17 +15606,17 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15797,12 +15797,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2707.TW</t>
+          <t>2610.TW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>晶華</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -15821,28 +15821,28 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>176.5</v>
+        <v>20.35</v>
       </c>
       <c r="G89" t="n">
-        <v>177.4</v>
+        <v>20.58</v>
       </c>
       <c r="H89" t="n">
-        <v>176.75</v>
+        <v>20.49</v>
       </c>
       <c r="I89" t="n">
-        <v>176.38</v>
+        <v>20.39</v>
       </c>
       <c r="J89" t="n">
-        <v>91345</v>
+        <v>12501711</v>
       </c>
       <c r="K89" t="n">
-        <v>149422</v>
+        <v>21779894</v>
       </c>
       <c r="L89" t="n">
-        <v>179</v>
+        <v>21.2</v>
       </c>
       <c r="M89" t="n">
-        <v>174.5</v>
+        <v>20</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -15850,71 +15850,71 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>-18989</v>
+        <v>-4881735</v>
       </c>
       <c r="P89" t="n">
-        <v>-63088</v>
+        <v>-15203625</v>
       </c>
       <c r="Q89" t="n">
-        <v>266684</v>
+        <v>24365037</v>
       </c>
       <c r="R89" t="n">
-        <v>374932</v>
+        <v>52666211</v>
       </c>
       <c r="S89" t="n">
-        <v>-18973</v>
+        <v>-2445632</v>
       </c>
       <c r="T89" t="n">
-        <v>-58973</v>
+        <v>-5557888</v>
       </c>
       <c r="U89" t="n">
-        <v>270799</v>
+        <v>28238799</v>
       </c>
       <c r="V89" t="n">
-        <v>377234</v>
+        <v>53624099</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>-2007000</v>
       </c>
       <c r="X89" t="n">
-        <v>-1000</v>
+        <v>-8832180</v>
       </c>
       <c r="Y89" t="n">
-        <v>-2000</v>
+        <v>-3412180</v>
       </c>
       <c r="Z89" t="n">
-        <v>-2000</v>
+        <v>2484820</v>
       </c>
       <c r="AA89" t="n">
-        <v>-16</v>
+        <v>-429103</v>
       </c>
       <c r="AB89" t="n">
-        <v>-3115</v>
+        <v>-813557</v>
       </c>
       <c r="AC89" t="n">
-        <v>-2115</v>
+        <v>-461582</v>
       </c>
       <c r="AD89" t="n">
-        <v>-302</v>
+        <v>-3442708</v>
       </c>
       <c r="AE89" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF89" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG89" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ89" t="n">
         <v>10</v>
       </c>
-      <c r="AH89" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ89" t="n">
-        <v>12</v>
-      </c>
       <c r="AK89" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -15927,10 +15927,10 @@
         <v>0</v>
       </c>
       <c r="AN89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AO89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
@@ -15954,17 +15954,17 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -16145,12 +16145,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2610.TW</t>
+          <t>2850.TW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>新產</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16169,28 +16169,28 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>20.35</v>
+        <v>165.5</v>
       </c>
       <c r="G91" t="n">
-        <v>20.58</v>
+        <v>167.5</v>
       </c>
       <c r="H91" t="n">
-        <v>20.49</v>
+        <v>166.65</v>
       </c>
       <c r="I91" t="n">
-        <v>20.39</v>
+        <v>163.03</v>
       </c>
       <c r="J91" t="n">
-        <v>12501711</v>
+        <v>179830</v>
       </c>
       <c r="K91" t="n">
-        <v>21779894</v>
+        <v>324949</v>
       </c>
       <c r="L91" t="n">
-        <v>21.2</v>
+        <v>174</v>
       </c>
       <c r="M91" t="n">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -16198,52 +16198,52 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>-4881735</v>
+        <v>52062</v>
       </c>
       <c r="P91" t="n">
-        <v>-15203625</v>
+        <v>-130898</v>
       </c>
       <c r="Q91" t="n">
-        <v>24365037</v>
+        <v>344002</v>
       </c>
       <c r="R91" t="n">
-        <v>52666211</v>
+        <v>951903</v>
       </c>
       <c r="S91" t="n">
-        <v>-2445632</v>
+        <v>93062</v>
       </c>
       <c r="T91" t="n">
-        <v>-5557888</v>
+        <v>-72801</v>
       </c>
       <c r="U91" t="n">
-        <v>28238799</v>
+        <v>423099</v>
       </c>
       <c r="V91" t="n">
-        <v>53624099</v>
+        <v>1038971</v>
       </c>
       <c r="W91" t="n">
-        <v>-2007000</v>
+        <v>-41000</v>
       </c>
       <c r="X91" t="n">
-        <v>-8832180</v>
+        <v>-44097</v>
       </c>
       <c r="Y91" t="n">
-        <v>-3412180</v>
+        <v>-46097</v>
       </c>
       <c r="Z91" t="n">
-        <v>2484820</v>
+        <v>-47097</v>
       </c>
       <c r="AA91" t="n">
-        <v>-429103</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>-813557</v>
+        <v>-14000</v>
       </c>
       <c r="AC91" t="n">
-        <v>-461582</v>
+        <v>-33000</v>
       </c>
       <c r="AD91" t="n">
-        <v>-3442708</v>
+        <v>-39971</v>
       </c>
       <c r="AE91" t="n">
         <v>10</v>
@@ -16252,16 +16252,16 @@
         <v>10</v>
       </c>
       <c r="AG91" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AH91" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
       </c>
       <c r="AJ91" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
@@ -16269,16 +16269,16 @@
         </is>
       </c>
       <c r="AL91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM91" t="n">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="AN91" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AO91" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
@@ -16302,29 +16302,29 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2850.TW</t>
+          <t>2014.TW</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>新產</t>
+          <t>中鴻</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -16343,28 +16343,28 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>165.5</v>
+        <v>16.95</v>
       </c>
       <c r="G92" t="n">
-        <v>167.5</v>
+        <v>16.98</v>
       </c>
       <c r="H92" t="n">
-        <v>166.65</v>
+        <v>16.98</v>
       </c>
       <c r="I92" t="n">
-        <v>163.03</v>
+        <v>16.93</v>
       </c>
       <c r="J92" t="n">
-        <v>179830</v>
+        <v>1043780</v>
       </c>
       <c r="K92" t="n">
-        <v>324949</v>
+        <v>1992288</v>
       </c>
       <c r="L92" t="n">
-        <v>174</v>
+        <v>17.45</v>
       </c>
       <c r="M92" t="n">
-        <v>156</v>
+        <v>16.3</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -16372,52 +16372,52 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>52062</v>
+        <v>-477540</v>
       </c>
       <c r="P92" t="n">
-        <v>-130898</v>
+        <v>-639005</v>
       </c>
       <c r="Q92" t="n">
-        <v>344002</v>
+        <v>647237</v>
       </c>
       <c r="R92" t="n">
-        <v>951903</v>
+        <v>3733000</v>
       </c>
       <c r="S92" t="n">
-        <v>93062</v>
+        <v>-477540</v>
       </c>
       <c r="T92" t="n">
-        <v>-72801</v>
+        <v>-590146</v>
       </c>
       <c r="U92" t="n">
-        <v>423099</v>
+        <v>719096</v>
       </c>
       <c r="V92" t="n">
-        <v>1038971</v>
+        <v>3695859</v>
       </c>
       <c r="W92" t="n">
-        <v>-41000</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>-44097</v>
+        <v>-393</v>
       </c>
       <c r="Y92" t="n">
-        <v>-46097</v>
+        <v>-393</v>
       </c>
       <c r="Z92" t="n">
-        <v>-47097</v>
+        <v>-393</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>-14000</v>
+        <v>-48466</v>
       </c>
       <c r="AC92" t="n">
-        <v>-33000</v>
+        <v>-71466</v>
       </c>
       <c r="AD92" t="n">
-        <v>-39971</v>
+        <v>37534</v>
       </c>
       <c r="AE92" t="n">
         <v>10</v>
@@ -16426,33 +16426,33 @@
         <v>10</v>
       </c>
       <c r="AG92" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AH92" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AL92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN92" t="n">
         <v>20</v>
       </c>
-      <c r="AI92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ92" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AL92" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM92" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="AN92" t="n">
-        <v>28</v>
-      </c>
       <c r="AO92" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
@@ -16476,29 +16476,29 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2014.TW</t>
+          <t>2498.TW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>中鴻</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -16517,28 +16517,28 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>16.95</v>
+        <v>40.55</v>
       </c>
       <c r="G93" t="n">
-        <v>16.98</v>
+        <v>40.12</v>
       </c>
       <c r="H93" t="n">
-        <v>16.98</v>
+        <v>40.77</v>
       </c>
       <c r="I93" t="n">
-        <v>16.93</v>
+        <v>41.38</v>
       </c>
       <c r="J93" t="n">
-        <v>1043780</v>
+        <v>3605951</v>
       </c>
       <c r="K93" t="n">
-        <v>1992288</v>
+        <v>3196298</v>
       </c>
       <c r="L93" t="n">
-        <v>17.45</v>
+        <v>46.85</v>
       </c>
       <c r="M93" t="n">
-        <v>16.3</v>
+        <v>39.6</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -16546,52 +16546,52 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>-477540</v>
+        <v>500301</v>
       </c>
       <c r="P93" t="n">
-        <v>-639005</v>
+        <v>816946</v>
       </c>
       <c r="Q93" t="n">
-        <v>647237</v>
+        <v>134650</v>
       </c>
       <c r="R93" t="n">
-        <v>3733000</v>
+        <v>1112638</v>
       </c>
       <c r="S93" t="n">
-        <v>-477540</v>
+        <v>-235368</v>
       </c>
       <c r="T93" t="n">
-        <v>-590146</v>
+        <v>-37979</v>
       </c>
       <c r="U93" t="n">
-        <v>719096</v>
+        <v>-607249</v>
       </c>
       <c r="V93" t="n">
-        <v>3695859</v>
+        <v>626312</v>
       </c>
       <c r="W93" t="n">
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>-393</v>
+        <v>-211</v>
       </c>
       <c r="Y93" t="n">
-        <v>-393</v>
+        <v>-211</v>
       </c>
       <c r="Z93" t="n">
-        <v>-393</v>
+        <v>-15211</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>735669</v>
       </c>
       <c r="AB93" t="n">
-        <v>-48466</v>
+        <v>855136</v>
       </c>
       <c r="AC93" t="n">
-        <v>-71466</v>
+        <v>742110</v>
       </c>
       <c r="AD93" t="n">
-        <v>37534</v>
+        <v>501537</v>
       </c>
       <c r="AE93" t="n">
         <v>10</v>
@@ -16609,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
@@ -16617,25 +16617,25 @@
         </is>
       </c>
       <c r="AL93" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AM93" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AN93" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AO93" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
@@ -16650,29 +16650,29 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2498.TW</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -16691,99 +16691,99 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>40.55</v>
+        <v>30.85</v>
       </c>
       <c r="G94" t="n">
-        <v>40.12</v>
+        <v>27.64</v>
       </c>
       <c r="H94" t="n">
-        <v>40.77</v>
+        <v>25.77</v>
       </c>
       <c r="I94" t="n">
-        <v>41.38</v>
+        <v>24.71</v>
       </c>
       <c r="J94" t="n">
-        <v>3605951</v>
+        <v>54240918</v>
       </c>
       <c r="K94" t="n">
-        <v>3196298</v>
+        <v>26703055</v>
       </c>
       <c r="L94" t="n">
-        <v>46.85</v>
+        <v>32</v>
       </c>
       <c r="M94" t="n">
-        <v>39.6</v>
+        <v>22.1</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>500301</v>
+        <v>-4587227</v>
       </c>
       <c r="P94" t="n">
-        <v>816946</v>
+        <v>-5308745</v>
       </c>
       <c r="Q94" t="n">
-        <v>134650</v>
+        <v>-6472584</v>
       </c>
       <c r="R94" t="n">
-        <v>1112638</v>
+        <v>-5082800</v>
       </c>
       <c r="S94" t="n">
-        <v>-235368</v>
+        <v>-4102008</v>
       </c>
       <c r="T94" t="n">
-        <v>-37979</v>
+        <v>-5729071</v>
       </c>
       <c r="U94" t="n">
-        <v>-607249</v>
+        <v>-6972544</v>
       </c>
       <c r="V94" t="n">
-        <v>626312</v>
+        <v>-5548008</v>
       </c>
       <c r="W94" t="n">
         <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>-211</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>-211</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>-15211</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>735669</v>
+        <v>-485219</v>
       </c>
       <c r="AB94" t="n">
-        <v>855136</v>
+        <v>420326</v>
       </c>
       <c r="AC94" t="n">
-        <v>742110</v>
+        <v>499960</v>
       </c>
       <c r="AD94" t="n">
-        <v>501537</v>
+        <v>465208</v>
       </c>
       <c r="AE94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG94" t="n">
-        <v>-5</v>
+        <v>65</v>
       </c>
       <c r="AH94" t="n">
-        <v>30</v>
+        <v>-55</v>
       </c>
       <c r="AI94" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AJ94" t="n">
-        <v>-2</v>
+        <v>19</v>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
@@ -16791,25 +16791,25 @@
         </is>
       </c>
       <c r="AL94" t="n">
-        <v>12</v>
+        <v>-10</v>
       </c>
       <c r="AM94" t="n">
-        <v>600</v>
+        <v>-52.63</v>
       </c>
       <c r="AN94" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="AO94" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、離5MA偏遠、均線多頭排列、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
@@ -16824,29 +16824,29 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>8070.TW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -16865,99 +16865,99 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>30.85</v>
+        <v>50.6</v>
       </c>
       <c r="G95" t="n">
-        <v>27.64</v>
+        <v>51.12</v>
       </c>
       <c r="H95" t="n">
-        <v>25.77</v>
+        <v>51.42</v>
       </c>
       <c r="I95" t="n">
-        <v>24.71</v>
+        <v>50.84</v>
       </c>
       <c r="J95" t="n">
-        <v>54240918</v>
+        <v>935492</v>
       </c>
       <c r="K95" t="n">
-        <v>26703055</v>
+        <v>1560200</v>
       </c>
       <c r="L95" t="n">
-        <v>32</v>
+        <v>53.7</v>
       </c>
       <c r="M95" t="n">
-        <v>22.1</v>
+        <v>48.75</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>-4587227</v>
+        <v>204862</v>
       </c>
       <c r="P95" t="n">
-        <v>-5308745</v>
+        <v>-281885</v>
       </c>
       <c r="Q95" t="n">
-        <v>-6472584</v>
+        <v>893862</v>
       </c>
       <c r="R95" t="n">
-        <v>-5082800</v>
+        <v>1682960</v>
       </c>
       <c r="S95" t="n">
-        <v>-4102008</v>
+        <v>209187</v>
       </c>
       <c r="T95" t="n">
-        <v>-5729071</v>
+        <v>-249868</v>
       </c>
       <c r="U95" t="n">
-        <v>-6972544</v>
+        <v>885200</v>
       </c>
       <c r="V95" t="n">
-        <v>-5548008</v>
+        <v>256044</v>
       </c>
       <c r="W95" t="n">
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>34646</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>53424</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1389441</v>
       </c>
       <c r="AA95" t="n">
-        <v>-485219</v>
+        <v>-4325</v>
       </c>
       <c r="AB95" t="n">
-        <v>420326</v>
+        <v>-66663</v>
       </c>
       <c r="AC95" t="n">
-        <v>499960</v>
+        <v>-44762</v>
       </c>
       <c r="AD95" t="n">
-        <v>465208</v>
+        <v>37475</v>
       </c>
       <c r="AE95" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF95" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG95" t="n">
-        <v>65</v>
+        <v>-30</v>
       </c>
       <c r="AH95" t="n">
-        <v>-55</v>
+        <v>50</v>
       </c>
       <c r="AI95" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AJ95" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
@@ -16965,16 +16965,16 @@
         </is>
       </c>
       <c r="AL95" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AM95" t="n">
-        <v>-52.63</v>
+        <v>0</v>
       </c>
       <c r="AN95" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AO95" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>DT尚未轉強、離5MA偏遠、均線多頭排列、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
@@ -16998,17 +16998,17 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2928862</v>
+        <v>2926862</v>
       </c>
       <c r="P41" t="n">
-        <v>4289387</v>
+        <v>4287387</v>
       </c>
       <c r="Q41" t="n">
-        <v>10806604</v>
+        <v>10804604</v>
       </c>
       <c r="R41" t="n">
-        <v>46085649</v>
+        <v>46083649</v>
       </c>
       <c r="S41" t="n">
         <v>2724762</v>
@@ -7514,16 +7514,16 @@
         <v>29594288</v>
       </c>
       <c r="W41" t="n">
-        <v>-537000</v>
+        <v>-539000</v>
       </c>
       <c r="X41" t="n">
-        <v>-966001</v>
+        <v>-968001</v>
       </c>
       <c r="Y41" t="n">
-        <v>4128973</v>
+        <v>4126973</v>
       </c>
       <c r="Z41" t="n">
-        <v>11981138</v>
+        <v>11979138</v>
       </c>
       <c r="AA41" t="n">
         <v>741100</v>
@@ -12710,16 +12710,16 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>-781968</v>
+        <v>-761968</v>
       </c>
       <c r="P71" t="n">
-        <v>1533173</v>
+        <v>1553173</v>
       </c>
       <c r="Q71" t="n">
-        <v>993723</v>
+        <v>1013723</v>
       </c>
       <c r="R71" t="n">
-        <v>1751903</v>
+        <v>1771903</v>
       </c>
       <c r="S71" t="n">
         <v>-563901</v>
@@ -12734,16 +12734,16 @@
         <v>1245010</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="X71" t="n">
-        <v>44940</v>
+        <v>64940</v>
       </c>
       <c r="Y71" t="n">
-        <v>89940</v>
+        <v>109940</v>
       </c>
       <c r="Z71" t="n">
-        <v>149940</v>
+        <v>169940</v>
       </c>
       <c r="AA71" t="n">
         <v>-218067</v>
@@ -13179,12 +13179,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6269.TW</t>
+          <t>5439.TWO</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -13203,28 +13203,28 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>78.7</v>
+        <v>254</v>
       </c>
       <c r="G74" t="n">
-        <v>83.18000000000001</v>
+        <v>253.3</v>
       </c>
       <c r="H74" t="n">
-        <v>74.73</v>
+        <v>247.8</v>
       </c>
       <c r="I74" t="n">
-        <v>69.90000000000001</v>
+        <v>254.18</v>
       </c>
       <c r="J74" t="n">
-        <v>83826860</v>
+        <v>2609000</v>
       </c>
       <c r="K74" t="n">
-        <v>93011683</v>
+        <v>1326000</v>
       </c>
       <c r="L74" t="n">
-        <v>93</v>
+        <v>280.5</v>
       </c>
       <c r="M74" t="n">
-        <v>60.3</v>
+        <v>237</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -13232,28 +13232,28 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>-1491851</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>-1612670</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>1679769</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2443765</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>-1582984</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>-2325211</v>
+        <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>1013186</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>1942528</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
         <v>0</v>
@@ -13268,16 +13268,16 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>91133</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>712541</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>666583</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>501237</v>
+        <v>0</v>
       </c>
       <c r="AE74" t="n">
         <v>14</v>
@@ -13286,42 +13286,42 @@
         <v>14</v>
       </c>
       <c r="AG74" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="AH74" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
       </c>
       <c r="AJ74" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AL74" t="n">
-        <v>-34</v>
+        <v>6</v>
       </c>
       <c r="AM74" t="n">
-        <v>-70.83</v>
+        <v>75</v>
       </c>
       <c r="AN74" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="AO74" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、量能偏強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
@@ -13336,17 +13336,17 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14049,12 +14049,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6191.TW</t>
+          <t>6269.TW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -14073,28 +14073,28 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>89.8</v>
+        <v>78.7</v>
       </c>
       <c r="G79" t="n">
-        <v>91.16</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="H79" t="n">
-        <v>91.90000000000001</v>
+        <v>74.73</v>
       </c>
       <c r="I79" t="n">
-        <v>88.23</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="J79" t="n">
-        <v>2757587</v>
+        <v>83826860</v>
       </c>
       <c r="K79" t="n">
-        <v>4388925</v>
+        <v>93011683</v>
       </c>
       <c r="L79" t="n">
-        <v>97.5</v>
+        <v>93</v>
       </c>
       <c r="M79" t="n">
-        <v>82.09999999999999</v>
+        <v>60.3</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -14102,70 +14102,70 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>-74047</v>
+        <v>-1491851</v>
       </c>
       <c r="P79" t="n">
-        <v>980186</v>
+        <v>-1612670</v>
       </c>
       <c r="Q79" t="n">
-        <v>1044806</v>
+        <v>1679769</v>
       </c>
       <c r="R79" t="n">
-        <v>-2269779</v>
+        <v>2443765</v>
       </c>
       <c r="S79" t="n">
-        <v>-8752</v>
+        <v>-1582984</v>
       </c>
       <c r="T79" t="n">
-        <v>945148</v>
+        <v>-2325211</v>
       </c>
       <c r="U79" t="n">
-        <v>755836</v>
+        <v>1013186</v>
       </c>
       <c r="V79" t="n">
-        <v>-2818002</v>
+        <v>1942528</v>
       </c>
       <c r="W79" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>22979</v>
+        <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>45979</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>100979</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>-70295</v>
+        <v>91133</v>
       </c>
       <c r="AB79" t="n">
-        <v>12059</v>
+        <v>712541</v>
       </c>
       <c r="AC79" t="n">
-        <v>242991</v>
+        <v>666583</v>
       </c>
       <c r="AD79" t="n">
-        <v>447244</v>
+        <v>501237</v>
       </c>
       <c r="AE79" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF79" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG79" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="AH79" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
       </c>
       <c r="AJ79" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
@@ -14173,16 +14173,16 @@
         </is>
       </c>
       <c r="AL79" t="n">
-        <v>-16</v>
+        <v>-34</v>
       </c>
       <c r="AM79" t="n">
-        <v>-57.14</v>
+        <v>-70.83</v>
       </c>
       <c r="AN79" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO79" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
@@ -14206,17 +14206,17 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14745,12 +14745,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4766.TW</t>
+          <t>6191.TW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -14769,28 +14769,28 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>357.5</v>
+        <v>89.8</v>
       </c>
       <c r="G83" t="n">
-        <v>358.8</v>
+        <v>91.16</v>
       </c>
       <c r="H83" t="n">
-        <v>359.1</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>352.73</v>
+        <v>88.23</v>
       </c>
       <c r="J83" t="n">
-        <v>162953</v>
+        <v>2757587</v>
       </c>
       <c r="K83" t="n">
-        <v>170422</v>
+        <v>4388925</v>
       </c>
       <c r="L83" t="n">
-        <v>369.5</v>
+        <v>97.5</v>
       </c>
       <c r="M83" t="n">
-        <v>339.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -14798,52 +14798,52 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>92938</v>
+        <v>-74047</v>
       </c>
       <c r="P83" t="n">
-        <v>167019</v>
+        <v>980186</v>
       </c>
       <c r="Q83" t="n">
-        <v>273654</v>
+        <v>1044806</v>
       </c>
       <c r="R83" t="n">
-        <v>871513</v>
+        <v>-2269779</v>
       </c>
       <c r="S83" t="n">
-        <v>93455</v>
+        <v>-8752</v>
       </c>
       <c r="T83" t="n">
-        <v>172180</v>
+        <v>945148</v>
       </c>
       <c r="U83" t="n">
-        <v>323515</v>
+        <v>755836</v>
       </c>
       <c r="V83" t="n">
-        <v>948417</v>
+        <v>-2818002</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X83" t="n">
-        <v>-23</v>
+        <v>22979</v>
       </c>
       <c r="Y83" t="n">
-        <v>-38023</v>
+        <v>45979</v>
       </c>
       <c r="Z83" t="n">
-        <v>-58023</v>
+        <v>100979</v>
       </c>
       <c r="AA83" t="n">
-        <v>-517</v>
+        <v>-70295</v>
       </c>
       <c r="AB83" t="n">
-        <v>-5138</v>
+        <v>12059</v>
       </c>
       <c r="AC83" t="n">
-        <v>-11838</v>
+        <v>242991</v>
       </c>
       <c r="AD83" t="n">
-        <v>-18881</v>
+        <v>447244</v>
       </c>
       <c r="AE83" t="n">
         <v>12</v>
@@ -14861,7 +14861,7 @@
         <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
@@ -14869,10 +14869,10 @@
         </is>
       </c>
       <c r="AL83" t="n">
-        <v>-26</v>
+        <v>-16</v>
       </c>
       <c r="AM83" t="n">
-        <v>-68.42</v>
+        <v>-57.14</v>
       </c>
       <c r="AN83" t="n">
         <v>0</v>
@@ -14907,24 +14907,24 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2610.TW</t>
+          <t>4766.TW</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -14943,28 +14943,28 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>20.5</v>
+        <v>357.5</v>
       </c>
       <c r="G84" t="n">
-        <v>20.57</v>
+        <v>358.8</v>
       </c>
       <c r="H84" t="n">
-        <v>20.51</v>
+        <v>359.1</v>
       </c>
       <c r="I84" t="n">
-        <v>20.41</v>
+        <v>352.73</v>
       </c>
       <c r="J84" t="n">
-        <v>13512197</v>
+        <v>162953</v>
       </c>
       <c r="K84" t="n">
-        <v>21072753</v>
+        <v>170422</v>
       </c>
       <c r="L84" t="n">
-        <v>21.2</v>
+        <v>369.5</v>
       </c>
       <c r="M84" t="n">
-        <v>20</v>
+        <v>339.5</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -14972,70 +14972,70 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>5716240</v>
+        <v>92938</v>
       </c>
       <c r="P84" t="n">
-        <v>-4550860</v>
+        <v>167019</v>
       </c>
       <c r="Q84" t="n">
-        <v>19188836</v>
+        <v>273654</v>
       </c>
       <c r="R84" t="n">
-        <v>54853461</v>
+        <v>871513</v>
       </c>
       <c r="S84" t="n">
-        <v>5578240</v>
+        <v>93455</v>
       </c>
       <c r="T84" t="n">
-        <v>325011</v>
+        <v>172180</v>
       </c>
       <c r="U84" t="n">
-        <v>22644039</v>
+        <v>323515</v>
       </c>
       <c r="V84" t="n">
-        <v>58141349</v>
+        <v>948417</v>
       </c>
       <c r="W84" t="n">
-        <v>167000</v>
+        <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>-4222180</v>
+        <v>-23</v>
       </c>
       <c r="Y84" t="n">
-        <v>-2847180</v>
+        <v>-38023</v>
       </c>
       <c r="Z84" t="n">
-        <v>115820</v>
+        <v>-58023</v>
       </c>
       <c r="AA84" t="n">
-        <v>-29000</v>
+        <v>-517</v>
       </c>
       <c r="AB84" t="n">
-        <v>-653691</v>
+        <v>-5138</v>
       </c>
       <c r="AC84" t="n">
-        <v>-608023</v>
+        <v>-11838</v>
       </c>
       <c r="AD84" t="n">
-        <v>-3403708</v>
+        <v>-18881</v>
       </c>
       <c r="AE84" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF84" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG84" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="AH84" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
       </c>
       <c r="AJ84" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
@@ -15043,16 +15043,16 @@
         </is>
       </c>
       <c r="AL84" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="AM84" t="n">
-        <v>0</v>
+        <v>-68.42</v>
       </c>
       <c r="AN84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AO84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR84" t="inlineStr">
@@ -15076,29 +15076,29 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3443.TW</t>
+          <t>2610.TW</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -15117,28 +15117,28 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>7585</v>
+        <v>20.5</v>
       </c>
       <c r="G85" t="n">
-        <v>7728</v>
+        <v>20.57</v>
       </c>
       <c r="H85" t="n">
-        <v>7911</v>
+        <v>20.51</v>
       </c>
       <c r="I85" t="n">
-        <v>8079.75</v>
+        <v>20.41</v>
       </c>
       <c r="J85" t="n">
-        <v>1513570</v>
+        <v>13512197</v>
       </c>
       <c r="K85" t="n">
-        <v>1737989</v>
+        <v>21072753</v>
       </c>
       <c r="L85" t="n">
-        <v>8750</v>
+        <v>21.2</v>
       </c>
       <c r="M85" t="n">
-        <v>7065</v>
+        <v>20</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -15146,52 +15146,52 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>70545</v>
+        <v>5716240</v>
       </c>
       <c r="P85" t="n">
-        <v>295418</v>
+        <v>-4550860</v>
       </c>
       <c r="Q85" t="n">
-        <v>425950</v>
+        <v>19188836</v>
       </c>
       <c r="R85" t="n">
-        <v>1200037</v>
+        <v>54853461</v>
       </c>
       <c r="S85" t="n">
-        <v>32133</v>
+        <v>5578240</v>
       </c>
       <c r="T85" t="n">
-        <v>28710</v>
+        <v>325011</v>
       </c>
       <c r="U85" t="n">
-        <v>36848</v>
+        <v>22644039</v>
       </c>
       <c r="V85" t="n">
-        <v>584120</v>
+        <v>58141349</v>
       </c>
       <c r="W85" t="n">
-        <v>39000</v>
+        <v>167000</v>
       </c>
       <c r="X85" t="n">
-        <v>315807</v>
+        <v>-4222180</v>
       </c>
       <c r="Y85" t="n">
-        <v>555115</v>
+        <v>-2847180</v>
       </c>
       <c r="Z85" t="n">
-        <v>833814</v>
+        <v>115820</v>
       </c>
       <c r="AA85" t="n">
-        <v>-588</v>
+        <v>-29000</v>
       </c>
       <c r="AB85" t="n">
-        <v>-49099</v>
+        <v>-653691</v>
       </c>
       <c r="AC85" t="n">
-        <v>-166013</v>
+        <v>-608023</v>
       </c>
       <c r="AD85" t="n">
-        <v>-217897</v>
+        <v>-3403708</v>
       </c>
       <c r="AE85" t="n">
         <v>10</v>
@@ -15200,16 +15200,16 @@
         <v>10</v>
       </c>
       <c r="AG85" t="n">
-        <v>-45</v>
+        <v>-5</v>
       </c>
       <c r="AH85" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
       </c>
       <c r="AJ85" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
@@ -15217,16 +15217,16 @@
         </is>
       </c>
       <c r="AL85" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="AM85" t="n">
-        <v>-70.59</v>
+        <v>0</v>
       </c>
       <c r="AN85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
@@ -15250,29 +15250,29 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏買、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3702.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -15291,28 +15291,28 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>114.5</v>
+        <v>5070</v>
       </c>
       <c r="G86" t="n">
-        <v>114.8</v>
+        <v>5059</v>
       </c>
       <c r="H86" t="n">
-        <v>115.9</v>
+        <v>5363</v>
       </c>
       <c r="I86" t="n">
-        <v>116.42</v>
+        <v>5311</v>
       </c>
       <c r="J86" t="n">
-        <v>8371199</v>
+        <v>4750904</v>
       </c>
       <c r="K86" t="n">
-        <v>9376851</v>
+        <v>2761928</v>
       </c>
       <c r="L86" t="n">
-        <v>122</v>
+        <v>6325</v>
       </c>
       <c r="M86" t="n">
-        <v>111.5</v>
+        <v>4855</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -15320,52 +15320,52 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>956731</v>
+        <v>263098</v>
       </c>
       <c r="P86" t="n">
-        <v>5234216</v>
+        <v>-113477</v>
       </c>
       <c r="Q86" t="n">
-        <v>5848199</v>
+        <v>-255029</v>
       </c>
       <c r="R86" t="n">
-        <v>22107911</v>
+        <v>-1626147</v>
       </c>
       <c r="S86" t="n">
-        <v>314154</v>
+        <v>162970</v>
       </c>
       <c r="T86" t="n">
-        <v>3451507</v>
+        <v>-182721</v>
       </c>
       <c r="U86" t="n">
-        <v>2157216</v>
+        <v>30323</v>
       </c>
       <c r="V86" t="n">
-        <v>16036507</v>
+        <v>-1988857</v>
       </c>
       <c r="W86" t="n">
-        <v>230000</v>
+        <v>36400</v>
       </c>
       <c r="X86" t="n">
-        <v>661924</v>
+        <v>243960</v>
       </c>
       <c r="Y86" t="n">
-        <v>2235964</v>
+        <v>73616</v>
       </c>
       <c r="Z86" t="n">
-        <v>2840757</v>
+        <v>540262</v>
       </c>
       <c r="AA86" t="n">
-        <v>412577</v>
+        <v>63728</v>
       </c>
       <c r="AB86" t="n">
-        <v>1120785</v>
+        <v>-174716</v>
       </c>
       <c r="AC86" t="n">
-        <v>1455019</v>
+        <v>-358968</v>
       </c>
       <c r="AD86" t="n">
-        <v>3230647</v>
+        <v>-177552</v>
       </c>
       <c r="AE86" t="n">
         <v>10</v>
@@ -15374,16 +15374,16 @@
         <v>10</v>
       </c>
       <c r="AG86" t="n">
-        <v>-55</v>
+        <v>25</v>
       </c>
       <c r="AH86" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
       </c>
       <c r="AJ86" t="n">
-        <v>24</v>
+        <v>-34</v>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
@@ -15391,25 +15391,25 @@
         </is>
       </c>
       <c r="AL86" t="n">
-        <v>-14</v>
+        <v>44</v>
       </c>
       <c r="AM86" t="n">
-        <v>-58.33</v>
+        <v>129.41</v>
       </c>
       <c r="AN86" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO86" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
@@ -15424,29 +15424,29 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人賣超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、成交量放大、接近20日低點、5日法人賣超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>3443.TW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -15465,28 +15465,28 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>5070</v>
+        <v>7585</v>
       </c>
       <c r="G87" t="n">
-        <v>5059</v>
+        <v>7728</v>
       </c>
       <c r="H87" t="n">
-        <v>5363</v>
+        <v>7911</v>
       </c>
       <c r="I87" t="n">
-        <v>5311</v>
+        <v>8079.75</v>
       </c>
       <c r="J87" t="n">
-        <v>4750904</v>
+        <v>1513570</v>
       </c>
       <c r="K87" t="n">
-        <v>2761928</v>
+        <v>1737989</v>
       </c>
       <c r="L87" t="n">
-        <v>6325</v>
+        <v>8750</v>
       </c>
       <c r="M87" t="n">
-        <v>4855</v>
+        <v>7065</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -15494,52 +15494,52 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>261098</v>
+        <v>70545</v>
       </c>
       <c r="P87" t="n">
-        <v>-115477</v>
+        <v>295418</v>
       </c>
       <c r="Q87" t="n">
-        <v>-257029</v>
+        <v>425950</v>
       </c>
       <c r="R87" t="n">
-        <v>-1628147</v>
+        <v>1200037</v>
       </c>
       <c r="S87" t="n">
-        <v>162970</v>
+        <v>32133</v>
       </c>
       <c r="T87" t="n">
-        <v>-182721</v>
+        <v>28710</v>
       </c>
       <c r="U87" t="n">
-        <v>30323</v>
+        <v>36848</v>
       </c>
       <c r="V87" t="n">
-        <v>-1988857</v>
+        <v>584120</v>
       </c>
       <c r="W87" t="n">
-        <v>34400</v>
+        <v>39000</v>
       </c>
       <c r="X87" t="n">
-        <v>241960</v>
+        <v>315807</v>
       </c>
       <c r="Y87" t="n">
-        <v>71616</v>
+        <v>555115</v>
       </c>
       <c r="Z87" t="n">
-        <v>538262</v>
+        <v>833814</v>
       </c>
       <c r="AA87" t="n">
-        <v>63728</v>
+        <v>-588</v>
       </c>
       <c r="AB87" t="n">
-        <v>-174716</v>
+        <v>-49099</v>
       </c>
       <c r="AC87" t="n">
-        <v>-358968</v>
+        <v>-166013</v>
       </c>
       <c r="AD87" t="n">
-        <v>-177552</v>
+        <v>-217897</v>
       </c>
       <c r="AE87" t="n">
         <v>10</v>
@@ -15548,16 +15548,16 @@
         <v>10</v>
       </c>
       <c r="AG87" t="n">
-        <v>25</v>
+        <v>-45</v>
       </c>
       <c r="AH87" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
       </c>
       <c r="AJ87" t="n">
-        <v>-34</v>
+        <v>34</v>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
@@ -15565,25 +15565,25 @@
         </is>
       </c>
       <c r="AL87" t="n">
-        <v>44</v>
+        <v>-24</v>
       </c>
       <c r="AM87" t="n">
-        <v>129.41</v>
+        <v>-70.59</v>
       </c>
       <c r="AN87" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AO87" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -15598,29 +15598,29 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>5日法人賣超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、接近20日低點、5日法人賣超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏買、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2707.TW</t>
+          <t>3702.TW</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>晶華</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -15639,28 +15639,28 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>176</v>
+        <v>114.5</v>
       </c>
       <c r="G88" t="n">
-        <v>176.9</v>
+        <v>114.8</v>
       </c>
       <c r="H88" t="n">
-        <v>176.85</v>
+        <v>115.9</v>
       </c>
       <c r="I88" t="n">
-        <v>176.3</v>
+        <v>116.42</v>
       </c>
       <c r="J88" t="n">
-        <v>119906</v>
+        <v>8371199</v>
       </c>
       <c r="K88" t="n">
-        <v>104019</v>
+        <v>9376851</v>
       </c>
       <c r="L88" t="n">
-        <v>179</v>
+        <v>122</v>
       </c>
       <c r="M88" t="n">
-        <v>174.5</v>
+        <v>111.5</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -15668,70 +15668,70 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>53170</v>
+        <v>956731</v>
       </c>
       <c r="P88" t="n">
-        <v>-12819</v>
+        <v>5234216</v>
       </c>
       <c r="Q88" t="n">
-        <v>40622</v>
+        <v>5848199</v>
       </c>
       <c r="R88" t="n">
-        <v>422102</v>
+        <v>22107911</v>
       </c>
       <c r="S88" t="n">
-        <v>53170</v>
+        <v>314154</v>
       </c>
       <c r="T88" t="n">
-        <v>-8803</v>
+        <v>3451507</v>
       </c>
       <c r="U88" t="n">
-        <v>45737</v>
+        <v>2157216</v>
       </c>
       <c r="V88" t="n">
-        <v>427404</v>
+        <v>16036507</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>661924</v>
       </c>
       <c r="Y88" t="n">
-        <v>-2000</v>
+        <v>2235964</v>
       </c>
       <c r="Z88" t="n">
-        <v>-2000</v>
+        <v>2840757</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>412577</v>
       </c>
       <c r="AB88" t="n">
-        <v>-4016</v>
+        <v>1120785</v>
       </c>
       <c r="AC88" t="n">
-        <v>-3115</v>
+        <v>1455019</v>
       </c>
       <c r="AD88" t="n">
-        <v>-3302</v>
+        <v>3230647</v>
       </c>
       <c r="AE88" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF88" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG88" t="n">
-        <v>20</v>
+        <v>-55</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
@@ -15739,10 +15739,10 @@
         </is>
       </c>
       <c r="AL88" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="AM88" t="n">
-        <v>-33.33</v>
+        <v>-58.33</v>
       </c>
       <c r="AN88" t="n">
         <v>0</v>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
@@ -15772,17 +15772,17 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>籌碼中性、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點、籌碼中性、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15963,12 +15963,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2617.TW</t>
+          <t>2707.TW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>台航</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -15987,28 +15987,28 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>31.5</v>
+        <v>176</v>
       </c>
       <c r="G90" t="n">
-        <v>31.62</v>
+        <v>176.9</v>
       </c>
       <c r="H90" t="n">
-        <v>32.04</v>
+        <v>176.85</v>
       </c>
       <c r="I90" t="n">
-        <v>32.05</v>
+        <v>176.3</v>
       </c>
       <c r="J90" t="n">
-        <v>574473</v>
+        <v>119906</v>
       </c>
       <c r="K90" t="n">
-        <v>754683</v>
+        <v>104019</v>
       </c>
       <c r="L90" t="n">
-        <v>33.35</v>
+        <v>179</v>
       </c>
       <c r="M90" t="n">
-        <v>30.85</v>
+        <v>174.5</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -16016,70 +16016,70 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>274052</v>
+        <v>53170</v>
       </c>
       <c r="P90" t="n">
-        <v>39106</v>
+        <v>-12819</v>
       </c>
       <c r="Q90" t="n">
-        <v>206663</v>
+        <v>40622</v>
       </c>
       <c r="R90" t="n">
-        <v>1970931</v>
+        <v>422102</v>
       </c>
       <c r="S90" t="n">
-        <v>278410</v>
+        <v>53170</v>
       </c>
       <c r="T90" t="n">
-        <v>-141839</v>
+        <v>-8803</v>
       </c>
       <c r="U90" t="n">
-        <v>71488</v>
+        <v>45737</v>
       </c>
       <c r="V90" t="n">
-        <v>1826058</v>
+        <v>427404</v>
       </c>
       <c r="W90" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>286000</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>288000</v>
+        <v>-2000</v>
       </c>
       <c r="Z90" t="n">
-        <v>288000</v>
+        <v>-2000</v>
       </c>
       <c r="AA90" t="n">
-        <v>-17358</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>-105055</v>
+        <v>-4016</v>
       </c>
       <c r="AC90" t="n">
-        <v>-152825</v>
+        <v>-3115</v>
       </c>
       <c r="AD90" t="n">
-        <v>-143127</v>
+        <v>-3302</v>
       </c>
       <c r="AE90" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF90" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG90" t="n">
-        <v>-55</v>
+        <v>20</v>
       </c>
       <c r="AH90" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
       </c>
       <c r="AJ90" t="n">
-        <v>-18</v>
+        <v>12</v>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
@@ -16087,16 +16087,16 @@
         </is>
       </c>
       <c r="AL90" t="n">
-        <v>24</v>
+        <v>-4</v>
       </c>
       <c r="AM90" t="n">
-        <v>133.33</v>
+        <v>-33.33</v>
       </c>
       <c r="AN90" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO90" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
@@ -16120,29 +16120,29 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
+          <t>籌碼中性、外資買投信賣</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點、籌碼中性、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2395.TW</t>
+          <t>2617.TW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>台航</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16161,28 +16161,28 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>670</v>
+        <v>31.5</v>
       </c>
       <c r="G91" t="n">
-        <v>680.2</v>
+        <v>31.62</v>
       </c>
       <c r="H91" t="n">
-        <v>697.9</v>
+        <v>32.04</v>
       </c>
       <c r="I91" t="n">
-        <v>710.55</v>
+        <v>32.05</v>
       </c>
       <c r="J91" t="n">
-        <v>1662824</v>
+        <v>574473</v>
       </c>
       <c r="K91" t="n">
-        <v>2018295</v>
+        <v>754683</v>
       </c>
       <c r="L91" t="n">
-        <v>754</v>
+        <v>33.35</v>
       </c>
       <c r="M91" t="n">
-        <v>658</v>
+        <v>30.85</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -16190,52 +16190,52 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>172429</v>
+        <v>274052</v>
       </c>
       <c r="P91" t="n">
-        <v>147470</v>
+        <v>39106</v>
       </c>
       <c r="Q91" t="n">
-        <v>290485</v>
+        <v>206663</v>
       </c>
       <c r="R91" t="n">
-        <v>43858</v>
+        <v>1970931</v>
       </c>
       <c r="S91" t="n">
-        <v>155020</v>
+        <v>278410</v>
       </c>
       <c r="T91" t="n">
-        <v>61373</v>
+        <v>-141839</v>
       </c>
       <c r="U91" t="n">
-        <v>273675</v>
+        <v>71488</v>
       </c>
       <c r="V91" t="n">
-        <v>99727</v>
+        <v>1826058</v>
       </c>
       <c r="W91" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="X91" t="n">
-        <v>94847</v>
+        <v>286000</v>
       </c>
       <c r="Y91" t="n">
-        <v>16014</v>
+        <v>288000</v>
       </c>
       <c r="Z91" t="n">
-        <v>-207639</v>
+        <v>288000</v>
       </c>
       <c r="AA91" t="n">
-        <v>5409</v>
+        <v>-17358</v>
       </c>
       <c r="AB91" t="n">
-        <v>-8750</v>
+        <v>-105055</v>
       </c>
       <c r="AC91" t="n">
-        <v>796</v>
+        <v>-152825</v>
       </c>
       <c r="AD91" t="n">
-        <v>151770</v>
+        <v>-143127</v>
       </c>
       <c r="AE91" t="n">
         <v>6</v>
@@ -16253,7 +16253,7 @@
         <v>0</v>
       </c>
       <c r="AJ91" t="n">
-        <v>-24</v>
+        <v>-18</v>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
@@ -16261,16 +16261,16 @@
         </is>
       </c>
       <c r="AL91" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AM91" t="n">
-        <v>125</v>
+        <v>133.33</v>
       </c>
       <c r="AN91" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO91" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
@@ -16311,12 +16311,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -16335,28 +16335,28 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>986</v>
+        <v>45.25</v>
       </c>
       <c r="G92" t="n">
-        <v>984.6</v>
+        <v>45.87</v>
       </c>
       <c r="H92" t="n">
-        <v>1012.7</v>
+        <v>45.92</v>
       </c>
       <c r="I92" t="n">
-        <v>1007.7</v>
+        <v>46.75</v>
       </c>
       <c r="J92" t="n">
-        <v>19629047</v>
+        <v>2943858</v>
       </c>
       <c r="K92" t="n">
-        <v>16218162</v>
+        <v>2760495</v>
       </c>
       <c r="L92" t="n">
-        <v>1150</v>
+        <v>50.3</v>
       </c>
       <c r="M92" t="n">
-        <v>875</v>
+        <v>44.5</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -16364,52 +16364,52 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>1153340</v>
+        <v>159089</v>
       </c>
       <c r="P92" t="n">
-        <v>413671</v>
+        <v>1032491</v>
       </c>
       <c r="Q92" t="n">
-        <v>-1129569</v>
+        <v>1148988</v>
       </c>
       <c r="R92" t="n">
-        <v>-1999465</v>
+        <v>1225279</v>
       </c>
       <c r="S92" t="n">
-        <v>45572</v>
+        <v>197516</v>
       </c>
       <c r="T92" t="n">
-        <v>-1352820</v>
+        <v>781582</v>
       </c>
       <c r="U92" t="n">
-        <v>-4691801</v>
+        <v>751396</v>
       </c>
       <c r="V92" t="n">
-        <v>-7114090</v>
+        <v>973610</v>
       </c>
       <c r="W92" t="n">
-        <v>1060000</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>2082872</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>4571241</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>6434518</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>47768</v>
+        <v>-38427</v>
       </c>
       <c r="AB92" t="n">
-        <v>-316381</v>
+        <v>250909</v>
       </c>
       <c r="AC92" t="n">
-        <v>-1009009</v>
+        <v>397592</v>
       </c>
       <c r="AD92" t="n">
-        <v>-1319893</v>
+        <v>251669</v>
       </c>
       <c r="AE92" t="n">
         <v>6</v>
@@ -16418,16 +16418,16 @@
         <v>6</v>
       </c>
       <c r="AG92" t="n">
-        <v>30</v>
+        <v>-45</v>
       </c>
       <c r="AH92" t="n">
-        <v>-15</v>
+        <v>60</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
       </c>
       <c r="AJ92" t="n">
-        <v>-10</v>
+        <v>18</v>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
@@ -16435,25 +16435,25 @@
         </is>
       </c>
       <c r="AL92" t="n">
-        <v>16</v>
+        <v>-12</v>
       </c>
       <c r="AM92" t="n">
-        <v>160</v>
+        <v>-66.67</v>
       </c>
       <c r="AN92" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AO92" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
@@ -16468,29 +16468,29 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>2395.TW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -16509,28 +16509,28 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>45.25</v>
+        <v>670</v>
       </c>
       <c r="G93" t="n">
-        <v>45.87</v>
+        <v>680.2</v>
       </c>
       <c r="H93" t="n">
-        <v>45.92</v>
+        <v>697.9</v>
       </c>
       <c r="I93" t="n">
-        <v>46.75</v>
+        <v>710.55</v>
       </c>
       <c r="J93" t="n">
-        <v>2943858</v>
+        <v>1662824</v>
       </c>
       <c r="K93" t="n">
-        <v>2760495</v>
+        <v>2018295</v>
       </c>
       <c r="L93" t="n">
-        <v>50.3</v>
+        <v>754</v>
       </c>
       <c r="M93" t="n">
-        <v>44.5</v>
+        <v>658</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -16538,52 +16538,52 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>159089</v>
+        <v>172429</v>
       </c>
       <c r="P93" t="n">
-        <v>1032491</v>
+        <v>147470</v>
       </c>
       <c r="Q93" t="n">
-        <v>1148988</v>
+        <v>290485</v>
       </c>
       <c r="R93" t="n">
-        <v>1225279</v>
+        <v>43858</v>
       </c>
       <c r="S93" t="n">
-        <v>197516</v>
+        <v>155020</v>
       </c>
       <c r="T93" t="n">
-        <v>781582</v>
+        <v>61373</v>
       </c>
       <c r="U93" t="n">
-        <v>751396</v>
+        <v>273675</v>
       </c>
       <c r="V93" t="n">
-        <v>973610</v>
+        <v>99727</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>94847</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>16014</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>-207639</v>
       </c>
       <c r="AA93" t="n">
-        <v>-38427</v>
+        <v>5409</v>
       </c>
       <c r="AB93" t="n">
-        <v>250909</v>
+        <v>-8750</v>
       </c>
       <c r="AC93" t="n">
-        <v>397592</v>
+        <v>796</v>
       </c>
       <c r="AD93" t="n">
-        <v>251669</v>
+        <v>151770</v>
       </c>
       <c r="AE93" t="n">
         <v>6</v>
@@ -16592,16 +16592,16 @@
         <v>6</v>
       </c>
       <c r="AG93" t="n">
-        <v>-45</v>
+        <v>-55</v>
       </c>
       <c r="AH93" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>18</v>
+        <v>-24</v>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
@@ -16609,10 +16609,10 @@
         </is>
       </c>
       <c r="AL93" t="n">
-        <v>-12</v>
+        <v>30</v>
       </c>
       <c r="AM93" t="n">
-        <v>-66.67</v>
+        <v>125</v>
       </c>
       <c r="AN93" t="n">
         <v>0</v>
@@ -16627,7 +16627,7 @@
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
@@ -16642,29 +16642,29 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2368.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -16683,28 +16683,28 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1115</v>
+        <v>986</v>
       </c>
       <c r="G94" t="n">
-        <v>1198</v>
+        <v>984.6</v>
       </c>
       <c r="H94" t="n">
-        <v>1213</v>
+        <v>1012.7</v>
       </c>
       <c r="I94" t="n">
-        <v>1178.75</v>
+        <v>1007.7</v>
       </c>
       <c r="J94" t="n">
-        <v>9433960</v>
+        <v>19629047</v>
       </c>
       <c r="K94" t="n">
-        <v>11360803</v>
+        <v>16218162</v>
       </c>
       <c r="L94" t="n">
-        <v>1310</v>
+        <v>1150</v>
       </c>
       <c r="M94" t="n">
-        <v>1025</v>
+        <v>875</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -16712,70 +16712,70 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>743712</v>
+        <v>1166340</v>
       </c>
       <c r="P94" t="n">
-        <v>-627512</v>
+        <v>426671</v>
       </c>
       <c r="Q94" t="n">
-        <v>665367</v>
+        <v>-1116569</v>
       </c>
       <c r="R94" t="n">
-        <v>2264587</v>
+        <v>-1986465</v>
       </c>
       <c r="S94" t="n">
-        <v>368093</v>
+        <v>45572</v>
       </c>
       <c r="T94" t="n">
-        <v>-2240885</v>
+        <v>-1352820</v>
       </c>
       <c r="U94" t="n">
-        <v>-5388211</v>
+        <v>-4691801</v>
       </c>
       <c r="V94" t="n">
-        <v>-11928900</v>
+        <v>-7114090</v>
       </c>
       <c r="W94" t="n">
-        <v>518000</v>
+        <v>1073000</v>
       </c>
       <c r="X94" t="n">
-        <v>1655079</v>
+        <v>2095872</v>
       </c>
       <c r="Y94" t="n">
-        <v>5821338</v>
+        <v>4584241</v>
       </c>
       <c r="Z94" t="n">
-        <v>14134148</v>
+        <v>6447518</v>
       </c>
       <c r="AA94" t="n">
-        <v>-142381</v>
+        <v>47768</v>
       </c>
       <c r="AB94" t="n">
-        <v>-41706</v>
+        <v>-316381</v>
       </c>
       <c r="AC94" t="n">
-        <v>232240</v>
+        <v>-1009009</v>
       </c>
       <c r="AD94" t="n">
-        <v>59339</v>
+        <v>-1319893</v>
       </c>
       <c r="AE94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG94" t="n">
-        <v>-20</v>
+        <v>30</v>
       </c>
       <c r="AH94" t="n">
-        <v>30</v>
+        <v>-15</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
       </c>
       <c r="AJ94" t="n">
-        <v>-40</v>
+        <v>-10</v>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
@@ -16783,25 +16783,25 @@
         </is>
       </c>
       <c r="AL94" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="AM94" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AN94" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO94" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
@@ -16816,29 +16816,29 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2607.TW</t>
+          <t>2368.TW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>榮運</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -16857,28 +16857,28 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>55.7</v>
+        <v>1115</v>
       </c>
       <c r="G95" t="n">
-        <v>56.56</v>
+        <v>1198</v>
       </c>
       <c r="H95" t="n">
-        <v>57.21</v>
+        <v>1213</v>
       </c>
       <c r="I95" t="n">
-        <v>55.49</v>
+        <v>1178.75</v>
       </c>
       <c r="J95" t="n">
-        <v>657620</v>
+        <v>9433960</v>
       </c>
       <c r="K95" t="n">
-        <v>909150</v>
+        <v>11360803</v>
       </c>
       <c r="L95" t="n">
-        <v>59.8</v>
+        <v>1310</v>
       </c>
       <c r="M95" t="n">
-        <v>53</v>
+        <v>1025</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -16886,52 +16886,52 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>160985</v>
+        <v>723262</v>
       </c>
       <c r="P95" t="n">
-        <v>-112766</v>
+        <v>-647962</v>
       </c>
       <c r="Q95" t="n">
-        <v>685939</v>
+        <v>644917</v>
       </c>
       <c r="R95" t="n">
-        <v>2633162</v>
+        <v>2244137</v>
       </c>
       <c r="S95" t="n">
-        <v>157985</v>
+        <v>368093</v>
       </c>
       <c r="T95" t="n">
-        <v>-103891</v>
+        <v>-2240885</v>
       </c>
       <c r="U95" t="n">
-        <v>715489</v>
+        <v>-5388211</v>
       </c>
       <c r="V95" t="n">
-        <v>2539712</v>
+        <v>-11928900</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>497550</v>
       </c>
       <c r="X95" t="n">
-        <v>-122</v>
+        <v>1634629</v>
       </c>
       <c r="Y95" t="n">
-        <v>-122</v>
+        <v>5800888</v>
       </c>
       <c r="Z95" t="n">
-        <v>-122</v>
+        <v>14113698</v>
       </c>
       <c r="AA95" t="n">
-        <v>3000</v>
+        <v>-142381</v>
       </c>
       <c r="AB95" t="n">
-        <v>-8753</v>
+        <v>-41706</v>
       </c>
       <c r="AC95" t="n">
-        <v>-29428</v>
+        <v>232240</v>
       </c>
       <c r="AD95" t="n">
-        <v>93572</v>
+        <v>59339</v>
       </c>
       <c r="AE95" t="n">
         <v>4</v>
@@ -16949,7 +16949,7 @@
         <v>0</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
@@ -16957,9 +16957,11 @@
         </is>
       </c>
       <c r="AL95" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM95" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>110</v>
+      </c>
       <c r="AN95" t="n">
         <v>0</v>
       </c>
@@ -16973,7 +16975,7 @@
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
@@ -16993,24 +16995,24 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4903.TWO</t>
+          <t>2607.TW</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>榮運</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -17029,28 +17031,28 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>48.55</v>
+        <v>55.7</v>
       </c>
       <c r="G96" t="n">
-        <v>53.27</v>
+        <v>56.56</v>
       </c>
       <c r="H96" t="n">
-        <v>52.08</v>
+        <v>57.21</v>
       </c>
       <c r="I96" t="n">
-        <v>47.82</v>
+        <v>55.49</v>
       </c>
       <c r="J96" t="n">
-        <v>7160000</v>
+        <v>657620</v>
       </c>
       <c r="K96" t="n">
-        <v>15449800</v>
+        <v>909150</v>
       </c>
       <c r="L96" t="n">
-        <v>59.3</v>
+        <v>59.8</v>
       </c>
       <c r="M96" t="n">
-        <v>40.6</v>
+        <v>53</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -17058,70 +17060,70 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>160985</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>-112766</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>685939</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2633162</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>157985</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>-103891</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>715489</v>
       </c>
       <c r="V96" t="n">
-        <v>0</v>
+        <v>2539712</v>
       </c>
       <c r="W96" t="n">
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>-122</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>-122</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>-122</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>-8753</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>-29428</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>93572</v>
       </c>
       <c r="AE96" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF96" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG96" t="n">
-        <v>5</v>
+        <v>-20</v>
       </c>
       <c r="AH96" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
       </c>
       <c r="AJ96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
@@ -17129,16 +17131,14 @@
         </is>
       </c>
       <c r="AL96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM96" t="n">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AM96" t="inlineStr"/>
       <c r="AN96" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AO96" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
+          <t>DT尚未轉強、尚未站上5MA、分數剛升溫</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
@@ -17162,29 +17162,29 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2816.TW</t>
+          <t>4903.TWO</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>旺旺保</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -17203,28 +17203,28 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>42.15</v>
+        <v>48.55</v>
       </c>
       <c r="G97" t="n">
-        <v>43.25</v>
+        <v>53.27</v>
       </c>
       <c r="H97" t="n">
-        <v>43.04</v>
+        <v>52.08</v>
       </c>
       <c r="I97" t="n">
-        <v>41.53</v>
+        <v>47.82</v>
       </c>
       <c r="J97" t="n">
-        <v>249478</v>
+        <v>7160000</v>
       </c>
       <c r="K97" t="n">
-        <v>350932</v>
+        <v>15449800</v>
       </c>
       <c r="L97" t="n">
-        <v>45.5</v>
+        <v>59.3</v>
       </c>
       <c r="M97" t="n">
-        <v>39.35</v>
+        <v>40.6</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -17232,28 +17232,28 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>13647</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>13921</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>-29422</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>402670</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>13647</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>11921</v>
+        <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>-71422</v>
+        <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>361670</v>
+        <v>0</v>
       </c>
       <c r="W97" t="n">
         <v>0</v>
@@ -17262,22 +17262,22 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>67000</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>67000</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>-26000</v>
+        <v>0</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -17295,7 +17295,7 @@
         <v>0</v>
       </c>
       <c r="AJ97" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
@@ -17303,16 +17303,16 @@
         </is>
       </c>
       <c r="AL97" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="AM97" t="n">
-        <v>-93.33</v>
+        <v>0</v>
       </c>
       <c r="AN97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AO97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
@@ -17341,12 +17341,12 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>籌碼中性、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -17527,12 +17527,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2331.TW</t>
+          <t>2816.TW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>精英</t>
+          <t>旺旺保</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -17551,28 +17551,28 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>17.95</v>
+        <v>42.15</v>
       </c>
       <c r="G99" t="n">
-        <v>18.07</v>
+        <v>43.25</v>
       </c>
       <c r="H99" t="n">
-        <v>18.31</v>
+        <v>43.04</v>
       </c>
       <c r="I99" t="n">
-        <v>18.64</v>
+        <v>41.53</v>
       </c>
       <c r="J99" t="n">
-        <v>1081765</v>
+        <v>249478</v>
       </c>
       <c r="K99" t="n">
-        <v>854640</v>
+        <v>350932</v>
       </c>
       <c r="L99" t="n">
-        <v>19.65</v>
+        <v>45.5</v>
       </c>
       <c r="M99" t="n">
-        <v>17.85</v>
+        <v>39.35</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -17580,28 +17580,28 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>188585</v>
+        <v>13647</v>
       </c>
       <c r="P99" t="n">
-        <v>375646</v>
+        <v>13921</v>
       </c>
       <c r="Q99" t="n">
-        <v>106763</v>
+        <v>-29422</v>
       </c>
       <c r="R99" t="n">
-        <v>379833</v>
+        <v>402670</v>
       </c>
       <c r="S99" t="n">
-        <v>146886</v>
+        <v>13647</v>
       </c>
       <c r="T99" t="n">
-        <v>370319</v>
+        <v>11921</v>
       </c>
       <c r="U99" t="n">
-        <v>289319</v>
+        <v>-71422</v>
       </c>
       <c r="V99" t="n">
-        <v>377390</v>
+        <v>361670</v>
       </c>
       <c r="W99" t="n">
         <v>0</v>
@@ -17610,22 +17610,22 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="AA99" t="n">
-        <v>41699</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>5327</v>
+        <v>2000</v>
       </c>
       <c r="AC99" t="n">
-        <v>-182556</v>
+        <v>-25000</v>
       </c>
       <c r="AD99" t="n">
-        <v>2443</v>
+        <v>-26000</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -17634,16 +17634,16 @@
         <v>2</v>
       </c>
       <c r="AG99" t="n">
-        <v>-45</v>
+        <v>5</v>
       </c>
       <c r="AH99" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AI99" t="n">
         <v>0</v>
       </c>
       <c r="AJ99" t="n">
-        <v>-40</v>
+        <v>30</v>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
@@ -17651,16 +17651,16 @@
         </is>
       </c>
       <c r="AL99" t="n">
-        <v>42</v>
+        <v>-28</v>
       </c>
       <c r="AM99" t="n">
-        <v>105</v>
+        <v>-93.33</v>
       </c>
       <c r="AN99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AO99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
@@ -17684,29 +17684,29 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>籌碼中性、投信買外資賣</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>2331.TW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>精英</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -17725,28 +17725,28 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>24.9</v>
+        <v>17.95</v>
       </c>
       <c r="G100" t="n">
-        <v>25.29</v>
+        <v>18.07</v>
       </c>
       <c r="H100" t="n">
-        <v>25.71</v>
+        <v>18.31</v>
       </c>
       <c r="I100" t="n">
-        <v>25.25</v>
+        <v>18.64</v>
       </c>
       <c r="J100" t="n">
-        <v>5597146</v>
+        <v>1081765</v>
       </c>
       <c r="K100" t="n">
-        <v>6646959</v>
+        <v>854640</v>
       </c>
       <c r="L100" t="n">
-        <v>27.4</v>
+        <v>19.65</v>
       </c>
       <c r="M100" t="n">
-        <v>23.85</v>
+        <v>17.85</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -17754,70 +17754,70 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>160795</v>
+        <v>188585</v>
       </c>
       <c r="P100" t="n">
-        <v>-769381</v>
+        <v>375646</v>
       </c>
       <c r="Q100" t="n">
-        <v>2527075</v>
+        <v>106763</v>
       </c>
       <c r="R100" t="n">
-        <v>10629745</v>
+        <v>379833</v>
       </c>
       <c r="S100" t="n">
-        <v>255278</v>
+        <v>146886</v>
       </c>
       <c r="T100" t="n">
-        <v>-383302</v>
+        <v>370319</v>
       </c>
       <c r="U100" t="n">
-        <v>3072692</v>
+        <v>289319</v>
       </c>
       <c r="V100" t="n">
-        <v>11376310</v>
+        <v>377390</v>
       </c>
       <c r="W100" t="n">
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>-2118</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>-7118</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>131882</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>-94483</v>
+        <v>41699</v>
       </c>
       <c r="AB100" t="n">
-        <v>-383961</v>
+        <v>5327</v>
       </c>
       <c r="AC100" t="n">
-        <v>-538499</v>
+        <v>-182556</v>
       </c>
       <c r="AD100" t="n">
-        <v>-878447</v>
+        <v>2443</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG100" t="n">
-        <v>-30</v>
+        <v>-45</v>
       </c>
       <c r="AH100" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>
       </c>
       <c r="AJ100" t="n">
-        <v>-30</v>
+        <v>-40</v>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
@@ -17825,16 +17825,16 @@
         </is>
       </c>
       <c r="AL100" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AM100" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AN100" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AO100" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR100" t="inlineStr">
@@ -17858,17 +17858,17 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -18223,12 +18223,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1906.TW</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>寶隆</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -18247,28 +18247,28 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>10.85</v>
+        <v>24.9</v>
       </c>
       <c r="G103" t="n">
-        <v>10.87</v>
+        <v>25.29</v>
       </c>
       <c r="H103" t="n">
-        <v>10.86</v>
+        <v>25.71</v>
       </c>
       <c r="I103" t="n">
-        <v>10.8</v>
+        <v>25.25</v>
       </c>
       <c r="J103" t="n">
-        <v>67465</v>
+        <v>5597146</v>
       </c>
       <c r="K103" t="n">
-        <v>35982</v>
+        <v>6646959</v>
       </c>
       <c r="L103" t="n">
-        <v>11.05</v>
+        <v>27.4</v>
       </c>
       <c r="M103" t="n">
-        <v>10.6</v>
+        <v>23.85</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -18276,52 +18276,52 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>-392</v>
+        <v>160795</v>
       </c>
       <c r="P103" t="n">
-        <v>-3219</v>
+        <v>-769381</v>
       </c>
       <c r="Q103" t="n">
-        <v>-5359</v>
+        <v>2527075</v>
       </c>
       <c r="R103" t="n">
-        <v>-4970</v>
+        <v>10629745</v>
       </c>
       <c r="S103" t="n">
-        <v>-392</v>
+        <v>255278</v>
       </c>
       <c r="T103" t="n">
-        <v>-3219</v>
+        <v>-383302</v>
       </c>
       <c r="U103" t="n">
-        <v>-5359</v>
+        <v>3072692</v>
       </c>
       <c r="V103" t="n">
-        <v>-970</v>
+        <v>11376310</v>
       </c>
       <c r="W103" t="n">
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>-2118</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>-7118</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>131882</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>-94483</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>-383961</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>-538499</v>
       </c>
       <c r="AD103" t="n">
-        <v>-4000</v>
+        <v>-878447</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -18330,16 +18330,16 @@
         <v>0</v>
       </c>
       <c r="AG103" t="n">
-        <v>25</v>
+        <v>-30</v>
       </c>
       <c r="AH103" t="n">
-        <v>-25</v>
+        <v>30</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>
       </c>
       <c r="AJ103" t="n">
-        <v>26</v>
+        <v>-30</v>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
@@ -18347,16 +18347,16 @@
         </is>
       </c>
       <c r="AL103" t="n">
-        <v>-26</v>
+        <v>30</v>
       </c>
       <c r="AM103" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AN103" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AO103" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
@@ -18380,17 +18380,17 @@
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、成交量放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>法人連續偏賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、成交量放大、接近20日高點、接近20日低點、法人連續偏賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -18745,12 +18745,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8299.TWO</t>
+          <t>1906.TW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>寶隆</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -18769,28 +18769,28 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1880</v>
+        <v>10.85</v>
       </c>
       <c r="G106" t="n">
-        <v>1878</v>
+        <v>10.87</v>
       </c>
       <c r="H106" t="n">
-        <v>1926.5</v>
+        <v>10.86</v>
       </c>
       <c r="I106" t="n">
-        <v>2025.5</v>
+        <v>10.8</v>
       </c>
       <c r="J106" t="n">
-        <v>1898000</v>
+        <v>67465</v>
       </c>
       <c r="K106" t="n">
-        <v>2298200</v>
+        <v>35982</v>
       </c>
       <c r="L106" t="n">
-        <v>2350</v>
+        <v>11.05</v>
       </c>
       <c r="M106" t="n">
-        <v>1785</v>
+        <v>10.6</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -18798,28 +18798,28 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>-392</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>-3219</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>-5359</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>-4970</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>-392</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>-3219</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>-5359</v>
       </c>
       <c r="V106" t="n">
-        <v>0</v>
+        <v>-970</v>
       </c>
       <c r="W106" t="n">
         <v>0</v>
@@ -18843,25 +18843,25 @@
         <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="AE106" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
-        <v>-5</v>
+        <v>25</v>
       </c>
       <c r="AH106" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AI106" t="n">
         <v>0</v>
       </c>
       <c r="AJ106" t="n">
-        <v>-2</v>
+        <v>26</v>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
@@ -18869,25 +18869,25 @@
         </is>
       </c>
       <c r="AL106" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="AM106" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AN106" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AO106" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
@@ -18902,17 +18902,17 @@
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、成交量放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、成交量放大、接近20日高點、接近20日低點、法人連續偏賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -19093,12 +19093,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6426.TW</t>
+          <t>8299.TWO</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -19117,28 +19117,28 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>313</v>
+        <v>1880</v>
       </c>
       <c r="G108" t="n">
-        <v>327.9</v>
+        <v>1878</v>
       </c>
       <c r="H108" t="n">
-        <v>329.85</v>
+        <v>1926.5</v>
       </c>
       <c r="I108" t="n">
-        <v>344.55</v>
+        <v>2025.5</v>
       </c>
       <c r="J108" t="n">
-        <v>1945198</v>
+        <v>1898000</v>
       </c>
       <c r="K108" t="n">
-        <v>1349250</v>
+        <v>2298200</v>
       </c>
       <c r="L108" t="n">
-        <v>412</v>
+        <v>2350</v>
       </c>
       <c r="M108" t="n">
-        <v>310</v>
+        <v>1785</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -19146,52 +19146,52 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>-118441</v>
+        <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>98439</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>175986</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>142912</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>-182000</v>
+        <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>40950</v>
+        <v>0</v>
       </c>
       <c r="U108" t="n">
-        <v>94367</v>
+        <v>0</v>
       </c>
       <c r="V108" t="n">
-        <v>81749</v>
+        <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>68000</v>
+        <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>104000</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>-4441</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>-46511</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>-33381</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
-        <v>-53837</v>
+        <v>0</v>
       </c>
       <c r="AE108" t="n">
         <v>-2</v>
@@ -19200,16 +19200,16 @@
         <v>-2</v>
       </c>
       <c r="AG108" t="n">
-        <v>-45</v>
+        <v>-5</v>
       </c>
       <c r="AH108" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AI108" t="n">
         <v>0</v>
       </c>
       <c r="AJ108" t="n">
-        <v>32</v>
+        <v>-2</v>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
@@ -19217,25 +19217,25 @@
         </is>
       </c>
       <c r="AL108" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="AM108" t="n">
-        <v>-106.25</v>
+        <v>0</v>
       </c>
       <c r="AN108" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO108" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
@@ -19250,29 +19250,29 @@
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1304.TW</t>
+          <t>6426.TW</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -19291,28 +19291,28 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>12.65</v>
+        <v>313</v>
       </c>
       <c r="G109" t="n">
-        <v>12.98</v>
+        <v>327.9</v>
       </c>
       <c r="H109" t="n">
-        <v>13.19</v>
+        <v>329.85</v>
       </c>
       <c r="I109" t="n">
-        <v>12.86</v>
+        <v>344.55</v>
       </c>
       <c r="J109" t="n">
-        <v>1781836</v>
+        <v>1945198</v>
       </c>
       <c r="K109" t="n">
-        <v>2515645</v>
+        <v>1349250</v>
       </c>
       <c r="L109" t="n">
-        <v>14.35</v>
+        <v>412</v>
       </c>
       <c r="M109" t="n">
-        <v>12.1</v>
+        <v>310</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -19320,70 +19320,70 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>-347830</v>
+        <v>-118441</v>
       </c>
       <c r="P109" t="n">
-        <v>-339664</v>
+        <v>98439</v>
       </c>
       <c r="Q109" t="n">
-        <v>275347</v>
+        <v>175986</v>
       </c>
       <c r="R109" t="n">
-        <v>3490236</v>
+        <v>142912</v>
       </c>
       <c r="S109" t="n">
-        <v>-297882</v>
+        <v>-182000</v>
       </c>
       <c r="T109" t="n">
-        <v>-212504</v>
+        <v>40950</v>
       </c>
       <c r="U109" t="n">
-        <v>795588</v>
+        <v>94367</v>
       </c>
       <c r="V109" t="n">
-        <v>3623968</v>
+        <v>81749</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>104000</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>115000</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>115000</v>
       </c>
       <c r="AA109" t="n">
-        <v>-49948</v>
+        <v>-4441</v>
       </c>
       <c r="AB109" t="n">
-        <v>-127160</v>
+        <v>-46511</v>
       </c>
       <c r="AC109" t="n">
-        <v>-520241</v>
+        <v>-33381</v>
       </c>
       <c r="AD109" t="n">
-        <v>-133732</v>
+        <v>-53837</v>
       </c>
       <c r="AE109" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AF109" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AG109" t="n">
-        <v>-30</v>
+        <v>-45</v>
       </c>
       <c r="AH109" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AI109" t="n">
         <v>0</v>
       </c>
       <c r="AJ109" t="n">
-        <v>-30</v>
+        <v>32</v>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
@@ -19391,10 +19391,10 @@
         </is>
       </c>
       <c r="AL109" t="n">
-        <v>26</v>
+        <v>-34</v>
       </c>
       <c r="AM109" t="n">
-        <v>86.67</v>
+        <v>-106.25</v>
       </c>
       <c r="AN109" t="n">
         <v>0</v>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
@@ -19424,29 +19424,29 @@
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2498.TW</t>
+          <t>1304.TW</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -19465,28 +19465,28 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>39.75</v>
+        <v>12.65</v>
       </c>
       <c r="G110" t="n">
-        <v>40.1</v>
+        <v>12.98</v>
       </c>
       <c r="H110" t="n">
-        <v>40.51</v>
+        <v>13.19</v>
       </c>
       <c r="I110" t="n">
-        <v>41.36</v>
+        <v>12.86</v>
       </c>
       <c r="J110" t="n">
-        <v>3517549</v>
+        <v>1781836</v>
       </c>
       <c r="K110" t="n">
-        <v>2873898</v>
+        <v>2515645</v>
       </c>
       <c r="L110" t="n">
-        <v>46.85</v>
+        <v>14.35</v>
       </c>
       <c r="M110" t="n">
-        <v>39.6</v>
+        <v>12.1</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -19494,70 +19494,70 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>-895385</v>
+        <v>-347830</v>
       </c>
       <c r="P110" t="n">
-        <v>90608</v>
+        <v>-339664</v>
       </c>
       <c r="Q110" t="n">
-        <v>839191</v>
+        <v>275347</v>
       </c>
       <c r="R110" t="n">
-        <v>-183866</v>
+        <v>3490236</v>
       </c>
       <c r="S110" t="n">
-        <v>-730195</v>
+        <v>-297882</v>
       </c>
       <c r="T110" t="n">
-        <v>-584651</v>
+        <v>-212504</v>
       </c>
       <c r="U110" t="n">
-        <v>177456</v>
+        <v>795588</v>
       </c>
       <c r="V110" t="n">
-        <v>-487055</v>
+        <v>3623968</v>
       </c>
       <c r="W110" t="n">
         <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>-211</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>-211</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>-15211</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>-165190</v>
+        <v>-49948</v>
       </c>
       <c r="AB110" t="n">
-        <v>675470</v>
+        <v>-127160</v>
       </c>
       <c r="AC110" t="n">
-        <v>661946</v>
+        <v>-520241</v>
       </c>
       <c r="AD110" t="n">
-        <v>318400</v>
+        <v>-133732</v>
       </c>
       <c r="AE110" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AF110" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AG110" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="AH110" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
       </c>
       <c r="AJ110" t="n">
-        <v>10</v>
+        <v>-30</v>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
@@ -19565,10 +19565,10 @@
         </is>
       </c>
       <c r="AL110" t="n">
-        <v>-16</v>
+        <v>26</v>
       </c>
       <c r="AM110" t="n">
-        <v>-160</v>
+        <v>86.67</v>
       </c>
       <c r="AN110" t="n">
         <v>0</v>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
@@ -19598,17 +19598,17 @@
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -19789,12 +19789,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>2498.TW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -19813,125 +19813,125 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>73</v>
+        <v>39.75</v>
       </c>
       <c r="G112" t="n">
-        <v>72.73999999999999</v>
+        <v>40.1</v>
       </c>
       <c r="H112" t="n">
-        <v>72.81999999999999</v>
+        <v>40.51</v>
       </c>
       <c r="I112" t="n">
-        <v>72.61</v>
+        <v>41.36</v>
       </c>
       <c r="J112" t="n">
-        <v>36223049</v>
+        <v>3517549</v>
       </c>
       <c r="K112" t="n">
-        <v>17341534</v>
+        <v>2873898</v>
       </c>
       <c r="L112" t="n">
-        <v>81</v>
+        <v>46.85</v>
       </c>
       <c r="M112" t="n">
-        <v>64.2</v>
+        <v>39.6</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>-2541256</v>
+        <v>-895385</v>
       </c>
       <c r="P112" t="n">
-        <v>-6327062</v>
+        <v>90608</v>
       </c>
       <c r="Q112" t="n">
-        <v>-5498046</v>
+        <v>839191</v>
       </c>
       <c r="R112" t="n">
-        <v>-5543345</v>
+        <v>-183866</v>
       </c>
       <c r="S112" t="n">
-        <v>-2161322</v>
+        <v>-730195</v>
       </c>
       <c r="T112" t="n">
-        <v>-7056057</v>
+        <v>-584651</v>
       </c>
       <c r="U112" t="n">
-        <v>-5983326</v>
+        <v>177456</v>
       </c>
       <c r="V112" t="n">
-        <v>-5138283</v>
+        <v>-487055</v>
       </c>
       <c r="W112" t="n">
         <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>-211</v>
       </c>
       <c r="Y112" t="n">
-        <v>-128000</v>
+        <v>-211</v>
       </c>
       <c r="Z112" t="n">
-        <v>-128000</v>
+        <v>-15211</v>
       </c>
       <c r="AA112" t="n">
-        <v>-379934</v>
+        <v>-165190</v>
       </c>
       <c r="AB112" t="n">
-        <v>728995</v>
+        <v>675470</v>
       </c>
       <c r="AC112" t="n">
-        <v>613280</v>
+        <v>661946</v>
       </c>
       <c r="AD112" t="n">
-        <v>-277062</v>
+        <v>318400</v>
       </c>
       <c r="AE112" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AF112" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AG112" t="n">
-        <v>65</v>
+        <v>-45</v>
       </c>
       <c r="AH112" t="n">
-        <v>-75</v>
+        <v>30</v>
       </c>
       <c r="AI112" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AJ112" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AL112" t="n">
         <v>-16</v>
       </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AL112" t="n">
-        <v>8</v>
-      </c>
       <c r="AM112" t="n">
-        <v>50</v>
+        <v>-160</v>
       </c>
       <c r="AN112" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="AO112" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -19946,17 +19946,17 @@
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、爆量、爆量價未漲</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、黃金交叉、爆量、爆量價未漲、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -20137,12 +20137,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8039.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -20161,99 +20161,99 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>266</v>
+        <v>73</v>
       </c>
       <c r="G114" t="n">
-        <v>293.1</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="H114" t="n">
-        <v>292.9</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>288.4</v>
+        <v>72.61</v>
       </c>
       <c r="J114" t="n">
-        <v>35048706</v>
+        <v>36223049</v>
       </c>
       <c r="K114" t="n">
-        <v>50873115</v>
+        <v>17341534</v>
       </c>
       <c r="L114" t="n">
-        <v>331.5</v>
+        <v>81</v>
       </c>
       <c r="M114" t="n">
-        <v>253</v>
+        <v>64.2</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>159515</v>
+        <v>-2541256</v>
       </c>
       <c r="P114" t="n">
-        <v>-5421886</v>
+        <v>-6327062</v>
       </c>
       <c r="Q114" t="n">
-        <v>-3170496</v>
+        <v>-5498046</v>
       </c>
       <c r="R114" t="n">
-        <v>-4196682</v>
+        <v>-5543345</v>
       </c>
       <c r="S114" t="n">
-        <v>343882</v>
+        <v>-2161322</v>
       </c>
       <c r="T114" t="n">
-        <v>-4501444</v>
+        <v>-7056057</v>
       </c>
       <c r="U114" t="n">
-        <v>-2549740</v>
+        <v>-5983326</v>
       </c>
       <c r="V114" t="n">
-        <v>-1681040</v>
+        <v>-5138283</v>
       </c>
       <c r="W114" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>15905</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>108905</v>
+        <v>-128000</v>
       </c>
       <c r="Z114" t="n">
-        <v>164905</v>
+        <v>-128000</v>
       </c>
       <c r="AA114" t="n">
-        <v>-187367</v>
+        <v>-379934</v>
       </c>
       <c r="AB114" t="n">
-        <v>-936347</v>
+        <v>728995</v>
       </c>
       <c r="AC114" t="n">
-        <v>-729661</v>
+        <v>613280</v>
       </c>
       <c r="AD114" t="n">
-        <v>-2680547</v>
+        <v>-277062</v>
       </c>
       <c r="AE114" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AF114" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AG114" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="AH114" t="n">
-        <v>-30</v>
+        <v>-75</v>
       </c>
       <c r="AI114" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ114" t="n">
-        <v>-30</v>
+        <v>-16</v>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
@@ -20261,25 +20261,25 @@
         </is>
       </c>
       <c r="AL114" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AM114" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="AN114" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="AO114" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
@@ -20294,17 +20294,17 @@
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、黃金交叉、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、黃金交叉、爆量、爆量價未漲、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -20833,12 +20833,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>8028.TW</t>
+          <t>8039.TW</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -20857,28 +20857,28 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>246.5</v>
+        <v>266</v>
       </c>
       <c r="G118" t="n">
-        <v>254.1</v>
+        <v>293.1</v>
       </c>
       <c r="H118" t="n">
-        <v>264.75</v>
+        <v>292.9</v>
       </c>
       <c r="I118" t="n">
-        <v>270.98</v>
+        <v>288.4</v>
       </c>
       <c r="J118" t="n">
-        <v>2725463</v>
+        <v>35048706</v>
       </c>
       <c r="K118" t="n">
-        <v>2938395</v>
+        <v>50873115</v>
       </c>
       <c r="L118" t="n">
-        <v>295.5</v>
+        <v>331.5</v>
       </c>
       <c r="M118" t="n">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -20886,52 +20886,52 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>-768454</v>
+        <v>159515</v>
       </c>
       <c r="P118" t="n">
-        <v>743953</v>
+        <v>-5421886</v>
       </c>
       <c r="Q118" t="n">
-        <v>948985</v>
+        <v>-3170496</v>
       </c>
       <c r="R118" t="n">
-        <v>-577059</v>
+        <v>-4196682</v>
       </c>
       <c r="S118" t="n">
-        <v>-707703</v>
+        <v>343882</v>
       </c>
       <c r="T118" t="n">
-        <v>803513</v>
+        <v>-4501444</v>
       </c>
       <c r="U118" t="n">
-        <v>1364232</v>
+        <v>-2549740</v>
       </c>
       <c r="V118" t="n">
-        <v>221255</v>
+        <v>-1681040</v>
       </c>
       <c r="W118" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="X118" t="n">
-        <v>-42</v>
+        <v>15905</v>
       </c>
       <c r="Y118" t="n">
-        <v>-357042</v>
+        <v>108905</v>
       </c>
       <c r="Z118" t="n">
-        <v>-434042</v>
+        <v>164905</v>
       </c>
       <c r="AA118" t="n">
-        <v>-60751</v>
+        <v>-187367</v>
       </c>
       <c r="AB118" t="n">
-        <v>-59518</v>
+        <v>-936347</v>
       </c>
       <c r="AC118" t="n">
-        <v>-58205</v>
+        <v>-729661</v>
       </c>
       <c r="AD118" t="n">
-        <v>-364272</v>
+        <v>-2680547</v>
       </c>
       <c r="AE118" t="n">
         <v>-10</v>
@@ -20940,16 +20940,16 @@
         <v>-10</v>
       </c>
       <c r="AG118" t="n">
-        <v>-55</v>
+        <v>5</v>
       </c>
       <c r="AH118" t="n">
-        <v>30</v>
+        <v>-30</v>
       </c>
       <c r="AI118" t="n">
         <v>0</v>
       </c>
       <c r="AJ118" t="n">
-        <v>26</v>
+        <v>-30</v>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
@@ -20957,16 +20957,16 @@
         </is>
       </c>
       <c r="AL118" t="n">
-        <v>-36</v>
+        <v>20</v>
       </c>
       <c r="AM118" t="n">
-        <v>-138.46</v>
+        <v>66.67</v>
       </c>
       <c r="AN118" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO118" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
@@ -20990,29 +20990,29 @@
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -21031,28 +21031,28 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>567</v>
+        <v>154.5</v>
       </c>
       <c r="G119" t="n">
-        <v>559.2</v>
+        <v>156.7</v>
       </c>
       <c r="H119" t="n">
-        <v>560.7</v>
+        <v>161.6</v>
       </c>
       <c r="I119" t="n">
-        <v>543.3</v>
+        <v>169.07</v>
       </c>
       <c r="J119" t="n">
-        <v>46056903</v>
+        <v>43722058</v>
       </c>
       <c r="K119" t="n">
-        <v>31610181</v>
+        <v>48195126</v>
       </c>
       <c r="L119" t="n">
-        <v>614</v>
+        <v>184</v>
       </c>
       <c r="M119" t="n">
-        <v>470</v>
+        <v>151</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -21060,52 +21060,52 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>-2801047</v>
+        <v>-2086985</v>
       </c>
       <c r="P119" t="n">
-        <v>-3047855</v>
+        <v>9953765</v>
       </c>
       <c r="Q119" t="n">
-        <v>-1217499</v>
+        <v>13114855</v>
       </c>
       <c r="R119" t="n">
-        <v>-7847215</v>
+        <v>-60269981</v>
       </c>
       <c r="S119" t="n">
-        <v>-2981974</v>
+        <v>-1707840</v>
       </c>
       <c r="T119" t="n">
-        <v>-5164239</v>
+        <v>10441528</v>
       </c>
       <c r="U119" t="n">
-        <v>-5166262</v>
+        <v>11649726</v>
       </c>
       <c r="V119" t="n">
-        <v>-14119684</v>
+        <v>-50944651</v>
       </c>
       <c r="W119" t="n">
-        <v>134000</v>
+        <v>-1100000</v>
       </c>
       <c r="X119" t="n">
-        <v>1751290</v>
+        <v>-3635594</v>
       </c>
       <c r="Y119" t="n">
-        <v>3577220</v>
+        <v>-5111975</v>
       </c>
       <c r="Z119" t="n">
-        <v>6670987</v>
+        <v>-9622910</v>
       </c>
       <c r="AA119" t="n">
-        <v>46927</v>
+        <v>720855</v>
       </c>
       <c r="AB119" t="n">
-        <v>365094</v>
+        <v>3147831</v>
       </c>
       <c r="AC119" t="n">
-        <v>371543</v>
+        <v>6577104</v>
       </c>
       <c r="AD119" t="n">
-        <v>-398518</v>
+        <v>297580</v>
       </c>
       <c r="AE119" t="n">
         <v>-10</v>
@@ -21114,16 +21114,16 @@
         <v>-10</v>
       </c>
       <c r="AG119" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AH119" t="n">
         <v>30</v>
       </c>
-      <c r="AH119" t="n">
-        <v>-55</v>
-      </c>
       <c r="AI119" t="n">
         <v>0</v>
       </c>
       <c r="AJ119" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
@@ -21131,25 +21131,25 @@
         </is>
       </c>
       <c r="AL119" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM119" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="AN119" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="AO119" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
@@ -21164,29 +21164,29 @@
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -21205,28 +21205,28 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>154.5</v>
+        <v>567</v>
       </c>
       <c r="G120" t="n">
-        <v>156.7</v>
+        <v>559.2</v>
       </c>
       <c r="H120" t="n">
-        <v>161.6</v>
+        <v>560.7</v>
       </c>
       <c r="I120" t="n">
-        <v>169.07</v>
+        <v>543.3</v>
       </c>
       <c r="J120" t="n">
-        <v>43722058</v>
+        <v>46056903</v>
       </c>
       <c r="K120" t="n">
-        <v>48195126</v>
+        <v>31610181</v>
       </c>
       <c r="L120" t="n">
-        <v>184</v>
+        <v>614</v>
       </c>
       <c r="M120" t="n">
-        <v>151</v>
+        <v>470</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -21234,52 +21234,52 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>-2086985</v>
+        <v>-2801047</v>
       </c>
       <c r="P120" t="n">
-        <v>9953765</v>
+        <v>-3047855</v>
       </c>
       <c r="Q120" t="n">
-        <v>13114855</v>
+        <v>-1217499</v>
       </c>
       <c r="R120" t="n">
-        <v>-60269981</v>
+        <v>-7847215</v>
       </c>
       <c r="S120" t="n">
-        <v>-1707840</v>
+        <v>-2981974</v>
       </c>
       <c r="T120" t="n">
-        <v>10441528</v>
+        <v>-5164239</v>
       </c>
       <c r="U120" t="n">
-        <v>11649726</v>
+        <v>-5166262</v>
       </c>
       <c r="V120" t="n">
-        <v>-50944651</v>
+        <v>-14119684</v>
       </c>
       <c r="W120" t="n">
-        <v>-1100000</v>
+        <v>134000</v>
       </c>
       <c r="X120" t="n">
-        <v>-3635594</v>
+        <v>1751290</v>
       </c>
       <c r="Y120" t="n">
-        <v>-5111975</v>
+        <v>3577220</v>
       </c>
       <c r="Z120" t="n">
-        <v>-9622910</v>
+        <v>6670987</v>
       </c>
       <c r="AA120" t="n">
-        <v>720855</v>
+        <v>46927</v>
       </c>
       <c r="AB120" t="n">
-        <v>3147831</v>
+        <v>365094</v>
       </c>
       <c r="AC120" t="n">
-        <v>6577104</v>
+        <v>371543</v>
       </c>
       <c r="AD120" t="n">
-        <v>297580</v>
+        <v>-398518</v>
       </c>
       <c r="AE120" t="n">
         <v>-10</v>
@@ -21288,16 +21288,16 @@
         <v>-10</v>
       </c>
       <c r="AG120" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH120" t="n">
         <v>-55</v>
       </c>
-      <c r="AH120" t="n">
-        <v>30</v>
-      </c>
       <c r="AI120" t="n">
         <v>0</v>
       </c>
       <c r="AJ120" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
@@ -21305,25 +21305,25 @@
         </is>
       </c>
       <c r="AL120" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AM120" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="AN120" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="AO120" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
@@ -21338,29 +21338,29 @@
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>8028.TW</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -21379,28 +21379,28 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>486</v>
+        <v>246.5</v>
       </c>
       <c r="G121" t="n">
-        <v>491.2</v>
+        <v>254.1</v>
       </c>
       <c r="H121" t="n">
-        <v>523.2</v>
+        <v>264.75</v>
       </c>
       <c r="I121" t="n">
-        <v>534.55</v>
+        <v>270.98</v>
       </c>
       <c r="J121" t="n">
-        <v>24584000</v>
+        <v>2725463</v>
       </c>
       <c r="K121" t="n">
-        <v>21512000</v>
+        <v>2938395</v>
       </c>
       <c r="L121" t="n">
-        <v>630</v>
+        <v>295.5</v>
       </c>
       <c r="M121" t="n">
-        <v>454</v>
+        <v>242</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -21408,70 +21408,70 @@
         </is>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>-768454</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>743953</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>948985</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>-577059</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>-707703</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>803513</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>1364232</v>
       </c>
       <c r="V121" t="n">
-        <v>0</v>
+        <v>221255</v>
       </c>
       <c r="W121" t="n">
         <v>0</v>
       </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>-357042</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>-434042</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>-60751</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>-59518</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>-58205</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>-364272</v>
       </c>
       <c r="AE121" t="n">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="AF121" t="n">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="AG121" t="n">
-        <v>-35</v>
+        <v>-55</v>
       </c>
       <c r="AH121" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
       </c>
       <c r="AJ121" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
@@ -21479,10 +21479,10 @@
         </is>
       </c>
       <c r="AL121" t="n">
-        <v>-16</v>
+        <v>-36</v>
       </c>
       <c r="AM121" t="n">
-        <v>-800</v>
+        <v>-138.46</v>
       </c>
       <c r="AN121" t="n">
         <v>0</v>
@@ -21512,29 +21512,29 @@
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1303.TW</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -21553,28 +21553,28 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>301</v>
+        <v>486</v>
       </c>
       <c r="G122" t="n">
-        <v>305.6</v>
+        <v>491.2</v>
       </c>
       <c r="H122" t="n">
-        <v>312.35</v>
+        <v>523.2</v>
       </c>
       <c r="I122" t="n">
-        <v>286.5</v>
+        <v>534.55</v>
       </c>
       <c r="J122" t="n">
-        <v>101068589</v>
+        <v>24584000</v>
       </c>
       <c r="K122" t="n">
-        <v>109993779</v>
+        <v>21512000</v>
       </c>
       <c r="L122" t="n">
-        <v>350.5</v>
+        <v>630</v>
       </c>
       <c r="M122" t="n">
-        <v>223</v>
+        <v>454</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -21582,52 +21582,52 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>-20712762</v>
+        <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>1581819</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>-21414183</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>-45835178</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>-20416205</v>
+        <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>-1375375</v>
+        <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>-29179722</v>
+        <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>-67652934</v>
+        <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>-475000</v>
+        <v>0</v>
       </c>
       <c r="X122" t="n">
-        <v>-1951004</v>
+        <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1020783</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>12490683</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>178443</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>4908198</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>6744756</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>9327073</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
         <v>-14</v>
@@ -21636,16 +21636,16 @@
         <v>-14</v>
       </c>
       <c r="AG122" t="n">
-        <v>-20</v>
+        <v>-35</v>
       </c>
       <c r="AH122" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
       </c>
       <c r="AJ122" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
@@ -21653,10 +21653,10 @@
         </is>
       </c>
       <c r="AL122" t="n">
-        <v>-20</v>
+        <v>-16</v>
       </c>
       <c r="AM122" t="n">
-        <v>-333.33</v>
+        <v>-800</v>
       </c>
       <c r="AN122" t="n">
         <v>0</v>
@@ -21671,7 +21671,7 @@
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
@@ -21686,17 +21686,17 @@
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -21877,12 +21877,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4967.TW</t>
+          <t>1303.TW</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -21901,28 +21901,28 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>250</v>
+        <v>301</v>
       </c>
       <c r="G124" t="n">
-        <v>252.1</v>
+        <v>305.6</v>
       </c>
       <c r="H124" t="n">
-        <v>258.2</v>
+        <v>312.35</v>
       </c>
       <c r="I124" t="n">
-        <v>264.6</v>
+        <v>286.5</v>
       </c>
       <c r="J124" t="n">
-        <v>866881</v>
+        <v>101068589</v>
       </c>
       <c r="K124" t="n">
-        <v>1081201</v>
+        <v>109993779</v>
       </c>
       <c r="L124" t="n">
-        <v>278.5</v>
+        <v>350.5</v>
       </c>
       <c r="M124" t="n">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
@@ -21930,52 +21930,52 @@
         </is>
       </c>
       <c r="O124" t="n">
-        <v>98223</v>
+        <v>-20712762</v>
       </c>
       <c r="P124" t="n">
-        <v>-81808</v>
+        <v>1581819</v>
       </c>
       <c r="Q124" t="n">
-        <v>390917</v>
+        <v>-21414183</v>
       </c>
       <c r="R124" t="n">
-        <v>-660921</v>
+        <v>-45835178</v>
       </c>
       <c r="S124" t="n">
-        <v>120555</v>
+        <v>-20416205</v>
       </c>
       <c r="T124" t="n">
-        <v>-26542</v>
+        <v>-1375375</v>
       </c>
       <c r="U124" t="n">
-        <v>421580</v>
+        <v>-29179722</v>
       </c>
       <c r="V124" t="n">
-        <v>-576564</v>
+        <v>-67652934</v>
       </c>
       <c r="W124" t="n">
-        <v>0</v>
+        <v>-475000</v>
       </c>
       <c r="X124" t="n">
-        <v>0</v>
+        <v>-1951004</v>
       </c>
       <c r="Y124" t="n">
-        <v>-3000</v>
+        <v>1020783</v>
       </c>
       <c r="Z124" t="n">
-        <v>-7000</v>
+        <v>12490683</v>
       </c>
       <c r="AA124" t="n">
-        <v>-22332</v>
+        <v>178443</v>
       </c>
       <c r="AB124" t="n">
-        <v>-55266</v>
+        <v>4908198</v>
       </c>
       <c r="AC124" t="n">
-        <v>-27663</v>
+        <v>6744756</v>
       </c>
       <c r="AD124" t="n">
-        <v>-77357</v>
+        <v>9327073</v>
       </c>
       <c r="AE124" t="n">
         <v>-14</v>
@@ -21984,16 +21984,16 @@
         <v>-14</v>
       </c>
       <c r="AG124" t="n">
-        <v>-55</v>
+        <v>-20</v>
       </c>
       <c r="AH124" t="n">
-        <v>20</v>
+        <v>-15</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
       </c>
       <c r="AJ124" t="n">
-        <v>-48</v>
+        <v>6</v>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
@@ -22001,10 +22001,10 @@
         </is>
       </c>
       <c r="AL124" t="n">
-        <v>34</v>
+        <v>-20</v>
       </c>
       <c r="AM124" t="n">
-        <v>70.83</v>
+        <v>-333.33</v>
       </c>
       <c r="AN124" t="n">
         <v>0</v>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
@@ -22034,17 +22034,17 @@
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -22104,16 +22104,16 @@
         </is>
       </c>
       <c r="O125" t="n">
-        <v>200786</v>
+        <v>321786</v>
       </c>
       <c r="P125" t="n">
-        <v>-147158</v>
+        <v>-26158</v>
       </c>
       <c r="Q125" t="n">
-        <v>261009</v>
+        <v>382009</v>
       </c>
       <c r="R125" t="n">
-        <v>-4196004</v>
+        <v>-4075004</v>
       </c>
       <c r="S125" t="n">
         <v>1277659</v>
@@ -22128,16 +22128,16 @@
         <v>7140903</v>
       </c>
       <c r="W125" t="n">
-        <v>-1065315</v>
+        <v>-944315</v>
       </c>
       <c r="X125" t="n">
-        <v>-1313479</v>
+        <v>-1192479</v>
       </c>
       <c r="Y125" t="n">
-        <v>-6829294</v>
+        <v>-6708294</v>
       </c>
       <c r="Z125" t="n">
-        <v>-11033562</v>
+        <v>-10912562</v>
       </c>
       <c r="AA125" t="n">
         <v>-11558</v>
@@ -22225,12 +22225,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>6230.TW</t>
+          <t>4967.TW</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>超眾</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -22249,28 +22249,28 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>108</v>
+        <v>250</v>
       </c>
       <c r="G126" t="n">
-        <v>109.8</v>
+        <v>252.1</v>
       </c>
       <c r="H126" t="n">
-        <v>111.25</v>
+        <v>258.2</v>
       </c>
       <c r="I126" t="n">
-        <v>111.88</v>
+        <v>264.6</v>
       </c>
       <c r="J126" t="n">
-        <v>59583</v>
+        <v>866881</v>
       </c>
       <c r="K126" t="n">
-        <v>39076</v>
+        <v>1081201</v>
       </c>
       <c r="L126" t="n">
-        <v>118.5</v>
+        <v>278.5</v>
       </c>
       <c r="M126" t="n">
-        <v>108</v>
+        <v>248</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
@@ -22278,28 +22278,28 @@
         </is>
       </c>
       <c r="O126" t="n">
-        <v>-12000</v>
+        <v>98223</v>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>-81808</v>
       </c>
       <c r="Q126" t="n">
-        <v>91</v>
+        <v>390917</v>
       </c>
       <c r="R126" t="n">
-        <v>-7732</v>
+        <v>-660921</v>
       </c>
       <c r="S126" t="n">
-        <v>-12000</v>
+        <v>120555</v>
       </c>
       <c r="T126" t="n">
-        <v>2000</v>
+        <v>-26542</v>
       </c>
       <c r="U126" t="n">
-        <v>2091</v>
+        <v>421580</v>
       </c>
       <c r="V126" t="n">
-        <v>-5410</v>
+        <v>-576564</v>
       </c>
       <c r="W126" t="n">
         <v>0</v>
@@ -22308,40 +22308,40 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>-22332</v>
       </c>
       <c r="AB126" t="n">
-        <v>-2000</v>
+        <v>-55266</v>
       </c>
       <c r="AC126" t="n">
-        <v>-2000</v>
+        <v>-27663</v>
       </c>
       <c r="AD126" t="n">
-        <v>-2322</v>
+        <v>-77357</v>
       </c>
       <c r="AE126" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AF126" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AG126" t="n">
-        <v>-40</v>
+        <v>-55</v>
       </c>
       <c r="AH126" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI126" t="n">
         <v>0</v>
       </c>
       <c r="AJ126" t="n">
-        <v>6</v>
+        <v>-48</v>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
@@ -22349,10 +22349,10 @@
         </is>
       </c>
       <c r="AL126" t="n">
-        <v>-22</v>
+        <v>34</v>
       </c>
       <c r="AM126" t="n">
-        <v>-366.67</v>
+        <v>70.83</v>
       </c>
       <c r="AN126" t="n">
         <v>0</v>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
@@ -22382,29 +22382,29 @@
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、成交量放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、成交量放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>6275.TWO</t>
+          <t>6230.TW</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>超眾</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -22423,28 +22423,28 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>44.5</v>
+        <v>108</v>
       </c>
       <c r="G127" t="n">
-        <v>44.86</v>
+        <v>109.8</v>
       </c>
       <c r="H127" t="n">
-        <v>45.41</v>
+        <v>111.25</v>
       </c>
       <c r="I127" t="n">
-        <v>46.12</v>
+        <v>111.88</v>
       </c>
       <c r="J127" t="n">
-        <v>187000</v>
+        <v>59583</v>
       </c>
       <c r="K127" t="n">
-        <v>108000</v>
+        <v>39076</v>
       </c>
       <c r="L127" t="n">
-        <v>48.05</v>
+        <v>118.5</v>
       </c>
       <c r="M127" t="n">
-        <v>44.5</v>
+        <v>108</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -22452,28 +22452,28 @@
         </is>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>-7732</v>
       </c>
       <c r="S127" t="n">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="T127" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="U127" t="n">
-        <v>0</v>
+        <v>2091</v>
       </c>
       <c r="V127" t="n">
-        <v>0</v>
+        <v>-5410</v>
       </c>
       <c r="W127" t="n">
         <v>0</v>
@@ -22491,13 +22491,13 @@
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="AD127" t="n">
-        <v>0</v>
+        <v>-2322</v>
       </c>
       <c r="AE127" t="n">
         <v>-16</v>
@@ -22515,7 +22515,7 @@
         <v>0</v>
       </c>
       <c r="AJ127" t="n">
-        <v>-18</v>
+        <v>6</v>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
@@ -22523,16 +22523,16 @@
         </is>
       </c>
       <c r="AL127" t="n">
-        <v>2</v>
+        <v>-22</v>
       </c>
       <c r="AM127" t="n">
-        <v>11.11</v>
+        <v>-366.67</v>
       </c>
       <c r="AN127" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AO127" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
@@ -22573,12 +22573,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>6275.TWO</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -22597,28 +22597,28 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>197</v>
+        <v>44.5</v>
       </c>
       <c r="G128" t="n">
-        <v>206.8</v>
+        <v>44.86</v>
       </c>
       <c r="H128" t="n">
-        <v>217.95</v>
+        <v>45.41</v>
       </c>
       <c r="I128" t="n">
-        <v>219.15</v>
+        <v>46.12</v>
       </c>
       <c r="J128" t="n">
-        <v>2276000</v>
+        <v>187000</v>
       </c>
       <c r="K128" t="n">
-        <v>2254200</v>
+        <v>108000</v>
       </c>
       <c r="L128" t="n">
-        <v>256</v>
+        <v>48.05</v>
       </c>
       <c r="M128" t="n">
-        <v>194</v>
+        <v>44.5</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -22674,39 +22674,39 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ128" t="n">
         <v>-18</v>
       </c>
-      <c r="AF128" t="n">
-        <v>-18</v>
-      </c>
-      <c r="AG128" t="n">
-        <v>-45</v>
-      </c>
-      <c r="AH128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ128" t="n">
-        <v>12</v>
-      </c>
       <c r="AK128" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
       <c r="AL128" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
       <c r="AM128" t="n">
-        <v>-250</v>
+        <v>11.11</v>
       </c>
       <c r="AN128" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO128" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
@@ -22730,7 +22730,7 @@
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
@@ -22740,19 +22740,19 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、成交量放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3081.TWO</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -22771,28 +22771,28 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2375</v>
+        <v>320</v>
       </c>
       <c r="G129" t="n">
-        <v>2521</v>
+        <v>337.9</v>
       </c>
       <c r="H129" t="n">
-        <v>2683.5</v>
+        <v>353.1</v>
       </c>
       <c r="I129" t="n">
-        <v>2751.5</v>
+        <v>371.68</v>
       </c>
       <c r="J129" t="n">
-        <v>3614000</v>
+        <v>2118000</v>
       </c>
       <c r="K129" t="n">
-        <v>3020400</v>
+        <v>1725400</v>
       </c>
       <c r="L129" t="n">
-        <v>3210</v>
+        <v>406.5</v>
       </c>
       <c r="M129" t="n">
-        <v>2365</v>
+        <v>320</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>0</v>
       </c>
       <c r="AJ129" t="n">
-        <v>-2</v>
+        <v>-22</v>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
@@ -22871,16 +22871,16 @@
         </is>
       </c>
       <c r="AL129" t="n">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="AM129" t="n">
-        <v>-800</v>
+        <v>18.18</v>
       </c>
       <c r="AN129" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO129" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
@@ -22921,12 +22921,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3211.TWO</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -22945,28 +22945,28 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>320</v>
+        <v>552</v>
       </c>
       <c r="G130" t="n">
-        <v>337.9</v>
+        <v>570.6</v>
       </c>
       <c r="H130" t="n">
-        <v>353.1</v>
+        <v>613.3</v>
       </c>
       <c r="I130" t="n">
-        <v>371.68</v>
+        <v>643.45</v>
       </c>
       <c r="J130" t="n">
-        <v>2118000</v>
+        <v>1815000</v>
       </c>
       <c r="K130" t="n">
-        <v>1725400</v>
+        <v>1636800</v>
       </c>
       <c r="L130" t="n">
-        <v>406.5</v>
+        <v>725</v>
       </c>
       <c r="M130" t="n">
-        <v>320</v>
+        <v>547</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>0</v>
       </c>
       <c r="AJ130" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
@@ -23045,16 +23045,16 @@
         </is>
       </c>
       <c r="AL130" t="n">
-        <v>4</v>
+        <v>-16</v>
       </c>
       <c r="AM130" t="n">
-        <v>18.18</v>
+        <v>-800</v>
       </c>
       <c r="AN130" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AO130" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
@@ -23095,12 +23095,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>3081.TWO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -23119,28 +23119,28 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>552</v>
+        <v>2375</v>
       </c>
       <c r="G131" t="n">
-        <v>570.6</v>
+        <v>2521</v>
       </c>
       <c r="H131" t="n">
-        <v>613.3</v>
+        <v>2683.5</v>
       </c>
       <c r="I131" t="n">
-        <v>643.45</v>
+        <v>2751.5</v>
       </c>
       <c r="J131" t="n">
-        <v>1815000</v>
+        <v>3614000</v>
       </c>
       <c r="K131" t="n">
-        <v>1636800</v>
+        <v>3020400</v>
       </c>
       <c r="L131" t="n">
-        <v>725</v>
+        <v>3210</v>
       </c>
       <c r="M131" t="n">
-        <v>547</v>
+        <v>2365</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -23269,12 +23269,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -23293,28 +23293,28 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1360</v>
+        <v>197</v>
       </c>
       <c r="G132" t="n">
-        <v>1387</v>
+        <v>206.8</v>
       </c>
       <c r="H132" t="n">
-        <v>1437</v>
+        <v>217.95</v>
       </c>
       <c r="I132" t="n">
-        <v>1503.5</v>
+        <v>219.15</v>
       </c>
       <c r="J132" t="n">
-        <v>4914000</v>
+        <v>2276000</v>
       </c>
       <c r="K132" t="n">
-        <v>3867000</v>
+        <v>2254200</v>
       </c>
       <c r="L132" t="n">
-        <v>1750</v>
+        <v>256</v>
       </c>
       <c r="M132" t="n">
-        <v>1320</v>
+        <v>194</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>0</v>
       </c>
       <c r="AJ132" t="n">
-        <v>-16</v>
+        <v>12</v>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
@@ -23393,10 +23393,10 @@
         </is>
       </c>
       <c r="AL132" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
       <c r="AM132" t="n">
-        <v>-12.5</v>
+        <v>-250</v>
       </c>
       <c r="AN132" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
@@ -23443,12 +23443,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -23467,28 +23467,28 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>200</v>
+        <v>1360</v>
       </c>
       <c r="G133" t="n">
-        <v>209.7</v>
+        <v>1387</v>
       </c>
       <c r="H133" t="n">
-        <v>220.8</v>
+        <v>1437</v>
       </c>
       <c r="I133" t="n">
-        <v>234.4</v>
+        <v>1503.5</v>
       </c>
       <c r="J133" t="n">
-        <v>1660000</v>
+        <v>4914000</v>
       </c>
       <c r="K133" t="n">
-        <v>1419000</v>
+        <v>3867000</v>
       </c>
       <c r="L133" t="n">
-        <v>264</v>
+        <v>1750</v>
       </c>
       <c r="M133" t="n">
-        <v>200</v>
+        <v>1320</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>0</v>
       </c>
       <c r="AJ133" t="n">
-        <v>-6</v>
+        <v>-16</v>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
@@ -23567,10 +23567,10 @@
         </is>
       </c>
       <c r="AL133" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="AM133" t="n">
-        <v>-200</v>
+        <v>-12.5</v>
       </c>
       <c r="AN133" t="n">
         <v>0</v>
@@ -23585,7 +23585,7 @@
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
@@ -24139,12 +24139,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1714.TW</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>和桐</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>18.3</v>
+        <v>200</v>
       </c>
       <c r="G137" t="n">
-        <v>18.85</v>
+        <v>209.7</v>
       </c>
       <c r="H137" t="n">
-        <v>19.37</v>
+        <v>220.8</v>
       </c>
       <c r="I137" t="n">
-        <v>18.19</v>
+        <v>234.4</v>
       </c>
       <c r="J137" t="n">
-        <v>15771882</v>
+        <v>1660000</v>
       </c>
       <c r="K137" t="n">
-        <v>18754431</v>
+        <v>1419000</v>
       </c>
       <c r="L137" t="n">
-        <v>20.9</v>
+        <v>264</v>
       </c>
       <c r="M137" t="n">
-        <v>15.55</v>
+        <v>200</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
@@ -24192,70 +24192,70 @@
         </is>
       </c>
       <c r="O137" t="n">
-        <v>872980</v>
+        <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>-1509171</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>-2053393</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>-5918380</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>1598406</v>
+        <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>478478</v>
+        <v>0</v>
       </c>
       <c r="U137" t="n">
-        <v>404009</v>
+        <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>-3817522</v>
+        <v>0</v>
       </c>
       <c r="W137" t="n">
-        <v>-460000</v>
+        <v>0</v>
       </c>
       <c r="X137" t="n">
-        <v>-1351000</v>
+        <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>-1571000</v>
+        <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>-1637000</v>
+        <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>-265426</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>-636649</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
-        <v>-886402</v>
+        <v>0</v>
       </c>
       <c r="AD137" t="n">
-        <v>-463858</v>
+        <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="AF137" t="n">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="AG137" t="n">
-        <v>-20</v>
+        <v>-45</v>
       </c>
       <c r="AH137" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="AI137" t="n">
         <v>0</v>
       </c>
       <c r="AJ137" t="n">
-        <v>-38</v>
+        <v>-6</v>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
@@ -24263,16 +24263,16 @@
         </is>
       </c>
       <c r="AL137" t="n">
-        <v>18</v>
+        <v>-12</v>
       </c>
       <c r="AM137" t="n">
-        <v>47.37</v>
+        <v>-200</v>
       </c>
       <c r="AN137" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO137" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
@@ -24296,29 +24296,29 @@
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2402.TW</t>
+          <t>1714.TW</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>毅嘉</t>
+          <t>和桐</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -24337,28 +24337,28 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>57.3</v>
+        <v>18.3</v>
       </c>
       <c r="G138" t="n">
-        <v>59.5</v>
+        <v>18.85</v>
       </c>
       <c r="H138" t="n">
-        <v>61.03</v>
+        <v>19.37</v>
       </c>
       <c r="I138" t="n">
-        <v>59.23</v>
+        <v>18.19</v>
       </c>
       <c r="J138" t="n">
-        <v>3317480</v>
+        <v>15771882</v>
       </c>
       <c r="K138" t="n">
-        <v>5540352</v>
+        <v>18754431</v>
       </c>
       <c r="L138" t="n">
-        <v>66.90000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="M138" t="n">
-        <v>53.1</v>
+        <v>15.55</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
@@ -24366,52 +24366,52 @@
         </is>
       </c>
       <c r="O138" t="n">
-        <v>394905</v>
+        <v>872980</v>
       </c>
       <c r="P138" t="n">
-        <v>1196246</v>
+        <v>-1509171</v>
       </c>
       <c r="Q138" t="n">
-        <v>-1389701</v>
+        <v>-2053393</v>
       </c>
       <c r="R138" t="n">
-        <v>1561578</v>
+        <v>-5918380</v>
       </c>
       <c r="S138" t="n">
-        <v>477087</v>
+        <v>1598406</v>
       </c>
       <c r="T138" t="n">
-        <v>1329798</v>
+        <v>478478</v>
       </c>
       <c r="U138" t="n">
-        <v>-818274</v>
+        <v>404009</v>
       </c>
       <c r="V138" t="n">
-        <v>1876287</v>
+        <v>-3817522</v>
       </c>
       <c r="W138" t="n">
-        <v>0</v>
+        <v>-460000</v>
       </c>
       <c r="X138" t="n">
-        <v>0</v>
+        <v>-1351000</v>
       </c>
       <c r="Y138" t="n">
-        <v>0</v>
+        <v>-1571000</v>
       </c>
       <c r="Z138" t="n">
-        <v>0</v>
+        <v>-1637000</v>
       </c>
       <c r="AA138" t="n">
-        <v>-82182</v>
+        <v>-265426</v>
       </c>
       <c r="AB138" t="n">
-        <v>-133552</v>
+        <v>-636649</v>
       </c>
       <c r="AC138" t="n">
-        <v>-571427</v>
+        <v>-886402</v>
       </c>
       <c r="AD138" t="n">
-        <v>-314709</v>
+        <v>-463858</v>
       </c>
       <c r="AE138" t="n">
         <v>-20</v>
@@ -24429,7 +24429,7 @@
         <v>0</v>
       </c>
       <c r="AJ138" t="n">
-        <v>-20</v>
+        <v>-38</v>
       </c>
       <c r="AK138" t="inlineStr">
         <is>
@@ -24437,16 +24437,16 @@
         </is>
       </c>
       <c r="AL138" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AM138" t="n">
-        <v>0</v>
+        <v>47.37</v>
       </c>
       <c r="AN138" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO138" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR138" t="inlineStr">
@@ -24475,24 +24475,24 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>2402.TW</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>毅嘉</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -24511,28 +24511,28 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>219.5</v>
+        <v>57.3</v>
       </c>
       <c r="G139" t="n">
-        <v>225</v>
+        <v>59.5</v>
       </c>
       <c r="H139" t="n">
-        <v>235.4</v>
+        <v>61.03</v>
       </c>
       <c r="I139" t="n">
-        <v>245.6</v>
+        <v>59.23</v>
       </c>
       <c r="J139" t="n">
-        <v>1034000</v>
+        <v>3317480</v>
       </c>
       <c r="K139" t="n">
-        <v>1037600</v>
+        <v>5540352</v>
       </c>
       <c r="L139" t="n">
-        <v>270</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M139" t="n">
-        <v>219</v>
+        <v>53.1</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
@@ -24540,28 +24540,28 @@
         </is>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>394905</v>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1196246</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>-1389701</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>1561578</v>
       </c>
       <c r="S139" t="n">
-        <v>0</v>
+        <v>477087</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>1329798</v>
       </c>
       <c r="U139" t="n">
-        <v>0</v>
+        <v>-818274</v>
       </c>
       <c r="V139" t="n">
-        <v>0</v>
+        <v>1876287</v>
       </c>
       <c r="W139" t="n">
         <v>0</v>
@@ -24576,34 +24576,34 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>-82182</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>-133552</v>
       </c>
       <c r="AC139" t="n">
-        <v>0</v>
+        <v>-571427</v>
       </c>
       <c r="AD139" t="n">
-        <v>0</v>
+        <v>-314709</v>
       </c>
       <c r="AE139" t="n">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="AF139" t="n">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="AG139" t="n">
-        <v>-55</v>
+        <v>-20</v>
       </c>
       <c r="AH139" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AI139" t="n">
         <v>0</v>
       </c>
       <c r="AJ139" t="n">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
@@ -24644,17 +24644,17 @@
       </c>
       <c r="AT139" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -27498,16 +27498,16 @@
         </is>
       </c>
       <c r="O156" t="n">
-        <v>-757000</v>
+        <v>-754000</v>
       </c>
       <c r="P156" t="n">
-        <v>-1969639</v>
+        <v>-1966639</v>
       </c>
       <c r="Q156" t="n">
-        <v>-3259393</v>
+        <v>-3256393</v>
       </c>
       <c r="R156" t="n">
-        <v>-2535732</v>
+        <v>-2532732</v>
       </c>
       <c r="S156" t="n">
         <v>-1033261</v>
@@ -27522,16 +27522,16 @@
         <v>-5500725</v>
       </c>
       <c r="W156" t="n">
-        <v>286000</v>
+        <v>289000</v>
       </c>
       <c r="X156" t="n">
-        <v>1286987</v>
+        <v>1289987</v>
       </c>
       <c r="Y156" t="n">
-        <v>2223078</v>
+        <v>2226078</v>
       </c>
       <c r="Z156" t="n">
-        <v>3353641</v>
+        <v>3356641</v>
       </c>
       <c r="AA156" t="n">
         <v>-9739</v>
@@ -27619,12 +27619,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>2345.TW</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -27643,28 +27643,28 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1085</v>
+        <v>1775</v>
       </c>
       <c r="G157" t="n">
-        <v>1090</v>
+        <v>1909</v>
       </c>
       <c r="H157" t="n">
-        <v>1141.5</v>
+        <v>1978.5</v>
       </c>
       <c r="I157" t="n">
-        <v>1184</v>
+        <v>1953.75</v>
       </c>
       <c r="J157" t="n">
-        <v>21289785</v>
+        <v>3503891</v>
       </c>
       <c r="K157" t="n">
-        <v>16356295</v>
+        <v>4690345</v>
       </c>
       <c r="L157" t="n">
-        <v>1420</v>
+        <v>2145</v>
       </c>
       <c r="M157" t="n">
-        <v>1040</v>
+        <v>1770</v>
       </c>
       <c r="N157" t="inlineStr">
         <is>
@@ -27672,52 +27672,52 @@
         </is>
       </c>
       <c r="O157" t="n">
-        <v>1464195</v>
+        <v>-112057</v>
       </c>
       <c r="P157" t="n">
-        <v>-1181326</v>
+        <v>-1719590</v>
       </c>
       <c r="Q157" t="n">
-        <v>-4139295</v>
+        <v>-495782</v>
       </c>
       <c r="R157" t="n">
-        <v>-10591492</v>
+        <v>-1300461</v>
       </c>
       <c r="S157" t="n">
-        <v>28150</v>
+        <v>-240640</v>
       </c>
       <c r="T157" t="n">
-        <v>-4189690</v>
+        <v>-2337460</v>
       </c>
       <c r="U157" t="n">
-        <v>-8727518</v>
+        <v>-1391694</v>
       </c>
       <c r="V157" t="n">
-        <v>-15368857</v>
+        <v>-4316414</v>
       </c>
       <c r="W157" t="n">
-        <v>1415000</v>
+        <v>86000</v>
       </c>
       <c r="X157" t="n">
-        <v>3092742</v>
+        <v>892530</v>
       </c>
       <c r="Y157" t="n">
-        <v>4882231</v>
+        <v>1184941</v>
       </c>
       <c r="Z157" t="n">
-        <v>4308307</v>
+        <v>3191710</v>
       </c>
       <c r="AA157" t="n">
-        <v>21045</v>
+        <v>42583</v>
       </c>
       <c r="AB157" t="n">
-        <v>-84378</v>
+        <v>-274660</v>
       </c>
       <c r="AC157" t="n">
-        <v>-294008</v>
+        <v>-289029</v>
       </c>
       <c r="AD157" t="n">
-        <v>469058</v>
+        <v>-175757</v>
       </c>
       <c r="AE157" t="n">
         <v>-30</v>
@@ -27726,16 +27726,16 @@
         <v>-30</v>
       </c>
       <c r="AG157" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AH157" t="n">
         <v>-45</v>
       </c>
-      <c r="AH157" t="n">
-        <v>-30</v>
-      </c>
       <c r="AI157" t="n">
         <v>0</v>
       </c>
       <c r="AJ157" t="n">
-        <v>-20</v>
+        <v>-38</v>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
@@ -27743,16 +27743,16 @@
         </is>
       </c>
       <c r="AL157" t="n">
-        <v>-10</v>
+        <v>8</v>
       </c>
       <c r="AM157" t="n">
-        <v>-50</v>
+        <v>21.05</v>
       </c>
       <c r="AN157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
@@ -27776,17 +27776,17 @@
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -27967,12 +27967,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2455.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -27991,28 +27991,28 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>467</v>
+        <v>1085</v>
       </c>
       <c r="G159" t="n">
-        <v>485.5</v>
+        <v>1090</v>
       </c>
       <c r="H159" t="n">
-        <v>506.4</v>
+        <v>1141.5</v>
       </c>
       <c r="I159" t="n">
-        <v>533.5</v>
+        <v>1184</v>
       </c>
       <c r="J159" t="n">
-        <v>4355682</v>
+        <v>21289785</v>
       </c>
       <c r="K159" t="n">
-        <v>5554332</v>
+        <v>16356295</v>
       </c>
       <c r="L159" t="n">
-        <v>613</v>
+        <v>1420</v>
       </c>
       <c r="M159" t="n">
-        <v>459</v>
+        <v>1040</v>
       </c>
       <c r="N159" t="inlineStr">
         <is>
@@ -28020,61 +28020,61 @@
         </is>
       </c>
       <c r="O159" t="n">
-        <v>830934</v>
+        <v>1464195</v>
       </c>
       <c r="P159" t="n">
-        <v>-1258224</v>
+        <v>-1181326</v>
       </c>
       <c r="Q159" t="n">
-        <v>-1911773</v>
+        <v>-4139295</v>
       </c>
       <c r="R159" t="n">
-        <v>-999268</v>
+        <v>-10591492</v>
       </c>
       <c r="S159" t="n">
-        <v>838251</v>
+        <v>28150</v>
       </c>
       <c r="T159" t="n">
-        <v>-1033882</v>
+        <v>-4189690</v>
       </c>
       <c r="U159" t="n">
-        <v>-1615929</v>
+        <v>-8727518</v>
       </c>
       <c r="V159" t="n">
-        <v>2884979</v>
+        <v>-15368857</v>
       </c>
       <c r="W159" t="n">
-        <v>56000</v>
+        <v>1415000</v>
       </c>
       <c r="X159" t="n">
-        <v>484971</v>
+        <v>3092742</v>
       </c>
       <c r="Y159" t="n">
-        <v>1119971</v>
+        <v>4882231</v>
       </c>
       <c r="Z159" t="n">
-        <v>-639029</v>
+        <v>4308307</v>
       </c>
       <c r="AA159" t="n">
-        <v>-63317</v>
+        <v>21045</v>
       </c>
       <c r="AB159" t="n">
-        <v>-709313</v>
+        <v>-84378</v>
       </c>
       <c r="AC159" t="n">
-        <v>-1415815</v>
+        <v>-294008</v>
       </c>
       <c r="AD159" t="n">
-        <v>-3245218</v>
+        <v>469058</v>
       </c>
       <c r="AE159" t="n">
-        <v>-34</v>
+        <v>-30</v>
       </c>
       <c r="AF159" t="n">
-        <v>-34</v>
+        <v>-30</v>
       </c>
       <c r="AG159" t="n">
-        <v>-55</v>
+        <v>-45</v>
       </c>
       <c r="AH159" t="n">
         <v>-30</v>
@@ -28083,7 +28083,7 @@
         <v>0</v>
       </c>
       <c r="AJ159" t="n">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="AK159" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>-10</v>
       </c>
       <c r="AM159" t="n">
-        <v>-41.67</v>
+        <v>-50</v>
       </c>
       <c r="AN159" t="n">
         <v>0</v>
@@ -28109,7 +28109,7 @@
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
@@ -28124,7 +28124,7 @@
       </c>
       <c r="AT159" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU159" t="inlineStr">
@@ -28134,7 +28134,7 @@
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -28315,12 +28315,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2345.TW</t>
+          <t>3017.TW</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -28339,28 +28339,28 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1775</v>
+        <v>3145</v>
       </c>
       <c r="G161" t="n">
-        <v>1909</v>
+        <v>3268</v>
       </c>
       <c r="H161" t="n">
-        <v>1978.5</v>
+        <v>3284.5</v>
       </c>
       <c r="I161" t="n">
-        <v>1953.75</v>
+        <v>3393</v>
       </c>
       <c r="J161" t="n">
-        <v>3503891</v>
+        <v>2517842</v>
       </c>
       <c r="K161" t="n">
-        <v>4690345</v>
+        <v>3071917</v>
       </c>
       <c r="L161" t="n">
-        <v>2145</v>
+        <v>3700</v>
       </c>
       <c r="M161" t="n">
-        <v>1770</v>
+        <v>3050</v>
       </c>
       <c r="N161" t="inlineStr">
         <is>
@@ -28368,52 +28368,52 @@
         </is>
       </c>
       <c r="O161" t="n">
-        <v>-119057</v>
+        <v>283422</v>
       </c>
       <c r="P161" t="n">
-        <v>-1726590</v>
+        <v>-353479</v>
       </c>
       <c r="Q161" t="n">
-        <v>-502782</v>
+        <v>-530680</v>
       </c>
       <c r="R161" t="n">
-        <v>-1307461</v>
+        <v>-2978608</v>
       </c>
       <c r="S161" t="n">
-        <v>-240640</v>
+        <v>69641</v>
       </c>
       <c r="T161" t="n">
-        <v>-2337460</v>
+        <v>-1701298</v>
       </c>
       <c r="U161" t="n">
-        <v>-1391694</v>
+        <v>-2952656</v>
       </c>
       <c r="V161" t="n">
-        <v>-4316414</v>
+        <v>-5542240</v>
       </c>
       <c r="W161" t="n">
-        <v>79000</v>
+        <v>212000</v>
       </c>
       <c r="X161" t="n">
-        <v>885530</v>
+        <v>1545202</v>
       </c>
       <c r="Y161" t="n">
-        <v>1177941</v>
+        <v>2645815</v>
       </c>
       <c r="Z161" t="n">
-        <v>3184710</v>
+        <v>2853290</v>
       </c>
       <c r="AA161" t="n">
-        <v>42583</v>
+        <v>1781</v>
       </c>
       <c r="AB161" t="n">
-        <v>-274660</v>
+        <v>-197383</v>
       </c>
       <c r="AC161" t="n">
-        <v>-289029</v>
+        <v>-223839</v>
       </c>
       <c r="AD161" t="n">
-        <v>-175757</v>
+        <v>-289658</v>
       </c>
       <c r="AE161" t="n">
         <v>-34</v>
@@ -28422,16 +28422,16 @@
         <v>-34</v>
       </c>
       <c r="AG161" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AH161" t="n">
         <v>-30</v>
       </c>
-      <c r="AH161" t="n">
-        <v>-55</v>
-      </c>
       <c r="AI161" t="n">
         <v>0</v>
       </c>
       <c r="AJ161" t="n">
-        <v>-38</v>
+        <v>-36</v>
       </c>
       <c r="AK161" t="inlineStr">
         <is>
@@ -28439,10 +28439,10 @@
         </is>
       </c>
       <c r="AL161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AM161" t="n">
-        <v>10.53</v>
+        <v>5.56</v>
       </c>
       <c r="AN161" t="n">
         <v>3</v>
@@ -28472,29 +28472,29 @@
       </c>
       <c r="AT161" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3017.TW</t>
+          <t>2455.TW</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -28513,28 +28513,28 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>3145</v>
+        <v>467</v>
       </c>
       <c r="G162" t="n">
-        <v>3268</v>
+        <v>485.5</v>
       </c>
       <c r="H162" t="n">
-        <v>3284.5</v>
+        <v>506.4</v>
       </c>
       <c r="I162" t="n">
-        <v>3393</v>
+        <v>533.5</v>
       </c>
       <c r="J162" t="n">
-        <v>2517842</v>
+        <v>4355682</v>
       </c>
       <c r="K162" t="n">
-        <v>3071917</v>
+        <v>5554332</v>
       </c>
       <c r="L162" t="n">
-        <v>3700</v>
+        <v>613</v>
       </c>
       <c r="M162" t="n">
-        <v>3050</v>
+        <v>459</v>
       </c>
       <c r="N162" t="inlineStr">
         <is>
@@ -28542,52 +28542,52 @@
         </is>
       </c>
       <c r="O162" t="n">
-        <v>283422</v>
+        <v>830934</v>
       </c>
       <c r="P162" t="n">
-        <v>-353479</v>
+        <v>-1258224</v>
       </c>
       <c r="Q162" t="n">
-        <v>-530680</v>
+        <v>-1911773</v>
       </c>
       <c r="R162" t="n">
-        <v>-2978608</v>
+        <v>-999268</v>
       </c>
       <c r="S162" t="n">
-        <v>69641</v>
+        <v>838251</v>
       </c>
       <c r="T162" t="n">
-        <v>-1701298</v>
+        <v>-1033882</v>
       </c>
       <c r="U162" t="n">
-        <v>-2952656</v>
+        <v>-1615929</v>
       </c>
       <c r="V162" t="n">
-        <v>-5542240</v>
+        <v>2884979</v>
       </c>
       <c r="W162" t="n">
-        <v>212000</v>
+        <v>56000</v>
       </c>
       <c r="X162" t="n">
-        <v>1545202</v>
+        <v>484971</v>
       </c>
       <c r="Y162" t="n">
-        <v>2645815</v>
+        <v>1119971</v>
       </c>
       <c r="Z162" t="n">
-        <v>2853290</v>
+        <v>-639029</v>
       </c>
       <c r="AA162" t="n">
-        <v>1781</v>
+        <v>-63317</v>
       </c>
       <c r="AB162" t="n">
-        <v>-197383</v>
+        <v>-709313</v>
       </c>
       <c r="AC162" t="n">
-        <v>-223839</v>
+        <v>-1415815</v>
       </c>
       <c r="AD162" t="n">
-        <v>-289658</v>
+        <v>-3245218</v>
       </c>
       <c r="AE162" t="n">
         <v>-34</v>
@@ -28605,7 +28605,7 @@
         <v>0</v>
       </c>
       <c r="AJ162" t="n">
-        <v>-36</v>
+        <v>-24</v>
       </c>
       <c r="AK162" t="inlineStr">
         <is>
@@ -28613,16 +28613,16 @@
         </is>
       </c>
       <c r="AL162" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="AM162" t="n">
-        <v>5.56</v>
+        <v>-41.67</v>
       </c>
       <c r="AN162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
@@ -32544,16 +32544,16 @@
         </is>
       </c>
       <c r="O185" t="n">
-        <v>-10149126</v>
+        <v>-10149175</v>
       </c>
       <c r="P185" t="n">
-        <v>-24316916</v>
+        <v>-24316965</v>
       </c>
       <c r="Q185" t="n">
-        <v>-51292718</v>
+        <v>-51292767</v>
       </c>
       <c r="R185" t="n">
-        <v>-118777328</v>
+        <v>-118777377</v>
       </c>
       <c r="S185" t="n">
         <v>-12694626</v>
@@ -32568,16 +32568,16 @@
         <v>-148324642</v>
       </c>
       <c r="W185" t="n">
-        <v>1350000</v>
+        <v>1349951</v>
       </c>
       <c r="X185" t="n">
-        <v>3777185</v>
+        <v>3777136</v>
       </c>
       <c r="Y185" t="n">
-        <v>8371999</v>
+        <v>8371950</v>
       </c>
       <c r="Z185" t="n">
-        <v>16793752</v>
+        <v>16793703</v>
       </c>
       <c r="AA185" t="n">
         <v>1195500</v>
@@ -32892,16 +32892,16 @@
         </is>
       </c>
       <c r="O187" t="n">
-        <v>-5585000</v>
+        <v>-5575000</v>
       </c>
       <c r="P187" t="n">
-        <v>-19219916</v>
+        <v>-19209916</v>
       </c>
       <c r="Q187" t="n">
-        <v>-2652491</v>
+        <v>-2642491</v>
       </c>
       <c r="R187" t="n">
-        <v>1994695</v>
+        <v>2004695</v>
       </c>
       <c r="S187" t="n">
         <v>-5006961</v>
@@ -32916,16 +32916,16 @@
         <v>-4894721</v>
       </c>
       <c r="W187" t="n">
-        <v>131000</v>
+        <v>141000</v>
       </c>
       <c r="X187" t="n">
-        <v>1098661</v>
+        <v>1108661</v>
       </c>
       <c r="Y187" t="n">
-        <v>3533901</v>
+        <v>3543901</v>
       </c>
       <c r="Z187" t="n">
-        <v>8949901</v>
+        <v>8959901</v>
       </c>
       <c r="AA187" t="n">
         <v>-709039</v>
@@ -35154,16 +35154,16 @@
         </is>
       </c>
       <c r="O200" t="n">
-        <v>-3680279</v>
+        <v>-3679399</v>
       </c>
       <c r="P200" t="n">
-        <v>-4004851</v>
+        <v>-4003971</v>
       </c>
       <c r="Q200" t="n">
-        <v>-17046712</v>
+        <v>-17045832</v>
       </c>
       <c r="R200" t="n">
-        <v>-91849745</v>
+        <v>-91848865</v>
       </c>
       <c r="S200" t="n">
         <v>-1522533</v>
@@ -35178,16 +35178,16 @@
         <v>-75591480</v>
       </c>
       <c r="W200" t="n">
-        <v>-2186000</v>
+        <v>-2185120</v>
       </c>
       <c r="X200" t="n">
-        <v>-3598230</v>
+        <v>-3597350</v>
       </c>
       <c r="Y200" t="n">
-        <v>-4428031</v>
+        <v>-4427151</v>
       </c>
       <c r="Z200" t="n">
-        <v>-16032738</v>
+        <v>-16031858</v>
       </c>
       <c r="AA200" t="n">
         <v>28254</v>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -13179,12 +13179,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>6269.TW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -13203,28 +13203,28 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>254</v>
+        <v>78.7</v>
       </c>
       <c r="G74" t="n">
-        <v>253.3</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>247.8</v>
+        <v>74.73</v>
       </c>
       <c r="I74" t="n">
-        <v>254.18</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>2609000</v>
+        <v>83826860</v>
       </c>
       <c r="K74" t="n">
-        <v>1326000</v>
+        <v>93011683</v>
       </c>
       <c r="L74" t="n">
-        <v>280.5</v>
+        <v>93</v>
       </c>
       <c r="M74" t="n">
-        <v>237</v>
+        <v>60.3</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -13232,28 +13232,28 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>-1491851</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>-1612670</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>1679769</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2443765</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>-1582984</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>-2325211</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1013186</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>1942528</v>
       </c>
       <c r="W74" t="n">
         <v>0</v>
@@ -13268,16 +13268,16 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>91133</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>712541</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>666583</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>501237</v>
       </c>
       <c r="AE74" t="n">
         <v>14</v>
@@ -13286,42 +13286,42 @@
         <v>14</v>
       </c>
       <c r="AG74" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
       </c>
       <c r="AJ74" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AL74" t="n">
-        <v>6</v>
+        <v>-34</v>
       </c>
       <c r="AM74" t="n">
-        <v>75</v>
+        <v>-70.83</v>
       </c>
       <c r="AN74" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="AO74" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、量能偏強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
@@ -13336,17 +13336,17 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14049,12 +14049,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6269.TW</t>
+          <t>6191.TW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -14073,28 +14073,28 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>78.7</v>
+        <v>89.8</v>
       </c>
       <c r="G79" t="n">
-        <v>83.18000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="H79" t="n">
-        <v>74.73</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>69.90000000000001</v>
+        <v>88.23</v>
       </c>
       <c r="J79" t="n">
-        <v>83826860</v>
+        <v>2757587</v>
       </c>
       <c r="K79" t="n">
-        <v>93011683</v>
+        <v>4388925</v>
       </c>
       <c r="L79" t="n">
-        <v>93</v>
+        <v>97.5</v>
       </c>
       <c r="M79" t="n">
-        <v>60.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -14102,70 +14102,70 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>-1491851</v>
+        <v>-74047</v>
       </c>
       <c r="P79" t="n">
-        <v>-1612670</v>
+        <v>980186</v>
       </c>
       <c r="Q79" t="n">
-        <v>1679769</v>
+        <v>1044806</v>
       </c>
       <c r="R79" t="n">
-        <v>2443765</v>
+        <v>-2269779</v>
       </c>
       <c r="S79" t="n">
-        <v>-1582984</v>
+        <v>-8752</v>
       </c>
       <c r="T79" t="n">
-        <v>-2325211</v>
+        <v>945148</v>
       </c>
       <c r="U79" t="n">
-        <v>1013186</v>
+        <v>755836</v>
       </c>
       <c r="V79" t="n">
-        <v>1942528</v>
+        <v>-2818002</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>22979</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>45979</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>100979</v>
       </c>
       <c r="AA79" t="n">
-        <v>91133</v>
+        <v>-70295</v>
       </c>
       <c r="AB79" t="n">
-        <v>712541</v>
+        <v>12059</v>
       </c>
       <c r="AC79" t="n">
-        <v>666583</v>
+        <v>242991</v>
       </c>
       <c r="AD79" t="n">
-        <v>501237</v>
+        <v>447244</v>
       </c>
       <c r="AE79" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AF79" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG79" t="n">
-        <v>5</v>
+        <v>-20</v>
       </c>
       <c r="AH79" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
       </c>
       <c r="AJ79" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
@@ -14173,16 +14173,16 @@
         </is>
       </c>
       <c r="AL79" t="n">
-        <v>-34</v>
+        <v>-16</v>
       </c>
       <c r="AM79" t="n">
-        <v>-70.83</v>
+        <v>-57.14</v>
       </c>
       <c r="AN79" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO79" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
@@ -14206,17 +14206,17 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -14745,12 +14745,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6191.TW</t>
+          <t>4766.TW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -14769,28 +14769,28 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>89.8</v>
+        <v>357.5</v>
       </c>
       <c r="G83" t="n">
-        <v>91.16</v>
+        <v>358.8</v>
       </c>
       <c r="H83" t="n">
-        <v>91.90000000000001</v>
+        <v>359.1</v>
       </c>
       <c r="I83" t="n">
-        <v>88.23</v>
+        <v>352.73</v>
       </c>
       <c r="J83" t="n">
-        <v>2757587</v>
+        <v>162953</v>
       </c>
       <c r="K83" t="n">
-        <v>4388925</v>
+        <v>170422</v>
       </c>
       <c r="L83" t="n">
-        <v>97.5</v>
+        <v>369.5</v>
       </c>
       <c r="M83" t="n">
-        <v>82.09999999999999</v>
+        <v>339.5</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -14798,52 +14798,52 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>-74047</v>
+        <v>92938</v>
       </c>
       <c r="P83" t="n">
-        <v>980186</v>
+        <v>167019</v>
       </c>
       <c r="Q83" t="n">
-        <v>1044806</v>
+        <v>273654</v>
       </c>
       <c r="R83" t="n">
-        <v>-2269779</v>
+        <v>871513</v>
       </c>
       <c r="S83" t="n">
-        <v>-8752</v>
+        <v>93455</v>
       </c>
       <c r="T83" t="n">
-        <v>945148</v>
+        <v>172180</v>
       </c>
       <c r="U83" t="n">
-        <v>755836</v>
+        <v>323515</v>
       </c>
       <c r="V83" t="n">
-        <v>-2818002</v>
+        <v>948417</v>
       </c>
       <c r="W83" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>22979</v>
+        <v>-23</v>
       </c>
       <c r="Y83" t="n">
-        <v>45979</v>
+        <v>-38023</v>
       </c>
       <c r="Z83" t="n">
-        <v>100979</v>
+        <v>-58023</v>
       </c>
       <c r="AA83" t="n">
-        <v>-70295</v>
+        <v>-517</v>
       </c>
       <c r="AB83" t="n">
-        <v>12059</v>
+        <v>-5138</v>
       </c>
       <c r="AC83" t="n">
-        <v>242991</v>
+        <v>-11838</v>
       </c>
       <c r="AD83" t="n">
-        <v>447244</v>
+        <v>-18881</v>
       </c>
       <c r="AE83" t="n">
         <v>12</v>
@@ -14861,7 +14861,7 @@
         <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
@@ -14869,10 +14869,10 @@
         </is>
       </c>
       <c r="AL83" t="n">
-        <v>-16</v>
+        <v>-26</v>
       </c>
       <c r="AM83" t="n">
-        <v>-57.14</v>
+        <v>-68.42</v>
       </c>
       <c r="AN83" t="n">
         <v>0</v>
@@ -14907,24 +14907,24 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4766.TW</t>
+          <t>2610.TW</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -14943,28 +14943,28 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>357.5</v>
+        <v>20.5</v>
       </c>
       <c r="G84" t="n">
-        <v>358.8</v>
+        <v>20.57</v>
       </c>
       <c r="H84" t="n">
-        <v>359.1</v>
+        <v>20.51</v>
       </c>
       <c r="I84" t="n">
-        <v>352.73</v>
+        <v>20.41</v>
       </c>
       <c r="J84" t="n">
-        <v>162953</v>
+        <v>13512197</v>
       </c>
       <c r="K84" t="n">
-        <v>170422</v>
+        <v>21072753</v>
       </c>
       <c r="L84" t="n">
-        <v>369.5</v>
+        <v>21.2</v>
       </c>
       <c r="M84" t="n">
-        <v>339.5</v>
+        <v>20</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -14972,70 +14972,70 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>92938</v>
+        <v>5716240</v>
       </c>
       <c r="P84" t="n">
-        <v>167019</v>
+        <v>-4550860</v>
       </c>
       <c r="Q84" t="n">
-        <v>273654</v>
+        <v>19188836</v>
       </c>
       <c r="R84" t="n">
-        <v>871513</v>
+        <v>54853461</v>
       </c>
       <c r="S84" t="n">
-        <v>93455</v>
+        <v>5578240</v>
       </c>
       <c r="T84" t="n">
-        <v>172180</v>
+        <v>325011</v>
       </c>
       <c r="U84" t="n">
-        <v>323515</v>
+        <v>22644039</v>
       </c>
       <c r="V84" t="n">
-        <v>948417</v>
+        <v>58141349</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>167000</v>
       </c>
       <c r="X84" t="n">
-        <v>-23</v>
+        <v>-4222180</v>
       </c>
       <c r="Y84" t="n">
-        <v>-38023</v>
+        <v>-2847180</v>
       </c>
       <c r="Z84" t="n">
-        <v>-58023</v>
+        <v>115820</v>
       </c>
       <c r="AA84" t="n">
-        <v>-517</v>
+        <v>-29000</v>
       </c>
       <c r="AB84" t="n">
-        <v>-5138</v>
+        <v>-653691</v>
       </c>
       <c r="AC84" t="n">
-        <v>-11838</v>
+        <v>-608023</v>
       </c>
       <c r="AD84" t="n">
-        <v>-18881</v>
+        <v>-3403708</v>
       </c>
       <c r="AE84" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF84" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG84" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
       <c r="AH84" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
       </c>
       <c r="AJ84" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
@@ -15043,16 +15043,16 @@
         </is>
       </c>
       <c r="AL84" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
       <c r="AM84" t="n">
-        <v>-68.42</v>
+        <v>0</v>
       </c>
       <c r="AN84" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO84" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AR84" t="inlineStr">
@@ -15076,29 +15076,29 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2610.TW</t>
+          <t>3443.TW</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -15117,28 +15117,28 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>20.5</v>
+        <v>7585</v>
       </c>
       <c r="G85" t="n">
-        <v>20.57</v>
+        <v>7728</v>
       </c>
       <c r="H85" t="n">
-        <v>20.51</v>
+        <v>7911</v>
       </c>
       <c r="I85" t="n">
-        <v>20.41</v>
+        <v>8079.75</v>
       </c>
       <c r="J85" t="n">
-        <v>13512197</v>
+        <v>1513570</v>
       </c>
       <c r="K85" t="n">
-        <v>21072753</v>
+        <v>1737989</v>
       </c>
       <c r="L85" t="n">
-        <v>21.2</v>
+        <v>8750</v>
       </c>
       <c r="M85" t="n">
-        <v>20</v>
+        <v>7065</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -15146,52 +15146,52 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>5716240</v>
+        <v>70545</v>
       </c>
       <c r="P85" t="n">
-        <v>-4550860</v>
+        <v>295418</v>
       </c>
       <c r="Q85" t="n">
-        <v>19188836</v>
+        <v>425950</v>
       </c>
       <c r="R85" t="n">
-        <v>54853461</v>
+        <v>1200037</v>
       </c>
       <c r="S85" t="n">
-        <v>5578240</v>
+        <v>32133</v>
       </c>
       <c r="T85" t="n">
-        <v>325011</v>
+        <v>28710</v>
       </c>
       <c r="U85" t="n">
-        <v>22644039</v>
+        <v>36848</v>
       </c>
       <c r="V85" t="n">
-        <v>58141349</v>
+        <v>584120</v>
       </c>
       <c r="W85" t="n">
-        <v>167000</v>
+        <v>39000</v>
       </c>
       <c r="X85" t="n">
-        <v>-4222180</v>
+        <v>315807</v>
       </c>
       <c r="Y85" t="n">
-        <v>-2847180</v>
+        <v>555115</v>
       </c>
       <c r="Z85" t="n">
-        <v>115820</v>
+        <v>833814</v>
       </c>
       <c r="AA85" t="n">
-        <v>-29000</v>
+        <v>-588</v>
       </c>
       <c r="AB85" t="n">
-        <v>-653691</v>
+        <v>-49099</v>
       </c>
       <c r="AC85" t="n">
-        <v>-608023</v>
+        <v>-166013</v>
       </c>
       <c r="AD85" t="n">
-        <v>-3403708</v>
+        <v>-217897</v>
       </c>
       <c r="AE85" t="n">
         <v>10</v>
@@ -15200,16 +15200,16 @@
         <v>10</v>
       </c>
       <c r="AG85" t="n">
-        <v>-5</v>
+        <v>-45</v>
       </c>
       <c r="AH85" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
       </c>
       <c r="AJ85" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
@@ -15217,16 +15217,16 @@
         </is>
       </c>
       <c r="AL85" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AM85" t="n">
-        <v>0</v>
+        <v>-70.59</v>
       </c>
       <c r="AN85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AO85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
@@ -15250,29 +15250,29 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏買、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>3702.TW</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -15291,28 +15291,28 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>5070</v>
+        <v>114.5</v>
       </c>
       <c r="G86" t="n">
-        <v>5059</v>
+        <v>114.8</v>
       </c>
       <c r="H86" t="n">
-        <v>5363</v>
+        <v>115.9</v>
       </c>
       <c r="I86" t="n">
-        <v>5311</v>
+        <v>116.42</v>
       </c>
       <c r="J86" t="n">
-        <v>4750904</v>
+        <v>8371199</v>
       </c>
       <c r="K86" t="n">
-        <v>2761928</v>
+        <v>9376851</v>
       </c>
       <c r="L86" t="n">
-        <v>6325</v>
+        <v>122</v>
       </c>
       <c r="M86" t="n">
-        <v>4855</v>
+        <v>111.5</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -15320,52 +15320,52 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>263098</v>
+        <v>956731</v>
       </c>
       <c r="P86" t="n">
-        <v>-113477</v>
+        <v>5234216</v>
       </c>
       <c r="Q86" t="n">
-        <v>-255029</v>
+        <v>5848199</v>
       </c>
       <c r="R86" t="n">
-        <v>-1626147</v>
+        <v>22107911</v>
       </c>
       <c r="S86" t="n">
-        <v>162970</v>
+        <v>314154</v>
       </c>
       <c r="T86" t="n">
-        <v>-182721</v>
+        <v>3451507</v>
       </c>
       <c r="U86" t="n">
-        <v>30323</v>
+        <v>2157216</v>
       </c>
       <c r="V86" t="n">
-        <v>-1988857</v>
+        <v>16036507</v>
       </c>
       <c r="W86" t="n">
-        <v>36400</v>
+        <v>230000</v>
       </c>
       <c r="X86" t="n">
-        <v>243960</v>
+        <v>661924</v>
       </c>
       <c r="Y86" t="n">
-        <v>73616</v>
+        <v>2235964</v>
       </c>
       <c r="Z86" t="n">
-        <v>540262</v>
+        <v>2840757</v>
       </c>
       <c r="AA86" t="n">
-        <v>63728</v>
+        <v>412577</v>
       </c>
       <c r="AB86" t="n">
-        <v>-174716</v>
+        <v>1120785</v>
       </c>
       <c r="AC86" t="n">
-        <v>-358968</v>
+        <v>1455019</v>
       </c>
       <c r="AD86" t="n">
-        <v>-177552</v>
+        <v>3230647</v>
       </c>
       <c r="AE86" t="n">
         <v>10</v>
@@ -15374,16 +15374,16 @@
         <v>10</v>
       </c>
       <c r="AG86" t="n">
-        <v>25</v>
+        <v>-55</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
       </c>
       <c r="AJ86" t="n">
-        <v>-34</v>
+        <v>24</v>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
@@ -15391,25 +15391,25 @@
         </is>
       </c>
       <c r="AL86" t="n">
-        <v>44</v>
+        <v>-14</v>
       </c>
       <c r="AM86" t="n">
-        <v>129.41</v>
+        <v>-58.33</v>
       </c>
       <c r="AN86" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AO86" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
@@ -15424,29 +15424,29 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>5日法人賣超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、接近20日低點、5日法人賣超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3443.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -15465,28 +15465,28 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>7585</v>
+        <v>5070</v>
       </c>
       <c r="G87" t="n">
-        <v>7728</v>
+        <v>5059</v>
       </c>
       <c r="H87" t="n">
-        <v>7911</v>
+        <v>5363</v>
       </c>
       <c r="I87" t="n">
-        <v>8079.75</v>
+        <v>5311</v>
       </c>
       <c r="J87" t="n">
-        <v>1513570</v>
+        <v>4750904</v>
       </c>
       <c r="K87" t="n">
-        <v>1737989</v>
+        <v>2761928</v>
       </c>
       <c r="L87" t="n">
-        <v>8750</v>
+        <v>6325</v>
       </c>
       <c r="M87" t="n">
-        <v>7065</v>
+        <v>4855</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -15494,52 +15494,52 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>70545</v>
+        <v>263098</v>
       </c>
       <c r="P87" t="n">
-        <v>295418</v>
+        <v>-113477</v>
       </c>
       <c r="Q87" t="n">
-        <v>425950</v>
+        <v>-255029</v>
       </c>
       <c r="R87" t="n">
-        <v>1200037</v>
+        <v>-1626147</v>
       </c>
       <c r="S87" t="n">
-        <v>32133</v>
+        <v>162970</v>
       </c>
       <c r="T87" t="n">
-        <v>28710</v>
+        <v>-182721</v>
       </c>
       <c r="U87" t="n">
-        <v>36848</v>
+        <v>30323</v>
       </c>
       <c r="V87" t="n">
-        <v>584120</v>
+        <v>-1988857</v>
       </c>
       <c r="W87" t="n">
-        <v>39000</v>
+        <v>36400</v>
       </c>
       <c r="X87" t="n">
-        <v>315807</v>
+        <v>243960</v>
       </c>
       <c r="Y87" t="n">
-        <v>555115</v>
+        <v>73616</v>
       </c>
       <c r="Z87" t="n">
-        <v>833814</v>
+        <v>540262</v>
       </c>
       <c r="AA87" t="n">
-        <v>-588</v>
+        <v>63728</v>
       </c>
       <c r="AB87" t="n">
-        <v>-49099</v>
+        <v>-174716</v>
       </c>
       <c r="AC87" t="n">
-        <v>-166013</v>
+        <v>-358968</v>
       </c>
       <c r="AD87" t="n">
-        <v>-217897</v>
+        <v>-177552</v>
       </c>
       <c r="AE87" t="n">
         <v>10</v>
@@ -15548,16 +15548,16 @@
         <v>10</v>
       </c>
       <c r="AG87" t="n">
-        <v>-45</v>
+        <v>25</v>
       </c>
       <c r="AH87" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
       </c>
       <c r="AJ87" t="n">
-        <v>34</v>
+        <v>-34</v>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
@@ -15565,25 +15565,25 @@
         </is>
       </c>
       <c r="AL87" t="n">
-        <v>-24</v>
+        <v>44</v>
       </c>
       <c r="AM87" t="n">
-        <v>-70.59</v>
+        <v>129.41</v>
       </c>
       <c r="AN87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -15598,29 +15598,29 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
+          <t>5日法人賣超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏買、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、成交量放大、接近20日低點、5日法人賣超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3702.TW</t>
+          <t>2707.TW</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -15639,28 +15639,28 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>114.5</v>
+        <v>176</v>
       </c>
       <c r="G88" t="n">
-        <v>114.8</v>
+        <v>176.9</v>
       </c>
       <c r="H88" t="n">
-        <v>115.9</v>
+        <v>176.85</v>
       </c>
       <c r="I88" t="n">
-        <v>116.42</v>
+        <v>176.3</v>
       </c>
       <c r="J88" t="n">
-        <v>8371199</v>
+        <v>119906</v>
       </c>
       <c r="K88" t="n">
-        <v>9376851</v>
+        <v>104019</v>
       </c>
       <c r="L88" t="n">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="M88" t="n">
-        <v>111.5</v>
+        <v>174.5</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -15668,70 +15668,70 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>956731</v>
+        <v>53170</v>
       </c>
       <c r="P88" t="n">
-        <v>5234216</v>
+        <v>-12819</v>
       </c>
       <c r="Q88" t="n">
-        <v>5848199</v>
+        <v>40622</v>
       </c>
       <c r="R88" t="n">
-        <v>22107911</v>
+        <v>422102</v>
       </c>
       <c r="S88" t="n">
-        <v>314154</v>
+        <v>53170</v>
       </c>
       <c r="T88" t="n">
-        <v>3451507</v>
+        <v>-8803</v>
       </c>
       <c r="U88" t="n">
-        <v>2157216</v>
+        <v>45737</v>
       </c>
       <c r="V88" t="n">
-        <v>16036507</v>
+        <v>427404</v>
       </c>
       <c r="W88" t="n">
-        <v>230000</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>661924</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2235964</v>
+        <v>-2000</v>
       </c>
       <c r="Z88" t="n">
-        <v>2840757</v>
+        <v>-2000</v>
       </c>
       <c r="AA88" t="n">
-        <v>412577</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1120785</v>
+        <v>-4016</v>
       </c>
       <c r="AC88" t="n">
-        <v>1455019</v>
+        <v>-3115</v>
       </c>
       <c r="AD88" t="n">
-        <v>3230647</v>
+        <v>-3302</v>
       </c>
       <c r="AE88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG88" t="n">
-        <v>-55</v>
+        <v>20</v>
       </c>
       <c r="AH88" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
@@ -15739,10 +15739,10 @@
         </is>
       </c>
       <c r="AL88" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="AM88" t="n">
-        <v>-58.33</v>
+        <v>-33.33</v>
       </c>
       <c r="AN88" t="n">
         <v>0</v>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
@@ -15772,17 +15772,17 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>籌碼中性、外資買投信賣</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點、籌碼中性、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -15963,12 +15963,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2707.TW</t>
+          <t>2617.TW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>晶華</t>
+          <t>台航</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -15987,28 +15987,28 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>176</v>
+        <v>31.5</v>
       </c>
       <c r="G90" t="n">
-        <v>176.9</v>
+        <v>31.62</v>
       </c>
       <c r="H90" t="n">
-        <v>176.85</v>
+        <v>32.04</v>
       </c>
       <c r="I90" t="n">
-        <v>176.3</v>
+        <v>32.05</v>
       </c>
       <c r="J90" t="n">
-        <v>119906</v>
+        <v>574473</v>
       </c>
       <c r="K90" t="n">
-        <v>104019</v>
+        <v>754683</v>
       </c>
       <c r="L90" t="n">
-        <v>179</v>
+        <v>33.35</v>
       </c>
       <c r="M90" t="n">
-        <v>174.5</v>
+        <v>30.85</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -16016,70 +16016,70 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>53170</v>
+        <v>274052</v>
       </c>
       <c r="P90" t="n">
-        <v>-12819</v>
+        <v>39106</v>
       </c>
       <c r="Q90" t="n">
-        <v>40622</v>
+        <v>206663</v>
       </c>
       <c r="R90" t="n">
-        <v>422102</v>
+        <v>1970931</v>
       </c>
       <c r="S90" t="n">
-        <v>53170</v>
+        <v>278410</v>
       </c>
       <c r="T90" t="n">
-        <v>-8803</v>
+        <v>-141839</v>
       </c>
       <c r="U90" t="n">
-        <v>45737</v>
+        <v>71488</v>
       </c>
       <c r="V90" t="n">
-        <v>427404</v>
+        <v>1826058</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>286000</v>
       </c>
       <c r="Y90" t="n">
-        <v>-2000</v>
+        <v>288000</v>
       </c>
       <c r="Z90" t="n">
-        <v>-2000</v>
+        <v>288000</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>-17358</v>
       </c>
       <c r="AB90" t="n">
-        <v>-4016</v>
+        <v>-105055</v>
       </c>
       <c r="AC90" t="n">
-        <v>-3115</v>
+        <v>-152825</v>
       </c>
       <c r="AD90" t="n">
-        <v>-3302</v>
+        <v>-143127</v>
       </c>
       <c r="AE90" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF90" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG90" t="n">
-        <v>20</v>
+        <v>-55</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
       </c>
       <c r="AJ90" t="n">
-        <v>12</v>
+        <v>-18</v>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
@@ -16087,16 +16087,16 @@
         </is>
       </c>
       <c r="AL90" t="n">
-        <v>-4</v>
+        <v>24</v>
       </c>
       <c r="AM90" t="n">
-        <v>-33.33</v>
+        <v>133.33</v>
       </c>
       <c r="AN90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
@@ -16120,29 +16120,29 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>籌碼中性、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點、籌碼中性、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2617.TW</t>
+          <t>2395.TW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>台航</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16161,28 +16161,28 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>31.5</v>
+        <v>670</v>
       </c>
       <c r="G91" t="n">
-        <v>31.62</v>
+        <v>680.2</v>
       </c>
       <c r="H91" t="n">
-        <v>32.04</v>
+        <v>697.9</v>
       </c>
       <c r="I91" t="n">
-        <v>32.05</v>
+        <v>710.55</v>
       </c>
       <c r="J91" t="n">
-        <v>574473</v>
+        <v>1662824</v>
       </c>
       <c r="K91" t="n">
-        <v>754683</v>
+        <v>2018295</v>
       </c>
       <c r="L91" t="n">
-        <v>33.35</v>
+        <v>754</v>
       </c>
       <c r="M91" t="n">
-        <v>30.85</v>
+        <v>658</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -16190,52 +16190,52 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>274052</v>
+        <v>172429</v>
       </c>
       <c r="P91" t="n">
-        <v>39106</v>
+        <v>147470</v>
       </c>
       <c r="Q91" t="n">
-        <v>206663</v>
+        <v>290485</v>
       </c>
       <c r="R91" t="n">
-        <v>1970931</v>
+        <v>43858</v>
       </c>
       <c r="S91" t="n">
-        <v>278410</v>
+        <v>155020</v>
       </c>
       <c r="T91" t="n">
-        <v>-141839</v>
+        <v>61373</v>
       </c>
       <c r="U91" t="n">
-        <v>71488</v>
+        <v>273675</v>
       </c>
       <c r="V91" t="n">
-        <v>1826058</v>
+        <v>99727</v>
       </c>
       <c r="W91" t="n">
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="X91" t="n">
-        <v>286000</v>
+        <v>94847</v>
       </c>
       <c r="Y91" t="n">
-        <v>288000</v>
+        <v>16014</v>
       </c>
       <c r="Z91" t="n">
-        <v>288000</v>
+        <v>-207639</v>
       </c>
       <c r="AA91" t="n">
-        <v>-17358</v>
+        <v>5409</v>
       </c>
       <c r="AB91" t="n">
-        <v>-105055</v>
+        <v>-8750</v>
       </c>
       <c r="AC91" t="n">
-        <v>-152825</v>
+        <v>796</v>
       </c>
       <c r="AD91" t="n">
-        <v>-143127</v>
+        <v>151770</v>
       </c>
       <c r="AE91" t="n">
         <v>6</v>
@@ -16253,7 +16253,7 @@
         <v>0</v>
       </c>
       <c r="AJ91" t="n">
-        <v>-18</v>
+        <v>-24</v>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
@@ -16261,16 +16261,16 @@
         </is>
       </c>
       <c r="AL91" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AM91" t="n">
-        <v>133.33</v>
+        <v>125</v>
       </c>
       <c r="AN91" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO91" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
@@ -16311,12 +16311,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -16335,28 +16335,28 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>45.25</v>
+        <v>986</v>
       </c>
       <c r="G92" t="n">
-        <v>45.87</v>
+        <v>984.6</v>
       </c>
       <c r="H92" t="n">
-        <v>45.92</v>
+        <v>1012.7</v>
       </c>
       <c r="I92" t="n">
-        <v>46.75</v>
+        <v>1007.7</v>
       </c>
       <c r="J92" t="n">
-        <v>2943858</v>
+        <v>19629047</v>
       </c>
       <c r="K92" t="n">
-        <v>2760495</v>
+        <v>16218162</v>
       </c>
       <c r="L92" t="n">
-        <v>50.3</v>
+        <v>1150</v>
       </c>
       <c r="M92" t="n">
-        <v>44.5</v>
+        <v>875</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -16364,52 +16364,52 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>159089</v>
+        <v>1166340</v>
       </c>
       <c r="P92" t="n">
-        <v>1032491</v>
+        <v>426671</v>
       </c>
       <c r="Q92" t="n">
-        <v>1148988</v>
+        <v>-1116569</v>
       </c>
       <c r="R92" t="n">
-        <v>1225279</v>
+        <v>-1986465</v>
       </c>
       <c r="S92" t="n">
-        <v>197516</v>
+        <v>45572</v>
       </c>
       <c r="T92" t="n">
-        <v>781582</v>
+        <v>-1352820</v>
       </c>
       <c r="U92" t="n">
-        <v>751396</v>
+        <v>-4691801</v>
       </c>
       <c r="V92" t="n">
-        <v>973610</v>
+        <v>-7114090</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1073000</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>2095872</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>4584241</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>6447518</v>
       </c>
       <c r="AA92" t="n">
-        <v>-38427</v>
+        <v>47768</v>
       </c>
       <c r="AB92" t="n">
-        <v>250909</v>
+        <v>-316381</v>
       </c>
       <c r="AC92" t="n">
-        <v>397592</v>
+        <v>-1009009</v>
       </c>
       <c r="AD92" t="n">
-        <v>251669</v>
+        <v>-1319893</v>
       </c>
       <c r="AE92" t="n">
         <v>6</v>
@@ -16418,16 +16418,16 @@
         <v>6</v>
       </c>
       <c r="AG92" t="n">
-        <v>-45</v>
+        <v>30</v>
       </c>
       <c r="AH92" t="n">
-        <v>60</v>
+        <v>-15</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
       </c>
       <c r="AJ92" t="n">
-        <v>18</v>
+        <v>-10</v>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
@@ -16435,25 +16435,25 @@
         </is>
       </c>
       <c r="AL92" t="n">
-        <v>-12</v>
+        <v>16</v>
       </c>
       <c r="AM92" t="n">
-        <v>-66.6